--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\cardclient\Config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cardclient\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25380" windowHeight="15840"/>
+    <workbookView windowWidth="12645" windowHeight="9090"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>##var</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>##</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>描述</t>
@@ -60,44 +66,18 @@
   <si>
     <t>珍贵而又精美的钻石,可以用来购买日常所需材料</t>
   </si>
-  <si>
-    <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Currency</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,29 +86,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -136,34 +432,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -212,7 +791,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -247,7 +826,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -450,95 +1029,80 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="45.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="34.75" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="45.375" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="5" customFormat="1" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1"/>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" customFormat="1" spans="1:5">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12645" windowHeight="9090"/>
+    <workbookView windowWidth="15690" windowHeight="14160"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="115">
   <si>
     <t>##var</t>
   </si>
@@ -40,6 +40,27 @@
     <t>Id</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>RefreshProbability</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>SellingPrice</t>
+  </si>
+  <si>
+    <t>MechanismId</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -49,22 +70,313 @@
     <t>int</t>
   </si>
   <si>
+    <t>QualityType</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>出现概率</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+  <si>
+    <t>出售价格</t>
+  </si>
+  <si>
+    <t>机制ID</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
-    <t>1010001</t>
-  </si>
-  <si>
-    <t>卡德大陆的常用货币,可以用来购买日常所需材料</t>
-  </si>
-  <si>
-    <t>1010002</t>
-  </si>
-  <si>
-    <t>珍贵而又精美的钻石,可以用来购买日常所需材料</t>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Ordinary</t>
+  </si>
+  <si>
+    <t>粗制长剑</t>
+  </si>
+  <si>
+    <t>结算时倍率+1</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>青铜项链</t>
+  </si>
+  <si>
+    <t>结算时方片花色牌可使倍率+1</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>青铜手镯</t>
+  </si>
+  <si>
+    <t>结算时黑桃花色牌可使倍率+1</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>青铜耳环</t>
+  </si>
+  <si>
+    <t>结算时红心花色牌可使倍率+1</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>青铜戒指</t>
+  </si>
+  <si>
+    <t>结算时梅花花色牌可使倍率+1</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>木制长剑</t>
+  </si>
+  <si>
+    <t>对子在攻击时提供的倍率+1</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>青铜法杖</t>
+  </si>
+  <si>
+    <t>同花在攻击时提供的倍率+1</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>铁质长剑</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10008</t>
+  </si>
+  <si>
+    <t>对子在攻击时提供的倍率+2</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>白银法杖</t>
+  </si>
+  <si>
+    <t>10009</t>
+  </si>
+  <si>
+    <t>同花在攻击时提供的倍率+2</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>翡翠诗篇</t>
+  </si>
+  <si>
+    <t>10010</t>
+  </si>
+  <si>
+    <t>顺子在攻击时提供的倍率+2</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>白银项链</t>
+  </si>
+  <si>
+    <t>10011</t>
+  </si>
+  <si>
+    <t>结算时方片花色牌可使倍率+2</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>白银手镯</t>
+  </si>
+  <si>
+    <t>10012</t>
+  </si>
+  <si>
+    <t>结算时黑桃花色牌可使倍率+2</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>白银耳环</t>
+  </si>
+  <si>
+    <t>10013</t>
+  </si>
+  <si>
+    <t>结算时红心花色牌可使倍率+2</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>白银戒指</t>
+  </si>
+  <si>
+    <t>10014</t>
+  </si>
+  <si>
+    <t>结算时梅花花色牌可使倍率+2</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>小精灵</t>
+  </si>
+  <si>
+    <t>10015|10016</t>
+  </si>
+  <si>
+    <t>立即获得300生命值,每次结算生命值+20</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>翡翠长剑</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>10017</t>
+  </si>
+  <si>
+    <t>对子在攻击时提供的倍率+3</t>
+  </si>
+  <si>
+    <t>黄金法杖</t>
+  </si>
+  <si>
+    <t>10018</t>
+  </si>
+  <si>
+    <t>同花在攻击时提供的倍率+3</t>
+  </si>
+  <si>
+    <t>黄金头冠</t>
+  </si>
+  <si>
+    <t>10019</t>
+  </si>
+  <si>
+    <t>同花顺在攻击时提供的倍率+6</t>
+  </si>
+  <si>
+    <t>黄金诗篇</t>
+  </si>
+  <si>
+    <t>10020</t>
+  </si>
+  <si>
+    <t>顺子在攻击时提供的倍率+3</t>
+  </si>
+  <si>
+    <t>疯狂面具</t>
+  </si>
+  <si>
+    <t>10021</t>
+  </si>
+  <si>
+    <t>每次攻击时,可获得1%的生命窃取</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>钻石头冠</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>10022</t>
+  </si>
+  <si>
+    <t>同花顺在攻击时提供的倍率+12</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>国王权杖</t>
+  </si>
+  <si>
+    <t>10023</t>
+  </si>
+  <si>
+    <t>豹子在攻击时提供的倍率+50</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>10024</t>
+  </si>
+  <si>
+    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>奢华沙发</t>
+  </si>
+  <si>
+    <t>10025</t>
+  </si>
+  <si>
+    <t>立即获得5000生命值</t>
   </si>
 </sst>
 </file>
@@ -680,11 +992,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1035,17 +1353,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="45.375" customWidth="1"/>
-    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.4083333333333" customWidth="1"/>
+    <col min="4" max="4" width="18.475" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.8" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.04166666666667" customWidth="1"/>
+    <col min="7" max="7" width="5.975" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.825" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.8416666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="26.1916666666667" customWidth="1"/>
+    <col min="11" max="11" width="11.875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1055,50 +1381,739 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:5">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:12">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:5">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10</v>
+      </c>
+      <c r="H5" s="2">
+        <v>5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>10001</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2">
         <v>10</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10002</v>
+      </c>
+      <c r="J6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2">
+        <v>5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>10003</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="2">
+        <v>10</v>
+      </c>
+      <c r="H8" s="2">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>10004</v>
+      </c>
+      <c r="J8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="I9" s="2">
+        <v>10005</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2">
+        <v>5</v>
+      </c>
+      <c r="I10" s="2">
+        <v>10006</v>
+      </c>
+      <c r="J10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5</v>
+      </c>
+      <c r="I11" s="2">
+        <v>10007</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15"/>
+      <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16"/>
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17"/>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18"/>
+      <c r="B18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19"/>
+      <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20"/>
+      <c r="B20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21"/>
+      <c r="B21" s="2"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22"/>
+      <c r="B22" s="2">
+        <v>301</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23"/>
+      <c r="B23" s="2">
+        <v>302</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24"/>
+      <c r="B24" s="2">
+        <v>303</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25"/>
+      <c r="B25" s="2">
+        <v>304</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26"/>
+      <c r="B26" s="2">
+        <v>305</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="B28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="B29" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="B30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E30" s="2">
+        <v>235</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="B31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J31" t="s">
+        <v>114</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15690" windowHeight="14160"/>
+    <workbookView windowWidth="18270" windowHeight="13050"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -992,14 +992,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1362,9 +1359,9 @@
     <col min="4" max="4" width="18.475" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.8" style="2" customWidth="1"/>
     <col min="6" max="6" width="8.04166666666667" customWidth="1"/>
-    <col min="7" max="7" width="5.975" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.825" style="3" customWidth="1"/>
-    <col min="9" max="9" width="11.8416666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.975" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.825" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.8416666666667" style="2" customWidth="1"/>
     <col min="10" max="10" width="26.1916666666667" customWidth="1"/>
     <col min="11" max="11" width="11.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
@@ -1390,13 +1387,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1422,13 +1419,13 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J2" t="s">
@@ -1454,13 +1451,13 @@
       <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J3" t="s">

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18270" windowHeight="13050"/>
+    <workbookView windowWidth="18270" windowHeight="14775"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
   <si>
     <t>##var</t>
   </si>
@@ -115,6 +115,9 @@
     <t>粗制长剑</t>
   </si>
   <si>
+    <t>Sword1</t>
+  </si>
+  <si>
     <t>结算时倍率+1</t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t>青铜项链</t>
   </si>
   <si>
+    <t>Necklace1</t>
+  </si>
+  <si>
     <t>结算时方片花色牌可使倍率+1</t>
   </si>
   <si>
@@ -359,6 +365,9 @@
   </si>
   <si>
     <t>403</t>
+  </si>
+  <si>
+    <t>TwoThreeFive</t>
   </si>
   <si>
     <t>10024</t>
@@ -1358,7 +1367,7 @@
     <col min="3" max="3" width="11.4083333333333" customWidth="1"/>
     <col min="4" max="4" width="18.475" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.8" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.04166666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.9333333333333" customWidth="1"/>
     <col min="7" max="7" width="5.975" style="2" customWidth="1"/>
     <col min="8" max="8" width="12.825" style="2" customWidth="1"/>
     <col min="9" max="9" width="11.8416666666667" style="2" customWidth="1"/>
@@ -1478,6 +1487,9 @@
       <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
       <c r="G5" s="2">
         <v>10</v>
       </c>
@@ -1488,7 +1500,7 @@
         <v>10001</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1496,7 +1508,7 @@
     <row r="6" customFormat="1" spans="1:12">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>25</v>
@@ -1505,7 +1517,10 @@
         <v>0.6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
       </c>
       <c r="G6" s="2">
         <v>10</v>
@@ -1517,14 +1532,14 @@
         <v>10002</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>25</v>
@@ -1533,7 +1548,7 @@
         <v>0.6</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2">
         <v>10</v>
@@ -1545,12 +1560,12 @@
         <v>10003</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>25</v>
@@ -1559,7 +1574,7 @@
         <v>0.6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" s="2">
         <v>10</v>
@@ -1571,12 +1586,12 @@
         <v>10004</v>
       </c>
       <c r="J8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
@@ -1585,7 +1600,7 @@
         <v>0.6</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" s="2">
         <v>10</v>
@@ -1597,12 +1612,12 @@
         <v>10005</v>
       </c>
       <c r="J9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>25</v>
@@ -1611,7 +1626,7 @@
         <v>0.6</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G10" s="2">
         <v>10</v>
@@ -1623,12 +1638,12 @@
         <v>10006</v>
       </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
@@ -1637,7 +1652,7 @@
         <v>0.6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G11" s="2">
         <v>10</v>
@@ -1649,221 +1664,221 @@
         <v>10007</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="2">
         <v>0.4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2">
         <v>0.4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15"/>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D15" s="2">
         <v>0.4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16"/>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" s="2">
         <v>0.4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17"/>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D17" s="2">
         <v>0.4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18"/>
       <c r="B18" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D18" s="2">
         <v>0.4</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19"/>
       <c r="B19" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2">
         <v>0.4</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20"/>
       <c r="B20" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2">
         <v>0.4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1879,25 +1894,25 @@
         <v>301</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D22" s="2">
         <v>0.2</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1906,25 +1921,25 @@
         <v>302</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D23" s="2">
         <v>0.2</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1933,25 +1948,25 @@
         <v>303</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D24" s="2">
         <v>0.2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1960,25 +1975,25 @@
         <v>304</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D25" s="2">
         <v>0.2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1987,85 +2002,85 @@
         <v>305</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D26" s="2">
         <v>0.2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="B28" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D28" s="2">
         <v>0.1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="B29" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D29" s="2">
         <v>0.1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J29" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="B30" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D30" s="2">
         <v>0.1</v>
@@ -2073,43 +2088,46 @@
       <c r="E30" s="2">
         <v>235</v>
       </c>
+      <c r="F30" t="s">
+        <v>111</v>
+      </c>
       <c r="G30" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="B31" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D31" s="2">
         <v>0.1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="139">
   <si>
     <t>##var</t>
   </si>
@@ -139,6 +139,9 @@
     <t>青铜手镯</t>
   </si>
   <si>
+    <t>Bracelet1</t>
+  </si>
+  <si>
     <t>结算时黑桃花色牌可使倍率+1</t>
   </si>
   <si>
@@ -148,6 +151,9 @@
     <t>青铜耳环</t>
   </si>
   <si>
+    <t>Earrings1</t>
+  </si>
+  <si>
     <t>结算时红心花色牌可使倍率+1</t>
   </si>
   <si>
@@ -157,6 +163,9 @@
     <t>青铜戒指</t>
   </si>
   <si>
+    <t>Ring1</t>
+  </si>
+  <si>
     <t>结算时梅花花色牌可使倍率+1</t>
   </si>
   <si>
@@ -166,6 +175,9 @@
     <t>木制长剑</t>
   </si>
   <si>
+    <t>Sword2</t>
+  </si>
+  <si>
     <t>对子在攻击时提供的倍率+1</t>
   </si>
   <si>
@@ -175,6 +187,9 @@
     <t>青铜法杖</t>
   </si>
   <si>
+    <t>Staff1</t>
+  </si>
+  <si>
     <t>同花在攻击时提供的倍率+1</t>
   </si>
   <si>
@@ -187,6 +202,9 @@
     <t>铁质长剑</t>
   </si>
   <si>
+    <t>Sword3</t>
+  </si>
+  <si>
     <t>20</t>
   </si>
   <si>
@@ -205,6 +223,9 @@
     <t>白银法杖</t>
   </si>
   <si>
+    <t>Staff2</t>
+  </si>
+  <si>
     <t>10009</t>
   </si>
   <si>
@@ -217,6 +238,9 @@
     <t>翡翠诗篇</t>
   </si>
   <si>
+    <t>Poetry1</t>
+  </si>
+  <si>
     <t>10010</t>
   </si>
   <si>
@@ -229,6 +253,9 @@
     <t>白银项链</t>
   </si>
   <si>
+    <t>Necklace2</t>
+  </si>
+  <si>
     <t>10011</t>
   </si>
   <si>
@@ -241,6 +268,9 @@
     <t>白银手镯</t>
   </si>
   <si>
+    <t>Bracelet2</t>
+  </si>
+  <si>
     <t>10012</t>
   </si>
   <si>
@@ -253,6 +283,9 @@
     <t>白银耳环</t>
   </si>
   <si>
+    <t>Earrings2</t>
+  </si>
+  <si>
     <t>10013</t>
   </si>
   <si>
@@ -265,6 +298,9 @@
     <t>白银戒指</t>
   </si>
   <si>
+    <t>Ring2</t>
+  </si>
+  <si>
     <t>10014</t>
   </si>
   <si>
@@ -277,6 +313,9 @@
     <t>小精灵</t>
   </si>
   <si>
+    <t>Elf</t>
+  </si>
+  <si>
     <t>10015|10016</t>
   </si>
   <si>
@@ -289,6 +328,9 @@
     <t>翡翠长剑</t>
   </si>
   <si>
+    <t>Sword4</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
@@ -301,6 +343,9 @@
     <t>黄金法杖</t>
   </si>
   <si>
+    <t>Staff3</t>
+  </si>
+  <si>
     <t>10018</t>
   </si>
   <si>
@@ -310,6 +355,9 @@
     <t>黄金头冠</t>
   </si>
   <si>
+    <t>Crown1</t>
+  </si>
+  <si>
     <t>10019</t>
   </si>
   <si>
@@ -319,6 +367,9 @@
     <t>黄金诗篇</t>
   </si>
   <si>
+    <t>Poetry2</t>
+  </si>
+  <si>
     <t>10020</t>
   </si>
   <si>
@@ -328,6 +379,9 @@
     <t>疯狂面具</t>
   </si>
   <si>
+    <t>CrazyMask</t>
+  </si>
+  <si>
     <t>10021</t>
   </si>
   <si>
@@ -343,6 +397,9 @@
     <t>钻石头冠</t>
   </si>
   <si>
+    <t>Crown2</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
@@ -358,6 +415,9 @@
     <t>国王权杖</t>
   </si>
   <si>
+    <t>Staff4</t>
+  </si>
+  <si>
     <t>10023</t>
   </si>
   <si>
@@ -382,10 +442,13 @@
     <t>奢华沙发</t>
   </si>
   <si>
+    <t>LuxurySofa</t>
+  </si>
+  <si>
     <t>10025</t>
   </si>
   <si>
-    <t>立即获得5000生命值</t>
+    <t>立即获得2000生命值</t>
   </si>
 </sst>
 </file>
@@ -1550,6 +1613,9 @@
       <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
       <c r="G7" s="2">
         <v>10</v>
       </c>
@@ -1560,12 +1626,12 @@
         <v>10003</v>
       </c>
       <c r="J7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>25</v>
@@ -1574,7 +1640,10 @@
         <v>0.6</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
       </c>
       <c r="G8" s="2">
         <v>10</v>
@@ -1586,12 +1655,12 @@
         <v>10004</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>25</v>
@@ -1600,7 +1669,10 @@
         <v>0.6</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
       </c>
       <c r="G9" s="2">
         <v>10</v>
@@ -1612,12 +1684,12 @@
         <v>10005</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>25</v>
@@ -1626,7 +1698,10 @@
         <v>0.6</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
       </c>
       <c r="G10" s="2">
         <v>10</v>
@@ -1638,12 +1713,12 @@
         <v>10006</v>
       </c>
       <c r="J10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>25</v>
@@ -1652,7 +1727,10 @@
         <v>0.6</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
       </c>
       <c r="G11" s="2">
         <v>10</v>
@@ -1664,221 +1742,245 @@
         <v>10007</v>
       </c>
       <c r="J11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2">
         <v>0.4</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J13" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D14" s="2">
         <v>0.4</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15"/>
       <c r="B15" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2">
         <v>0.4</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="J15" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16"/>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D16" s="2">
         <v>0.4</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
+      </c>
+      <c r="F16" t="s">
+        <v>73</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17"/>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D17" s="2">
         <v>0.4</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>78</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18"/>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2">
         <v>0.4</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
+      </c>
+      <c r="F18" t="s">
+        <v>83</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="J18" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19"/>
       <c r="B19" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D19" s="2">
         <v>0.4</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
+      </c>
+      <c r="F19" t="s">
+        <v>88</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20"/>
       <c r="B20" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D20" s="2">
         <v>0.4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
+      </c>
+      <c r="F20" t="s">
+        <v>93</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J20" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1894,25 +1996,28 @@
         <v>301</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2">
         <v>0.2</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
+      </c>
+      <c r="F22" t="s">
+        <v>98</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="J22" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1921,25 +2026,28 @@
         <v>302</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2">
         <v>0.2</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
+        <v>103</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="J23" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1948,25 +2056,28 @@
         <v>303</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D24" s="2">
         <v>0.2</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>91</v>
+        <v>106</v>
+      </c>
+      <c r="F24" t="s">
+        <v>107</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1975,25 +2086,28 @@
         <v>304</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D25" s="2">
         <v>0.2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>94</v>
+        <v>110</v>
+      </c>
+      <c r="F25" t="s">
+        <v>111</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="J25" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2002,85 +2116,94 @@
         <v>305</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D26" s="2">
         <v>0.2</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
+      </c>
+      <c r="F26" t="s">
+        <v>115</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="J26" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="B28" s="1" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="D28" s="2">
         <v>0.1</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>102</v>
+        <v>120</v>
+      </c>
+      <c r="F28" t="s">
+        <v>121</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="J28" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="B29" s="1" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="D29" s="2">
         <v>0.1</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>107</v>
+        <v>126</v>
+      </c>
+      <c r="F29" t="s">
+        <v>127</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="J29" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="B30" s="1" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="D30" s="2">
         <v>0.1</v>
@@ -2089,45 +2212,48 @@
         <v>235</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="J30" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="B31" s="1" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="D31" s="2">
         <v>0.1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>115</v>
+        <v>135</v>
+      </c>
+      <c r="F31" t="s">
+        <v>136</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="J31" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18270" windowHeight="14775"/>
+    <workbookView windowWidth="12315" windowHeight="9165"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="240">
   <si>
     <t>##var</t>
   </si>
@@ -112,13 +112,13 @@
     <t>Ordinary</t>
   </si>
   <si>
-    <t>粗制长剑</t>
+    <t>冒险证明</t>
   </si>
   <si>
     <t>Sword1</t>
   </si>
   <si>
-    <t>结算时倍率+1</t>
+    <t>结算时提供+1倍率</t>
   </si>
   <si>
     <t>102</t>
@@ -130,7 +130,7 @@
     <t>Necklace1</t>
   </si>
   <si>
-    <t>结算时方片花色牌可使倍率+1</t>
+    <t>亮出的每张方片牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>103</t>
@@ -142,7 +142,7 @@
     <t>Bracelet1</t>
   </si>
   <si>
-    <t>结算时黑桃花色牌可使倍率+1</t>
+    <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>104</t>
@@ -154,7 +154,7 @@
     <t>Earrings1</t>
   </si>
   <si>
-    <t>结算时红心花色牌可使倍率+1</t>
+    <t>亮出的每张红心牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>105</t>
@@ -166,7 +166,7 @@
     <t>Ring1</t>
   </si>
   <si>
-    <t>结算时梅花花色牌可使倍率+1</t>
+    <t>亮出的每张梅花牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>106</t>
@@ -178,19 +178,55 @@
     <t>Sword2</t>
   </si>
   <si>
-    <t>对子在攻击时提供的倍率+1</t>
+    <t>亮出的对子牌型在结算时提供+2倍率</t>
   </si>
   <si>
     <t>107</t>
   </si>
   <si>
-    <t>青铜法杖</t>
+    <t>木制法杖</t>
   </si>
   <si>
     <t>Staff1</t>
   </si>
   <si>
-    <t>同花在攻击时提供的倍率+1</t>
+    <t>亮出的顺子牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>木制长弓</t>
+  </si>
+  <si>
+    <t>亮出的同花牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>木制长矛</t>
+  </si>
+  <si>
+    <t>亮出的同花顺牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>木制长斧</t>
+  </si>
+  <si>
+    <t>亮出的豹子牌型在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>木制圆盾</t>
+  </si>
+  <si>
+    <t>每次受到的伤害降低2点</t>
   </si>
   <si>
     <t>201</t>
@@ -199,10 +235,7 @@
     <t>Rare</t>
   </si>
   <si>
-    <t>铁质长剑</t>
-  </si>
-  <si>
-    <t>Sword3</t>
+    <t>白银项链</t>
   </si>
   <si>
     <t>20</t>
@@ -211,181 +244,337 @@
     <t>10</t>
   </si>
   <si>
-    <t>10008</t>
-  </si>
-  <si>
-    <t>对子在攻击时提供的倍率+2</t>
+    <t>20001</t>
+  </si>
+  <si>
+    <t>亮出的每张方片牌在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>202</t>
   </si>
   <si>
-    <t>白银法杖</t>
-  </si>
-  <si>
-    <t>Staff2</t>
-  </si>
-  <si>
-    <t>10009</t>
-  </si>
-  <si>
-    <t>同花在攻击时提供的倍率+2</t>
+    <t>白银手镯</t>
+  </si>
+  <si>
+    <t>20002</t>
+  </si>
+  <si>
+    <t>亮出的每张黑桃牌在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>203</t>
   </si>
   <si>
-    <t>翡翠诗篇</t>
-  </si>
-  <si>
-    <t>Poetry1</t>
-  </si>
-  <si>
-    <t>10010</t>
-  </si>
-  <si>
-    <t>顺子在攻击时提供的倍率+2</t>
+    <t>白银耳环</t>
+  </si>
+  <si>
+    <t>20003</t>
+  </si>
+  <si>
+    <t>亮出的每张红心牌在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>204</t>
   </si>
   <si>
-    <t>白银项链</t>
-  </si>
-  <si>
-    <t>Necklace2</t>
-  </si>
-  <si>
-    <t>10011</t>
-  </si>
-  <si>
-    <t>结算时方片花色牌可使倍率+2</t>
+    <t>白银戒指</t>
+  </si>
+  <si>
+    <t>20004</t>
+  </si>
+  <si>
+    <t>亮出的每张梅花牌在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>205</t>
   </si>
   <si>
-    <t>白银手镯</t>
-  </si>
-  <si>
-    <t>Bracelet2</t>
-  </si>
-  <si>
-    <t>10012</t>
-  </si>
-  <si>
-    <t>结算时黑桃花色牌可使倍率+2</t>
+    <t>铁制长剑</t>
+  </si>
+  <si>
+    <t>20005</t>
+  </si>
+  <si>
+    <t>亮出的对子牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>206</t>
   </si>
   <si>
-    <t>白银耳环</t>
-  </si>
-  <si>
-    <t>Earrings2</t>
-  </si>
-  <si>
-    <t>10013</t>
-  </si>
-  <si>
-    <t>结算时红心花色牌可使倍率+2</t>
+    <t>铁制法杖</t>
+  </si>
+  <si>
+    <t>20006</t>
+  </si>
+  <si>
+    <t>亮出的顺子牌型在结算时提供+4攻击力</t>
   </si>
   <si>
     <t>207</t>
   </si>
   <si>
-    <t>白银戒指</t>
-  </si>
-  <si>
-    <t>Ring2</t>
-  </si>
-  <si>
-    <t>10014</t>
-  </si>
-  <si>
-    <t>结算时梅花花色牌可使倍率+2</t>
+    <t>铁制长弓</t>
+  </si>
+  <si>
+    <t>20007</t>
+  </si>
+  <si>
+    <t>亮出的同花牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>208</t>
   </si>
   <si>
+    <t>铁制长矛</t>
+  </si>
+  <si>
+    <t>20008</t>
+  </si>
+  <si>
+    <t>亮出的同花顺牌型在结算时提供+8攻击力</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>铁制长斧</t>
+  </si>
+  <si>
+    <t>20009</t>
+  </si>
+  <si>
+    <t>亮出的豹子牌型在结算时提供+10攻击力</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
     <t>小精灵</t>
   </si>
   <si>
-    <t>Elf</t>
-  </si>
-  <si>
-    <t>10015|10016</t>
-  </si>
-  <si>
-    <t>立即获得300生命值,每次结算生命值+20</t>
+    <t>20010|200101</t>
+  </si>
+  <si>
+    <t>获得30点生命值上限,每回合结束后恢复2点当前生命值</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>白条</t>
+  </si>
+  <si>
+    <t>20011</t>
+  </si>
+  <si>
+    <t>可以负债,最多-20资金</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>旗帜</t>
+  </si>
+  <si>
+    <t>20012</t>
+  </si>
+  <si>
+    <t>在结算时,每剩余1个未使用的搓牌次数,都提供+1倍率</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>恐怖面具</t>
+  </si>
+  <si>
+    <t>20013</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+4攻击力</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>黄金面具</t>
+  </si>
+  <si>
+    <t>20014</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时有30%概率+1资金</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>黑白相机</t>
+  </si>
+  <si>
+    <t>20015</t>
+  </si>
+  <si>
+    <t>结算时,未亮出的牌里每有1张黑桃或梅花,提供+4倍率</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>丘比特</t>
+  </si>
+  <si>
+    <t>20016</t>
+  </si>
+  <si>
+    <t>结算时,未亮出的牌里每有1张方片或红心,提供+4倍率</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>投资</t>
+  </si>
+  <si>
+    <t>20017</t>
+  </si>
+  <si>
+    <t>每花费10资金,英雄+1基础攻击力</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>补偿金</t>
+  </si>
+  <si>
+    <t>20018</t>
+  </si>
+  <si>
+    <t>每次受到伤害时,+1资金</t>
   </si>
   <si>
     <t>Epic</t>
   </si>
   <si>
-    <t>翡翠长剑</t>
-  </si>
-  <si>
-    <t>Sword4</t>
+    <t>疯狂面具</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>10017</t>
-  </si>
-  <si>
-    <t>对子在攻击时提供的倍率+3</t>
-  </si>
-  <si>
-    <t>黄金法杖</t>
-  </si>
-  <si>
-    <t>Staff3</t>
-  </si>
-  <si>
-    <t>10018</t>
-  </si>
-  <si>
-    <t>同花在攻击时提供的倍率+3</t>
-  </si>
-  <si>
-    <t>黄金头冠</t>
-  </si>
-  <si>
-    <t>Crown1</t>
-  </si>
-  <si>
-    <t>10019</t>
-  </si>
-  <si>
-    <t>同花顺在攻击时提供的倍率+6</t>
-  </si>
-  <si>
-    <t>黄金诗篇</t>
-  </si>
-  <si>
-    <t>Poetry2</t>
-  </si>
-  <si>
-    <t>10020</t>
-  </si>
-  <si>
-    <t>顺子在攻击时提供的倍率+3</t>
-  </si>
-  <si>
-    <t>疯狂面具</t>
-  </si>
-  <si>
-    <t>CrazyMask</t>
-  </si>
-  <si>
-    <t>10021</t>
-  </si>
-  <si>
-    <t>每次攻击时,可获得1%的生命窃取</t>
+    <t>30001</t>
+  </si>
+  <si>
+    <t>造成伤害时,获得1%的生命窃取</t>
+  </si>
+  <si>
+    <t>回旋刃</t>
+  </si>
+  <si>
+    <t>30002</t>
+  </si>
+  <si>
+    <t>亮出的牌点数提供的攻击力加成翻倍</t>
+  </si>
+  <si>
+    <t>致胜之剑</t>
+  </si>
+  <si>
+    <t>30003</t>
+  </si>
+  <si>
+    <t>结算伤害时,会将留在手牌上最小的牌点数转化为额外攻击力</t>
+  </si>
+  <si>
+    <t>搓牌能手</t>
+  </si>
+  <si>
+    <t>30004</t>
+  </si>
+  <si>
+    <t>每回合内,每搓1次牌,结算时提供的倍率+1</t>
+  </si>
+  <si>
+    <t>会员卡</t>
+  </si>
+  <si>
+    <t>30005</t>
+  </si>
+  <si>
+    <t>每次进入商店提供1次免费刷新的机会</t>
+  </si>
+  <si>
+    <t>错峰出行</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t>顺子牌型可以相隔1点组成</t>
+  </si>
+  <si>
+    <t>致命黑八</t>
+  </si>
+  <si>
+    <t>30007</t>
+  </si>
+  <si>
+    <t>亮出的每张8在结算时提供+8攻击力</t>
+  </si>
+  <si>
+    <t>偶数韵律</t>
+  </si>
+  <si>
+    <t>30008</t>
+  </si>
+  <si>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+4倍率</t>
+  </si>
+  <si>
+    <t>奇数韵律</t>
+  </si>
+  <si>
+    <t>30009</t>
+  </si>
+  <si>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+4倍率</t>
+  </si>
+  <si>
+    <t>贵族</t>
+  </si>
+  <si>
+    <t>30010</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+6倍率</t>
+  </si>
+  <si>
+    <t>工资卡</t>
+  </si>
+  <si>
+    <t>30011</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,该收藏品的出售价格+1资金</t>
+  </si>
+  <si>
+    <t>训练</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久+1</t>
+  </si>
+  <si>
+    <t>九霄云外</t>
+  </si>
+  <si>
+    <t>30013</t>
+  </si>
+  <si>
+    <t>亮出的每张9在结算时提供2资金</t>
   </si>
   <si>
     <t>401</t>
@@ -394,61 +583,175 @@
     <t>Legend</t>
   </si>
   <si>
-    <t>钻石头冠</t>
-  </si>
-  <si>
-    <t>Crown2</t>
+    <t>TwoThreeFive</t>
   </si>
   <si>
     <t>80</t>
   </si>
   <si>
-    <t>10022</t>
-  </si>
-  <si>
-    <t>同花顺在攻击时提供的倍率+12</t>
+    <t>40001</t>
+  </si>
+  <si>
+    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
   </si>
   <si>
     <t>402</t>
   </si>
   <si>
-    <t>国王权杖</t>
-  </si>
-  <si>
-    <t>Staff4</t>
-  </si>
-  <si>
-    <t>10023</t>
-  </si>
-  <si>
-    <t>豹子在攻击时提供的倍率+50</t>
+    <t>奢华沙发</t>
+  </si>
+  <si>
+    <t>LuxurySofa</t>
+  </si>
+  <si>
+    <t>40002</t>
+  </si>
+  <si>
+    <t>获得500点生命值上限</t>
   </si>
   <si>
     <t>403</t>
   </si>
   <si>
-    <t>TwoThreeFive</t>
-  </si>
-  <si>
-    <t>10024</t>
-  </si>
-  <si>
-    <t>散排235牌型等同于豹子牌型,并且可以战胜所有牌型</t>
+    <t>老花眼</t>
+  </si>
+  <si>
+    <t>40003</t>
+  </si>
+  <si>
+    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
   </si>
   <si>
     <t>404</t>
   </si>
   <si>
-    <t>奢华沙发</t>
-  </si>
-  <si>
-    <t>LuxurySofa</t>
-  </si>
-  <si>
-    <t>10025</t>
-  </si>
-  <si>
-    <t>立即获得2000生命值</t>
+    <t>周星星</t>
+  </si>
+  <si>
+    <t>40004</t>
+  </si>
+  <si>
+    <t>每回合搓牌次数+1</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>穷途末路</t>
+  </si>
+  <si>
+    <t>40005</t>
+  </si>
+  <si>
+    <t>结算时,所有技能都无剩余使用次数,则提供+15倍率</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>收藏夹</t>
+  </si>
+  <si>
+    <t>40006</t>
+  </si>
+  <si>
+    <t>每有1个收藏品,结算时提供+5倍率</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>奢侈品</t>
+  </si>
+  <si>
+    <t>40007</t>
+  </si>
+  <si>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>近视眼</t>
+  </si>
+  <si>
+    <t>40008</t>
+  </si>
+  <si>
+    <t>所有牌均视为人头牌</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>顶尖学者</t>
+  </si>
+  <si>
+    <t>40009|400091</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算伤害时提供+6攻击力和+6倍率</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>老千</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>40011</t>
+  </si>
+  <si>
+    <t>亮牌时,有25%概率将该牌型提供的倍率永久+1</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>双刃剑</t>
+  </si>
+  <si>
+    <t>40012|400121</t>
+  </si>
+  <si>
+    <t>每回合失去2次搓牌机会,但结算时提供+20倍率</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>老搓家</t>
+  </si>
+  <si>
+    <t>40013</t>
+  </si>
+  <si>
+    <t>每使用1次搓牌,结算时该收藏品永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>幸运七</t>
+  </si>
+  <si>
+    <t>40014|400141|400142</t>
+  </si>
+  <si>
+    <t>亮出的每张7结算时有7%概率提供+77攻击力和+7倍率</t>
   </si>
 </sst>
 </file>
@@ -1422,18 +1725,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
+    <col min="1" max="1" width="5.21666666666667" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.4083333333333" customWidth="1"/>
-    <col min="4" max="4" width="18.475" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.8" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.8" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.9333333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" customWidth="1"/>
     <col min="7" max="7" width="5.975" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.825" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.8416666666667" style="2" customWidth="1"/>
+    <col min="8" max="8" width="4.78333333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="2" customWidth="1"/>
     <col min="10" max="10" width="26.1916666666667" customWidth="1"/>
     <col min="11" max="11" width="11.875" style="1" customWidth="1"/>
     <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
@@ -1745,515 +2048,1453 @@
         <v>52</v>
       </c>
     </row>
+    <row r="12" spans="1:12">
+      <c r="B12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10</v>
+      </c>
+      <c r="H12" s="2">
+        <v>5</v>
+      </c>
+      <c r="I12" s="2">
+        <v>10008</v>
+      </c>
+      <c r="J12" t="s">
+        <v>55</v>
+      </c>
+    </row>
     <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D13" s="2">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5</v>
+      </c>
+      <c r="I13" s="2">
+        <v>10009</v>
+      </c>
+      <c r="J13" t="s">
         <v>58</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="2">
+        <v>10</v>
+      </c>
+      <c r="H14" s="2">
+        <v>5</v>
+      </c>
+      <c r="I14" s="2">
+        <v>10010</v>
+      </c>
+      <c r="J14" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F14" t="s">
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15" s="2">
+        <v>10</v>
+      </c>
+      <c r="H15" s="2">
+        <v>5</v>
+      </c>
+      <c r="I15" s="2">
+        <v>10011</v>
+      </c>
+      <c r="J15" t="s">
         <v>64</v>
       </c>
-      <c r="J14" t="s">
+    </row>
+    <row r="17" spans="1:10">
+      <c r="B17" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15"/>
-      <c r="B15" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16"/>
-      <c r="B16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17"/>
-      <c r="B17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D17" s="2">
         <v>0.4</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>77</v>
+      <c r="E17" t="s">
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="J17" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18"/>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2">
         <v>0.4</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>82</v>
+      <c r="E18" t="s">
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19"/>
       <c r="B19" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2">
         <v>0.4</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>87</v>
+      <c r="E19" t="s">
+        <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J19" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20"/>
       <c r="B20" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D20" s="2">
         <v>0.4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21"/>
-      <c r="B21" s="2"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22"/>
-      <c r="B22" s="2">
-        <v>301</v>
+      <c r="B22" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D22" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J22" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23"/>
-      <c r="B23" s="2">
-        <v>302</v>
+      <c r="B23" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D23" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24"/>
-      <c r="B24" s="2">
-        <v>303</v>
+      <c r="B24" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D24" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J24" t="s">
         <v>99</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J24" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25"/>
-      <c r="B25" s="2">
-        <v>304</v>
+      <c r="B25" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="J25" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26"/>
-      <c r="B26" s="2">
+      <c r="B26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J26" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27"/>
+      <c r="B27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28"/>
+      <c r="B28" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J28" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29"/>
+      <c r="B29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30"/>
+      <c r="B30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F30" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31"/>
+      <c r="B31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32"/>
+      <c r="B32" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33"/>
+      <c r="B33" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J33" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34"/>
+      <c r="B34" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35"/>
+      <c r="B35" s="2"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36"/>
+      <c r="B36" s="2">
+        <v>301</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37"/>
+      <c r="B37" s="2">
+        <v>302</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38"/>
+      <c r="B38" s="2">
+        <v>303</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J38" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39"/>
+      <c r="B39" s="2">
+        <v>304</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>151</v>
+      </c>
+      <c r="F39" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J39" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40"/>
+      <c r="B40" s="2">
         <v>305</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="C40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="2">
         <v>0.2</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" t="s">
-        <v>115</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="B28" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="E40" t="s">
+        <v>154</v>
+      </c>
+      <c r="F40" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="B41" s="2">
+        <v>306</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="B42" s="2">
+        <v>307</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>160</v>
+      </c>
+      <c r="F42" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J42" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="B43" s="2">
+        <v>308</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E43" t="s">
+        <v>163</v>
+      </c>
+      <c r="F43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="J43" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="B44" s="2">
+        <v>309</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>166</v>
+      </c>
+      <c r="F44" t="s">
+        <v>51</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="B45" s="2">
+        <v>310</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E45" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="J45" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="B46" s="2">
+        <v>311</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" t="s">
+        <v>51</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="J46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="B47" s="2">
+        <v>312</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" t="s">
+        <v>51</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="J47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="B48" s="2">
+        <v>313</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="E48" t="s">
+        <v>178</v>
+      </c>
+      <c r="F48" t="s">
+        <v>51</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J48" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="B50" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D50" s="2">
         <v>0.1</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F28" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J28" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="B29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="E50" s="2">
+        <v>235</v>
+      </c>
+      <c r="F50" t="s">
+        <v>183</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D51" s="2">
         <v>0.1</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" t="s">
-        <v>127</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J29" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="B30" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="E51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F51" t="s">
+        <v>189</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J51" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" s="2">
         <v>0.1</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E52" t="s">
+        <v>193</v>
+      </c>
+      <c r="F52" t="s">
+        <v>51</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J52" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" t="s">
+        <v>51</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J53" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E54" t="s">
+        <v>201</v>
+      </c>
+      <c r="F54" t="s">
+        <v>51</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J54" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E55" t="s">
+        <v>205</v>
+      </c>
+      <c r="F55" t="s">
+        <v>51</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="J55" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>209</v>
+      </c>
+      <c r="F56" t="s">
+        <v>51</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J56" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E57" t="s">
+        <v>213</v>
+      </c>
+      <c r="F57" t="s">
+        <v>51</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J57" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="B58" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>217</v>
+      </c>
+      <c r="F58" t="s">
+        <v>51</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J58" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="B59" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E59" t="s">
+        <v>221</v>
+      </c>
+      <c r="F59" t="s">
+        <v>51</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J59" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
+      <c r="B60" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E60" t="s">
+        <v>225</v>
+      </c>
+      <c r="F60" t="s">
+        <v>51</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J60" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="B61" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D61" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>229</v>
+      </c>
+      <c r="F61" t="s">
+        <v>51</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J61" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10">
+      <c r="B62" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D62" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>233</v>
+      </c>
+      <c r="F62" t="s">
+        <v>51</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J62" t="s">
         <v>235</v>
       </c>
-      <c r="F30" t="s">
-        <v>131</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J30" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="B31" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" s="2">
+    </row>
+    <row r="63" spans="2:10">
+      <c r="B63" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D63" s="2">
         <v>0.1</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J31" t="s">
-        <v>138</v>
+      <c r="E63" t="s">
+        <v>237</v>
+      </c>
+      <c r="F63" t="s">
+        <v>51</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J63" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12315" windowHeight="9165"/>
+    <workbookView windowWidth="10875" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="260">
   <si>
     <t>##var</t>
   </si>
@@ -238,10 +238,7 @@
     <t>白银项链</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>55</t>
   </si>
   <si>
     <t>20001</t>
@@ -292,6 +289,12 @@
     <t>铁制长剑</t>
   </si>
   <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
     <t>20005</t>
   </si>
   <si>
@@ -304,6 +307,12 @@
     <t>铁制法杖</t>
   </si>
   <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
     <t>20006</t>
   </si>
   <si>
@@ -328,6 +337,12 @@
     <t>铁制长矛</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>20008</t>
   </si>
   <si>
@@ -352,6 +367,12 @@
     <t>小精灵</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
     <t>20010|200101</t>
   </si>
   <si>
@@ -364,6 +385,12 @@
     <t>白条</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
     <t>20011</t>
   </si>
   <si>
@@ -388,6 +415,12 @@
     <t>恐怖面具</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>20013</t>
   </si>
   <si>
@@ -460,7 +493,7 @@
     <t>疯狂面具</t>
   </si>
   <si>
-    <t>40</t>
+    <t>300</t>
   </si>
   <si>
     <t>30001</t>
@@ -472,6 +505,12 @@
     <t>回旋刃</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
     <t>30002</t>
   </si>
   <si>
@@ -481,6 +520,12 @@
     <t>致胜之剑</t>
   </si>
   <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
     <t>30003</t>
   </si>
   <si>
@@ -490,6 +535,9 @@
     <t>搓牌能手</t>
   </si>
   <si>
+    <t>280</t>
+  </si>
+  <si>
     <t>30004</t>
   </si>
   <si>
@@ -499,6 +547,12 @@
     <t>会员卡</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>30005</t>
   </si>
   <si>
@@ -562,6 +616,9 @@
     <t>训练</t>
   </si>
   <si>
+    <t>260</t>
+  </si>
+  <si>
     <t>30012</t>
   </si>
   <si>
@@ -571,6 +628,12 @@
     <t>九霄云外</t>
   </si>
   <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
     <t>30013</t>
   </si>
   <si>
@@ -584,9 +647,6 @@
   </si>
   <si>
     <t>TwoThreeFive</t>
-  </si>
-  <si>
-    <t>80</t>
   </si>
   <si>
     <t>40001</t>
@@ -1367,11 +1427,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1848,7 +1911,7 @@
         <v>25</v>
       </c>
       <c r="D5" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>26</v>
@@ -1857,10 +1920,10 @@
         <v>27</v>
       </c>
       <c r="G5" s="2">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I5" s="2">
         <v>10001</v>
@@ -1880,7 +1943,7 @@
         <v>25</v>
       </c>
       <c r="D6" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>30</v>
@@ -1889,10 +1952,10 @@
         <v>31</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I6" s="2">
         <v>10002</v>
@@ -1911,7 +1974,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>34</v>
@@ -1920,10 +1983,10 @@
         <v>35</v>
       </c>
       <c r="G7" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2">
         <v>10003</v>
@@ -1940,7 +2003,7 @@
         <v>25</v>
       </c>
       <c r="D8" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>38</v>
@@ -1949,10 +2012,10 @@
         <v>39</v>
       </c>
       <c r="G8" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2">
         <v>10004</v>
@@ -1969,7 +2032,7 @@
         <v>25</v>
       </c>
       <c r="D9" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>42</v>
@@ -1978,10 +2041,10 @@
         <v>43</v>
       </c>
       <c r="G9" s="2">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2">
         <v>10005</v>
@@ -1998,7 +2061,7 @@
         <v>25</v>
       </c>
       <c r="D10" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>46</v>
@@ -2007,10 +2070,10 @@
         <v>47</v>
       </c>
       <c r="G10" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I10" s="2">
         <v>10006</v>
@@ -2027,7 +2090,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>50</v>
@@ -2036,10 +2099,10 @@
         <v>51</v>
       </c>
       <c r="G11" s="2">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H11" s="2">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="I11" s="2">
         <v>10007</v>
@@ -2056,7 +2119,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>54</v>
@@ -2065,10 +2128,10 @@
         <v>51</v>
       </c>
       <c r="G12" s="2">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H12" s="2">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="I12" s="2">
         <v>10008</v>
@@ -2085,7 +2148,7 @@
         <v>25</v>
       </c>
       <c r="D13" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>57</v>
@@ -2094,10 +2157,10 @@
         <v>51</v>
       </c>
       <c r="G13" s="2">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H13" s="2">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I13" s="2">
         <v>10009</v>
@@ -2114,7 +2177,7 @@
         <v>25</v>
       </c>
       <c r="D14" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>60</v>
@@ -2123,10 +2186,10 @@
         <v>51</v>
       </c>
       <c r="G14" s="2">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="H14" s="2">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I14" s="2">
         <v>10010</v>
@@ -2143,7 +2206,7 @@
         <v>25</v>
       </c>
       <c r="D15" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>63</v>
@@ -2152,10 +2215,10 @@
         <v>51</v>
       </c>
       <c r="G15" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H15" s="2">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2">
         <v>10011</v>
@@ -2181,21 +2244,21 @@
         <v>51</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" t="s">
         <v>70</v>
-      </c>
-      <c r="J17" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="B18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>66</v>
@@ -2204,28 +2267,28 @@
         <v>0.4</v>
       </c>
       <c r="E18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" t="s">
         <v>74</v>
-      </c>
-      <c r="J18" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19"/>
       <c r="B19" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>66</v>
@@ -2234,28 +2297,28 @@
         <v>0.4</v>
       </c>
       <c r="E19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" t="s">
         <v>78</v>
-      </c>
-      <c r="J19" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20"/>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>66</v>
@@ -2264,28 +2327,28 @@
         <v>0.4</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" t="s">
         <v>82</v>
-      </c>
-      <c r="J20" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21"/>
       <c r="B21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>66</v>
@@ -2294,28 +2357,28 @@
         <v>0.4</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H21" s="1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22"/>
       <c r="B22" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>66</v>
@@ -2324,28 +2387,28 @@
         <v>0.4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F22" t="s">
         <v>51</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J22" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23"/>
       <c r="B23" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>66</v>
@@ -2354,28 +2417,28 @@
         <v>0.4</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
         <v>51</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J23" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24"/>
       <c r="B24" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>66</v>
@@ -2384,28 +2447,28 @@
         <v>0.4</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F24" t="s">
         <v>51</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25"/>
       <c r="B25" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>66</v>
@@ -2414,28 +2477,28 @@
         <v>0.4</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="H25" s="1" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J25" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26"/>
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>66</v>
@@ -2444,28 +2507,28 @@
         <v>0.4</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s">
         <v>51</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="J26" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27"/>
       <c r="B27" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>66</v>
@@ -2474,28 +2537,28 @@
         <v>0.4</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s">
         <v>51</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J27" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28"/>
       <c r="B28" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>66</v>
@@ -2504,28 +2567,28 @@
         <v>0.4</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s">
         <v>51</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="J28" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29"/>
       <c r="B29" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>66</v>
@@ -2534,28 +2597,28 @@
         <v>0.4</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s">
         <v>51</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="J29" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30"/>
       <c r="B30" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>66</v>
@@ -2564,28 +2627,28 @@
         <v>0.4</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s">
         <v>51</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="J30" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31"/>
       <c r="B31" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>66</v>
@@ -2594,28 +2657,28 @@
         <v>0.4</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s">
         <v>51</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="J31" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32"/>
       <c r="B32" s="1" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>66</v>
@@ -2624,28 +2687,28 @@
         <v>0.4</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F32" t="s">
         <v>51</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="J32" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33"/>
       <c r="B33" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>66</v>
@@ -2654,28 +2717,28 @@
         <v>0.4</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F33" t="s">
         <v>51</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="J33" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34"/>
       <c r="B34" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>66</v>
@@ -2684,22 +2747,22 @@
         <v>0.4</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F34" t="s">
         <v>51</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J34" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2715,28 +2778,28 @@
         <v>301</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D36" s="2">
         <v>0.2</v>
       </c>
       <c r="E36" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F36" t="s">
         <v>51</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="J36" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2745,28 +2808,28 @@
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D37" s="2">
         <v>0.2</v>
       </c>
       <c r="E37" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="F37" t="s">
         <v>51</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="J37" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2775,28 +2838,28 @@
         <v>303</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D38" s="2">
         <v>0.2</v>
       </c>
       <c r="E38" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F38" t="s">
         <v>51</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="J38" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2805,28 +2868,28 @@
         <v>304</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D39" s="2">
         <v>0.2</v>
       </c>
       <c r="E39" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F39" t="s">
         <v>51</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="J39" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2835,28 +2898,28 @@
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D40" s="2">
         <v>0.2</v>
       </c>
       <c r="E40" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F40" t="s">
         <v>51</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="J40" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2864,28 +2927,28 @@
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D41" s="2">
         <v>0.2</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="F41" t="s">
         <v>51</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="J41" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2893,28 +2956,28 @@
         <v>307</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D42" s="2">
         <v>0.2</v>
       </c>
       <c r="E42" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="F42" t="s">
         <v>51</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="J42" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2922,28 +2985,28 @@
         <v>308</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D43" s="2">
         <v>0.2</v>
       </c>
       <c r="E43" t="s">
+        <v>181</v>
+      </c>
+      <c r="F43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F43" t="s">
-        <v>51</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="I43" s="1" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="J43" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2951,28 +3014,28 @@
         <v>309</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D44" s="2">
         <v>0.2</v>
       </c>
       <c r="E44" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="F44" t="s">
         <v>51</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="J44" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2980,28 +3043,28 @@
         <v>310</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D45" s="2">
         <v>0.2</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="F45" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="J45" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -3009,28 +3072,28 @@
         <v>311</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D46" s="2">
         <v>0.2</v>
       </c>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="F46" t="s">
         <v>51</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="J46" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="1:10">
@@ -3038,28 +3101,28 @@
         <v>312</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D47" s="2">
         <v>0.2</v>
       </c>
       <c r="E47" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="F47" t="s">
         <v>51</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="J47" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:10">
@@ -3067,36 +3130,37 @@
         <v>313</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D48" s="2">
         <v>0.2</v>
       </c>
       <c r="E48" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="F48" t="s">
         <v>51</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="J48" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25"/>
+    <row r="50" ht="14.25" spans="2:10">
       <c r="B50" s="1" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D50" s="2">
         <v>0.1</v>
@@ -3105,396 +3169,396 @@
         <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>183</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>142</v>
+        <v>204</v>
+      </c>
+      <c r="G50" s="3">
+        <v>650</v>
+      </c>
+      <c r="H50" s="3">
+        <v>325</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="J50" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25" spans="2:10">
       <c r="B51" s="1" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D51" s="2">
         <v>0.1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="F51" t="s">
-        <v>189</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>142</v>
+        <v>209</v>
+      </c>
+      <c r="G51" s="3">
+        <v>600</v>
+      </c>
+      <c r="H51" s="3">
+        <v>300</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="J51" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25" spans="2:10">
       <c r="B52" s="1" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D52" s="2">
         <v>0.1</v>
       </c>
       <c r="E52" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="F52" t="s">
         <v>51</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>142</v>
+      <c r="G52" s="3">
+        <v>580</v>
+      </c>
+      <c r="H52" s="3">
+        <v>290</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="J52" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25" spans="2:10">
       <c r="B53" s="1" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D53" s="2">
         <v>0.1</v>
       </c>
       <c r="E53" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="F53" t="s">
         <v>51</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>142</v>
+      <c r="G53" s="3">
+        <v>530</v>
+      </c>
+      <c r="H53" s="3">
+        <v>265</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="J53" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25" spans="2:10">
       <c r="B54" s="1" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D54" s="2">
         <v>0.1</v>
       </c>
       <c r="E54" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="F54" t="s">
         <v>51</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>142</v>
+      <c r="G54" s="3">
+        <v>560</v>
+      </c>
+      <c r="H54" s="3">
+        <v>280</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="J54" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25" spans="2:10">
+      <c r="B55" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="D55" s="2">
         <v>0.1</v>
       </c>
       <c r="E55" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="F55" t="s">
         <v>51</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>142</v>
+      <c r="G55" s="3">
+        <v>620</v>
+      </c>
+      <c r="H55" s="3">
+        <v>310</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="J55" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25" spans="2:10">
       <c r="B56" s="1" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D56" s="2">
         <v>0.1</v>
       </c>
       <c r="E56" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="F56" t="s">
         <v>51</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>142</v>
+      <c r="G56" s="3">
+        <v>590</v>
+      </c>
+      <c r="H56" s="3">
+        <v>295</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="J56" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25" spans="2:10">
       <c r="B57" s="1" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D57" s="2">
         <v>0.1</v>
       </c>
       <c r="E57" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="F57" t="s">
         <v>51</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>142</v>
+      <c r="G57" s="3">
+        <v>640</v>
+      </c>
+      <c r="H57" s="3">
+        <v>320</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="J57" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25" spans="2:10">
       <c r="B58" s="1" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D58" s="2">
         <v>0.1</v>
       </c>
       <c r="E58" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="F58" t="s">
         <v>51</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>142</v>
+      <c r="G58" s="3">
+        <v>610</v>
+      </c>
+      <c r="H58" s="3">
+        <v>305</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="J58" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25" spans="2:10">
       <c r="B59" s="1" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D59" s="2">
         <v>0.1</v>
       </c>
       <c r="E59" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="F59" t="s">
         <v>51</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>142</v>
+      <c r="G59" s="3">
+        <v>580</v>
+      </c>
+      <c r="H59" s="3">
+        <v>290</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="J59" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25" spans="2:10">
       <c r="B60" s="1" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D60" s="2">
         <v>0.1</v>
       </c>
       <c r="E60" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="F60" t="s">
         <v>51</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>142</v>
+      <c r="G60" s="3">
+        <v>600</v>
+      </c>
+      <c r="H60" s="3">
+        <v>300</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="J60" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25" spans="2:10">
       <c r="B61" s="1" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D61" s="2">
         <v>0.1</v>
       </c>
       <c r="E61" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="F61" t="s">
         <v>51</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>142</v>
+      <c r="G61" s="3">
+        <v>550</v>
+      </c>
+      <c r="H61" s="3">
+        <v>275</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="J61" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25" spans="2:10">
       <c r="B62" s="1" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D62" s="2">
         <v>0.1</v>
       </c>
       <c r="E62" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="F62" t="s">
         <v>51</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>142</v>
+      <c r="G62" s="3">
+        <v>560</v>
+      </c>
+      <c r="H62" s="3">
+        <v>280</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="J62" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="63" ht="14.25" spans="2:10">
       <c r="B63" s="1" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="D63" s="2">
         <v>0.1</v>
       </c>
       <c r="E63" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="F63" t="s">
         <v>51</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>142</v>
+      <c r="G63" s="3">
+        <v>630</v>
+      </c>
+      <c r="H63" s="3">
+        <v>315</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="J63" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10875" windowHeight="9750"/>
+    <workbookView windowWidth="14190" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -226,7 +226,7 @@
     <t>木制圆盾</t>
   </si>
   <si>
-    <t>每次受到的伤害降低2点</t>
+    <t>每次受到的伤害降低1点</t>
   </si>
   <si>
     <t>201</t>
@@ -316,7 +316,7 @@
     <t>20006</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+4攻击力</t>
+    <t>亮出的顺子牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>207</t>
@@ -328,7 +328,7 @@
     <t>20007</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+6攻击力</t>
+    <t>亮出的同花牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>208</t>
@@ -346,7 +346,7 @@
     <t>20008</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+8攻击力</t>
+    <t>亮出的同花顺牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>209</t>
@@ -358,7 +358,7 @@
     <t>20009</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+10攻击力</t>
+    <t>亮出的豹子牌型在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>210</t>
@@ -394,7 +394,7 @@
     <t>20011</t>
   </si>
   <si>
-    <t>可以负债,最多-20资金</t>
+    <t>可以负债,最多-50金币</t>
   </si>
   <si>
     <t>212</t>
@@ -406,7 +406,7 @@
     <t>20012</t>
   </si>
   <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,都提供+1倍率</t>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+1倍率</t>
   </si>
   <si>
     <t>213</t>
@@ -424,7 +424,7 @@
     <t>20013</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+4攻击力</t>
+    <t>亮出的每张人头牌在结算时提供+2攻击力</t>
   </si>
   <si>
     <t>214</t>
@@ -436,7 +436,7 @@
     <t>20014</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时有30%概率+1资金</t>
+    <t>亮出的每张人头牌在结算时有20%概率+1金币</t>
   </si>
   <si>
     <t>215</t>
@@ -448,7 +448,7 @@
     <t>20015</t>
   </si>
   <si>
-    <t>结算时,未亮出的牌里每有1张黑桃或梅花,提供+4倍率</t>
+    <t>结算时,未亮出的牌里每有1张黑桃或梅花,提供+2倍率</t>
   </si>
   <si>
     <t>216</t>
@@ -460,7 +460,7 @@
     <t>20016</t>
   </si>
   <si>
-    <t>结算时,未亮出的牌里每有1张方片或红心,提供+4倍率</t>
+    <t>结算时,未亮出的牌里每有1张方片或红心,提供+2倍率</t>
   </si>
   <si>
     <t>217</t>
@@ -472,7 +472,7 @@
     <t>20017</t>
   </si>
   <si>
-    <t>每花费10资金,英雄+1基础攻击力</t>
+    <t>每花费20资金,英雄+1攻击力</t>
   </si>
   <si>
     <t>218</t>
@@ -484,7 +484,7 @@
     <t>20018</t>
   </si>
   <si>
-    <t>每次受到伤害时,+1资金</t>
+    <t>每次受到伤害时,+10金币</t>
   </si>
   <si>
     <t>Epic</t>
@@ -499,7 +499,7 @@
     <t>30001</t>
   </si>
   <si>
-    <t>造成伤害时,获得1%的生命窃取</t>
+    <t>造成伤害时,获得2%的生命窃取</t>
   </si>
   <si>
     <t>回旋刃</t>
@@ -529,7 +529,7 @@
     <t>30003</t>
   </si>
   <si>
-    <t>结算伤害时,会将留在手牌上最小的牌点数转化为额外攻击力</t>
+    <t>结算伤害时,会将留在手牌上最大的牌点数转化为额外攻击力</t>
   </si>
   <si>
     <t>搓牌能手</t>
@@ -574,7 +574,7 @@
     <t>30007</t>
   </si>
   <si>
-    <t>亮出的每张8在结算时提供+8攻击力</t>
+    <t>亮出的每张8在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>偶数韵律</t>
@@ -583,7 +583,7 @@
     <t>30008</t>
   </si>
   <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+4倍率</t>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>奇数韵律</t>
@@ -592,7 +592,7 @@
     <t>30009</t>
   </si>
   <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+4倍率</t>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>贵族</t>
@@ -601,7 +601,7 @@
     <t>30010</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+6倍率</t>
+    <t>亮出的每张人头牌在结算时提供+3倍率</t>
   </si>
   <si>
     <t>工资卡</t>
@@ -610,7 +610,7 @@
     <t>30011</t>
   </si>
   <si>
-    <t>每击杀1名敌人,该收藏品的出售价格+1资金</t>
+    <t>每击杀1名敌人,该收藏品的出售价格+5金币</t>
   </si>
   <si>
     <t>训练</t>
@@ -637,7 +637,7 @@
     <t>30013</t>
   </si>
   <si>
-    <t>亮出的每张9在结算时提供2资金</t>
+    <t>亮出的每张9在结算时提供10金币</t>
   </si>
   <si>
     <t>401</t>
@@ -727,7 +727,7 @@
     <t>40007</t>
   </si>
   <si>
-    <t>结算时,若未使用过搓牌,每个搓牌次数提供+6倍率</t>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+5倍率</t>
   </si>
   <si>
     <t>408</t>
@@ -751,7 +751,7 @@
     <t>40009|400091</t>
   </si>
   <si>
-    <t>亮出的每张A在结算伤害时提供+6攻击力和+6倍率</t>
+    <t>亮出的每张A在结算伤害时提供+5攻击力和+5倍率</t>
   </si>
   <si>
     <t>410</t>
@@ -1427,14 +1427,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3154,8 +3151,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="49" ht="14.25"/>
-    <row r="50" ht="14.25" spans="2:10">
+    <row r="50" spans="2:10">
       <c r="B50" s="1" t="s">
         <v>202</v>
       </c>
@@ -3171,10 +3167,10 @@
       <c r="F50" t="s">
         <v>204</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="2">
         <v>650</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="2">
         <v>325</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3184,7 +3180,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="51" ht="14.25" spans="2:10">
+    <row r="51" spans="2:10">
       <c r="B51" s="1" t="s">
         <v>207</v>
       </c>
@@ -3200,10 +3196,10 @@
       <c r="F51" t="s">
         <v>209</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="2">
         <v>600</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="2">
         <v>300</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3213,7 +3209,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="52" ht="14.25" spans="2:10">
+    <row r="52" spans="2:10">
       <c r="B52" s="1" t="s">
         <v>212</v>
       </c>
@@ -3229,10 +3225,10 @@
       <c r="F52" t="s">
         <v>51</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="2">
         <v>580</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="2">
         <v>290</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -3242,7 +3238,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="53" ht="14.25" spans="2:10">
+    <row r="53" spans="2:10">
       <c r="B53" s="1" t="s">
         <v>216</v>
       </c>
@@ -3258,10 +3254,10 @@
       <c r="F53" t="s">
         <v>51</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="2">
         <v>530</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="2">
         <v>265</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3271,7 +3267,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="54" ht="14.25" spans="2:10">
+    <row r="54" spans="2:10">
       <c r="B54" s="1" t="s">
         <v>220</v>
       </c>
@@ -3287,10 +3283,10 @@
       <c r="F54" t="s">
         <v>51</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="2">
         <v>560</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="2">
         <v>280</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -3300,7 +3296,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="55" ht="14.25" spans="2:10">
+    <row r="55" spans="2:10">
       <c r="B55" s="1" t="s">
         <v>224</v>
       </c>
@@ -3316,10 +3312,10 @@
       <c r="F55" t="s">
         <v>51</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="2">
         <v>620</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55" s="2">
         <v>310</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -3329,7 +3325,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="56" ht="14.25" spans="2:10">
+    <row r="56" spans="2:10">
       <c r="B56" s="1" t="s">
         <v>228</v>
       </c>
@@ -3345,10 +3341,10 @@
       <c r="F56" t="s">
         <v>51</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="2">
         <v>590</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="2">
         <v>295</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -3358,7 +3354,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="57" ht="14.25" spans="2:10">
+    <row r="57" spans="2:10">
       <c r="B57" s="1" t="s">
         <v>232</v>
       </c>
@@ -3374,10 +3370,10 @@
       <c r="F57" t="s">
         <v>51</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="2">
         <v>640</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="2">
         <v>320</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -3387,7 +3383,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="58" ht="14.25" spans="2:10">
+    <row r="58" spans="2:10">
       <c r="B58" s="1" t="s">
         <v>236</v>
       </c>
@@ -3403,10 +3399,10 @@
       <c r="F58" t="s">
         <v>51</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="2">
         <v>610</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="2">
         <v>305</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -3416,7 +3412,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="59" ht="14.25" spans="2:10">
+    <row r="59" spans="2:10">
       <c r="B59" s="1" t="s">
         <v>240</v>
       </c>
@@ -3432,10 +3428,10 @@
       <c r="F59" t="s">
         <v>51</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="2">
         <v>580</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="2">
         <v>290</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -3445,7 +3441,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="60" ht="14.25" spans="2:10">
+    <row r="60" spans="2:10">
       <c r="B60" s="1" t="s">
         <v>244</v>
       </c>
@@ -3461,10 +3457,10 @@
       <c r="F60" t="s">
         <v>51</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="2">
         <v>600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60" s="2">
         <v>300</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -3474,7 +3470,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="61" ht="14.25" spans="2:10">
+    <row r="61" spans="2:10">
       <c r="B61" s="1" t="s">
         <v>248</v>
       </c>
@@ -3490,10 +3486,10 @@
       <c r="F61" t="s">
         <v>51</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="2">
         <v>550</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61" s="2">
         <v>275</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -3503,7 +3499,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="62" ht="14.25" spans="2:10">
+    <row r="62" spans="2:10">
       <c r="B62" s="1" t="s">
         <v>252</v>
       </c>
@@ -3519,10 +3515,10 @@
       <c r="F62" t="s">
         <v>51</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="2">
         <v>560</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="2">
         <v>280</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -3532,7 +3528,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="63" ht="14.25" spans="2:10">
+    <row r="63" spans="2:10">
       <c r="B63" s="1" t="s">
         <v>256</v>
       </c>
@@ -3548,10 +3544,10 @@
       <c r="F63" t="s">
         <v>51</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="2">
         <v>630</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63" s="2">
         <v>315</v>
       </c>
       <c r="I63" s="1" t="s">

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14190" windowHeight="9750"/>
+    <workbookView windowWidth="16065" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
     <t>20005</t>
   </si>
   <si>
-    <t>亮出的对子牌型在结算时提供+2攻击力</t>
+    <t>亮出的对子牌型在结算时提供+4攻击力</t>
   </si>
   <si>
     <t>206</t>
@@ -316,7 +316,7 @@
     <t>20006</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+2攻击力</t>
+    <t>亮出的顺子牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>207</t>
@@ -328,7 +328,7 @@
     <t>20007</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+2攻击力</t>
+    <t>亮出的同花牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>208</t>
@@ -346,7 +346,7 @@
     <t>20008</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+2攻击力</t>
+    <t>亮出的同花顺牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>209</t>
@@ -358,7 +358,7 @@
     <t>20009</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+2攻击力</t>
+    <t>亮出的豹子牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>210</t>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16065" windowHeight="9750"/>
+    <workbookView windowWidth="12450" windowHeight="9750"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12450" windowHeight="9750"/>
+    <workbookView windowWidth="11850" windowHeight="11805"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="262">
   <si>
     <t>##var</t>
   </si>
@@ -61,6 +61,9 @@
     <t>MechanismId</t>
   </si>
   <si>
+    <t>UnlockConditionId</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
   </si>
   <si>
     <t>机制ID</t>
+  </si>
+  <si>
+    <t>解锁条件ID</t>
   </si>
   <si>
     <t>描述</t>
@@ -1427,11 +1433,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1785,7 +1794,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.21666666666667" style="1" customWidth="1"/>
@@ -1797,13 +1806,14 @@
     <col min="7" max="7" width="5.975" style="2" customWidth="1"/>
     <col min="8" max="8" width="4.78333333333333" style="2" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.1916666666667" customWidth="1"/>
-    <col min="11" max="11" width="11.875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34.75" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="10" style="3" customWidth="1"/>
+    <col min="11" max="11" width="7.70833333333333" customWidth="1"/>
+    <col min="12" max="12" width="11.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="34.75" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1831,90 +1841,99 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:12">
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:13">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2">
         <v>0.8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2">
         <v>45</v>
@@ -1925,28 +1944,29 @@
       <c r="I5" s="2">
         <v>10001</v>
       </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" s="1"/>
+      <c r="J5" s="3"/>
+      <c r="K5" t="s">
+        <v>30</v>
+      </c>
       <c r="L5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:12">
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" customFormat="1" spans="1:13">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2">
         <v>0.8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2">
         <v>40</v>
@@ -1957,27 +1977,28 @@
       <c r="I6" s="2">
         <v>10002</v>
       </c>
-      <c r="J6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K6" s="1"/>
+      <c r="J6" s="3"/>
+      <c r="K6" t="s">
+        <v>34</v>
+      </c>
       <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2">
         <v>0.8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="2">
         <v>40</v>
@@ -1988,25 +2009,25 @@
       <c r="I7" s="2">
         <v>10003</v>
       </c>
-      <c r="J7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2">
         <v>0.8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2">
         <v>40</v>
@@ -2017,25 +2038,25 @@
       <c r="I8" s="2">
         <v>10004</v>
       </c>
-      <c r="J8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="K8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2">
         <v>0.8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G9" s="2">
         <v>40</v>
@@ -2046,25 +2067,25 @@
       <c r="I9" s="2">
         <v>10005</v>
       </c>
-      <c r="J9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="K9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="B10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D10" s="2">
         <v>0.8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2">
         <v>50</v>
@@ -2075,25 +2096,25 @@
       <c r="I10" s="2">
         <v>10006</v>
       </c>
-      <c r="J10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="K10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2">
         <v>0.8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G11" s="2">
         <v>52</v>
@@ -2104,25 +2125,25 @@
       <c r="I11" s="2">
         <v>10007</v>
       </c>
-      <c r="J11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="K11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D12" s="2">
         <v>0.8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G12" s="2">
         <v>52</v>
@@ -2133,25 +2154,25 @@
       <c r="I12" s="2">
         <v>10008</v>
       </c>
-      <c r="J12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="K12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D13" s="2">
         <v>0.8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2">
         <v>55</v>
@@ -2162,25 +2183,25 @@
       <c r="I13" s="2">
         <v>10009</v>
       </c>
-      <c r="J13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="K13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2">
         <v>0.8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G14" s="2">
         <v>55</v>
@@ -2191,25 +2212,25 @@
       <c r="I14" s="2">
         <v>10010</v>
       </c>
-      <c r="J14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="K14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" s="2">
         <v>0.8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2">
         <v>60</v>
@@ -2220,943 +2241,955 @@
       <c r="I15" s="2">
         <v>10011</v>
       </c>
-      <c r="J15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D17" s="2">
         <v>0.4</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="B18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="B18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="D18" s="2">
         <v>0.4</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>75</v>
+      </c>
+      <c r="K18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19"/>
       <c r="B19" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2">
         <v>0.4</v>
       </c>
       <c r="E19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>79</v>
+      </c>
+      <c r="K19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20"/>
       <c r="B20" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D20" s="2">
         <v>0.4</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>83</v>
+      </c>
+      <c r="K20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21"/>
       <c r="B21" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2">
         <v>0.4</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J21" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>89</v>
+      </c>
+      <c r="K21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22"/>
       <c r="B22" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D22" s="2">
         <v>0.4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>95</v>
+      </c>
+      <c r="K22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23"/>
       <c r="B23" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D23" s="2">
         <v>0.4</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>99</v>
+      </c>
+      <c r="K23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24"/>
       <c r="B24" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D24" s="2">
         <v>0.4</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>105</v>
+      </c>
+      <c r="K24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25"/>
       <c r="B25" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D25" s="2">
         <v>0.4</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J25" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>109</v>
+      </c>
+      <c r="K25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26"/>
       <c r="B26" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" s="2">
         <v>0.4</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>115</v>
+      </c>
+      <c r="K26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27"/>
       <c r="B27" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2">
         <v>0.4</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J27" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>121</v>
+      </c>
+      <c r="K27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28"/>
       <c r="B28" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2">
         <v>0.4</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J28" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>125</v>
+      </c>
+      <c r="K28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29"/>
       <c r="B29" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D29" s="2">
         <v>0.4</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>131</v>
+      </c>
+      <c r="K29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30"/>
       <c r="B30" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D30" s="2">
         <v>0.4</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>135</v>
+      </c>
+      <c r="K30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31"/>
       <c r="B31" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D31" s="2">
         <v>0.4</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J31" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>139</v>
+      </c>
+      <c r="K31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32"/>
       <c r="B32" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D32" s="2">
         <v>0.4</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J32" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>143</v>
+      </c>
+      <c r="K32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33"/>
       <c r="B33" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D33" s="2">
         <v>0.4</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F33" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J33" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>147</v>
+      </c>
+      <c r="K33" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34"/>
       <c r="B34" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D34" s="2">
         <v>0.4</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>151</v>
+      </c>
+      <c r="K34" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35"/>
       <c r="B35" s="2"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:11">
       <c r="A36"/>
       <c r="B36" s="2">
         <v>301</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D36" s="2">
         <v>0.2</v>
       </c>
       <c r="E36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J36" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>156</v>
+      </c>
+      <c r="J36" s="3">
+        <v>1001</v>
+      </c>
+      <c r="K36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37"/>
       <c r="B37" s="2">
         <v>302</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D37" s="2">
         <v>0.2</v>
       </c>
       <c r="E37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J37" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>161</v>
+      </c>
+      <c r="K37" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38"/>
       <c r="B38" s="2">
         <v>303</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D38" s="2">
         <v>0.2</v>
       </c>
       <c r="E38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J38" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>166</v>
+      </c>
+      <c r="K38" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39"/>
       <c r="B39" s="2">
         <v>304</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D39" s="2">
         <v>0.2</v>
       </c>
       <c r="E39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="J39" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>170</v>
+      </c>
+      <c r="J39" s="3">
+        <v>1002</v>
+      </c>
+      <c r="K39" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40"/>
       <c r="B40" s="2">
         <v>305</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D40" s="2">
         <v>0.2</v>
       </c>
       <c r="E40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J40" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>175</v>
+      </c>
+      <c r="J40" s="3">
+        <v>1003</v>
+      </c>
+      <c r="K40" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="B41" s="2">
         <v>306</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D41" s="2">
         <v>0.2</v>
       </c>
       <c r="E41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="J41" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>178</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1004</v>
+      </c>
+      <c r="K41" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="B42" s="2">
         <v>307</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D42" s="2">
         <v>0.2</v>
       </c>
       <c r="E42" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F42" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="J42" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>181</v>
+      </c>
+      <c r="K42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="B43" s="2">
         <v>308</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D43" s="2">
         <v>0.2</v>
       </c>
       <c r="E43" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F43" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>184</v>
+      </c>
+      <c r="K43" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="B44" s="2">
         <v>309</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D44" s="2">
         <v>0.2</v>
       </c>
       <c r="E44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F44" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="J44" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>187</v>
+      </c>
+      <c r="K44" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="B45" s="2">
         <v>310</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D45" s="2">
         <v>0.2</v>
       </c>
       <c r="E45" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J45" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>190</v>
+      </c>
+      <c r="K45" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="B46" s="2">
         <v>311</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D46" s="2">
         <v>0.2</v>
       </c>
       <c r="E46" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F46" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="J46" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>193</v>
+      </c>
+      <c r="K46" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="B47" s="2">
         <v>312</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D47" s="2">
         <v>0.2</v>
       </c>
       <c r="E47" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F47" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J47" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>197</v>
+      </c>
+      <c r="K47" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="B48" s="2">
         <v>313</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D48" s="2">
         <v>0.2</v>
       </c>
       <c r="E48" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="J48" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10">
+        <v>202</v>
+      </c>
+      <c r="K48" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
       <c r="B50" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D50" s="2">
         <v>0.1</v>
@@ -3165,7 +3198,7 @@
         <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G50" s="2">
         <v>650</v>
@@ -3174,27 +3207,30 @@
         <v>325</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="J50" s="3">
+        <v>1005</v>
+      </c>
+      <c r="K50" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="J50" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="D51" s="2">
         <v>0.1</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G51" s="2">
         <v>600</v>
@@ -3203,27 +3239,30 @@
         <v>300</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="J51" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10">
+        <v>212</v>
+      </c>
+      <c r="J51" s="3">
+        <v>1006</v>
+      </c>
+      <c r="K51" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
       <c r="B52" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D52" s="2">
         <v>0.1</v>
       </c>
       <c r="E52" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G52" s="2">
         <v>580</v>
@@ -3232,27 +3271,27 @@
         <v>290</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J52" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10">
+        <v>216</v>
+      </c>
+      <c r="K52" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
       <c r="B53" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D53" s="2">
         <v>0.1</v>
       </c>
       <c r="E53" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G53" s="2">
         <v>530</v>
@@ -3261,27 +3300,27 @@
         <v>265</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="J53" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10">
+        <v>220</v>
+      </c>
+      <c r="K53" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
       <c r="B54" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D54" s="2">
         <v>0.1</v>
       </c>
       <c r="E54" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G54" s="2">
         <v>560</v>
@@ -3290,27 +3329,27 @@
         <v>280</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="J54" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
+        <v>224</v>
+      </c>
+      <c r="K54" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
       <c r="B55" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D55" s="2">
         <v>0.1</v>
       </c>
       <c r="E55" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F55" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G55" s="2">
         <v>620</v>
@@ -3319,27 +3358,27 @@
         <v>310</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="J55" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10">
+        <v>228</v>
+      </c>
+      <c r="K55" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
       <c r="B56" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D56" s="2">
         <v>0.1</v>
       </c>
       <c r="E56" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G56" s="2">
         <v>590</v>
@@ -3348,27 +3387,27 @@
         <v>295</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="J56" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10">
+        <v>232</v>
+      </c>
+      <c r="K56" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
       <c r="B57" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D57" s="2">
         <v>0.1</v>
       </c>
       <c r="E57" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G57" s="2">
         <v>640</v>
@@ -3377,27 +3416,27 @@
         <v>320</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="J57" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10">
+        <v>236</v>
+      </c>
+      <c r="K57" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
       <c r="B58" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D58" s="2">
         <v>0.1</v>
       </c>
       <c r="E58" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F58" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G58" s="2">
         <v>610</v>
@@ -3406,27 +3445,27 @@
         <v>305</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J58" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
+        <v>240</v>
+      </c>
+      <c r="K58" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
       <c r="B59" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D59" s="2">
         <v>0.1</v>
       </c>
       <c r="E59" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G59" s="2">
         <v>580</v>
@@ -3435,27 +3474,27 @@
         <v>290</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="J59" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10">
+        <v>244</v>
+      </c>
+      <c r="K59" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
       <c r="B60" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D60" s="2">
         <v>0.1</v>
       </c>
       <c r="E60" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G60" s="2">
         <v>600</v>
@@ -3464,27 +3503,27 @@
         <v>300</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J60" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
+        <v>248</v>
+      </c>
+      <c r="K60" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
       <c r="B61" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D61" s="2">
         <v>0.1</v>
       </c>
       <c r="E61" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F61" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G61" s="2">
         <v>550</v>
@@ -3493,27 +3532,27 @@
         <v>275</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="J61" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10">
+        <v>252</v>
+      </c>
+      <c r="K61" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
       <c r="B62" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D62" s="2">
         <v>0.1</v>
       </c>
       <c r="E62" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F62" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G62" s="2">
         <v>560</v>
@@ -3522,27 +3561,30 @@
         <v>280</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="J62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10">
+        <v>256</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1007</v>
+      </c>
+      <c r="K62" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
       <c r="B63" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D63" s="2">
         <v>0.1</v>
       </c>
       <c r="E63" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F63" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G63" s="2">
         <v>630</v>
@@ -3551,10 +3593,13 @@
         <v>315</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="J63" t="s">
-        <v>259</v>
+        <v>260</v>
+      </c>
+      <c r="J63" s="3">
+        <v>1008</v>
+      </c>
+      <c r="K63" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11850" windowHeight="11805"/>
+    <workbookView windowWidth="16050" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="395">
   <si>
     <t>##var</t>
   </si>
@@ -235,6 +235,60 @@
     <t>每次受到的伤害降低1点</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>小钱包</t>
+  </si>
+  <si>
+    <t>每回合开始时,获得1金币</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>绷带</t>
+  </si>
+  <si>
+    <t>每回合开始时,恢复2点生命</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>幸运草</t>
+  </si>
+  <si>
+    <t>每回合结束后,有10%概率获得5金币</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>暴击拳套</t>
+  </si>
+  <si>
+    <t>每回合结束后,提高1%暴击率,至多叠加20层</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>垫脚石</t>
+  </si>
+  <si>
+    <t>每当你亮牌时大于场上所有敌人,就永久提供+1攻击力</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>反击拳套</t>
+  </si>
+  <si>
+    <t>每当你受到伤害时,反弹2点伤害给攻击者</t>
+  </si>
+  <si>
     <t>201</t>
   </si>
   <si>
@@ -493,6 +547,138 @@
     <t>每次受到伤害时,+10金币</t>
   </si>
   <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>和平鸽</t>
+  </si>
+  <si>
+    <t>20019</t>
+  </si>
+  <si>
+    <t>有25%概率将自身造成的伤害或受到的伤害降低为0</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>勇气徽章</t>
+  </si>
+  <si>
+    <t>20020</t>
+  </si>
+  <si>
+    <t>亮牌时,若牌型小于对方,则永久+1攻击力</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>激励徽章</t>
+  </si>
+  <si>
+    <t>20021</t>
+  </si>
+  <si>
+    <t>亮牌时,若牌型小于对方,则永久+3血量上限</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>记账本</t>
+  </si>
+  <si>
+    <t>20022</t>
+  </si>
+  <si>
+    <t>每回合结束时,若本回合未造成任何伤害,则获得5金币</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>铁饭碗</t>
+  </si>
+  <si>
+    <t>20023</t>
+  </si>
+  <si>
+    <t>亮牌后无论胜负,均可获得1金币</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>永恒之心</t>
+  </si>
+  <si>
+    <t>20024</t>
+  </si>
+  <si>
+    <t>每回合开始时,永久+2血量上限</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>幸运同花</t>
+  </si>
+  <si>
+    <t>20025</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>运动鞋</t>
+  </si>
+  <si>
+    <t>20026</t>
+  </si>
+  <si>
+    <t>每回合结束后,提高1%闪避率,至多叠加20层</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>保温杯</t>
+  </si>
+  <si>
+    <t>20027</t>
+  </si>
+  <si>
+    <t>每回合结束后,若你的血量低于50%,则恢复6点生命</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>利息</t>
+  </si>
+  <si>
+    <t>20028</t>
+  </si>
+  <si>
+    <t>每拥有10金币,在回合结束后就会获得1金币</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>小算盘</t>
+  </si>
+  <si>
+    <t>20029</t>
+  </si>
+  <si>
+    <t>每回合结束时,每剩余1次搓牌次数就获得3金币</t>
+  </si>
+  <si>
     <t>Epic</t>
   </si>
   <si>
@@ -646,6 +832,114 @@
     <t>亮出的每张9在结算时提供10金币</t>
   </si>
   <si>
+    <t>后备计划</t>
+  </si>
+  <si>
+    <t>30014</t>
+  </si>
+  <si>
+    <t>如果本回合牌型小于所有敌人,则立即获得10金币并回复15点生命值</t>
+  </si>
+  <si>
+    <t>护身符</t>
+  </si>
+  <si>
+    <t>30015</t>
+  </si>
+  <si>
+    <t>每回合受到的第1次伤害完全免疫</t>
+  </si>
+  <si>
+    <t>复盘笔记</t>
+  </si>
+  <si>
+    <t>30016</t>
+  </si>
+  <si>
+    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
+  </si>
+  <si>
+    <t>幸运顺子</t>
+  </si>
+  <si>
+    <t>30017</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于顺子,则会被强行视作顺子</t>
+  </si>
+  <si>
+    <t>逆转沙漏</t>
+  </si>
+  <si>
+    <t>30018</t>
+  </si>
+  <si>
+    <t>当牌型小于敌人时,有30%概率反转对比结果,但伤害按自身牌型计算</t>
+  </si>
+  <si>
+    <t>练习卷</t>
+  </si>
+  <si>
+    <t>30019</t>
+  </si>
+  <si>
+    <t>每回合结束后,若本回合你未击杀任何敌人,则永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>小本本</t>
+  </si>
+  <si>
+    <t>30020</t>
+  </si>
+  <si>
+    <t>本局内,对自己曾经输过的敌人造成伤害时,伤害+20%</t>
+  </si>
+  <si>
+    <t>高贵徽章</t>
+  </si>
+  <si>
+    <t>30021</t>
+  </si>
+  <si>
+    <t>每回合开始时,若生命值高于50%,获得10金币</t>
+  </si>
+  <si>
+    <t>陷阱</t>
+  </si>
+  <si>
+    <t>30022</t>
+  </si>
+  <si>
+    <t>本局内,自己曾经输过的敌人在造成伤害时,伤害-20%</t>
+  </si>
+  <si>
+    <t>好运来</t>
+  </si>
+  <si>
+    <t>30023</t>
+  </si>
+  <si>
+    <t>每回合有15%概率使本回合所有敌人亮出的牌型自动降一级</t>
+  </si>
+  <si>
+    <t>入场券</t>
+  </si>
+  <si>
+    <t>30024</t>
+  </si>
+  <si>
+    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>条约</t>
+  </si>
+  <si>
+    <t>30025</t>
+  </si>
+  <si>
+    <t>所有敌人造成的伤害降低30%</t>
+  </si>
+  <si>
     <t>401</t>
   </si>
   <si>
@@ -818,6 +1112,111 @@
   </si>
   <si>
     <t>亮出的每张7结算时有7%概率提供+77攻击力和+7倍率</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>武林秘籍</t>
+  </si>
+  <si>
+    <t>40015|400151</t>
+  </si>
+  <si>
+    <t>获得50%闪避率,且闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>幸运对子</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>小强</t>
+  </si>
+  <si>
+    <t>每输1次敌人,后续自身造成的所有伤害提高5%</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>救命稻草</t>
+  </si>
+  <si>
+    <t>如果你受到了1次致命伤害,会将血量降低为1,且下次造成伤害的同时恢复本次伤害20%的血量,每关生效1次</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>专注</t>
+  </si>
+  <si>
+    <t>当场上只剩下一个敌人时,你对其造成的伤害+100%</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>变形魔方</t>
+  </si>
+  <si>
+    <t>每回合亮出的牌型强制提升一级</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>毒药</t>
+  </si>
+  <si>
+    <t>所有敌人血量降低30%[BOSS除外]</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>刺客秘籍</t>
+  </si>
+  <si>
+    <t>40022|400221</t>
+  </si>
+  <si>
+    <t>获得50%暴击率,且触发暴击时会对其他所有敌人造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>透视眼</t>
+  </si>
+  <si>
+    <t>每回合透视次数+1</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>每回合结束后,本回合自身总伤害输出的2%转化为金币</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>差距胶囊</t>
+  </si>
+  <si>
+    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低15%</t>
   </si>
 </sst>
 </file>
@@ -983,12 +1382,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1309,7 +1720,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1333,16 +1744,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1351,92 +1762,95 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1444,6 +1858,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1794,1812 +2220,3024 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="5.21666666666667" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.93333333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="8.8" customWidth="1"/>
-    <col min="4" max="4" width="4.78333333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.8" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.8" style="3" customWidth="1"/>
     <col min="6" max="6" width="10.1083333333333" customWidth="1"/>
-    <col min="7" max="7" width="5.975" style="2" customWidth="1"/>
-    <col min="8" max="8" width="4.78333333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.38333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10" style="3" customWidth="1"/>
-    <col min="11" max="11" width="7.70833333333333" customWidth="1"/>
-    <col min="12" max="12" width="11.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="34.75" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="5.975" style="3" customWidth="1"/>
+    <col min="8" max="8" width="4.78333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="5.53333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="7.70833333333333" style="4" customWidth="1"/>
+    <col min="12" max="12" width="11.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="34.75" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:13">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
+    <row r="4" ht="14.25"/>
+    <row r="5" customFormat="1" ht="14.25" spans="1:13">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>0.8</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="2">
-        <v>45</v>
-      </c>
-      <c r="H5" s="2">
-        <v>22</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="G5" s="4">
+        <v>20</v>
+      </c>
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
+      <c r="I5" s="3">
         <v>10001</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" t="s">
+      <c r="K5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:13">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" customFormat="1" ht="14.25" spans="1:13">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>0.8</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="2">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="G6" s="4">
         <v>20</v>
       </c>
-      <c r="I6" s="2">
+      <c r="H6" s="4">
+        <v>10</v>
+      </c>
+      <c r="I6" s="3">
         <v>10002</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" t="s">
+      <c r="K6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7" s="1" t="s">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" ht="14.25" spans="1:13">
+      <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>0.8</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="2">
-        <v>40</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="G7" s="4">
         <v>20</v>
       </c>
-      <c r="I7" s="2">
+      <c r="H7" s="4">
+        <v>10</v>
+      </c>
+      <c r="I7" s="3">
         <v>10003</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="1" t="s">
+    <row r="8" ht="14.25" spans="1:13">
+      <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>0.8</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F8" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="2">
-        <v>40</v>
-      </c>
-      <c r="H8" s="2">
+      <c r="G8" s="4">
         <v>20</v>
       </c>
-      <c r="I8" s="2">
+      <c r="H8" s="4">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3">
         <v>10004</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="B9" s="1" t="s">
+    <row r="9" ht="14.25" spans="1:13">
+      <c r="B9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>0.8</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F9" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="2">
-        <v>40</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="G9" s="4">
         <v>20</v>
       </c>
-      <c r="I9" s="2">
+      <c r="H9" s="4">
+        <v>10</v>
+      </c>
+      <c r="I9" s="3">
         <v>10005</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="1" t="s">
+    <row r="10" ht="14.25" spans="1:13">
+      <c r="B10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>0.8</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="4">
+        <v>25</v>
+      </c>
+      <c r="H10" s="4">
+        <v>12</v>
+      </c>
+      <c r="I10" s="3">
+        <v>10006</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="2">
+    </row>
+    <row r="11" ht="14.25" spans="1:13">
+      <c r="B11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="4">
         <v>25</v>
       </c>
-      <c r="I10" s="2">
-        <v>10006</v>
-      </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="B11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="H11" s="4">
+        <v>12</v>
+      </c>
+      <c r="I11" s="3">
+        <v>10007</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:13">
+      <c r="B12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="3">
         <v>0.8</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11" s="2">
-        <v>52</v>
-      </c>
-      <c r="H11" s="2">
-        <v>26</v>
-      </c>
-      <c r="I11" s="2">
-        <v>10007</v>
-      </c>
-      <c r="K11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="B12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="4">
+        <v>25</v>
+      </c>
+      <c r="H12" s="4">
+        <v>12</v>
+      </c>
+      <c r="I12" s="3">
+        <v>10008</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:13">
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D13" s="3">
         <v>0.8</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="2">
-        <v>52</v>
-      </c>
-      <c r="H12" s="2">
-        <v>26</v>
-      </c>
-      <c r="I12" s="2">
-        <v>10008</v>
-      </c>
-      <c r="K12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="4">
+        <v>28</v>
+      </c>
+      <c r="H13" s="4">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3">
+        <v>10009</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="B14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D14" s="3">
         <v>0.8</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="2">
-        <v>55</v>
-      </c>
-      <c r="H13" s="2">
+      <c r="E14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="4">
+        <v>28</v>
+      </c>
+      <c r="H14" s="4">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3">
+        <v>10010</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="B15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="2">
-        <v>10009</v>
-      </c>
-      <c r="K13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="B14" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="D15" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="4">
+        <v>30</v>
+      </c>
+      <c r="H15" s="4">
+        <v>15</v>
+      </c>
+      <c r="I15" s="3">
+        <v>10011</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:13">
+      <c r="B16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D16" s="5">
         <v>0.8</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="2">
-        <v>55</v>
-      </c>
-      <c r="H14" s="2">
+      <c r="E16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="6">
+        <v>25</v>
+      </c>
+      <c r="H16" s="6">
+        <v>12</v>
+      </c>
+      <c r="I16" s="5">
+        <v>10012</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:11">
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="2">
-        <v>10010</v>
-      </c>
-      <c r="K14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="B15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="2">
+      <c r="D17" s="5">
         <v>0.8</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="2">
-        <v>60</v>
-      </c>
-      <c r="H15" s="2">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2">
-        <v>10011</v>
-      </c>
-      <c r="K15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="B17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="E17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K17" t="s">
+      <c r="F17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="6">
+        <v>25</v>
+      </c>
+      <c r="H17" s="6">
+        <v>12</v>
+      </c>
+      <c r="I17" s="5">
+        <v>10013</v>
+      </c>
+      <c r="J17" s="5"/>
+      <c r="K17" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" s="1" customFormat="1" spans="1:11">
       <c r="B18" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="2">
+        <v>27</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="6">
+        <v>25</v>
+      </c>
+      <c r="H18" s="6">
+        <v>12</v>
+      </c>
+      <c r="I18" s="5">
+        <v>10014</v>
+      </c>
+      <c r="J18" s="5"/>
+      <c r="K18" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="14.25" spans="1:11">
+      <c r="B19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="6">
+        <v>30</v>
+      </c>
+      <c r="H19" s="6">
+        <v>15</v>
+      </c>
+      <c r="I19" s="5">
+        <v>10015</v>
+      </c>
+      <c r="J19" s="5"/>
+      <c r="K19" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:11">
+      <c r="B20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="6">
+        <v>30</v>
+      </c>
+      <c r="H20" s="6">
+        <v>15</v>
+      </c>
+      <c r="I20" s="5">
+        <v>10016</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="K20" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:11">
+      <c r="B21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="6">
+        <v>30</v>
+      </c>
+      <c r="H21" s="6">
+        <v>15</v>
+      </c>
+      <c r="I21" s="5">
+        <v>10017</v>
+      </c>
+      <c r="J21" s="5"/>
+      <c r="K21" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="B23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="3">
         <v>0.4</v>
       </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="E23" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19"/>
-      <c r="B19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="H23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="B24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="3">
         <v>0.4</v>
       </c>
-      <c r="E19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="E24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20"/>
-      <c r="B20" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21"/>
-      <c r="B21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="H24" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22"/>
-      <c r="B22" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="I24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="K24" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="K22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23"/>
-      <c r="B23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24"/>
-      <c r="B24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K24" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25"/>
-      <c r="B25" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="B25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D25" s="3">
         <v>0.4</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>108</v>
+      <c r="E25" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="F25" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K25" t="s">
-        <v>110</v>
+      <c r="G25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26"/>
-      <c r="B26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="B26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="3">
         <v>0.4</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>112</v>
+      <c r="E26" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="F26" t="s">
         <v>53</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K26" t="s">
-        <v>116</v>
+      <c r="G26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27"/>
-      <c r="B27" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="B27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="3">
         <v>0.4</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>118</v>
+      <c r="E27" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="F27" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K27" t="s">
-        <v>122</v>
+      <c r="G27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28"/>
-      <c r="B28" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="3">
         <v>0.4</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>124</v>
+      <c r="E28" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F28" t="s">
         <v>53</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K28" t="s">
-        <v>126</v>
+      <c r="G28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29"/>
-      <c r="B29" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="B29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="3">
         <v>0.4</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>128</v>
+      <c r="E29" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="F29" t="s">
         <v>53</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="K29" t="s">
-        <v>132</v>
+      <c r="G29" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30"/>
-      <c r="B30" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="B30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="3">
         <v>0.4</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>134</v>
+      <c r="E30" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="F30" t="s">
         <v>53</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="K30" t="s">
-        <v>136</v>
+      <c r="G30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31"/>
-      <c r="B31" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="B31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="3">
         <v>0.4</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>138</v>
+      <c r="E31" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="F31" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K31" t="s">
-        <v>140</v>
+      <c r="G31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32"/>
-      <c r="B32" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="B32" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="3">
         <v>0.4</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>142</v>
+      <c r="E32" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="F32" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K32" t="s">
-        <v>144</v>
+      <c r="G32" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33"/>
-      <c r="B33" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="B33" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="3">
         <v>0.4</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>146</v>
+      <c r="E33" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="F33" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K33" t="s">
-        <v>148</v>
+      <c r="G33" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34"/>
-      <c r="B34" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="2">
+      <c r="B34" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="3">
         <v>0.4</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>150</v>
+      <c r="E34" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="F34" t="s">
         <v>53</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K34" t="s">
-        <v>152</v>
+      <c r="G34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35"/>
-      <c r="B35" s="2"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
+      <c r="B35" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36"/>
-      <c r="B36" s="2">
-        <v>301</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="B36" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D36" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="K36" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J36" s="3">
-        <v>1001</v>
-      </c>
-      <c r="K36" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37"/>
-      <c r="B37" s="2">
-        <v>302</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="B37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F37" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="K37" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38"/>
-      <c r="B38" s="2">
-        <v>303</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D38" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E38" t="s">
-        <v>163</v>
+      <c r="B38" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>160</v>
       </c>
       <c r="F38" t="s">
         <v>53</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="K38" t="s">
-        <v>167</v>
+      <c r="G38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39"/>
-      <c r="B39" s="2">
-        <v>304</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E39" t="s">
-        <v>168</v>
+      <c r="B39" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="F39" t="s">
         <v>53</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J39" s="3">
-        <v>1002</v>
-      </c>
-      <c r="K39" t="s">
-        <v>171</v>
+      <c r="G39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40"/>
-      <c r="B40" s="2">
-        <v>305</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="B40" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F40" t="s">
+        <v>53</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:11">
+      <c r="A41" s="7"/>
+      <c r="B41" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F40" t="s">
-        <v>53</v>
-      </c>
-      <c r="G40" s="1" t="s">
+      <c r="F41" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="6">
+        <v>140</v>
+      </c>
+      <c r="H41" s="6">
+        <v>70</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="J41" s="5"/>
+      <c r="K41" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I40" s="1" t="s">
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:11">
+      <c r="A42" s="7"/>
+      <c r="B42" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J40" s="3">
-        <v>1003</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="C42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="B41" s="2">
-        <v>306</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D41" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F42" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" s="6">
+        <v>150</v>
+      </c>
+      <c r="H42" s="6">
+        <v>75</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I41" s="1" t="s">
+      <c r="J42" s="5"/>
+      <c r="K42" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="J41" s="3">
-        <v>1004</v>
-      </c>
-      <c r="K41" t="s">
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:11">
+      <c r="A43" s="7"/>
+      <c r="B43" s="1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="B42" s="2">
-        <v>307</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="C43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I42" s="1" t="s">
+      <c r="F43" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="6">
+        <v>150</v>
+      </c>
+      <c r="H43" s="6">
+        <v>75</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="K42" t="s">
+      <c r="J43" s="5"/>
+      <c r="K43" s="7" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
-      <c r="B43" s="2">
-        <v>308</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E43" t="s">
+    <row r="44" s="1" customFormat="1" spans="1:11">
+      <c r="A44" s="7"/>
+      <c r="B44" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F43" t="s">
-        <v>53</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I43" s="1" t="s">
+      <c r="C44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="K43" t="s">
+      <c r="F44" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="6">
+        <v>140</v>
+      </c>
+      <c r="H44" s="6">
+        <v>70</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="B44" s="2">
-        <v>309</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D44" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="J44" s="5"/>
+      <c r="K44" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F44" t="s">
-        <v>53</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="I44" s="1" t="s">
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:11">
+      <c r="A45" s="7"/>
+      <c r="B45" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K44" t="s">
+      <c r="C45" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="B45" s="2">
-        <v>310</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D45" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F45" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="6">
+        <v>120</v>
+      </c>
+      <c r="H45" s="6">
+        <v>60</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F45" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I45" s="1" t="s">
+      <c r="J45" s="5"/>
+      <c r="K45" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="K45" t="s">
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:11">
+      <c r="A46" s="7"/>
+      <c r="B46" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="B46" s="2">
-        <v>311</v>
-      </c>
       <c r="C46" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E46" t="s">
+        <v>86</v>
+      </c>
+      <c r="D46" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F46" t="s">
-        <v>53</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>113</v>
+      <c r="F46" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G46" s="6">
+        <v>150</v>
+      </c>
+      <c r="H46" s="6">
+        <v>75</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K46" t="s">
+      <c r="J46" s="5"/>
+      <c r="K46" s="7" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
-      <c r="B47" s="2">
-        <v>312</v>
+    <row r="47" s="1" customFormat="1" spans="1:11">
+      <c r="A47" s="7"/>
+      <c r="B47" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="E47" t="s">
-        <v>195</v>
-      </c>
-      <c r="F47" t="s">
-        <v>53</v>
-      </c>
-      <c r="G47" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>87</v>
+      <c r="F47" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" s="6">
+        <v>150</v>
+      </c>
+      <c r="H47" s="6">
+        <v>75</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K47" t="s">
+      <c r="J47" s="5"/>
+      <c r="K47" s="7" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
-      <c r="B48" s="2">
+    <row r="48" s="1" customFormat="1" spans="1:11">
+      <c r="A48" s="7"/>
+      <c r="B48" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D48" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48" s="6">
+        <v>150</v>
+      </c>
+      <c r="H48" s="6">
+        <v>75</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J48" s="5"/>
+      <c r="K48" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:11">
+      <c r="A49" s="7"/>
+      <c r="B49" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D49" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G49" s="6">
+        <v>140</v>
+      </c>
+      <c r="H49" s="6">
+        <v>70</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J49" s="5"/>
+      <c r="K49" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:11">
+      <c r="A50" s="7"/>
+      <c r="B50" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D50" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G50" s="6">
+        <v>140</v>
+      </c>
+      <c r="H50" s="6">
+        <v>70</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J50" s="5"/>
+      <c r="K50" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:11">
+      <c r="A51" s="7"/>
+      <c r="B51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G51" s="6">
+        <v>140</v>
+      </c>
+      <c r="H51" s="6">
+        <v>70</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J51" s="5"/>
+      <c r="K51" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52"/>
+      <c r="B52" s="3"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53"/>
+      <c r="B53" s="3">
+        <v>301</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F53" t="s">
+        <v>53</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J53" s="3">
+        <v>1001</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54"/>
+      <c r="B54" s="3">
+        <v>302</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F54" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55"/>
+      <c r="B55" s="3">
+        <v>303</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="F55" t="s">
+        <v>53</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56"/>
+      <c r="B56" s="3">
+        <v>304</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F56" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="J56" s="3">
+        <v>1002</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57"/>
+      <c r="B57" s="3">
+        <v>305</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F57" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1003</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="B58" s="3">
+        <v>306</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F58" t="s">
+        <v>53</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1004</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="B59" s="3">
+        <v>307</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D59" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F59" t="s">
+        <v>53</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="B60" s="3">
+        <v>308</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F60" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="B61" s="3">
+        <v>309</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F61" t="s">
+        <v>53</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="B62" s="3">
+        <v>310</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D62" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F62" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="B63" s="3">
+        <v>311</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="F63" t="s">
+        <v>53</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="B64" s="3">
+        <v>312</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D64" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="F64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" s="3">
         <v>313</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D48" s="2">
+      <c r="C65" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D65" s="3">
         <v>0.2</v>
       </c>
-      <c r="E48" t="s">
-        <v>199</v>
-      </c>
-      <c r="F48" t="s">
-        <v>53</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="K48" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D50" s="2">
+      <c r="E65" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F65" t="s">
+        <v>53</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="2:11">
+      <c r="B66" s="5">
+        <v>314</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D66" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G66" s="6">
+        <v>300</v>
+      </c>
+      <c r="H66" s="6">
+        <v>150</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J66" s="5"/>
+      <c r="K66" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="2:11">
+      <c r="B67" s="5">
+        <v>315</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D67" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G67" s="6">
+        <v>280</v>
+      </c>
+      <c r="H67" s="6">
+        <v>140</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J67" s="5"/>
+      <c r="K67" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="2:11">
+      <c r="B68" s="5">
+        <v>316</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D68" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G68" s="6">
+        <v>280</v>
+      </c>
+      <c r="H68" s="6">
+        <v>140</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J68" s="5"/>
+      <c r="K68" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="2:11">
+      <c r="B69" s="5">
+        <v>317</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D69" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G69" s="6">
+        <v>300</v>
+      </c>
+      <c r="H69" s="6">
+        <v>150</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J69" s="5"/>
+      <c r="K69" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="2:11">
+      <c r="B70" s="5">
+        <v>318</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D70" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G70" s="6">
+        <v>280</v>
+      </c>
+      <c r="H70" s="6">
+        <v>140</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="J70" s="5"/>
+      <c r="K70" s="7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="2:11">
+      <c r="B71" s="5">
+        <v>319</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D71" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G71" s="6">
+        <v>300</v>
+      </c>
+      <c r="H71" s="6">
+        <v>150</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J71" s="5"/>
+      <c r="K71" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="2:11">
+      <c r="B72" s="5">
+        <v>320</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D72" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G72" s="6">
+        <v>300</v>
+      </c>
+      <c r="H72" s="6">
+        <v>150</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="J72" s="5"/>
+      <c r="K72" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="2:11">
+      <c r="B73" s="5">
+        <v>321</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D73" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G73" s="6">
+        <v>300</v>
+      </c>
+      <c r="H73" s="6">
+        <v>150</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J73" s="5"/>
+      <c r="K73" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="2:11">
+      <c r="B74" s="5">
+        <v>322</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D74" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G74" s="6">
+        <v>300</v>
+      </c>
+      <c r="H74" s="6">
+        <v>150</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J74" s="5"/>
+      <c r="K74" s="7" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="2:11">
+      <c r="B75" s="5">
+        <v>323</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D75" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G75" s="6">
+        <v>280</v>
+      </c>
+      <c r="H75" s="6">
+        <v>140</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J75" s="5"/>
+      <c r="K75" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="2:11">
+      <c r="B76" s="5">
+        <v>324</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D76" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G76" s="6">
+        <v>300</v>
+      </c>
+      <c r="H76" s="6">
+        <v>150</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J76" s="5"/>
+      <c r="K76" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="2:11">
+      <c r="B77" s="5">
+        <v>325</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D77" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G77" s="6">
+        <v>300</v>
+      </c>
+      <c r="H77" s="6">
+        <v>150</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J77" s="5"/>
+      <c r="K77" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D79" s="3">
         <v>0.1</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E79" s="3">
         <v>235</v>
       </c>
-      <c r="F50" t="s">
-        <v>206</v>
-      </c>
-      <c r="G50" s="2">
+      <c r="F79" t="s">
+        <v>304</v>
+      </c>
+      <c r="G79" s="3">
         <v>650</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H79" s="3">
         <v>325</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J50" s="3">
+      <c r="I79" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J79" s="3">
         <v>1005</v>
       </c>
-      <c r="K50" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D51" s="2">
+      <c r="K79" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D80" s="3">
         <v>0.1</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F51" t="s">
-        <v>211</v>
-      </c>
-      <c r="G51" s="2">
+      <c r="E80" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F80" t="s">
+        <v>309</v>
+      </c>
+      <c r="G80" s="3">
         <v>600</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H80" s="3">
         <v>300</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J51" s="3">
+      <c r="I80" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="J80" s="3">
         <v>1006</v>
       </c>
-      <c r="K51" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D52" s="2">
+      <c r="K80" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D81" s="3">
         <v>0.1</v>
       </c>
-      <c r="E52" t="s">
-        <v>215</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-      <c r="G52" s="2">
+      <c r="E81" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F81" t="s">
+        <v>53</v>
+      </c>
+      <c r="G81" s="3">
         <v>580</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H81" s="3">
         <v>290</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="K52" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D53" s="2">
+      <c r="I81" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D82" s="3">
         <v>0.1</v>
       </c>
-      <c r="E53" t="s">
-        <v>219</v>
-      </c>
-      <c r="F53" t="s">
-        <v>53</v>
-      </c>
-      <c r="G53" s="2">
+      <c r="E82" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="F82" t="s">
+        <v>53</v>
+      </c>
+      <c r="G82" s="3">
         <v>530</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H82" s="3">
         <v>265</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K53" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
-      <c r="B54" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D54" s="2">
+      <c r="I82" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D83" s="3">
         <v>0.1</v>
       </c>
-      <c r="E54" t="s">
-        <v>223</v>
-      </c>
-      <c r="F54" t="s">
-        <v>53</v>
-      </c>
-      <c r="G54" s="2">
+      <c r="E83" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F83" t="s">
+        <v>53</v>
+      </c>
+      <c r="G83" s="3">
         <v>560</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H83" s="3">
         <v>280</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="K54" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D55" s="2">
+      <c r="I83" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D84" s="3">
         <v>0.1</v>
       </c>
-      <c r="E55" t="s">
-        <v>227</v>
-      </c>
-      <c r="F55" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55" s="2">
+      <c r="E84" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="F84" t="s">
+        <v>53</v>
+      </c>
+      <c r="G84" s="3">
         <v>620</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H84" s="3">
         <v>310</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="K55" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D56" s="2">
+      <c r="I84" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D85" s="3">
         <v>0.1</v>
       </c>
-      <c r="E56" t="s">
-        <v>231</v>
-      </c>
-      <c r="F56" t="s">
-        <v>53</v>
-      </c>
-      <c r="G56" s="2">
+      <c r="E85" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="F85" t="s">
+        <v>53</v>
+      </c>
+      <c r="G85" s="3">
         <v>590</v>
       </c>
-      <c r="H56" s="2">
+      <c r="H85" s="3">
         <v>295</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="K56" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D57" s="2">
+      <c r="I85" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D86" s="3">
         <v>0.1</v>
       </c>
-      <c r="E57" t="s">
-        <v>235</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
-      </c>
-      <c r="G57" s="2">
+      <c r="E86" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="F86" t="s">
+        <v>53</v>
+      </c>
+      <c r="G86" s="3">
         <v>640</v>
       </c>
-      <c r="H57" s="2">
+      <c r="H86" s="3">
         <v>320</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="K57" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D58" s="2">
+      <c r="I86" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D87" s="3">
         <v>0.1</v>
       </c>
-      <c r="E58" t="s">
-        <v>239</v>
-      </c>
-      <c r="F58" t="s">
-        <v>53</v>
-      </c>
-      <c r="G58" s="2">
+      <c r="E87" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F87" t="s">
+        <v>53</v>
+      </c>
+      <c r="G87" s="3">
         <v>610</v>
       </c>
-      <c r="H58" s="2">
+      <c r="H87" s="3">
         <v>305</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="K58" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D59" s="2">
+      <c r="I87" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D88" s="3">
         <v>0.1</v>
       </c>
-      <c r="E59" t="s">
-        <v>243</v>
-      </c>
-      <c r="F59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G59" s="2">
+      <c r="E88" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="F88" t="s">
+        <v>53</v>
+      </c>
+      <c r="G88" s="3">
         <v>580</v>
       </c>
-      <c r="H59" s="2">
+      <c r="H88" s="3">
         <v>290</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="K59" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D60" s="2">
+      <c r="I88" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D89" s="3">
         <v>0.1</v>
       </c>
-      <c r="E60" t="s">
-        <v>247</v>
-      </c>
-      <c r="F60" t="s">
-        <v>53</v>
-      </c>
-      <c r="G60" s="2">
+      <c r="E89" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F89" t="s">
+        <v>53</v>
+      </c>
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="H60" s="2">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="K60" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D61" s="2">
+      <c r="I89" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D90" s="3">
         <v>0.1</v>
       </c>
-      <c r="E61" t="s">
-        <v>251</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
-      </c>
-      <c r="G61" s="2">
+      <c r="E90" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="F90" t="s">
+        <v>53</v>
+      </c>
+      <c r="G90" s="3">
         <v>550</v>
       </c>
-      <c r="H61" s="2">
+      <c r="H90" s="3">
         <v>275</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="K61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D62" s="2">
+      <c r="I90" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D91" s="3">
         <v>0.1</v>
       </c>
-      <c r="E62" t="s">
-        <v>255</v>
-      </c>
-      <c r="F62" t="s">
-        <v>53</v>
-      </c>
-      <c r="G62" s="2">
+      <c r="E91" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="F91" t="s">
+        <v>53</v>
+      </c>
+      <c r="G91" s="3">
         <v>560</v>
       </c>
-      <c r="H62" s="2">
+      <c r="H91" s="3">
         <v>280</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="I91" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="J91" s="3">
         <v>1007</v>
       </c>
-      <c r="K62" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D63" s="2">
+      <c r="K91" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D92" s="3">
         <v>0.1</v>
       </c>
-      <c r="E63" t="s">
-        <v>259</v>
-      </c>
-      <c r="F63" t="s">
-        <v>53</v>
-      </c>
-      <c r="G63" s="2">
+      <c r="E92" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="F92" t="s">
+        <v>53</v>
+      </c>
+      <c r="G92" s="3">
         <v>630</v>
       </c>
-      <c r="H63" s="2">
+      <c r="H92" s="3">
         <v>315</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J63" s="3">
+      <c r="I92" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="J92" s="3">
         <v>1008</v>
       </c>
-      <c r="K63" t="s">
-        <v>261</v>
+      <c r="K92" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="2:11">
+      <c r="B93" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D93" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G93" s="6">
+        <v>600</v>
+      </c>
+      <c r="H93" s="6">
+        <v>300</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="J93" s="5"/>
+      <c r="K93" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" spans="2:11">
+      <c r="B94" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D94" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G94" s="6">
+        <v>600</v>
+      </c>
+      <c r="H94" s="6">
+        <v>300</v>
+      </c>
+      <c r="I94" s="8">
+        <v>40016</v>
+      </c>
+      <c r="J94" s="5"/>
+      <c r="K94" s="7" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" spans="2:11">
+      <c r="B95" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D95" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G95" s="6">
+        <v>630</v>
+      </c>
+      <c r="H95" s="6">
+        <v>315</v>
+      </c>
+      <c r="I95" s="8">
+        <v>40017</v>
+      </c>
+      <c r="J95" s="5"/>
+      <c r="K95" s="7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="2:11">
+      <c r="B96" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D96" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G96" s="6">
+        <v>630</v>
+      </c>
+      <c r="H96" s="6">
+        <v>315</v>
+      </c>
+      <c r="I96" s="8">
+        <v>40018</v>
+      </c>
+      <c r="J96" s="5"/>
+      <c r="K96" s="7" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" spans="2:11">
+      <c r="B97" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D97" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G97" s="6">
+        <v>600</v>
+      </c>
+      <c r="H97" s="6">
+        <v>300</v>
+      </c>
+      <c r="I97" s="8">
+        <v>40019</v>
+      </c>
+      <c r="J97" s="5"/>
+      <c r="K97" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" spans="2:11">
+      <c r="B98" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D98" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G98" s="6">
+        <v>630</v>
+      </c>
+      <c r="H98" s="6">
+        <v>315</v>
+      </c>
+      <c r="I98" s="8">
+        <v>40020</v>
+      </c>
+      <c r="J98" s="5"/>
+      <c r="K98" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" spans="2:11">
+      <c r="B99" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D99" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G99" s="6">
+        <v>600</v>
+      </c>
+      <c r="H99" s="6">
+        <v>300</v>
+      </c>
+      <c r="I99" s="8">
+        <v>40021</v>
+      </c>
+      <c r="J99" s="5"/>
+      <c r="K99" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" spans="2:11">
+      <c r="B100" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D100" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G100" s="6">
+        <v>600</v>
+      </c>
+      <c r="H100" s="6">
+        <v>300</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="J100" s="5"/>
+      <c r="K100" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" spans="2:11">
+      <c r="B101" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D101" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G101" s="6">
+        <v>600</v>
+      </c>
+      <c r="H101" s="6">
+        <v>300</v>
+      </c>
+      <c r="I101" s="8">
+        <v>40023</v>
+      </c>
+      <c r="J101" s="5"/>
+      <c r="K101" s="7" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" spans="2:11">
+      <c r="B102" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D102" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G102" s="6">
+        <v>600</v>
+      </c>
+      <c r="H102" s="6">
+        <v>300</v>
+      </c>
+      <c r="I102" s="8">
+        <v>40024</v>
+      </c>
+      <c r="J102" s="5"/>
+      <c r="K102" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="2:11">
+      <c r="B103" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D103" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G103" s="6">
+        <v>630</v>
+      </c>
+      <c r="H103" s="6">
+        <v>315</v>
+      </c>
+      <c r="I103" s="8">
+        <v>40025</v>
+      </c>
+      <c r="J103" s="5"/>
+      <c r="K103" s="7" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16050" windowHeight="10815"/>
+    <workbookView windowWidth="15480" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="482">
   <si>
     <t>##var</t>
   </si>
@@ -121,7 +121,7 @@
     <t>冒险证明</t>
   </si>
   <si>
-    <t>Sword1</t>
+    <t>AdventureCertificate</t>
   </si>
   <si>
     <t>结算时提供+1倍率</t>
@@ -133,7 +133,7 @@
     <t>青铜项链</t>
   </si>
   <si>
-    <t>Necklace1</t>
+    <t>BronzeNecklace</t>
   </si>
   <si>
     <t>亮出的每张方片牌在结算时提供+1倍率</t>
@@ -145,7 +145,7 @@
     <t>青铜手镯</t>
   </si>
   <si>
-    <t>Bracelet1</t>
+    <t>BronzeBracelet</t>
   </si>
   <si>
     <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
@@ -157,7 +157,7 @@
     <t>青铜耳环</t>
   </si>
   <si>
-    <t>Earrings1</t>
+    <t>BronzeEarrings</t>
   </si>
   <si>
     <t>亮出的每张红心牌在结算时提供+1倍率</t>
@@ -169,7 +169,7 @@
     <t>青铜戒指</t>
   </si>
   <si>
-    <t>Ring1</t>
+    <t>BronzeRing</t>
   </si>
   <si>
     <t>亮出的每张梅花牌在结算时提供+1倍率</t>
@@ -181,7 +181,7 @@
     <t>木制长剑</t>
   </si>
   <si>
-    <t>Sword2</t>
+    <t>WoodenLongSword</t>
   </si>
   <si>
     <t>亮出的对子牌型在结算时提供+2倍率</t>
@@ -193,7 +193,7 @@
     <t>木制法杖</t>
   </si>
   <si>
-    <t>Staff1</t>
+    <t>WoodenStaff</t>
   </si>
   <si>
     <t>亮出的顺子牌型在结算时提供+2倍率</t>
@@ -205,6 +205,9 @@
     <t>木制长弓</t>
   </si>
   <si>
+    <t>WoodenLongBow</t>
+  </si>
+  <si>
     <t>亮出的同花牌型在结算时提供+2倍率</t>
   </si>
   <si>
@@ -214,6 +217,9 @@
     <t>木制长矛</t>
   </si>
   <si>
+    <t>WoodenSpear</t>
+  </si>
+  <si>
     <t>亮出的同花顺牌型在结算时提供+2倍率</t>
   </si>
   <si>
@@ -223,6 +229,9 @@
     <t>木制长斧</t>
   </si>
   <si>
+    <t>WoodenLongAxe</t>
+  </si>
+  <si>
     <t>亮出的豹子牌型在结算时提供+2倍率</t>
   </si>
   <si>
@@ -232,6 +241,9 @@
     <t>木制圆盾</t>
   </si>
   <si>
+    <t>WoodenRoundShield</t>
+  </si>
+  <si>
     <t>每次受到的伤害降低1点</t>
   </si>
   <si>
@@ -241,6 +253,9 @@
     <t>小钱包</t>
   </si>
   <si>
+    <t>SmallWallet</t>
+  </si>
+  <si>
     <t>每回合开始时,获得1金币</t>
   </si>
   <si>
@@ -250,6 +265,9 @@
     <t>绷带</t>
   </si>
   <si>
+    <t>Bandage</t>
+  </si>
+  <si>
     <t>每回合开始时,恢复2点生命</t>
   </si>
   <si>
@@ -259,6 +277,9 @@
     <t>幸运草</t>
   </si>
   <si>
+    <t>LuckyClover</t>
+  </si>
+  <si>
     <t>每回合结束后,有10%概率获得5金币</t>
   </si>
   <si>
@@ -268,6 +289,9 @@
     <t>暴击拳套</t>
   </si>
   <si>
+    <t>CritGlove</t>
+  </si>
+  <si>
     <t>每回合结束后,提高1%暴击率,至多叠加20层</t>
   </si>
   <si>
@@ -277,6 +301,9 @@
     <t>垫脚石</t>
   </si>
   <si>
+    <t>SteppingStone</t>
+  </si>
+  <si>
     <t>每当你亮牌时大于场上所有敌人,就永久提供+1攻击力</t>
   </si>
   <si>
@@ -286,6 +313,9 @@
     <t>反击拳套</t>
   </si>
   <si>
+    <t>CounterGlove</t>
+  </si>
+  <si>
     <t>每当你受到伤害时,反弹2点伤害给攻击者</t>
   </si>
   <si>
@@ -298,6 +328,9 @@
     <t>白银项链</t>
   </si>
   <si>
+    <t>SilverNecklace</t>
+  </si>
+  <si>
     <t>55</t>
   </si>
   <si>
@@ -313,6 +346,9 @@
     <t>白银手镯</t>
   </si>
   <si>
+    <t>SilverBracelet</t>
+  </si>
+  <si>
     <t>20002</t>
   </si>
   <si>
@@ -325,6 +361,9 @@
     <t>白银耳环</t>
   </si>
   <si>
+    <t>SilverEarrings</t>
+  </si>
+  <si>
     <t>20003</t>
   </si>
   <si>
@@ -337,6 +376,9 @@
     <t>白银戒指</t>
   </si>
   <si>
+    <t>SilverRing</t>
+  </si>
+  <si>
     <t>20004</t>
   </si>
   <si>
@@ -349,6 +391,9 @@
     <t>铁制长剑</t>
   </si>
   <si>
+    <t>IronLongSword</t>
+  </si>
+  <si>
     <t>130</t>
   </si>
   <si>
@@ -367,6 +412,9 @@
     <t>铁制法杖</t>
   </si>
   <si>
+    <t>IronStaff</t>
+  </si>
+  <si>
     <t>135</t>
   </si>
   <si>
@@ -385,6 +433,9 @@
     <t>铁制长弓</t>
   </si>
   <si>
+    <t>IronLongBow</t>
+  </si>
+  <si>
     <t>20007</t>
   </si>
   <si>
@@ -397,6 +448,9 @@
     <t>铁制长矛</t>
   </si>
   <si>
+    <t>IronSpear</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
@@ -415,6 +469,9 @@
     <t>铁制长斧</t>
   </si>
   <si>
+    <t>IronLongAxe</t>
+  </si>
+  <si>
     <t>20009</t>
   </si>
   <si>
@@ -427,6 +484,9 @@
     <t>小精灵</t>
   </si>
   <si>
+    <t>Elf</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
@@ -445,6 +505,9 @@
     <t>白条</t>
   </si>
   <si>
+    <t>WhiteStrip</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
@@ -463,6 +526,9 @@
     <t>旗帜</t>
   </si>
   <si>
+    <t>Flag</t>
+  </si>
+  <si>
     <t>20012</t>
   </si>
   <si>
@@ -475,6 +541,9 @@
     <t>恐怖面具</t>
   </si>
   <si>
+    <t>HorrorMask</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
@@ -493,6 +562,9 @@
     <t>黄金面具</t>
   </si>
   <si>
+    <t>GoldMask</t>
+  </si>
+  <si>
     <t>20014</t>
   </si>
   <si>
@@ -505,6 +577,9 @@
     <t>黑白相机</t>
   </si>
   <si>
+    <t>BlackWhiteCamera</t>
+  </si>
+  <si>
     <t>20015</t>
   </si>
   <si>
@@ -517,6 +592,9 @@
     <t>丘比特</t>
   </si>
   <si>
+    <t>Cupid</t>
+  </si>
+  <si>
     <t>20016</t>
   </si>
   <si>
@@ -529,6 +607,9 @@
     <t>投资</t>
   </si>
   <si>
+    <t>Investment</t>
+  </si>
+  <si>
     <t>20017</t>
   </si>
   <si>
@@ -541,6 +622,9 @@
     <t>补偿金</t>
   </si>
   <si>
+    <t>CompensationFund</t>
+  </si>
+  <si>
     <t>20018</t>
   </si>
   <si>
@@ -553,6 +637,9 @@
     <t>和平鸽</t>
   </si>
   <si>
+    <t>PeaceDove</t>
+  </si>
+  <si>
     <t>20019</t>
   </si>
   <si>
@@ -565,6 +652,9 @@
     <t>勇气徽章</t>
   </si>
   <si>
+    <t>CourageBadge</t>
+  </si>
+  <si>
     <t>20020</t>
   </si>
   <si>
@@ -577,6 +667,9 @@
     <t>激励徽章</t>
   </si>
   <si>
+    <t>InspireBadge</t>
+  </si>
+  <si>
     <t>20021</t>
   </si>
   <si>
@@ -589,6 +682,9 @@
     <t>记账本</t>
   </si>
   <si>
+    <t>AccountBook</t>
+  </si>
+  <si>
     <t>20022</t>
   </si>
   <si>
@@ -601,6 +697,9 @@
     <t>铁饭碗</t>
   </si>
   <si>
+    <t>IronBowl</t>
+  </si>
+  <si>
     <t>20023</t>
   </si>
   <si>
@@ -613,6 +712,9 @@
     <t>永恒之心</t>
   </si>
   <si>
+    <t>EternalHeart</t>
+  </si>
+  <si>
     <t>20024</t>
   </si>
   <si>
@@ -625,6 +727,9 @@
     <t>幸运同花</t>
   </si>
   <si>
+    <t>LuckySameSuit</t>
+  </si>
+  <si>
     <t>20025</t>
   </si>
   <si>
@@ -637,6 +742,9 @@
     <t>运动鞋</t>
   </si>
   <si>
+    <t>SportsShoes</t>
+  </si>
+  <si>
     <t>20026</t>
   </si>
   <si>
@@ -649,6 +757,9 @@
     <t>保温杯</t>
   </si>
   <si>
+    <t>ThermalMug</t>
+  </si>
+  <si>
     <t>20027</t>
   </si>
   <si>
@@ -661,6 +772,9 @@
     <t>利息</t>
   </si>
   <si>
+    <t>Interest</t>
+  </si>
+  <si>
     <t>20028</t>
   </si>
   <si>
@@ -673,6 +787,9 @@
     <t>小算盘</t>
   </si>
   <si>
+    <t>LittleAbacus</t>
+  </si>
+  <si>
     <t>20029</t>
   </si>
   <si>
@@ -685,6 +802,9 @@
     <t>疯狂面具</t>
   </si>
   <si>
+    <t>MadMask</t>
+  </si>
+  <si>
     <t>300</t>
   </si>
   <si>
@@ -697,6 +817,9 @@
     <t>回旋刃</t>
   </si>
   <si>
+    <t>BoomerangBlade</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
@@ -712,6 +835,9 @@
     <t>致胜之剑</t>
   </si>
   <si>
+    <t>WinningSword</t>
+  </si>
+  <si>
     <t>290</t>
   </si>
   <si>
@@ -727,6 +853,9 @@
     <t>搓牌能手</t>
   </si>
   <si>
+    <t>CardMaster</t>
+  </si>
+  <si>
     <t>280</t>
   </si>
   <si>
@@ -739,6 +868,9 @@
     <t>会员卡</t>
   </si>
   <si>
+    <t>MemberCard</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
@@ -754,6 +886,9 @@
     <t>错峰出行</t>
   </si>
   <si>
+    <t>StaggeredTravel</t>
+  </si>
+  <si>
     <t>30006</t>
   </si>
   <si>
@@ -763,6 +898,9 @@
     <t>致命黑八</t>
   </si>
   <si>
+    <t>DeadlyBlackEight</t>
+  </si>
+  <si>
     <t>30007</t>
   </si>
   <si>
@@ -772,6 +910,9 @@
     <t>偶数韵律</t>
   </si>
   <si>
+    <t>EvenRhythm</t>
+  </si>
+  <si>
     <t>30008</t>
   </si>
   <si>
@@ -781,6 +922,9 @@
     <t>奇数韵律</t>
   </si>
   <si>
+    <t>OddRhythm</t>
+  </si>
+  <si>
     <t>30009</t>
   </si>
   <si>
@@ -790,6 +934,9 @@
     <t>贵族</t>
   </si>
   <si>
+    <t>Noble</t>
+  </si>
+  <si>
     <t>30010</t>
   </si>
   <si>
@@ -799,6 +946,9 @@
     <t>工资卡</t>
   </si>
   <si>
+    <t>SalaryCard</t>
+  </si>
+  <si>
     <t>30011</t>
   </si>
   <si>
@@ -808,6 +958,9 @@
     <t>训练</t>
   </si>
   <si>
+    <t>Training</t>
+  </si>
+  <si>
     <t>260</t>
   </si>
   <si>
@@ -820,6 +973,9 @@
     <t>九霄云外</t>
   </si>
   <si>
+    <t>BeyondTheClouds</t>
+  </si>
+  <si>
     <t>250</t>
   </si>
   <si>
@@ -835,6 +991,9 @@
     <t>后备计划</t>
   </si>
   <si>
+    <t>BackupPlan</t>
+  </si>
+  <si>
     <t>30014</t>
   </si>
   <si>
@@ -844,6 +1003,9 @@
     <t>护身符</t>
   </si>
   <si>
+    <t>Amulet</t>
+  </si>
+  <si>
     <t>30015</t>
   </si>
   <si>
@@ -853,6 +1015,9 @@
     <t>复盘笔记</t>
   </si>
   <si>
+    <t>ReviewPlan</t>
+  </si>
+  <si>
     <t>30016</t>
   </si>
   <si>
@@ -862,6 +1027,9 @@
     <t>幸运顺子</t>
   </si>
   <si>
+    <t>LuckyStraight</t>
+  </si>
+  <si>
     <t>30017</t>
   </si>
   <si>
@@ -871,6 +1039,9 @@
     <t>逆转沙漏</t>
   </si>
   <si>
+    <t>ReverseHourglass</t>
+  </si>
+  <si>
     <t>30018</t>
   </si>
   <si>
@@ -880,6 +1051,9 @@
     <t>练习卷</t>
   </si>
   <si>
+    <t>PracticePaper</t>
+  </si>
+  <si>
     <t>30019</t>
   </si>
   <si>
@@ -889,6 +1063,9 @@
     <t>小本本</t>
   </si>
   <si>
+    <t>LittleNotebook</t>
+  </si>
+  <si>
     <t>30020</t>
   </si>
   <si>
@@ -898,6 +1075,9 @@
     <t>高贵徽章</t>
   </si>
   <si>
+    <t>NobleBadge</t>
+  </si>
+  <si>
     <t>30021</t>
   </si>
   <si>
@@ -907,6 +1087,9 @@
     <t>陷阱</t>
   </si>
   <si>
+    <t>Trap</t>
+  </si>
+  <si>
     <t>30022</t>
   </si>
   <si>
@@ -916,6 +1099,9 @@
     <t>好运来</t>
   </si>
   <si>
+    <t>LuckComes</t>
+  </si>
+  <si>
     <t>30023</t>
   </si>
   <si>
@@ -925,6 +1111,9 @@
     <t>入场券</t>
   </si>
   <si>
+    <t>AdmissionTicket</t>
+  </si>
+  <si>
     <t>30024</t>
   </si>
   <si>
@@ -934,6 +1123,9 @@
     <t>条约</t>
   </si>
   <si>
+    <t>Treaty</t>
+  </si>
+  <si>
     <t>30025</t>
   </si>
   <si>
@@ -976,6 +1168,9 @@
     <t>老花眼</t>
   </si>
   <si>
+    <t>Presbyopia</t>
+  </si>
+  <si>
     <t>40003</t>
   </si>
   <si>
@@ -988,6 +1183,9 @@
     <t>周星星</t>
   </si>
   <si>
+    <t>ZhouXingxing</t>
+  </si>
+  <si>
     <t>40004</t>
   </si>
   <si>
@@ -1000,6 +1198,9 @@
     <t>穷途末路</t>
   </si>
   <si>
+    <t>DeadEnd</t>
+  </si>
+  <si>
     <t>40005</t>
   </si>
   <si>
@@ -1012,6 +1213,9 @@
     <t>收藏夹</t>
   </si>
   <si>
+    <t>FavoriteFolder</t>
+  </si>
+  <si>
     <t>40006</t>
   </si>
   <si>
@@ -1024,6 +1228,9 @@
     <t>奢侈品</t>
   </si>
   <si>
+    <t>LuxuryGoods</t>
+  </si>
+  <si>
     <t>40007</t>
   </si>
   <si>
@@ -1036,6 +1243,9 @@
     <t>近视眼</t>
   </si>
   <si>
+    <t>Myopia</t>
+  </si>
+  <si>
     <t>40008</t>
   </si>
   <si>
@@ -1048,6 +1258,9 @@
     <t>顶尖学者</t>
   </si>
   <si>
+    <t>TopScholar</t>
+  </si>
+  <si>
     <t>40009|400091</t>
   </si>
   <si>
@@ -1060,6 +1273,9 @@
     <t>老千</t>
   </si>
   <si>
+    <t>CheatPlayer</t>
+  </si>
+  <si>
     <t>40010</t>
   </si>
   <si>
@@ -1072,6 +1288,9 @@
     <t>天使</t>
   </si>
   <si>
+    <t>Angel</t>
+  </si>
+  <si>
     <t>40011</t>
   </si>
   <si>
@@ -1084,6 +1303,9 @@
     <t>双刃剑</t>
   </si>
   <si>
+    <t>DoubleEdgedSword</t>
+  </si>
+  <si>
     <t>40012|400121</t>
   </si>
   <si>
@@ -1096,6 +1318,9 @@
     <t>老搓家</t>
   </si>
   <si>
+    <t>OldCardPlayer</t>
+  </si>
+  <si>
     <t>40013</t>
   </si>
   <si>
@@ -1108,6 +1333,9 @@
     <t>幸运七</t>
   </si>
   <si>
+    <t>LuckySeven</t>
+  </si>
+  <si>
     <t>40014|400141|400142</t>
   </si>
   <si>
@@ -1120,6 +1348,9 @@
     <t>武林秘籍</t>
   </si>
   <si>
+    <t>MartialSecretBook</t>
+  </si>
+  <si>
     <t>40015|400151</t>
   </si>
   <si>
@@ -1132,6 +1363,9 @@
     <t>幸运对子</t>
   </si>
   <si>
+    <t>LuckyPair</t>
+  </si>
+  <si>
     <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
   </si>
   <si>
@@ -1141,6 +1375,9 @@
     <t>小强</t>
   </si>
   <si>
+    <t>LittleCockroach</t>
+  </si>
+  <si>
     <t>每输1次敌人,后续自身造成的所有伤害提高5%</t>
   </si>
   <si>
@@ -1150,6 +1387,9 @@
     <t>救命稻草</t>
   </si>
   <si>
+    <t>LifeSavingStraw</t>
+  </si>
+  <si>
     <t>如果你受到了1次致命伤害,会将血量降低为1,且下次造成伤害的同时恢复本次伤害20%的血量,每关生效1次</t>
   </si>
   <si>
@@ -1159,6 +1399,9 @@
     <t>专注</t>
   </si>
   <si>
+    <t>Concentration</t>
+  </si>
+  <si>
     <t>当场上只剩下一个敌人时,你对其造成的伤害+100%</t>
   </si>
   <si>
@@ -1168,6 +1411,9 @@
     <t>变形魔方</t>
   </si>
   <si>
+    <t>TransformCube</t>
+  </si>
+  <si>
     <t>每回合亮出的牌型强制提升一级</t>
   </si>
   <si>
@@ -1177,6 +1423,9 @@
     <t>毒药</t>
   </si>
   <si>
+    <t>Poison</t>
+  </si>
+  <si>
     <t>所有敌人血量降低30%[BOSS除外]</t>
   </si>
   <si>
@@ -1186,6 +1435,9 @@
     <t>刺客秘籍</t>
   </si>
   <si>
+    <t>AssassinSecretBook</t>
+  </si>
+  <si>
     <t>40022|400221</t>
   </si>
   <si>
@@ -1198,6 +1450,9 @@
     <t>透视眼</t>
   </si>
   <si>
+    <t>PerspectiveEye</t>
+  </si>
+  <si>
     <t>每回合透视次数+1</t>
   </si>
   <si>
@@ -1207,6 +1462,9 @@
     <t>聚宝盆</t>
   </si>
   <si>
+    <t>TreasurePot</t>
+  </si>
+  <si>
     <t>每回合结束后,本回合自身总伤害输出的2%转化为金币</t>
   </si>
   <si>
@@ -1214,6 +1472,9 @@
   </si>
   <si>
     <t>差距胶囊</t>
+  </si>
+  <si>
+    <t>GapCapsule</t>
   </si>
   <si>
     <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低15%</t>
@@ -1382,24 +1643,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1720,7 +1969,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1744,16 +1993,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1762,93 +2011,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1860,17 +2109,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2228,12 +2474,12 @@
     <col min="3" max="3" width="8.8" customWidth="1"/>
     <col min="4" max="4" width="4.78333333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="8.8" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" style="4" customWidth="1"/>
     <col min="7" max="7" width="5.975" style="3" customWidth="1"/>
     <col min="8" max="8" width="4.78333333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="5.53333333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="7.70833333333333" style="4" customWidth="1"/>
+    <col min="11" max="11" width="7.70833333333333" style="3" customWidth="1"/>
     <col min="12" max="12" width="11.875" style="2" customWidth="1"/>
     <col min="13" max="13" width="34.75" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
@@ -2255,7 +2501,7 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -2270,7 +2516,7 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2290,7 +2536,7 @@
       <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -2305,7 +2551,7 @@
       <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2325,7 +2571,7 @@
       <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -2340,12 +2586,11 @@
       <c r="J3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="14.25"/>
-    <row r="5" customFormat="1" ht="14.25" spans="1:13">
+    <row r="5" customFormat="1" spans="1:13">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>26</v>
@@ -2362,23 +2607,23 @@
       <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>20</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <v>10</v>
       </c>
       <c r="I5" s="3">
         <v>10001</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
     </row>
-    <row r="6" customFormat="1" ht="14.25" spans="1:13">
+    <row r="6" customFormat="1" spans="1:13">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>31</v>
@@ -2392,26 +2637,26 @@
       <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>20</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <v>10</v>
       </c>
       <c r="I6" s="3">
         <v>10002</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" ht="14.25" spans="1:13">
+    <row r="7" spans="1:13">
       <c r="B7" s="2" t="s">
         <v>35</v>
       </c>
@@ -2424,23 +2669,23 @@
       <c r="E7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>20</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="3">
         <v>10</v>
       </c>
       <c r="I7" s="3">
         <v>10003</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:13">
+    <row r="8" spans="1:13">
       <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
@@ -2453,23 +2698,23 @@
       <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>20</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <v>10</v>
       </c>
       <c r="I8" s="3">
         <v>10004</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:13">
+    <row r="9" spans="1:13">
       <c r="B9" s="2" t="s">
         <v>43</v>
       </c>
@@ -2482,23 +2727,23 @@
       <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>20</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>10</v>
       </c>
       <c r="I9" s="3">
         <v>10005</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:13">
+    <row r="10" spans="1:13">
       <c r="B10" s="2" t="s">
         <v>47</v>
       </c>
@@ -2511,23 +2756,23 @@
       <c r="E10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>25</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="3">
         <v>12</v>
       </c>
       <c r="I10" s="3">
         <v>10006</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:13">
+    <row r="11" spans="1:13">
       <c r="B11" s="2" t="s">
         <v>51</v>
       </c>
@@ -2540,23 +2785,23 @@
       <c r="E11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>25</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="3">
         <v>12</v>
       </c>
       <c r="I11" s="3">
         <v>10007</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:13">
+    <row r="12" spans="1:13">
       <c r="B12" s="2" t="s">
         <v>55</v>
       </c>
@@ -2569,25 +2814,25 @@
       <c r="E12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="4">
+      <c r="F12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="3">
         <v>25</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="3">
         <v>12</v>
       </c>
       <c r="I12" s="3">
         <v>10008</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:13">
+      <c r="K12" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="B13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>27</v>
@@ -2596,27 +2841,27 @@
         <v>0.8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="4">
+        <v>60</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="3">
         <v>28</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="3">
         <v>14</v>
       </c>
       <c r="I13" s="3">
         <v>10009</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>60</v>
+      <c r="K13" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>27</v>
@@ -2625,27 +2870,27 @@
         <v>0.8</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="4">
+        <v>64</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="3">
         <v>28</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="3">
         <v>14</v>
       </c>
       <c r="I14" s="3">
         <v>10010</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>63</v>
+      <c r="K14" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="B15" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>27</v>
@@ -2654,27 +2899,27 @@
         <v>0.8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="4">
+        <v>68</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="3">
         <v>30</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="3">
         <v>15</v>
       </c>
       <c r="I15" s="3">
         <v>10011</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>66</v>
+      <c r="K15" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:13">
       <c r="B16" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>27</v>
@@ -2682,29 +2927,29 @@
       <c r="D16" s="5">
         <v>0.8</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="E16" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="5">
         <v>25</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>12</v>
       </c>
       <c r="I16" s="5">
         <v>10012</v>
       </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="6" t="s">
-        <v>69</v>
+      <c r="K16" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:11">
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>27</v>
@@ -2712,29 +2957,29 @@
       <c r="D17" s="5">
         <v>0.8</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" s="6">
+      <c r="E17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="5">
         <v>25</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>12</v>
       </c>
       <c r="I17" s="5">
         <v>10013</v>
       </c>
       <c r="J17" s="5"/>
-      <c r="K17" s="6" t="s">
-        <v>72</v>
+      <c r="K17" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:11">
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>27</v>
@@ -2742,29 +2987,29 @@
       <c r="D18" s="5">
         <v>0.8</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="E18" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="5">
         <v>25</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>12</v>
       </c>
       <c r="I18" s="5">
         <v>10014</v>
       </c>
       <c r="J18" s="5"/>
-      <c r="K18" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="14.25" spans="1:11">
+      <c r="K18" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:11">
       <c r="B19" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>27</v>
@@ -2772,29 +3017,29 @@
       <c r="D19" s="5">
         <v>0.8</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="E19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="5">
         <v>30</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>15</v>
       </c>
       <c r="I19" s="5">
         <v>10015</v>
       </c>
       <c r="J19" s="5"/>
-      <c r="K19" s="6" t="s">
-        <v>78</v>
+      <c r="K19" s="5" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:11">
       <c r="B20" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>27</v>
@@ -2802,16 +3047,16 @@
       <c r="D20" s="5">
         <v>0.8</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="E20" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="5">
         <v>30</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>15</v>
       </c>
       <c r="I20" s="5">
@@ -2819,12 +3064,12 @@
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="7" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:11">
       <c r="B21" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>27</v>
@@ -2832,16 +3077,16 @@
       <c r="D21" s="5">
         <v>0.8</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="E21" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="5">
         <v>30</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>15</v>
       </c>
       <c r="I21" s="5">
@@ -2849,886 +3094,886 @@
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="B23" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D23" s="3">
         <v>0.4</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
+      <c r="E23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>90</v>
+        <v>100</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="B24" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D24" s="3">
         <v>0.4</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
+      <c r="E24" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>94</v>
+        <v>105</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25"/>
       <c r="B25" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D25" s="3">
         <v>0.4</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
+      <c r="E25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>98</v>
+        <v>110</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26"/>
       <c r="B26" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D26" s="3">
         <v>0.4</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
+        <v>113</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>102</v>
+        <v>115</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27"/>
       <c r="B27" s="2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D27" s="3">
         <v>0.4</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
+        <v>118</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>108</v>
+        <v>122</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28"/>
       <c r="B28" s="2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D28" s="3">
         <v>0.4</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
+        <v>125</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>114</v>
+        <v>129</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29"/>
       <c r="B29" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D29" s="3">
         <v>0.4</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
+        <v>132</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>118</v>
+        <v>134</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30"/>
       <c r="B30" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D30" s="3">
         <v>0.4</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
+        <v>137</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>124</v>
+        <v>141</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31"/>
       <c r="B31" s="2" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D31" s="3">
         <v>0.4</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
+        <v>144</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>128</v>
+        <v>146</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32"/>
       <c r="B32" s="2" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D32" s="3">
         <v>0.4</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
+        <v>149</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>134</v>
+        <v>153</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33"/>
       <c r="B33" s="2" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D33" s="3">
         <v>0.4</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
+        <v>156</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>140</v>
+        <v>160</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34"/>
       <c r="B34" s="2" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D34" s="3">
         <v>0.4</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
+        <v>163</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>144</v>
+        <v>165</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35"/>
       <c r="B35" s="2" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D35" s="3">
         <v>0.4</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
+        <v>168</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>150</v>
+        <v>172</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36"/>
       <c r="B36" s="2" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D36" s="3">
         <v>0.4</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
+        <v>175</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>154</v>
+        <v>177</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37"/>
       <c r="B37" s="2" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D37" s="3">
         <v>0.4</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
+        <v>180</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>158</v>
+        <v>182</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38"/>
       <c r="B38" s="2" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D38" s="3">
         <v>0.4</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
+        <v>185</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>162</v>
+        <v>187</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39"/>
       <c r="B39" s="2" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D39" s="3">
         <v>0.4</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="F39" t="s">
-        <v>53</v>
+        <v>190</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>166</v>
+        <v>192</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40"/>
       <c r="B40" s="2" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D40" s="3">
         <v>0.4</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F40" t="s">
-        <v>53</v>
+        <v>195</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>170</v>
+        <v>197</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:11">
       <c r="A41" s="7"/>
       <c r="B41" s="1" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D41" s="5">
         <v>0.4</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" s="6">
+      <c r="E41" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="G41" s="5">
         <v>140</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="5">
         <v>70</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="7" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:11">
       <c r="A42" s="7"/>
       <c r="B42" s="1" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D42" s="5">
         <v>0.4</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G42" s="6">
+      <c r="E42" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="G42" s="5">
         <v>150</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="5">
         <v>75</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="7" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:11">
       <c r="A43" s="7"/>
       <c r="B43" s="1" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D43" s="5">
         <v>0.4</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G43" s="6">
+      <c r="E43" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="G43" s="5">
         <v>150</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="5">
         <v>75</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="7" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:11">
       <c r="A44" s="7"/>
       <c r="B44" s="1" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D44" s="5">
         <v>0.4</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G44" s="6">
+      <c r="E44" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="G44" s="5">
         <v>140</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="5">
         <v>70</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="7" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:11">
       <c r="A45" s="7"/>
       <c r="B45" s="1" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D45" s="5">
         <v>0.4</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="6">
+      <c r="E45" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G45" s="5">
         <v>120</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="5">
         <v>60</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="7" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:11">
       <c r="A46" s="7"/>
       <c r="B46" s="1" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D46" s="5">
         <v>0.4</v>
       </c>
-      <c r="E46" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G46" s="6">
+      <c r="E46" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="G46" s="5">
         <v>150</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="5">
         <v>75</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="7" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:11">
       <c r="A47" s="7"/>
       <c r="B47" s="1" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D47" s="5">
         <v>0.4</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G47" s="6">
+      <c r="E47" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="G47" s="5">
         <v>150</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="5">
         <v>75</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="7" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:11">
       <c r="A48" s="7"/>
       <c r="B48" s="1" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D48" s="5">
         <v>0.4</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G48" s="6">
+      <c r="E48" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="G48" s="5">
         <v>150</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="5">
         <v>75</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="7" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:11">
       <c r="A49" s="7"/>
       <c r="B49" s="1" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D49" s="5">
         <v>0.4</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G49" s="6">
+      <c r="E49" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="G49" s="5">
         <v>140</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="5">
         <v>70</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="7" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:11">
       <c r="A50" s="7"/>
       <c r="B50" s="1" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D50" s="5">
         <v>0.4</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G50" s="6">
+      <c r="E50" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="G50" s="5">
         <v>140</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="5">
         <v>70</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="7" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:11">
       <c r="A51" s="7"/>
       <c r="B51" s="1" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D51" s="5">
         <v>0.4</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G51" s="6">
+      <c r="E51" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="G51" s="5">
         <v>140</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="5">
         <v>70</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>213</v>
+        <v>252</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="7" t="s">
-        <v>214</v>
+        <v>253</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -3744,31 +3989,31 @@
         <v>301</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D53" s="3">
         <v>0.2</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="F53" t="s">
-        <v>53</v>
+      <c r="E53" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>256</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>218</v>
+        <v>258</v>
       </c>
       <c r="J53" s="3">
         <v>1001</v>
       </c>
-      <c r="K53" s="4" t="s">
-        <v>219</v>
+      <c r="K53" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -3777,28 +4022,28 @@
         <v>302</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D54" s="3">
         <v>0.2</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="F54" t="s">
-        <v>53</v>
+      <c r="E54" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>261</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>224</v>
+        <v>264</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -3807,28 +4052,28 @@
         <v>303</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D55" s="3">
         <v>0.2</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="F55" t="s">
-        <v>53</v>
+      <c r="E55" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>267</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>229</v>
+        <v>270</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -3837,31 +4082,31 @@
         <v>304</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D56" s="3">
         <v>0.2</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="F56" t="s">
-        <v>53</v>
+      <c r="E56" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>273</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="J56" s="3">
         <v>1002</v>
       </c>
-      <c r="K56" s="4" t="s">
-        <v>233</v>
+      <c r="K56" s="3" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -3870,31 +4115,31 @@
         <v>305</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D57" s="3">
         <v>0.2</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="F57" t="s">
-        <v>53</v>
+      <c r="E57" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>278</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="J57" s="3">
         <v>1003</v>
       </c>
-      <c r="K57" s="4" t="s">
-        <v>238</v>
+      <c r="K57" s="3" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3902,31 +4147,31 @@
         <v>306</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D58" s="3">
         <v>0.2</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F58" t="s">
-        <v>53</v>
+      <c r="E58" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>240</v>
+        <v>285</v>
       </c>
       <c r="J58" s="3">
         <v>1004</v>
       </c>
-      <c r="K58" s="4" t="s">
-        <v>241</v>
+      <c r="K58" s="3" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3934,28 +4179,28 @@
         <v>307</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D59" s="3">
         <v>0.2</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="F59" t="s">
-        <v>53</v>
+      <c r="E59" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>288</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>244</v>
+        <v>289</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3963,28 +4208,28 @@
         <v>308</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D60" s="3">
         <v>0.2</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="F60" t="s">
-        <v>53</v>
+      <c r="E60" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>247</v>
+        <v>293</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -3992,28 +4237,28 @@
         <v>309</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D61" s="3">
         <v>0.2</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="F61" t="s">
-        <v>53</v>
+      <c r="E61" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>296</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>250</v>
+        <v>297</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4021,28 +4266,28 @@
         <v>310</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D62" s="3">
         <v>0.2</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="F62" t="s">
-        <v>53</v>
+      <c r="E62" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>300</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>253</v>
+        <v>301</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -4050,28 +4295,28 @@
         <v>311</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D63" s="3">
         <v>0.2</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="F63" t="s">
-        <v>53</v>
+      <c r="E63" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>304</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>217</v>
+        <v>257</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>256</v>
+        <v>305</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4079,28 +4324,28 @@
         <v>312</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D64" s="3">
         <v>0.2</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F64" t="s">
-        <v>53</v>
+      <c r="E64" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>260</v>
+        <v>310</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="65" spans="2:11">
@@ -4108,28 +4353,28 @@
         <v>313</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D65" s="3">
         <v>0.2</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="F65" t="s">
-        <v>53</v>
+      <c r="E65" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>313</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>263</v>
+        <v>315</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>265</v>
+        <v>316</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="2:11">
@@ -4137,29 +4382,29 @@
         <v>314</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D66" s="5">
         <v>0.2</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G66" s="6">
+      <c r="E66" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="G66" s="5">
         <v>300</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="5">
         <v>150</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="7" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="2:11">
@@ -4167,29 +4412,29 @@
         <v>315</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D67" s="5">
         <v>0.2</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G67" s="6">
+      <c r="E67" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G67" s="5">
         <v>280</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H67" s="5">
         <v>140</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="J67" s="5"/>
       <c r="K67" s="7" t="s">
-        <v>271</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="2:11">
@@ -4197,29 +4442,29 @@
         <v>316</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D68" s="5">
         <v>0.2</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G68" s="6">
+      <c r="E68" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="G68" s="5">
         <v>280</v>
       </c>
-      <c r="H68" s="6">
+      <c r="H68" s="5">
         <v>140</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="7" t="s">
-        <v>274</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="2:11">
@@ -4227,29 +4472,29 @@
         <v>317</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D69" s="5">
         <v>0.2</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G69" s="6">
+      <c r="E69" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G69" s="5">
         <v>300</v>
       </c>
-      <c r="H69" s="6">
+      <c r="H69" s="5">
         <v>150</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>276</v>
+        <v>332</v>
       </c>
       <c r="J69" s="5"/>
       <c r="K69" s="7" t="s">
-        <v>277</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="2:11">
@@ -4257,29 +4502,29 @@
         <v>318</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D70" s="5">
         <v>0.2</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G70" s="6">
+      <c r="E70" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G70" s="5">
         <v>280</v>
       </c>
-      <c r="H70" s="6">
+      <c r="H70" s="5">
         <v>140</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="7" t="s">
-        <v>280</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="2:11">
@@ -4287,29 +4532,29 @@
         <v>319</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D71" s="5">
         <v>0.2</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G71" s="6">
+      <c r="E71" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G71" s="5">
         <v>300</v>
       </c>
-      <c r="H71" s="6">
+      <c r="H71" s="5">
         <v>150</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>282</v>
+        <v>340</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="7" t="s">
-        <v>283</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="2:11">
@@ -4317,29 +4562,29 @@
         <v>320</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D72" s="5">
         <v>0.2</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G72" s="6">
+      <c r="E72" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="G72" s="5">
         <v>300</v>
       </c>
-      <c r="H72" s="6">
+      <c r="H72" s="5">
         <v>150</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>285</v>
+        <v>344</v>
       </c>
       <c r="J72" s="5"/>
       <c r="K72" s="7" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="2:11">
@@ -4347,29 +4592,29 @@
         <v>321</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D73" s="5">
         <v>0.2</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G73" s="6">
+      <c r="E73" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="G73" s="5">
         <v>300</v>
       </c>
-      <c r="H73" s="6">
+      <c r="H73" s="5">
         <v>150</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="J73" s="5"/>
       <c r="K73" s="7" t="s">
-        <v>289</v>
+        <v>349</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="2:11">
@@ -4377,29 +4622,29 @@
         <v>322</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D74" s="5">
         <v>0.2</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G74" s="6">
+      <c r="E74" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G74" s="5">
         <v>300</v>
       </c>
-      <c r="H74" s="6">
+      <c r="H74" s="5">
         <v>150</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="J74" s="5"/>
       <c r="K74" s="7" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="2:11">
@@ -4407,29 +4652,29 @@
         <v>323</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D75" s="5">
         <v>0.2</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G75" s="6">
+      <c r="E75" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G75" s="5">
         <v>280</v>
       </c>
-      <c r="H75" s="6">
+      <c r="H75" s="5">
         <v>140</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>294</v>
+        <v>356</v>
       </c>
       <c r="J75" s="5"/>
       <c r="K75" s="7" t="s">
-        <v>295</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="2:11">
@@ -4437,29 +4682,29 @@
         <v>324</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D76" s="5">
         <v>0.2</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G76" s="6">
+      <c r="E76" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="G76" s="5">
         <v>300</v>
       </c>
-      <c r="H76" s="6">
+      <c r="H76" s="5">
         <v>150</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>297</v>
+        <v>360</v>
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="7" t="s">
-        <v>298</v>
+        <v>361</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="2:11">
@@ -4467,37 +4712,37 @@
         <v>325</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>215</v>
+        <v>254</v>
       </c>
       <c r="D77" s="5">
         <v>0.2</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G77" s="6">
+      <c r="E77" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="G77" s="5">
         <v>300</v>
       </c>
-      <c r="H77" s="6">
+      <c r="H77" s="5">
         <v>150</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>300</v>
+        <v>364</v>
       </c>
       <c r="J77" s="5"/>
       <c r="K77" s="7" t="s">
-        <v>301</v>
+        <v>365</v>
       </c>
     </row>
     <row r="79" spans="2:11">
       <c r="B79" s="2" t="s">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D79" s="3">
         <v>0.1</v>
@@ -4505,8 +4750,8 @@
       <c r="E79" s="3">
         <v>235</v>
       </c>
-      <c r="F79" t="s">
-        <v>304</v>
+      <c r="F79" s="4" t="s">
+        <v>368</v>
       </c>
       <c r="G79" s="3">
         <v>650</v>
@@ -4515,30 +4760,30 @@
         <v>325</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>305</v>
+        <v>369</v>
       </c>
       <c r="J79" s="3">
         <v>1005</v>
       </c>
-      <c r="K79" s="4" t="s">
-        <v>306</v>
+      <c r="K79" s="3" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="80" spans="2:11">
       <c r="B80" s="2" t="s">
-        <v>307</v>
+        <v>371</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D80" s="3">
         <v>0.1</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F80" t="s">
-        <v>309</v>
+        <v>372</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="G80" s="3">
         <v>600</v>
@@ -4547,30 +4792,30 @@
         <v>300</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="J80" s="3">
         <v>1006</v>
       </c>
-      <c r="K80" s="4" t="s">
-        <v>311</v>
+      <c r="K80" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="81" spans="2:11">
       <c r="B81" s="2" t="s">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D81" s="3">
         <v>0.1</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="F81" t="s">
-        <v>53</v>
+      <c r="E81" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="G81" s="3">
         <v>580</v>
@@ -4579,27 +4824,27 @@
         <v>290</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="K81" s="4" t="s">
-        <v>315</v>
+        <v>379</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="2:11">
       <c r="B82" s="2" t="s">
-        <v>316</v>
+        <v>381</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D82" s="3">
         <v>0.1</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="F82" t="s">
-        <v>53</v>
+      <c r="E82" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>383</v>
       </c>
       <c r="G82" s="3">
         <v>530</v>
@@ -4608,27 +4853,27 @@
         <v>265</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>319</v>
+        <v>384</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="2" t="s">
-        <v>320</v>
+        <v>386</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D83" s="3">
         <v>0.1</v>
       </c>
-      <c r="E83" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="F83" t="s">
-        <v>53</v>
+      <c r="E83" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>388</v>
       </c>
       <c r="G83" s="3">
         <v>560</v>
@@ -4637,27 +4882,27 @@
         <v>280</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="K83" s="4" t="s">
-        <v>323</v>
+        <v>389</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="84" spans="2:11">
       <c r="B84" s="2" t="s">
-        <v>324</v>
+        <v>391</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D84" s="3">
         <v>0.1</v>
       </c>
-      <c r="E84" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="F84" t="s">
-        <v>53</v>
+      <c r="E84" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>393</v>
       </c>
       <c r="G84" s="3">
         <v>620</v>
@@ -4666,27 +4911,27 @@
         <v>310</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="K84" s="4" t="s">
-        <v>327</v>
+        <v>394</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="2" t="s">
-        <v>328</v>
+        <v>396</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D85" s="3">
         <v>0.1</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="F85" t="s">
-        <v>53</v>
+      <c r="E85" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>398</v>
       </c>
       <c r="G85" s="3">
         <v>590</v>
@@ -4695,27 +4940,27 @@
         <v>295</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>331</v>
+        <v>399</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="86" spans="2:11">
       <c r="B86" s="2" t="s">
-        <v>332</v>
+        <v>401</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D86" s="3">
         <v>0.1</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="F86" t="s">
-        <v>53</v>
+      <c r="E86" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>403</v>
       </c>
       <c r="G86" s="3">
         <v>640</v>
@@ -4724,27 +4969,27 @@
         <v>320</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>335</v>
+        <v>404</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="87" spans="2:11">
       <c r="B87" s="2" t="s">
-        <v>336</v>
+        <v>406</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D87" s="3">
         <v>0.1</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="F87" t="s">
-        <v>53</v>
+      <c r="E87" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>408</v>
       </c>
       <c r="G87" s="3">
         <v>610</v>
@@ -4753,27 +4998,27 @@
         <v>305</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>339</v>
+        <v>409</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="2" t="s">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D88" s="3">
         <v>0.1</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="F88" t="s">
-        <v>53</v>
+      <c r="E88" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>413</v>
       </c>
       <c r="G88" s="3">
         <v>580</v>
@@ -4782,27 +5027,27 @@
         <v>290</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="K88" s="4" t="s">
-        <v>343</v>
+        <v>414</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="89" spans="2:11">
       <c r="B89" s="2" t="s">
-        <v>344</v>
+        <v>416</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D89" s="3">
         <v>0.1</v>
       </c>
-      <c r="E89" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="F89" t="s">
-        <v>53</v>
+      <c r="E89" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>418</v>
       </c>
       <c r="G89" s="3">
         <v>600</v>
@@ -4811,27 +5056,27 @@
         <v>300</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>347</v>
+        <v>419</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:11">
       <c r="B90" s="2" t="s">
-        <v>348</v>
+        <v>421</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D90" s="3">
         <v>0.1</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F90" t="s">
-        <v>53</v>
+      <c r="E90" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>423</v>
       </c>
       <c r="G90" s="3">
         <v>550</v>
@@ -4840,27 +5085,27 @@
         <v>275</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>351</v>
+        <v>424</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="91" spans="2:11">
       <c r="B91" s="2" t="s">
-        <v>352</v>
+        <v>426</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D91" s="3">
         <v>0.1</v>
       </c>
-      <c r="E91" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="F91" t="s">
-        <v>53</v>
+      <c r="E91" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>428</v>
       </c>
       <c r="G91" s="3">
         <v>560</v>
@@ -4869,30 +5114,30 @@
         <v>280</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>354</v>
+        <v>429</v>
       </c>
       <c r="J91" s="3">
         <v>1007</v>
       </c>
-      <c r="K91" s="4" t="s">
-        <v>355</v>
+      <c r="K91" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="92" spans="2:11">
       <c r="B92" s="2" t="s">
-        <v>356</v>
+        <v>431</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D92" s="3">
         <v>0.1</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="F92" t="s">
-        <v>53</v>
+      <c r="E92" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="G92" s="3">
         <v>630</v>
@@ -4901,343 +5146,343 @@
         <v>315</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>358</v>
+        <v>434</v>
       </c>
       <c r="J92" s="3">
         <v>1008</v>
       </c>
-      <c r="K92" s="4" t="s">
-        <v>359</v>
+      <c r="K92" s="3" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:11">
       <c r="B93" s="1" t="s">
-        <v>360</v>
+        <v>436</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D93" s="5">
         <v>0.1</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G93" s="6">
+        <v>437</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="G93" s="5">
         <v>600</v>
       </c>
-      <c r="H93" s="6">
+      <c r="H93" s="5">
         <v>300</v>
       </c>
-      <c r="I93" s="8" t="s">
-        <v>362</v>
+      <c r="I93" s="5" t="s">
+        <v>439</v>
       </c>
       <c r="J93" s="5"/>
       <c r="K93" s="7" t="s">
-        <v>363</v>
+        <v>440</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:11">
       <c r="B94" s="1" t="s">
-        <v>364</v>
+        <v>441</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D94" s="5">
         <v>0.1</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G94" s="6">
+        <v>442</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G94" s="5">
         <v>600</v>
       </c>
-      <c r="H94" s="6">
+      <c r="H94" s="5">
         <v>300</v>
       </c>
-      <c r="I94" s="8">
+      <c r="I94" s="5">
         <v>40016</v>
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="7" t="s">
-        <v>366</v>
+        <v>444</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:11">
       <c r="B95" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="D95" s="5">
         <v>0.1</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G95" s="6">
+        <v>446</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="G95" s="5">
         <v>630</v>
       </c>
-      <c r="H95" s="6">
+      <c r="H95" s="5">
         <v>315</v>
       </c>
-      <c r="I95" s="8">
+      <c r="I95" s="5">
         <v>40017</v>
       </c>
       <c r="J95" s="5"/>
       <c r="K95" s="7" t="s">
-        <v>369</v>
+        <v>448</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" spans="2:11">
       <c r="B96" s="1" t="s">
-        <v>370</v>
+        <v>449</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D96" s="5">
         <v>0.1</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G96" s="6">
+        <v>450</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="G96" s="5">
         <v>630</v>
       </c>
-      <c r="H96" s="6">
+      <c r="H96" s="5">
         <v>315</v>
       </c>
-      <c r="I96" s="8">
+      <c r="I96" s="5">
         <v>40018</v>
       </c>
       <c r="J96" s="5"/>
       <c r="K96" s="7" t="s">
-        <v>372</v>
+        <v>452</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:11">
       <c r="B97" s="1" t="s">
-        <v>373</v>
+        <v>453</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D97" s="5">
         <v>0.1</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G97" s="6">
+        <v>454</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="G97" s="5">
         <v>600</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H97" s="5">
         <v>300</v>
       </c>
-      <c r="I97" s="8">
+      <c r="I97" s="5">
         <v>40019</v>
       </c>
       <c r="J97" s="5"/>
       <c r="K97" s="7" t="s">
-        <v>375</v>
+        <v>456</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:11">
       <c r="B98" s="1" t="s">
-        <v>376</v>
+        <v>457</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D98" s="5">
         <v>0.1</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G98" s="6">
+        <v>458</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="G98" s="5">
         <v>630</v>
       </c>
-      <c r="H98" s="6">
+      <c r="H98" s="5">
         <v>315</v>
       </c>
-      <c r="I98" s="8">
+      <c r="I98" s="5">
         <v>40020</v>
       </c>
       <c r="J98" s="5"/>
       <c r="K98" s="7" t="s">
-        <v>378</v>
+        <v>460</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:11">
       <c r="B99" s="1" t="s">
-        <v>379</v>
+        <v>461</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D99" s="5">
         <v>0.1</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G99" s="6">
+        <v>462</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="G99" s="5">
         <v>600</v>
       </c>
-      <c r="H99" s="6">
+      <c r="H99" s="5">
         <v>300</v>
       </c>
-      <c r="I99" s="8">
+      <c r="I99" s="5">
         <v>40021</v>
       </c>
       <c r="J99" s="5"/>
       <c r="K99" s="7" t="s">
-        <v>381</v>
+        <v>464</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:11">
       <c r="B100" s="1" t="s">
-        <v>382</v>
+        <v>465</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D100" s="5">
         <v>0.1</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G100" s="6">
+        <v>466</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="G100" s="5">
         <v>600</v>
       </c>
-      <c r="H100" s="6">
+      <c r="H100" s="5">
         <v>300</v>
       </c>
-      <c r="I100" s="8" t="s">
-        <v>384</v>
+      <c r="I100" s="5" t="s">
+        <v>468</v>
       </c>
       <c r="J100" s="5"/>
       <c r="K100" s="7" t="s">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:11">
       <c r="B101" s="1" t="s">
-        <v>386</v>
+        <v>470</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D101" s="5">
         <v>0.1</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G101" s="6">
+        <v>471</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="G101" s="5">
         <v>600</v>
       </c>
-      <c r="H101" s="6">
+      <c r="H101" s="5">
         <v>300</v>
       </c>
-      <c r="I101" s="8">
+      <c r="I101" s="5">
         <v>40023</v>
       </c>
       <c r="J101" s="5"/>
       <c r="K101" s="7" t="s">
-        <v>388</v>
+        <v>473</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:11">
       <c r="B102" s="1" t="s">
-        <v>389</v>
+        <v>474</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D102" s="5">
         <v>0.1</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G102" s="6">
+        <v>475</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="G102" s="5">
         <v>600</v>
       </c>
-      <c r="H102" s="6">
+      <c r="H102" s="5">
         <v>300</v>
       </c>
-      <c r="I102" s="8">
+      <c r="I102" s="5">
         <v>40024</v>
       </c>
       <c r="J102" s="5"/>
       <c r="K102" s="7" t="s">
-        <v>391</v>
+        <v>477</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:11">
       <c r="B103" s="1" t="s">
-        <v>392</v>
+        <v>478</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="D103" s="5">
         <v>0.1</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G103" s="6">
+        <v>479</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="G103" s="5">
         <v>630</v>
       </c>
-      <c r="H103" s="6">
+      <c r="H103" s="5">
         <v>315</v>
       </c>
-      <c r="I103" s="8">
+      <c r="I103" s="5">
         <v>40025</v>
       </c>
       <c r="J103" s="5"/>
       <c r="K103" s="7" t="s">
-        <v>394</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15480" windowHeight="10815"/>
+    <workbookView windowWidth="15600" windowHeight="10260"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="458">
   <si>
     <t>##var</t>
   </si>
@@ -184,7 +184,7 @@
     <t>WoodenLongSword</t>
   </si>
   <si>
-    <t>亮出的对子牌型在结算时提供+2倍率</t>
+    <t>亮出的对子牌型在结算时提供+3倍率</t>
   </si>
   <si>
     <t>107</t>
@@ -196,7 +196,7 @@
     <t>WoodenStaff</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+2倍率</t>
+    <t>亮出的顺子牌型在结算时提供+3倍率</t>
   </si>
   <si>
     <t>108</t>
@@ -208,7 +208,7 @@
     <t>WoodenLongBow</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+2倍率</t>
+    <t>亮出的同花牌型在结算时提供+3倍率</t>
   </si>
   <si>
     <t>109</t>
@@ -220,7 +220,7 @@
     <t>WoodenSpear</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+2倍率</t>
+    <t>亮出的同花顺牌型在结算时提供+5倍率</t>
   </si>
   <si>
     <t>110</t>
@@ -232,7 +232,7 @@
     <t>WoodenLongAxe</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+2倍率</t>
+    <t>亮出的豹子牌型在结算时提供+6倍率</t>
   </si>
   <si>
     <t>111</t>
@@ -280,7 +280,7 @@
     <t>LuckyClover</t>
   </si>
   <si>
-    <t>每回合结束后,有10%概率获得5金币</t>
+    <t>每回合结束后,有20%概率获得5金币</t>
   </si>
   <si>
     <t>115</t>
@@ -304,7 +304,7 @@
     <t>SteppingStone</t>
   </si>
   <si>
-    <t>每当你亮牌时大于场上所有敌人,就永久提供+1攻击力</t>
+    <t>每关首次亮牌大于场上所有敌人时,永久+1攻击力</t>
   </si>
   <si>
     <t>117</t>
@@ -316,7 +316,7 @@
     <t>CounterGlove</t>
   </si>
   <si>
-    <t>每当你受到伤害时,反弹2点伤害给攻击者</t>
+    <t>每当你受到伤害时,反弹3点伤害给攻击者</t>
   </si>
   <si>
     <t>201</t>
@@ -331,13 +331,10 @@
     <t>SilverNecklace</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>20001</t>
   </si>
   <si>
-    <t>亮出的每张方片牌在结算时提供+2攻击力</t>
+    <t>亮出的每张方片牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>202</t>
@@ -352,7 +349,7 @@
     <t>20002</t>
   </si>
   <si>
-    <t>亮出的每张黑桃牌在结算时提供+2攻击力</t>
+    <t>亮出的每张黑桃牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>203</t>
@@ -367,7 +364,7 @@
     <t>20003</t>
   </si>
   <si>
-    <t>亮出的每张红心牌在结算时提供+2攻击力</t>
+    <t>亮出的每张红心牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>204</t>
@@ -382,7 +379,7 @@
     <t>20004</t>
   </si>
   <si>
-    <t>亮出的每张梅花牌在结算时提供+2攻击力</t>
+    <t>亮出的每张梅花牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>205</t>
@@ -394,16 +391,10 @@
     <t>IronLongSword</t>
   </si>
   <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>20005</t>
   </si>
   <si>
-    <t>亮出的对子牌型在结算时提供+4攻击力</t>
+    <t>亮出的对子牌型在结算时提供+120攻击力</t>
   </si>
   <si>
     <t>206</t>
@@ -415,16 +406,10 @@
     <t>IronStaff</t>
   </si>
   <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
     <t>20006</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+6攻击力</t>
+    <t>亮出的顺子牌型在结算时提供+150攻击力</t>
   </si>
   <si>
     <t>207</t>
@@ -439,7 +424,7 @@
     <t>20007</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+6攻击力</t>
+    <t>亮出的同花牌型在结算时提供+150攻击力</t>
   </si>
   <si>
     <t>208</t>
@@ -451,16 +436,10 @@
     <t>IronSpear</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>20008</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+6攻击力</t>
+    <t>亮出的同花顺牌型在结算时提供+300攻击力</t>
   </si>
   <si>
     <t>209</t>
@@ -475,7 +454,7 @@
     <t>20009</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+6攻击力</t>
+    <t>亮出的豹子牌型在结算时提供+300攻击力</t>
   </si>
   <si>
     <t>210</t>
@@ -487,16 +466,10 @@
     <t>Elf</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>20010|200101</t>
   </si>
   <si>
-    <t>获得30点生命值上限,每回合结束后恢复2点当前生命值</t>
+    <t>获得30点生命值上限,每回合结束后恢复2点生命</t>
   </si>
   <si>
     <t>211</t>
@@ -508,12 +481,6 @@
     <t>WhiteStrip</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>20011</t>
   </si>
   <si>
@@ -544,16 +511,10 @@
     <t>HorrorMask</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>20013</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+2攻击力</t>
+    <t>亮出的每张人头牌在结算时提供+40攻击力</t>
   </si>
   <si>
     <t>214</t>
@@ -568,7 +529,7 @@
     <t>20014</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时有20%概率+1金币</t>
+    <t>亮出的每张人头牌在结算时获得2金币</t>
   </si>
   <si>
     <t>215</t>
@@ -613,7 +574,7 @@
     <t>20017</t>
   </si>
   <si>
-    <t>每花费20资金,英雄+1攻击力</t>
+    <t>每花费60金币,英雄永久+1攻击力</t>
   </si>
   <si>
     <t>218</t>
@@ -688,7 +649,7 @@
     <t>20022</t>
   </si>
   <si>
-    <t>每回合结束时,若本回合未造成任何伤害,则获得5金币</t>
+    <t>每回合结束时,若本回合未造成任何伤害,则获得10金币</t>
   </si>
   <si>
     <t>223</t>
@@ -703,7 +664,7 @@
     <t>20023</t>
   </si>
   <si>
-    <t>亮牌后无论胜负,均可获得1金币</t>
+    <t>亮牌后无论胜负,均可获得2金币</t>
   </si>
   <si>
     <t>224</t>
@@ -718,7 +679,7 @@
     <t>20024</t>
   </si>
   <si>
-    <t>每回合开始时,永久+2血量上限</t>
+    <t>每回合开始时,永久+1血量上限</t>
   </si>
   <si>
     <t>225</t>
@@ -778,7 +739,7 @@
     <t>20028</t>
   </si>
   <si>
-    <t>每拥有10金币,在回合结束后就会获得1金币</t>
+    <t>每通过1关时,每拥有15金币获得1金币,每关至多10金币</t>
   </si>
   <si>
     <t>229</t>
@@ -805,13 +766,10 @@
     <t>MadMask</t>
   </si>
   <si>
-    <t>300</t>
-  </si>
-  <si>
     <t>30001</t>
   </si>
   <si>
-    <t>造成伤害时,获得2%的生命窃取</t>
+    <t>造成伤害时,获得5%的生命窃取</t>
   </si>
   <si>
     <t>回旋刃</t>
@@ -820,16 +778,10 @@
     <t>BoomerangBlade</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
     <t>30002</t>
   </si>
   <si>
-    <t>亮出的牌点数提供的攻击力加成翻倍</t>
+    <t>亮出的牌点数提供的攻击力加成×3</t>
   </si>
   <si>
     <t>致胜之剑</t>
@@ -838,16 +790,10 @@
     <t>WinningSword</t>
   </si>
   <si>
-    <t>290</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
     <t>30003</t>
   </si>
   <si>
-    <t>结算伤害时,会将留在手牌上最大的牌点数转化为额外攻击力</t>
+    <t>结算伤害时,将留在手牌上最大的牌点数×4转化为额外攻击力</t>
   </si>
   <si>
     <t>搓牌能手</t>
@@ -856,9 +802,6 @@
     <t>CardMaster</t>
   </si>
   <si>
-    <t>280</t>
-  </si>
-  <si>
     <t>30004</t>
   </si>
   <si>
@@ -871,12 +814,6 @@
     <t>MemberCard</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>30005</t>
   </si>
   <si>
@@ -904,7 +841,7 @@
     <t>30007</t>
   </si>
   <si>
-    <t>亮出的每张8在结算时提供+6攻击力</t>
+    <t>亮出的每张8在结算时提供+200攻击力</t>
   </si>
   <si>
     <t>偶数韵律</t>
@@ -916,7 +853,7 @@
     <t>30008</t>
   </si>
   <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+6倍率</t>
   </si>
   <si>
     <t>奇数韵律</t>
@@ -928,7 +865,7 @@
     <t>30009</t>
   </si>
   <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+6倍率</t>
   </si>
   <si>
     <t>贵族</t>
@@ -940,7 +877,7 @@
     <t>30010</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+3倍率</t>
+    <t>亮出的每张人头牌在结算时提供+5倍率</t>
   </si>
   <si>
     <t>工资卡</t>
@@ -961,13 +898,10 @@
     <t>Training</t>
   </si>
   <si>
-    <t>260</t>
-  </si>
-  <si>
     <t>30012</t>
   </si>
   <si>
-    <t>亮出的每张牌的点数在结算时会使其提供的攻击力永久+1</t>
+    <t>每回合首次亮牌时,随机1张亮出牌点数的攻击力永久+1,至多累计+30</t>
   </si>
   <si>
     <t>九霄云外</t>
@@ -976,16 +910,10 @@
     <t>BeyondTheClouds</t>
   </si>
   <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>125</t>
-  </si>
-  <si>
     <t>30013</t>
   </si>
   <si>
-    <t>亮出的每张9在结算时提供10金币</t>
+    <t>亮出的每张9在结算时提供15金币</t>
   </si>
   <si>
     <t>后备计划</t>
@@ -997,7 +925,7 @@
     <t>30014</t>
   </si>
   <si>
-    <t>如果本回合牌型小于所有敌人,则立即获得10金币并回复15点生命值</t>
+    <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点生命值</t>
   </si>
   <si>
     <t>护身符</t>
@@ -1009,7 +937,7 @@
     <t>30015</t>
   </si>
   <si>
-    <t>每回合受到的第1次伤害完全免疫</t>
+    <t>每关受到的第1次伤害完全免疫</t>
   </si>
   <si>
     <t>复盘笔记</t>
@@ -1057,7 +985,7 @@
     <t>30019</t>
   </si>
   <si>
-    <t>每回合结束后,若本回合你未击杀任何敌人,则永久提供+0.5倍率</t>
+    <t>每回合结束后,若本回合你未击杀任何敌人,则永久提供+0.2倍率,至多+6</t>
   </si>
   <si>
     <t>小本本</t>
@@ -1081,7 +1009,7 @@
     <t>30021</t>
   </si>
   <si>
-    <t>每回合开始时,若生命值高于50%,获得10金币</t>
+    <t>每关开始时,若生命值高于50%,获得15金币</t>
   </si>
   <si>
     <t>陷阱</t>
@@ -1105,7 +1033,7 @@
     <t>30023</t>
   </si>
   <si>
-    <t>每回合有15%概率使本回合所有敌人亮出的牌型自动降一级</t>
+    <t>每回合有15%概率使本回合所有敌人亮出的牌型自动降1级</t>
   </si>
   <si>
     <t>入场券</t>
@@ -1117,7 +1045,7 @@
     <t>30024</t>
   </si>
   <si>
-    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
+    <t>每关开始时,对所有敌人造成2次自身攻击力的伤害</t>
   </si>
   <si>
     <t>条约</t>
@@ -1204,7 +1132,7 @@
     <t>40005</t>
   </si>
   <si>
-    <t>结算时,所有技能都无剩余使用次数,则提供+15倍率</t>
+    <t>结算时,所有技能都无剩余使用次数,则提供+12倍率</t>
   </si>
   <si>
     <t>406</t>
@@ -1219,7 +1147,7 @@
     <t>40006</t>
   </si>
   <si>
-    <t>每有1个收藏品,结算时提供+5倍率</t>
+    <t>每有1个收藏品,结算时提供+1倍率</t>
   </si>
   <si>
     <t>407</t>
@@ -1234,7 +1162,7 @@
     <t>40007</t>
   </si>
   <si>
-    <t>结算时,若未使用过搓牌,每个搓牌次数提供+5倍率</t>
+    <t>结算时,若未使用过搓牌,每个搓牌次数提供+3倍率</t>
   </si>
   <si>
     <t>408</t>
@@ -1264,7 +1192,7 @@
     <t>40009|400091</t>
   </si>
   <si>
-    <t>亮出的每张A在结算伤害时提供+5攻击力和+5倍率</t>
+    <t>亮出的每张A在结算伤害时提供+400攻击力和+8倍率</t>
   </si>
   <si>
     <t>410</t>
@@ -1279,7 +1207,7 @@
     <t>40010</t>
   </si>
   <si>
-    <t>亮牌时,将该牌型在本局内亮出过的次数来提供倍率</t>
+    <t>亮牌时,该牌型本局内每重复亮出1次提供+0.5倍率,至多+10</t>
   </si>
   <si>
     <t>411</t>
@@ -1309,7 +1237,7 @@
     <t>40012|400121</t>
   </si>
   <si>
-    <t>每回合失去2次搓牌机会,但结算时提供+20倍率</t>
+    <t>每回合失去2次搓牌机会,但结算时提供+10倍率</t>
   </si>
   <si>
     <t>413</t>
@@ -1324,7 +1252,7 @@
     <t>40013</t>
   </si>
   <si>
-    <t>每使用1次搓牌,结算时该收藏品永久提供+0.5倍率</t>
+    <t>每使用1次搓牌,结算时该收藏品永久提供+0.1倍率</t>
   </si>
   <si>
     <t>414</t>
@@ -1339,7 +1267,7 @@
     <t>40014|400141|400142</t>
   </si>
   <si>
-    <t>亮出的每张7结算时有7%概率提供+77攻击力和+7倍率</t>
+    <t>亮出的每张7结算时有25%概率提供+77攻击力和+7倍率</t>
   </si>
   <si>
     <t>415</t>
@@ -1390,7 +1318,7 @@
     <t>LifeSavingStraw</t>
   </si>
   <si>
-    <t>如果你受到了1次致命伤害,会将血量降低为1,且下次造成伤害的同时恢复本次伤害20%的血量,每关生效1次</t>
+    <t>受到致命伤害时血量降为1,且下次造成伤害后回复该伤害20%的血量,每关生效1次</t>
   </si>
   <si>
     <t>419</t>
@@ -1465,7 +1393,7 @@
     <t>TreasurePot</t>
   </si>
   <si>
-    <t>每回合结束后,本回合自身总伤害输出的2%转化为金币</t>
+    <t>每回合结束后,本回合自身总伤害输出的15%转化为金币</t>
   </si>
   <si>
     <t>425</t>
@@ -1477,7 +1405,7 @@
     <t>GapCapsule</t>
   </si>
   <si>
-    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低15%</t>
+    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
   </si>
 </sst>
 </file>
@@ -1948,175 +1876,161 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2466,30 +2380,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="2.93333333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.8" customWidth="1"/>
+    <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="2" customWidth="1"/>
     <col min="4" max="4" width="4.78333333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="8.8" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.1083333333333" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" style="3" customWidth="1"/>
     <col min="7" max="7" width="5.975" style="3" customWidth="1"/>
     <col min="8" max="8" width="4.78333333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="5.53333333333333" style="3" customWidth="1"/>
     <col min="11" max="11" width="7.70833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="34.75" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="12" max="12" width="11.875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="34.75" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -2501,7 +2415,7 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -2520,11 +2434,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
@@ -2536,7 +2450,7 @@
       <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="3" t="s">
@@ -2555,11 +2469,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -2571,7 +2485,7 @@
       <c r="E3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -2590,12 +2504,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:13">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:11">
+      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="3">
@@ -2608,27 +2521,23 @@
         <v>29</v>
       </c>
       <c r="G5" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I5" s="3">
         <v>10001</v>
       </c>
-      <c r="J5" s="3"/>
       <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" customFormat="1" spans="1:13">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="3">
@@ -2637,30 +2546,27 @@
       <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G6" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I6" s="3">
         <v>10002</v>
       </c>
-      <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D7" s="3">
@@ -2669,14 +2575,14 @@
       <c r="E7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="G7" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H7" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I7" s="3">
         <v>10003</v>
@@ -2685,11 +2591,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:11">
+      <c r="B8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="3">
@@ -2698,14 +2604,14 @@
       <c r="E8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H8" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I8" s="3">
         <v>10004</v>
@@ -2714,11 +2620,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:11">
+      <c r="B9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="3">
@@ -2727,14 +2633,14 @@
       <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G9" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H9" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I9" s="3">
         <v>10005</v>
@@ -2743,11 +2649,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:11">
+      <c r="B10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D10" s="3">
@@ -2756,14 +2662,14 @@
       <c r="E10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>49</v>
       </c>
       <c r="G10" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I10" s="3">
         <v>10006</v>
@@ -2772,11 +2678,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="1:11">
+      <c r="B11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D11" s="3">
@@ -2785,14 +2691,14 @@
       <c r="E11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G11" s="3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I11" s="3">
         <v>10007</v>
@@ -2801,11 +2707,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:11">
+      <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="3">
@@ -2814,14 +2720,14 @@
       <c r="E12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H12" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I12" s="3">
         <v>10008</v>
@@ -2830,11 +2736,11 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:11">
+      <c r="B13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="3">
@@ -2843,14 +2749,14 @@
       <c r="E13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>61</v>
       </c>
       <c r="G13" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H13" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I13" s="3">
         <v>10009</v>
@@ -2859,11 +2765,11 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="1:11">
+      <c r="B14" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D14" s="3">
@@ -2872,14 +2778,14 @@
       <c r="E14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G14" s="3">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="H14" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>10010</v>
@@ -2888,11 +2794,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:11">
+      <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="3">
@@ -2901,14 +2807,14 @@
       <c r="E15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I15" s="3">
         <v>10011</v>
@@ -2917,33 +2823,33 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:13">
+    <row r="16" s="1" customFormat="1" spans="1:11">
       <c r="B16" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="3">
         <v>0.8</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="5">
-        <v>25</v>
-      </c>
-      <c r="H16" s="5">
-        <v>12</v>
-      </c>
-      <c r="I16" s="5">
+      <c r="G16" s="3">
+        <v>30</v>
+      </c>
+      <c r="H16" s="3">
+        <v>15</v>
+      </c>
+      <c r="I16" s="3">
         <v>10012</v>
       </c>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5" t="s">
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2954,26 +2860,26 @@
       <c r="C17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="3">
         <v>0.8</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="5">
-        <v>25</v>
-      </c>
-      <c r="H17" s="5">
-        <v>12</v>
-      </c>
-      <c r="I17" s="5">
+      <c r="G17" s="3">
+        <v>35</v>
+      </c>
+      <c r="H17" s="3">
+        <v>17</v>
+      </c>
+      <c r="I17" s="3">
         <v>10013</v>
       </c>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5" t="s">
+      <c r="J17" s="3"/>
+      <c r="K17" s="3" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2984,26 +2890,26 @@
       <c r="C18" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="3">
         <v>0.8</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="5">
-        <v>25</v>
-      </c>
-      <c r="H18" s="5">
-        <v>12</v>
-      </c>
-      <c r="I18" s="5">
+      <c r="G18" s="3">
+        <v>26</v>
+      </c>
+      <c r="H18" s="3">
+        <v>13</v>
+      </c>
+      <c r="I18" s="3">
         <v>10014</v>
       </c>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5" t="s">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3014,26 +2920,26 @@
       <c r="C19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="3">
         <v>0.8</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="5">
-        <v>30</v>
-      </c>
-      <c r="H19" s="5">
-        <v>15</v>
-      </c>
-      <c r="I19" s="5">
+      <c r="G19" s="3">
+        <v>22</v>
+      </c>
+      <c r="H19" s="3">
+        <v>11</v>
+      </c>
+      <c r="I19" s="3">
         <v>10015</v>
       </c>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5" t="s">
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3044,26 +2950,26 @@
       <c r="C20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="3">
         <v>0.8</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G20" s="5">
-        <v>30</v>
-      </c>
-      <c r="H20" s="5">
-        <v>15</v>
-      </c>
-      <c r="I20" s="5">
+      <c r="G20" s="3">
+        <v>28</v>
+      </c>
+      <c r="H20" s="3">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3">
         <v>10016</v>
       </c>
-      <c r="J20" s="5"/>
-      <c r="K20" s="7" t="s">
+      <c r="J20" s="3"/>
+      <c r="K20" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3074,34 +2980,34 @@
       <c r="C21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="3">
         <v>0.8</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="5">
-        <v>30</v>
-      </c>
-      <c r="H21" s="5">
-        <v>15</v>
-      </c>
-      <c r="I21" s="5">
+      <c r="G21" s="3">
+        <v>20</v>
+      </c>
+      <c r="H21" s="3">
+        <v>10</v>
+      </c>
+      <c r="I21" s="3">
         <v>10017</v>
       </c>
-      <c r="J21" s="5"/>
-      <c r="K21" s="7" t="s">
+      <c r="J21" s="3"/>
+      <c r="K21" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="3">
@@ -3110,910 +3016,910 @@
       <c r="E23" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" s="2" t="s">
+      <c r="G23" s="1">
+        <v>115</v>
+      </c>
+      <c r="H23" s="1">
+        <v>57</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="K23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="K23" s="3" t="s">
+    </row>
+    <row r="24" spans="1:11">
+      <c r="B24" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="B24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D24" s="3">
         <v>0.4</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="1">
+        <v>115</v>
+      </c>
+      <c r="H24" s="1">
+        <v>57</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I24" s="2" t="s">
+      <c r="K24" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25"/>
-      <c r="B25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="B25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D25" s="3">
         <v>0.4</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="1">
+        <v>115</v>
+      </c>
+      <c r="H25" s="1">
+        <v>57</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="2" t="s">
+      <c r="K25" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26"/>
-      <c r="B26" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D26" s="3">
         <v>0.4</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="1">
+        <v>115</v>
+      </c>
+      <c r="H26" s="1">
+        <v>57</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="2" t="s">
+      <c r="K26" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27"/>
-      <c r="B27" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D27" s="3">
         <v>0.4</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="1">
+        <v>120</v>
+      </c>
+      <c r="H27" s="1">
+        <v>60</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="K27" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28"/>
-      <c r="B28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D28" s="3">
         <v>0.4</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" s="1">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1">
+        <v>50</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29"/>
-      <c r="B29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B29" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D29" s="3">
         <v>0.4</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G29" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>134</v>
+      <c r="G29" s="1">
+        <v>155</v>
+      </c>
+      <c r="H29" s="1">
+        <v>77</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30"/>
-      <c r="B30" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B30" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D30" s="3">
         <v>0.4</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" s="1">
+        <v>75</v>
+      </c>
+      <c r="H30" s="1">
+        <v>37</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31"/>
-      <c r="B31" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D31" s="3">
         <v>0.4</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="1">
+        <v>75</v>
+      </c>
+      <c r="H31" s="1">
+        <v>37</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="K31" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32"/>
-      <c r="B32" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="B32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D32" s="3">
         <v>0.4</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G32" s="1">
+        <v>110</v>
+      </c>
+      <c r="H32" s="1">
+        <v>55</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33"/>
-      <c r="B33" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D33" s="3">
         <v>0.4</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G33" s="1">
+        <v>80</v>
+      </c>
+      <c r="H33" s="1">
+        <v>40</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34"/>
-      <c r="B34" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="B34" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D34" s="3">
         <v>0.4</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G34" s="1">
+        <v>105</v>
+      </c>
+      <c r="H34" s="1">
+        <v>52</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35"/>
-      <c r="B35" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="B35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D35" s="3">
         <v>0.4</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G35" s="1">
+        <v>135</v>
+      </c>
+      <c r="H35" s="1">
+        <v>67</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36"/>
-      <c r="B36" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D36" s="3">
         <v>0.4</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>177</v>
+        <v>162</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G36" s="1">
+        <v>70</v>
+      </c>
+      <c r="H36" s="1">
+        <v>35</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37"/>
-      <c r="B37" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="B37" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D37" s="3">
         <v>0.4</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" s="1">
+        <v>110</v>
+      </c>
+      <c r="H37" s="1">
+        <v>55</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38"/>
-      <c r="B38" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="B38" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D38" s="3">
         <v>0.4</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>187</v>
+        <v>172</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38" s="1">
+        <v>110</v>
+      </c>
+      <c r="H38" s="1">
+        <v>55</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39"/>
-      <c r="B39" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C39" s="2" t="s">
+      <c r="B39" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D39" s="3">
         <v>0.4</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="G39" s="1">
+        <v>115</v>
+      </c>
+      <c r="H39" s="1">
+        <v>57</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40"/>
-      <c r="B40" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="B40" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D40" s="3">
         <v>0.4</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G40" s="1">
+        <v>80</v>
+      </c>
+      <c r="H40" s="1">
+        <v>40</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:11">
-      <c r="A41" s="7"/>
+      <c r="A41"/>
       <c r="B41" s="1" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="3">
         <v>0.4</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="G41" s="5">
-        <v>140</v>
-      </c>
-      <c r="H41" s="5">
-        <v>70</v>
+      <c r="E41" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G41" s="3">
+        <v>85</v>
+      </c>
+      <c r="H41" s="3">
+        <v>42</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="J41" s="5"/>
-      <c r="K41" s="7" t="s">
-        <v>203</v>
+        <v>189</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:11">
-      <c r="A42" s="7"/>
+      <c r="A42"/>
       <c r="B42" s="1" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="3">
         <v>0.4</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="G42" s="5">
-        <v>150</v>
-      </c>
-      <c r="H42" s="5">
+      <c r="E42" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G42" s="3">
         <v>75</v>
       </c>
+      <c r="H42" s="3">
+        <v>37</v>
+      </c>
       <c r="I42" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="J42" s="5"/>
-      <c r="K42" s="7" t="s">
-        <v>208</v>
+        <v>194</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:11">
-      <c r="A43" s="7"/>
+      <c r="A43"/>
       <c r="B43" s="1" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="3">
         <v>0.4</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="G43" s="5">
-        <v>150</v>
-      </c>
-      <c r="H43" s="5">
+      <c r="E43" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G43" s="3">
         <v>75</v>
       </c>
+      <c r="H43" s="3">
+        <v>37</v>
+      </c>
       <c r="I43" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="J43" s="5"/>
-      <c r="K43" s="7" t="s">
-        <v>213</v>
+        <v>199</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:11">
-      <c r="A44" s="7"/>
+      <c r="A44"/>
       <c r="B44" s="1" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="3">
         <v>0.4</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="G44" s="5">
-        <v>140</v>
-      </c>
-      <c r="H44" s="5">
-        <v>70</v>
+      <c r="E44" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" s="3">
+        <v>80</v>
+      </c>
+      <c r="H44" s="3">
+        <v>40</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="J44" s="5"/>
-      <c r="K44" s="7" t="s">
-        <v>218</v>
+        <v>204</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:11">
-      <c r="A45" s="7"/>
+      <c r="A45"/>
       <c r="B45" s="1" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="3">
         <v>0.4</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G45" s="5">
-        <v>120</v>
-      </c>
-      <c r="H45" s="5">
-        <v>60</v>
+      <c r="E45" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G45" s="3">
+        <v>70</v>
+      </c>
+      <c r="H45" s="3">
+        <v>35</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="J45" s="5"/>
-      <c r="K45" s="7" t="s">
-        <v>223</v>
+        <v>209</v>
+      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:11">
-      <c r="A46" s="7"/>
+      <c r="A46"/>
       <c r="B46" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="3">
         <v>0.4</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="G46" s="5">
-        <v>150</v>
-      </c>
-      <c r="H46" s="5">
+      <c r="E46" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G46" s="3">
         <v>75</v>
       </c>
+      <c r="H46" s="3">
+        <v>37</v>
+      </c>
       <c r="I46" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="7" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:11">
-      <c r="A47" s="7"/>
+      <c r="A47"/>
       <c r="B47" s="1" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="3">
         <v>0.4</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="G47" s="5">
-        <v>150</v>
-      </c>
-      <c r="H47" s="5">
-        <v>75</v>
+      <c r="E47" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G47" s="3">
+        <v>70</v>
+      </c>
+      <c r="H47" s="3">
+        <v>35</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="J47" s="5"/>
-      <c r="K47" s="7" t="s">
-        <v>233</v>
+        <v>219</v>
+      </c>
+      <c r="J47" s="3"/>
+      <c r="K47" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:11">
-      <c r="A48" s="7"/>
+      <c r="A48"/>
       <c r="B48" s="1" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="3">
         <v>0.4</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="G48" s="5">
-        <v>150</v>
-      </c>
-      <c r="H48" s="5">
-        <v>75</v>
+      <c r="E48" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G48" s="3">
+        <v>120</v>
+      </c>
+      <c r="H48" s="3">
+        <v>60</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="J48" s="5"/>
-      <c r="K48" s="7" t="s">
-        <v>238</v>
+        <v>224</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:11">
-      <c r="A49" s="7"/>
+      <c r="A49"/>
       <c r="B49" s="1" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="3">
         <v>0.4</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="G49" s="5">
-        <v>140</v>
-      </c>
-      <c r="H49" s="5">
-        <v>70</v>
+      <c r="E49" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G49" s="3">
+        <v>110</v>
+      </c>
+      <c r="H49" s="3">
+        <v>55</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="J49" s="5"/>
-      <c r="K49" s="7" t="s">
-        <v>243</v>
+        <v>229</v>
+      </c>
+      <c r="J49" s="3"/>
+      <c r="K49" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:11">
-      <c r="A50" s="7"/>
+      <c r="A50"/>
       <c r="B50" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="3">
         <v>0.4</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="G50" s="5">
-        <v>140</v>
-      </c>
-      <c r="H50" s="5">
+      <c r="E50" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G50" s="3">
         <v>70</v>
       </c>
+      <c r="H50" s="3">
+        <v>35</v>
+      </c>
       <c r="I50" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="J50" s="5"/>
-      <c r="K50" s="7" t="s">
-        <v>248</v>
+        <v>234</v>
+      </c>
+      <c r="J50" s="3"/>
+      <c r="K50" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:11">
-      <c r="A51" s="7"/>
+      <c r="A51"/>
       <c r="B51" s="1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="3">
         <v>0.4</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="G51" s="5">
-        <v>140</v>
-      </c>
-      <c r="H51" s="5">
-        <v>70</v>
+      <c r="E51" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G51" s="3">
+        <v>160</v>
+      </c>
+      <c r="H51" s="3">
+        <v>80</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J51" s="5"/>
-      <c r="K51" s="7" t="s">
-        <v>253</v>
+        <v>239</v>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52"/>
       <c r="B52" s="3"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
     </row>
     <row r="53" spans="1:11">
       <c r="A53"/>
       <c r="B53" s="3">
         <v>301</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>254</v>
+      <c r="C53" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D53" s="3">
         <v>0.2</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>258</v>
+        <v>242</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G53" s="1">
+        <v>190</v>
+      </c>
+      <c r="H53" s="1">
+        <v>95</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="J53" s="3">
         <v>1001</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4021,29 +3927,29 @@
       <c r="B54" s="3">
         <v>302</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>254</v>
+      <c r="C54" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D54" s="3">
         <v>0.2</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>264</v>
+        <v>246</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G54" s="1">
+        <v>270</v>
+      </c>
+      <c r="H54" s="1">
+        <v>135</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4051,29 +3957,29 @@
       <c r="B55" s="3">
         <v>303</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>254</v>
+      <c r="C55" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D55" s="3">
         <v>0.2</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>270</v>
+        <v>250</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G55" s="1">
+        <v>190</v>
+      </c>
+      <c r="H55" s="1">
+        <v>95</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4081,32 +3987,32 @@
       <c r="B56" s="3">
         <v>304</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>254</v>
+      <c r="C56" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D56" s="3">
         <v>0.2</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>275</v>
+        <v>254</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G56" s="1">
+        <v>185</v>
+      </c>
+      <c r="H56" s="1">
+        <v>92</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="J56" s="3">
         <v>1002</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4114,635 +4020,635 @@
       <c r="B57" s="3">
         <v>305</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>254</v>
+      <c r="C57" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D57" s="3">
         <v>0.2</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>281</v>
+        <v>258</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G57" s="1">
+        <v>170</v>
+      </c>
+      <c r="H57" s="1">
+        <v>85</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="J57" s="3">
         <v>1003</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="B58" s="3">
         <v>306</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>254</v>
+      <c r="C58" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D58" s="3">
         <v>0.2</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>285</v>
+        <v>262</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G58" s="1">
+        <v>240</v>
+      </c>
+      <c r="H58" s="1">
+        <v>120</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="J58" s="3">
         <v>1004</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="B59" s="3">
         <v>307</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>254</v>
+      <c r="C59" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D59" s="3">
         <v>0.2</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G59" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="G59" s="1">
+        <v>265</v>
+      </c>
+      <c r="H59" s="1">
+        <v>132</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="K59" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="B60" s="3">
         <v>308</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>254</v>
+      <c r="C60" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D60" s="3">
         <v>0.2</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>293</v>
+        <v>270</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G60" s="1">
+        <v>360</v>
+      </c>
+      <c r="H60" s="1">
+        <v>180</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="B61" s="3">
         <v>309</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>254</v>
+      <c r="C61" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D61" s="3">
         <v>0.2</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>297</v>
+        <v>274</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G61" s="1">
+        <v>350</v>
+      </c>
+      <c r="H61" s="1">
+        <v>175</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="B62" s="3">
         <v>310</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>254</v>
+      <c r="C62" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D62" s="3">
         <v>0.2</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>301</v>
+        <v>278</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="G62" s="1">
+        <v>275</v>
+      </c>
+      <c r="H62" s="1">
+        <v>137</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="B63" s="3">
         <v>311</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>254</v>
+      <c r="C63" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D63" s="3">
         <v>0.2</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>305</v>
+        <v>282</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G63" s="1">
+        <v>170</v>
+      </c>
+      <c r="H63" s="1">
+        <v>85</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="B64" s="3">
         <v>312</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>254</v>
+      <c r="C64" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D64" s="3">
         <v>0.2</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>310</v>
+        <v>286</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G64" s="1">
+        <v>210</v>
+      </c>
+      <c r="H64" s="1">
+        <v>105</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65" spans="2:11">
       <c r="B65" s="3">
         <v>313</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>254</v>
+      <c r="C65" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="D65" s="3">
         <v>0.2</v>
       </c>
       <c r="E65" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G65" s="1">
+        <v>160</v>
+      </c>
+      <c r="H65" s="1">
+        <v>80</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="2:11">
+      <c r="B66" s="3">
+        <v>314</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D66" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G66" s="3">
+        <v>180</v>
+      </c>
+      <c r="H66" s="3">
+        <v>90</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J66" s="3"/>
+      <c r="K66" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="2:11">
+      <c r="B67" s="3">
+        <v>315</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D67" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G67" s="3">
+        <v>380</v>
+      </c>
+      <c r="H67" s="3">
+        <v>190</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J67" s="3"/>
+      <c r="K67" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="2:11">
+      <c r="B68" s="3">
+        <v>316</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G68" s="3">
+        <v>170</v>
+      </c>
+      <c r="H68" s="3">
+        <v>85</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="2:11">
+      <c r="B69" s="3">
+        <v>317</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D69" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G69" s="3">
+        <v>175</v>
+      </c>
+      <c r="H69" s="3">
+        <v>87</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="J69" s="3"/>
+      <c r="K69" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="2:11">
+      <c r="B70" s="3">
+        <v>318</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D70" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G70" s="3">
+        <v>170</v>
+      </c>
+      <c r="H70" s="3">
+        <v>85</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="J70" s="3"/>
+      <c r="K70" t="s">
         <v>313</v>
       </c>
-      <c r="G65" s="2" t="s">
+    </row>
+    <row r="71" s="1" customFormat="1" spans="2:11">
+      <c r="B71" s="3">
+        <v>319</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H65" s="2" t="s">
+      <c r="F71" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="I65" s="2" t="s">
+      <c r="G71" s="3">
+        <v>160</v>
+      </c>
+      <c r="H71" s="3">
+        <v>80</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="J71" s="3"/>
+      <c r="K71" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" spans="2:11">
-      <c r="B66" s="5">
-        <v>314</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D66" s="5">
+    <row r="72" s="1" customFormat="1" spans="2:11">
+      <c r="B72" s="3">
+        <v>320</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D72" s="3">
         <v>0.2</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="E72" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F72" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="G66" s="5">
-        <v>300</v>
-      </c>
-      <c r="H66" s="5">
-        <v>150</v>
-      </c>
-      <c r="I66" s="1" t="s">
+      <c r="G72" s="3">
+        <v>160</v>
+      </c>
+      <c r="H72" s="3">
+        <v>80</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="J66" s="5"/>
-      <c r="K66" s="7" t="s">
+      <c r="J72" s="3"/>
+      <c r="K72" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="2:11">
-      <c r="B67" s="5">
-        <v>315</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D67" s="5">
+    <row r="73" s="1" customFormat="1" spans="2:11">
+      <c r="B73" s="3">
+        <v>321</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D73" s="3">
         <v>0.2</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="E73" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F73" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G67" s="5">
-        <v>280</v>
-      </c>
-      <c r="H67" s="5">
-        <v>140</v>
-      </c>
-      <c r="I67" s="1" t="s">
+      <c r="G73" s="3">
+        <v>160</v>
+      </c>
+      <c r="H73" s="3">
+        <v>80</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J67" s="5"/>
-      <c r="K67" s="7" t="s">
+      <c r="J73" s="3"/>
+      <c r="K73" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="2:11">
-      <c r="B68" s="5">
-        <v>316</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D68" s="5">
+    <row r="74" s="1" customFormat="1" spans="2:11">
+      <c r="B74" s="3">
+        <v>322</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D74" s="3">
         <v>0.2</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="E74" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F74" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G68" s="5">
-        <v>280</v>
-      </c>
-      <c r="H68" s="5">
-        <v>140</v>
-      </c>
-      <c r="I68" s="1" t="s">
+      <c r="G74" s="3">
+        <v>160</v>
+      </c>
+      <c r="H74" s="3">
+        <v>80</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="J68" s="5"/>
-      <c r="K68" s="7" t="s">
+      <c r="J74" s="3"/>
+      <c r="K74" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="2:11">
-      <c r="B69" s="5">
-        <v>317</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D69" s="5">
+    <row r="75" s="1" customFormat="1" spans="2:11">
+      <c r="B75" s="3">
+        <v>323</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D75" s="3">
         <v>0.2</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E75" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F75" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G69" s="5">
-        <v>300</v>
-      </c>
-      <c r="H69" s="5">
-        <v>150</v>
-      </c>
-      <c r="I69" s="1" t="s">
+      <c r="G75" s="3">
+        <v>190</v>
+      </c>
+      <c r="H75" s="3">
+        <v>95</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="J69" s="5"/>
-      <c r="K69" s="7" t="s">
+      <c r="J75" s="3"/>
+      <c r="K75" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="2:11">
-      <c r="B70" s="5">
-        <v>318</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D70" s="5">
+    <row r="76" s="1" customFormat="1" spans="2:11">
+      <c r="B76" s="3">
+        <v>324</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D76" s="3">
         <v>0.2</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="E76" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F76" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="G70" s="5">
-        <v>280</v>
-      </c>
-      <c r="H70" s="5">
-        <v>140</v>
-      </c>
-      <c r="I70" s="1" t="s">
+      <c r="G76" s="3">
+        <v>175</v>
+      </c>
+      <c r="H76" s="3">
+        <v>87</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J70" s="5"/>
-      <c r="K70" s="7" t="s">
+      <c r="J76" s="3"/>
+      <c r="K76" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="2:11">
-      <c r="B71" s="5">
-        <v>319</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D71" s="5">
+    <row r="77" s="1" customFormat="1" spans="2:11">
+      <c r="B77" s="3">
+        <v>325</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D77" s="3">
         <v>0.2</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="E77" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F77" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G71" s="5">
-        <v>300</v>
-      </c>
-      <c r="H71" s="5">
-        <v>150</v>
-      </c>
-      <c r="I71" s="1" t="s">
+      <c r="G77" s="3">
+        <v>270</v>
+      </c>
+      <c r="H77" s="3">
+        <v>135</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="J71" s="5"/>
-      <c r="K71" s="7" t="s">
+      <c r="J77" s="3"/>
+      <c r="K77" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="2:11">
-      <c r="B72" s="5">
-        <v>320</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D72" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E72" s="5" t="s">
+    <row r="79" spans="2:11">
+      <c r="B79" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="C79" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="G72" s="5">
-        <v>300</v>
-      </c>
-      <c r="H72" s="5">
-        <v>150</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="J72" s="5"/>
-      <c r="K72" s="7" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" spans="2:11">
-      <c r="B73" s="5">
-        <v>321</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D73" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="G73" s="5">
-        <v>300</v>
-      </c>
-      <c r="H73" s="5">
-        <v>150</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="J73" s="5"/>
-      <c r="K73" s="7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" spans="2:11">
-      <c r="B74" s="5">
-        <v>322</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D74" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="G74" s="5">
-        <v>300</v>
-      </c>
-      <c r="H74" s="5">
-        <v>150</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="J74" s="5"/>
-      <c r="K74" s="7" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" spans="2:11">
-      <c r="B75" s="5">
-        <v>323</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D75" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="G75" s="5">
-        <v>280</v>
-      </c>
-      <c r="H75" s="5">
-        <v>140</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="J75" s="5"/>
-      <c r="K75" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" spans="2:11">
-      <c r="B76" s="5">
-        <v>324</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D76" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="G76" s="5">
-        <v>300</v>
-      </c>
-      <c r="H76" s="5">
-        <v>150</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="J76" s="5"/>
-      <c r="K76" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="2:11">
-      <c r="B77" s="5">
-        <v>325</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D77" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="G77" s="5">
-        <v>300</v>
-      </c>
-      <c r="H77" s="5">
-        <v>150</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="J77" s="5"/>
-      <c r="K77" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>367</v>
       </c>
       <c r="D79" s="3">
         <v>0.1</v>
@@ -4750,8 +4656,8 @@
       <c r="E79" s="3">
         <v>235</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>368</v>
+      <c r="F79" s="3" t="s">
+        <v>344</v>
       </c>
       <c r="G79" s="3">
         <v>650</v>
@@ -4759,730 +4665,730 @@
       <c r="H79" s="3">
         <v>325</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>369</v>
+      <c r="I79" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="J79" s="3">
         <v>1005</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="2:11">
-      <c r="B80" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>367</v>
+      <c r="B80" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D80" s="3">
         <v>0.1</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>373</v>
+        <v>348</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>349</v>
       </c>
       <c r="G80" s="3">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="H80" s="3">
-        <v>300</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>374</v>
+        <v>340</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>350</v>
       </c>
       <c r="J80" s="3">
         <v>1006</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="2:11">
-      <c r="B81" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>367</v>
+      <c r="B81" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D81" s="3">
         <v>0.1</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>378</v>
+        <v>353</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="G81" s="3">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="H81" s="3">
-        <v>290</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>379</v>
+        <v>300</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>355</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
     </row>
     <row r="82" spans="2:11">
-      <c r="B82" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>367</v>
+      <c r="B82" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D82" s="3">
         <v>0.1</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>383</v>
+        <v>358</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="G82" s="3">
-        <v>530</v>
+        <v>480</v>
       </c>
       <c r="H82" s="3">
-        <v>265</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>384</v>
+        <v>240</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>360</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="2:11">
-      <c r="B83" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>367</v>
+      <c r="B83" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D83" s="3">
         <v>0.1</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>388</v>
+        <v>363</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>364</v>
       </c>
       <c r="G83" s="3">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="H83" s="3">
-        <v>280</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>389</v>
+        <v>230</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>365</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84" spans="2:11">
-      <c r="B84" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="B84" s="1" t="s">
         <v>367</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D84" s="3">
         <v>0.1</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>393</v>
+        <v>368</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>369</v>
       </c>
       <c r="G84" s="3">
-        <v>620</v>
+        <v>320</v>
       </c>
       <c r="H84" s="3">
-        <v>310</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>394</v>
+        <v>160</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
     </row>
     <row r="85" spans="2:11">
-      <c r="B85" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>367</v>
+      <c r="B85" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D85" s="3">
         <v>0.1</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>398</v>
+        <v>373</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>374</v>
       </c>
       <c r="G85" s="3">
-        <v>590</v>
+        <v>380</v>
       </c>
       <c r="H85" s="3">
-        <v>295</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>399</v>
+        <v>190</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>375</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
     </row>
     <row r="86" spans="2:11">
-      <c r="B86" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>367</v>
+      <c r="B86" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D86" s="3">
         <v>0.1</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>403</v>
+        <v>378</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>379</v>
       </c>
       <c r="G86" s="3">
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="H86" s="3">
-        <v>320</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>404</v>
+        <v>300</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
     </row>
     <row r="87" spans="2:11">
-      <c r="B87" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>367</v>
+      <c r="B87" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D87" s="3">
         <v>0.1</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>408</v>
+        <v>383</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>384</v>
       </c>
       <c r="G87" s="3">
-        <v>610</v>
+        <v>300</v>
       </c>
       <c r="H87" s="3">
-        <v>305</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>409</v>
+        <v>150</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
     </row>
     <row r="88" spans="2:11">
-      <c r="B88" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>367</v>
+      <c r="B88" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D88" s="3">
         <v>0.1</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>413</v>
+        <v>388</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>389</v>
       </c>
       <c r="G88" s="3">
-        <v>580</v>
+        <v>300</v>
       </c>
       <c r="H88" s="3">
-        <v>290</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>414</v>
+        <v>150</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
     </row>
     <row r="89" spans="2:11">
-      <c r="B89" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>367</v>
+      <c r="B89" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D89" s="3">
         <v>0.1</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>418</v>
+        <v>393</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>394</v>
       </c>
       <c r="G89" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="H89" s="3">
-        <v>300</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>419</v>
+        <v>200</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>395</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
     </row>
     <row r="90" spans="2:11">
-      <c r="B90" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>367</v>
+      <c r="B90" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D90" s="3">
         <v>0.1</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>423</v>
+        <v>398</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="G90" s="3">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="H90" s="3">
-        <v>275</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>424</v>
+        <v>230</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
     </row>
     <row r="91" spans="2:11">
-      <c r="B91" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>367</v>
+      <c r="B91" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D91" s="3">
         <v>0.1</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>428</v>
+        <v>403</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>404</v>
       </c>
       <c r="G91" s="3">
-        <v>560</v>
+        <v>340</v>
       </c>
       <c r="H91" s="3">
-        <v>280</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>429</v>
+        <v>170</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="J91" s="3">
         <v>1007</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
     </row>
     <row r="92" spans="2:11">
-      <c r="B92" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>367</v>
+      <c r="B92" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="D92" s="3">
         <v>0.1</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>433</v>
+        <v>408</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="G92" s="3">
-        <v>630</v>
+        <v>280</v>
       </c>
       <c r="H92" s="3">
-        <v>315</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>434</v>
+        <v>140</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="J92" s="3">
         <v>1008</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:11">
       <c r="B93" s="1" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D93" s="5">
+        <v>343</v>
+      </c>
+      <c r="D93" s="3">
         <v>0.1</v>
       </c>
-      <c r="E93" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="G93" s="5">
+      <c r="E93" t="s">
+        <v>413</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G93" s="3">
         <v>600</v>
       </c>
-      <c r="H93" s="5">
+      <c r="H93" s="3">
         <v>300</v>
       </c>
-      <c r="I93" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="J93" s="5"/>
-      <c r="K93" s="7" t="s">
-        <v>440</v>
+      <c r="I93" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="J93" s="3"/>
+      <c r="K93" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:11">
       <c r="B94" s="1" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D94" s="5">
+        <v>343</v>
+      </c>
+      <c r="D94" s="3">
         <v>0.1</v>
       </c>
-      <c r="E94" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="G94" s="5">
-        <v>600</v>
-      </c>
-      <c r="H94" s="5">
-        <v>300</v>
-      </c>
-      <c r="I94" s="5">
+      <c r="E94" t="s">
+        <v>418</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G94" s="3">
+        <v>280</v>
+      </c>
+      <c r="H94" s="3">
+        <v>140</v>
+      </c>
+      <c r="I94" s="3">
         <v>40016</v>
       </c>
-      <c r="J94" s="5"/>
-      <c r="K94" s="7" t="s">
-        <v>444</v>
+      <c r="J94" s="3"/>
+      <c r="K94" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:11">
       <c r="B95" s="1" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D95" s="5">
+        <v>343</v>
+      </c>
+      <c r="D95" s="3">
         <v>0.1</v>
       </c>
-      <c r="E95" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="G95" s="5">
-        <v>630</v>
-      </c>
-      <c r="H95" s="5">
-        <v>315</v>
-      </c>
-      <c r="I95" s="5">
+      <c r="E95" t="s">
+        <v>422</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="G95" s="3">
+        <v>300</v>
+      </c>
+      <c r="H95" s="3">
+        <v>150</v>
+      </c>
+      <c r="I95" s="3">
         <v>40017</v>
       </c>
-      <c r="J95" s="5"/>
-      <c r="K95" s="7" t="s">
-        <v>448</v>
+      <c r="J95" s="3"/>
+      <c r="K95" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" spans="2:11">
       <c r="B96" s="1" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D96" s="5">
+        <v>343</v>
+      </c>
+      <c r="D96" s="3">
         <v>0.1</v>
       </c>
-      <c r="E96" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="G96" s="5">
-        <v>630</v>
-      </c>
-      <c r="H96" s="5">
-        <v>315</v>
-      </c>
-      <c r="I96" s="5">
+      <c r="E96" t="s">
+        <v>426</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G96" s="3">
+        <v>520</v>
+      </c>
+      <c r="H96" s="3">
+        <v>260</v>
+      </c>
+      <c r="I96" s="3">
         <v>40018</v>
       </c>
-      <c r="J96" s="5"/>
-      <c r="K96" s="7" t="s">
-        <v>452</v>
+      <c r="J96" s="3"/>
+      <c r="K96" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:11">
       <c r="B97" s="1" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D97" s="5">
+        <v>343</v>
+      </c>
+      <c r="D97" s="3">
         <v>0.1</v>
       </c>
-      <c r="E97" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="G97" s="5">
-        <v>600</v>
-      </c>
-      <c r="H97" s="5">
+      <c r="E97" t="s">
+        <v>430</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="G97" s="3">
         <v>300</v>
       </c>
-      <c r="I97" s="5">
+      <c r="H97" s="3">
+        <v>150</v>
+      </c>
+      <c r="I97" s="3">
         <v>40019</v>
       </c>
-      <c r="J97" s="5"/>
-      <c r="K97" s="7" t="s">
-        <v>456</v>
+      <c r="J97" s="3"/>
+      <c r="K97" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:11">
       <c r="B98" s="1" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D98" s="5">
+        <v>343</v>
+      </c>
+      <c r="D98" s="3">
         <v>0.1</v>
       </c>
-      <c r="E98" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="G98" s="5">
-        <v>630</v>
-      </c>
-      <c r="H98" s="5">
-        <v>315</v>
-      </c>
-      <c r="I98" s="5">
+      <c r="E98" t="s">
+        <v>434</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="G98" s="3">
+        <v>560</v>
+      </c>
+      <c r="H98" s="3">
+        <v>280</v>
+      </c>
+      <c r="I98" s="3">
         <v>40020</v>
       </c>
-      <c r="J98" s="5"/>
-      <c r="K98" s="7" t="s">
-        <v>460</v>
+      <c r="J98" s="3"/>
+      <c r="K98" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:11">
       <c r="B99" s="1" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D99" s="5">
+        <v>343</v>
+      </c>
+      <c r="D99" s="3">
         <v>0.1</v>
       </c>
-      <c r="E99" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="G99" s="5">
-        <v>600</v>
-      </c>
-      <c r="H99" s="5">
-        <v>300</v>
-      </c>
-      <c r="I99" s="5">
+      <c r="E99" t="s">
+        <v>438</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G99" s="3">
+        <v>620</v>
+      </c>
+      <c r="H99" s="3">
+        <v>310</v>
+      </c>
+      <c r="I99" s="3">
         <v>40021</v>
       </c>
-      <c r="J99" s="5"/>
-      <c r="K99" s="7" t="s">
-        <v>464</v>
+      <c r="J99" s="3"/>
+      <c r="K99" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:11">
       <c r="B100" s="1" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D100" s="5">
+        <v>343</v>
+      </c>
+      <c r="D100" s="3">
         <v>0.1</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="G100" s="5">
-        <v>600</v>
-      </c>
-      <c r="H100" s="5">
-        <v>300</v>
-      </c>
-      <c r="I100" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="J100" s="5"/>
-      <c r="K100" s="7" t="s">
-        <v>469</v>
+      <c r="E100" t="s">
+        <v>442</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="G100" s="3">
+        <v>320</v>
+      </c>
+      <c r="H100" s="3">
+        <v>160</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="J100" s="3"/>
+      <c r="K100" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:11">
       <c r="B101" s="1" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D101" s="5">
+        <v>343</v>
+      </c>
+      <c r="D101" s="3">
         <v>0.1</v>
       </c>
-      <c r="E101" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>472</v>
-      </c>
-      <c r="G101" s="5">
-        <v>600</v>
-      </c>
-      <c r="H101" s="5">
-        <v>300</v>
-      </c>
-      <c r="I101" s="5">
+      <c r="E101" t="s">
+        <v>447</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G101" s="3">
+        <v>450</v>
+      </c>
+      <c r="H101" s="3">
+        <v>225</v>
+      </c>
+      <c r="I101" s="3">
         <v>40023</v>
       </c>
-      <c r="J101" s="5"/>
-      <c r="K101" s="7" t="s">
-        <v>473</v>
+      <c r="J101" s="3"/>
+      <c r="K101" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:11">
       <c r="B102" s="1" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D102" s="5">
+        <v>343</v>
+      </c>
+      <c r="D102" s="3">
         <v>0.1</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G102" s="5">
-        <v>600</v>
-      </c>
-      <c r="H102" s="5">
-        <v>300</v>
-      </c>
-      <c r="I102" s="5">
+      <c r="E102" t="s">
+        <v>451</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="G102" s="3">
+        <v>550</v>
+      </c>
+      <c r="H102" s="3">
+        <v>275</v>
+      </c>
+      <c r="I102" s="3">
         <v>40024</v>
       </c>
-      <c r="J102" s="5"/>
-      <c r="K102" s="7" t="s">
-        <v>477</v>
+      <c r="J102" s="3"/>
+      <c r="K102" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:11">
       <c r="B103" s="1" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="D103" s="5">
+        <v>343</v>
+      </c>
+      <c r="D103" s="3">
         <v>0.1</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="G103" s="5">
-        <v>630</v>
-      </c>
-      <c r="H103" s="5">
-        <v>315</v>
-      </c>
-      <c r="I103" s="5">
+      <c r="E103" t="s">
+        <v>455</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G103" s="3">
+        <v>300</v>
+      </c>
+      <c r="H103" s="3">
+        <v>150</v>
+      </c>
+      <c r="I103" s="3">
         <v>40025</v>
       </c>
-      <c r="J103" s="5"/>
-      <c r="K103" s="7" t="s">
-        <v>481</v>
+      <c r="J103" s="3"/>
+      <c r="K103" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15600" windowHeight="10260"/>
+    <workbookView windowWidth="14655" windowHeight="10035"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="520">
   <si>
     <t>##var</t>
   </si>
@@ -64,6 +64,9 @@
     <t>UnlockConditionId</t>
   </si>
   <si>
+    <t>UseType</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>解锁条件ID</t>
   </si>
   <si>
+    <t>使用类型(0被动/1即时消耗/2永久消耗)</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
@@ -319,6 +325,42 @@
     <t>每当你受到伤害时,反弹3点伤害给攻击者</t>
   </si>
   <si>
+    <t>磨刀石</t>
+  </si>
+  <si>
+    <t>Whetstone</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你造成的伤害+50%</t>
+  </si>
+  <si>
+    <t>顺子心得</t>
+  </si>
+  <si>
+    <t>StraightExperience</t>
+  </si>
+  <si>
+    <t>使用后,顺子牌型提供的倍率永久+1</t>
+  </si>
+  <si>
+    <t>急救粉</t>
+  </si>
+  <si>
+    <t>FirstAidPowder</t>
+  </si>
+  <si>
+    <t>使用后,立即恢复30%最大生命</t>
+  </si>
+  <si>
+    <t>复仇之刺</t>
+  </si>
+  <si>
+    <t>RevengeThorn</t>
+  </si>
+  <si>
+    <t>每输1次比牌,你造成的伤害+20%,至多+100%,输后一直保留</t>
+  </si>
+  <si>
     <t>201</t>
   </si>
   <si>
@@ -757,6 +799,60 @@
     <t>每回合结束时,每剩余1次搓牌次数就获得3金币</t>
   </si>
   <si>
+    <t>火药</t>
+  </si>
+  <si>
+    <t>Gunpowder</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你造成的伤害翻倍</t>
+  </si>
+  <si>
+    <t>对子心得</t>
+  </si>
+  <si>
+    <t>PairExperience</t>
+  </si>
+  <si>
+    <t>使用后,对子牌型提供的倍率永久+3</t>
+  </si>
+  <si>
+    <t>黄金急救包</t>
+  </si>
+  <si>
+    <t>GoldenFirstAidKit</t>
+  </si>
+  <si>
+    <t>使用后,立即恢复60%最大生命</t>
+  </si>
+  <si>
+    <t>月光酒</t>
+  </si>
+  <si>
+    <t>MoonlightWine</t>
+  </si>
+  <si>
+    <t>每回合比牌获胜后,恢复3点生命</t>
+  </si>
+  <si>
+    <t>商人票据</t>
+  </si>
+  <si>
+    <t>MerchantTicket</t>
+  </si>
+  <si>
+    <t>使用后,下一次进入商店时所有购买价格-50%</t>
+  </si>
+  <si>
+    <t>净化药水</t>
+  </si>
+  <si>
+    <t>PurificationPotion</t>
+  </si>
+  <si>
+    <t>使用后,移除本关内的1条BOSS词缀效果</t>
+  </si>
+  <si>
     <t>Epic</t>
   </si>
   <si>
@@ -1060,6 +1156,51 @@
     <t>所有敌人造成的伤害降低30%</t>
   </si>
   <si>
+    <t>同花心得</t>
+  </si>
+  <si>
+    <t>FlushExperience</t>
+  </si>
+  <si>
+    <t>使用后,同花牌型提供的倍率永久+8</t>
+  </si>
+  <si>
+    <t>豹子精髓</t>
+  </si>
+  <si>
+    <t>LeopardEssence</t>
+  </si>
+  <si>
+    <t>使用后,本局内你首次亮出豹子时,额外获得300金币</t>
+  </si>
+  <si>
+    <t>时之沙</t>
+  </si>
+  <si>
+    <t>SandOfTime</t>
+  </si>
+  <si>
+    <t>使用后,本关内你比牌获胜时的伤害+30%</t>
+  </si>
+  <si>
+    <t>巨人药剂</t>
+  </si>
+  <si>
+    <t>GiantPotion</t>
+  </si>
+  <si>
+    <t>使用后,本关内生命上限+80,并立即恢复80点生命</t>
+  </si>
+  <si>
+    <t>丰收图腾</t>
+  </si>
+  <si>
+    <t>HarvestTotem</t>
+  </si>
+  <si>
+    <t>每通过1关时,获得25金币</t>
+  </si>
+  <si>
     <t>401</t>
   </si>
   <si>
@@ -1406,6 +1547,51 @@
   </si>
   <si>
     <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
+  </si>
+  <si>
+    <t>神之左手</t>
+  </si>
+  <si>
+    <t>GodLeftHand</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你造成的伤害固定为500点</t>
+  </si>
+  <si>
+    <t>凤凰羽毛</t>
+  </si>
+  <si>
+    <t>PhoenixFeather</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你受到的所有伤害变为0,并立即恢复30%最大生命</t>
+  </si>
+  <si>
+    <t>时光宝盒</t>
+  </si>
+  <si>
+    <t>TimeTreasureBox</t>
+  </si>
+  <si>
+    <t>使用后,随机3种牌型的倍率永久+5</t>
+  </si>
+  <si>
+    <t>龙心</t>
+  </si>
+  <si>
+    <t>DragonHeart</t>
+  </si>
+  <si>
+    <t>使用后,永久获得120点生命上限,并立即恢复120点生命</t>
+  </si>
+  <si>
+    <t>贪欲之冠</t>
+  </si>
+  <si>
+    <t>GreedCrown</t>
+  </si>
+  <si>
+    <t>每拥有40金币,你造成的伤害+8%,至多+100%</t>
   </si>
 </sst>
 </file>
@@ -2380,7 +2566,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
@@ -2393,13 +2579,13 @@
     <col min="8" max="8" width="4.78333333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="5.53333333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="7.70833333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="34.75" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.5583333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7.70833333333333" style="3" customWidth="1"/>
+    <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2433,92 +2619,101 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>26</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3">
         <v>0.8</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" s="3">
         <v>30</v>
@@ -2529,25 +2724,28 @@
       <c r="I5" s="3">
         <v>10001</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3">
         <v>0.8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" s="3">
         <v>28</v>
@@ -2558,25 +2756,28 @@
       <c r="I6" s="3">
         <v>10002</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3">
         <v>0.8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3">
         <v>28</v>
@@ -2587,25 +2788,28 @@
       <c r="I7" s="3">
         <v>10003</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7" s="3">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>0.8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" s="3">
         <v>28</v>
@@ -2616,25 +2820,28 @@
       <c r="I8" s="3">
         <v>10004</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3">
         <v>0.8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3">
         <v>28</v>
@@ -2645,25 +2852,28 @@
       <c r="I9" s="3">
         <v>10005</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3">
         <v>0.8</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3">
         <v>28</v>
@@ -2674,25 +2884,28 @@
       <c r="I10" s="3">
         <v>10006</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="B11" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3">
         <v>0.8</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G11" s="3">
         <v>22</v>
@@ -2703,25 +2916,28 @@
       <c r="I11" s="3">
         <v>10007</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D12" s="3">
         <v>0.8</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G12" s="3">
         <v>35</v>
@@ -2732,25 +2948,28 @@
       <c r="I12" s="3">
         <v>10008</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3">
         <v>0.8</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G13" s="3">
         <v>16</v>
@@ -2761,25 +2980,28 @@
       <c r="I13" s="3">
         <v>10009</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14" s="3">
         <v>0.8</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14" s="3">
         <v>16</v>
@@ -2790,25 +3012,28 @@
       <c r="I14" s="3">
         <v>10010</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" s="3">
         <v>0.8</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" s="3">
         <v>15</v>
@@ -2819,25 +3044,28 @@
       <c r="I15" s="3">
         <v>10011</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:11">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:12">
       <c r="B16" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D16" s="3">
         <v>0.8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G16" s="3">
         <v>30</v>
@@ -2849,25 +3077,28 @@
         <v>10012</v>
       </c>
       <c r="J16" s="3"/>
-      <c r="K16" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:11">
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:12">
       <c r="B17" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D17" s="3">
         <v>0.8</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G17" s="3">
         <v>35</v>
@@ -2879,25 +3110,28 @@
         <v>10013</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:11">
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:12">
       <c r="B18" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" s="3">
         <v>0.8</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G18" s="3">
         <v>26</v>
@@ -2909,25 +3143,28 @@
         <v>10014</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:11">
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:12">
       <c r="B19" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D19" s="3">
         <v>0.8</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G19" s="3">
         <v>22</v>
@@ -2939,25 +3176,28 @@
         <v>10015</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:11">
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:12">
       <c r="B20" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D20" s="3">
         <v>0.8</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G20" s="3">
         <v>28</v>
@@ -2969,25 +3209,28 @@
         <v>10016</v>
       </c>
       <c r="J20" s="3"/>
-      <c r="K20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:11">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:12">
       <c r="B21" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21" s="3">
         <v>0.8</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G21" s="3">
         <v>20</v>
@@ -2999,719 +3242,783 @@
         <v>10017</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="B23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
         <v>96</v>
       </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="B22">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22">
+        <v>25</v>
+      </c>
+      <c r="H22">
+        <v>12</v>
+      </c>
+      <c r="I22">
+        <v>10018</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="B23">
+        <v>119</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
       <c r="D23" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G23" s="1">
-        <v>115</v>
-      </c>
-      <c r="H23" s="1">
-        <v>57</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K23" s="3" t="s">
+        <v>0.8</v>
+      </c>
+      <c r="E23" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="B24" s="1" t="s">
+      <c r="F23" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>96</v>
+      <c r="G23">
+        <v>15</v>
+      </c>
+      <c r="H23">
+        <v>7</v>
+      </c>
+      <c r="I23">
+        <v>10019</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2</v>
+      </c>
+      <c r="L23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="B24">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
       </c>
       <c r="D24" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24" s="3" t="s">
+        <v>0.8</v>
+      </c>
+      <c r="E24" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="1">
-        <v>115</v>
-      </c>
-      <c r="H24" s="1">
-        <v>57</v>
-      </c>
-      <c r="I24" s="1" t="s">
+      <c r="F24" t="s">
         <v>104</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="G24">
+        <v>25</v>
+      </c>
+      <c r="H24">
+        <v>12</v>
+      </c>
+      <c r="I24">
+        <v>10020</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1</v>
+      </c>
+      <c r="L24" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25"/>
-      <c r="B25" s="1" t="s">
+    <row r="25" spans="1:12">
+      <c r="B25">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E25" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" t="s">
         <v>107</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25">
+        <v>30</v>
+      </c>
+      <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="I25">
+        <v>10021</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" t="s">
         <v>108</v>
       </c>
-      <c r="G25" s="1">
-        <v>115</v>
-      </c>
-      <c r="H25" s="1">
-        <v>57</v>
-      </c>
-      <c r="I25" s="1" t="s">
+    </row>
+    <row r="27" spans="1:12">
+      <c r="B27" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26"/>
-      <c r="B26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="1">
-        <v>115</v>
-      </c>
-      <c r="H26" s="1">
-        <v>57</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27"/>
-      <c r="B27" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="D27" s="3">
         <v>0.4</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G27" s="1">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H27" s="1">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28"/>
+        <v>113</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="B28" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D28" s="3">
         <v>0.4</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G28" s="1">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H28" s="1">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>118</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29"/>
       <c r="B29" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D29" s="3">
         <v>0.4</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G29" s="1">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="H29" s="1">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>123</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30"/>
       <c r="B30" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D30" s="3">
         <v>0.4</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G30" s="1">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="H30" s="1">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>128</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31"/>
       <c r="B31" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D31" s="3">
         <v>0.4</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G31" s="1">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="H31" s="1">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>133</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32"/>
       <c r="B32" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D32" s="3">
         <v>0.4</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G32" s="1">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>138</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33"/>
       <c r="B33" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D33" s="3">
         <v>0.4</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G33" s="1">
-        <v>80</v>
+        <v>155</v>
       </c>
       <c r="H33" s="1">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>143</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34"/>
       <c r="B34" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D34" s="3">
         <v>0.4</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G34" s="1">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="H34" s="1">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>148</v>
+      </c>
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35"/>
       <c r="B35" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D35" s="3">
         <v>0.4</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G35" s="1">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="H35" s="1">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>153</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36"/>
       <c r="B36" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D36" s="3">
         <v>0.4</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G36" s="1">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="H36" s="1">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>158</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37"/>
       <c r="B37" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D37" s="3">
         <v>0.4</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G37" s="1">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="H37" s="1">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>163</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38"/>
       <c r="B38" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D38" s="3">
         <v>0.4</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G38" s="1">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H38" s="1">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>168</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39"/>
       <c r="B39" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D39" s="3">
         <v>0.4</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G39" s="1">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H39" s="1">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>173</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40"/>
       <c r="B40" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D40" s="3">
         <v>0.4</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G40" s="1">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H40" s="1">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:11">
+        <v>178</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:12">
       <c r="A41"/>
       <c r="B41" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D41" s="3">
         <v>0.4</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G41" s="3">
-        <v>85</v>
-      </c>
-      <c r="H41" s="3">
-        <v>42</v>
+        <v>182</v>
+      </c>
+      <c r="G41" s="1">
+        <v>110</v>
+      </c>
+      <c r="H41" s="1">
+        <v>55</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J41" s="3"/>
-      <c r="K41" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:11">
+        <v>183</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:12">
       <c r="A42"/>
       <c r="B42" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D42" s="3">
         <v>0.4</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G42" s="3">
-        <v>75</v>
-      </c>
-      <c r="H42" s="3">
-        <v>37</v>
+        <v>187</v>
+      </c>
+      <c r="G42" s="1">
+        <v>110</v>
+      </c>
+      <c r="H42" s="1">
+        <v>55</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="J42" s="3"/>
-      <c r="K42" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:11">
+        <v>188</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:12">
       <c r="A43"/>
       <c r="B43" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D43" s="3">
         <v>0.4</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G43" s="3">
-        <v>75</v>
-      </c>
-      <c r="H43" s="3">
-        <v>37</v>
+        <v>192</v>
+      </c>
+      <c r="G43" s="1">
+        <v>115</v>
+      </c>
+      <c r="H43" s="1">
+        <v>57</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="J43" s="3"/>
-      <c r="K43" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" spans="1:11">
+        <v>193</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:12">
       <c r="A44"/>
       <c r="B44" s="1" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D44" s="3">
         <v>0.4</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G44" s="3">
+        <v>197</v>
+      </c>
+      <c r="G44" s="1">
         <v>80</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="1">
         <v>40</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="J44" s="3"/>
-      <c r="K44" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:11">
+        <v>198</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:12">
       <c r="A45"/>
       <c r="B45" s="1" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D45" s="3">
         <v>0.4</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G45" s="3">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H45" s="3">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="J45" s="3"/>
-      <c r="K45" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="1:11">
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:12">
       <c r="A46"/>
       <c r="B46" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D46" s="3">
         <v>0.4</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G46" s="3">
         <v>75</v>
@@ -3720,218 +4027,262 @@
         <v>37</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="J46" s="3"/>
-      <c r="K46" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="1:11">
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:12">
       <c r="A47"/>
       <c r="B47" s="1" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D47" s="3">
         <v>0.4</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="G47" s="3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H47" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="J47" s="3"/>
-      <c r="K47" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="1:11">
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:12">
       <c r="A48"/>
       <c r="B48" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D48" s="3">
         <v>0.4</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G48" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H48" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="J48" s="3"/>
-      <c r="K48" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" spans="1:11">
+      <c r="K48" s="3">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:12">
       <c r="A49"/>
       <c r="B49" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D49" s="3">
         <v>0.4</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="G49" s="3">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H49" s="3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="J49" s="3"/>
-      <c r="K49" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="1:11">
+      <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:12">
       <c r="A50"/>
       <c r="B50" s="1" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D50" s="3">
         <v>0.4</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G50" s="3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H50" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J50" s="3"/>
-      <c r="K50" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:11">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:12">
       <c r="A51"/>
       <c r="B51" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D51" s="3">
         <v>0.4</v>
       </c>
       <c r="E51" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G51" s="3">
+        <v>70</v>
+      </c>
+      <c r="H51" s="3">
+        <v>35</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52"/>
+      <c r="B52" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="G52" s="3">
+        <v>120</v>
+      </c>
+      <c r="H52" s="3">
+        <v>60</v>
+      </c>
+      <c r="I52" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="G51" s="3">
-        <v>160</v>
-      </c>
-      <c r="H51" s="3">
-        <v>80</v>
-      </c>
-      <c r="I51" s="1" t="s">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
         <v>239</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" t="s">
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53"/>
+      <c r="B53" s="1" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52"/>
-      <c r="B52" s="3"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53"/>
-      <c r="B53" s="3">
-        <v>301</v>
-      </c>
       <c r="C53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D53" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="3">
+        <v>110</v>
+      </c>
+      <c r="H53" s="3">
+        <v>55</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G53" s="1">
-        <v>190</v>
-      </c>
-      <c r="H53" s="1">
-        <v>95</v>
-      </c>
-      <c r="I53" s="1" t="s">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" t="s">
         <v>244</v>
       </c>
-      <c r="J53" s="3">
-        <v>1001</v>
-      </c>
-      <c r="K53" s="3" t="s">
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54"/>
+      <c r="B54" s="1" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54"/>
-      <c r="B54" s="3">
-        <v>302</v>
-      </c>
       <c r="C54" s="1" t="s">
-        <v>241</v>
+        <v>110</v>
       </c>
       <c r="D54" s="3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>246</v>
@@ -3939,1443 +4290,1543 @@
       <c r="F54" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="G54" s="1">
-        <v>270</v>
-      </c>
-      <c r="H54" s="1">
-        <v>135</v>
+      <c r="G54" s="3">
+        <v>70</v>
+      </c>
+      <c r="H54" s="3">
+        <v>35</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="K54" s="3" t="s">
+      <c r="K54" s="3">
+        <v>0</v>
+      </c>
+      <c r="L54" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:12">
       <c r="A55"/>
-      <c r="B55" s="3">
-        <v>303</v>
+      <c r="B55" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>241</v>
+        <v>110</v>
       </c>
       <c r="D55" s="3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G55" s="1">
-        <v>190</v>
-      </c>
-      <c r="H55" s="1">
-        <v>95</v>
+        <v>252</v>
+      </c>
+      <c r="G55" s="3">
+        <v>160</v>
+      </c>
+      <c r="H55" s="3">
+        <v>80</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="K55" s="3" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56"/>
-      <c r="B56" s="3">
-        <v>304</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>241</v>
+      <c r="K55" s="3">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="B56">
+        <v>230</v>
+      </c>
+      <c r="C56" t="s">
+        <v>110</v>
       </c>
       <c r="D56" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="F56" s="3" t="s">
+        <v>0.4</v>
+      </c>
+      <c r="E56" t="s">
         <v>255</v>
       </c>
-      <c r="G56" s="1">
-        <v>185</v>
-      </c>
-      <c r="H56" s="1">
-        <v>92</v>
-      </c>
-      <c r="I56" s="1" t="s">
+      <c r="F56" t="s">
         <v>256</v>
       </c>
-      <c r="J56" s="3">
-        <v>1002</v>
-      </c>
-      <c r="K56" s="3" t="s">
+      <c r="G56">
+        <v>90</v>
+      </c>
+      <c r="H56">
+        <v>45</v>
+      </c>
+      <c r="I56">
+        <v>20030</v>
+      </c>
+      <c r="K56" s="3">
+        <v>1</v>
+      </c>
+      <c r="L56" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
-      <c r="A57"/>
-      <c r="B57" s="3">
-        <v>305</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>241</v>
+    <row r="57" spans="1:12">
+      <c r="B57">
+        <v>231</v>
+      </c>
+      <c r="C57" t="s">
+        <v>110</v>
       </c>
       <c r="D57" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E57" s="3" t="s">
+        <v>0.4</v>
+      </c>
+      <c r="E57" t="s">
         <v>258</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" t="s">
         <v>259</v>
       </c>
-      <c r="G57" s="1">
-        <v>170</v>
-      </c>
-      <c r="H57" s="1">
-        <v>85</v>
-      </c>
-      <c r="I57" s="1" t="s">
+      <c r="G57">
+        <v>70</v>
+      </c>
+      <c r="H57">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>20031</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2</v>
+      </c>
+      <c r="L57" t="s">
         <v>260</v>
       </c>
-      <c r="J57" s="3">
-        <v>1003</v>
-      </c>
-      <c r="K57" s="3" t="s">
+    </row>
+    <row r="58" spans="1:12">
+      <c r="B58">
+        <v>232</v>
+      </c>
+      <c r="C58" t="s">
+        <v>110</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E58" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="B58" s="3">
-        <v>306</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D58" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" t="s">
         <v>262</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58">
+        <v>145</v>
+      </c>
+      <c r="H58">
+        <v>72</v>
+      </c>
+      <c r="I58">
+        <v>20032</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1</v>
+      </c>
+      <c r="L58" t="s">
         <v>263</v>
       </c>
-      <c r="G58" s="1">
-        <v>240</v>
-      </c>
-      <c r="H58" s="1">
-        <v>120</v>
-      </c>
-      <c r="I58" s="1" t="s">
+    </row>
+    <row r="59" spans="1:12">
+      <c r="B59">
+        <v>233</v>
+      </c>
+      <c r="C59" t="s">
+        <v>110</v>
+      </c>
+      <c r="D59" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E59" t="s">
         <v>264</v>
       </c>
-      <c r="J58" s="3">
-        <v>1004</v>
-      </c>
-      <c r="K58" s="3" t="s">
+      <c r="F59" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="B59" s="3">
-        <v>307</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D59" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="G59">
+        <v>75</v>
+      </c>
+      <c r="H59">
+        <v>37</v>
+      </c>
+      <c r="I59">
+        <v>20033</v>
+      </c>
+      <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
         <v>266</v>
       </c>
-      <c r="F59" s="3" t="s">
+    </row>
+    <row r="60" spans="1:12">
+      <c r="B60">
+        <v>234</v>
+      </c>
+      <c r="C60" t="s">
+        <v>110</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E60" t="s">
         <v>267</v>
       </c>
-      <c r="G59" s="1">
-        <v>265</v>
-      </c>
-      <c r="H59" s="1">
-        <v>132</v>
-      </c>
-      <c r="I59" s="1" t="s">
+      <c r="F60" t="s">
         <v>268</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="G60">
+        <v>110</v>
+      </c>
+      <c r="H60">
+        <v>55</v>
+      </c>
+      <c r="I60">
+        <v>20034</v>
+      </c>
+      <c r="K60" s="3">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
-      <c r="B60" s="3">
-        <v>308</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D60" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E60" s="3" t="s">
+    <row r="61" spans="1:12">
+      <c r="B61">
+        <v>235</v>
+      </c>
+      <c r="C61" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E61" t="s">
         <v>270</v>
       </c>
-      <c r="F60" s="3" t="s">
+      <c r="F61" t="s">
         <v>271</v>
       </c>
-      <c r="G60" s="1">
-        <v>360</v>
-      </c>
-      <c r="H60" s="1">
-        <v>180</v>
-      </c>
-      <c r="I60" s="1" t="s">
+      <c r="G61">
+        <v>140</v>
+      </c>
+      <c r="H61">
+        <v>70</v>
+      </c>
+      <c r="I61">
+        <v>20035</v>
+      </c>
+      <c r="K61" s="3">
+        <v>1</v>
+      </c>
+      <c r="L61" t="s">
         <v>272</v>
       </c>
-      <c r="K60" s="3" t="s">
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62"/>
+      <c r="B62" s="3"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63"/>
+      <c r="B63" s="3">
+        <v>301</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>273</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="B61" s="3">
-        <v>309</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D61" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G61" s="1">
-        <v>350</v>
-      </c>
-      <c r="H61" s="1">
-        <v>175</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="B62" s="3">
-        <v>310</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D62" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G62" s="1">
-        <v>275</v>
-      </c>
-      <c r="H62" s="1">
-        <v>137</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="B63" s="3">
-        <v>311</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="D63" s="3">
         <v>0.2</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G63" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H63" s="1">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>276</v>
+      </c>
+      <c r="J63" s="3">
+        <v>1001</v>
+      </c>
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64"/>
       <c r="B64" s="3">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D64" s="3">
         <v>0.2</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="G64" s="1">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="H64" s="1">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
+        <v>280</v>
+      </c>
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65"/>
       <c r="B65" s="3">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D65" s="3">
         <v>0.2</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="G65" s="1">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="H65" s="1">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" spans="2:11">
+        <v>284</v>
+      </c>
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:12">
+      <c r="A66"/>
       <c r="B66" s="3">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D66" s="3">
         <v>0.2</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G66" s="3">
-        <v>180</v>
-      </c>
-      <c r="H66" s="3">
-        <v>90</v>
+        <v>287</v>
+      </c>
+      <c r="G66" s="1">
+        <v>185</v>
+      </c>
+      <c r="H66" s="1">
+        <v>92</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="J66" s="3"/>
-      <c r="K66" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" spans="2:11">
+        <v>288</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1002</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" spans="1:12">
+      <c r="A67"/>
       <c r="B67" s="3">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D67" s="3">
         <v>0.2</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G67" s="3">
-        <v>380</v>
-      </c>
-      <c r="H67" s="3">
-        <v>190</v>
+        <v>291</v>
+      </c>
+      <c r="G67" s="1">
+        <v>170</v>
+      </c>
+      <c r="H67" s="1">
+        <v>85</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="J67" s="3"/>
-      <c r="K67" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" spans="2:11">
+        <v>292</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1003</v>
+      </c>
+      <c r="K67" s="3">
+        <v>0</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" spans="1:12">
       <c r="B68" s="3">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D68" s="3">
         <v>0.2</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G68" s="3">
-        <v>170</v>
-      </c>
-      <c r="H68" s="3">
-        <v>85</v>
+        <v>295</v>
+      </c>
+      <c r="G68" s="1">
+        <v>240</v>
+      </c>
+      <c r="H68" s="1">
+        <v>120</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J68" s="3"/>
-      <c r="K68" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" spans="2:11">
+        <v>296</v>
+      </c>
+      <c r="J68" s="3">
+        <v>1004</v>
+      </c>
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" spans="1:12">
       <c r="B69" s="3">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D69" s="3">
         <v>0.2</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G69" s="3">
-        <v>175</v>
-      </c>
-      <c r="H69" s="3">
-        <v>87</v>
+        <v>299</v>
+      </c>
+      <c r="G69" s="1">
+        <v>265</v>
+      </c>
+      <c r="H69" s="1">
+        <v>132</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" spans="1:12">
+      <c r="B70" s="3">
         <v>308</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" spans="2:11">
-      <c r="B70" s="3">
-        <v>318</v>
-      </c>
       <c r="C70" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D70" s="3">
         <v>0.2</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G70" s="3">
-        <v>170</v>
-      </c>
-      <c r="H70" s="3">
-        <v>85</v>
+        <v>303</v>
+      </c>
+      <c r="G70" s="1">
+        <v>360</v>
+      </c>
+      <c r="H70" s="1">
+        <v>180</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="J70" s="3"/>
-      <c r="K70" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" spans="2:11">
+        <v>304</v>
+      </c>
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" spans="1:12">
       <c r="B71" s="3">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D71" s="3">
         <v>0.2</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="G71" s="3">
-        <v>160</v>
-      </c>
-      <c r="H71" s="3">
-        <v>80</v>
+        <v>307</v>
+      </c>
+      <c r="G71" s="1">
+        <v>350</v>
+      </c>
+      <c r="H71" s="1">
+        <v>175</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="J71" s="3"/>
-      <c r="K71" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" spans="2:11">
+        <v>308</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" spans="1:12">
       <c r="B72" s="3">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D72" s="3">
         <v>0.2</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G72" s="3">
-        <v>160</v>
-      </c>
-      <c r="H72" s="3">
-        <v>80</v>
+        <v>311</v>
+      </c>
+      <c r="G72" s="1">
+        <v>275</v>
+      </c>
+      <c r="H72" s="1">
+        <v>137</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="J72" s="3"/>
-      <c r="K72" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" spans="2:11">
+        <v>312</v>
+      </c>
+      <c r="K72" s="3">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" spans="1:12">
       <c r="B73" s="3">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D73" s="3">
         <v>0.2</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G73" s="3">
-        <v>160</v>
-      </c>
-      <c r="H73" s="3">
-        <v>80</v>
+        <v>315</v>
+      </c>
+      <c r="G73" s="1">
+        <v>170</v>
+      </c>
+      <c r="H73" s="1">
+        <v>85</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="J73" s="3"/>
-      <c r="K73" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="74" s="1" customFormat="1" spans="2:11">
+        <v>316</v>
+      </c>
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" spans="1:12">
       <c r="B74" s="3">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D74" s="3">
         <v>0.2</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G74" s="3">
-        <v>160</v>
-      </c>
-      <c r="H74" s="3">
-        <v>80</v>
+        <v>319</v>
+      </c>
+      <c r="G74" s="1">
+        <v>210</v>
+      </c>
+      <c r="H74" s="1">
+        <v>105</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="J74" s="3"/>
-      <c r="K74" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" spans="2:11">
+        <v>320</v>
+      </c>
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" spans="1:12">
       <c r="B75" s="3">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D75" s="3">
         <v>0.2</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G75" s="3">
-        <v>190</v>
-      </c>
-      <c r="H75" s="3">
-        <v>95</v>
+        <v>323</v>
+      </c>
+      <c r="G75" s="1">
+        <v>160</v>
+      </c>
+      <c r="H75" s="1">
+        <v>80</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="J75" s="3"/>
-      <c r="K75" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" spans="2:11">
+        <v>324</v>
+      </c>
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" spans="1:12">
       <c r="B76" s="3">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D76" s="3">
         <v>0.2</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="G76" s="3">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H76" s="3">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="J76" s="3"/>
-      <c r="K76" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="2:11">
+      <c r="K76" s="3">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:12">
       <c r="B77" s="3">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="D77" s="3">
         <v>0.2</v>
       </c>
       <c r="E77" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G77" s="3">
+        <v>380</v>
+      </c>
+      <c r="H77" s="3">
+        <v>190</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="B78" s="3">
+        <v>316</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D78" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G78" s="3">
+        <v>170</v>
+      </c>
+      <c r="H78" s="3">
+        <v>85</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="K78" s="3">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="B79" s="3">
+        <v>317</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D79" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F79" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G79" s="3">
+        <v>175</v>
+      </c>
+      <c r="H79" s="3">
+        <v>87</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="K79" s="3">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="B80" s="3">
+        <v>318</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D80" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G80" s="3">
+        <v>170</v>
+      </c>
+      <c r="H80" s="3">
+        <v>85</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="K80" s="3">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12">
+      <c r="B81" s="3">
+        <v>319</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D81" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G81" s="3">
+        <v>160</v>
+      </c>
+      <c r="H81" s="3">
+        <v>80</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12">
+      <c r="B82" s="3">
+        <v>320</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D82" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G82" s="3">
+        <v>160</v>
+      </c>
+      <c r="H82" s="3">
+        <v>80</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="K82" s="3">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12">
+      <c r="B83" s="3">
+        <v>321</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D83" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G83" s="3">
+        <v>160</v>
+      </c>
+      <c r="H83" s="3">
+        <v>80</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12">
+      <c r="B84" s="3">
+        <v>322</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D84" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G84" s="3">
+        <v>160</v>
+      </c>
+      <c r="H84" s="3">
+        <v>80</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12">
+      <c r="B85" s="3">
+        <v>323</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D85" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G85" s="3">
+        <v>190</v>
+      </c>
+      <c r="H85" s="3">
+        <v>95</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="86" spans="2:12">
+      <c r="B86" s="3">
+        <v>324</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D86" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G86" s="3">
+        <v>175</v>
+      </c>
+      <c r="H86" s="3">
+        <v>87</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="87" spans="2:12">
+      <c r="B87" s="3">
+        <v>325</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D87" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="G87" s="3">
         <v>270</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H87" s="3">
         <v>135</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="J77" s="3"/>
-      <c r="K77" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D79" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E79" s="3">
-        <v>235</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="G79" s="3">
-        <v>650</v>
-      </c>
-      <c r="H79" s="3">
-        <v>325</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="J79" s="3">
-        <v>1005</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D80" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="G80" s="3">
-        <v>680</v>
-      </c>
-      <c r="H80" s="3">
-        <v>340</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="J80" s="3">
-        <v>1006</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D81" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="G81" s="3">
-        <v>600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>300</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D82" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="G82" s="3">
-        <v>480</v>
-      </c>
-      <c r="H82" s="3">
-        <v>240</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D83" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="G83" s="3">
-        <v>460</v>
-      </c>
-      <c r="H83" s="3">
-        <v>230</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D84" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="G84" s="3">
-        <v>320</v>
-      </c>
-      <c r="H84" s="3">
+      <c r="I87" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="88" spans="2:12">
+      <c r="B88">
+        <v>326</v>
+      </c>
+      <c r="C88" t="s">
+        <v>273</v>
+      </c>
+      <c r="D88" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E88" t="s">
+        <v>374</v>
+      </c>
+      <c r="F88" t="s">
+        <v>375</v>
+      </c>
+      <c r="G88">
+        <v>190</v>
+      </c>
+      <c r="H88">
+        <v>95</v>
+      </c>
+      <c r="I88">
+        <v>30026</v>
+      </c>
+      <c r="K88" s="3">
+        <v>2</v>
+      </c>
+      <c r="L88" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="89" spans="2:12">
+      <c r="B89">
+        <v>327</v>
+      </c>
+      <c r="C89" t="s">
+        <v>273</v>
+      </c>
+      <c r="D89" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E89" t="s">
+        <v>377</v>
+      </c>
+      <c r="F89" t="s">
+        <v>378</v>
+      </c>
+      <c r="G89">
         <v>160</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D85" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="G85" s="3">
+      <c r="H89">
+        <v>80</v>
+      </c>
+      <c r="I89">
+        <v>30027</v>
+      </c>
+      <c r="K89" s="3">
+        <v>2</v>
+      </c>
+      <c r="L89" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="90" spans="2:12">
+      <c r="B90">
+        <v>328</v>
+      </c>
+      <c r="C90" t="s">
+        <v>273</v>
+      </c>
+      <c r="D90" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E90" t="s">
         <v>380</v>
       </c>
-      <c r="H85" s="3">
-        <v>190</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D86" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="G86" s="3">
-        <v>600</v>
-      </c>
-      <c r="H86" s="3">
-        <v>300</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="K86" s="3" t="s">
+      <c r="F90" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="1" t="s">
+      <c r="G90">
+        <v>200</v>
+      </c>
+      <c r="H90">
+        <v>100</v>
+      </c>
+      <c r="I90">
+        <v>30028</v>
+      </c>
+      <c r="K90" s="3">
+        <v>1</v>
+      </c>
+      <c r="L90" t="s">
         <v>382</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D87" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E87" s="3" t="s">
+    </row>
+    <row r="91" spans="2:12">
+      <c r="B91">
+        <v>329</v>
+      </c>
+      <c r="C91" t="s">
+        <v>273</v>
+      </c>
+      <c r="D91" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E91" t="s">
         <v>383</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F91" t="s">
         <v>384</v>
       </c>
-      <c r="G87" s="3">
-        <v>300</v>
-      </c>
-      <c r="H87" s="3">
-        <v>150</v>
-      </c>
-      <c r="I87" s="1" t="s">
+      <c r="G91">
+        <v>170</v>
+      </c>
+      <c r="H91">
+        <v>85</v>
+      </c>
+      <c r="I91">
+        <v>30029</v>
+      </c>
+      <c r="K91" s="3">
+        <v>1</v>
+      </c>
+      <c r="L91" t="s">
         <v>385</v>
       </c>
-      <c r="K87" s="3" t="s">
+    </row>
+    <row r="92" spans="2:12">
+      <c r="B92">
+        <v>330</v>
+      </c>
+      <c r="C92" t="s">
+        <v>273</v>
+      </c>
+      <c r="D92" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E92" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="1" t="s">
+      <c r="F92" t="s">
         <v>387</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D88" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E88" s="3" t="s">
+      <c r="G92">
+        <v>180</v>
+      </c>
+      <c r="H92">
+        <v>90</v>
+      </c>
+      <c r="I92">
+        <v>30030</v>
+      </c>
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" t="s">
         <v>388</v>
       </c>
-      <c r="F88" s="3" t="s">
+    </row>
+    <row r="93" s="1" customFormat="1"/>
+    <row r="94" s="1" customFormat="1" spans="2:12">
+      <c r="B94" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="G88" s="3">
-        <v>300</v>
-      </c>
-      <c r="H88" s="3">
-        <v>150</v>
-      </c>
-      <c r="I88" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D89" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="G89" s="3">
-        <v>400</v>
-      </c>
-      <c r="H89" s="3">
-        <v>200</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D90" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G90" s="3">
-        <v>460</v>
-      </c>
-      <c r="H90" s="3">
-        <v>230</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D91" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="G91" s="3">
-        <v>340</v>
-      </c>
-      <c r="H91" s="3">
-        <v>170</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="J91" s="3">
-        <v>1007</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="B92" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D92" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="G92" s="3">
-        <v>280</v>
-      </c>
-      <c r="H92" s="3">
-        <v>140</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="J92" s="3">
-        <v>1008</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="2:11">
-      <c r="B93" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D93" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E93" t="s">
-        <v>413</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="G93" s="3">
-        <v>600</v>
-      </c>
-      <c r="H93" s="3">
-        <v>300</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="J93" s="3"/>
-      <c r="K93" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="2:11">
-      <c r="B94" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="D94" s="3">
         <v>0.1</v>
       </c>
-      <c r="E94" t="s">
-        <v>418</v>
+      <c r="E94" s="3">
+        <v>235</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="G94" s="3">
-        <v>280</v>
+        <v>650</v>
       </c>
       <c r="H94" s="3">
-        <v>140</v>
-      </c>
-      <c r="I94" s="3">
-        <v>40016</v>
-      </c>
-      <c r="J94" s="3"/>
-      <c r="K94" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="2:11">
+        <v>325</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="J94" s="3">
+        <v>1005</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" spans="2:12">
       <c r="B95" s="1" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D95" s="3">
         <v>0.1</v>
       </c>
-      <c r="E95" t="s">
-        <v>422</v>
+      <c r="E95" s="3" t="s">
+        <v>395</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>423</v>
+        <v>396</v>
       </c>
       <c r="G95" s="3">
-        <v>300</v>
+        <v>680</v>
       </c>
       <c r="H95" s="3">
-        <v>150</v>
-      </c>
-      <c r="I95" s="3">
-        <v>40017</v>
-      </c>
-      <c r="J95" s="3"/>
-      <c r="K95" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="2:11">
+        <v>340</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="J95" s="3">
+        <v>1006</v>
+      </c>
+      <c r="K95" s="3">
+        <v>0</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="2:12">
       <c r="B96" s="1" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D96" s="3">
         <v>0.1</v>
       </c>
-      <c r="E96" t="s">
-        <v>426</v>
+      <c r="E96" s="3" t="s">
+        <v>400</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="G96" s="3">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="H96" s="3">
-        <v>260</v>
-      </c>
-      <c r="I96" s="3">
-        <v>40018</v>
-      </c>
-      <c r="J96" s="3"/>
-      <c r="K96" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="2:11">
+        <v>300</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" spans="2:12">
       <c r="B97" s="1" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D97" s="3">
         <v>0.1</v>
       </c>
-      <c r="E97" t="s">
-        <v>430</v>
+      <c r="E97" s="3" t="s">
+        <v>405</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
       <c r="G97" s="3">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="H97" s="3">
-        <v>150</v>
-      </c>
-      <c r="I97" s="3">
-        <v>40019</v>
-      </c>
-      <c r="J97" s="3"/>
-      <c r="K97" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="98" s="1" customFormat="1" spans="2:11">
+        <v>240</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" spans="2:12">
       <c r="B98" s="1" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D98" s="3">
         <v>0.1</v>
       </c>
-      <c r="E98" t="s">
-        <v>434</v>
+      <c r="E98" s="3" t="s">
+        <v>410</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="G98" s="3">
-        <v>560</v>
+        <v>460</v>
       </c>
       <c r="H98" s="3">
-        <v>280</v>
-      </c>
-      <c r="I98" s="3">
-        <v>40020</v>
-      </c>
-      <c r="J98" s="3"/>
-      <c r="K98" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1" spans="2:11">
+        <v>230</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" spans="2:12">
       <c r="B99" s="1" t="s">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D99" s="3">
         <v>0.1</v>
       </c>
-      <c r="E99" t="s">
-        <v>438</v>
+      <c r="E99" s="3" t="s">
+        <v>415</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>439</v>
+        <v>416</v>
       </c>
       <c r="G99" s="3">
-        <v>620</v>
+        <v>320</v>
       </c>
       <c r="H99" s="3">
-        <v>310</v>
-      </c>
-      <c r="I99" s="3">
-        <v>40021</v>
-      </c>
-      <c r="J99" s="3"/>
-      <c r="K99" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" spans="2:11">
+        <v>160</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" spans="2:12">
       <c r="B100" s="1" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D100" s="3">
         <v>0.1</v>
       </c>
-      <c r="E100" t="s">
-        <v>442</v>
+      <c r="E100" s="3" t="s">
+        <v>420</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="G100" s="3">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="H100" s="3">
-        <v>160</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="J100" s="3"/>
-      <c r="K100" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" spans="2:11">
+        <v>190</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" spans="2:12">
       <c r="B101" s="1" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D101" s="3">
         <v>0.1</v>
       </c>
-      <c r="E101" t="s">
-        <v>447</v>
+      <c r="E101" s="3" t="s">
+        <v>425</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="G101" s="3">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="H101" s="3">
-        <v>225</v>
-      </c>
-      <c r="I101" s="3">
-        <v>40023</v>
-      </c>
-      <c r="J101" s="3"/>
-      <c r="K101" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" spans="2:11">
+        <v>300</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" spans="2:12">
       <c r="B102" s="1" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D102" s="3">
         <v>0.1</v>
       </c>
-      <c r="E102" t="s">
-        <v>451</v>
+      <c r="E102" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="G102" s="3">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="H102" s="3">
-        <v>275</v>
-      </c>
-      <c r="I102" s="3">
-        <v>40024</v>
-      </c>
-      <c r="J102" s="3"/>
-      <c r="K102" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="2:11">
+        <v>150</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="2:12">
       <c r="B103" s="1" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="D103" s="3">
         <v>0.1</v>
       </c>
-      <c r="E103" t="s">
-        <v>455</v>
+      <c r="E103" s="3" t="s">
+        <v>435</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="G103" s="3">
         <v>300</v>
@@ -5383,12 +5834,660 @@
       <c r="H103" s="3">
         <v>150</v>
       </c>
-      <c r="I103" s="3">
+      <c r="I103" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K103" s="3">
+        <v>0</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="104" spans="2:12">
+      <c r="B104" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D104" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G104" s="3">
+        <v>400</v>
+      </c>
+      <c r="H104" s="3">
+        <v>200</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="K104" s="3">
+        <v>0</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="105" spans="2:12">
+      <c r="B105" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D105" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="G105" s="3">
+        <v>460</v>
+      </c>
+      <c r="H105" s="3">
+        <v>230</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="K105" s="3">
+        <v>0</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="106" spans="2:12">
+      <c r="B106" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D106" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="G106" s="3">
+        <v>340</v>
+      </c>
+      <c r="H106" s="3">
+        <v>170</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="J106" s="3">
+        <v>1007</v>
+      </c>
+      <c r="K106" s="3">
+        <v>0</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="107" spans="2:12">
+      <c r="B107" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D107" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="G107" s="3">
+        <v>280</v>
+      </c>
+      <c r="H107" s="3">
+        <v>140</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J107" s="3">
+        <v>1008</v>
+      </c>
+      <c r="K107" s="3">
+        <v>0</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="108" spans="2:12">
+      <c r="B108" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D108" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E108" t="s">
+        <v>460</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="G108" s="3">
+        <v>600</v>
+      </c>
+      <c r="H108" s="3">
+        <v>300</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="K108" s="3">
+        <v>0</v>
+      </c>
+      <c r="L108" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="109" spans="2:12">
+      <c r="B109" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D109" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E109" t="s">
+        <v>465</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="G109" s="3">
+        <v>280</v>
+      </c>
+      <c r="H109" s="3">
+        <v>140</v>
+      </c>
+      <c r="I109" s="3">
+        <v>40016</v>
+      </c>
+      <c r="K109" s="3">
+        <v>0</v>
+      </c>
+      <c r="L109" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="110" spans="2:12">
+      <c r="B110" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D110" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E110" t="s">
+        <v>469</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="G110" s="3">
+        <v>300</v>
+      </c>
+      <c r="H110" s="3">
+        <v>150</v>
+      </c>
+      <c r="I110" s="3">
+        <v>40017</v>
+      </c>
+      <c r="K110" s="3">
+        <v>0</v>
+      </c>
+      <c r="L110" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="111" spans="2:12">
+      <c r="B111" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D111" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E111" t="s">
+        <v>473</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="G111" s="3">
+        <v>520</v>
+      </c>
+      <c r="H111" s="3">
+        <v>260</v>
+      </c>
+      <c r="I111" s="3">
+        <v>40018</v>
+      </c>
+      <c r="K111" s="3">
+        <v>0</v>
+      </c>
+      <c r="L111" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="112" spans="2:12">
+      <c r="B112" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D112" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E112" t="s">
+        <v>477</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="G112" s="3">
+        <v>300</v>
+      </c>
+      <c r="H112" s="3">
+        <v>150</v>
+      </c>
+      <c r="I112" s="3">
+        <v>40019</v>
+      </c>
+      <c r="K112" s="3">
+        <v>0</v>
+      </c>
+      <c r="L112" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="113" spans="2:12">
+      <c r="B113" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D113" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E113" t="s">
+        <v>481</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="G113" s="3">
+        <v>560</v>
+      </c>
+      <c r="H113" s="3">
+        <v>280</v>
+      </c>
+      <c r="I113" s="3">
+        <v>40020</v>
+      </c>
+      <c r="K113" s="3">
+        <v>0</v>
+      </c>
+      <c r="L113" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="114" spans="2:12">
+      <c r="B114" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D114" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E114" t="s">
+        <v>485</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="G114" s="3">
+        <v>620</v>
+      </c>
+      <c r="H114" s="3">
+        <v>310</v>
+      </c>
+      <c r="I114" s="3">
+        <v>40021</v>
+      </c>
+      <c r="K114" s="3">
+        <v>0</v>
+      </c>
+      <c r="L114" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="115" spans="2:12">
+      <c r="B115" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D115" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E115" t="s">
+        <v>489</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="G115" s="3">
+        <v>320</v>
+      </c>
+      <c r="H115" s="3">
+        <v>160</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="K115" s="3">
+        <v>0</v>
+      </c>
+      <c r="L115" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="116" spans="2:12">
+      <c r="B116" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D116" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E116" t="s">
+        <v>494</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="G116" s="3">
+        <v>450</v>
+      </c>
+      <c r="H116" s="3">
+        <v>225</v>
+      </c>
+      <c r="I116" s="3">
+        <v>40023</v>
+      </c>
+      <c r="K116" s="3">
+        <v>0</v>
+      </c>
+      <c r="L116" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="117" spans="2:12">
+      <c r="B117" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D117" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E117" t="s">
+        <v>498</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="G117" s="3">
+        <v>550</v>
+      </c>
+      <c r="H117" s="3">
+        <v>275</v>
+      </c>
+      <c r="I117" s="3">
+        <v>40024</v>
+      </c>
+      <c r="K117" s="3">
+        <v>0</v>
+      </c>
+      <c r="L117" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="118" spans="2:12">
+      <c r="B118" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D118" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E118" t="s">
+        <v>502</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G118" s="3">
+        <v>300</v>
+      </c>
+      <c r="H118" s="3">
+        <v>150</v>
+      </c>
+      <c r="I118" s="3">
         <v>40025</v>
       </c>
-      <c r="J103" s="3"/>
-      <c r="K103" t="s">
-        <v>457</v>
+      <c r="K118" s="3">
+        <v>0</v>
+      </c>
+      <c r="L118" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="119" spans="2:12">
+      <c r="B119">
+        <v>426</v>
+      </c>
+      <c r="C119" t="s">
+        <v>390</v>
+      </c>
+      <c r="D119" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E119" t="s">
+        <v>505</v>
+      </c>
+      <c r="F119" t="s">
+        <v>506</v>
+      </c>
+      <c r="G119">
+        <v>400</v>
+      </c>
+      <c r="H119">
+        <v>200</v>
+      </c>
+      <c r="I119">
+        <v>40026</v>
+      </c>
+      <c r="K119" s="3">
+        <v>1</v>
+      </c>
+      <c r="L119" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="120" spans="2:12">
+      <c r="B120">
+        <v>427</v>
+      </c>
+      <c r="C120" t="s">
+        <v>390</v>
+      </c>
+      <c r="D120" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E120" t="s">
+        <v>508</v>
+      </c>
+      <c r="F120" t="s">
+        <v>509</v>
+      </c>
+      <c r="G120">
+        <v>330</v>
+      </c>
+      <c r="H120">
+        <v>165</v>
+      </c>
+      <c r="I120">
+        <v>40027</v>
+      </c>
+      <c r="K120" s="3">
+        <v>1</v>
+      </c>
+      <c r="L120" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="121" spans="2:12">
+      <c r="B121">
+        <v>428</v>
+      </c>
+      <c r="C121" t="s">
+        <v>390</v>
+      </c>
+      <c r="D121" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E121" t="s">
+        <v>511</v>
+      </c>
+      <c r="F121" t="s">
+        <v>512</v>
+      </c>
+      <c r="G121">
+        <v>260</v>
+      </c>
+      <c r="H121">
+        <v>130</v>
+      </c>
+      <c r="I121">
+        <v>40028</v>
+      </c>
+      <c r="K121" s="3">
+        <v>2</v>
+      </c>
+      <c r="L121" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="122" spans="2:12">
+      <c r="B122">
+        <v>429</v>
+      </c>
+      <c r="C122" t="s">
+        <v>390</v>
+      </c>
+      <c r="D122" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E122" t="s">
+        <v>514</v>
+      </c>
+      <c r="F122" t="s">
+        <v>515</v>
+      </c>
+      <c r="G122">
+        <v>270</v>
+      </c>
+      <c r="H122">
+        <v>135</v>
+      </c>
+      <c r="I122">
+        <v>40029</v>
+      </c>
+      <c r="K122" s="3">
+        <v>2</v>
+      </c>
+      <c r="L122" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="123" spans="2:12">
+      <c r="B123">
+        <v>430</v>
+      </c>
+      <c r="C123" t="s">
+        <v>390</v>
+      </c>
+      <c r="D123" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E123" t="s">
+        <v>517</v>
+      </c>
+      <c r="F123" t="s">
+        <v>518</v>
+      </c>
+      <c r="G123">
+        <v>280</v>
+      </c>
+      <c r="H123">
+        <v>140</v>
+      </c>
+      <c r="I123">
+        <v>40030</v>
+      </c>
+      <c r="K123" s="3">
+        <v>0</v>
+      </c>
+      <c r="L123" t="s">
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14655" windowHeight="10035"/>
+    <workbookView windowWidth="17820" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -727,337 +727,337 @@
     <t>225</t>
   </si>
   <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>幸运顺子</t>
+  </si>
+  <si>
+    <t>LuckyStraight</t>
+  </si>
+  <si>
+    <t>20025</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于顺子,则会被强行视作顺子</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>运动鞋</t>
+  </si>
+  <si>
+    <t>SportsShoes</t>
+  </si>
+  <si>
+    <t>20026</t>
+  </si>
+  <si>
+    <t>每回合结束后,提高1%闪避率,至多叠加20层</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>保温杯</t>
+  </si>
+  <si>
+    <t>ThermalMug</t>
+  </si>
+  <si>
+    <t>20027</t>
+  </si>
+  <si>
+    <t>每回合结束后,若你的血量低于50%,则恢复6点生命</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>利息</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>20028</t>
+  </si>
+  <si>
+    <t>每通过1关时,每拥有15金币获得1金币,每关至多10金币</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>小算盘</t>
+  </si>
+  <si>
+    <t>LittleAbacus</t>
+  </si>
+  <si>
+    <t>20029</t>
+  </si>
+  <si>
+    <t>每回合结束时,每剩余1次搓牌次数就获得3金币</t>
+  </si>
+  <si>
+    <t>火药</t>
+  </si>
+  <si>
+    <t>Gunpowder</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你造成的伤害翻倍</t>
+  </si>
+  <si>
+    <t>对子心得</t>
+  </si>
+  <si>
+    <t>PairExperience</t>
+  </si>
+  <si>
+    <t>使用后,对子牌型提供的倍率永久+3</t>
+  </si>
+  <si>
+    <t>黄金急救包</t>
+  </si>
+  <si>
+    <t>GoldenFirstAidKit</t>
+  </si>
+  <si>
+    <t>使用后,立即恢复60%最大生命</t>
+  </si>
+  <si>
+    <t>月光酒</t>
+  </si>
+  <si>
+    <t>MoonlightWine</t>
+  </si>
+  <si>
+    <t>每回合比牌获胜后,恢复3点生命</t>
+  </si>
+  <si>
+    <t>商人票据</t>
+  </si>
+  <si>
+    <t>MerchantTicket</t>
+  </si>
+  <si>
+    <t>使用后,下一次进入商店时所有购买价格-50%</t>
+  </si>
+  <si>
+    <t>净化药水</t>
+  </si>
+  <si>
+    <t>PurificationPotion</t>
+  </si>
+  <si>
+    <t>使用后,移除本关内的1条BOSS词缀效果</t>
+  </si>
+  <si>
+    <t>疯狂面具</t>
+  </si>
+  <si>
+    <t>MadMask</t>
+  </si>
+  <si>
+    <t>30001</t>
+  </si>
+  <si>
+    <t>造成伤害时,获得5%的生命窃取</t>
+  </si>
+  <si>
+    <t>回旋刃</t>
+  </si>
+  <si>
+    <t>BoomerangBlade</t>
+  </si>
+  <si>
+    <t>30002</t>
+  </si>
+  <si>
+    <t>亮出的牌点数提供的攻击力加成×3</t>
+  </si>
+  <si>
+    <t>致胜之剑</t>
+  </si>
+  <si>
+    <t>WinningSword</t>
+  </si>
+  <si>
+    <t>30003</t>
+  </si>
+  <si>
+    <t>结算伤害时,将留在手牌上最大的牌点数×4转化为额外攻击力</t>
+  </si>
+  <si>
+    <t>搓牌能手</t>
+  </si>
+  <si>
+    <t>CardMaster</t>
+  </si>
+  <si>
+    <t>30004</t>
+  </si>
+  <si>
+    <t>每回合内,每搓1次牌,结算时提供的倍率+1</t>
+  </si>
+  <si>
+    <t>会员卡</t>
+  </si>
+  <si>
+    <t>MemberCard</t>
+  </si>
+  <si>
+    <t>30005</t>
+  </si>
+  <si>
+    <t>每次进入商店提供1次免费刷新的机会</t>
+  </si>
+  <si>
+    <t>错峰出行</t>
+  </si>
+  <si>
+    <t>StaggeredTravel</t>
+  </si>
+  <si>
+    <t>30006</t>
+  </si>
+  <si>
+    <t>顺子牌型可以相隔1点组成</t>
+  </si>
+  <si>
+    <t>致命黑八</t>
+  </si>
+  <si>
+    <t>DeadlyBlackEight</t>
+  </si>
+  <si>
+    <t>30007</t>
+  </si>
+  <si>
+    <t>亮出的每张8在结算时提供+200攻击力</t>
+  </si>
+  <si>
+    <t>偶数韵律</t>
+  </si>
+  <si>
+    <t>EvenRhythm</t>
+  </si>
+  <si>
+    <t>30008</t>
+  </si>
+  <si>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+6倍率</t>
+  </si>
+  <si>
+    <t>奇数韵律</t>
+  </si>
+  <si>
+    <t>OddRhythm</t>
+  </si>
+  <si>
+    <t>30009</t>
+  </si>
+  <si>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+6倍率</t>
+  </si>
+  <si>
+    <t>贵族</t>
+  </si>
+  <si>
+    <t>Noble</t>
+  </si>
+  <si>
+    <t>30010</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+5倍率</t>
+  </si>
+  <si>
+    <t>工资卡</t>
+  </si>
+  <si>
+    <t>SalaryCard</t>
+  </si>
+  <si>
+    <t>30011</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,该收藏品的出售价格+5金币</t>
+  </si>
+  <si>
+    <t>训练</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>每回合首次亮牌时,随机1张亮出牌点数的攻击力永久+1,至多累计+30</t>
+  </si>
+  <si>
+    <t>九霄云外</t>
+  </si>
+  <si>
+    <t>BeyondTheClouds</t>
+  </si>
+  <si>
+    <t>30013</t>
+  </si>
+  <si>
+    <t>亮出的每张9在结算时提供15金币</t>
+  </si>
+  <si>
+    <t>后备计划</t>
+  </si>
+  <si>
+    <t>BackupPlan</t>
+  </si>
+  <si>
+    <t>30014</t>
+  </si>
+  <si>
+    <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点生命值</t>
+  </si>
+  <si>
+    <t>护身符</t>
+  </si>
+  <si>
+    <t>Amulet</t>
+  </si>
+  <si>
+    <t>30015</t>
+  </si>
+  <si>
+    <t>每关受到的第1次伤害完全免疫</t>
+  </si>
+  <si>
+    <t>复盘笔记</t>
+  </si>
+  <si>
+    <t>ReviewPlan</t>
+  </si>
+  <si>
+    <t>30016</t>
+  </si>
+  <si>
+    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
+  </si>
+  <si>
     <t>幸运同花</t>
   </si>
   <si>
     <t>LuckySameSuit</t>
   </si>
   <si>
-    <t>20025</t>
+    <t>30017</t>
   </si>
   <si>
     <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
-  </si>
-  <si>
-    <t>226</t>
-  </si>
-  <si>
-    <t>运动鞋</t>
-  </si>
-  <si>
-    <t>SportsShoes</t>
-  </si>
-  <si>
-    <t>20026</t>
-  </si>
-  <si>
-    <t>每回合结束后,提高1%闪避率,至多叠加20层</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>保温杯</t>
-  </si>
-  <si>
-    <t>ThermalMug</t>
-  </si>
-  <si>
-    <t>20027</t>
-  </si>
-  <si>
-    <t>每回合结束后,若你的血量低于50%,则恢复6点生命</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>利息</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>20028</t>
-  </si>
-  <si>
-    <t>每通过1关时,每拥有15金币获得1金币,每关至多10金币</t>
-  </si>
-  <si>
-    <t>229</t>
-  </si>
-  <si>
-    <t>小算盘</t>
-  </si>
-  <si>
-    <t>LittleAbacus</t>
-  </si>
-  <si>
-    <t>20029</t>
-  </si>
-  <si>
-    <t>每回合结束时,每剩余1次搓牌次数就获得3金币</t>
-  </si>
-  <si>
-    <t>火药</t>
-  </si>
-  <si>
-    <t>Gunpowder</t>
-  </si>
-  <si>
-    <t>使用后,本次比牌你造成的伤害翻倍</t>
-  </si>
-  <si>
-    <t>对子心得</t>
-  </si>
-  <si>
-    <t>PairExperience</t>
-  </si>
-  <si>
-    <t>使用后,对子牌型提供的倍率永久+3</t>
-  </si>
-  <si>
-    <t>黄金急救包</t>
-  </si>
-  <si>
-    <t>GoldenFirstAidKit</t>
-  </si>
-  <si>
-    <t>使用后,立即恢复60%最大生命</t>
-  </si>
-  <si>
-    <t>月光酒</t>
-  </si>
-  <si>
-    <t>MoonlightWine</t>
-  </si>
-  <si>
-    <t>每回合比牌获胜后,恢复3点生命</t>
-  </si>
-  <si>
-    <t>商人票据</t>
-  </si>
-  <si>
-    <t>MerchantTicket</t>
-  </si>
-  <si>
-    <t>使用后,下一次进入商店时所有购买价格-50%</t>
-  </si>
-  <si>
-    <t>净化药水</t>
-  </si>
-  <si>
-    <t>PurificationPotion</t>
-  </si>
-  <si>
-    <t>使用后,移除本关内的1条BOSS词缀效果</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>疯狂面具</t>
-  </si>
-  <si>
-    <t>MadMask</t>
-  </si>
-  <si>
-    <t>30001</t>
-  </si>
-  <si>
-    <t>造成伤害时,获得5%的生命窃取</t>
-  </si>
-  <si>
-    <t>回旋刃</t>
-  </si>
-  <si>
-    <t>BoomerangBlade</t>
-  </si>
-  <si>
-    <t>30002</t>
-  </si>
-  <si>
-    <t>亮出的牌点数提供的攻击力加成×3</t>
-  </si>
-  <si>
-    <t>致胜之剑</t>
-  </si>
-  <si>
-    <t>WinningSword</t>
-  </si>
-  <si>
-    <t>30003</t>
-  </si>
-  <si>
-    <t>结算伤害时,将留在手牌上最大的牌点数×4转化为额外攻击力</t>
-  </si>
-  <si>
-    <t>搓牌能手</t>
-  </si>
-  <si>
-    <t>CardMaster</t>
-  </si>
-  <si>
-    <t>30004</t>
-  </si>
-  <si>
-    <t>每回合内,每搓1次牌,结算时提供的倍率+1</t>
-  </si>
-  <si>
-    <t>会员卡</t>
-  </si>
-  <si>
-    <t>MemberCard</t>
-  </si>
-  <si>
-    <t>30005</t>
-  </si>
-  <si>
-    <t>每次进入商店提供1次免费刷新的机会</t>
-  </si>
-  <si>
-    <t>错峰出行</t>
-  </si>
-  <si>
-    <t>StaggeredTravel</t>
-  </si>
-  <si>
-    <t>30006</t>
-  </si>
-  <si>
-    <t>顺子牌型可以相隔1点组成</t>
-  </si>
-  <si>
-    <t>致命黑八</t>
-  </si>
-  <si>
-    <t>DeadlyBlackEight</t>
-  </si>
-  <si>
-    <t>30007</t>
-  </si>
-  <si>
-    <t>亮出的每张8在结算时提供+200攻击力</t>
-  </si>
-  <si>
-    <t>偶数韵律</t>
-  </si>
-  <si>
-    <t>EvenRhythm</t>
-  </si>
-  <si>
-    <t>30008</t>
-  </si>
-  <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+6倍率</t>
-  </si>
-  <si>
-    <t>奇数韵律</t>
-  </si>
-  <si>
-    <t>OddRhythm</t>
-  </si>
-  <si>
-    <t>30009</t>
-  </si>
-  <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+6倍率</t>
-  </si>
-  <si>
-    <t>贵族</t>
-  </si>
-  <si>
-    <t>Noble</t>
-  </si>
-  <si>
-    <t>30010</t>
-  </si>
-  <si>
-    <t>亮出的每张人头牌在结算时提供+5倍率</t>
-  </si>
-  <si>
-    <t>工资卡</t>
-  </si>
-  <si>
-    <t>SalaryCard</t>
-  </si>
-  <si>
-    <t>30011</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,该收藏品的出售价格+5金币</t>
-  </si>
-  <si>
-    <t>训练</t>
-  </si>
-  <si>
-    <t>Training</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>每回合首次亮牌时,随机1张亮出牌点数的攻击力永久+1,至多累计+30</t>
-  </si>
-  <si>
-    <t>九霄云外</t>
-  </si>
-  <si>
-    <t>BeyondTheClouds</t>
-  </si>
-  <si>
-    <t>30013</t>
-  </si>
-  <si>
-    <t>亮出的每张9在结算时提供15金币</t>
-  </si>
-  <si>
-    <t>后备计划</t>
-  </si>
-  <si>
-    <t>BackupPlan</t>
-  </si>
-  <si>
-    <t>30014</t>
-  </si>
-  <si>
-    <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点生命值</t>
-  </si>
-  <si>
-    <t>护身符</t>
-  </si>
-  <si>
-    <t>Amulet</t>
-  </si>
-  <si>
-    <t>30015</t>
-  </si>
-  <si>
-    <t>每关受到的第1次伤害完全免疫</t>
-  </si>
-  <si>
-    <t>复盘笔记</t>
-  </si>
-  <si>
-    <t>ReviewPlan</t>
-  </si>
-  <si>
-    <t>30016</t>
-  </si>
-  <si>
-    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
-  </si>
-  <si>
-    <t>幸运顺子</t>
-  </si>
-  <si>
-    <t>LuckyStraight</t>
-  </si>
-  <si>
-    <t>30017</t>
-  </si>
-  <si>
-    <t>亮牌时,若敌人的牌型大于顺子,则会被强行视作顺子</t>
   </si>
   <si>
     <t>逆转沙漏</t>
@@ -2579,7 +2579,7 @@
     <col min="8" max="8" width="4.78333333333333" style="3" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="5.53333333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="34.5583333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.03333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="7.70833333333333" style="3" customWidth="1"/>
     <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1" customWidth="1"/>
@@ -3212,7 +3212,7 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" s="3" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="B22">
+      <c r="B22" s="3">
         <v>118</v>
       </c>
       <c r="C22" t="s">
@@ -3265,24 +3265,24 @@
       <c r="F22" t="s">
         <v>98</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="3">
         <v>25</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="3">
         <v>12</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="3">
         <v>10018</v>
       </c>
       <c r="K22" s="3">
         <v>1</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="B23">
+      <c r="B23" s="3">
         <v>119</v>
       </c>
       <c r="C23" t="s">
@@ -3297,24 +3297,24 @@
       <c r="F23" t="s">
         <v>101</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="3">
         <v>15</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>7</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="3">
         <v>10019</v>
       </c>
       <c r="K23" s="3">
         <v>2</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="B24">
+      <c r="B24" s="3">
         <v>120</v>
       </c>
       <c r="C24" t="s">
@@ -3329,24 +3329,24 @@
       <c r="F24" t="s">
         <v>104</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="3">
         <v>25</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="3">
         <v>12</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="3">
         <v>10020</v>
       </c>
       <c r="K24" s="3">
         <v>1</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="B25">
+      <c r="B25" s="3">
         <v>121</v>
       </c>
       <c r="C25" t="s">
@@ -3361,21 +3361,25 @@
       <c r="F25" t="s">
         <v>107</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="3">
         <v>30</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="3">
         <v>15</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="3">
         <v>10021</v>
       </c>
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="3" t="s">
         <v>108</v>
       </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="K26" s="3"/>
+      <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12">
       <c r="B27" s="1" t="s">
@@ -3999,7 +4003,7 @@
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" t="s">
+      <c r="L45" s="3" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4033,7 +4037,7 @@
       <c r="K46" s="3">
         <v>0</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" s="3" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4067,7 +4071,7 @@
       <c r="K47" s="3">
         <v>0</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="3" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4101,7 +4105,7 @@
       <c r="K48" s="3">
         <v>0</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" s="3" t="s">
         <v>219</v>
       </c>
     </row>
@@ -4135,7 +4139,7 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L49" s="3" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4169,48 +4173,47 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" spans="1:12">
-      <c r="A51"/>
+    <row r="51" spans="1:12">
       <c r="B51" s="1" t="s">
         <v>230</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>110</v>
+        <v>231</v>
       </c>
       <c r="D51" s="3">
         <v>0.4</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G51" s="3">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H51" s="3">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J51" s="3"/>
+        <v>234</v>
+      </c>
+      <c r="J51" s="1"/>
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" t="s">
-        <v>234</v>
+      <c r="L51" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52"/>
       <c r="B52" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>110</v>
@@ -4219,10 +4222,10 @@
         <v>0.4</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G52" s="3">
         <v>120</v>
@@ -4231,19 +4234,19 @@
         <v>60</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" t="s">
-        <v>239</v>
+      <c r="L52" s="3" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53"/>
       <c r="B53" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>110</v>
@@ -4252,10 +4255,10 @@
         <v>0.4</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G53" s="3">
         <v>110</v>
@@ -4264,19 +4267,19 @@
         <v>55</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" t="s">
-        <v>244</v>
+      <c r="L53" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54"/>
       <c r="B54" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>110</v>
@@ -4285,10 +4288,10 @@
         <v>0.4</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G54" s="3">
         <v>70</v>
@@ -4297,19 +4300,19 @@
         <v>35</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K54" s="3">
         <v>0</v>
       </c>
-      <c r="L54" t="s">
-        <v>249</v>
+      <c r="L54" s="3" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55"/>
       <c r="B55" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>110</v>
@@ -4318,10 +4321,10 @@
         <v>0.4</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G55" s="3">
         <v>160</v>
@@ -4330,17 +4333,17 @@
         <v>80</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K55" s="3">
         <v>0</v>
       </c>
-      <c r="L55" t="s">
-        <v>254</v>
+      <c r="L55" s="3" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="56" spans="1:12">
-      <c r="B56">
+      <c r="B56" s="3">
         <v>230</v>
       </c>
       <c r="C56" t="s">
@@ -4350,29 +4353,29 @@
         <v>0.4</v>
       </c>
       <c r="E56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F56" t="s">
-        <v>256</v>
-      </c>
-      <c r="G56">
+        <v>257</v>
+      </c>
+      <c r="G56" s="3">
         <v>90</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="3">
         <v>45</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="3">
         <v>20030</v>
       </c>
       <c r="K56" s="3">
         <v>1</v>
       </c>
-      <c r="L56" t="s">
-        <v>257</v>
+      <c r="L56" s="3" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:12">
-      <c r="B57">
+      <c r="B57" s="3">
         <v>231</v>
       </c>
       <c r="C57" t="s">
@@ -4382,29 +4385,29 @@
         <v>0.4</v>
       </c>
       <c r="E57" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F57" t="s">
-        <v>259</v>
-      </c>
-      <c r="G57">
+        <v>260</v>
+      </c>
+      <c r="G57" s="3">
         <v>70</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="3">
         <v>35</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="3">
         <v>20031</v>
       </c>
       <c r="K57" s="3">
         <v>2</v>
       </c>
-      <c r="L57" t="s">
-        <v>260</v>
+      <c r="L57" s="3" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:12">
-      <c r="B58">
+      <c r="B58" s="3">
         <v>232</v>
       </c>
       <c r="C58" t="s">
@@ -4414,29 +4417,29 @@
         <v>0.4</v>
       </c>
       <c r="E58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F58" t="s">
-        <v>262</v>
-      </c>
-      <c r="G58">
+        <v>263</v>
+      </c>
+      <c r="G58" s="3">
         <v>145</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="3">
         <v>72</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="3">
         <v>20032</v>
       </c>
       <c r="K58" s="3">
         <v>1</v>
       </c>
-      <c r="L58" t="s">
-        <v>263</v>
+      <c r="L58" s="3" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:12">
-      <c r="B59">
+      <c r="B59" s="3">
         <v>233</v>
       </c>
       <c r="C59" t="s">
@@ -4446,29 +4449,29 @@
         <v>0.4</v>
       </c>
       <c r="E59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F59" t="s">
-        <v>265</v>
-      </c>
-      <c r="G59">
+        <v>266</v>
+      </c>
+      <c r="G59" s="3">
         <v>75</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="3">
         <v>37</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <v>20033</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" t="s">
-        <v>266</v>
+      <c r="L59" s="3" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="60" spans="1:12">
-      <c r="B60">
+      <c r="B60" s="3">
         <v>234</v>
       </c>
       <c r="C60" t="s">
@@ -4478,29 +4481,29 @@
         <v>0.4</v>
       </c>
       <c r="E60" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F60" t="s">
-        <v>268</v>
-      </c>
-      <c r="G60">
+        <v>269</v>
+      </c>
+      <c r="G60" s="3">
         <v>110</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="3">
         <v>55</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="3">
         <v>20034</v>
       </c>
       <c r="K60" s="3">
         <v>1</v>
       </c>
-      <c r="L60" t="s">
-        <v>269</v>
+      <c r="L60" s="3" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:12">
-      <c r="B61">
+      <c r="B61" s="3">
         <v>235</v>
       </c>
       <c r="C61" t="s">
@@ -4510,25 +4513,25 @@
         <v>0.4</v>
       </c>
       <c r="E61" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F61" t="s">
-        <v>271</v>
-      </c>
-      <c r="G61">
+        <v>272</v>
+      </c>
+      <c r="G61" s="3">
         <v>140</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="3">
         <v>70</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="3">
         <v>20035</v>
       </c>
       <c r="K61" s="3">
         <v>1</v>
       </c>
-      <c r="L61" t="s">
-        <v>272</v>
+      <c r="L61" s="3" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -4537,6 +4540,8 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
+      <c r="K62" s="3"/>
+      <c r="L62" s="1"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63"/>
@@ -4544,7 +4549,7 @@
         <v>301</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D63" s="3">
         <v>0.2</v>
@@ -4580,7 +4585,7 @@
         <v>302</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D64" s="3">
         <v>0.2</v>
@@ -4613,7 +4618,7 @@
         <v>303</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D65" s="3">
         <v>0.2</v>
@@ -4646,7 +4651,7 @@
         <v>304</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D66" s="3">
         <v>0.2</v>
@@ -4682,7 +4687,7 @@
         <v>305</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D67" s="3">
         <v>0.2</v>
@@ -4717,7 +4722,7 @@
         <v>306</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D68" s="3">
         <v>0.2</v>
@@ -4752,7 +4757,7 @@
         <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D69" s="3">
         <v>0.2</v>
@@ -4784,7 +4789,7 @@
         <v>308</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D70" s="3">
         <v>0.2</v>
@@ -4816,7 +4821,7 @@
         <v>309</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D71" s="3">
         <v>0.2</v>
@@ -4848,7 +4853,7 @@
         <v>310</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D72" s="3">
         <v>0.2</v>
@@ -4880,7 +4885,7 @@
         <v>311</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D73" s="3">
         <v>0.2</v>
@@ -4912,7 +4917,7 @@
         <v>312</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D74" s="3">
         <v>0.2</v>
@@ -4944,7 +4949,7 @@
         <v>313</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D75" s="3">
         <v>0.2</v>
@@ -4976,7 +4981,7 @@
         <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D76" s="3">
         <v>0.2</v>
@@ -5000,7 +5005,7 @@
       <c r="K76" s="3">
         <v>0</v>
       </c>
-      <c r="L76" t="s">
+      <c r="L76" s="3" t="s">
         <v>329</v>
       </c>
     </row>
@@ -5009,7 +5014,7 @@
         <v>315</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D77" s="3">
         <v>0.2</v>
@@ -5033,7 +5038,7 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" t="s">
+      <c r="L77" s="3" t="s">
         <v>333</v>
       </c>
     </row>
@@ -5042,7 +5047,7 @@
         <v>316</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D78" s="3">
         <v>0.2</v>
@@ -5065,7 +5070,7 @@
       <c r="K78" s="3">
         <v>0</v>
       </c>
-      <c r="L78" t="s">
+      <c r="L78" s="3" t="s">
         <v>337</v>
       </c>
     </row>
@@ -5074,7 +5079,7 @@
         <v>317</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="D79" s="3">
         <v>0.2</v>
@@ -5086,18 +5091,19 @@
         <v>339</v>
       </c>
       <c r="G79" s="3">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="H79" s="3">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>340</v>
       </c>
+      <c r="J79" s="1"/>
       <c r="K79" s="3">
         <v>0</v>
       </c>
-      <c r="L79" t="s">
+      <c r="L79" s="3" t="s">
         <v>341</v>
       </c>
     </row>
@@ -5106,7 +5112,7 @@
         <v>318</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D80" s="3">
         <v>0.2</v>
@@ -5129,7 +5135,7 @@
       <c r="K80" s="3">
         <v>0</v>
       </c>
-      <c r="L80" t="s">
+      <c r="L80" s="3" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5138,7 +5144,7 @@
         <v>319</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D81" s="3">
         <v>0.2</v>
@@ -5161,7 +5167,7 @@
       <c r="K81" s="3">
         <v>0</v>
       </c>
-      <c r="L81" t="s">
+      <c r="L81" s="3" t="s">
         <v>349</v>
       </c>
     </row>
@@ -5170,7 +5176,7 @@
         <v>320</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D82" s="3">
         <v>0.2</v>
@@ -5193,7 +5199,7 @@
       <c r="K82" s="3">
         <v>0</v>
       </c>
-      <c r="L82" t="s">
+      <c r="L82" s="3" t="s">
         <v>353</v>
       </c>
     </row>
@@ -5202,7 +5208,7 @@
         <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D83" s="3">
         <v>0.2</v>
@@ -5225,7 +5231,7 @@
       <c r="K83" s="3">
         <v>0</v>
       </c>
-      <c r="L83" t="s">
+      <c r="L83" s="3" t="s">
         <v>357</v>
       </c>
     </row>
@@ -5234,7 +5240,7 @@
         <v>322</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D84" s="3">
         <v>0.2</v>
@@ -5257,7 +5263,7 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" t="s">
+      <c r="L84" s="3" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5266,7 +5272,7 @@
         <v>323</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D85" s="3">
         <v>0.2</v>
@@ -5289,7 +5295,7 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" t="s">
+      <c r="L85" s="3" t="s">
         <v>365</v>
       </c>
     </row>
@@ -5298,7 +5304,7 @@
         <v>324</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D86" s="3">
         <v>0.2</v>
@@ -5321,7 +5327,7 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" t="s">
+      <c r="L86" s="3" t="s">
         <v>369</v>
       </c>
     </row>
@@ -5330,7 +5336,7 @@
         <v>325</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D87" s="3">
         <v>0.2</v>
@@ -5353,16 +5359,16 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" t="s">
+      <c r="L87" s="3" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="88" spans="2:12">
-      <c r="B88">
+      <c r="B88" s="3">
         <v>326</v>
       </c>
       <c r="C88" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D88" s="3">
         <v>0.2</v>
@@ -5373,28 +5379,28 @@
       <c r="F88" t="s">
         <v>375</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="3">
         <v>190</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="3">
         <v>95</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="3">
         <v>30026</v>
       </c>
       <c r="K88" s="3">
         <v>2</v>
       </c>
-      <c r="L88" t="s">
+      <c r="L88" s="3" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="89" spans="2:12">
-      <c r="B89">
+      <c r="B89" s="3">
         <v>327</v>
       </c>
       <c r="C89" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D89" s="3">
         <v>0.2</v>
@@ -5405,28 +5411,28 @@
       <c r="F89" t="s">
         <v>378</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="3">
         <v>160</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="3">
         <v>80</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="3">
         <v>30027</v>
       </c>
       <c r="K89" s="3">
         <v>2</v>
       </c>
-      <c r="L89" t="s">
+      <c r="L89" s="3" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="90" spans="2:12">
-      <c r="B90">
+      <c r="B90" s="3">
         <v>328</v>
       </c>
       <c r="C90" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D90" s="3">
         <v>0.2</v>
@@ -5437,28 +5443,28 @@
       <c r="F90" t="s">
         <v>381</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="3">
         <v>200</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="3">
         <v>100</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="3">
         <v>30028</v>
       </c>
       <c r="K90" s="3">
         <v>1</v>
       </c>
-      <c r="L90" t="s">
+      <c r="L90" s="3" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="91" spans="2:12">
-      <c r="B91">
+      <c r="B91" s="3">
         <v>329</v>
       </c>
       <c r="C91" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D91" s="3">
         <v>0.2</v>
@@ -5469,28 +5475,28 @@
       <c r="F91" t="s">
         <v>384</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="3">
         <v>170</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="3">
         <v>85</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="3">
         <v>30029</v>
       </c>
       <c r="K91" s="3">
         <v>1</v>
       </c>
-      <c r="L91" t="s">
+      <c r="L91" s="3" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="92" spans="2:12">
-      <c r="B92">
+      <c r="B92" s="3">
         <v>330</v>
       </c>
       <c r="C92" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="D92" s="3">
         <v>0.2</v>
@@ -5501,19 +5507,19 @@
       <c r="F92" t="s">
         <v>387</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="3">
         <v>180</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="3">
         <v>90</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="3">
         <v>30030</v>
       </c>
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" t="s">
+      <c r="L92" s="3" t="s">
         <v>388</v>
       </c>
     </row>
@@ -6006,7 +6012,7 @@
       <c r="K108" s="3">
         <v>0</v>
       </c>
-      <c r="L108" t="s">
+      <c r="L108" s="3" t="s">
         <v>463</v>
       </c>
     </row>
@@ -6038,7 +6044,7 @@
       <c r="K109" s="3">
         <v>0</v>
       </c>
-      <c r="L109" t="s">
+      <c r="L109" s="3" t="s">
         <v>467</v>
       </c>
     </row>
@@ -6070,7 +6076,7 @@
       <c r="K110" s="3">
         <v>0</v>
       </c>
-      <c r="L110" t="s">
+      <c r="L110" s="3" t="s">
         <v>471</v>
       </c>
     </row>
@@ -6102,7 +6108,7 @@
       <c r="K111" s="3">
         <v>0</v>
       </c>
-      <c r="L111" t="s">
+      <c r="L111" s="3" t="s">
         <v>475</v>
       </c>
     </row>
@@ -6134,7 +6140,7 @@
       <c r="K112" s="3">
         <v>0</v>
       </c>
-      <c r="L112" t="s">
+      <c r="L112" s="3" t="s">
         <v>479</v>
       </c>
     </row>
@@ -6166,7 +6172,7 @@
       <c r="K113" s="3">
         <v>0</v>
       </c>
-      <c r="L113" t="s">
+      <c r="L113" s="3" t="s">
         <v>483</v>
       </c>
     </row>
@@ -6198,7 +6204,7 @@
       <c r="K114" s="3">
         <v>0</v>
       </c>
-      <c r="L114" t="s">
+      <c r="L114" s="3" t="s">
         <v>487</v>
       </c>
     </row>
@@ -6230,7 +6236,7 @@
       <c r="K115" s="3">
         <v>0</v>
       </c>
-      <c r="L115" t="s">
+      <c r="L115" s="3" t="s">
         <v>492</v>
       </c>
     </row>
@@ -6262,7 +6268,7 @@
       <c r="K116" s="3">
         <v>0</v>
       </c>
-      <c r="L116" t="s">
+      <c r="L116" s="3" t="s">
         <v>496</v>
       </c>
     </row>
@@ -6294,7 +6300,7 @@
       <c r="K117" s="3">
         <v>0</v>
       </c>
-      <c r="L117" t="s">
+      <c r="L117" s="3" t="s">
         <v>500</v>
       </c>
     </row>
@@ -6326,12 +6332,12 @@
       <c r="K118" s="3">
         <v>0</v>
       </c>
-      <c r="L118" t="s">
+      <c r="L118" s="3" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="119" spans="2:12">
-      <c r="B119">
+      <c r="B119" s="3">
         <v>426</v>
       </c>
       <c r="C119" t="s">
@@ -6346,24 +6352,24 @@
       <c r="F119" t="s">
         <v>506</v>
       </c>
-      <c r="G119">
+      <c r="G119" s="3">
         <v>400</v>
       </c>
-      <c r="H119">
+      <c r="H119" s="3">
         <v>200</v>
       </c>
-      <c r="I119">
+      <c r="I119" s="3">
         <v>40026</v>
       </c>
       <c r="K119" s="3">
         <v>1</v>
       </c>
-      <c r="L119" t="s">
+      <c r="L119" s="3" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="120" spans="2:12">
-      <c r="B120">
+      <c r="B120" s="3">
         <v>427</v>
       </c>
       <c r="C120" t="s">
@@ -6378,24 +6384,24 @@
       <c r="F120" t="s">
         <v>509</v>
       </c>
-      <c r="G120">
+      <c r="G120" s="3">
         <v>330</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="3">
         <v>165</v>
       </c>
-      <c r="I120">
+      <c r="I120" s="3">
         <v>40027</v>
       </c>
       <c r="K120" s="3">
         <v>1</v>
       </c>
-      <c r="L120" t="s">
+      <c r="L120" s="3" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="121" spans="2:12">
-      <c r="B121">
+      <c r="B121" s="3">
         <v>428</v>
       </c>
       <c r="C121" t="s">
@@ -6410,24 +6416,24 @@
       <c r="F121" t="s">
         <v>512</v>
       </c>
-      <c r="G121">
+      <c r="G121" s="3">
         <v>260</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="3">
         <v>130</v>
       </c>
-      <c r="I121">
+      <c r="I121" s="3">
         <v>40028</v>
       </c>
       <c r="K121" s="3">
         <v>2</v>
       </c>
-      <c r="L121" t="s">
+      <c r="L121" s="3" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="122" spans="2:12">
-      <c r="B122">
+      <c r="B122" s="3">
         <v>429</v>
       </c>
       <c r="C122" t="s">
@@ -6442,24 +6448,24 @@
       <c r="F122" t="s">
         <v>515</v>
       </c>
-      <c r="G122">
+      <c r="G122" s="3">
         <v>270</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="3">
         <v>135</v>
       </c>
-      <c r="I122">
+      <c r="I122" s="3">
         <v>40029</v>
       </c>
       <c r="K122" s="3">
         <v>2</v>
       </c>
-      <c r="L122" t="s">
+      <c r="L122" s="3" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="123" spans="2:12">
-      <c r="B123">
+      <c r="B123" s="3">
         <v>430</v>
       </c>
       <c r="C123" t="s">
@@ -6474,19 +6480,19 @@
       <c r="F123" t="s">
         <v>518</v>
       </c>
-      <c r="G123">
+      <c r="G123" s="3">
         <v>280</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="3">
         <v>140</v>
       </c>
-      <c r="I123">
+      <c r="I123" s="3">
         <v>40030</v>
       </c>
       <c r="K123" s="3">
         <v>0</v>
       </c>
-      <c r="L123" t="s">
+      <c r="L123" s="3" t="s">
         <v>519</v>
       </c>
     </row>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17820" windowHeight="11520"/>
+    <workbookView windowWidth="19995" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1757,12 +1757,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2083,7 +2089,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -2107,16 +2113,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -2125,89 +2131,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2216,6 +2222,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4809,6 +4818,9 @@
       <c r="I70" s="1" t="s">
         <v>304</v>
       </c>
+      <c r="J70" s="4">
+        <v>1009</v>
+      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -4873,6 +4885,9 @@
       <c r="I72" s="1" t="s">
         <v>312</v>
       </c>
+      <c r="J72" s="4">
+        <v>1013</v>
+      </c>
       <c r="K72" s="3">
         <v>0</v>
       </c>
@@ -4969,6 +4984,9 @@
       <c r="I75" s="1" t="s">
         <v>324</v>
       </c>
+      <c r="J75" s="4">
+        <v>1010</v>
+      </c>
       <c r="K75" s="3">
         <v>0</v>
       </c>
@@ -5164,6 +5182,9 @@
       <c r="I81" s="1" t="s">
         <v>348</v>
       </c>
+      <c r="J81" s="4">
+        <v>1011</v>
+      </c>
       <c r="K81" s="3">
         <v>0</v>
       </c>
@@ -5324,6 +5345,9 @@
       <c r="I86" s="1" t="s">
         <v>368</v>
       </c>
+      <c r="J86" s="4">
+        <v>1012</v>
+      </c>
       <c r="K86" s="3">
         <v>0</v>
       </c>
@@ -5387,6 +5411,9 @@
       </c>
       <c r="I88" s="3">
         <v>30026</v>
+      </c>
+      <c r="J88" s="4">
+        <v>1013</v>
       </c>
       <c r="K88" s="3">
         <v>2</v>
@@ -5683,6 +5710,9 @@
       <c r="I98" s="1" t="s">
         <v>412</v>
       </c>
+      <c r="J98" s="4">
+        <v>1014</v>
+      </c>
       <c r="K98" s="3">
         <v>0</v>
       </c>
@@ -5779,6 +5809,9 @@
       <c r="I101" s="1" t="s">
         <v>427</v>
       </c>
+      <c r="J101" s="4">
+        <v>1015</v>
+      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
@@ -5907,6 +5940,9 @@
       <c r="I105" s="1" t="s">
         <v>447</v>
       </c>
+      <c r="J105" s="4">
+        <v>1016</v>
+      </c>
       <c r="K105" s="3">
         <v>0</v>
       </c>
@@ -6041,6 +6077,9 @@
       <c r="I109" s="3">
         <v>40016</v>
       </c>
+      <c r="J109" s="4">
+        <v>1017</v>
+      </c>
       <c r="K109" s="3">
         <v>0</v>
       </c>
@@ -6169,6 +6208,9 @@
       <c r="I113" s="3">
         <v>40020</v>
       </c>
+      <c r="J113" s="4">
+        <v>1018</v>
+      </c>
       <c r="K113" s="3">
         <v>0</v>
       </c>
@@ -6296,6 +6338,9 @@
       </c>
       <c r="I117" s="3">
         <v>40024</v>
+      </c>
+      <c r="J117" s="4">
+        <v>1020</v>
       </c>
       <c r="K117" s="3">
         <v>0</v>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19995" windowHeight="11520"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="527">
   <si>
     <t>##var</t>
   </si>
@@ -1199,6 +1199,27 @@
   </si>
   <si>
     <t>每通过1关时,获得25金币</t>
+  </si>
+  <si>
+    <t>降低</t>
+  </si>
+  <si>
+    <t>ReduceLevel</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>比牌时,对方的牌型顺位降低1级</t>
+  </si>
+  <si>
+    <t>升职</t>
+  </si>
+  <si>
+    <t>UpLevel</t>
+  </si>
+  <si>
+    <t>比牌时,自己的牌型顺位提高1级</t>
   </si>
   <si>
     <t>401</t>
@@ -2213,7 +2234,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2225,6 +2246,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2575,7 +2602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
@@ -5518,7 +5545,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="92" spans="2:12">
+    <row r="92" ht="14.25" spans="2:12">
       <c r="B92" s="3">
         <v>330</v>
       </c>
@@ -5550,523 +5577,520 @@
         <v>388</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1"/>
+    <row r="93" s="1" customFormat="1" spans="2:12">
+      <c r="B93" s="3">
+        <v>331</v>
+      </c>
+      <c r="C93" t="s">
+        <v>231</v>
+      </c>
+      <c r="D93" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G93" s="6">
+        <v>260</v>
+      </c>
+      <c r="H93" s="6">
+        <v>130</v>
+      </c>
+      <c r="I93" s="3">
+        <v>30031</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="L93" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
     <row r="94" s="1" customFormat="1" spans="2:12">
-      <c r="B94" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>390</v>
+      <c r="B94" s="3">
+        <v>332</v>
+      </c>
+      <c r="C94" t="s">
+        <v>231</v>
       </c>
       <c r="D94" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E94" s="3">
-        <v>235</v>
-      </c>
-      <c r="F94" s="3" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G94" s="6">
+        <v>260</v>
+      </c>
+      <c r="H94" s="6">
+        <v>130</v>
+      </c>
+      <c r="I94" s="3">
+        <v>30032</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="G94" s="3">
-        <v>650</v>
-      </c>
-      <c r="H94" s="3">
-        <v>325</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="J94" s="3">
-        <v>1005</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="2:12">
-      <c r="B95" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="D95" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E95" s="3" t="s">
+      <c r="L94" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="G95" s="3">
-        <v>680</v>
-      </c>
-      <c r="H95" s="3">
-        <v>340</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="J95" s="3">
-        <v>1006</v>
-      </c>
-      <c r="K95" s="3">
-        <v>0</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
+    </row>
+    <row r="95" s="1" customFormat="1"/>
     <row r="96" s="1" customFormat="1" spans="2:12">
       <c r="B96" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D96" s="3">
         <v>0.1</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="3">
+        <v>235</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="G96" s="3">
+        <v>650</v>
+      </c>
+      <c r="H96" s="3">
+        <v>325</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1005</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="G96" s="3">
-        <v>600</v>
-      </c>
-      <c r="H96" s="3">
-        <v>300</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:12">
       <c r="B97" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D97" s="3">
         <v>0.1</v>
       </c>
       <c r="E97" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="G97" s="3">
+        <v>680</v>
+      </c>
+      <c r="H97" s="3">
+        <v>340</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="J97" s="3">
+        <v>1006</v>
+      </c>
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="G97" s="3">
-        <v>480</v>
-      </c>
-      <c r="H97" s="3">
-        <v>240</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="K97" s="3">
-        <v>0</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:12">
       <c r="B98" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D98" s="3">
         <v>0.1</v>
       </c>
       <c r="E98" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="G98" s="3">
+        <v>600</v>
+      </c>
+      <c r="H98" s="3">
+        <v>300</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="G98" s="3">
-        <v>460</v>
-      </c>
-      <c r="H98" s="3">
-        <v>230</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="J98" s="4">
-        <v>1014</v>
-      </c>
-      <c r="K98" s="3">
-        <v>0</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="2:12">
       <c r="B99" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D99" s="3">
         <v>0.1</v>
       </c>
       <c r="E99" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="G99" s="3">
+        <v>480</v>
+      </c>
+      <c r="H99" s="3">
+        <v>240</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="G99" s="3">
-        <v>320</v>
-      </c>
-      <c r="H99" s="3">
-        <v>160</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="K99" s="3">
-        <v>0</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:12">
       <c r="B100" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D100" s="3">
         <v>0.1</v>
       </c>
       <c r="E100" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="G100" s="3">
+        <v>460</v>
+      </c>
+      <c r="H100" s="3">
+        <v>230</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="J100" s="4">
+        <v>1014</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="G100" s="3">
-        <v>380</v>
-      </c>
-      <c r="H100" s="3">
-        <v>190</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:12">
       <c r="B101" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D101" s="3">
         <v>0.1</v>
       </c>
       <c r="E101" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="G101" s="3">
+        <v>320</v>
+      </c>
+      <c r="H101" s="3">
+        <v>160</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
         <v>425</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="G101" s="3">
-        <v>600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>300</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="J101" s="4">
-        <v>1015</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="2:12">
       <c r="B102" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D102" s="3">
         <v>0.1</v>
       </c>
       <c r="E102" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G102" s="3">
+        <v>380</v>
+      </c>
+      <c r="H102" s="3">
+        <v>190</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="G102" s="3">
-        <v>300</v>
-      </c>
-      <c r="H102" s="3">
-        <v>150</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:12">
       <c r="B103" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D103" s="3">
         <v>0.1</v>
       </c>
       <c r="E103" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="G103" s="3">
+        <v>600</v>
+      </c>
+      <c r="H103" s="3">
+        <v>300</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="J103" s="4">
+        <v>1015</v>
+      </c>
+      <c r="K103" s="3">
+        <v>0</v>
+      </c>
+      <c r="L103" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="F103" s="3" t="s">
+    </row>
+    <row r="104" s="1" customFormat="1" spans="2:12">
+      <c r="B104" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="G103" s="3">
-        <v>300</v>
-      </c>
-      <c r="H103" s="3">
-        <v>150</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="K103" s="3">
-        <v>0</v>
-      </c>
-      <c r="L103" s="3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="104" spans="2:12">
-      <c r="B104" s="1" t="s">
-        <v>439</v>
-      </c>
       <c r="C104" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D104" s="3">
         <v>0.1</v>
       </c>
       <c r="E104" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="G104" s="3">
+        <v>300</v>
+      </c>
+      <c r="H104" s="3">
+        <v>150</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="K104" s="3">
+        <v>0</v>
+      </c>
+      <c r="L104" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="F104" s="3" t="s">
+    </row>
+    <row r="105" s="1" customFormat="1" spans="2:12">
+      <c r="B105" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="G104" s="3">
-        <v>400</v>
-      </c>
-      <c r="H104" s="3">
-        <v>200</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="K104" s="3">
-        <v>0</v>
-      </c>
-      <c r="L104" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="105" spans="2:12">
-      <c r="B105" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="C105" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D105" s="3">
         <v>0.1</v>
       </c>
       <c r="E105" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="G105" s="3">
+        <v>300</v>
+      </c>
+      <c r="H105" s="3">
+        <v>150</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="K105" s="3">
+        <v>0</v>
+      </c>
+      <c r="L105" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="G105" s="3">
-        <v>460</v>
-      </c>
-      <c r="H105" s="3">
-        <v>230</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="J105" s="4">
-        <v>1016</v>
-      </c>
-      <c r="K105" s="3">
-        <v>0</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="106" spans="2:12">
       <c r="B106" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D106" s="3">
         <v>0.1</v>
       </c>
       <c r="E106" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G106" s="3">
+        <v>400</v>
+      </c>
+      <c r="H106" s="3">
+        <v>200</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="K106" s="3">
+        <v>0</v>
+      </c>
+      <c r="L106" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="G106" s="3">
-        <v>340</v>
-      </c>
-      <c r="H106" s="3">
-        <v>170</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="J106" s="3">
-        <v>1007</v>
-      </c>
-      <c r="K106" s="3">
-        <v>0</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="107" spans="2:12">
       <c r="B107" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D107" s="3">
         <v>0.1</v>
       </c>
       <c r="E107" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="G107" s="3">
+        <v>460</v>
+      </c>
+      <c r="H107" s="3">
+        <v>230</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="J107" s="4">
+        <v>1016</v>
+      </c>
+      <c r="K107" s="3">
+        <v>0</v>
+      </c>
+      <c r="L107" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G107" s="3">
-        <v>280</v>
-      </c>
-      <c r="H107" s="3">
-        <v>140</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J107" s="3">
-        <v>1008</v>
-      </c>
-      <c r="K107" s="3">
-        <v>0</v>
-      </c>
-      <c r="L107" s="3" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="108" spans="2:12">
       <c r="B108" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D108" s="3">
         <v>0.1</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="G108" s="3">
+        <v>340</v>
+      </c>
+      <c r="H108" s="3">
+        <v>170</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="J108" s="3">
+        <v>1007</v>
+      </c>
+      <c r="K108" s="3">
+        <v>0</v>
+      </c>
+      <c r="L108" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="G108" s="3">
-        <v>600</v>
-      </c>
-      <c r="H108" s="3">
-        <v>300</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="K108" s="3">
-        <v>0</v>
-      </c>
-      <c r="L108" s="3" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="109" spans="2:12">
       <c r="B109" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D109" s="3">
         <v>0.1</v>
       </c>
-      <c r="E109" t="s">
-        <v>465</v>
+      <c r="E109" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G109" s="3">
         <v>280</v>
@@ -6074,98 +6098,101 @@
       <c r="H109" s="3">
         <v>140</v>
       </c>
-      <c r="I109" s="3">
-        <v>40016</v>
-      </c>
-      <c r="J109" s="4">
-        <v>1017</v>
+      <c r="I109" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J109" s="3">
+        <v>1008</v>
       </c>
       <c r="K109" s="3">
         <v>0</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="110" spans="2:12">
       <c r="B110" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D110" s="3">
         <v>0.1</v>
       </c>
       <c r="E110" t="s">
+        <v>467</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="G110" s="3">
+        <v>600</v>
+      </c>
+      <c r="H110" s="3">
+        <v>300</v>
+      </c>
+      <c r="I110" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="K110" s="3">
+        <v>0</v>
+      </c>
+      <c r="L110" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="G110" s="3">
-        <v>300</v>
-      </c>
-      <c r="H110" s="3">
-        <v>150</v>
-      </c>
-      <c r="I110" s="3">
-        <v>40017</v>
-      </c>
-      <c r="K110" s="3">
-        <v>0</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="111" spans="2:12">
       <c r="B111" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D111" s="3">
         <v>0.1</v>
       </c>
       <c r="E111" t="s">
+        <v>472</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="G111" s="3">
+        <v>280</v>
+      </c>
+      <c r="H111" s="3">
+        <v>140</v>
+      </c>
+      <c r="I111" s="3">
+        <v>40016</v>
+      </c>
+      <c r="J111" s="4">
+        <v>1017</v>
+      </c>
+      <c r="K111" s="3">
+        <v>0</v>
+      </c>
+      <c r="L111" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="G111" s="3">
-        <v>520</v>
-      </c>
-      <c r="H111" s="3">
-        <v>260</v>
-      </c>
-      <c r="I111" s="3">
-        <v>40018</v>
-      </c>
-      <c r="K111" s="3">
-        <v>0</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="112" spans="2:12">
       <c r="B112" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D112" s="3">
         <v>0.1</v>
       </c>
       <c r="E112" t="s">
+        <v>476</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="G112" s="3">
         <v>300</v>
@@ -6174,219 +6201,216 @@
         <v>150</v>
       </c>
       <c r="I112" s="3">
-        <v>40019</v>
+        <v>40017</v>
       </c>
       <c r="K112" s="3">
         <v>0</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="113" spans="2:12">
       <c r="B113" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D113" s="3">
         <v>0.1</v>
       </c>
       <c r="E113" t="s">
+        <v>480</v>
+      </c>
+      <c r="F113" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="G113" s="3">
+        <v>520</v>
+      </c>
+      <c r="H113" s="3">
+        <v>260</v>
+      </c>
+      <c r="I113" s="3">
+        <v>40018</v>
+      </c>
+      <c r="K113" s="3">
+        <v>0</v>
+      </c>
+      <c r="L113" s="3" t="s">
         <v>482</v>
-      </c>
-      <c r="G113" s="3">
-        <v>560</v>
-      </c>
-      <c r="H113" s="3">
-        <v>280</v>
-      </c>
-      <c r="I113" s="3">
-        <v>40020</v>
-      </c>
-      <c r="J113" s="4">
-        <v>1018</v>
-      </c>
-      <c r="K113" s="3">
-        <v>0</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="114" spans="2:12">
       <c r="B114" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D114" s="3">
         <v>0.1</v>
       </c>
       <c r="E114" t="s">
+        <v>484</v>
+      </c>
+      <c r="F114" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="G114" s="3">
+        <v>300</v>
+      </c>
+      <c r="H114" s="3">
+        <v>150</v>
+      </c>
+      <c r="I114" s="3">
+        <v>40019</v>
+      </c>
+      <c r="K114" s="3">
+        <v>0</v>
+      </c>
+      <c r="L114" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="G114" s="3">
-        <v>620</v>
-      </c>
-      <c r="H114" s="3">
-        <v>310</v>
-      </c>
-      <c r="I114" s="3">
-        <v>40021</v>
-      </c>
-      <c r="K114" s="3">
-        <v>0</v>
-      </c>
-      <c r="L114" s="3" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="115" spans="2:12">
       <c r="B115" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D115" s="3">
         <v>0.1</v>
       </c>
       <c r="E115" t="s">
+        <v>488</v>
+      </c>
+      <c r="F115" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="G115" s="3">
+        <v>560</v>
+      </c>
+      <c r="H115" s="3">
+        <v>280</v>
+      </c>
+      <c r="I115" s="3">
+        <v>40020</v>
+      </c>
+      <c r="J115" s="4">
+        <v>1018</v>
+      </c>
+      <c r="K115" s="3">
+        <v>0</v>
+      </c>
+      <c r="L115" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="G115" s="3">
-        <v>320</v>
-      </c>
-      <c r="H115" s="3">
-        <v>160</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="K115" s="3">
-        <v>0</v>
-      </c>
-      <c r="L115" s="3" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="116" spans="2:12">
       <c r="B116" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D116" s="3">
         <v>0.1</v>
       </c>
       <c r="E116" t="s">
+        <v>492</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="G116" s="3">
+        <v>620</v>
+      </c>
+      <c r="H116" s="3">
+        <v>310</v>
+      </c>
+      <c r="I116" s="3">
+        <v>40021</v>
+      </c>
+      <c r="K116" s="3">
+        <v>0</v>
+      </c>
+      <c r="L116" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="G116" s="3">
-        <v>450</v>
-      </c>
-      <c r="H116" s="3">
-        <v>225</v>
-      </c>
-      <c r="I116" s="3">
-        <v>40023</v>
-      </c>
-      <c r="K116" s="3">
-        <v>0</v>
-      </c>
-      <c r="L116" s="3" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="117" spans="2:12">
       <c r="B117" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D117" s="3">
         <v>0.1</v>
       </c>
       <c r="E117" t="s">
+        <v>496</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="G117" s="3">
+        <v>320</v>
+      </c>
+      <c r="H117" s="3">
+        <v>160</v>
+      </c>
+      <c r="I117" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="K117" s="3">
+        <v>0</v>
+      </c>
+      <c r="L117" s="3" t="s">
         <v>499</v>
-      </c>
-      <c r="G117" s="3">
-        <v>550</v>
-      </c>
-      <c r="H117" s="3">
-        <v>275</v>
-      </c>
-      <c r="I117" s="3">
-        <v>40024</v>
-      </c>
-      <c r="J117" s="4">
-        <v>1020</v>
-      </c>
-      <c r="K117" s="3">
-        <v>0</v>
-      </c>
-      <c r="L117" s="3" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="118" spans="2:12">
       <c r="B118" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D118" s="3">
         <v>0.1</v>
       </c>
       <c r="E118" t="s">
+        <v>501</v>
+      </c>
+      <c r="F118" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="G118" s="3">
+        <v>450</v>
+      </c>
+      <c r="H118" s="3">
+        <v>225</v>
+      </c>
+      <c r="I118" s="3">
+        <v>40023</v>
+      </c>
+      <c r="K118" s="3">
+        <v>0</v>
+      </c>
+      <c r="L118" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="G118" s="3">
-        <v>300</v>
-      </c>
-      <c r="H118" s="3">
-        <v>150</v>
-      </c>
-      <c r="I118" s="3">
-        <v>40025</v>
-      </c>
-      <c r="K118" s="3">
-        <v>0</v>
-      </c>
-      <c r="L118" s="3" t="s">
+    </row>
+    <row r="119" spans="2:12">
+      <c r="B119" s="1" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="119" spans="2:12">
-      <c r="B119" s="3">
-        <v>426</v>
-      </c>
-      <c r="C119" t="s">
-        <v>390</v>
+      <c r="C119" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="D119" s="3">
         <v>0.1</v>
@@ -6394,151 +6418,218 @@
       <c r="E119" t="s">
         <v>505</v>
       </c>
-      <c r="F119" t="s">
+      <c r="F119" s="3" t="s">
         <v>506</v>
       </c>
       <c r="G119" s="3">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="H119" s="3">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="I119" s="3">
-        <v>40026</v>
+        <v>40024</v>
+      </c>
+      <c r="J119" s="4">
+        <v>1020</v>
       </c>
       <c r="K119" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="3" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="120" spans="2:12">
-      <c r="B120" s="3">
-        <v>427</v>
-      </c>
-      <c r="C120" t="s">
-        <v>390</v>
+      <c r="B120" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="D120" s="3">
         <v>0.1</v>
       </c>
       <c r="E120" t="s">
-        <v>508</v>
-      </c>
-      <c r="F120" t="s">
         <v>509</v>
       </c>
+      <c r="F120" s="3" t="s">
+        <v>510</v>
+      </c>
       <c r="G120" s="3">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="H120" s="3">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="I120" s="3">
-        <v>40027</v>
+        <v>40025</v>
       </c>
       <c r="K120" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="121" spans="2:12">
       <c r="B121" s="3">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C121" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D121" s="3">
         <v>0.1</v>
       </c>
       <c r="E121" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F121" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G121" s="3">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="H121" s="3">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="I121" s="3">
-        <v>40028</v>
+        <v>40026</v>
       </c>
       <c r="K121" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="122" spans="2:12">
       <c r="B122" s="3">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C122" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D122" s="3">
         <v>0.1</v>
       </c>
       <c r="E122" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F122" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G122" s="3">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="H122" s="3">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="I122" s="3">
-        <v>40029</v>
+        <v>40027</v>
       </c>
       <c r="K122" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="123" spans="2:12">
       <c r="B123" s="3">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C123" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D123" s="3">
         <v>0.1</v>
       </c>
       <c r="E123" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F123" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G123" s="3">
+        <v>260</v>
+      </c>
+      <c r="H123" s="3">
+        <v>130</v>
+      </c>
+      <c r="I123" s="3">
+        <v>40028</v>
+      </c>
+      <c r="K123" s="3">
+        <v>2</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="124" spans="2:12">
+      <c r="B124" s="3">
+        <v>429</v>
+      </c>
+      <c r="C124" t="s">
+        <v>397</v>
+      </c>
+      <c r="D124" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E124" t="s">
+        <v>521</v>
+      </c>
+      <c r="F124" t="s">
+        <v>522</v>
+      </c>
+      <c r="G124" s="3">
+        <v>270</v>
+      </c>
+      <c r="H124" s="3">
+        <v>135</v>
+      </c>
+      <c r="I124" s="3">
+        <v>40029</v>
+      </c>
+      <c r="K124" s="3">
+        <v>2</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="125" spans="2:12">
+      <c r="B125" s="3">
+        <v>430</v>
+      </c>
+      <c r="C125" t="s">
+        <v>397</v>
+      </c>
+      <c r="D125" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E125" t="s">
+        <v>524</v>
+      </c>
+      <c r="F125" t="s">
+        <v>525</v>
+      </c>
+      <c r="G125" s="3">
         <v>280</v>
       </c>
-      <c r="H123" s="3">
+      <c r="H125" s="3">
         <v>140</v>
       </c>
-      <c r="I123" s="3">
+      <c r="I125" s="3">
         <v>40030</v>
       </c>
-      <c r="K123" s="3">
-        <v>0</v>
-      </c>
-      <c r="L123" s="3" t="s">
-        <v>519</v>
+      <c r="K125" s="3">
+        <v>0</v>
+      </c>
+      <c r="L125" s="3" t="s">
+        <v>526</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -1778,12 +1778,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2110,7 +2116,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -2134,16 +2140,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -2152,107 +2158,113 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2607,16 +2619,16 @@
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8" style="2" customWidth="1"/>
-    <col min="4" max="4" width="4.78333333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.8" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.1083333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.975" style="3" customWidth="1"/>
-    <col min="8" max="8" width="4.78333333333333" style="3" customWidth="1"/>
-    <col min="9" max="9" width="7.38333333333333" style="3" customWidth="1"/>
-    <col min="10" max="10" width="5.53333333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="3" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.8" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" style="4" customWidth="1"/>
+    <col min="7" max="7" width="5.975" style="4" customWidth="1"/>
+    <col min="8" max="8" width="4.78333333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="4" customWidth="1"/>
+    <col min="10" max="10" width="5.53333333333333" style="4" customWidth="1"/>
     <col min="11" max="11" width="8.03333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.70833333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.70833333333333" style="4" customWidth="1"/>
     <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
@@ -2631,31 +2643,31 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2669,31 +2681,31 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2707,31 +2719,31 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2742,28 +2754,28 @@
       <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>0.8</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <v>30</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <v>15</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <v>10001</v>
       </c>
-      <c r="K5" s="3">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="K5" s="4">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2774,28 +2786,28 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>0.8</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>28</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <v>14</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>10002</v>
       </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="s">
+      <c r="K6" s="4">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2806,28 +2818,28 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>0.8</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <v>28</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <v>14</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="4">
         <v>10003</v>
       </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="K7" s="4">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2838,28 +2850,28 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>0.8</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="4">
         <v>28</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="4">
         <v>14</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="4">
         <v>10004</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
+      <c r="K8" s="4">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2870,28 +2882,28 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>0.8</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="4">
         <v>28</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <v>14</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="4">
         <v>10005</v>
       </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="s">
+      <c r="K9" s="4">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2902,28 +2914,28 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>0.8</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>28</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>14</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="4">
         <v>10006</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="s">
+      <c r="K10" s="4">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2934,28 +2946,28 @@
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>0.8</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>22</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <v>11</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <v>10007</v>
       </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="s">
+      <c r="K11" s="4">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2966,28 +2978,28 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>0.8</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>35</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>17</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>10008</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="s">
+      <c r="K12" s="4">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2998,28 +3010,28 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>0.8</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="4">
         <v>16</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="4">
         <v>8</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="4">
         <v>10009</v>
       </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="s">
+      <c r="K13" s="4">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3030,28 +3042,28 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>0.8</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="4">
         <v>10010</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K14" s="4">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3062,28 +3074,28 @@
       <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>0.8</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="4">
         <v>15</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="4">
         <v>7</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="4">
         <v>10011</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="s">
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3094,29 +3106,29 @@
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>0.8</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="4">
         <v>30</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <v>15</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="4">
         <v>10012</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="s">
+      <c r="J16" s="4"/>
+      <c r="K16" s="4">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3127,29 +3139,29 @@
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <v>0.8</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <v>35</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <v>17</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <v>10013</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="s">
+      <c r="J17" s="4"/>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3160,29 +3172,29 @@
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="4">
         <v>0.8</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <v>26</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <v>13</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <v>10014</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="s">
+      <c r="J18" s="4"/>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3193,29 +3205,29 @@
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="4">
         <v>0.8</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="4">
         <v>22</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <v>11</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="4">
         <v>10015</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="s">
+      <c r="J19" s="4"/>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3226,29 +3238,29 @@
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>0.8</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="4">
         <v>28</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <v>14</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <v>10016</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
+      <c r="J20" s="4"/>
+      <c r="K20" s="4">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3259,40 +3271,40 @@
       <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>0.8</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="4">
         <v>20</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="4">
         <v>10</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="4">
         <v>10017</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
+      <c r="J21" s="4"/>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>118</v>
       </c>
       <c r="C22" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="4">
         <v>0.8</v>
       </c>
       <c r="E22" t="s">
@@ -3301,30 +3313,30 @@
       <c r="F22" t="s">
         <v>98</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="4">
         <v>25</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="4">
         <v>12</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="4">
         <v>10018</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="4">
         <v>1</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="L22" s="4" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>119</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="4">
         <v>0.8</v>
       </c>
       <c r="E23" t="s">
@@ -3333,30 +3345,30 @@
       <c r="F23" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="4">
         <v>15</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="4">
         <v>7</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="4">
         <v>10019</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="4">
         <v>2</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="L23" s="4" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>120</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="4">
         <v>0.8</v>
       </c>
       <c r="E24" t="s">
@@ -3365,30 +3377,30 @@
       <c r="F24" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="4">
         <v>25</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="4">
         <v>12</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="4">
         <v>10020</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="4">
         <v>1</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" s="4" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>121</v>
       </c>
       <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="3">
+      <c r="D25" s="4">
         <v>0.8</v>
       </c>
       <c r="E25" t="s">
@@ -3397,24 +3409,24 @@
       <c r="F25" t="s">
         <v>107</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="4">
         <v>30</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="4">
         <v>15</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="4">
         <v>10021</v>
       </c>
-      <c r="K25" s="3">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3" t="s">
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="K26" s="3"/>
+      <c r="K26" s="4"/>
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12">
@@ -3424,13 +3436,13 @@
       <c r="C27" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="4">
         <v>0.4</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="4" t="s">
         <v>112</v>
       </c>
       <c r="G27" s="1">
@@ -3442,10 +3454,10 @@
       <c r="I27" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="s">
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3456,13 +3468,13 @@
       <c r="C28" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="3">
+      <c r="D28" s="4">
         <v>0.4</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>117</v>
       </c>
       <c r="G28" s="1">
@@ -3474,10 +3486,10 @@
       <c r="I28" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="K28" s="3">
-        <v>0</v>
-      </c>
-      <c r="L28" s="3" t="s">
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3489,13 +3501,13 @@
       <c r="C29" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="4">
         <v>0.4</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="4" t="s">
         <v>122</v>
       </c>
       <c r="G29" s="1">
@@ -3507,10 +3519,10 @@
       <c r="I29" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="s">
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3522,13 +3534,13 @@
       <c r="C30" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D30" s="4">
         <v>0.4</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="4" t="s">
         <v>127</v>
       </c>
       <c r="G30" s="1">
@@ -3540,10 +3552,10 @@
       <c r="I30" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="K30" s="3">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3" t="s">
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3555,13 +3567,13 @@
       <c r="C31" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D31" s="4">
         <v>0.4</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="4" t="s">
         <v>132</v>
       </c>
       <c r="G31" s="1">
@@ -3573,10 +3585,10 @@
       <c r="I31" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K31" s="3">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3" t="s">
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3588,13 +3600,13 @@
       <c r="C32" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="4">
         <v>0.4</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="4" t="s">
         <v>137</v>
       </c>
       <c r="G32" s="1">
@@ -3606,10 +3618,10 @@
       <c r="I32" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>139</v>
       </c>
     </row>
@@ -3621,13 +3633,13 @@
       <c r="C33" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="4">
         <v>0.4</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="4" t="s">
         <v>142</v>
       </c>
       <c r="G33" s="1">
@@ -3639,10 +3651,10 @@
       <c r="I33" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="s">
+      <c r="K33" s="4">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3654,13 +3666,13 @@
       <c r="C34" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D34" s="4">
         <v>0.4</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="4" t="s">
         <v>147</v>
       </c>
       <c r="G34" s="1">
@@ -3672,10 +3684,10 @@
       <c r="I34" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="K34" s="3">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3" t="s">
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3687,13 +3699,13 @@
       <c r="C35" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="4">
         <v>0.4</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="4" t="s">
         <v>152</v>
       </c>
       <c r="G35" s="1">
@@ -3705,10 +3717,10 @@
       <c r="I35" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3" t="s">
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3720,13 +3732,13 @@
       <c r="C36" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D36" s="3">
+      <c r="D36" s="4">
         <v>0.4</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="4" t="s">
         <v>157</v>
       </c>
       <c r="G36" s="1">
@@ -3738,10 +3750,10 @@
       <c r="I36" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="K36" s="3">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="s">
+      <c r="K36" s="4">
+        <v>0</v>
+      </c>
+      <c r="L36" s="4" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3753,13 +3765,13 @@
       <c r="C37" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="3">
+      <c r="D37" s="4">
         <v>0.4</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="4" t="s">
         <v>162</v>
       </c>
       <c r="G37" s="1">
@@ -3771,10 +3783,10 @@
       <c r="I37" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="K37" s="3">
-        <v>0</v>
-      </c>
-      <c r="L37" s="3" t="s">
+      <c r="K37" s="4">
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3786,13 +3798,13 @@
       <c r="C38" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D38" s="4">
         <v>0.4</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="4" t="s">
         <v>167</v>
       </c>
       <c r="G38" s="1">
@@ -3804,10 +3816,10 @@
       <c r="I38" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="K38" s="3">
-        <v>0</v>
-      </c>
-      <c r="L38" s="3" t="s">
+      <c r="K38" s="4">
+        <v>0</v>
+      </c>
+      <c r="L38" s="4" t="s">
         <v>169</v>
       </c>
     </row>
@@ -3819,13 +3831,13 @@
       <c r="C39" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="4">
         <v>0.4</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="4" t="s">
         <v>172</v>
       </c>
       <c r="G39" s="1">
@@ -3837,10 +3849,10 @@
       <c r="I39" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="K39" s="3">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="s">
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>174</v>
       </c>
     </row>
@@ -3852,13 +3864,13 @@
       <c r="C40" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D40" s="3">
+      <c r="D40" s="4">
         <v>0.4</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="4" t="s">
         <v>177</v>
       </c>
       <c r="G40" s="1">
@@ -3870,10 +3882,10 @@
       <c r="I40" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K40" s="3">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="s">
+      <c r="K40" s="4">
+        <v>0</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3885,13 +3897,13 @@
       <c r="C41" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="4">
         <v>0.4</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="4" t="s">
         <v>182</v>
       </c>
       <c r="G41" s="1">
@@ -3903,10 +3915,10 @@
       <c r="I41" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="s">
+      <c r="K41" s="4">
+        <v>0</v>
+      </c>
+      <c r="L41" s="4" t="s">
         <v>184</v>
       </c>
     </row>
@@ -3918,13 +3930,13 @@
       <c r="C42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="4">
         <v>0.4</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="4" t="s">
         <v>187</v>
       </c>
       <c r="G42" s="1">
@@ -3936,10 +3948,10 @@
       <c r="I42" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
+      <c r="K42" s="4">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>189</v>
       </c>
     </row>
@@ -3951,13 +3963,13 @@
       <c r="C43" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="4">
         <v>0.4</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="4" t="s">
         <v>192</v>
       </c>
       <c r="G43" s="1">
@@ -3969,10 +3981,10 @@
       <c r="I43" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3" t="s">
+      <c r="K43" s="4">
+        <v>0</v>
+      </c>
+      <c r="L43" s="4" t="s">
         <v>194</v>
       </c>
     </row>
@@ -3984,13 +3996,13 @@
       <c r="C44" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="4">
         <v>0.4</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="4" t="s">
         <v>197</v>
       </c>
       <c r="G44" s="1">
@@ -4002,10 +4014,10 @@
       <c r="I44" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
+      <c r="K44" s="4">
+        <v>0</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4017,29 +4029,29 @@
       <c r="C45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="4">
         <v>0.4</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="F45" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="4">
         <v>85</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="4">
         <v>42</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
+      <c r="J45" s="4"/>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4051,29 +4063,29 @@
       <c r="C46" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="4">
         <v>0.4</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="4">
         <v>75</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="4">
         <v>37</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="s">
+      <c r="J46" s="4"/>
+      <c r="K46" s="4">
+        <v>0</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>209</v>
       </c>
     </row>
@@ -4085,29 +4097,29 @@
       <c r="C47" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="4">
         <v>0.4</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="4">
         <v>75</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="4">
         <v>37</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3" t="s">
+      <c r="J47" s="4"/>
+      <c r="K47" s="4">
+        <v>0</v>
+      </c>
+      <c r="L47" s="4" t="s">
         <v>214</v>
       </c>
     </row>
@@ -4119,29 +4131,29 @@
       <c r="C48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="4">
         <v>0.4</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="4">
         <v>80</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="4">
         <v>40</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3" t="s">
+      <c r="J48" s="4"/>
+      <c r="K48" s="4">
+        <v>0</v>
+      </c>
+      <c r="L48" s="4" t="s">
         <v>219</v>
       </c>
     </row>
@@ -4153,29 +4165,29 @@
       <c r="C49" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="4">
         <v>0.4</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="4">
         <v>70</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="4">
         <v>35</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
+      <c r="J49" s="4"/>
+      <c r="K49" s="4">
+        <v>0</v>
+      </c>
+      <c r="L49" s="4" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4187,29 +4199,29 @@
       <c r="C50" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D50" s="4">
         <v>0.4</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="4">
         <v>75</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="4">
         <v>37</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3">
-        <v>0</v>
-      </c>
-      <c r="L50" s="3" t="s">
+      <c r="J50" s="4"/>
+      <c r="K50" s="4">
+        <v>0</v>
+      </c>
+      <c r="L50" s="4" t="s">
         <v>229</v>
       </c>
     </row>
@@ -4220,29 +4232,29 @@
       <c r="C51" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D51" s="4">
         <v>0.4</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="F51" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="4">
         <v>90</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="4">
         <v>45</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>234</v>
       </c>
       <c r="J51" s="1"/>
-      <c r="K51" s="3">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3" t="s">
+      <c r="K51" s="4">
+        <v>0</v>
+      </c>
+      <c r="L51" s="4" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4254,28 +4266,28 @@
       <c r="C52" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="4">
         <v>0.4</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="4">
         <v>120</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="4">
         <v>60</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
+      <c r="K52" s="4">
+        <v>0</v>
+      </c>
+      <c r="L52" s="4" t="s">
         <v>240</v>
       </c>
     </row>
@@ -4287,28 +4299,28 @@
       <c r="C53" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D53" s="4">
         <v>0.4</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="4">
         <v>110</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="4">
         <v>55</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="K53" s="3">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3" t="s">
+      <c r="K53" s="4">
+        <v>0</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4320,28 +4332,28 @@
       <c r="C54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="4">
         <v>0.4</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="4">
         <v>70</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="4">
         <v>35</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="K54" s="3">
-        <v>0</v>
-      </c>
-      <c r="L54" s="3" t="s">
+      <c r="K54" s="4">
+        <v>0</v>
+      </c>
+      <c r="L54" s="4" t="s">
         <v>250</v>
       </c>
     </row>
@@ -4353,39 +4365,39 @@
       <c r="C55" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D55" s="4">
         <v>0.4</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="4">
         <v>160</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55" s="4">
         <v>80</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="K55" s="3">
-        <v>0</v>
-      </c>
-      <c r="L55" s="3" t="s">
+      <c r="K55" s="4">
+        <v>0</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="56" spans="1:12">
-      <c r="B56" s="3">
+      <c r="B56" s="4">
         <v>230</v>
       </c>
       <c r="C56" t="s">
         <v>110</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D56" s="4">
         <v>0.4</v>
       </c>
       <c r="E56" t="s">
@@ -4394,30 +4406,30 @@
       <c r="F56" t="s">
         <v>257</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="4">
         <v>90</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="4">
         <v>45</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="4">
         <v>20030</v>
       </c>
-      <c r="K56" s="3">
+      <c r="K56" s="4">
         <v>1</v>
       </c>
-      <c r="L56" s="3" t="s">
+      <c r="L56" s="4" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:12">
-      <c r="B57" s="3">
+      <c r="B57" s="4">
         <v>231</v>
       </c>
       <c r="C57" t="s">
         <v>110</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="4">
         <v>0.4</v>
       </c>
       <c r="E57" t="s">
@@ -4426,30 +4438,30 @@
       <c r="F57" t="s">
         <v>260</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="4">
         <v>70</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="4">
         <v>35</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="4">
         <v>20031</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="4">
         <v>2</v>
       </c>
-      <c r="L57" s="3" t="s">
+      <c r="L57" s="4" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:12">
-      <c r="B58" s="3">
+      <c r="B58" s="4">
         <v>232</v>
       </c>
       <c r="C58" t="s">
         <v>110</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="4">
         <v>0.4</v>
       </c>
       <c r="E58" t="s">
@@ -4458,30 +4470,30 @@
       <c r="F58" t="s">
         <v>263</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="4">
         <v>145</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="4">
         <v>72</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="4">
         <v>20032</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="4">
         <v>1</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="L58" s="4" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:12">
-      <c r="B59" s="3">
+      <c r="B59" s="4">
         <v>233</v>
       </c>
       <c r="C59" t="s">
         <v>110</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="4">
         <v>0.4</v>
       </c>
       <c r="E59" t="s">
@@ -4490,30 +4502,30 @@
       <c r="F59" t="s">
         <v>266</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="4">
         <v>75</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="4">
         <v>37</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="4">
         <v>20033</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="s">
+      <c r="K59" s="4">
+        <v>0</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="60" spans="1:12">
-      <c r="B60" s="3">
+      <c r="B60" s="4">
         <v>234</v>
       </c>
       <c r="C60" t="s">
         <v>110</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="4">
         <v>0.4</v>
       </c>
       <c r="E60" t="s">
@@ -4522,30 +4534,30 @@
       <c r="F60" t="s">
         <v>269</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="4">
         <v>110</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60" s="4">
         <v>55</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="4">
         <v>20034</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="4">
         <v>1</v>
       </c>
-      <c r="L60" s="3" t="s">
+      <c r="L60" s="4" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:12">
-      <c r="B61" s="3">
+      <c r="B61" s="4">
         <v>235</v>
       </c>
       <c r="C61" t="s">
         <v>110</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61" s="4">
         <v>0.4</v>
       </c>
       <c r="E61" t="s">
@@ -4554,46 +4566,46 @@
       <c r="F61" t="s">
         <v>272</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="4">
         <v>140</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61" s="4">
         <v>70</v>
       </c>
-      <c r="I61" s="3">
+      <c r="I61" s="4">
         <v>20035</v>
       </c>
-      <c r="K61" s="3">
+      <c r="K61" s="4">
         <v>1</v>
       </c>
-      <c r="L61" s="3" t="s">
+      <c r="L61" s="4" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62"/>
-      <c r="B62" s="3"/>
+      <c r="B62" s="4"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="K62" s="3"/>
+      <c r="K62" s="4"/>
       <c r="L62" s="1"/>
     </row>
     <row r="63" spans="1:12">
       <c r="A63"/>
-      <c r="B63" s="3">
+      <c r="B63" s="4">
         <v>301</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D63" s="4">
         <v>0.2</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="4" t="s">
         <v>275</v>
       </c>
       <c r="G63" s="1">
@@ -4605,31 +4617,31 @@
       <c r="I63" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="J63" s="3">
+      <c r="J63" s="4">
         <v>1001</v>
       </c>
-      <c r="K63" s="3">
-        <v>0</v>
-      </c>
-      <c r="L63" s="3" t="s">
+      <c r="K63" s="4">
+        <v>0</v>
+      </c>
+      <c r="L63" s="4" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64"/>
-      <c r="B64" s="3">
+      <c r="B64" s="4">
         <v>302</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D64" s="4">
         <v>0.2</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="4" t="s">
         <v>279</v>
       </c>
       <c r="G64" s="1">
@@ -4641,28 +4653,28 @@
       <c r="I64" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K64" s="3">
-        <v>0</v>
-      </c>
-      <c r="L64" s="3" t="s">
+      <c r="K64" s="4">
+        <v>0</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65"/>
-      <c r="B65" s="3">
+      <c r="B65" s="4">
         <v>303</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D65" s="4">
         <v>0.2</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="4" t="s">
         <v>283</v>
       </c>
       <c r="G65" s="1">
@@ -4674,28 +4686,28 @@
       <c r="I65" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="K65" s="3">
-        <v>0</v>
-      </c>
-      <c r="L65" s="3" t="s">
+      <c r="K65" s="4">
+        <v>0</v>
+      </c>
+      <c r="L65" s="4" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:12">
       <c r="A66"/>
-      <c r="B66" s="3">
+      <c r="B66" s="4">
         <v>304</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="4">
         <v>0.2</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G66" s="1">
@@ -4707,31 +4719,31 @@
       <c r="I66" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="4">
         <v>1002</v>
       </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
-      <c r="L66" s="3" t="s">
+      <c r="K66" s="4">
+        <v>0</v>
+      </c>
+      <c r="L66" s="4" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:12">
       <c r="A67"/>
-      <c r="B67" s="3">
+      <c r="B67" s="4">
         <v>305</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D67" s="4">
         <v>0.2</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="4" t="s">
         <v>291</v>
       </c>
       <c r="G67" s="1">
@@ -4743,30 +4755,30 @@
       <c r="I67" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="J67" s="3">
+      <c r="J67" s="4">
         <v>1003</v>
       </c>
-      <c r="K67" s="3">
-        <v>0</v>
-      </c>
-      <c r="L67" s="3" t="s">
+      <c r="K67" s="4">
+        <v>0</v>
+      </c>
+      <c r="L67" s="4" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:12">
-      <c r="B68" s="3">
+      <c r="B68" s="4">
         <v>306</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D68" s="4">
         <v>0.2</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="4" t="s">
         <v>295</v>
       </c>
       <c r="G68" s="1">
@@ -4778,30 +4790,30 @@
       <c r="I68" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="J68" s="3">
+      <c r="J68" s="4">
         <v>1004</v>
       </c>
-      <c r="K68" s="3">
-        <v>0</v>
-      </c>
-      <c r="L68" s="3" t="s">
+      <c r="K68" s="4">
+        <v>0</v>
+      </c>
+      <c r="L68" s="4" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:12">
-      <c r="B69" s="3">
+      <c r="B69" s="4">
         <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D69" s="4">
         <v>0.2</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="4" t="s">
         <v>299</v>
       </c>
       <c r="G69" s="1">
@@ -4813,27 +4825,27 @@
       <c r="I69" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="K69" s="3">
-        <v>0</v>
-      </c>
-      <c r="L69" s="3" t="s">
+      <c r="K69" s="4">
+        <v>0</v>
+      </c>
+      <c r="L69" s="4" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:12">
-      <c r="B70" s="3">
+      <c r="B70" s="4">
         <v>308</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D70" s="4">
         <v>0.2</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="4" t="s">
         <v>303</v>
       </c>
       <c r="G70" s="1">
@@ -4845,30 +4857,30 @@
       <c r="I70" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="J70" s="4">
+      <c r="J70" s="5">
         <v>1009</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3" t="s">
+      <c r="K70" s="4">
+        <v>0</v>
+      </c>
+      <c r="L70" s="4" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:12">
-      <c r="B71" s="3">
+      <c r="B71" s="4">
         <v>309</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D71" s="4">
         <v>0.2</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="F71" s="4" t="s">
         <v>307</v>
       </c>
       <c r="G71" s="1">
@@ -4880,27 +4892,27 @@
       <c r="I71" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="K71" s="3">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3" t="s">
+      <c r="K71" s="4">
+        <v>0</v>
+      </c>
+      <c r="L71" s="4" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:12">
-      <c r="B72" s="3">
+      <c r="B72" s="4">
         <v>310</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="4">
         <v>0.2</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="4" t="s">
         <v>311</v>
       </c>
       <c r="G72" s="1">
@@ -4912,30 +4924,30 @@
       <c r="I72" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="J72" s="4">
+      <c r="J72" s="5">
         <v>1013</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3" t="s">
+      <c r="K72" s="4">
+        <v>0</v>
+      </c>
+      <c r="L72" s="4" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:12">
-      <c r="B73" s="3">
+      <c r="B73" s="4">
         <v>311</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73" s="4">
         <v>0.2</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="F73" s="4" t="s">
         <v>315</v>
       </c>
       <c r="G73" s="1">
@@ -4947,27 +4959,27 @@
       <c r="I73" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K73" s="3">
-        <v>0</v>
-      </c>
-      <c r="L73" s="3" t="s">
+      <c r="K73" s="4">
+        <v>0</v>
+      </c>
+      <c r="L73" s="4" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:12">
-      <c r="B74" s="3">
+      <c r="B74" s="4">
         <v>312</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74" s="4">
         <v>0.2</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="4" t="s">
         <v>319</v>
       </c>
       <c r="G74" s="1">
@@ -4979,27 +4991,27 @@
       <c r="I74" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="K74" s="3">
-        <v>0</v>
-      </c>
-      <c r="L74" s="3" t="s">
+      <c r="K74" s="4">
+        <v>0</v>
+      </c>
+      <c r="L74" s="4" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:12">
-      <c r="B75" s="3">
+      <c r="B75" s="4">
         <v>313</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75" s="4">
         <v>0.2</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="4" t="s">
         <v>323</v>
       </c>
       <c r="G75" s="1">
@@ -5011,417 +5023,417 @@
       <c r="I75" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J75" s="4">
+      <c r="J75" s="5">
         <v>1010</v>
       </c>
-      <c r="K75" s="3">
-        <v>0</v>
-      </c>
-      <c r="L75" s="3" t="s">
+      <c r="K75" s="4">
+        <v>0</v>
+      </c>
+      <c r="L75" s="4" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:12">
-      <c r="B76" s="3">
+      <c r="B76" s="4">
         <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="4">
         <v>0.2</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G76" s="4">
         <v>180</v>
       </c>
-      <c r="H76" s="3">
+      <c r="H76" s="4">
         <v>90</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3" t="s">
+      <c r="J76" s="4"/>
+      <c r="K76" s="4">
+        <v>0</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:12">
-      <c r="B77" s="3">
+      <c r="B77" s="4">
         <v>315</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77" s="4">
         <v>0.2</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G77" s="4">
         <v>380</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77" s="4">
         <v>190</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3">
-        <v>0</v>
-      </c>
-      <c r="L77" s="3" t="s">
+      <c r="J77" s="4"/>
+      <c r="K77" s="4">
+        <v>0</v>
+      </c>
+      <c r="L77" s="4" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="78" spans="1:12">
-      <c r="B78" s="3">
+      <c r="B78" s="4">
         <v>316</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78" s="4">
         <v>0.2</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G78" s="4">
         <v>170</v>
       </c>
-      <c r="H78" s="3">
+      <c r="H78" s="4">
         <v>85</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="K78" s="3">
-        <v>0</v>
-      </c>
-      <c r="L78" s="3" t="s">
+      <c r="K78" s="4">
+        <v>0</v>
+      </c>
+      <c r="L78" s="4" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:12">
-      <c r="B79" s="3">
+      <c r="B79" s="4">
         <v>317</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79" s="4">
         <v>0.2</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G79" s="4">
         <v>200</v>
       </c>
-      <c r="H79" s="3">
+      <c r="H79" s="4">
         <v>100</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>340</v>
       </c>
       <c r="J79" s="1"/>
-      <c r="K79" s="3">
-        <v>0</v>
-      </c>
-      <c r="L79" s="3" t="s">
+      <c r="K79" s="4">
+        <v>0</v>
+      </c>
+      <c r="L79" s="4" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:12">
-      <c r="B80" s="3">
+      <c r="B80" s="4">
         <v>318</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80" s="4">
         <v>0.2</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G80" s="4">
         <v>170</v>
       </c>
-      <c r="H80" s="3">
+      <c r="H80" s="4">
         <v>85</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="K80" s="3">
-        <v>0</v>
-      </c>
-      <c r="L80" s="3" t="s">
+      <c r="K80" s="4">
+        <v>0</v>
+      </c>
+      <c r="L80" s="4" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="81" spans="2:12">
-      <c r="B81" s="3">
+      <c r="B81" s="4">
         <v>319</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="4">
         <v>0.2</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81" s="4">
         <v>160</v>
       </c>
-      <c r="H81" s="3">
+      <c r="H81" s="4">
         <v>80</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="J81" s="4">
+      <c r="J81" s="5">
         <v>1011</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3" t="s">
+      <c r="K81" s="4">
+        <v>0</v>
+      </c>
+      <c r="L81" s="4" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="82" spans="2:12">
-      <c r="B82" s="3">
+      <c r="B82" s="4">
         <v>320</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="4">
         <v>0.2</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="G82" s="3">
+      <c r="G82" s="4">
         <v>160</v>
       </c>
-      <c r="H82" s="3">
+      <c r="H82" s="4">
         <v>80</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="K82" s="3">
-        <v>0</v>
-      </c>
-      <c r="L82" s="3" t="s">
+      <c r="K82" s="4">
+        <v>0</v>
+      </c>
+      <c r="L82" s="4" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="83" spans="2:12">
-      <c r="B83" s="3">
+      <c r="B83" s="4">
         <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="4">
         <v>0.2</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="4">
         <v>160</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="4">
         <v>80</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
+      <c r="K83" s="4">
+        <v>0</v>
+      </c>
+      <c r="L83" s="4" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="84" spans="2:12">
-      <c r="B84" s="3">
+      <c r="B84" s="4">
         <v>322</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D84" s="3">
+      <c r="D84" s="4">
         <v>0.2</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="G84" s="3">
+      <c r="G84" s="4">
         <v>160</v>
       </c>
-      <c r="H84" s="3">
+      <c r="H84" s="4">
         <v>80</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="K84" s="3">
-        <v>0</v>
-      </c>
-      <c r="L84" s="3" t="s">
+      <c r="K84" s="4">
+        <v>0</v>
+      </c>
+      <c r="L84" s="4" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="85" spans="2:12">
-      <c r="B85" s="3">
+      <c r="B85" s="4">
         <v>323</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D85" s="3">
+      <c r="D85" s="4">
         <v>0.2</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="G85" s="3">
+      <c r="G85" s="4">
         <v>190</v>
       </c>
-      <c r="H85" s="3">
+      <c r="H85" s="4">
         <v>95</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="K85" s="3">
-        <v>0</v>
-      </c>
-      <c r="L85" s="3" t="s">
+      <c r="K85" s="4">
+        <v>0</v>
+      </c>
+      <c r="L85" s="4" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="86" spans="2:12">
-      <c r="B86" s="3">
+      <c r="B86" s="4">
         <v>324</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D86" s="3">
+      <c r="D86" s="4">
         <v>0.2</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="G86" s="3">
+      <c r="G86" s="4">
         <v>175</v>
       </c>
-      <c r="H86" s="3">
+      <c r="H86" s="4">
         <v>87</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J86" s="4">
+      <c r="J86" s="5">
         <v>1012</v>
       </c>
-      <c r="K86" s="3">
-        <v>0</v>
-      </c>
-      <c r="L86" s="3" t="s">
+      <c r="K86" s="4">
+        <v>0</v>
+      </c>
+      <c r="L86" s="4" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="87" spans="2:12">
-      <c r="B87" s="3">
+      <c r="B87" s="4">
         <v>325</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D87" s="3">
+      <c r="D87" s="4">
         <v>0.2</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="G87" s="3">
+      <c r="G87" s="4">
         <v>270</v>
       </c>
-      <c r="H87" s="3">
+      <c r="H87" s="4">
         <v>135</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K87" s="3">
-        <v>0</v>
-      </c>
-      <c r="L87" s="3" t="s">
+      <c r="K87" s="4">
+        <v>0</v>
+      </c>
+      <c r="L87" s="4" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="88" spans="2:12">
-      <c r="B88" s="3">
+      <c r="B88" s="4">
         <v>326</v>
       </c>
       <c r="C88" t="s">
         <v>231</v>
       </c>
-      <c r="D88" s="3">
+      <c r="D88" s="4">
         <v>0.2</v>
       </c>
       <c r="E88" t="s">
@@ -5430,33 +5442,33 @@
       <c r="F88" t="s">
         <v>375</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G88" s="4">
         <v>190</v>
       </c>
-      <c r="H88" s="3">
+      <c r="H88" s="4">
         <v>95</v>
       </c>
-      <c r="I88" s="3">
+      <c r="I88" s="4">
         <v>30026</v>
       </c>
-      <c r="J88" s="4">
+      <c r="J88" s="5">
         <v>1013</v>
       </c>
-      <c r="K88" s="3">
+      <c r="K88" s="4">
         <v>2</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="L88" s="4" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="89" spans="2:12">
-      <c r="B89" s="3">
+      <c r="B89" s="4">
         <v>327</v>
       </c>
       <c r="C89" t="s">
         <v>231</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="4">
         <v>0.2</v>
       </c>
       <c r="E89" t="s">
@@ -5465,30 +5477,30 @@
       <c r="F89" t="s">
         <v>378</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="4">
         <v>160</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89" s="4">
         <v>80</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="4">
         <v>30027</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="4">
         <v>2</v>
       </c>
-      <c r="L89" s="3" t="s">
+      <c r="L89" s="4" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="90" spans="2:12">
-      <c r="B90" s="3">
+      <c r="B90" s="4">
         <v>328</v>
       </c>
       <c r="C90" t="s">
         <v>231</v>
       </c>
-      <c r="D90" s="3">
+      <c r="D90" s="4">
         <v>0.2</v>
       </c>
       <c r="E90" t="s">
@@ -5497,30 +5509,30 @@
       <c r="F90" t="s">
         <v>381</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G90" s="4">
         <v>200</v>
       </c>
-      <c r="H90" s="3">
+      <c r="H90" s="4">
         <v>100</v>
       </c>
-      <c r="I90" s="3">
+      <c r="I90" s="4">
         <v>30028</v>
       </c>
-      <c r="K90" s="3">
+      <c r="K90" s="4">
         <v>1</v>
       </c>
-      <c r="L90" s="3" t="s">
+      <c r="L90" s="4" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="91" spans="2:12">
-      <c r="B91" s="3">
+      <c r="B91" s="4">
         <v>329</v>
       </c>
       <c r="C91" t="s">
         <v>231</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="4">
         <v>0.2</v>
       </c>
       <c r="E91" t="s">
@@ -5529,30 +5541,30 @@
       <c r="F91" t="s">
         <v>384</v>
       </c>
-      <c r="G91" s="3">
+      <c r="G91" s="4">
         <v>170</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91" s="4">
         <v>85</v>
       </c>
-      <c r="I91" s="3">
+      <c r="I91" s="4">
         <v>30029</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="4">
         <v>1</v>
       </c>
-      <c r="L91" s="3" t="s">
+      <c r="L91" s="4" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="92" ht="14.25" spans="2:12">
-      <c r="B92" s="3">
+    <row r="92" spans="2:12">
+      <c r="B92" s="4">
         <v>330</v>
       </c>
       <c r="C92" t="s">
         <v>231</v>
       </c>
-      <c r="D92" s="3">
+      <c r="D92" s="4">
         <v>0.2</v>
       </c>
       <c r="E92" t="s">
@@ -5561,36 +5573,36 @@
       <c r="F92" t="s">
         <v>387</v>
       </c>
-      <c r="G92" s="3">
+      <c r="G92" s="4">
         <v>180</v>
       </c>
-      <c r="H92" s="3">
+      <c r="H92" s="4">
         <v>90</v>
       </c>
-      <c r="I92" s="3">
+      <c r="I92" s="4">
         <v>30030</v>
       </c>
-      <c r="K92" s="3">
-        <v>0</v>
-      </c>
-      <c r="L92" s="3" t="s">
+      <c r="K92" s="4">
+        <v>0</v>
+      </c>
+      <c r="L92" s="4" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" spans="2:12">
-      <c r="B93" s="3">
+    <row r="93" s="2" customFormat="1" spans="2:12">
+      <c r="B93" s="6">
         <v>331</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="D93" s="3">
+      <c r="D93" s="6">
         <v>0.2</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E93" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" s="2" t="s">
         <v>390</v>
       </c>
       <c r="G93" s="6">
@@ -5599,30 +5611,30 @@
       <c r="H93" s="6">
         <v>130</v>
       </c>
-      <c r="I93" s="3">
+      <c r="I93" s="6">
         <v>30031</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K93" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="L93" s="5" t="s">
+      <c r="L93" s="8" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" spans="2:12">
-      <c r="B94" s="3">
+    <row r="94" s="2" customFormat="1" spans="2:12">
+      <c r="B94" s="6">
         <v>332</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="6">
         <v>0.2</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E94" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F94" s="2" t="s">
         <v>394</v>
       </c>
       <c r="G94" s="6">
@@ -5631,13 +5643,13 @@
       <c r="H94" s="6">
         <v>130</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="6">
         <v>30032</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="K94" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="L94" s="5" t="s">
+      <c r="L94" s="8" t="s">
         <v>395</v>
       </c>
     </row>
@@ -5649,31 +5661,31 @@
       <c r="C96" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="4">
         <v>0.1</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="4">
         <v>235</v>
       </c>
-      <c r="F96" s="3" t="s">
+      <c r="F96" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="G96" s="3">
+      <c r="G96" s="4">
         <v>650</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="4">
         <v>325</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="4">
         <v>1005</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="s">
+      <c r="K96" s="4">
+        <v>0</v>
+      </c>
+      <c r="L96" s="4" t="s">
         <v>400</v>
       </c>
     </row>
@@ -5684,31 +5696,31 @@
       <c r="C97" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D97" s="3">
+      <c r="D97" s="4">
         <v>0.1</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G97" s="3">
+      <c r="G97" s="4">
         <v>680</v>
       </c>
-      <c r="H97" s="3">
+      <c r="H97" s="4">
         <v>340</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J97" s="3">
+      <c r="J97" s="4">
         <v>1006</v>
       </c>
-      <c r="K97" s="3">
-        <v>0</v>
-      </c>
-      <c r="L97" s="3" t="s">
+      <c r="K97" s="4">
+        <v>0</v>
+      </c>
+      <c r="L97" s="4" t="s">
         <v>405</v>
       </c>
     </row>
@@ -5719,28 +5731,28 @@
       <c r="C98" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="4">
         <v>0.1</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="G98" s="3">
+      <c r="G98" s="4">
         <v>600</v>
       </c>
-      <c r="H98" s="3">
+      <c r="H98" s="4">
         <v>300</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="K98" s="3">
-        <v>0</v>
-      </c>
-      <c r="L98" s="3" t="s">
+      <c r="K98" s="4">
+        <v>0</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>410</v>
       </c>
     </row>
@@ -5751,28 +5763,28 @@
       <c r="C99" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D99" s="3">
+      <c r="D99" s="4">
         <v>0.1</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="G99" s="3">
+      <c r="G99" s="4">
         <v>480</v>
       </c>
-      <c r="H99" s="3">
+      <c r="H99" s="4">
         <v>240</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="K99" s="3">
-        <v>0</v>
-      </c>
-      <c r="L99" s="3" t="s">
+      <c r="K99" s="4">
+        <v>0</v>
+      </c>
+      <c r="L99" s="4" t="s">
         <v>415</v>
       </c>
     </row>
@@ -5783,31 +5795,31 @@
       <c r="C100" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="4">
         <v>0.1</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="4">
         <v>460</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100" s="4">
         <v>230</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="J100" s="4">
+      <c r="J100" s="5">
         <v>1014</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
+      <c r="K100" s="4">
+        <v>0</v>
+      </c>
+      <c r="L100" s="4" t="s">
         <v>420</v>
       </c>
     </row>
@@ -5818,28 +5830,28 @@
       <c r="C101" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="4">
         <v>0.1</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="4">
         <v>320</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="4">
         <v>160</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
+      <c r="K101" s="4">
+        <v>0</v>
+      </c>
+      <c r="L101" s="4" t="s">
         <v>425</v>
       </c>
     </row>
@@ -5850,28 +5862,28 @@
       <c r="C102" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D102" s="3">
+      <c r="D102" s="4">
         <v>0.1</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="4">
         <v>380</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102" s="4">
         <v>190</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
+      <c r="K102" s="4">
+        <v>0</v>
+      </c>
+      <c r="L102" s="4" t="s">
         <v>430</v>
       </c>
     </row>
@@ -5882,31 +5894,31 @@
       <c r="C103" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D103" s="3">
+      <c r="D103" s="4">
         <v>0.1</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="G103" s="3">
+      <c r="G103" s="4">
         <v>600</v>
       </c>
-      <c r="H103" s="3">
+      <c r="H103" s="4">
         <v>300</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="J103" s="4">
+      <c r="J103" s="5">
         <v>1015</v>
       </c>
-      <c r="K103" s="3">
-        <v>0</v>
-      </c>
-      <c r="L103" s="3" t="s">
+      <c r="K103" s="4">
+        <v>0</v>
+      </c>
+      <c r="L103" s="4" t="s">
         <v>435</v>
       </c>
     </row>
@@ -5917,28 +5929,28 @@
       <c r="C104" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D104" s="3">
+      <c r="D104" s="4">
         <v>0.1</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E104" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="F104" s="3" t="s">
+      <c r="F104" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="G104" s="3">
+      <c r="G104" s="4">
         <v>300</v>
       </c>
-      <c r="H104" s="3">
+      <c r="H104" s="4">
         <v>150</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="K104" s="3">
-        <v>0</v>
-      </c>
-      <c r="L104" s="3" t="s">
+      <c r="K104" s="4">
+        <v>0</v>
+      </c>
+      <c r="L104" s="4" t="s">
         <v>440</v>
       </c>
     </row>
@@ -5949,28 +5961,28 @@
       <c r="C105" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D105" s="3">
+      <c r="D105" s="4">
         <v>0.1</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="G105" s="3">
+      <c r="G105" s="4">
         <v>300</v>
       </c>
-      <c r="H105" s="3">
+      <c r="H105" s="4">
         <v>150</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="K105" s="3">
-        <v>0</v>
-      </c>
-      <c r="L105" s="3" t="s">
+      <c r="K105" s="4">
+        <v>0</v>
+      </c>
+      <c r="L105" s="4" t="s">
         <v>445</v>
       </c>
     </row>
@@ -5981,28 +5993,28 @@
       <c r="C106" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D106" s="3">
+      <c r="D106" s="4">
         <v>0.1</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E106" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="G106" s="3">
+      <c r="G106" s="4">
         <v>400</v>
       </c>
-      <c r="H106" s="3">
+      <c r="H106" s="4">
         <v>200</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="K106" s="3">
-        <v>0</v>
-      </c>
-      <c r="L106" s="3" t="s">
+      <c r="K106" s="4">
+        <v>0</v>
+      </c>
+      <c r="L106" s="4" t="s">
         <v>450</v>
       </c>
     </row>
@@ -6013,31 +6025,31 @@
       <c r="C107" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D107" s="3">
+      <c r="D107" s="4">
         <v>0.1</v>
       </c>
-      <c r="E107" s="3" t="s">
+      <c r="E107" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="F107" s="3" t="s">
+      <c r="F107" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="G107" s="3">
+      <c r="G107" s="4">
         <v>460</v>
       </c>
-      <c r="H107" s="3">
+      <c r="H107" s="4">
         <v>230</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="J107" s="4">
+      <c r="J107" s="5">
         <v>1016</v>
       </c>
-      <c r="K107" s="3">
-        <v>0</v>
-      </c>
-      <c r="L107" s="3" t="s">
+      <c r="K107" s="4">
+        <v>0</v>
+      </c>
+      <c r="L107" s="4" t="s">
         <v>455</v>
       </c>
     </row>
@@ -6048,31 +6060,31 @@
       <c r="C108" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D108" s="3">
+      <c r="D108" s="4">
         <v>0.1</v>
       </c>
-      <c r="E108" s="3" t="s">
+      <c r="E108" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="G108" s="3">
+      <c r="G108" s="4">
         <v>340</v>
       </c>
-      <c r="H108" s="3">
+      <c r="H108" s="4">
         <v>170</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="J108" s="3">
+      <c r="J108" s="4">
         <v>1007</v>
       </c>
-      <c r="K108" s="3">
-        <v>0</v>
-      </c>
-      <c r="L108" s="3" t="s">
+      <c r="K108" s="4">
+        <v>0</v>
+      </c>
+      <c r="L108" s="4" t="s">
         <v>460</v>
       </c>
     </row>
@@ -6083,31 +6095,31 @@
       <c r="C109" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D109" s="3">
+      <c r="D109" s="4">
         <v>0.1</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="G109" s="3">
+      <c r="G109" s="4">
         <v>280</v>
       </c>
-      <c r="H109" s="3">
+      <c r="H109" s="4">
         <v>140</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="J109" s="3">
+      <c r="J109" s="4">
         <v>1008</v>
       </c>
-      <c r="K109" s="3">
-        <v>0</v>
-      </c>
-      <c r="L109" s="3" t="s">
+      <c r="K109" s="4">
+        <v>0</v>
+      </c>
+      <c r="L109" s="4" t="s">
         <v>465</v>
       </c>
     </row>
@@ -6118,28 +6130,28 @@
       <c r="C110" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D110" s="3">
+      <c r="D110" s="4">
         <v>0.1</v>
       </c>
       <c r="E110" t="s">
         <v>467</v>
       </c>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="G110" s="3">
+      <c r="G110" s="4">
         <v>600</v>
       </c>
-      <c r="H110" s="3">
+      <c r="H110" s="4">
         <v>300</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="I110" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="K110" s="3">
-        <v>0</v>
-      </c>
-      <c r="L110" s="3" t="s">
+      <c r="K110" s="4">
+        <v>0</v>
+      </c>
+      <c r="L110" s="4" t="s">
         <v>470</v>
       </c>
     </row>
@@ -6150,31 +6162,31 @@
       <c r="C111" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D111" s="3">
+      <c r="D111" s="4">
         <v>0.1</v>
       </c>
       <c r="E111" t="s">
         <v>472</v>
       </c>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="G111" s="3">
+      <c r="G111" s="4">
         <v>280</v>
       </c>
-      <c r="H111" s="3">
+      <c r="H111" s="4">
         <v>140</v>
       </c>
-      <c r="I111" s="3">
+      <c r="I111" s="4">
         <v>40016</v>
       </c>
-      <c r="J111" s="4">
+      <c r="J111" s="5">
         <v>1017</v>
       </c>
-      <c r="K111" s="3">
-        <v>0</v>
-      </c>
-      <c r="L111" s="3" t="s">
+      <c r="K111" s="4">
+        <v>0</v>
+      </c>
+      <c r="L111" s="4" t="s">
         <v>474</v>
       </c>
     </row>
@@ -6185,28 +6197,28 @@
       <c r="C112" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D112" s="3">
+      <c r="D112" s="4">
         <v>0.1</v>
       </c>
       <c r="E112" t="s">
         <v>476</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="G112" s="3">
+      <c r="G112" s="4">
         <v>300</v>
       </c>
-      <c r="H112" s="3">
+      <c r="H112" s="4">
         <v>150</v>
       </c>
-      <c r="I112" s="3">
+      <c r="I112" s="4">
         <v>40017</v>
       </c>
-      <c r="K112" s="3">
-        <v>0</v>
-      </c>
-      <c r="L112" s="3" t="s">
+      <c r="K112" s="4">
+        <v>0</v>
+      </c>
+      <c r="L112" s="4" t="s">
         <v>478</v>
       </c>
     </row>
@@ -6217,28 +6229,28 @@
       <c r="C113" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D113" s="3">
+      <c r="D113" s="4">
         <v>0.1</v>
       </c>
       <c r="E113" t="s">
         <v>480</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="G113" s="3">
+      <c r="G113" s="4">
         <v>520</v>
       </c>
-      <c r="H113" s="3">
+      <c r="H113" s="4">
         <v>260</v>
       </c>
-      <c r="I113" s="3">
+      <c r="I113" s="4">
         <v>40018</v>
       </c>
-      <c r="K113" s="3">
-        <v>0</v>
-      </c>
-      <c r="L113" s="3" t="s">
+      <c r="K113" s="4">
+        <v>0</v>
+      </c>
+      <c r="L113" s="4" t="s">
         <v>482</v>
       </c>
     </row>
@@ -6249,28 +6261,28 @@
       <c r="C114" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D114" s="3">
+      <c r="D114" s="4">
         <v>0.1</v>
       </c>
       <c r="E114" t="s">
         <v>484</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="G114" s="3">
+      <c r="G114" s="4">
         <v>300</v>
       </c>
-      <c r="H114" s="3">
+      <c r="H114" s="4">
         <v>150</v>
       </c>
-      <c r="I114" s="3">
+      <c r="I114" s="4">
         <v>40019</v>
       </c>
-      <c r="K114" s="3">
-        <v>0</v>
-      </c>
-      <c r="L114" s="3" t="s">
+      <c r="K114" s="4">
+        <v>0</v>
+      </c>
+      <c r="L114" s="4" t="s">
         <v>486</v>
       </c>
     </row>
@@ -6281,31 +6293,31 @@
       <c r="C115" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D115" s="3">
+      <c r="D115" s="4">
         <v>0.1</v>
       </c>
       <c r="E115" t="s">
         <v>488</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="G115" s="3">
+      <c r="G115" s="4">
         <v>560</v>
       </c>
-      <c r="H115" s="3">
+      <c r="H115" s="4">
         <v>280</v>
       </c>
-      <c r="I115" s="3">
+      <c r="I115" s="4">
         <v>40020</v>
       </c>
-      <c r="J115" s="4">
+      <c r="J115" s="5">
         <v>1018</v>
       </c>
-      <c r="K115" s="3">
-        <v>0</v>
-      </c>
-      <c r="L115" s="3" t="s">
+      <c r="K115" s="4">
+        <v>0</v>
+      </c>
+      <c r="L115" s="4" t="s">
         <v>490</v>
       </c>
     </row>
@@ -6316,28 +6328,28 @@
       <c r="C116" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D116" s="3">
+      <c r="D116" s="4">
         <v>0.1</v>
       </c>
       <c r="E116" t="s">
         <v>492</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="G116" s="3">
+      <c r="G116" s="4">
         <v>620</v>
       </c>
-      <c r="H116" s="3">
+      <c r="H116" s="4">
         <v>310</v>
       </c>
-      <c r="I116" s="3">
+      <c r="I116" s="4">
         <v>40021</v>
       </c>
-      <c r="K116" s="3">
-        <v>0</v>
-      </c>
-      <c r="L116" s="3" t="s">
+      <c r="K116" s="4">
+        <v>0</v>
+      </c>
+      <c r="L116" s="4" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6348,28 +6360,28 @@
       <c r="C117" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D117" s="3">
+      <c r="D117" s="4">
         <v>0.1</v>
       </c>
       <c r="E117" t="s">
         <v>496</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="G117" s="3">
+      <c r="G117" s="4">
         <v>320</v>
       </c>
-      <c r="H117" s="3">
+      <c r="H117" s="4">
         <v>160</v>
       </c>
-      <c r="I117" s="3" t="s">
+      <c r="I117" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="K117" s="3">
-        <v>0</v>
-      </c>
-      <c r="L117" s="3" t="s">
+      <c r="K117" s="4">
+        <v>0</v>
+      </c>
+      <c r="L117" s="4" t="s">
         <v>499</v>
       </c>
     </row>
@@ -6380,28 +6392,28 @@
       <c r="C118" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D118" s="3">
+      <c r="D118" s="4">
         <v>0.1</v>
       </c>
       <c r="E118" t="s">
         <v>501</v>
       </c>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="G118" s="3">
+      <c r="G118" s="4">
         <v>450</v>
       </c>
-      <c r="H118" s="3">
+      <c r="H118" s="4">
         <v>225</v>
       </c>
-      <c r="I118" s="3">
+      <c r="I118" s="4">
         <v>40023</v>
       </c>
-      <c r="K118" s="3">
-        <v>0</v>
-      </c>
-      <c r="L118" s="3" t="s">
+      <c r="K118" s="4">
+        <v>0</v>
+      </c>
+      <c r="L118" s="4" t="s">
         <v>503</v>
       </c>
     </row>
@@ -6412,31 +6424,31 @@
       <c r="C119" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D119" s="3">
+      <c r="D119" s="4">
         <v>0.1</v>
       </c>
       <c r="E119" t="s">
         <v>505</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="G119" s="3">
+      <c r="G119" s="4">
         <v>550</v>
       </c>
-      <c r="H119" s="3">
+      <c r="H119" s="4">
         <v>275</v>
       </c>
-      <c r="I119" s="3">
+      <c r="I119" s="4">
         <v>40024</v>
       </c>
-      <c r="J119" s="4">
+      <c r="J119" s="5">
         <v>1020</v>
       </c>
-      <c r="K119" s="3">
-        <v>0</v>
-      </c>
-      <c r="L119" s="3" t="s">
+      <c r="K119" s="4">
+        <v>0</v>
+      </c>
+      <c r="L119" s="4" t="s">
         <v>507</v>
       </c>
     </row>
@@ -6447,39 +6459,39 @@
       <c r="C120" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120" s="4">
         <v>0.1</v>
       </c>
       <c r="E120" t="s">
         <v>509</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G120" s="4">
         <v>300</v>
       </c>
-      <c r="H120" s="3">
+      <c r="H120" s="4">
         <v>150</v>
       </c>
-      <c r="I120" s="3">
+      <c r="I120" s="4">
         <v>40025</v>
       </c>
-      <c r="K120" s="3">
-        <v>0</v>
-      </c>
-      <c r="L120" s="3" t="s">
+      <c r="K120" s="4">
+        <v>0</v>
+      </c>
+      <c r="L120" s="4" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="121" spans="2:12">
-      <c r="B121" s="3">
+      <c r="B121" s="4">
         <v>426</v>
       </c>
       <c r="C121" t="s">
         <v>397</v>
       </c>
-      <c r="D121" s="3">
+      <c r="D121" s="4">
         <v>0.1</v>
       </c>
       <c r="E121" t="s">
@@ -6488,30 +6500,30 @@
       <c r="F121" t="s">
         <v>513</v>
       </c>
-      <c r="G121" s="3">
+      <c r="G121" s="4">
         <v>400</v>
       </c>
-      <c r="H121" s="3">
+      <c r="H121" s="4">
         <v>200</v>
       </c>
-      <c r="I121" s="3">
+      <c r="I121" s="4">
         <v>40026</v>
       </c>
-      <c r="K121" s="3">
+      <c r="K121" s="4">
         <v>1</v>
       </c>
-      <c r="L121" s="3" t="s">
+      <c r="L121" s="4" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="122" spans="2:12">
-      <c r="B122" s="3">
+      <c r="B122" s="4">
         <v>427</v>
       </c>
       <c r="C122" t="s">
         <v>397</v>
       </c>
-      <c r="D122" s="3">
+      <c r="D122" s="4">
         <v>0.1</v>
       </c>
       <c r="E122" t="s">
@@ -6520,30 +6532,30 @@
       <c r="F122" t="s">
         <v>516</v>
       </c>
-      <c r="G122" s="3">
+      <c r="G122" s="4">
         <v>330</v>
       </c>
-      <c r="H122" s="3">
+      <c r="H122" s="4">
         <v>165</v>
       </c>
-      <c r="I122" s="3">
+      <c r="I122" s="4">
         <v>40027</v>
       </c>
-      <c r="K122" s="3">
+      <c r="K122" s="4">
         <v>1</v>
       </c>
-      <c r="L122" s="3" t="s">
+      <c r="L122" s="4" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="123" spans="2:12">
-      <c r="B123" s="3">
+      <c r="B123" s="4">
         <v>428</v>
       </c>
       <c r="C123" t="s">
         <v>397</v>
       </c>
-      <c r="D123" s="3">
+      <c r="D123" s="4">
         <v>0.1</v>
       </c>
       <c r="E123" t="s">
@@ -6552,30 +6564,30 @@
       <c r="F123" t="s">
         <v>519</v>
       </c>
-      <c r="G123" s="3">
+      <c r="G123" s="4">
         <v>260</v>
       </c>
-      <c r="H123" s="3">
+      <c r="H123" s="4">
         <v>130</v>
       </c>
-      <c r="I123" s="3">
+      <c r="I123" s="4">
         <v>40028</v>
       </c>
-      <c r="K123" s="3">
+      <c r="K123" s="4">
         <v>2</v>
       </c>
-      <c r="L123" s="3" t="s">
+      <c r="L123" s="4" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="124" spans="2:12">
-      <c r="B124" s="3">
+      <c r="B124" s="4">
         <v>429</v>
       </c>
       <c r="C124" t="s">
         <v>397</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124" s="4">
         <v>0.1</v>
       </c>
       <c r="E124" t="s">
@@ -6584,30 +6596,30 @@
       <c r="F124" t="s">
         <v>522</v>
       </c>
-      <c r="G124" s="3">
+      <c r="G124" s="4">
         <v>270</v>
       </c>
-      <c r="H124" s="3">
+      <c r="H124" s="4">
         <v>135</v>
       </c>
-      <c r="I124" s="3">
+      <c r="I124" s="4">
         <v>40029</v>
       </c>
-      <c r="K124" s="3">
+      <c r="K124" s="4">
         <v>2</v>
       </c>
-      <c r="L124" s="3" t="s">
+      <c r="L124" s="4" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="125" spans="2:12">
-      <c r="B125" s="3">
+      <c r="B125" s="4">
         <v>430</v>
       </c>
       <c r="C125" t="s">
         <v>397</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125" s="4">
         <v>0.1</v>
       </c>
       <c r="E125" t="s">
@@ -6616,19 +6628,19 @@
       <c r="F125" t="s">
         <v>525</v>
       </c>
-      <c r="G125" s="3">
+      <c r="G125" s="4">
         <v>280</v>
       </c>
-      <c r="H125" s="3">
+      <c r="H125" s="4">
         <v>140</v>
       </c>
-      <c r="I125" s="3">
+      <c r="I125" s="4">
         <v>40030</v>
       </c>
-      <c r="K125" s="3">
-        <v>0</v>
-      </c>
-      <c r="L125" s="3" t="s">
+      <c r="K125" s="4">
+        <v>0</v>
+      </c>
+      <c r="L125" s="4" t="s">
         <v>526</v>
       </c>
     </row>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -1778,7 +1778,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>每回合开始时,获得1金币</t>
+          <t>每回合开始时,获得2金币</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>每回合结束后,有20%概率获得5金币</t>
+          <t>每回合结束后,有25%概率获得8金币</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>亮出的每张人头牌在结算时获得2金币</t>
+          <t>亮出的每张人头牌在结算时获得3金币</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>每次受到伤害时,+10金币</t>
+          <t>每次受到伤害时,+15金币</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>每回合结束时,若本回合未造成任何伤害,则获得10金币</t>
+          <t>每回合结束时,若本回合未造成任何伤害,则获得15金币</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>亮牌后无论胜负,均可获得2金币</t>
+          <t>亮牌后无论胜负,均可获得3金币</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>每通过1关时,每拥有15金币获得1金币,每关至多10金币</t>
+          <t>每通过1关时,每拥有10金币获得1金币,每关至多15金币</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>每回合结束时,每剩余1次搓牌次数就获得3金币</t>
+          <t>每回合结束时,每剩余1次搓牌次数就获得5金币</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>每击杀1名敌人,该收藏品的出售价格+5金币</t>
+          <t>每击杀1名敌人,该收藏品的出售价格+8金币</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>亮出的每张9在结算时提供15金币</t>
+          <t>亮出的每张9在结算时提供20金币</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点生命值</t>
+          <t>如果本回合牌型小于所有敌人,则立即获得25金币并回复20点生命值</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>每关开始时,若生命值高于50%,获得15金币</t>
+          <t>每关开始时,若生命值高于50%,获得25金币</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>每通过1关时,获得25金币</t>
+          <t>每通过1关时,获得40金币</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>每回合结束后,本回合自身总伤害输出的15%转化为金币</t>
+          <t>每回合结束后,本回合自身总伤害输出的20%转化为金币</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>使用后,随机3种牌型的倍率永久+5</t>
+          <t>使用后,随机3种牌型的倍率永久+6</t>
         </is>
       </c>
     </row>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="17145" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1576,7 +1576,7 @@
     <t>GodLeftHand</t>
   </si>
   <si>
-    <t>使用后,本次比牌你造成的伤害固定为500点</t>
+    <t>使用后,本次比牌你造成的伤害提高300%</t>
   </si>
   <si>
     <t>凤凰羽毛</t>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13170" windowHeight="10470"/>
+    <workbookView windowWidth="13170" windowHeight="11550"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="549">
   <si>
     <t>##var</t>
   </si>
@@ -856,6 +856,42 @@
     <t>使用后,顺子牌型提供的倍率永久+1</t>
   </si>
   <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>第一位</t>
+  </si>
+  <si>
+    <t>20033</t>
+  </si>
+  <si>
+    <t>亮牌时的第一张牌提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>第二位</t>
+  </si>
+  <si>
+    <t>20034</t>
+  </si>
+  <si>
+    <t>亮牌时的第二张牌提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>第三位</t>
+  </si>
+  <si>
+    <t>20035</t>
+  </si>
+  <si>
+    <t>亮牌时的第三张牌提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
     <t>Epic</t>
   </si>
   <si>
@@ -1232,6 +1268,15 @@
   </si>
   <si>
     <t>使用后,移除本关内的1条BOSS词缀效果</t>
+  </si>
+  <si>
+    <t>三花聚顶</t>
+  </si>
+  <si>
+    <t>30032</t>
+  </si>
+  <si>
+    <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
   </si>
   <si>
     <t>401</t>
@@ -1805,7 +1850,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1821,12 +1866,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2149,7 +2188,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -2173,16 +2212,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -2191,89 +2230,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2290,9 +2329,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -2337,21 +2373,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2701,21 +2722,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="3" customWidth="1"/>
     <col min="2" max="2" width="4.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.8" style="7" customWidth="1"/>
-    <col min="4" max="4" width="4.78333333333333" style="8" customWidth="1"/>
-    <col min="5" max="5" width="8.8" style="8" customWidth="1"/>
-    <col min="6" max="6" width="10.1083333333333" style="8" customWidth="1"/>
-    <col min="7" max="7" width="5.975" style="8" customWidth="1"/>
-    <col min="8" max="8" width="4.78333333333333" style="8" customWidth="1"/>
-    <col min="9" max="9" width="7.38333333333333" style="8" customWidth="1"/>
-    <col min="10" max="10" width="5.53333333333333" style="8" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="6" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="7" customWidth="1"/>
+    <col min="5" max="5" width="8.8" style="7" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" style="7" customWidth="1"/>
+    <col min="7" max="7" width="5.975" style="7" customWidth="1"/>
+    <col min="8" max="8" width="4.78333333333333" style="7" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="7" customWidth="1"/>
+    <col min="10" max="10" width="5.53333333333333" style="7" customWidth="1"/>
     <col min="11" max="11" width="8.03333333333333" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.70833333333333" style="8" customWidth="1"/>
+    <col min="12" max="12" width="7.70833333333333" style="7" customWidth="1"/>
     <col min="14" max="14" width="34.75" style="3" customWidth="1"/>
     <col min="15" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
@@ -2730,31 +2751,31 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2768,31 +2789,31 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2806,31 +2827,31 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2841,28 +2862,28 @@
       <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>0.8</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>30</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>15</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>10001</v>
       </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9" t="s">
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2873,32 +2894,32 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="9">
         <v>0.8</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="9">
         <v>28</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>14</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>10002</v>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="11" t="s">
+      <c r="J6" s="9"/>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="12"/>
+      <c r="M6" s="11"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:13">
       <c r="B7" s="1" t="s">
@@ -2907,32 +2928,32 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>0.8</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>28</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>14</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>10003</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="11" t="s">
+      <c r="J7" s="9"/>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="12"/>
+      <c r="M7" s="11"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:13">
       <c r="B8" s="1" t="s">
@@ -2941,32 +2962,32 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="9">
         <v>0.8</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="9">
         <v>28</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>14</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="9">
         <v>10004</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="11" t="s">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="12"/>
+      <c r="M8" s="11"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:13">
       <c r="B9" s="1" t="s">
@@ -2975,32 +2996,32 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="9">
         <v>0.8</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="9">
         <v>28</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <v>14</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="9">
         <v>10005</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="s">
+      <c r="J9" s="9"/>
+      <c r="K9" s="9">
+        <v>0</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="12"/>
+      <c r="M9" s="11"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:13">
       <c r="B10" s="1" t="s">
@@ -3009,32 +3030,32 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="9">
         <v>0.8</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="9">
         <v>28</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="9">
         <v>14</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>10006</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10">
-        <v>0</v>
-      </c>
-      <c r="L10" s="11" t="s">
+      <c r="J10" s="9"/>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="12"/>
+      <c r="M10" s="11"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:13">
       <c r="B11" s="1" t="s">
@@ -3043,32 +3064,32 @@
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="9">
         <v>0.8</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="9">
         <v>22</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <v>11</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="9">
         <v>10007</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="11" t="s">
+      <c r="J11" s="9"/>
+      <c r="K11" s="9">
+        <v>0</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="12"/>
+      <c r="M11" s="11"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:13">
       <c r="B12" s="1" t="s">
@@ -3077,32 +3098,32 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="9">
         <v>0.8</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="9">
         <v>35</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="9">
         <v>17</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="9">
         <v>10008</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="11" t="s">
+      <c r="J12" s="9"/>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="12"/>
+      <c r="M12" s="11"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:13">
       <c r="B13" s="1" t="s">
@@ -3111,32 +3132,32 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="9">
         <v>0.8</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="9">
         <v>16</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="9">
         <v>8</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="9">
         <v>10009</v>
       </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11" t="s">
+      <c r="J13" s="9"/>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="M13" s="12"/>
+      <c r="M13" s="11"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:13">
       <c r="B14" s="1" t="s">
@@ -3145,32 +3166,32 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="9">
         <v>0.8</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="9">
         <v>16</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="9">
         <v>8</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>10010</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="11" t="s">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="12"/>
+      <c r="M14" s="11"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:13">
       <c r="B15" s="2" t="s">
@@ -3179,32 +3200,32 @@
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <v>0.8</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <v>15</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="12">
         <v>7</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <v>10011</v>
       </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14" t="s">
+      <c r="J15" s="12"/>
+      <c r="K15" s="12">
+        <v>0</v>
+      </c>
+      <c r="L15" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="15"/>
+      <c r="M15" s="14"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:13">
       <c r="B16" s="3" t="s">
@@ -3213,29 +3234,29 @@
       <c r="C16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>0.8</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>30</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>15</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <v>10012</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9" t="s">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3246,29 +3267,29 @@
       <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>0.8</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>35</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>17</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <v>10013</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9" t="s">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3279,29 +3300,29 @@
       <c r="C18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>0.8</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>26</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>13</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <v>10014</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9" t="s">
+      <c r="J18" s="7"/>
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3312,29 +3333,29 @@
       <c r="C19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>0.8</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>22</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>11</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <v>10015</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="9" t="s">
+      <c r="J19" s="7"/>
+      <c r="K19" s="7">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3345,29 +3366,29 @@
       <c r="C20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="12">
         <v>0.8</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="12">
         <v>28</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="12">
         <v>14</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <v>10016</v>
       </c>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13">
-        <v>0</v>
-      </c>
-      <c r="L20" s="14" t="s">
+      <c r="J20" s="12"/>
+      <c r="K20" s="12">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3378,29 +3399,29 @@
       <c r="C21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <v>0.8</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="12">
         <v>20</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="12">
         <v>10</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <v>10017</v>
       </c>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="14" t="s">
+      <c r="J21" s="12"/>
+      <c r="K21" s="12">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3411,7 +3432,7 @@
       <c r="C22" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>0.8</v>
       </c>
       <c r="E22" t="s">
@@ -3420,19 +3441,19 @@
       <c r="F22" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="7">
         <v>25</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="7">
         <v>12</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="7">
         <v>10018</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="7">
         <v>1</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="8" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3443,7 +3464,7 @@
       <c r="C23" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>0.8</v>
       </c>
       <c r="E23" t="s">
@@ -3452,19 +3473,19 @@
       <c r="F23" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="7">
         <v>25</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <v>12</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="7">
         <v>10019</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <v>1</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="8" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3472,35 +3493,35 @@
       <c r="B24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="12">
         <v>0.8</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="12">
         <v>30</v>
       </c>
-      <c r="H24" s="13">
+      <c r="H24" s="12">
         <v>15</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="12">
         <v>10020</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13">
-        <v>0</v>
-      </c>
-      <c r="L24" s="14" t="s">
+      <c r="J24" s="12"/>
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="15"/>
+      <c r="M24" s="14"/>
     </row>
     <row r="25" spans="1:13">
       <c r="B25" s="3" t="s">
@@ -3509,7 +3530,7 @@
       <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>0.8</v>
       </c>
       <c r="E25" t="s">
@@ -3518,19 +3539,19 @@
       <c r="F25" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="7">
         <v>70</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>35</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="7">
         <v>10021</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="7">
         <v>2</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3539,7 +3560,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="K26" s="8"/>
+      <c r="K26" s="7"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
       <c r="B27" s="1" t="s">
@@ -3548,13 +3569,13 @@
       <c r="C27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="9">
         <v>0.4</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="9" t="s">
         <v>116</v>
       </c>
       <c r="G27" s="1">
@@ -3566,14 +3587,14 @@
       <c r="I27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10">
-        <v>0</v>
-      </c>
-      <c r="L27" s="11" t="s">
+      <c r="J27" s="9"/>
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="M27" s="12"/>
+      <c r="M27" s="11"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:13">
       <c r="B28" s="1" t="s">
@@ -3582,13 +3603,13 @@
       <c r="C28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="9">
         <v>0.4</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="9" t="s">
         <v>121</v>
       </c>
       <c r="G28" s="1">
@@ -3600,30 +3621,30 @@
       <c r="I28" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10">
-        <v>0</v>
-      </c>
-      <c r="L28" s="11" t="s">
+      <c r="J28" s="9"/>
+      <c r="K28" s="9">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="M28" s="12"/>
+      <c r="M28" s="11"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="12"/>
+      <c r="A29" s="11"/>
       <c r="B29" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="9">
         <v>0.4</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="9" t="s">
         <v>126</v>
       </c>
       <c r="G29" s="1">
@@ -3635,30 +3656,30 @@
       <c r="I29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10">
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="s">
+      <c r="J29" s="9"/>
+      <c r="K29" s="9">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="M29" s="12"/>
+      <c r="M29" s="11"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:13">
-      <c r="A30" s="12"/>
+      <c r="A30" s="11"/>
       <c r="B30" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="9">
         <v>0.4</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="9" t="s">
         <v>131</v>
       </c>
       <c r="G30" s="1">
@@ -3670,30 +3691,30 @@
       <c r="I30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10">
-        <v>0</v>
-      </c>
-      <c r="L30" s="11" t="s">
+      <c r="J30" s="9"/>
+      <c r="K30" s="9">
+        <v>0</v>
+      </c>
+      <c r="L30" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="M30" s="12"/>
+      <c r="M30" s="11"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:13">
-      <c r="A31" s="12"/>
+      <c r="A31" s="11"/>
       <c r="B31" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <v>0.4</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="9" t="s">
         <v>136</v>
       </c>
       <c r="G31" s="1">
@@ -3705,30 +3726,30 @@
       <c r="I31" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10">
-        <v>0</v>
-      </c>
-      <c r="L31" s="11" t="s">
+      <c r="J31" s="9"/>
+      <c r="K31" s="9">
+        <v>0</v>
+      </c>
+      <c r="L31" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="M31" s="12"/>
+      <c r="M31" s="11"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:13">
-      <c r="A32" s="12"/>
+      <c r="A32" s="11"/>
       <c r="B32" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="9">
         <v>0.4</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="9" t="s">
         <v>141</v>
       </c>
       <c r="G32" s="1">
@@ -3740,30 +3761,30 @@
       <c r="I32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10">
-        <v>0</v>
-      </c>
-      <c r="L32" s="11" t="s">
+      <c r="J32" s="9"/>
+      <c r="K32" s="9">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="M32" s="12"/>
+      <c r="M32" s="11"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="12"/>
+      <c r="A33" s="11"/>
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="9">
         <v>0.4</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="9" t="s">
         <v>146</v>
       </c>
       <c r="G33" s="1">
@@ -3775,30 +3796,30 @@
       <c r="I33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10">
-        <v>0</v>
-      </c>
-      <c r="L33" s="11" t="s">
+      <c r="J33" s="9"/>
+      <c r="K33" s="9">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="M33" s="12"/>
+      <c r="M33" s="11"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:13">
-      <c r="A34" s="12"/>
+      <c r="A34" s="11"/>
       <c r="B34" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="9">
         <v>0.4</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="9" t="s">
         <v>151</v>
       </c>
       <c r="G34" s="1">
@@ -3810,30 +3831,30 @@
       <c r="I34" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J34" s="10"/>
-      <c r="K34" s="10">
-        <v>0</v>
-      </c>
-      <c r="L34" s="11" t="s">
+      <c r="J34" s="9"/>
+      <c r="K34" s="9">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="M34" s="12"/>
+      <c r="M34" s="11"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="12"/>
+      <c r="A35" s="11"/>
       <c r="B35" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="9">
         <v>0.4</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="9" t="s">
         <v>156</v>
       </c>
       <c r="G35" s="1">
@@ -3845,30 +3866,30 @@
       <c r="I35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10">
-        <v>0</v>
-      </c>
-      <c r="L35" s="11" t="s">
+      <c r="J35" s="9"/>
+      <c r="K35" s="9">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="M35" s="12"/>
+      <c r="M35" s="11"/>
     </row>
     <row r="36" s="4" customFormat="1" spans="1:13">
-      <c r="A36" s="16"/>
+      <c r="A36" s="15"/>
       <c r="B36" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="16">
         <v>0.4</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="16" t="s">
         <v>161</v>
       </c>
       <c r="G36" s="4">
@@ -3880,14 +3901,14 @@
       <c r="I36" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17">
-        <v>0</v>
-      </c>
-      <c r="L36" s="9" t="s">
+      <c r="J36" s="16"/>
+      <c r="K36" s="16">
+        <v>0</v>
+      </c>
+      <c r="L36" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="M36" s="16"/>
+      <c r="M36" s="15"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37"/>
@@ -3897,13 +3918,13 @@
       <c r="C37" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="7">
         <v>0.4</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="7" t="s">
         <v>166</v>
       </c>
       <c r="G37" s="3">
@@ -3915,28 +3936,28 @@
       <c r="I37" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="8">
-        <v>0</v>
-      </c>
-      <c r="L37" s="8" t="s">
+      <c r="K37" s="7">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" spans="1:13">
-      <c r="A38" s="18"/>
+      <c r="A38" s="17"/>
       <c r="B38" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="18">
         <v>0.4</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="18" t="s">
         <v>171</v>
       </c>
       <c r="G38" s="5">
@@ -3948,14 +3969,14 @@
       <c r="I38" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19">
-        <v>0</v>
-      </c>
-      <c r="L38" s="20" t="s">
+      <c r="J38" s="18"/>
+      <c r="K38" s="18">
+        <v>0</v>
+      </c>
+      <c r="L38" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="M38" s="18"/>
+      <c r="M38" s="17"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39"/>
@@ -3965,13 +3986,13 @@
       <c r="C39" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="7">
         <v>0.4</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="7" t="s">
         <v>176</v>
       </c>
       <c r="G39" s="3">
@@ -3983,10 +4004,10 @@
       <c r="I39" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="K39" s="8">
-        <v>0</v>
-      </c>
-      <c r="L39" s="9" t="s">
+      <c r="K39" s="7">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3998,13 +4019,13 @@
       <c r="C40" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <v>0.4</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="7" t="s">
         <v>181</v>
       </c>
       <c r="G40" s="3">
@@ -4016,10 +4037,10 @@
       <c r="I40" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="K40" s="8">
-        <v>0</v>
-      </c>
-      <c r="L40" s="9" t="s">
+      <c r="K40" s="7">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4031,13 +4052,13 @@
       <c r="C41" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <v>0.4</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G41" s="3">
@@ -4049,10 +4070,10 @@
       <c r="I41" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="K41" s="8">
-        <v>0</v>
-      </c>
-      <c r="L41" s="9" t="s">
+      <c r="K41" s="7">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8" t="s">
         <v>188</v>
       </c>
     </row>
@@ -4064,13 +4085,13 @@
       <c r="C42" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>0.4</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="7" t="s">
         <v>191</v>
       </c>
       <c r="G42" s="3">
@@ -4082,10 +4103,10 @@
       <c r="I42" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="K42" s="8">
-        <v>0</v>
-      </c>
-      <c r="L42" s="9" t="s">
+      <c r="K42" s="7">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8" t="s">
         <v>193</v>
       </c>
     </row>
@@ -4097,13 +4118,13 @@
       <c r="C43" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="7">
         <v>0.4</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="7" t="s">
         <v>196</v>
       </c>
       <c r="G43" s="3">
@@ -4115,10 +4136,10 @@
       <c r="I43" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K43" s="8">
-        <v>0</v>
-      </c>
-      <c r="L43" s="9" t="s">
+      <c r="K43" s="7">
+        <v>0</v>
+      </c>
+      <c r="L43" s="8" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4130,97 +4151,97 @@
       <c r="C44" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="7">
         <v>0.4</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="7">
         <v>85</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="7">
         <v>42</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8">
-        <v>0</v>
-      </c>
-      <c r="L44" s="8" t="s">
+      <c r="J44" s="7"/>
+      <c r="K44" s="7">
+        <v>0</v>
+      </c>
+      <c r="L44" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" spans="1:13">
-      <c r="A45" s="15"/>
+      <c r="A45" s="14"/>
       <c r="B45" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="12">
         <v>0.4</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="G45" s="13">
+      <c r="G45" s="12">
         <v>75</v>
       </c>
-      <c r="H45" s="13">
+      <c r="H45" s="12">
         <v>37</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13">
-        <v>0</v>
-      </c>
-      <c r="L45" s="14" t="s">
+      <c r="J45" s="12"/>
+      <c r="K45" s="12">
+        <v>0</v>
+      </c>
+      <c r="L45" s="13" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="1:13">
-      <c r="A46" s="15"/>
+      <c r="A46" s="14"/>
       <c r="B46" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="12">
         <v>0.4</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="13">
+      <c r="G46" s="12">
         <v>75</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H46" s="12">
         <v>37</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13">
-        <v>0</v>
-      </c>
-      <c r="L46" s="14" t="s">
+      <c r="J46" s="12"/>
+      <c r="K46" s="12">
+        <v>0</v>
+      </c>
+      <c r="L46" s="13" t="s">
         <v>213</v>
       </c>
     </row>
@@ -4232,29 +4253,29 @@
       <c r="C47" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="7">
         <v>0.4</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="7">
         <v>70</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="7">
         <v>35</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8">
-        <v>0</v>
-      </c>
-      <c r="L47" s="9" t="s">
+      <c r="J47" s="7"/>
+      <c r="K47" s="7">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8" t="s">
         <v>218</v>
       </c>
     </row>
@@ -4266,29 +4287,29 @@
       <c r="C48" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="7">
         <v>0.4</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="7">
         <v>75</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="7">
         <v>37</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8">
-        <v>0</v>
-      </c>
-      <c r="L48" s="9" t="s">
+      <c r="J48" s="7"/>
+      <c r="K48" s="7">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4299,31 +4320,31 @@
       <c r="C49" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="7">
         <v>0.4</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="7">
         <v>90</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="7">
         <v>45</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="7">
         <v>10301</v>
       </c>
-      <c r="K49" s="8">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8" t="s">
+      <c r="K49" s="7">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>228</v>
       </c>
     </row>
@@ -4335,28 +4356,28 @@
       <c r="C50" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="7">
         <v>0.4</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="7">
         <v>120</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="7">
         <v>60</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="K50" s="8">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8" t="s">
+      <c r="K50" s="7">
+        <v>0</v>
+      </c>
+      <c r="L50" s="7" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4368,65 +4389,65 @@
       <c r="C51" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="7">
         <v>0.4</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="7">
         <v>110</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="7">
         <v>55</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="K51" s="8">
-        <v>0</v>
-      </c>
-      <c r="L51" s="9" t="s">
+      <c r="K51" s="7">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:13">
-      <c r="A52" s="15"/>
+      <c r="A52" s="14"/>
       <c r="B52" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="13">
+      <c r="D52" s="12">
         <v>0.4</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="F52" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="G52" s="13">
+      <c r="G52" s="12">
         <v>70</v>
       </c>
-      <c r="H52" s="13">
+      <c r="H52" s="12">
         <v>35</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13">
-        <v>0</v>
-      </c>
-      <c r="L52" s="14" t="s">
+      <c r="J52" s="12"/>
+      <c r="K52" s="12">
+        <v>0</v>
+      </c>
+      <c r="L52" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="M52" s="15"/>
+      <c r="M52" s="14"/>
     </row>
     <row r="53" spans="1:13">
       <c r="B53" s="1" t="s">
@@ -4435,7 +4456,7 @@
       <c r="C53" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="7">
         <v>0.4</v>
       </c>
       <c r="E53" t="s">
@@ -4444,19 +4465,19 @@
       <c r="F53" t="s">
         <v>246</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="7">
         <v>90</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="7">
         <v>45</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="K53" s="8">
+      <c r="K53" s="7">
         <v>1</v>
       </c>
-      <c r="L53" s="9" t="s">
+      <c r="L53" s="8" t="s">
         <v>248</v>
       </c>
     </row>
@@ -4467,7 +4488,7 @@
       <c r="C54" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="7">
         <v>0.4</v>
       </c>
       <c r="E54" t="s">
@@ -4476,19 +4497,19 @@
       <c r="F54" t="s">
         <v>251</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="7">
         <v>145</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="7">
         <v>72</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="K54" s="8">
+      <c r="K54" s="7">
         <v>1</v>
       </c>
-      <c r="L54" s="9" t="s">
+      <c r="L54" s="8" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4499,7 +4520,7 @@
       <c r="C55" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="7">
         <v>0.4</v>
       </c>
       <c r="E55" t="s">
@@ -4508,19 +4529,19 @@
       <c r="F55" t="s">
         <v>256</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="7">
         <v>75</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="7">
         <v>37</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K55" s="8">
-        <v>0</v>
-      </c>
-      <c r="L55" s="9" t="s">
+      <c r="K55" s="7">
+        <v>0</v>
+      </c>
+      <c r="L55" s="8" t="s">
         <v>258</v>
       </c>
     </row>
@@ -4531,7 +4552,7 @@
       <c r="C56" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="7">
         <v>0.4</v>
       </c>
       <c r="E56" t="s">
@@ -4540,19 +4561,19 @@
       <c r="F56" t="s">
         <v>261</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="7">
         <v>110</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="7">
         <v>55</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K56" s="8">
+      <c r="K56" s="7">
         <v>1</v>
       </c>
-      <c r="L56" s="9" t="s">
+      <c r="L56" s="8" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4560,44 +4581,44 @@
       <c r="B57" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57" s="9">
         <v>0.4</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="F57" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57" s="9">
         <v>190</v>
       </c>
-      <c r="H57" s="10">
+      <c r="H57" s="9">
         <v>95</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10">
+      <c r="J57" s="9"/>
+      <c r="K57" s="9">
         <v>2</v>
       </c>
-      <c r="L57" s="11" t="s">
+      <c r="L57" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="M57" s="12"/>
-    </row>
-    <row r="58" spans="1:13">
+      <c r="M57" s="11"/>
+    </row>
+    <row r="58" ht="14.25" spans="1:13">
       <c r="B58" s="1" t="s">
         <v>269</v>
       </c>
       <c r="C58" t="s">
         <v>114</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="7">
         <v>0.4</v>
       </c>
       <c r="E58" t="s">
@@ -4606,2124 +4627,2261 @@
       <c r="F58" t="s">
         <v>271</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="9">
         <v>190</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="9">
         <v>95</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="K58" s="8">
+      <c r="K58" s="7">
         <v>2</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L58" s="7" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
-      <c r="A59"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="K59" s="8"/>
-    </row>
-    <row r="60" spans="1:13">
-      <c r="A60"/>
-      <c r="B60" s="8">
-        <v>301</v>
-      </c>
-      <c r="C60" s="3" t="s">
+    <row r="59" s="2" customFormat="1" spans="1:13">
+      <c r="A59" s="14"/>
+      <c r="B59" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D60" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="E60" s="8" t="s">
+      <c r="C59" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="E59" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="F60" s="8" t="s">
+      <c r="F59" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="G59" s="12">
+        <v>190</v>
+      </c>
+      <c r="H59" s="12">
+        <v>95</v>
+      </c>
+      <c r="I59" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J59" s="12"/>
+      <c r="K59" s="12">
+        <v>0</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="M59" s="14"/>
+    </row>
+    <row r="60" s="2" customFormat="1" spans="1:13">
+      <c r="A60" s="14"/>
+      <c r="B60" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="F60" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="G60" s="12">
         <v>190</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60" s="12">
         <v>95</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="J60" s="8">
-        <v>10401</v>
-      </c>
-      <c r="K60" s="8">
-        <v>0</v>
-      </c>
-      <c r="L60" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="A61"/>
-      <c r="B61" s="8">
-        <v>302</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D61" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="F61" s="8" t="s">
+      <c r="I60" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="G61" s="3">
-        <v>270</v>
-      </c>
-      <c r="H61" s="3">
-        <v>135</v>
-      </c>
-      <c r="I61" s="3" t="s">
+      <c r="J60" s="12"/>
+      <c r="K60" s="12">
+        <v>0</v>
+      </c>
+      <c r="L60" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="K61" s="8">
-        <v>0</v>
-      </c>
-      <c r="L61" s="9" t="s">
+      <c r="M60" s="14"/>
+    </row>
+    <row r="61" s="2" customFormat="1" spans="1:13">
+      <c r="A61" s="14"/>
+      <c r="B61" s="2" t="s">
         <v>282</v>
       </c>
+      <c r="C61" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="G61" s="12">
+        <v>190</v>
+      </c>
+      <c r="H61" s="12">
+        <v>95</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12">
+        <v>0</v>
+      </c>
+      <c r="L61" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="M61" s="14"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62"/>
-      <c r="B62" s="8">
-        <v>303</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D62" s="8">
+      <c r="B62" s="7"/>
+      <c r="C62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="K62" s="7"/>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="A63"/>
+      <c r="B63" s="7">
+        <v>301</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D63" s="7">
         <v>0.2</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="F62" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="E63" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G63" s="3">
         <v>190</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H63" s="3">
         <v>95</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="J62" s="21">
-        <v>10501</v>
-      </c>
-      <c r="K62" s="8">
-        <v>0</v>
-      </c>
-      <c r="L62" s="9" t="s">
+      <c r="I63" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J63" s="7">
+        <v>10401</v>
+      </c>
+      <c r="K63" s="7">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13">
+      <c r="A64"/>
+      <c r="B64" s="7">
+        <v>302</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="63" s="2" customFormat="1" spans="1:13">
-      <c r="A63" s="15"/>
-      <c r="B63" s="13">
-        <v>304</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D63" s="13">
+      <c r="D64" s="7">
         <v>0.2</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="F63" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="G63" s="2">
-        <v>160</v>
-      </c>
-      <c r="H63" s="2">
-        <v>80</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J63" s="13">
-        <v>10601</v>
-      </c>
-      <c r="K63" s="13">
-        <v>0</v>
-      </c>
-      <c r="L63" s="14" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="64" s="3" customFormat="1" spans="1:13">
-      <c r="A64"/>
-      <c r="B64" s="8">
-        <v>305</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D64" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="F64" s="7" t="s">
         <v>292</v>
       </c>
       <c r="G64" s="3">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="H64" s="3">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="J64" s="8">
-        <v>10701</v>
-      </c>
-      <c r="K64" s="8">
-        <v>0</v>
-      </c>
-      <c r="L64" s="9" t="s">
+      <c r="K64" s="7">
+        <v>0</v>
+      </c>
+      <c r="L64" s="8" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="65" s="3" customFormat="1" spans="2:13">
-      <c r="B65" s="8">
-        <v>306</v>
+    <row r="65" spans="1:12">
+      <c r="A65"/>
+      <c r="B65" s="7">
+        <v>303</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D65" s="8">
+        <v>286</v>
+      </c>
+      <c r="D65" s="7">
         <v>0.2</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="F65" s="7" t="s">
         <v>296</v>
       </c>
       <c r="G65" s="3">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="H65" s="3">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8">
-        <v>0</v>
-      </c>
-      <c r="L65" s="9" t="s">
+      <c r="J65" s="20">
+        <v>10501</v>
+      </c>
+      <c r="K65" s="7">
+        <v>0</v>
+      </c>
+      <c r="L65" s="8" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="66" s="3" customFormat="1" spans="2:13">
-      <c r="B66" s="8">
-        <v>307</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D66" s="8">
+    <row r="66" s="2" customFormat="1" spans="1:12">
+      <c r="A66" s="14"/>
+      <c r="B66" s="12">
+        <v>304</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D66" s="12">
         <v>0.2</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="F66" s="12" t="s">
         <v>300</v>
       </c>
-      <c r="G66" s="3">
-        <v>265</v>
-      </c>
-      <c r="H66" s="3">
-        <v>132</v>
-      </c>
-      <c r="I66" s="3" t="s">
+      <c r="G66" s="2">
+        <v>160</v>
+      </c>
+      <c r="H66" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="K66" s="8">
-        <v>0</v>
-      </c>
-      <c r="L66" s="9" t="s">
+      <c r="J66" s="12">
+        <v>10601</v>
+      </c>
+      <c r="K66" s="12">
+        <v>0</v>
+      </c>
+      <c r="L66" s="13" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="67" s="3" customFormat="1" spans="2:13">
-      <c r="B67" s="8">
-        <v>308</v>
+    <row r="67" s="3" customFormat="1" spans="1:12">
+      <c r="A67"/>
+      <c r="B67" s="7">
+        <v>305</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D67" s="8">
+        <v>286</v>
+      </c>
+      <c r="D67" s="7">
         <v>0.2</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="7" t="s">
         <v>304</v>
       </c>
       <c r="G67" s="3">
-        <v>360</v>
+        <v>170</v>
       </c>
       <c r="H67" s="3">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="J67" s="10"/>
-      <c r="K67" s="8">
-        <v>0</v>
-      </c>
-      <c r="L67" s="9" t="s">
+      <c r="J67" s="7">
+        <v>10701</v>
+      </c>
+      <c r="K67" s="7">
+        <v>0</v>
+      </c>
+      <c r="L67" s="8" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="68" s="3" customFormat="1" spans="2:13">
-      <c r="B68" s="8">
-        <v>309</v>
+    <row r="68" s="3" customFormat="1" spans="1:12">
+      <c r="B68" s="7">
+        <v>306</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D68" s="8">
+        <v>286</v>
+      </c>
+      <c r="D68" s="7">
         <v>0.2</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="7" t="s">
         <v>308</v>
       </c>
       <c r="G68" s="3">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="H68" s="3">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I68" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="K68" s="8">
-        <v>0</v>
-      </c>
-      <c r="L68" t="s">
+      <c r="J68" s="7"/>
+      <c r="K68" s="7">
+        <v>0</v>
+      </c>
+      <c r="L68" s="8" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="69" s="3" customFormat="1" spans="2:13">
-      <c r="B69" s="8">
-        <v>310</v>
+    <row r="69" s="3" customFormat="1" spans="1:12">
+      <c r="B69" s="7">
+        <v>307</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D69" s="8">
+        <v>286</v>
+      </c>
+      <c r="D69" s="7">
         <v>0.2</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="7" t="s">
         <v>312</v>
       </c>
       <c r="G69" s="3">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H69" s="3">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="J69" s="10"/>
-      <c r="K69" s="8">
+      <c r="K69" s="7">
         <v>0</v>
       </c>
       <c r="L69" s="8" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" spans="2:13">
-      <c r="B70" s="13">
-        <v>311</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D70" s="13">
+    <row r="70" s="3" customFormat="1" spans="1:12">
+      <c r="B70" s="7">
+        <v>308</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D70" s="7">
         <v>0.2</v>
       </c>
-      <c r="E70" s="13" t="s">
+      <c r="E70" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F70" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="G70" s="2">
-        <v>170</v>
-      </c>
-      <c r="H70" s="2">
-        <v>85</v>
-      </c>
-      <c r="I70" s="2" t="s">
+      <c r="G70" s="3">
+        <v>360</v>
+      </c>
+      <c r="H70" s="3">
+        <v>180</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="K70" s="13">
-        <v>0</v>
-      </c>
-      <c r="L70" s="14" t="s">
+      <c r="J70" s="9"/>
+      <c r="K70" s="7">
+        <v>0</v>
+      </c>
+      <c r="L70" s="8" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" spans="2:13">
-      <c r="B71" s="13">
-        <v>312</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D71" s="13">
+    <row r="71" s="3" customFormat="1" spans="1:12">
+      <c r="B71" s="7">
+        <v>309</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D71" s="7">
         <v>0.2</v>
       </c>
-      <c r="E71" s="13" t="s">
+      <c r="E71" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F71" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="G71" s="2">
-        <v>210</v>
-      </c>
-      <c r="H71" s="2">
-        <v>105</v>
-      </c>
-      <c r="I71" s="2" t="s">
+      <c r="G71" s="3">
+        <v>350</v>
+      </c>
+      <c r="H71" s="3">
+        <v>175</v>
+      </c>
+      <c r="I71" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="K71" s="13">
-        <v>0</v>
-      </c>
-      <c r="L71" s="14" t="s">
+      <c r="K71" s="7">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="72" s="3" customFormat="1" spans="2:13">
-      <c r="B72" s="8">
-        <v>313</v>
+    <row r="72" s="3" customFormat="1" spans="1:12">
+      <c r="B72" s="7">
+        <v>310</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D72" s="8">
+        <v>286</v>
+      </c>
+      <c r="D72" s="7">
         <v>0.2</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="F72" s="8" t="s">
+      <c r="F72" s="7" t="s">
         <v>324</v>
       </c>
       <c r="G72" s="3">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="H72" s="3">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="J72" s="10"/>
-      <c r="K72" s="8">
-        <v>0</v>
-      </c>
-      <c r="L72" s="9" t="s">
+      <c r="J72" s="9"/>
+      <c r="K72" s="7">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="73" s="3" customFormat="1" spans="2:13">
-      <c r="B73" s="8">
-        <v>314</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D73" s="8">
+    <row r="73" s="2" customFormat="1" spans="1:12">
+      <c r="B73" s="12">
+        <v>311</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D73" s="12">
         <v>0.2</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="G73" s="8">
-        <v>180</v>
-      </c>
-      <c r="H73" s="8">
-        <v>90</v>
-      </c>
-      <c r="I73" s="3" t="s">
+      <c r="G73" s="2">
+        <v>170</v>
+      </c>
+      <c r="H73" s="2">
+        <v>85</v>
+      </c>
+      <c r="I73" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8">
-        <v>0</v>
-      </c>
-      <c r="L73" s="9" t="s">
+      <c r="K73" s="12">
+        <v>0</v>
+      </c>
+      <c r="L73" s="13" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="74" s="3" customFormat="1" spans="2:13">
-      <c r="B74" s="8">
-        <v>315</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D74" s="8">
+    <row r="74" s="2" customFormat="1" spans="1:12">
+      <c r="B74" s="12">
+        <v>312</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D74" s="12">
         <v>0.2</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="12" t="s">
         <v>332</v>
       </c>
-      <c r="G74" s="8">
-        <v>380</v>
-      </c>
-      <c r="H74" s="8">
-        <v>190</v>
-      </c>
-      <c r="I74" s="3" t="s">
+      <c r="G74" s="2">
+        <v>210</v>
+      </c>
+      <c r="H74" s="2">
+        <v>105</v>
+      </c>
+      <c r="I74" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8">
-        <v>0</v>
-      </c>
-      <c r="L74" s="9" t="s">
+      <c r="K74" s="12">
+        <v>0</v>
+      </c>
+      <c r="L74" s="13" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="75" spans="2:13">
-      <c r="B75" s="8">
-        <v>316</v>
+    <row r="75" s="3" customFormat="1" spans="1:12">
+      <c r="B75" s="7">
+        <v>313</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D75" s="8">
+        <v>286</v>
+      </c>
+      <c r="D75" s="7">
         <v>0.2</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G75" s="8">
-        <v>170</v>
-      </c>
-      <c r="H75" s="8">
-        <v>85</v>
+      <c r="G75" s="3">
+        <v>160</v>
+      </c>
+      <c r="H75" s="3">
+        <v>80</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="K75" s="8">
-        <v>0</v>
-      </c>
-      <c r="L75" s="9" t="s">
+      <c r="J75" s="9"/>
+      <c r="K75" s="7">
+        <v>0</v>
+      </c>
+      <c r="L75" s="8" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="76" spans="2:13">
-      <c r="B76" s="8">
-        <v>317</v>
+    <row r="76" s="3" customFormat="1" spans="1:12">
+      <c r="B76" s="7">
+        <v>314</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D76" s="8">
+        <v>286</v>
+      </c>
+      <c r="D76" s="7">
         <v>0.2</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="G76" s="8">
-        <v>200</v>
-      </c>
-      <c r="H76" s="8">
-        <v>100</v>
+      <c r="G76" s="7">
+        <v>180</v>
+      </c>
+      <c r="H76" s="7">
+        <v>90</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="J76" s="22">
-        <v>10201</v>
-      </c>
-      <c r="K76" s="8">
+      <c r="J76" s="7"/>
+      <c r="K76" s="7">
         <v>0</v>
       </c>
       <c r="L76" s="8" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="77" spans="2:13">
-      <c r="B77" s="8">
-        <v>318</v>
+    <row r="77" s="3" customFormat="1" spans="1:12">
+      <c r="B77" s="7">
+        <v>315</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D77" s="8">
+        <v>286</v>
+      </c>
+      <c r="D77" s="7">
         <v>0.2</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E77" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="G77" s="8">
-        <v>170</v>
-      </c>
-      <c r="H77" s="8">
-        <v>85</v>
+      <c r="G77" s="7">
+        <v>380</v>
+      </c>
+      <c r="H77" s="7">
+        <v>190</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="J77" s="21">
-        <v>10801</v>
-      </c>
-      <c r="K77" s="8">
-        <v>0</v>
-      </c>
-      <c r="L77" s="9" t="s">
+      <c r="J77" s="7"/>
+      <c r="K77" s="7">
+        <v>0</v>
+      </c>
+      <c r="L77" s="8" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="78" s="2" customFormat="1" spans="2:13">
-      <c r="B78" s="13">
-        <v>319</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D78" s="13">
+    <row r="78" spans="1:12">
+      <c r="B78" s="7">
+        <v>316</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D78" s="7">
         <v>0.2</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="F78" s="13" t="s">
+      <c r="F78" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="G78" s="13">
-        <v>160</v>
-      </c>
-      <c r="H78" s="13">
-        <v>80</v>
-      </c>
-      <c r="I78" s="2" t="s">
+      <c r="G78" s="7">
+        <v>170</v>
+      </c>
+      <c r="H78" s="7">
+        <v>85</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="J78" s="13">
-        <v>10402</v>
-      </c>
-      <c r="K78" s="13">
-        <v>0</v>
-      </c>
-      <c r="L78" s="14" t="s">
+      <c r="K78" s="7">
+        <v>0</v>
+      </c>
+      <c r="L78" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="M78" s="15"/>
-    </row>
-    <row r="79" spans="2:13">
-      <c r="B79" s="8">
-        <v>320</v>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="B79" s="7">
+        <v>317</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D79" s="8">
+        <v>286</v>
+      </c>
+      <c r="D79" s="7">
         <v>0.2</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G79" s="8">
-        <v>160</v>
-      </c>
-      <c r="H79" s="8">
-        <v>80</v>
+      <c r="G79" s="7">
+        <v>200</v>
+      </c>
+      <c r="H79" s="7">
+        <v>100</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="K79" s="8">
-        <v>0</v>
-      </c>
-      <c r="L79" s="9" t="s">
+      <c r="J79" s="9">
+        <v>10201</v>
+      </c>
+      <c r="K79" s="7">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="2:13">
-      <c r="B80" s="8">
-        <v>321</v>
+    <row r="80" spans="1:12">
+      <c r="B80" s="7">
+        <v>318</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D80" s="8">
+        <v>286</v>
+      </c>
+      <c r="D80" s="7">
         <v>0.2</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="E80" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F80" s="8" t="s">
+      <c r="F80" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="G80" s="8">
-        <v>160</v>
-      </c>
-      <c r="H80" s="8">
-        <v>80</v>
+      <c r="G80" s="7">
+        <v>170</v>
+      </c>
+      <c r="H80" s="7">
+        <v>85</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="K80" s="8">
-        <v>0</v>
-      </c>
-      <c r="L80" s="9" t="s">
+      <c r="J80" s="20">
+        <v>10801</v>
+      </c>
+      <c r="K80" s="7">
+        <v>0</v>
+      </c>
+      <c r="L80" s="8" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="81" spans="2:13">
-      <c r="B81" s="8">
-        <v>322</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D81" s="8">
+    <row r="81" s="2" customFormat="1" spans="2:13">
+      <c r="B81" s="12">
+        <v>319</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D81" s="12">
         <v>0.2</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="F81" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="12">
         <v>160</v>
       </c>
-      <c r="H81" s="8">
+      <c r="H81" s="12">
         <v>80</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="K81" s="8">
-        <v>0</v>
-      </c>
-      <c r="L81" s="9" t="s">
+      <c r="J81" s="12">
+        <v>10402</v>
+      </c>
+      <c r="K81" s="12">
+        <v>0</v>
+      </c>
+      <c r="L81" s="13" t="s">
         <v>362</v>
       </c>
+      <c r="M81" s="14"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="8">
-        <v>323</v>
+      <c r="B82" s="7">
+        <v>320</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D82" s="8">
+        <v>286</v>
+      </c>
+      <c r="D82" s="7">
         <v>0.2</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="F82" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="G82" s="8">
-        <v>190</v>
-      </c>
-      <c r="H82" s="8">
-        <v>95</v>
+      <c r="G82" s="7">
+        <v>160</v>
+      </c>
+      <c r="H82" s="7">
+        <v>80</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="K82" s="8">
-        <v>0</v>
-      </c>
-      <c r="L82" s="9" t="s">
+      <c r="K82" s="7">
+        <v>0</v>
+      </c>
+      <c r="L82" s="8" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="83" s="2" customFormat="1" spans="2:13">
-      <c r="B83" s="13">
-        <v>324</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D83" s="13">
+    <row r="83" spans="2:13">
+      <c r="B83" s="7">
+        <v>321</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D83" s="7">
         <v>0.2</v>
       </c>
-      <c r="E83" s="13" t="s">
+      <c r="E83" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="F83" s="13" t="s">
+      <c r="F83" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="G83" s="13">
-        <v>175</v>
-      </c>
-      <c r="H83" s="13">
-        <v>87</v>
-      </c>
-      <c r="I83" s="2" t="s">
+      <c r="G83" s="7">
+        <v>160</v>
+      </c>
+      <c r="H83" s="7">
+        <v>80</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13">
-        <v>0</v>
-      </c>
-      <c r="L83" s="14" t="s">
+      <c r="K83" s="7">
+        <v>0</v>
+      </c>
+      <c r="L83" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="M83" s="15"/>
     </row>
     <row r="84" spans="2:13">
-      <c r="B84" s="8">
-        <v>325</v>
+      <c r="B84" s="7">
+        <v>322</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D84" s="8">
+        <v>286</v>
+      </c>
+      <c r="D84" s="7">
         <v>0.2</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F84" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="G84" s="8">
-        <v>270</v>
-      </c>
-      <c r="H84" s="8">
-        <v>135</v>
+      <c r="G84" s="7">
+        <v>160</v>
+      </c>
+      <c r="H84" s="7">
+        <v>80</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="J84" s="21">
-        <v>10502</v>
-      </c>
-      <c r="K84" s="8">
-        <v>0</v>
-      </c>
-      <c r="L84" s="9" t="s">
+      <c r="K84" s="7">
+        <v>0</v>
+      </c>
+      <c r="L84" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="85" s="2" customFormat="1" spans="2:13">
-      <c r="B85" s="13">
-        <v>326</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="D85" s="13">
+    <row r="85" spans="2:13">
+      <c r="B85" s="7">
+        <v>323</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D85" s="7">
         <v>0.2</v>
       </c>
-      <c r="E85" s="15" t="s">
+      <c r="E85" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="F85" s="15" t="s">
+      <c r="F85" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="G85" s="13">
-        <v>160</v>
-      </c>
-      <c r="H85" s="13">
-        <v>80</v>
-      </c>
-      <c r="I85" s="2" t="s">
+      <c r="G85" s="7">
+        <v>190</v>
+      </c>
+      <c r="H85" s="7">
+        <v>95</v>
+      </c>
+      <c r="I85" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="J85" s="13"/>
-      <c r="K85" s="13">
-        <v>2</v>
-      </c>
-      <c r="L85" s="14" t="s">
+      <c r="K85" s="7">
+        <v>0</v>
+      </c>
+      <c r="L85" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="M85" s="15"/>
     </row>
     <row r="86" s="2" customFormat="1" spans="2:13">
-      <c r="B86" s="13">
-        <v>327</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="D86" s="13">
+      <c r="B86" s="12">
+        <v>324</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D86" s="12">
         <v>0.2</v>
       </c>
-      <c r="E86" s="15" t="s">
+      <c r="E86" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="F86" s="15" t="s">
+      <c r="F86" s="12" t="s">
         <v>380</v>
       </c>
-      <c r="G86" s="13">
-        <v>200</v>
-      </c>
-      <c r="H86" s="13">
-        <v>100</v>
+      <c r="G86" s="12">
+        <v>175</v>
+      </c>
+      <c r="H86" s="12">
+        <v>87</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="J86" s="21">
+      <c r="J86" s="12"/>
+      <c r="K86" s="12">
+        <v>0</v>
+      </c>
+      <c r="L86" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="M86" s="14"/>
+    </row>
+    <row r="87" spans="2:13">
+      <c r="B87" s="7">
+        <v>325</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D87" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G87" s="7">
+        <v>270</v>
+      </c>
+      <c r="H87" s="7">
+        <v>135</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J87" s="20">
+        <v>10502</v>
+      </c>
+      <c r="K87" s="7">
+        <v>0</v>
+      </c>
+      <c r="L87" s="8" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="88" s="2" customFormat="1" spans="2:13">
+      <c r="B88" s="12">
+        <v>326</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D88" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="F88" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="G88" s="12">
+        <v>160</v>
+      </c>
+      <c r="H88" s="12">
+        <v>80</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J88" s="12"/>
+      <c r="K88" s="12">
+        <v>2</v>
+      </c>
+      <c r="L88" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="M88" s="14"/>
+    </row>
+    <row r="89" s="2" customFormat="1" spans="2:13">
+      <c r="B89" s="12">
+        <v>327</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D89" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="E89" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="G89" s="12">
+        <v>200</v>
+      </c>
+      <c r="H89" s="12">
+        <v>100</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J89" s="20">
         <v>10901</v>
       </c>
-      <c r="K86" s="13">
+      <c r="K89" s="12">
         <v>2</v>
       </c>
-      <c r="L86" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="M86" s="15"/>
-    </row>
-    <row r="87" s="2" customFormat="1" spans="2:13">
-      <c r="B87" s="13">
+      <c r="L89" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="M89" s="14"/>
+    </row>
+    <row r="90" s="2" customFormat="1" spans="2:13">
+      <c r="B90" s="12">
         <v>328</v>
       </c>
-      <c r="C87" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="D87" s="13">
+      <c r="C90" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="D90" s="12">
         <v>0.2</v>
       </c>
-      <c r="E87" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="F87" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="G87" s="13">
+      <c r="E90" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="G90" s="12">
         <v>170</v>
       </c>
-      <c r="H87" s="13">
+      <c r="H90" s="12">
         <v>85</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="J87" s="13"/>
-      <c r="K87" s="13">
+      <c r="I90" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="J90" s="12"/>
+      <c r="K90" s="12">
         <v>1</v>
       </c>
-      <c r="L87" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="M87" s="15"/>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="2:13">
-      <c r="B88" s="8">
+      <c r="L90" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="M90" s="14"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="2:13">
+      <c r="B91" s="7">
         <v>329</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="D88" s="10">
+      <c r="C91" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D91" s="9">
         <v>0.2</v>
       </c>
-      <c r="E88" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="G88" s="10">
+      <c r="E91" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="G91" s="9">
         <v>260</v>
       </c>
-      <c r="H88" s="10">
+      <c r="H91" s="9">
         <v>130</v>
       </c>
-      <c r="I88" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="L88" s="9" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="2:13">
-      <c r="B89" s="8">
+      <c r="I91" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="L91" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="2:13">
+      <c r="B92" s="7">
         <v>330</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="D89" s="10">
+      <c r="C92" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D92" s="9">
         <v>0.2</v>
       </c>
-      <c r="E89" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="G89" s="10">
+      <c r="E92" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="G92" s="9">
         <v>260</v>
       </c>
-      <c r="H89" s="10">
+      <c r="H92" s="9">
         <v>130</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="90" spans="2:13">
-      <c r="B90" s="8">
+      <c r="I92" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="L92" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="93" spans="2:13">
+      <c r="B93" s="7">
         <v>331</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="D90" s="10">
+      <c r="C93" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D93" s="9">
         <v>0.2</v>
       </c>
-      <c r="E90" t="s">
-        <v>396</v>
-      </c>
-      <c r="F90" t="s">
-        <v>397</v>
-      </c>
-      <c r="G90" s="8">
+      <c r="E93" t="s">
+        <v>408</v>
+      </c>
+      <c r="F93" t="s">
+        <v>409</v>
+      </c>
+      <c r="G93" s="7">
         <v>140</v>
       </c>
-      <c r="H90" s="8">
+      <c r="H93" s="7">
         <v>70</v>
       </c>
-      <c r="I90" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="K90" s="8">
+      <c r="I93" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="K93" s="7">
         <v>1</v>
       </c>
-      <c r="L90" s="9" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="91" s="3" customFormat="1" spans="2:13">
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-    </row>
-    <row r="92" s="3" customFormat="1" spans="2:13">
-      <c r="B92" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D92" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E92" s="8">
-        <v>235</v>
-      </c>
-      <c r="F92" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="G92" s="8">
-        <v>650</v>
-      </c>
-      <c r="H92" s="8">
-        <v>325</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="J92" s="8">
-        <v>11001</v>
-      </c>
-      <c r="K92" s="8">
-        <v>0</v>
-      </c>
-      <c r="L92" s="9" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="93" s="3" customFormat="1" spans="2:13">
-      <c r="B93" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D93" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>406</v>
-      </c>
-      <c r="F93" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="G93" s="8">
-        <v>680</v>
-      </c>
-      <c r="H93" s="8">
-        <v>340</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8">
-        <v>0</v>
-      </c>
-      <c r="L93" s="9" t="s">
+      <c r="L93" s="8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="94" s="3" customFormat="1" spans="2:13">
+      <c r="B94" s="7">
+        <v>332</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D94" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F94" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="94" s="3" customFormat="1" spans="2:13">
-      <c r="B94" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D94" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="G94" s="8">
-        <v>600</v>
-      </c>
-      <c r="H94" s="8">
-        <v>300</v>
+      <c r="G94" s="9">
+        <v>260</v>
+      </c>
+      <c r="H94" s="9">
+        <v>130</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="K94" s="8">
+      <c r="J94" s="7"/>
+      <c r="K94" s="7">
         <v>0</v>
       </c>
       <c r="L94" s="8" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="95" s="2" customFormat="1" spans="2:13">
-      <c r="B95" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D95" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="F95" s="13" t="s">
-        <v>417</v>
-      </c>
-      <c r="G95" s="13">
-        <v>480</v>
-      </c>
-      <c r="H95" s="13">
-        <v>240</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J95" s="23">
-        <v>11002</v>
-      </c>
-      <c r="K95" s="13">
-        <v>0</v>
-      </c>
-      <c r="L95" s="14" t="s">
-        <v>419</v>
-      </c>
+    <row r="95" s="3" customFormat="1" spans="2:13">
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="J95" s="7"/>
+      <c r="K95" s="7"/>
+      <c r="L95" s="7"/>
     </row>
     <row r="96" s="3" customFormat="1" spans="2:13">
       <c r="B96" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D96" s="8">
+        <v>416</v>
+      </c>
+      <c r="D96" s="7">
         <v>0.1</v>
       </c>
-      <c r="E96" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="G96" s="8">
-        <v>460</v>
-      </c>
-      <c r="H96" s="8">
-        <v>230</v>
+      <c r="E96" s="7">
+        <v>235</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="G96" s="7">
+        <v>650</v>
+      </c>
+      <c r="H96" s="7">
+        <v>325</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="J96" s="10"/>
-      <c r="K96" s="8">
-        <v>0</v>
-      </c>
-      <c r="L96" s="9" t="s">
-        <v>424</v>
+        <v>418</v>
+      </c>
+      <c r="J96" s="7">
+        <v>11001</v>
+      </c>
+      <c r="K96" s="7">
+        <v>0</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="97" s="3" customFormat="1" spans="2:13">
       <c r="B97" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D97" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G97" s="7">
+        <v>680</v>
+      </c>
+      <c r="H97" s="7">
+        <v>340</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J97" s="7"/>
+      <c r="K97" s="7">
+        <v>0</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="98" s="3" customFormat="1" spans="2:13">
+      <c r="B98" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D97" s="8">
+      <c r="C98" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D98" s="7">
         <v>0.1</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="E98" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="F98" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="G97" s="8">
-        <v>320</v>
-      </c>
-      <c r="H97" s="8">
-        <v>160</v>
-      </c>
-      <c r="I97" s="3" t="s">
+      <c r="G98" s="7">
+        <v>600</v>
+      </c>
+      <c r="H98" s="7">
+        <v>300</v>
+      </c>
+      <c r="I98" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="K97" s="8">
-        <v>0</v>
-      </c>
-      <c r="L97" s="9" t="s">
+      <c r="K98" s="7">
+        <v>0</v>
+      </c>
+      <c r="L98" s="7" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="98" s="2" customFormat="1" spans="2:13">
-      <c r="B98" s="2" t="s">
+    <row r="99" s="2" customFormat="1" spans="2:13">
+      <c r="B99" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D98" s="13">
+      <c r="C99" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D99" s="12">
         <v>0.1</v>
       </c>
-      <c r="E98" s="13" t="s">
+      <c r="E99" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="F98" s="13" t="s">
+      <c r="F99" s="12" t="s">
         <v>432</v>
       </c>
-      <c r="G98" s="13">
-        <v>380</v>
-      </c>
-      <c r="H98" s="13">
-        <v>190</v>
-      </c>
-      <c r="I98" s="2" t="s">
+      <c r="G99" s="12">
+        <v>480</v>
+      </c>
+      <c r="H99" s="12">
+        <v>240</v>
+      </c>
+      <c r="I99" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="J98" s="21">
-        <v>11003</v>
-      </c>
-      <c r="K98" s="13">
-        <v>0</v>
-      </c>
-      <c r="L98" s="14" t="s">
+      <c r="J99" s="12">
+        <v>11002</v>
+      </c>
+      <c r="K99" s="12">
+        <v>0</v>
+      </c>
+      <c r="L99" s="13" t="s">
         <v>434</v>
-      </c>
-    </row>
-    <row r="99" s="3" customFormat="1" spans="2:13">
-      <c r="B99" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D99" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="G99" s="8">
-        <v>600</v>
-      </c>
-      <c r="H99" s="8">
-        <v>300</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="J99" s="10"/>
-      <c r="K99" s="8">
-        <v>0</v>
-      </c>
-      <c r="L99" s="8" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="100" s="3" customFormat="1" spans="2:13">
       <c r="B100" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D100" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="G100" s="7">
+        <v>460</v>
+      </c>
+      <c r="H100" s="7">
+        <v>230</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J100" s="9"/>
+      <c r="K100" s="7">
+        <v>0</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="101" s="3" customFormat="1" spans="2:13">
+      <c r="B101" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D100" s="8">
+      <c r="C101" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D101" s="7">
         <v>0.1</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E101" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F101" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="G100" s="8">
+      <c r="G101" s="7">
+        <v>320</v>
+      </c>
+      <c r="H101" s="7">
+        <v>160</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="K101" s="7">
+        <v>0</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="102" s="2" customFormat="1" spans="2:13">
+      <c r="B102" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D102" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="G102" s="12">
+        <v>380</v>
+      </c>
+      <c r="H102" s="12">
+        <v>190</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J102" s="20">
+        <v>11003</v>
+      </c>
+      <c r="K102" s="12">
+        <v>0</v>
+      </c>
+      <c r="L102" s="13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="103" s="3" customFormat="1" spans="2:13">
+      <c r="B103" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D103" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="G103" s="7">
+        <v>600</v>
+      </c>
+      <c r="H103" s="7">
         <v>300</v>
       </c>
-      <c r="H100" s="8">
+      <c r="I103" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="J103" s="9"/>
+      <c r="K103" s="7">
+        <v>0</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="104" s="3" customFormat="1" spans="2:13">
+      <c r="B104" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D104" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="G104" s="7">
+        <v>300</v>
+      </c>
+      <c r="H104" s="7">
         <v>150</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="K100" s="8">
-        <v>0</v>
-      </c>
-      <c r="L100" s="9" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="101" s="2" customFormat="1" spans="2:13">
-      <c r="B101" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D101" s="13">
+      <c r="I104" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="K104" s="7">
+        <v>0</v>
+      </c>
+      <c r="L104" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" spans="2:13">
+      <c r="B105" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D105" s="12">
         <v>0.1</v>
       </c>
-      <c r="E101" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="F101" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="G101" s="13">
+      <c r="E105" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>462</v>
+      </c>
+      <c r="G105" s="12">
         <v>300</v>
       </c>
-      <c r="H101" s="13">
+      <c r="H105" s="12">
         <v>150</v>
       </c>
-      <c r="I101" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="K101" s="13">
-        <v>0</v>
-      </c>
-      <c r="L101" s="14" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="102" spans="2:13">
-      <c r="B102" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D102" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="G102" s="8">
-        <v>400</v>
-      </c>
-      <c r="H102" s="8">
-        <v>200</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="J102" s="21">
-        <v>11004</v>
-      </c>
-      <c r="K102" s="8">
-        <v>0</v>
-      </c>
-      <c r="L102" s="9" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="103" s="2" customFormat="1" spans="2:13">
-      <c r="B103" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D103" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="F103" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="G103" s="13">
-        <v>460</v>
-      </c>
-      <c r="H103" s="13">
-        <v>230</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="J103" s="13"/>
-      <c r="K103" s="13">
-        <v>0</v>
-      </c>
-      <c r="L103" s="14" t="s">
-        <v>459</v>
-      </c>
-      <c r="M103" s="15"/>
-    </row>
-    <row r="104" spans="2:13">
-      <c r="B104" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D104" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="G104" s="8">
-        <v>340</v>
-      </c>
-      <c r="H104" s="8">
-        <v>170</v>
-      </c>
-      <c r="I104" s="3" t="s">
+      <c r="I105" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="J104" s="8">
-        <v>10602</v>
-      </c>
-      <c r="K104" s="8">
-        <v>0</v>
-      </c>
-      <c r="L104" s="9" t="s">
+      <c r="K105" s="12">
+        <v>0</v>
+      </c>
+      <c r="L105" s="13" t="s">
         <v>464</v>
-      </c>
-    </row>
-    <row r="105" spans="2:13">
-      <c r="B105" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D105" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="F105" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="G105" s="8">
-        <v>280</v>
-      </c>
-      <c r="H105" s="8">
-        <v>140</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8">
-        <v>0</v>
-      </c>
-      <c r="L105" s="9" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="106" spans="2:13">
       <c r="B106" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D106" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="G106" s="7">
+        <v>400</v>
+      </c>
+      <c r="H106" s="7">
+        <v>200</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="J106" s="20">
+        <v>11004</v>
+      </c>
+      <c r="K106" s="7">
+        <v>0</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="107" s="2" customFormat="1" spans="2:13">
+      <c r="B107" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D106" s="8">
+      <c r="C107" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D107" s="12">
         <v>0.1</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E107" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F107" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="G106" s="8">
-        <v>600</v>
-      </c>
-      <c r="H106" s="8">
-        <v>300</v>
-      </c>
-      <c r="I106" s="8" t="s">
+      <c r="G107" s="12">
+        <v>460</v>
+      </c>
+      <c r="H107" s="12">
+        <v>230</v>
+      </c>
+      <c r="I107" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="K106" s="8">
-        <v>0</v>
-      </c>
-      <c r="L106" s="9" t="s">
+      <c r="J107" s="12"/>
+      <c r="K107" s="12">
+        <v>0</v>
+      </c>
+      <c r="L107" s="13" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="107" spans="2:13">
-      <c r="B107" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D107" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E107" t="s">
-        <v>476</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="G107" s="8">
-        <v>280</v>
-      </c>
-      <c r="H107" s="8">
-        <v>140</v>
-      </c>
-      <c r="I107" s="8">
-        <v>40016</v>
-      </c>
-      <c r="J107" s="21">
-        <v>10101</v>
-      </c>
-      <c r="K107" s="8">
-        <v>0</v>
-      </c>
-      <c r="L107" s="8" t="s">
-        <v>478</v>
-      </c>
+      <c r="M107" s="14"/>
     </row>
     <row r="108" spans="2:13">
       <c r="B108" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D108" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="G108" s="7">
+        <v>340</v>
+      </c>
+      <c r="H108" s="7">
+        <v>170</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="J108" s="7">
+        <v>10602</v>
+      </c>
+      <c r="K108" s="7">
+        <v>0</v>
+      </c>
+      <c r="L108" s="8" t="s">
         <v>479</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D108" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E108" t="s">
-        <v>480</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="G108" s="8">
-        <v>300</v>
-      </c>
-      <c r="H108" s="8">
-        <v>150</v>
-      </c>
-      <c r="I108" s="8">
-        <v>40017</v>
-      </c>
-      <c r="K108" s="8">
-        <v>0</v>
-      </c>
-      <c r="L108" s="9" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="109" spans="2:13">
       <c r="B109" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D109" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="G109" s="7">
+        <v>280</v>
+      </c>
+      <c r="H109" s="7">
+        <v>140</v>
+      </c>
+      <c r="I109" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D109" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="K109" s="7">
+        <v>0</v>
+      </c>
+      <c r="L109" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="G109" s="8">
-        <v>520</v>
-      </c>
-      <c r="H109" s="8">
-        <v>260</v>
-      </c>
-      <c r="I109" s="8">
-        <v>40018</v>
-      </c>
-      <c r="J109" s="21">
-        <v>11101</v>
-      </c>
-      <c r="K109" s="8">
-        <v>0</v>
-      </c>
-      <c r="L109" s="9" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="110" spans="2:13">
       <c r="B110" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D110" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E110" t="s">
+        <v>486</v>
+      </c>
+      <c r="F110" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D110" s="8">
+      <c r="G110" s="7">
+        <v>600</v>
+      </c>
+      <c r="H110" s="7">
+        <v>300</v>
+      </c>
+      <c r="I110" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="K110" s="7">
+        <v>0</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13">
+      <c r="B111" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D111" s="7">
         <v>0.1</v>
       </c>
-      <c r="E110" t="s">
-        <v>488</v>
-      </c>
-      <c r="F110" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="G110" s="8">
-        <v>300</v>
-      </c>
-      <c r="H110" s="8">
-        <v>150</v>
-      </c>
-      <c r="I110" s="8">
-        <v>40019</v>
-      </c>
-      <c r="K110" s="8">
-        <v>0</v>
-      </c>
-      <c r="L110" s="9" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="111" s="6" customFormat="1" spans="2:13">
-      <c r="B111" s="6" t="s">
+      <c r="E111" t="s">
         <v>491</v>
       </c>
-      <c r="C111" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="D111" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="E111" s="25" t="s">
+      <c r="F111" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="F111" s="24" t="s">
+      <c r="G111" s="7">
+        <v>280</v>
+      </c>
+      <c r="H111" s="7">
+        <v>140</v>
+      </c>
+      <c r="I111" s="7">
+        <v>40016</v>
+      </c>
+      <c r="J111" s="20">
+        <v>10101</v>
+      </c>
+      <c r="K111" s="7">
+        <v>0</v>
+      </c>
+      <c r="L111" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="G111" s="24">
-        <v>560</v>
-      </c>
-      <c r="H111" s="24">
-        <v>280</v>
-      </c>
-      <c r="I111" s="24">
-        <v>40020</v>
-      </c>
-      <c r="J111" s="22"/>
-      <c r="K111" s="24">
-        <v>0</v>
-      </c>
-      <c r="L111" s="26" t="s">
-        <v>494</v>
-      </c>
-      <c r="M111" s="25"/>
     </row>
     <row r="112" spans="2:13">
       <c r="B112" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D112" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E112" t="s">
         <v>495</v>
       </c>
-      <c r="C112" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D112" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="F112" s="8" t="s">
+      <c r="G112" s="7">
+        <v>300</v>
+      </c>
+      <c r="H112" s="7">
+        <v>150</v>
+      </c>
+      <c r="I112" s="7">
+        <v>40017</v>
+      </c>
+      <c r="K112" s="7">
+        <v>0</v>
+      </c>
+      <c r="L112" s="8" t="s">
         <v>497</v>
-      </c>
-      <c r="G112" s="8">
-        <v>620</v>
-      </c>
-      <c r="H112" s="8">
-        <v>310</v>
-      </c>
-      <c r="I112" s="8">
-        <v>40021</v>
-      </c>
-      <c r="K112" s="8">
-        <v>0</v>
-      </c>
-      <c r="L112" s="9" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="113" spans="1:13">
       <c r="B113" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D113" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E113" t="s">
         <v>499</v>
       </c>
-      <c r="C113" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D113" s="8">
+      <c r="F113" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="G113" s="7">
+        <v>520</v>
+      </c>
+      <c r="H113" s="7">
+        <v>260</v>
+      </c>
+      <c r="I113" s="7">
+        <v>40018</v>
+      </c>
+      <c r="J113" s="20">
+        <v>11101</v>
+      </c>
+      <c r="K113" s="7">
+        <v>0</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13">
+      <c r="B114" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D114" s="7">
         <v>0.1</v>
       </c>
-      <c r="E113" t="s">
-        <v>500</v>
-      </c>
-      <c r="F113" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="G113" s="8">
-        <v>320</v>
-      </c>
-      <c r="H113" s="8">
-        <v>160</v>
-      </c>
-      <c r="I113" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="J113" s="21">
-        <v>11201</v>
-      </c>
-      <c r="K113" s="8">
-        <v>0</v>
-      </c>
-      <c r="L113" s="9" t="s">
+      <c r="E114" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="114" s="2" customFormat="1" spans="1:13">
-      <c r="B114" s="2" t="s">
+      <c r="F114" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D114" s="13">
+      <c r="G114" s="7">
+        <v>300</v>
+      </c>
+      <c r="H114" s="7">
+        <v>150</v>
+      </c>
+      <c r="I114" s="7">
+        <v>40019</v>
+      </c>
+      <c r="K114" s="7">
+        <v>0</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" spans="1:13">
+      <c r="B115" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D115" s="9">
         <v>0.1</v>
       </c>
-      <c r="E114" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="F114" s="13" t="s">
-        <v>506</v>
-      </c>
-      <c r="G114" s="13">
-        <v>320</v>
-      </c>
-      <c r="H114" s="13">
-        <v>160</v>
-      </c>
-      <c r="I114" s="13">
-        <v>40023</v>
-      </c>
-      <c r="J114" s="21">
-        <v>11301</v>
-      </c>
-      <c r="K114" s="13">
-        <v>0</v>
-      </c>
-      <c r="L114" s="14" t="s">
+      <c r="E115" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="M114" s="15"/>
-    </row>
-    <row r="115" spans="1:13">
-      <c r="B115" s="3" t="s">
+      <c r="F115" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D115" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="G115" s="9">
+        <v>560</v>
+      </c>
+      <c r="H115" s="9">
+        <v>280</v>
+      </c>
+      <c r="I115" s="9">
+        <v>40020</v>
+      </c>
+      <c r="J115" s="9"/>
+      <c r="K115" s="9">
+        <v>0</v>
+      </c>
+      <c r="L115" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="F115" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="G115" s="8">
-        <v>550</v>
-      </c>
-      <c r="H115" s="8">
-        <v>275</v>
-      </c>
-      <c r="I115" s="8">
-        <v>40024</v>
-      </c>
-      <c r="J115" s="21">
-        <v>11401</v>
-      </c>
-      <c r="K115" s="8">
-        <v>0</v>
-      </c>
-      <c r="L115" s="8" t="s">
-        <v>511</v>
-      </c>
+      <c r="M115" s="11"/>
     </row>
     <row r="116" spans="1:13">
       <c r="B116" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D116" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E116" t="s">
+        <v>511</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D116" s="8">
+      <c r="G116" s="7">
+        <v>620</v>
+      </c>
+      <c r="H116" s="7">
+        <v>310</v>
+      </c>
+      <c r="I116" s="7">
+        <v>40021</v>
+      </c>
+      <c r="K116" s="7">
+        <v>0</v>
+      </c>
+      <c r="L116" s="8" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13">
+      <c r="B117" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D117" s="7">
         <v>0.1</v>
       </c>
-      <c r="E116" t="s">
-        <v>513</v>
-      </c>
-      <c r="F116" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="G116" s="8">
+      <c r="E117" t="s">
+        <v>515</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="G117" s="7">
+        <v>320</v>
+      </c>
+      <c r="H117" s="7">
+        <v>160</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="J117" s="20">
+        <v>11201</v>
+      </c>
+      <c r="K117" s="7">
+        <v>0</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="118" s="2" customFormat="1" spans="1:13">
+      <c r="B118" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D118" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="E118" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="G118" s="12">
+        <v>320</v>
+      </c>
+      <c r="H118" s="12">
+        <v>160</v>
+      </c>
+      <c r="I118" s="12">
+        <v>40023</v>
+      </c>
+      <c r="J118" s="20">
+        <v>11301</v>
+      </c>
+      <c r="K118" s="12">
+        <v>0</v>
+      </c>
+      <c r="L118" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="M118" s="14"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="B119" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D119" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E119" t="s">
+        <v>524</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="G119" s="7">
+        <v>550</v>
+      </c>
+      <c r="H119" s="7">
+        <v>275</v>
+      </c>
+      <c r="I119" s="7">
+        <v>40024</v>
+      </c>
+      <c r="J119" s="20">
+        <v>11401</v>
+      </c>
+      <c r="K119" s="7">
+        <v>0</v>
+      </c>
+      <c r="L119" s="7" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="B120" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D120" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E120" t="s">
+        <v>528</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="G120" s="7">
         <v>300</v>
       </c>
-      <c r="H116" s="8">
+      <c r="H120" s="7">
         <v>150</v>
       </c>
-      <c r="I116" s="8">
+      <c r="I120" s="7">
         <v>40025</v>
       </c>
-      <c r="K116" s="8">
-        <v>0</v>
-      </c>
-      <c r="L116" s="8" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="117" s="2" customFormat="1" spans="1:13">
-      <c r="B117" s="13">
+      <c r="K120" s="7">
+        <v>0</v>
+      </c>
+      <c r="L120" s="7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="121" s="2" customFormat="1" spans="1:13">
+      <c r="B121" s="12">
         <v>426</v>
       </c>
-      <c r="C117" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D117" s="13">
+      <c r="C121" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="D121" s="12">
         <v>0.1</v>
       </c>
-      <c r="E117" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="F117" s="15" t="s">
-        <v>517</v>
-      </c>
-      <c r="G117" s="13">
+      <c r="E121" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="G121" s="12">
         <v>400</v>
       </c>
-      <c r="H117" s="13">
+      <c r="H121" s="12">
         <v>200</v>
       </c>
-      <c r="I117" s="13">
+      <c r="I121" s="12">
         <v>40026</v>
       </c>
-      <c r="J117" s="21">
+      <c r="J121" s="20">
         <v>11501</v>
       </c>
-      <c r="K117" s="13">
+      <c r="K121" s="12">
         <v>1</v>
       </c>
-      <c r="L117" s="14" t="s">
-        <v>518</v>
-      </c>
-      <c r="M117" s="15"/>
-    </row>
-    <row r="118" spans="1:13">
-      <c r="B118" s="8">
+      <c r="L121" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="M121" s="14"/>
+    </row>
+    <row r="122" spans="1:13">
+      <c r="B122" s="7">
         <v>427</v>
       </c>
-      <c r="C118" t="s">
-        <v>401</v>
-      </c>
-      <c r="D118" s="8">
+      <c r="C122" t="s">
+        <v>416</v>
+      </c>
+      <c r="D122" s="7">
         <v>0.1</v>
       </c>
-      <c r="E118" t="s">
-        <v>519</v>
-      </c>
-      <c r="F118" t="s">
-        <v>520</v>
-      </c>
-      <c r="G118" s="8">
+      <c r="E122" t="s">
+        <v>534</v>
+      </c>
+      <c r="F122" t="s">
+        <v>535</v>
+      </c>
+      <c r="G122" s="7">
         <v>330</v>
       </c>
-      <c r="H118" s="8">
+      <c r="H122" s="7">
         <v>165</v>
       </c>
-      <c r="I118" s="8">
+      <c r="I122" s="7">
         <v>40027</v>
       </c>
-      <c r="K118" s="8">
+      <c r="K122" s="7">
         <v>1</v>
       </c>
-      <c r="L118" s="9" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="119" s="2" customFormat="1" spans="1:13">
-      <c r="B119" s="13">
+      <c r="L122" s="8" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="123" s="2" customFormat="1" spans="1:13">
+      <c r="B123" s="12">
         <v>428</v>
       </c>
-      <c r="C119" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D119" s="13">
+      <c r="C123" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="D123" s="12">
         <v>0.1</v>
       </c>
-      <c r="E119" s="15" t="s">
-        <v>522</v>
-      </c>
-      <c r="F119" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="G119" s="13">
+      <c r="E123" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>538</v>
+      </c>
+      <c r="G123" s="12">
         <v>260</v>
       </c>
-      <c r="H119" s="13">
+      <c r="H123" s="12">
         <v>130</v>
       </c>
-      <c r="I119" s="13">
+      <c r="I123" s="12">
         <v>40028</v>
       </c>
-      <c r="J119" s="13"/>
-      <c r="K119" s="13">
+      <c r="J123" s="12"/>
+      <c r="K123" s="12">
         <v>2</v>
       </c>
-      <c r="L119" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="M119" s="15"/>
-    </row>
-    <row r="120" s="2" customFormat="1" spans="1:13">
-      <c r="B120" s="13">
+      <c r="L123" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="M123" s="14"/>
+    </row>
+    <row r="124" s="2" customFormat="1" spans="1:13">
+      <c r="B124" s="12">
         <v>429</v>
       </c>
-      <c r="C120" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D120" s="13">
+      <c r="C124" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="D124" s="12">
         <v>0.1</v>
       </c>
-      <c r="E120" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="F120" s="15" t="s">
-        <v>526</v>
-      </c>
-      <c r="G120" s="13">
+      <c r="E124" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="G124" s="12">
         <v>270</v>
       </c>
-      <c r="H120" s="13">
+      <c r="H124" s="12">
         <v>135</v>
       </c>
-      <c r="I120" s="13">
+      <c r="I124" s="12">
         <v>40029</v>
       </c>
-      <c r="J120" s="13"/>
-      <c r="K120" s="13">
+      <c r="J124" s="12"/>
+      <c r="K124" s="12">
         <v>2</v>
       </c>
-      <c r="L120" s="14" t="s">
-        <v>527</v>
-      </c>
-      <c r="M120" s="15"/>
-    </row>
-    <row r="121" s="2" customFormat="1" spans="1:13">
-      <c r="B121" s="13">
+      <c r="L124" s="13" t="s">
+        <v>542</v>
+      </c>
+      <c r="M124" s="14"/>
+    </row>
+    <row r="125" s="2" customFormat="1" spans="1:13">
+      <c r="B125" s="12">
         <v>430</v>
       </c>
-      <c r="C121" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D121" s="13">
+      <c r="C125" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="D125" s="12">
         <v>0.1</v>
       </c>
-      <c r="E121" s="15" t="s">
-        <v>528</v>
-      </c>
-      <c r="F121" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="G121" s="13">
+      <c r="E125" s="14" t="s">
+        <v>543</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>544</v>
+      </c>
+      <c r="G125" s="12">
         <v>280</v>
       </c>
-      <c r="H121" s="13">
+      <c r="H125" s="12">
         <v>140</v>
       </c>
-      <c r="I121" s="13">
+      <c r="I125" s="12">
         <v>40030</v>
       </c>
-      <c r="J121" s="21">
+      <c r="J125" s="20">
         <v>11601</v>
       </c>
-      <c r="K121" s="13">
-        <v>0</v>
-      </c>
-      <c r="L121" s="14" t="s">
-        <v>530</v>
-      </c>
-      <c r="M121" s="15"/>
-    </row>
-    <row r="122" s="2" customFormat="1" spans="1:13">
-      <c r="A122" s="15"/>
-      <c r="B122" s="13">
+      <c r="K125" s="12">
+        <v>0</v>
+      </c>
+      <c r="L125" s="13" t="s">
+        <v>545</v>
+      </c>
+      <c r="M125" s="14"/>
+    </row>
+    <row r="126" s="2" customFormat="1" spans="1:13">
+      <c r="A126" s="14"/>
+      <c r="B126" s="12">
         <v>431</v>
       </c>
-      <c r="C122" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="D122" s="13">
+      <c r="C126" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="D126" s="12">
         <v>0.1</v>
       </c>
-      <c r="E122" s="13" t="s">
-        <v>531</v>
-      </c>
-      <c r="F122" s="13" t="s">
-        <v>532</v>
-      </c>
-      <c r="G122" s="2">
+      <c r="E126" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="G126" s="2">
         <v>130</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H126" s="2">
         <v>65</v>
       </c>
-      <c r="I122" s="13">
+      <c r="I126" s="12">
         <v>40031</v>
       </c>
-      <c r="J122" s="13"/>
-      <c r="K122" s="13">
-        <v>0</v>
-      </c>
-      <c r="L122" s="14" t="s">
-        <v>533</v>
-      </c>
-      <c r="M122" s="15"/>
+      <c r="J126" s="12"/>
+      <c r="K126" s="12">
+        <v>0</v>
+      </c>
+      <c r="L126" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="M126" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13170" windowHeight="11550"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -2312,7 +2312,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2372,6 +2372,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4611,7 +4614,7 @@
       </c>
       <c r="M57" s="11"/>
     </row>
-    <row r="58" ht="14.25" spans="1:13">
+    <row r="58" spans="1:13">
       <c r="B58" s="1" t="s">
         <v>269</v>
       </c>
@@ -5795,36 +5798,38 @@
         <v>411</v>
       </c>
     </row>
-    <row r="94" s="3" customFormat="1" spans="2:13">
-      <c r="B94" s="7">
+    <row r="94" s="2" customFormat="1" spans="2:13">
+      <c r="B94" s="12">
         <v>332</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="12">
         <v>0.2</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94" s="12">
         <v>260</v>
       </c>
-      <c r="H94" s="9">
+      <c r="H94" s="12">
         <v>130</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="I94" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="J94" s="7"/>
-      <c r="K94" s="7">
-        <v>0</v>
-      </c>
-      <c r="L94" s="8" t="s">
+      <c r="J94" s="21">
+        <v>11005</v>
+      </c>
+      <c r="K94" s="12">
+        <v>0</v>
+      </c>
+      <c r="L94" s="13" t="s">
         <v>414</v>
       </c>
     </row>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="16590" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -388,7 +388,7 @@
     <t>20001</t>
   </si>
   <si>
-    <t>亮出的每张方片牌在结算时提供+1倍率</t>
+    <t>亮出的每张方片牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>202</t>
@@ -403,7 +403,7 @@
     <t>20002</t>
   </si>
   <si>
-    <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
+    <t>亮出的每张黑桃牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>203</t>
@@ -418,7 +418,7 @@
     <t>20003</t>
   </si>
   <si>
-    <t>亮出的每张红心牌在结算时提供+1倍率</t>
+    <t>亮出的每张红心牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>204</t>
@@ -433,7 +433,7 @@
     <t>20004</t>
   </si>
   <si>
-    <t>亮出的每张梅花牌在结算时提供+1倍率</t>
+    <t>亮出的每张梅花牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>205</t>
@@ -553,7 +553,7 @@
     <t>20012</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+3倍率</t>
+    <t>亮出的每张人头牌在结算时提供+2倍率</t>
   </si>
   <si>
     <t>213</t>
@@ -838,7 +838,7 @@
     <t>20031</t>
   </si>
   <si>
-    <t>使用后,同花牌型提供的倍率永久+1</t>
+    <t>使用后,同花牌型提供的倍率永久+2</t>
   </si>
   <si>
     <t>232</t>
@@ -853,7 +853,7 @@
     <t>20032</t>
   </si>
   <si>
-    <t>使用后,顺子牌型提供的倍率永久+1</t>
+    <t>使用后,顺子牌型提供的倍率永久+2</t>
   </si>
   <si>
     <t>233</t>
@@ -928,7 +928,7 @@
     <t>30003</t>
   </si>
   <si>
-    <t>结算伤害时,将留在手牌上最大的牌点数×4转化为额外攻击力</t>
+    <t>结算伤害时,将留在手牌上最大的牌点数×2转化为额外攻击力</t>
   </si>
   <si>
     <t>搓牌能手</t>
@@ -976,7 +976,7 @@
     <t>30007</t>
   </si>
   <si>
-    <t>亮出的每张8在结算时提供+50攻击力</t>
+    <t>亮出的每张8在结算时提供+100攻击力</t>
   </si>
   <si>
     <t>偶数韵律</t>
@@ -988,7 +988,7 @@
     <t>30008</t>
   </si>
   <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+4倍率</t>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>奇数韵律</t>
@@ -1000,7 +1000,7 @@
     <t>30009</t>
   </si>
   <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+4倍率</t>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
   </si>
   <si>
     <t>贵族</t>
@@ -1012,7 +1012,7 @@
     <t>30010</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+5倍率</t>
+    <t>亮出的每张人头牌在结算时提供+4倍率</t>
   </si>
   <si>
     <t>工资卡</t>
@@ -1024,7 +1024,7 @@
     <t>30011</t>
   </si>
   <si>
-    <t>每击杀1名敌人,就会获得50金币</t>
+    <t>每击杀1名敌人,这件圣物的出售价格+10金币</t>
   </si>
   <si>
     <t>训练</t>
@@ -1366,7 +1366,7 @@
     <t>40006</t>
   </si>
   <si>
-    <t>每拥有1个圣物,结算时提供+3倍率</t>
+    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
   </si>
   <si>
     <t>407</t>
@@ -1411,7 +1411,7 @@
     <t>40009|400091</t>
   </si>
   <si>
-    <t>亮出的每张A在结算伤害时提供+50攻击力和+8倍率</t>
+    <t>亮出的每张A在结算伤害时提供+66攻击力和+6倍率</t>
   </si>
   <si>
     <t>410</t>
@@ -1486,7 +1486,7 @@
     <t>40014|400141|400142</t>
   </si>
   <si>
-    <t>亮出的每张7结算时有概率提供+77攻击力和+7倍率</t>
+    <t>亮出的每张7结算时必定提供+77攻击力和+7倍率</t>
   </si>
   <si>
     <t>415</t>
@@ -1678,7 +1678,7 @@
     <t>Flag</t>
   </si>
   <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+5攻击力</t>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
   </si>
 </sst>
 </file>
@@ -2312,17 +2312,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2331,27 +2328,15 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2368,13 +2353,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2728,8 +2716,8 @@
   <dimension ref="A1:M126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="2.93333333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.8" style="6" customWidth="1"/>
     <col min="4" max="4" width="4.78333333333333" style="7" customWidth="1"/>
     <col min="5" max="5" width="8.8" style="7" customWidth="1"/>
@@ -2738,17 +2726,17 @@
     <col min="8" max="8" width="4.78333333333333" style="7" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="7" customWidth="1"/>
     <col min="10" max="10" width="5.53333333333333" style="7" customWidth="1"/>
-    <col min="11" max="11" width="8.03333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.03333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="7.70833333333333" style="7" customWidth="1"/>
-    <col min="14" max="14" width="34.75" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -2783,10 +2771,10 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
@@ -2821,10 +2809,10 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -2859,10 +2847,10 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D5" s="7">
@@ -2886,7 +2874,7 @@
       <c r="K5" s="7">
         <v>0</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2897,32 +2885,32 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="7">
         <v>0.8</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="7">
         <v>28</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <v>14</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="7">
         <v>10002</v>
       </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9">
-        <v>0</v>
-      </c>
-      <c r="L6" s="10" t="s">
+      <c r="J6" s="7"/>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="11"/>
+      <c r="M6"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:13">
       <c r="B7" s="1" t="s">
@@ -2931,32 +2919,32 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="7">
         <v>0.8</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="7">
         <v>28</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="7">
         <v>14</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="7">
         <v>10003</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="J7" s="7"/>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="11"/>
+      <c r="M7"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:13">
       <c r="B8" s="1" t="s">
@@ -2965,32 +2953,32 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="7">
         <v>0.8</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="7">
         <v>28</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="7">
         <v>14</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
         <v>10004</v>
       </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10" t="s">
+      <c r="J8" s="7"/>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="11"/>
+      <c r="M8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:13">
       <c r="B9" s="1" t="s">
@@ -2999,32 +2987,32 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="7">
         <v>0.8</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="7">
         <v>28</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="7">
         <v>14</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="7">
         <v>10005</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="10" t="s">
+      <c r="J9" s="7"/>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="11"/>
+      <c r="M9"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:13">
       <c r="B10" s="1" t="s">
@@ -3033,32 +3021,32 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="7">
         <v>0.8</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="7">
         <v>28</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="7">
         <v>14</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="7">
         <v>10006</v>
       </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10" t="s">
+      <c r="J10" s="7"/>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="11"/>
+      <c r="M10"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:13">
       <c r="B11" s="1" t="s">
@@ -3067,32 +3055,32 @@
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="7">
         <v>0.8</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="7">
         <v>22</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="7">
         <v>11</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="7">
         <v>10007</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="10" t="s">
+      <c r="J11" s="7"/>
+      <c r="K11" s="7">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="11"/>
+      <c r="M11"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:13">
       <c r="B12" s="1" t="s">
@@ -3101,32 +3089,32 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="7">
         <v>0.8</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="7">
         <v>35</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="7">
         <v>17</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="7">
         <v>10008</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="10" t="s">
+      <c r="J12" s="7"/>
+      <c r="K12" s="7">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:13">
       <c r="B13" s="1" t="s">
@@ -3135,32 +3123,32 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="7">
         <v>0.8</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="7">
         <v>16</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="7">
         <v>8</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="7">
         <v>10009</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="10" t="s">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
         <v>64</v>
       </c>
-      <c r="M13" s="11"/>
+      <c r="M13"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:13">
       <c r="B14" s="1" t="s">
@@ -3169,32 +3157,32 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="7">
         <v>0.8</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="7">
         <v>16</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <v>8</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="7">
         <v>10010</v>
       </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="10" t="s">
+      <c r="J14" s="7"/>
+      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="11"/>
+      <c r="M14"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:13">
       <c r="B15" s="2" t="s">
@@ -3203,38 +3191,38 @@
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="8">
         <v>0.8</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="8">
         <v>15</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="8">
         <v>7</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="8">
         <v>10011</v>
       </c>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13" t="s">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="14"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:13">
-      <c r="B16" s="3" t="s">
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:13">
+      <c r="B16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="7">
@@ -3259,15 +3247,15 @@
       <c r="K16" s="7">
         <v>0</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:13">
-      <c r="B17" s="3" t="s">
+    <row r="17" s="1" customFormat="1" spans="1:13">
+      <c r="B17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="7">
@@ -3292,15 +3280,15 @@
       <c r="K17" s="7">
         <v>0</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="L17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:13">
-      <c r="B18" s="3" t="s">
+    <row r="18" s="1" customFormat="1" spans="1:13">
+      <c r="B18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="7">
@@ -3325,15 +3313,15 @@
       <c r="K18" s="7">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="L18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="19" s="3" customFormat="1" spans="1:13">
-      <c r="B19" s="3" t="s">
+    <row r="19" s="1" customFormat="1" spans="1:13">
+      <c r="B19" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D19" s="7">
@@ -3358,7 +3346,7 @@
       <c r="K19" s="7">
         <v>0</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="L19" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3369,29 +3357,29 @@
       <c r="C20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="8">
         <v>0.8</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="8">
         <v>28</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="8">
         <v>14</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="8">
         <v>10016</v>
       </c>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13" t="s">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3402,34 +3390,34 @@
       <c r="C21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="8">
         <v>0.8</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="8">
         <v>20</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="8">
         <v>10</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="8">
         <v>10017</v>
       </c>
-      <c r="J21" s="12"/>
-      <c r="K21" s="12">
-        <v>0</v>
-      </c>
-      <c r="L21" s="13" t="s">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:13">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>97</v>
       </c>
       <c r="C22" t="s">
@@ -3456,12 +3444,12 @@
       <c r="K22" s="7">
         <v>1</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="L22" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:13">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C23" t="s">
@@ -3488,7 +3476,7 @@
       <c r="K23" s="7">
         <v>1</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="L23" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3496,38 +3484,38 @@
       <c r="B24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="8">
         <v>0.8</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="8">
         <v>30</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="8">
         <v>15</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="8">
         <v>10020</v>
       </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12">
-        <v>0</v>
-      </c>
-      <c r="L24" s="13" t="s">
+      <c r="J24" s="8"/>
+      <c r="K24" s="8">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="14"/>
+      <c r="M24" s="9"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C25" t="s">
@@ -3543,10 +3531,10 @@
         <v>111</v>
       </c>
       <c r="G25" s="7">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="H25" s="7">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I25" s="7">
         <v>10021</v>
@@ -3554,15 +3542,15 @@
       <c r="K25" s="7">
         <v>2</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="L25" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:13">
-      <c r="C26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="C26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
       <c r="K26" s="7"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
@@ -3572,13 +3560,13 @@
       <c r="C27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="7">
         <v>0.4</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="7" t="s">
         <v>116</v>
       </c>
       <c r="G27" s="1">
@@ -3590,14 +3578,14 @@
       <c r="I27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9">
-        <v>0</v>
-      </c>
-      <c r="L27" s="10" t="s">
+      <c r="J27" s="7"/>
+      <c r="K27" s="7">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
         <v>118</v>
       </c>
-      <c r="M27" s="11"/>
+      <c r="M27"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:13">
       <c r="B28" s="1" t="s">
@@ -3606,13 +3594,13 @@
       <c r="C28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="7">
         <v>0.4</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="7" t="s">
         <v>121</v>
       </c>
       <c r="G28" s="1">
@@ -3624,30 +3612,30 @@
       <c r="I28" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9">
-        <v>0</v>
-      </c>
-      <c r="L28" s="10" t="s">
+      <c r="J28" s="7"/>
+      <c r="K28" s="7">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
         <v>123</v>
       </c>
-      <c r="M28" s="11"/>
+      <c r="M28"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="11"/>
+      <c r="A29"/>
       <c r="B29" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="7">
         <v>0.4</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="7" t="s">
         <v>126</v>
       </c>
       <c r="G29" s="1">
@@ -3659,30 +3647,30 @@
       <c r="I29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9">
-        <v>0</v>
-      </c>
-      <c r="L29" s="10" t="s">
+      <c r="J29" s="7"/>
+      <c r="K29" s="7">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
         <v>128</v>
       </c>
-      <c r="M29" s="11"/>
+      <c r="M29"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:13">
-      <c r="A30" s="11"/>
+      <c r="A30"/>
       <c r="B30" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="7">
         <v>0.4</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="7" t="s">
         <v>131</v>
       </c>
       <c r="G30" s="1">
@@ -3694,30 +3682,30 @@
       <c r="I30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9">
-        <v>0</v>
-      </c>
-      <c r="L30" s="10" t="s">
+      <c r="J30" s="7"/>
+      <c r="K30" s="7">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
         <v>133</v>
       </c>
-      <c r="M30" s="11"/>
+      <c r="M30"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:13">
-      <c r="A31" s="11"/>
+      <c r="A31"/>
       <c r="B31" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="7">
         <v>0.4</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="7" t="s">
         <v>136</v>
       </c>
       <c r="G31" s="1">
@@ -3729,30 +3717,30 @@
       <c r="I31" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9">
-        <v>0</v>
-      </c>
-      <c r="L31" s="10" t="s">
+      <c r="J31" s="7"/>
+      <c r="K31" s="7">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
         <v>138</v>
       </c>
-      <c r="M31" s="11"/>
+      <c r="M31"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:13">
-      <c r="A32" s="11"/>
+      <c r="A32"/>
       <c r="B32" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="7">
         <v>0.4</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="7" t="s">
         <v>141</v>
       </c>
       <c r="G32" s="1">
@@ -3764,30 +3752,30 @@
       <c r="I32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9">
-        <v>0</v>
-      </c>
-      <c r="L32" s="10" t="s">
+      <c r="J32" s="7"/>
+      <c r="K32" s="7">
+        <v>0</v>
+      </c>
+      <c r="L32" t="s">
         <v>143</v>
       </c>
-      <c r="M32" s="11"/>
+      <c r="M32"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="11"/>
+      <c r="A33"/>
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="7">
         <v>0.4</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="7" t="s">
         <v>146</v>
       </c>
       <c r="G33" s="1">
@@ -3799,30 +3787,30 @@
       <c r="I33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9">
-        <v>0</v>
-      </c>
-      <c r="L33" s="10" t="s">
+      <c r="J33" s="7"/>
+      <c r="K33" s="7">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
         <v>148</v>
       </c>
-      <c r="M33" s="11"/>
+      <c r="M33"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:13">
-      <c r="A34" s="11"/>
+      <c r="A34"/>
       <c r="B34" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="7">
         <v>0.4</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="7" t="s">
         <v>151</v>
       </c>
       <c r="G34" s="1">
@@ -3834,30 +3822,30 @@
       <c r="I34" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9">
-        <v>0</v>
-      </c>
-      <c r="L34" s="10" t="s">
+      <c r="J34" s="7"/>
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
         <v>153</v>
       </c>
-      <c r="M34" s="11"/>
+      <c r="M34"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="11"/>
+      <c r="A35"/>
       <c r="B35" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="7">
         <v>0.4</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="7" t="s">
         <v>156</v>
       </c>
       <c r="G35" s="1">
@@ -3869,56 +3857,56 @@
       <c r="I35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9">
-        <v>0</v>
-      </c>
-      <c r="L35" s="10" t="s">
+      <c r="J35" s="7"/>
+      <c r="K35" s="7">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
         <v>158</v>
       </c>
-      <c r="M35" s="11"/>
-    </row>
-    <row r="36" s="4" customFormat="1" spans="1:13">
-      <c r="A36" s="15"/>
+      <c r="M35"/>
+    </row>
+    <row r="36" s="3" customFormat="1" spans="1:13">
+      <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="11">
         <v>0.4</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G36" s="3">
         <v>110</v>
       </c>
-      <c r="H36" s="4">
+      <c r="H36" s="3">
         <v>55</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="s">
+      <c r="J36" s="11"/>
+      <c r="K36" s="11">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
         <v>163</v>
       </c>
-      <c r="M36" s="15"/>
+      <c r="M36" s="10"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37"/>
       <c r="B37" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D37" s="7">
@@ -3930,13 +3918,13 @@
       <c r="F37" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="1">
         <v>80</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="1">
         <v>40</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="1" t="s">
         <v>167</v>
       </c>
       <c r="K37" s="7">
@@ -3946,47 +3934,47 @@
         <v>168</v>
       </c>
     </row>
-    <row r="38" s="5" customFormat="1" spans="1:13">
-      <c r="A38" s="17"/>
+    <row r="38" s="4" customFormat="1" spans="1:13">
+      <c r="A38" s="12"/>
       <c r="B38" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="18">
+      <c r="D38" s="13">
         <v>0.4</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="F38" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="4">
         <v>135</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="4">
         <v>67</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18">
-        <v>0</v>
-      </c>
-      <c r="L38" s="19" t="s">
+      <c r="J38" s="13"/>
+      <c r="K38" s="13">
+        <v>0</v>
+      </c>
+      <c r="L38" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="M38" s="17"/>
+      <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39"/>
       <c r="B39" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D39" s="7">
@@ -3998,28 +3986,28 @@
       <c r="F39" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="1">
         <v>70</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="1">
         <v>35</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="1" t="s">
         <v>177</v>
       </c>
       <c r="K39" s="7">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="s">
+      <c r="L39" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="40" s="3" customFormat="1" spans="1:13">
+    <row r="40" s="1" customFormat="1" spans="1:13">
       <c r="A40"/>
       <c r="B40" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D40" s="7">
@@ -4031,28 +4019,28 @@
       <c r="F40" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="1">
         <v>110</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="1">
         <v>55</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="1" t="s">
         <v>182</v>
       </c>
       <c r="K40" s="7">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="s">
+      <c r="L40" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="41" s="3" customFormat="1" spans="1:13">
+    <row r="41" s="1" customFormat="1" spans="1:13">
       <c r="A41"/>
       <c r="B41" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D41" s="7">
@@ -4064,28 +4052,28 @@
       <c r="F41" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="1">
         <v>110</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="1">
         <v>55</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="1" t="s">
         <v>187</v>
       </c>
       <c r="K41" s="7">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="s">
+      <c r="L41" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="42" s="3" customFormat="1" spans="1:13">
+    <row r="42" s="1" customFormat="1" spans="1:13">
       <c r="A42"/>
       <c r="B42" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D42" s="7">
@@ -4097,28 +4085,28 @@
       <c r="F42" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="1">
         <v>115</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="1">
         <v>57</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="1" t="s">
         <v>192</v>
       </c>
       <c r="K42" s="7">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="s">
+      <c r="L42" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="43" s="3" customFormat="1" spans="1:13">
+    <row r="43" s="1" customFormat="1" spans="1:13">
       <c r="A43"/>
       <c r="B43" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D43" s="7">
@@ -4130,28 +4118,28 @@
       <c r="F43" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="1">
         <v>80</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="1">
         <v>40</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="1" t="s">
         <v>197</v>
       </c>
       <c r="K43" s="7">
         <v>0</v>
       </c>
-      <c r="L43" s="8" t="s">
+      <c r="L43" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="44" s="3" customFormat="1" spans="1:13">
+    <row r="44" s="1" customFormat="1" spans="1:13">
       <c r="A44"/>
       <c r="B44" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D44" s="7">
@@ -4169,7 +4157,7 @@
       <c r="H44" s="7">
         <v>42</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="1" t="s">
         <v>202</v>
       </c>
       <c r="J44" s="7"/>
@@ -4181,79 +4169,79 @@
       </c>
     </row>
     <row r="45" s="2" customFormat="1" spans="1:13">
-      <c r="A45" s="14"/>
+      <c r="A45" s="9"/>
       <c r="B45" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" s="8">
         <v>0.4</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="8">
         <v>75</v>
       </c>
-      <c r="H45" s="12">
+      <c r="H45" s="8">
         <v>37</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J45" s="12"/>
-      <c r="K45" s="12">
-        <v>0</v>
-      </c>
-      <c r="L45" s="13" t="s">
+      <c r="J45" s="8"/>
+      <c r="K45" s="8">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="1:13">
-      <c r="A46" s="14"/>
+      <c r="A46" s="9"/>
       <c r="B46" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" s="8">
         <v>0.4</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="8">
         <v>75</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="8">
         <v>37</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12">
-        <v>0</v>
-      </c>
-      <c r="L46" s="13" t="s">
+      <c r="J46" s="8"/>
+      <c r="K46" s="8">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="47" s="3" customFormat="1" spans="1:13">
+    <row r="47" s="1" customFormat="1" spans="1:13">
       <c r="A47"/>
       <c r="B47" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D47" s="7">
@@ -4271,23 +4259,23 @@
       <c r="H47" s="7">
         <v>35</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="1" t="s">
         <v>217</v>
       </c>
       <c r="J47" s="7"/>
       <c r="K47" s="7">
         <v>0</v>
       </c>
-      <c r="L47" s="8" t="s">
+      <c r="L47" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="48" s="3" customFormat="1" spans="1:13">
+    <row r="48" s="1" customFormat="1" spans="1:13">
       <c r="A48"/>
       <c r="B48" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D48" s="7">
@@ -4305,14 +4293,14 @@
       <c r="H48" s="7">
         <v>37</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I48" s="1" t="s">
         <v>222</v>
       </c>
       <c r="J48" s="7"/>
       <c r="K48" s="7">
         <v>0</v>
       </c>
-      <c r="L48" s="8" t="s">
+      <c r="L48" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4320,7 +4308,7 @@
       <c r="B49" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D49" s="7">
@@ -4338,7 +4326,7 @@
       <c r="H49" s="7">
         <v>45</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="1" t="s">
         <v>227</v>
       </c>
       <c r="J49" s="7">
@@ -4356,7 +4344,7 @@
       <c r="B50" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D50" s="7">
@@ -4374,7 +4362,7 @@
       <c r="H50" s="7">
         <v>60</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="1" t="s">
         <v>232</v>
       </c>
       <c r="K50" s="7">
@@ -4389,7 +4377,7 @@
       <c r="B51" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D51" s="7">
@@ -4407,50 +4395,50 @@
       <c r="H51" s="7">
         <v>55</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="1" t="s">
         <v>237</v>
       </c>
       <c r="K51" s="7">
         <v>0</v>
       </c>
-      <c r="L51" s="8" t="s">
+      <c r="L51" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:13">
-      <c r="A52" s="14"/>
+      <c r="A52" s="9"/>
       <c r="B52" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="8">
         <v>0.4</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G52" s="8">
         <v>70</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H52" s="8">
         <v>35</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12">
-        <v>0</v>
-      </c>
-      <c r="L52" s="13" t="s">
+      <c r="J52" s="8"/>
+      <c r="K52" s="8">
+        <v>0</v>
+      </c>
+      <c r="L52" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="M52" s="14"/>
+      <c r="M52" s="9"/>
     </row>
     <row r="53" spans="1:13">
       <c r="B53" s="1" t="s">
@@ -4474,13 +4462,13 @@
       <c r="H53" s="7">
         <v>45</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="I53" s="1" t="s">
         <v>247</v>
       </c>
       <c r="K53" s="7">
         <v>1</v>
       </c>
-      <c r="L53" s="8" t="s">
+      <c r="L53" t="s">
         <v>248</v>
       </c>
     </row>
@@ -4506,13 +4494,13 @@
       <c r="H54" s="7">
         <v>72</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="1" t="s">
         <v>252</v>
       </c>
       <c r="K54" s="7">
         <v>1</v>
       </c>
-      <c r="L54" s="8" t="s">
+      <c r="L54" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4538,13 +4526,13 @@
       <c r="H55" s="7">
         <v>37</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="I55" s="1" t="s">
         <v>257</v>
       </c>
       <c r="K55" s="7">
         <v>0</v>
       </c>
-      <c r="L55" s="8" t="s">
+      <c r="L55" t="s">
         <v>258</v>
       </c>
     </row>
@@ -4570,13 +4558,13 @@
       <c r="H56" s="7">
         <v>55</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="I56" s="1" t="s">
         <v>262</v>
       </c>
       <c r="K56" s="7">
         <v>1</v>
       </c>
-      <c r="L56" s="8" t="s">
+      <c r="L56" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4584,35 +4572,35 @@
       <c r="B57" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="7">
         <v>0.4</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" t="s">
         <v>265</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="9">
-        <v>190</v>
-      </c>
-      <c r="H57" s="9">
-        <v>95</v>
-      </c>
-      <c r="I57" s="3" t="s">
+      <c r="G57" s="7">
+        <v>160</v>
+      </c>
+      <c r="H57" s="7">
+        <v>80</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9">
+      <c r="J57" s="7"/>
+      <c r="K57" s="7">
         <v>2</v>
       </c>
-      <c r="L57" s="10" t="s">
+      <c r="L57" t="s">
         <v>268</v>
       </c>
-      <c r="M57" s="11"/>
+      <c r="M57"/>
     </row>
     <row r="58" spans="1:13">
       <c r="B58" s="1" t="s">
@@ -4630,13 +4618,13 @@
       <c r="F58" t="s">
         <v>271</v>
       </c>
-      <c r="G58" s="9">
-        <v>190</v>
-      </c>
-      <c r="H58" s="9">
-        <v>95</v>
-      </c>
-      <c r="I58" s="3" t="s">
+      <c r="G58" s="7">
+        <v>160</v>
+      </c>
+      <c r="H58" s="7">
+        <v>80</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>272</v>
       </c>
       <c r="K58" s="7">
@@ -4646,107 +4634,107 @@
         <v>273</v>
       </c>
     </row>
-    <row r="59" s="2" customFormat="1" spans="1:13">
+    <row r="59" s="5" customFormat="1" spans="1:13">
       <c r="A59" s="14"/>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="5" t="s">
         <v>274</v>
       </c>
       <c r="C59" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="15">
         <v>0.4</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="15" t="s">
         <v>275</v>
       </c>
       <c r="F59" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G59" s="12">
-        <v>190</v>
-      </c>
-      <c r="H59" s="12">
-        <v>95</v>
-      </c>
-      <c r="I59" s="2" t="s">
+      <c r="G59" s="15">
+        <v>80</v>
+      </c>
+      <c r="H59" s="15">
+        <v>40</v>
+      </c>
+      <c r="I59" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="J59" s="12"/>
-      <c r="K59" s="12">
-        <v>0</v>
-      </c>
-      <c r="L59" s="13" t="s">
+      <c r="J59" s="15"/>
+      <c r="K59" s="15">
+        <v>0</v>
+      </c>
+      <c r="L59" s="14" t="s">
         <v>277</v>
       </c>
       <c r="M59" s="14"/>
     </row>
-    <row r="60" s="2" customFormat="1" spans="1:13">
+    <row r="60" s="5" customFormat="1" spans="1:13">
       <c r="A60" s="14"/>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="5" t="s">
         <v>278</v>
       </c>
       <c r="C60" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="15">
         <v>0.4</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="15" t="s">
         <v>279</v>
       </c>
       <c r="F60" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G60" s="12">
-        <v>190</v>
-      </c>
-      <c r="H60" s="12">
-        <v>95</v>
-      </c>
-      <c r="I60" s="2" t="s">
+      <c r="G60" s="15">
+        <v>80</v>
+      </c>
+      <c r="H60" s="15">
+        <v>40</v>
+      </c>
+      <c r="I60" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="J60" s="12"/>
-      <c r="K60" s="12">
-        <v>0</v>
-      </c>
-      <c r="L60" s="13" t="s">
+      <c r="J60" s="15"/>
+      <c r="K60" s="15">
+        <v>0</v>
+      </c>
+      <c r="L60" s="14" t="s">
         <v>281</v>
       </c>
       <c r="M60" s="14"/>
     </row>
-    <row r="61" s="2" customFormat="1" spans="1:13">
+    <row r="61" s="5" customFormat="1" spans="1:13">
       <c r="A61" s="14"/>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="5" t="s">
         <v>282</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="15">
         <v>0.4</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="15" t="s">
         <v>283</v>
       </c>
       <c r="F61" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="G61" s="12">
-        <v>190</v>
-      </c>
-      <c r="H61" s="12">
-        <v>95</v>
-      </c>
-      <c r="I61" s="2" t="s">
+      <c r="G61" s="15">
+        <v>80</v>
+      </c>
+      <c r="H61" s="15">
+        <v>40</v>
+      </c>
+      <c r="I61" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="J61" s="12"/>
-      <c r="K61" s="12">
-        <v>0</v>
-      </c>
-      <c r="L61" s="13" t="s">
+      <c r="J61" s="15"/>
+      <c r="K61" s="15">
+        <v>0</v>
+      </c>
+      <c r="L61" s="14" t="s">
         <v>285</v>
       </c>
       <c r="M61" s="14"/>
@@ -4754,10 +4742,10 @@
     <row r="62" spans="1:13">
       <c r="A62"/>
       <c r="B62" s="7"/>
-      <c r="C62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="C62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
       <c r="K62" s="7"/>
     </row>
     <row r="63" spans="1:13">
@@ -4765,7 +4753,7 @@
       <c r="B63" s="7">
         <v>301</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D63" s="7">
@@ -4777,13 +4765,13 @@
       <c r="F63" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="1">
         <v>190</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63" s="1">
         <v>95</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="I63" s="1" t="s">
         <v>289</v>
       </c>
       <c r="J63" s="7">
@@ -4792,7 +4780,7 @@
       <c r="K63" s="7">
         <v>0</v>
       </c>
-      <c r="L63" s="8" t="s">
+      <c r="L63" t="s">
         <v>290</v>
       </c>
     </row>
@@ -4801,7 +4789,7 @@
       <c r="B64" s="7">
         <v>302</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D64" s="7">
@@ -4813,19 +4801,19 @@
       <c r="F64" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="1">
         <v>270</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64" s="1">
         <v>135</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I64" s="1" t="s">
         <v>293</v>
       </c>
       <c r="K64" s="7">
         <v>0</v>
       </c>
-      <c r="L64" s="8" t="s">
+      <c r="L64" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4834,7 +4822,7 @@
       <c r="B65" s="7">
         <v>303</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D65" s="7">
@@ -4846,40 +4834,40 @@
       <c r="F65" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65" s="1">
         <v>190</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65" s="1">
         <v>95</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="J65" s="20">
+      <c r="J65" s="16">
         <v>10501</v>
       </c>
       <c r="K65" s="7">
         <v>0</v>
       </c>
-      <c r="L65" s="8" t="s">
+      <c r="L65" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:12">
-      <c r="A66" s="14"/>
-      <c r="B66" s="12">
+      <c r="A66" s="9"/>
+      <c r="B66" s="8">
         <v>304</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="8">
         <v>0.2</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="F66" s="8" t="s">
         <v>300</v>
       </c>
       <c r="G66" s="2">
@@ -4891,22 +4879,22 @@
       <c r="I66" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="J66" s="12">
+      <c r="J66" s="8">
         <v>10601</v>
       </c>
-      <c r="K66" s="12">
-        <v>0</v>
-      </c>
-      <c r="L66" s="13" t="s">
+      <c r="K66" s="8">
+        <v>0</v>
+      </c>
+      <c r="L66" s="9" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="67" s="3" customFormat="1" spans="1:12">
+    <row r="67" s="1" customFormat="1" spans="1:12">
       <c r="A67"/>
       <c r="B67" s="7">
         <v>305</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D67" s="7">
@@ -4918,13 +4906,13 @@
       <c r="F67" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="1">
         <v>170</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67" s="1">
         <v>85</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="1" t="s">
         <v>305</v>
       </c>
       <c r="J67" s="7">
@@ -4933,15 +4921,15 @@
       <c r="K67" s="7">
         <v>0</v>
       </c>
-      <c r="L67" s="8" t="s">
+      <c r="L67" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="68" s="3" customFormat="1" spans="1:12">
+    <row r="68" s="1" customFormat="1" spans="1:12">
       <c r="B68" s="7">
         <v>306</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D68" s="7">
@@ -4953,28 +4941,28 @@
       <c r="F68" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="1">
         <v>240</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68" s="1">
         <v>120</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I68" s="1" t="s">
         <v>309</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7">
         <v>0</v>
       </c>
-      <c r="L68" s="8" t="s">
+      <c r="L68" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="69" s="3" customFormat="1" spans="1:12">
+    <row r="69" s="1" customFormat="1" spans="1:12">
       <c r="B69" s="7">
         <v>307</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D69" s="7">
@@ -4986,27 +4974,27 @@
       <c r="F69" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="G69" s="3">
-        <v>265</v>
-      </c>
-      <c r="H69" s="3">
-        <v>132</v>
-      </c>
-      <c r="I69" s="3" t="s">
+      <c r="G69" s="1">
+        <v>240</v>
+      </c>
+      <c r="H69" s="1">
+        <v>120</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>313</v>
       </c>
       <c r="K69" s="7">
         <v>0</v>
       </c>
-      <c r="L69" s="8" t="s">
+      <c r="L69" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="70" s="3" customFormat="1" spans="1:12">
+    <row r="70" s="1" customFormat="1" spans="1:12">
       <c r="B70" s="7">
         <v>308</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D70" s="7">
@@ -5018,28 +5006,28 @@
       <c r="F70" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="G70" s="3">
-        <v>360</v>
-      </c>
-      <c r="H70" s="3">
-        <v>180</v>
-      </c>
-      <c r="I70" s="3" t="s">
+      <c r="G70" s="1">
+        <v>280</v>
+      </c>
+      <c r="H70" s="1">
+        <v>140</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="J70" s="9"/>
+      <c r="J70" s="7"/>
       <c r="K70" s="7">
         <v>0</v>
       </c>
-      <c r="L70" s="8" t="s">
+      <c r="L70" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="71" s="3" customFormat="1" spans="1:12">
+    <row r="71" s="1" customFormat="1" spans="1:12">
       <c r="B71" s="7">
         <v>309</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D71" s="7">
@@ -5051,13 +5039,13 @@
       <c r="F71" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="G71" s="3">
-        <v>350</v>
-      </c>
-      <c r="H71" s="3">
-        <v>175</v>
-      </c>
-      <c r="I71" s="3" t="s">
+      <c r="G71" s="1">
+        <v>270</v>
+      </c>
+      <c r="H71" s="1">
+        <v>135</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>321</v>
       </c>
       <c r="K71" s="7">
@@ -5067,11 +5055,11 @@
         <v>322</v>
       </c>
     </row>
-    <row r="72" s="3" customFormat="1" spans="1:12">
+    <row r="72" s="1" customFormat="1" spans="1:12">
       <c r="B72" s="7">
         <v>310</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D72" s="7">
@@ -5083,16 +5071,16 @@
       <c r="F72" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="1">
         <v>275</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="1">
         <v>137</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="I72" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="J72" s="9"/>
+      <c r="J72" s="7"/>
       <c r="K72" s="7">
         <v>0</v>
       </c>
@@ -5101,19 +5089,19 @@
       </c>
     </row>
     <row r="73" s="2" customFormat="1" spans="1:12">
-      <c r="B73" s="12">
+      <c r="B73" s="8">
         <v>311</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="8">
         <v>0.2</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F73" s="8" t="s">
         <v>328</v>
       </c>
       <c r="G73" s="2">
@@ -5125,27 +5113,27 @@
       <c r="I73" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="K73" s="12">
-        <v>0</v>
-      </c>
-      <c r="L73" s="13" t="s">
+      <c r="K73" s="8">
+        <v>0</v>
+      </c>
+      <c r="L73" s="9" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" spans="1:12">
-      <c r="B74" s="12">
+      <c r="B74" s="8">
         <v>312</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D74" s="12">
+      <c r="D74" s="8">
         <v>0.2</v>
       </c>
-      <c r="E74" s="12" t="s">
+      <c r="E74" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F74" s="8" t="s">
         <v>332</v>
       </c>
       <c r="G74" s="2">
@@ -5157,18 +5145,18 @@
       <c r="I74" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="K74" s="12">
-        <v>0</v>
-      </c>
-      <c r="L74" s="13" t="s">
+      <c r="K74" s="8">
+        <v>0</v>
+      </c>
+      <c r="L74" s="9" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="75" s="3" customFormat="1" spans="1:12">
+    <row r="75" s="1" customFormat="1" spans="1:12">
       <c r="B75" s="7">
         <v>313</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D75" s="7">
@@ -5180,28 +5168,28 @@
       <c r="F75" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="1">
         <v>160</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75" s="1">
         <v>80</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="J75" s="9"/>
+      <c r="J75" s="7"/>
       <c r="K75" s="7">
         <v>0</v>
       </c>
-      <c r="L75" s="8" t="s">
+      <c r="L75" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="76" s="3" customFormat="1" spans="1:12">
+    <row r="76" s="1" customFormat="1" spans="1:12">
       <c r="B76" s="7">
         <v>314</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D76" s="7">
@@ -5219,22 +5207,22 @@
       <c r="H76" s="7">
         <v>90</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="I76" s="1" t="s">
         <v>341</v>
       </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7">
         <v>0</v>
       </c>
-      <c r="L76" s="8" t="s">
+      <c r="L76" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="77" s="3" customFormat="1" spans="1:12">
+    <row r="77" s="1" customFormat="1" spans="1:12">
       <c r="B77" s="7">
         <v>315</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D77" s="7">
@@ -5252,14 +5240,14 @@
       <c r="H77" s="7">
         <v>190</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" s="1" t="s">
         <v>345</v>
       </c>
       <c r="J77" s="7"/>
       <c r="K77" s="7">
         <v>0</v>
       </c>
-      <c r="L77" s="8" t="s">
+      <c r="L77" t="s">
         <v>346</v>
       </c>
     </row>
@@ -5267,7 +5255,7 @@
       <c r="B78" s="7">
         <v>316</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D78" s="7">
@@ -5285,13 +5273,13 @@
       <c r="H78" s="7">
         <v>85</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="I78" s="1" t="s">
         <v>349</v>
       </c>
       <c r="K78" s="7">
         <v>0</v>
       </c>
-      <c r="L78" s="8" t="s">
+      <c r="L78" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5299,7 +5287,7 @@
       <c r="B79" s="7">
         <v>317</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D79" s="7">
@@ -5317,10 +5305,10 @@
       <c r="H79" s="7">
         <v>100</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="I79" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="7">
         <v>10201</v>
       </c>
       <c r="K79" s="7">
@@ -5334,7 +5322,7 @@
       <c r="B80" s="7">
         <v>318</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D80" s="7">
@@ -5352,60 +5340,60 @@
       <c r="H80" s="7">
         <v>85</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="I80" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="J80" s="20">
+      <c r="J80" s="16">
         <v>10801</v>
       </c>
       <c r="K80" s="7">
         <v>0</v>
       </c>
-      <c r="L80" s="8" t="s">
+      <c r="L80" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" spans="2:13">
-      <c r="B81" s="12">
+      <c r="B81" s="8">
         <v>319</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="8">
         <v>0.2</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="E81" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="F81" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="G81" s="12">
+      <c r="G81" s="8">
         <v>160</v>
       </c>
-      <c r="H81" s="12">
+      <c r="H81" s="8">
         <v>80</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="J81" s="12">
+      <c r="J81" s="8">
         <v>10402</v>
       </c>
-      <c r="K81" s="12">
-        <v>0</v>
-      </c>
-      <c r="L81" s="13" t="s">
+      <c r="K81" s="8">
+        <v>0</v>
+      </c>
+      <c r="L81" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="M81" s="14"/>
+      <c r="M81" s="9"/>
     </row>
     <row r="82" spans="2:13">
       <c r="B82" s="7">
         <v>320</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D82" s="7">
@@ -5423,13 +5411,13 @@
       <c r="H82" s="7">
         <v>80</v>
       </c>
-      <c r="I82" s="3" t="s">
+      <c r="I82" s="1" t="s">
         <v>365</v>
       </c>
       <c r="K82" s="7">
         <v>0</v>
       </c>
-      <c r="L82" s="8" t="s">
+      <c r="L82" t="s">
         <v>366</v>
       </c>
     </row>
@@ -5437,7 +5425,7 @@
       <c r="B83" s="7">
         <v>321</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D83" s="7">
@@ -5455,13 +5443,13 @@
       <c r="H83" s="7">
         <v>80</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="I83" s="1" t="s">
         <v>369</v>
       </c>
       <c r="K83" s="7">
         <v>0</v>
       </c>
-      <c r="L83" s="8" t="s">
+      <c r="L83" t="s">
         <v>370</v>
       </c>
     </row>
@@ -5469,7 +5457,7 @@
       <c r="B84" s="7">
         <v>322</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D84" s="7">
@@ -5487,13 +5475,13 @@
       <c r="H84" s="7">
         <v>80</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="I84" s="1" t="s">
         <v>373</v>
       </c>
       <c r="K84" s="7">
         <v>0</v>
       </c>
-      <c r="L84" s="8" t="s">
+      <c r="L84" t="s">
         <v>374</v>
       </c>
     </row>
@@ -5501,7 +5489,7 @@
       <c r="B85" s="7">
         <v>323</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D85" s="7">
@@ -5519,55 +5507,55 @@
       <c r="H85" s="7">
         <v>95</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="I85" s="1" t="s">
         <v>377</v>
       </c>
       <c r="K85" s="7">
         <v>0</v>
       </c>
-      <c r="L85" s="8" t="s">
+      <c r="L85" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" spans="2:13">
-      <c r="B86" s="12">
+      <c r="B86" s="8">
         <v>324</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D86" s="12">
+      <c r="D86" s="8">
         <v>0.2</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="F86" s="12" t="s">
+      <c r="F86" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="G86" s="12">
+      <c r="G86" s="8">
         <v>175</v>
       </c>
-      <c r="H86" s="12">
+      <c r="H86" s="8">
         <v>87</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12">
-        <v>0</v>
-      </c>
-      <c r="L86" s="13" t="s">
+      <c r="J86" s="8"/>
+      <c r="K86" s="8">
+        <v>0</v>
+      </c>
+      <c r="L86" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="M86" s="14"/>
+      <c r="M86" s="9"/>
     </row>
     <row r="87" spans="2:13">
       <c r="B87" s="7">
         <v>325</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D87" s="7">
@@ -5585,152 +5573,152 @@
       <c r="H87" s="7">
         <v>135</v>
       </c>
-      <c r="I87" s="3" t="s">
+      <c r="I87" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="J87" s="20">
+      <c r="J87" s="16">
         <v>10502</v>
       </c>
       <c r="K87" s="7">
         <v>0</v>
       </c>
-      <c r="L87" s="8" t="s">
+      <c r="L87" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" spans="2:13">
-      <c r="B88" s="12">
+      <c r="B88" s="8">
         <v>326</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="D88" s="12">
+      <c r="D88" s="8">
         <v>0.2</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="E88" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="F88" s="14" t="s">
+      <c r="F88" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="G88" s="12">
+      <c r="G88" s="8">
         <v>160</v>
       </c>
-      <c r="H88" s="12">
+      <c r="H88" s="8">
         <v>80</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="J88" s="12"/>
-      <c r="K88" s="12">
+      <c r="J88" s="8"/>
+      <c r="K88" s="8">
         <v>2</v>
       </c>
-      <c r="L88" s="13" t="s">
+      <c r="L88" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="M88" s="14"/>
+      <c r="M88" s="9"/>
     </row>
     <row r="89" s="2" customFormat="1" spans="2:13">
-      <c r="B89" s="12">
+      <c r="B89" s="8">
         <v>327</v>
       </c>
-      <c r="C89" s="14" t="s">
+      <c r="C89" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="D89" s="12">
+      <c r="D89" s="8">
         <v>0.2</v>
       </c>
-      <c r="E89" s="14" t="s">
+      <c r="E89" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="F89" s="14" t="s">
+      <c r="F89" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="G89" s="12">
+      <c r="G89" s="8">
         <v>200</v>
       </c>
-      <c r="H89" s="12">
+      <c r="H89" s="8">
         <v>100</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="J89" s="20">
+      <c r="J89" s="16">
         <v>10901</v>
       </c>
-      <c r="K89" s="12">
+      <c r="K89" s="8">
         <v>2</v>
       </c>
-      <c r="L89" s="13" t="s">
+      <c r="L89" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="M89" s="14"/>
+      <c r="M89" s="9"/>
     </row>
     <row r="90" s="2" customFormat="1" spans="2:13">
-      <c r="B90" s="12">
+      <c r="B90" s="8">
         <v>328</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="D90" s="12">
+      <c r="D90" s="8">
         <v>0.2</v>
       </c>
-      <c r="E90" s="14" t="s">
+      <c r="E90" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="F90" s="14" t="s">
+      <c r="F90" s="9" t="s">
         <v>396</v>
       </c>
-      <c r="G90" s="12">
+      <c r="G90" s="8">
         <v>170</v>
       </c>
-      <c r="H90" s="12">
+      <c r="H90" s="8">
         <v>85</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="J90" s="12"/>
-      <c r="K90" s="12">
+      <c r="J90" s="8"/>
+      <c r="K90" s="8">
         <v>1</v>
       </c>
-      <c r="L90" s="13" t="s">
+      <c r="L90" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="M90" s="14"/>
+      <c r="M90" s="9"/>
     </row>
     <row r="91" s="1" customFormat="1" spans="2:13">
       <c r="B91" s="7">
         <v>329</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" t="s">
         <v>286</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="7">
         <v>0.2</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" t="s">
         <v>399</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="7">
         <v>260</v>
       </c>
-      <c r="H91" s="9">
+      <c r="H91" s="7">
         <v>130</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="I91" s="1" t="s">
         <v>401</v>
       </c>
       <c r="K91" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="L91" s="8" t="s">
+      <c r="L91" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5738,31 +5726,31 @@
       <c r="B92" s="7">
         <v>330</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" t="s">
         <v>286</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="7">
         <v>0.2</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" t="s">
         <v>404</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="7">
         <v>260</v>
       </c>
-      <c r="H92" s="9">
+      <c r="H92" s="7">
         <v>130</v>
       </c>
-      <c r="I92" s="3" t="s">
+      <c r="I92" s="1" t="s">
         <v>406</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="L92" s="8" t="s">
+      <c r="L92" t="s">
         <v>407</v>
       </c>
     </row>
@@ -5770,10 +5758,10 @@
       <c r="B93" s="7">
         <v>331</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" t="s">
         <v>286</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="7">
         <v>0.2</v>
       </c>
       <c r="E93" t="s">
@@ -5783,57 +5771,57 @@
         <v>409</v>
       </c>
       <c r="G93" s="7">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="H93" s="7">
-        <v>70</v>
-      </c>
-      <c r="I93" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>410</v>
       </c>
       <c r="K93" s="7">
         <v>1</v>
       </c>
-      <c r="L93" s="8" t="s">
+      <c r="L93" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="94" s="2" customFormat="1" spans="2:13">
-      <c r="B94" s="12">
+    <row r="94" s="5" customFormat="1" spans="2:13">
+      <c r="B94" s="15">
         <v>332</v>
       </c>
       <c r="C94" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="D94" s="12">
+      <c r="D94" s="15">
         <v>0.2</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="E94" s="15" t="s">
         <v>412</v>
       </c>
       <c r="F94" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="G94" s="12">
-        <v>260</v>
-      </c>
-      <c r="H94" s="12">
-        <v>130</v>
-      </c>
-      <c r="I94" s="2" t="s">
+      <c r="G94" s="15">
+        <v>200</v>
+      </c>
+      <c r="H94" s="15">
+        <v>100</v>
+      </c>
+      <c r="I94" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="J94" s="21">
+      <c r="J94" s="17">
         <v>11005</v>
       </c>
-      <c r="K94" s="12">
-        <v>0</v>
-      </c>
-      <c r="L94" s="13" t="s">
+      <c r="K94" s="15">
+        <v>0</v>
+      </c>
+      <c r="L94" s="14" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="95" s="3" customFormat="1" spans="2:13">
+    <row r="95" s="1" customFormat="1" spans="2:13">
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
       <c r="F95" s="7"/>
@@ -5843,11 +5831,11 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
     </row>
-    <row r="96" s="3" customFormat="1" spans="2:13">
-      <c r="B96" s="3" t="s">
+    <row r="96" s="1" customFormat="1" spans="2:13">
+      <c r="B96" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D96" s="7">
@@ -5865,7 +5853,7 @@
       <c r="H96" s="7">
         <v>325</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="I96" s="1" t="s">
         <v>418</v>
       </c>
       <c r="J96" s="7">
@@ -5874,15 +5862,15 @@
       <c r="K96" s="7">
         <v>0</v>
       </c>
-      <c r="L96" s="8" t="s">
+      <c r="L96" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="97" s="3" customFormat="1" spans="2:13">
-      <c r="B97" s="3" t="s">
+    <row r="97" s="1" customFormat="1" spans="2:13">
+      <c r="B97" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D97" s="7">
@@ -5900,22 +5888,22 @@
       <c r="H97" s="7">
         <v>340</v>
       </c>
-      <c r="I97" s="3" t="s">
+      <c r="I97" s="1" t="s">
         <v>423</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7">
         <v>0</v>
       </c>
-      <c r="L97" s="8" t="s">
+      <c r="L97" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="98" s="3" customFormat="1" spans="2:13">
-      <c r="B98" s="3" t="s">
+    <row r="98" s="1" customFormat="1" spans="2:13">
+      <c r="B98" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D98" s="7">
@@ -5933,7 +5921,7 @@
       <c r="H98" s="7">
         <v>300</v>
       </c>
-      <c r="I98" s="3" t="s">
+      <c r="I98" s="1" t="s">
         <v>428</v>
       </c>
       <c r="K98" s="7">
@@ -5950,39 +5938,39 @@
       <c r="C99" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D99" s="12">
+      <c r="D99" s="8">
         <v>0.1</v>
       </c>
-      <c r="E99" s="12" t="s">
+      <c r="E99" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="F99" s="12" t="s">
+      <c r="F99" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="G99" s="12">
+      <c r="G99" s="8">
         <v>480</v>
       </c>
-      <c r="H99" s="12">
+      <c r="H99" s="8">
         <v>240</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="J99" s="12">
+      <c r="J99" s="8">
         <v>11002</v>
       </c>
-      <c r="K99" s="12">
-        <v>0</v>
-      </c>
-      <c r="L99" s="13" t="s">
+      <c r="K99" s="8">
+        <v>0</v>
+      </c>
+      <c r="L99" s="9" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="100" s="3" customFormat="1" spans="2:13">
-      <c r="B100" s="3" t="s">
+    <row r="100" s="1" customFormat="1" spans="2:13">
+      <c r="B100" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D100" s="7">
@@ -6000,22 +5988,22 @@
       <c r="H100" s="7">
         <v>230</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="I100" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J100" s="9"/>
+      <c r="J100" s="7"/>
       <c r="K100" s="7">
         <v>0</v>
       </c>
-      <c r="L100" s="8" t="s">
+      <c r="L100" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="101" s="3" customFormat="1" spans="2:13">
-      <c r="B101" s="3" t="s">
+    <row r="101" s="1" customFormat="1" spans="2:13">
+      <c r="B101" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D101" s="7">
@@ -6033,13 +6021,13 @@
       <c r="H101" s="7">
         <v>160</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="I101" s="1" t="s">
         <v>443</v>
       </c>
       <c r="K101" s="7">
         <v>0</v>
       </c>
-      <c r="L101" s="8" t="s">
+      <c r="L101" t="s">
         <v>444</v>
       </c>
     </row>
@@ -6050,39 +6038,39 @@
       <c r="C102" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D102" s="12">
+      <c r="D102" s="8">
         <v>0.1</v>
       </c>
-      <c r="E102" s="12" t="s">
+      <c r="E102" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="F102" s="12" t="s">
+      <c r="F102" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="G102" s="12">
+      <c r="G102" s="8">
         <v>380</v>
       </c>
-      <c r="H102" s="12">
+      <c r="H102" s="8">
         <v>190</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="J102" s="20">
+      <c r="J102" s="16">
         <v>11003</v>
       </c>
-      <c r="K102" s="12">
-        <v>0</v>
-      </c>
-      <c r="L102" s="13" t="s">
+      <c r="K102" s="8">
+        <v>0</v>
+      </c>
+      <c r="L102" s="9" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="103" s="3" customFormat="1" spans="2:13">
-      <c r="B103" s="3" t="s">
+    <row r="103" s="1" customFormat="1" spans="2:13">
+      <c r="B103" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D103" s="7">
@@ -6100,10 +6088,10 @@
       <c r="H103" s="7">
         <v>300</v>
       </c>
-      <c r="I103" s="3" t="s">
+      <c r="I103" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="J103" s="9"/>
+      <c r="J103" s="7"/>
       <c r="K103" s="7">
         <v>0</v>
       </c>
@@ -6111,11 +6099,11 @@
         <v>454</v>
       </c>
     </row>
-    <row r="104" s="3" customFormat="1" spans="2:13">
-      <c r="B104" s="3" t="s">
+    <row r="104" s="1" customFormat="1" spans="2:13">
+      <c r="B104" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D104" s="7">
@@ -6128,18 +6116,18 @@
         <v>457</v>
       </c>
       <c r="G104" s="7">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="H104" s="7">
-        <v>150</v>
-      </c>
-      <c r="I104" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>458</v>
       </c>
       <c r="K104" s="7">
         <v>0</v>
       </c>
-      <c r="L104" s="8" t="s">
+      <c r="L104" t="s">
         <v>459</v>
       </c>
     </row>
@@ -6150,36 +6138,36 @@
       <c r="C105" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D105" s="12">
+      <c r="D105" s="8">
         <v>0.1</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="E105" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="F105" s="12" t="s">
+      <c r="F105" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="G105" s="12">
+      <c r="G105" s="8">
         <v>300</v>
       </c>
-      <c r="H105" s="12">
+      <c r="H105" s="8">
         <v>150</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="K105" s="12">
-        <v>0</v>
-      </c>
-      <c r="L105" s="13" t="s">
+      <c r="K105" s="8">
+        <v>0</v>
+      </c>
+      <c r="L105" s="9" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="106" spans="2:13">
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D106" s="7">
@@ -6197,16 +6185,16 @@
       <c r="H106" s="7">
         <v>200</v>
       </c>
-      <c r="I106" s="3" t="s">
+      <c r="I106" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="J106" s="20">
+      <c r="J106" s="16">
         <v>11004</v>
       </c>
       <c r="K106" s="7">
         <v>0</v>
       </c>
-      <c r="L106" s="8" t="s">
+      <c r="L106" t="s">
         <v>469</v>
       </c>
     </row>
@@ -6217,38 +6205,38 @@
       <c r="C107" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D107" s="12">
+      <c r="D107" s="8">
         <v>0.1</v>
       </c>
-      <c r="E107" s="12" t="s">
+      <c r="E107" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="F107" s="12" t="s">
+      <c r="F107" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="G107" s="12">
+      <c r="G107" s="8">
         <v>460</v>
       </c>
-      <c r="H107" s="12">
+      <c r="H107" s="8">
         <v>230</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12">
-        <v>0</v>
-      </c>
-      <c r="L107" s="13" t="s">
+      <c r="J107" s="8"/>
+      <c r="K107" s="8">
+        <v>0</v>
+      </c>
+      <c r="L107" s="9" t="s">
         <v>474</v>
       </c>
-      <c r="M107" s="14"/>
+      <c r="M107" s="9"/>
     </row>
     <row r="108" spans="2:13">
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D108" s="7">
@@ -6266,7 +6254,7 @@
       <c r="H108" s="7">
         <v>170</v>
       </c>
-      <c r="I108" s="3" t="s">
+      <c r="I108" s="1" t="s">
         <v>478</v>
       </c>
       <c r="J108" s="7">
@@ -6275,15 +6263,15 @@
       <c r="K108" s="7">
         <v>0</v>
       </c>
-      <c r="L108" s="8" t="s">
+      <c r="L108" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="109" spans="2:13">
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D109" s="7">
@@ -6301,21 +6289,21 @@
       <c r="H109" s="7">
         <v>140</v>
       </c>
-      <c r="I109" s="3" t="s">
+      <c r="I109" s="1" t="s">
         <v>483</v>
       </c>
       <c r="K109" s="7">
         <v>0</v>
       </c>
-      <c r="L109" s="8" t="s">
+      <c r="L109" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="110" spans="2:13">
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D110" s="7">
@@ -6339,15 +6327,15 @@
       <c r="K110" s="7">
         <v>0</v>
       </c>
-      <c r="L110" s="8" t="s">
+      <c r="L110" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="111" spans="2:13">
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D111" s="7">
@@ -6368,7 +6356,7 @@
       <c r="I111" s="7">
         <v>40016</v>
       </c>
-      <c r="J111" s="20">
+      <c r="J111" s="16">
         <v>10101</v>
       </c>
       <c r="K111" s="7">
@@ -6379,10 +6367,10 @@
       </c>
     </row>
     <row r="112" spans="2:13">
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D112" s="7">
@@ -6406,15 +6394,15 @@
       <c r="K112" s="7">
         <v>0</v>
       </c>
-      <c r="L112" s="8" t="s">
+      <c r="L112" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="113" spans="1:13">
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D113" s="7">
@@ -6435,21 +6423,21 @@
       <c r="I113" s="7">
         <v>40018</v>
       </c>
-      <c r="J113" s="20">
+      <c r="J113" s="16">
         <v>11101</v>
       </c>
       <c r="K113" s="7">
         <v>0</v>
       </c>
-      <c r="L113" s="8" t="s">
+      <c r="L113" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="114" spans="1:13">
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D114" s="7">
@@ -6473,7 +6461,7 @@
       <c r="K114" s="7">
         <v>0</v>
       </c>
-      <c r="L114" s="8" t="s">
+      <c r="L114" t="s">
         <v>505</v>
       </c>
     </row>
@@ -6484,38 +6472,38 @@
       <c r="C115" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D115" s="9">
+      <c r="D115" s="7">
         <v>0.1</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" t="s">
         <v>507</v>
       </c>
-      <c r="F115" s="9" t="s">
+      <c r="F115" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="G115" s="9">
+      <c r="G115" s="7">
         <v>560</v>
       </c>
-      <c r="H115" s="9">
+      <c r="H115" s="7">
         <v>280</v>
       </c>
-      <c r="I115" s="9">
+      <c r="I115" s="7">
         <v>40020</v>
       </c>
-      <c r="J115" s="9"/>
-      <c r="K115" s="9">
-        <v>0</v>
-      </c>
-      <c r="L115" s="10" t="s">
+      <c r="J115" s="7"/>
+      <c r="K115" s="7">
+        <v>0</v>
+      </c>
+      <c r="L115" t="s">
         <v>509</v>
       </c>
-      <c r="M115" s="11"/>
+      <c r="M115"/>
     </row>
     <row r="116" spans="1:13">
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D116" s="7">
@@ -6539,15 +6527,15 @@
       <c r="K116" s="7">
         <v>0</v>
       </c>
-      <c r="L116" s="8" t="s">
+      <c r="L116" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="117" spans="1:13">
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D117" s="7">
@@ -6568,13 +6556,13 @@
       <c r="I117" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="J117" s="20">
+      <c r="J117" s="16">
         <v>11201</v>
       </c>
       <c r="K117" s="7">
         <v>0</v>
       </c>
-      <c r="L117" s="8" t="s">
+      <c r="L117" t="s">
         <v>518</v>
       </c>
     </row>
@@ -6585,40 +6573,40 @@
       <c r="C118" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D118" s="12">
+      <c r="D118" s="8">
         <v>0.1</v>
       </c>
-      <c r="E118" s="14" t="s">
+      <c r="E118" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="F118" s="12" t="s">
+      <c r="F118" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="G118" s="12">
+      <c r="G118" s="8">
         <v>320</v>
       </c>
-      <c r="H118" s="12">
+      <c r="H118" s="8">
         <v>160</v>
       </c>
-      <c r="I118" s="12">
+      <c r="I118" s="8">
         <v>40023</v>
       </c>
-      <c r="J118" s="20">
+      <c r="J118" s="16">
         <v>11301</v>
       </c>
-      <c r="K118" s="12">
-        <v>0</v>
-      </c>
-      <c r="L118" s="13" t="s">
+      <c r="K118" s="8">
+        <v>0</v>
+      </c>
+      <c r="L118" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="M118" s="14"/>
+      <c r="M118" s="9"/>
     </row>
     <row r="119" spans="1:13">
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D119" s="7">
@@ -6639,7 +6627,7 @@
       <c r="I119" s="7">
         <v>40024</v>
       </c>
-      <c r="J119" s="20">
+      <c r="J119" s="16">
         <v>11401</v>
       </c>
       <c r="K119" s="7">
@@ -6650,10 +6638,10 @@
       </c>
     </row>
     <row r="120" spans="1:13">
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="1" t="s">
         <v>416</v>
       </c>
       <c r="D120" s="7">
@@ -6682,40 +6670,40 @@
       </c>
     </row>
     <row r="121" s="2" customFormat="1" spans="1:13">
-      <c r="B121" s="12">
+      <c r="B121" s="8">
         <v>426</v>
       </c>
-      <c r="C121" s="14" t="s">
+      <c r="C121" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D121" s="12">
+      <c r="D121" s="8">
         <v>0.1</v>
       </c>
-      <c r="E121" s="14" t="s">
+      <c r="E121" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="F121" s="14" t="s">
+      <c r="F121" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="G121" s="12">
+      <c r="G121" s="8">
         <v>400</v>
       </c>
-      <c r="H121" s="12">
+      <c r="H121" s="8">
         <v>200</v>
       </c>
-      <c r="I121" s="12">
+      <c r="I121" s="8">
         <v>40026</v>
       </c>
-      <c r="J121" s="20">
+      <c r="J121" s="16">
         <v>11501</v>
       </c>
-      <c r="K121" s="12">
+      <c r="K121" s="8">
         <v>1</v>
       </c>
-      <c r="L121" s="13" t="s">
+      <c r="L121" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="M121" s="14"/>
+      <c r="M121" s="9"/>
     </row>
     <row r="122" spans="1:13">
       <c r="B122" s="7">
@@ -6745,148 +6733,148 @@
       <c r="K122" s="7">
         <v>1</v>
       </c>
-      <c r="L122" s="8" t="s">
+      <c r="L122" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="123" s="2" customFormat="1" spans="1:13">
-      <c r="B123" s="12">
+      <c r="B123" s="8">
         <v>428</v>
       </c>
-      <c r="C123" s="14" t="s">
+      <c r="C123" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D123" s="12">
+      <c r="D123" s="8">
         <v>0.1</v>
       </c>
-      <c r="E123" s="14" t="s">
+      <c r="E123" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="F123" s="14" t="s">
+      <c r="F123" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="G123" s="12">
+      <c r="G123" s="8">
         <v>260</v>
       </c>
-      <c r="H123" s="12">
+      <c r="H123" s="8">
         <v>130</v>
       </c>
-      <c r="I123" s="12">
+      <c r="I123" s="8">
         <v>40028</v>
       </c>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12">
+      <c r="J123" s="8"/>
+      <c r="K123" s="8">
         <v>2</v>
       </c>
-      <c r="L123" s="13" t="s">
+      <c r="L123" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="M123" s="14"/>
+      <c r="M123" s="9"/>
     </row>
     <row r="124" s="2" customFormat="1" spans="1:13">
-      <c r="B124" s="12">
+      <c r="B124" s="8">
         <v>429</v>
       </c>
-      <c r="C124" s="14" t="s">
+      <c r="C124" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D124" s="12">
+      <c r="D124" s="8">
         <v>0.1</v>
       </c>
-      <c r="E124" s="14" t="s">
+      <c r="E124" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="F124" s="14" t="s">
+      <c r="F124" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="G124" s="12">
+      <c r="G124" s="8">
         <v>270</v>
       </c>
-      <c r="H124" s="12">
+      <c r="H124" s="8">
         <v>135</v>
       </c>
-      <c r="I124" s="12">
+      <c r="I124" s="8">
         <v>40029</v>
       </c>
-      <c r="J124" s="12"/>
-      <c r="K124" s="12">
+      <c r="J124" s="8"/>
+      <c r="K124" s="8">
         <v>2</v>
       </c>
-      <c r="L124" s="13" t="s">
+      <c r="L124" s="9" t="s">
         <v>542</v>
       </c>
-      <c r="M124" s="14"/>
+      <c r="M124" s="9"/>
     </row>
     <row r="125" s="2" customFormat="1" spans="1:13">
-      <c r="B125" s="12">
+      <c r="B125" s="8">
         <v>430</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D125" s="12">
+      <c r="D125" s="8">
         <v>0.1</v>
       </c>
-      <c r="E125" s="14" t="s">
+      <c r="E125" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="F125" s="14" t="s">
+      <c r="F125" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="G125" s="12">
+      <c r="G125" s="8">
         <v>280</v>
       </c>
-      <c r="H125" s="12">
+      <c r="H125" s="8">
         <v>140</v>
       </c>
-      <c r="I125" s="12">
+      <c r="I125" s="8">
         <v>40030</v>
       </c>
-      <c r="J125" s="20">
+      <c r="J125" s="16">
         <v>11601</v>
       </c>
-      <c r="K125" s="12">
-        <v>0</v>
-      </c>
-      <c r="L125" s="13" t="s">
+      <c r="K125" s="8">
+        <v>0</v>
+      </c>
+      <c r="L125" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="M125" s="14"/>
+      <c r="M125" s="9"/>
     </row>
     <row r="126" s="2" customFormat="1" spans="1:13">
-      <c r="A126" s="14"/>
-      <c r="B126" s="12">
+      <c r="A126" s="9"/>
+      <c r="B126" s="8">
         <v>431</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="D126" s="12">
+      <c r="D126" s="8">
         <v>0.1</v>
       </c>
-      <c r="E126" s="12" t="s">
+      <c r="E126" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="F126" s="12" t="s">
+      <c r="F126" s="8" t="s">
         <v>547</v>
       </c>
       <c r="G126" s="2">
+        <v>260</v>
+      </c>
+      <c r="H126" s="2">
         <v>130</v>
       </c>
-      <c r="H126" s="2">
-        <v>65</v>
-      </c>
-      <c r="I126" s="12">
+      <c r="I126" s="8">
         <v>40031</v>
       </c>
-      <c r="J126" s="12"/>
-      <c r="K126" s="12">
-        <v>0</v>
-      </c>
-      <c r="L126" s="13" t="s">
+      <c r="J126" s="8"/>
+      <c r="K126" s="8">
+        <v>0</v>
+      </c>
+      <c r="L126" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="M126" s="14"/>
+      <c r="M126" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -202,7 +202,7 @@
     <t>WoodenStaff</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+3攻击力</t>
+    <t>亮出的顺子牌型在结算时提供+5攻击力</t>
   </si>
   <si>
     <t>108</t>
@@ -214,7 +214,7 @@
     <t>WoodenLongBow</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+3攻击力</t>
+    <t>亮出的同花牌型在结算时提供+4攻击力</t>
   </si>
   <si>
     <t>109</t>
@@ -226,7 +226,7 @@
     <t>WoodenSpear</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+5攻击力</t>
+    <t>亮出的同花顺牌型在结算时提供+6攻击力</t>
   </si>
   <si>
     <t>110</t>
@@ -238,7 +238,7 @@
     <t>WoodenLongAxe</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+6攻击力</t>
+    <t>亮出的豹子牌型在结算时提供+7攻击力</t>
   </si>
   <si>
     <t>111</t>
@@ -250,7 +250,7 @@
     <t>WoodenRoundShield</t>
   </si>
   <si>
-    <t>每次受到的伤害降低2%</t>
+    <t>每次受到的伤害降低5%</t>
   </si>
   <si>
     <t>112</t>
@@ -388,7 +388,7 @@
     <t>20001</t>
   </si>
   <si>
-    <t>亮出的每张方片牌在结算时提供+2倍率</t>
+    <t>亮出的每张方片牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>202</t>
@@ -403,7 +403,7 @@
     <t>20002</t>
   </si>
   <si>
-    <t>亮出的每张黑桃牌在结算时提供+2倍率</t>
+    <t>亮出的每张黑桃牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>203</t>
@@ -418,7 +418,7 @@
     <t>20003</t>
   </si>
   <si>
-    <t>亮出的每张红心牌在结算时提供+2倍率</t>
+    <t>亮出的每张红心牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>204</t>
@@ -433,7 +433,7 @@
     <t>20004</t>
   </si>
   <si>
-    <t>亮出的每张梅花牌在结算时提供+2倍率</t>
+    <t>亮出的每张梅花牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>205</t>
@@ -463,7 +463,7 @@
     <t>20006</t>
   </si>
   <si>
-    <t>亮出的顺子牌型在结算时提供+3倍率</t>
+    <t>亮出的顺子牌型在结算时提供+5倍率</t>
   </si>
   <si>
     <t>207</t>
@@ -478,7 +478,7 @@
     <t>20007</t>
   </si>
   <si>
-    <t>亮出的同花牌型在结算时提供+3倍率</t>
+    <t>亮出的同花牌型在结算时提供+4倍率</t>
   </si>
   <si>
     <t>208</t>
@@ -493,7 +493,7 @@
     <t>20008</t>
   </si>
   <si>
-    <t>亮出的同花顺牌型在结算时提供+5倍率</t>
+    <t>亮出的同花顺牌型在结算时提供+6倍率</t>
   </si>
   <si>
     <t>209</t>
@@ -508,7 +508,7 @@
     <t>20009</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+6倍率</t>
+    <t>亮出的豹子牌型在结算时提供+7倍率</t>
   </si>
   <si>
     <t>210</t>
@@ -553,7 +553,7 @@
     <t>20012</t>
   </si>
   <si>
-    <t>亮出的每张人头牌在结算时提供+2倍率</t>
+    <t>亮出的每张人头牌在结算时提供+1倍率</t>
   </si>
   <si>
     <t>213</t>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16590" windowHeight="10440"/>
+    <workbookView windowWidth="16830" windowHeight="11025"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="553">
   <si>
     <t>##var</t>
   </si>
@@ -355,7 +355,7 @@
     <t>复仇之刺</t>
   </si>
   <si>
-    <t>RevengeThorn</t>
+    <t>VengeanceSpike</t>
   </si>
   <si>
     <t>每输1次比牌,你造成的伤害+10%,至多叠加5层</t>
@@ -367,7 +367,7 @@
     <t>对子心得</t>
   </si>
   <si>
-    <t>PairExperience</t>
+    <t>PairInsight</t>
   </si>
   <si>
     <t>使用后,对子牌型提供的倍率永久+1</t>
@@ -787,7 +787,7 @@
     <t>急救包</t>
   </si>
   <si>
-    <t>GoldenFirstAidKit</t>
+    <t>GoldFirstAidKit</t>
   </si>
   <si>
     <t>20028</t>
@@ -817,7 +817,7 @@
     <t>商人票据</t>
   </si>
   <si>
-    <t>MerchantTicket</t>
+    <t>MerchantBill</t>
   </si>
   <si>
     <t>20030</t>
@@ -832,7 +832,7 @@
     <t>同花心得</t>
   </si>
   <si>
-    <t>FlushExperience</t>
+    <t>SameSuitInsight</t>
   </si>
   <si>
     <t>20031</t>
@@ -847,7 +847,7 @@
     <t>顺子心得</t>
   </si>
   <si>
-    <t>StraightExperience</t>
+    <t>StraightInsight</t>
   </si>
   <si>
     <t>20032</t>
@@ -862,6 +862,9 @@
     <t>第一位</t>
   </si>
   <si>
+    <t>FirstPosition</t>
+  </si>
+  <si>
     <t>20033</t>
   </si>
   <si>
@@ -874,6 +877,9 @@
     <t>第二位</t>
   </si>
   <si>
+    <t>SecondPosition</t>
+  </si>
+  <si>
     <t>20034</t>
   </si>
   <si>
@@ -886,6 +892,9 @@
     <t>第三位</t>
   </si>
   <si>
+    <t>ThirdPosition</t>
+  </si>
+  <si>
     <t>20035</t>
   </si>
   <si>
@@ -1210,7 +1219,7 @@
     <t>时之沙</t>
   </si>
   <si>
-    <t>SandOfTime</t>
+    <t>TimeSand</t>
   </si>
   <si>
     <t>30027</t>
@@ -1234,7 +1243,7 @@
     <t>降低</t>
   </si>
   <si>
-    <t>ReduceLevel</t>
+    <t>LowerStatus</t>
   </si>
   <si>
     <t>30029</t>
@@ -1249,7 +1258,7 @@
     <t>升职</t>
   </si>
   <si>
-    <t>UpLevel</t>
+    <t>Promote</t>
   </si>
   <si>
     <t>30030</t>
@@ -1261,7 +1270,7 @@
     <t>净化药水</t>
   </si>
   <si>
-    <t>PurificationPotion</t>
+    <t>PurifyPotion</t>
   </si>
   <si>
     <t>30031</t>
@@ -1271,6 +1280,9 @@
   </si>
   <si>
     <t>三花聚顶</t>
+  </si>
+  <si>
+    <t>ThreeFlowersGatherAtTheTop</t>
   </si>
   <si>
     <t>30032</t>
@@ -4649,7 +4661,7 @@
         <v>275</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G59" s="15">
         <v>80</v>
@@ -4658,21 +4670,21 @@
         <v>40</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J59" s="15"/>
       <c r="K59" s="15">
         <v>0</v>
       </c>
       <c r="L59" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M59" s="14"/>
     </row>
     <row r="60" s="5" customFormat="1" spans="1:13">
       <c r="A60" s="14"/>
       <c r="B60" s="5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C60" s="14" t="s">
         <v>114</v>
@@ -4681,10 +4693,10 @@
         <v>0.4</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="G60" s="15">
         <v>80</v>
@@ -4693,21 +4705,21 @@
         <v>40</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J60" s="15"/>
       <c r="K60" s="15">
         <v>0</v>
       </c>
       <c r="L60" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M60" s="14"/>
     </row>
     <row r="61" s="5" customFormat="1" spans="1:13">
       <c r="A61" s="14"/>
       <c r="B61" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>114</v>
@@ -4716,10 +4728,10 @@
         <v>0.4</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="G61" s="15">
         <v>80</v>
@@ -4728,14 +4740,14 @@
         <v>40</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J61" s="15"/>
       <c r="K61" s="15">
         <v>0</v>
       </c>
       <c r="L61" s="14" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M61" s="14"/>
     </row>
@@ -4754,16 +4766,16 @@
         <v>301</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D63" s="7">
         <v>0.2</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G63" s="1">
         <v>190</v>
@@ -4772,7 +4784,7 @@
         <v>95</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J63" s="7">
         <v>10401</v>
@@ -4781,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -4790,16 +4802,16 @@
         <v>302</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D64" s="7">
         <v>0.2</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G64" s="1">
         <v>270</v>
@@ -4808,13 +4820,13 @@
         <v>135</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K64" s="7">
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -4823,16 +4835,16 @@
         <v>303</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D65" s="7">
         <v>0.2</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G65" s="1">
         <v>190</v>
@@ -4841,7 +4853,7 @@
         <v>95</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J65" s="16">
         <v>10501</v>
@@ -4850,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:12">
@@ -4859,16 +4871,16 @@
         <v>304</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D66" s="8">
         <v>0.2</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G66" s="2">
         <v>160</v>
@@ -4877,7 +4889,7 @@
         <v>80</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J66" s="8">
         <v>10601</v>
@@ -4886,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:12">
@@ -4895,16 +4907,16 @@
         <v>305</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D67" s="7">
         <v>0.2</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G67" s="1">
         <v>170</v>
@@ -4913,7 +4925,7 @@
         <v>85</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J67" s="7">
         <v>10701</v>
@@ -4922,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:12">
@@ -4930,16 +4942,16 @@
         <v>306</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D68" s="7">
         <v>0.2</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G68" s="1">
         <v>240</v>
@@ -4948,14 +4960,14 @@
         <v>120</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7">
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:12">
@@ -4963,16 +4975,16 @@
         <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D69" s="7">
         <v>0.2</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="G69" s="1">
         <v>240</v>
@@ -4981,13 +4993,13 @@
         <v>120</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K69" s="7">
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:12">
@@ -4995,16 +5007,16 @@
         <v>308</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D70" s="7">
         <v>0.2</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G70" s="1">
         <v>280</v>
@@ -5013,14 +5025,14 @@
         <v>140</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J70" s="7"/>
       <c r="K70" s="7">
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:12">
@@ -5028,16 +5040,16 @@
         <v>309</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D71" s="7">
         <v>0.2</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G71" s="1">
         <v>270</v>
@@ -5046,13 +5058,13 @@
         <v>135</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K71" s="7">
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:12">
@@ -5060,16 +5072,16 @@
         <v>310</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D72" s="7">
         <v>0.2</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G72" s="1">
         <v>275</v>
@@ -5078,14 +5090,14 @@
         <v>137</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J72" s="7"/>
       <c r="K72" s="7">
         <v>0</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" spans="1:12">
@@ -5093,16 +5105,16 @@
         <v>311</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D73" s="8">
         <v>0.2</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G73" s="2">
         <v>170</v>
@@ -5111,13 +5123,13 @@
         <v>85</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K73" s="8">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" spans="1:12">
@@ -5125,16 +5137,16 @@
         <v>312</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D74" s="8">
         <v>0.2</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G74" s="2">
         <v>210</v>
@@ -5143,13 +5155,13 @@
         <v>105</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K74" s="8">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:12">
@@ -5157,16 +5169,16 @@
         <v>313</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D75" s="7">
         <v>0.2</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G75" s="1">
         <v>160</v>
@@ -5175,14 +5187,14 @@
         <v>80</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J75" s="7"/>
       <c r="K75" s="7">
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:12">
@@ -5190,16 +5202,16 @@
         <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D76" s="7">
         <v>0.2</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G76" s="7">
         <v>180</v>
@@ -5208,14 +5220,14 @@
         <v>90</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:12">
@@ -5223,16 +5235,16 @@
         <v>315</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D77" s="7">
         <v>0.2</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G77" s="7">
         <v>380</v>
@@ -5241,14 +5253,14 @@
         <v>190</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J77" s="7"/>
       <c r="K77" s="7">
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -5256,16 +5268,16 @@
         <v>316</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D78" s="7">
         <v>0.2</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G78" s="7">
         <v>170</v>
@@ -5274,13 +5286,13 @@
         <v>85</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K78" s="7">
         <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -5288,16 +5300,16 @@
         <v>317</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D79" s="7">
         <v>0.2</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G79" s="7">
         <v>200</v>
@@ -5306,7 +5318,7 @@
         <v>100</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J79" s="7">
         <v>10201</v>
@@ -5315,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -5323,16 +5335,16 @@
         <v>318</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D80" s="7">
         <v>0.2</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G80" s="7">
         <v>170</v>
@@ -5341,7 +5353,7 @@
         <v>85</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="J80" s="16">
         <v>10801</v>
@@ -5350,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" spans="2:13">
@@ -5358,16 +5370,16 @@
         <v>319</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D81" s="8">
         <v>0.2</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G81" s="8">
         <v>160</v>
@@ -5376,7 +5388,7 @@
         <v>80</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J81" s="8">
         <v>10402</v>
@@ -5385,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="M81" s="9"/>
     </row>
@@ -5394,16 +5406,16 @@
         <v>320</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D82" s="7">
         <v>0.2</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G82" s="7">
         <v>160</v>
@@ -5412,13 +5424,13 @@
         <v>80</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K82" s="7">
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="83" spans="2:13">
@@ -5426,16 +5438,16 @@
         <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D83" s="7">
         <v>0.2</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G83" s="7">
         <v>160</v>
@@ -5444,13 +5456,13 @@
         <v>80</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K83" s="7">
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84" spans="2:13">
@@ -5458,16 +5470,16 @@
         <v>322</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D84" s="7">
         <v>0.2</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="G84" s="7">
         <v>160</v>
@@ -5476,13 +5488,13 @@
         <v>80</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K84" s="7">
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="85" spans="2:13">
@@ -5490,16 +5502,16 @@
         <v>323</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D85" s="7">
         <v>0.2</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G85" s="7">
         <v>190</v>
@@ -5508,13 +5520,13 @@
         <v>95</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K85" s="7">
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" spans="2:13">
@@ -5522,16 +5534,16 @@
         <v>324</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D86" s="8">
         <v>0.2</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G86" s="8">
         <v>175</v>
@@ -5540,14 +5552,14 @@
         <v>87</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="8">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M86" s="9"/>
     </row>
@@ -5556,16 +5568,16 @@
         <v>325</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D87" s="7">
         <v>0.2</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G87" s="7">
         <v>270</v>
@@ -5574,7 +5586,7 @@
         <v>135</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J87" s="16">
         <v>10502</v>
@@ -5583,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" spans="2:13">
@@ -5591,16 +5603,16 @@
         <v>326</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D88" s="8">
         <v>0.2</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G88" s="8">
         <v>160</v>
@@ -5609,14 +5621,14 @@
         <v>80</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="8">
         <v>2</v>
       </c>
       <c r="L88" s="9" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="M88" s="9"/>
     </row>
@@ -5625,16 +5637,16 @@
         <v>327</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D89" s="8">
         <v>0.2</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G89" s="8">
         <v>200</v>
@@ -5643,7 +5655,7 @@
         <v>100</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="J89" s="16">
         <v>10901</v>
@@ -5652,7 +5664,7 @@
         <v>2</v>
       </c>
       <c r="L89" s="9" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M89" s="9"/>
     </row>
@@ -5661,16 +5673,16 @@
         <v>328</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D90" s="8">
         <v>0.2</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G90" s="8">
         <v>170</v>
@@ -5679,14 +5691,14 @@
         <v>85</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="8">
         <v>1</v>
       </c>
       <c r="L90" s="9" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M90" s="9"/>
     </row>
@@ -5695,16 +5707,16 @@
         <v>329</v>
       </c>
       <c r="C91" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D91" s="7">
         <v>0.2</v>
       </c>
       <c r="E91" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G91" s="7">
         <v>260</v>
@@ -5713,13 +5725,13 @@
         <v>130</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L91" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:13">
@@ -5727,16 +5739,16 @@
         <v>330</v>
       </c>
       <c r="C92" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D92" s="7">
         <v>0.2</v>
       </c>
       <c r="E92" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G92" s="7">
         <v>260</v>
@@ -5745,13 +5757,13 @@
         <v>130</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L92" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="93" spans="2:13">
@@ -5759,16 +5771,16 @@
         <v>331</v>
       </c>
       <c r="C93" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D93" s="7">
         <v>0.2</v>
       </c>
       <c r="E93" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F93" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G93" s="7">
         <v>160</v>
@@ -5777,13 +5789,13 @@
         <v>80</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K93" s="7">
         <v>1</v>
       </c>
       <c r="L93" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="94" s="5" customFormat="1" spans="2:13">
@@ -5791,16 +5803,16 @@
         <v>332</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D94" s="15">
         <v>0.2</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="G94" s="15">
         <v>200</v>
@@ -5809,7 +5821,7 @@
         <v>100</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J94" s="17">
         <v>11005</v>
@@ -5818,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="L94" s="14" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:13">
@@ -5833,10 +5845,10 @@
     </row>
     <row r="96" s="1" customFormat="1" spans="2:13">
       <c r="B96" s="1" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D96" s="7">
         <v>0.1</v>
@@ -5845,7 +5857,7 @@
         <v>235</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="G96" s="7">
         <v>650</v>
@@ -5854,7 +5866,7 @@
         <v>325</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J96" s="7">
         <v>11001</v>
@@ -5863,24 +5875,24 @@
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:13">
       <c r="B97" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="D97" s="7">
         <v>0.1</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="G97" s="7">
         <v>680</v>
@@ -5889,31 +5901,31 @@
         <v>340</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7">
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:13">
       <c r="B98" s="1" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D98" s="7">
         <v>0.1</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G98" s="7">
         <v>600</v>
@@ -5922,30 +5934,30 @@
         <v>300</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="K98" s="7">
         <v>0</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" spans="2:13">
       <c r="B99" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D99" s="8">
         <v>0.1</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="G99" s="8">
         <v>480</v>
@@ -5954,7 +5966,7 @@
         <v>240</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="J99" s="8">
         <v>11002</v>
@@ -5963,24 +5975,24 @@
         <v>0</v>
       </c>
       <c r="L99" s="9" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:13">
       <c r="B100" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D100" s="7">
         <v>0.1</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G100" s="7">
         <v>460</v>
@@ -5989,31 +6001,31 @@
         <v>230</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="J100" s="7"/>
       <c r="K100" s="7">
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:13">
       <c r="B101" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D101" s="7">
         <v>0.1</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G101" s="7">
         <v>320</v>
@@ -6022,30 +6034,30 @@
         <v>160</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="K101" s="7">
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" spans="2:13">
       <c r="B102" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D102" s="8">
         <v>0.1</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G102" s="8">
         <v>380</v>
@@ -6054,7 +6066,7 @@
         <v>190</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="J102" s="16">
         <v>11003</v>
@@ -6063,24 +6075,24 @@
         <v>0</v>
       </c>
       <c r="L102" s="9" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:13">
       <c r="B103" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D103" s="7">
         <v>0.1</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="G103" s="7">
         <v>600</v>
@@ -6089,31 +6101,31 @@
         <v>300</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="J103" s="7"/>
       <c r="K103" s="7">
         <v>0</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="2:13">
       <c r="B104" s="1" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D104" s="7">
         <v>0.1</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="G104" s="7">
         <v>280</v>
@@ -6122,30 +6134,30 @@
         <v>140</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="K104" s="7">
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="105" s="2" customFormat="1" spans="2:13">
       <c r="B105" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D105" s="8">
         <v>0.1</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G105" s="8">
         <v>300</v>
@@ -6154,30 +6166,30 @@
         <v>150</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="K105" s="8">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="106" spans="2:13">
       <c r="B106" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D106" s="7">
         <v>0.1</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G106" s="7">
         <v>400</v>
@@ -6186,7 +6198,7 @@
         <v>200</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="J106" s="16">
         <v>11004</v>
@@ -6195,24 +6207,24 @@
         <v>0</v>
       </c>
       <c r="L106" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="107" s="2" customFormat="1" spans="2:13">
       <c r="B107" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D107" s="8">
         <v>0.1</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G107" s="8">
         <v>460</v>
@@ -6221,32 +6233,32 @@
         <v>230</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="J107" s="8"/>
       <c r="K107" s="8">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="M107" s="9"/>
     </row>
     <row r="108" spans="2:13">
       <c r="B108" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D108" s="7">
         <v>0.1</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G108" s="7">
         <v>340</v>
@@ -6255,7 +6267,7 @@
         <v>170</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="J108" s="7">
         <v>10602</v>
@@ -6264,24 +6276,24 @@
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="109" spans="2:13">
       <c r="B109" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D109" s="7">
         <v>0.1</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G109" s="7">
         <v>280</v>
@@ -6290,30 +6302,30 @@
         <v>140</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="K109" s="7">
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="110" spans="2:13">
       <c r="B110" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D110" s="7">
         <v>0.1</v>
       </c>
       <c r="E110" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G110" s="7">
         <v>600</v>
@@ -6322,30 +6334,30 @@
         <v>300</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="K110" s="7">
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="111" spans="2:13">
       <c r="B111" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D111" s="7">
         <v>0.1</v>
       </c>
       <c r="E111" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G111" s="7">
         <v>280</v>
@@ -6363,24 +6375,24 @@
         <v>0</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="112" spans="2:13">
       <c r="B112" s="1" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D112" s="7">
         <v>0.1</v>
       </c>
       <c r="E112" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="G112" s="7">
         <v>300</v>
@@ -6395,24 +6407,24 @@
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="113" spans="1:13">
       <c r="B113" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D113" s="7">
         <v>0.1</v>
       </c>
       <c r="E113" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="G113" s="7">
         <v>520</v>
@@ -6430,24 +6442,24 @@
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="114" spans="1:13">
       <c r="B114" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D114" s="7">
         <v>0.1</v>
       </c>
       <c r="E114" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G114" s="7">
         <v>300</v>
@@ -6462,24 +6474,24 @@
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" spans="1:13">
       <c r="B115" s="1" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D115" s="7">
         <v>0.1</v>
       </c>
       <c r="E115" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G115" s="7">
         <v>560</v>
@@ -6495,25 +6507,25 @@
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="M115"/>
     </row>
     <row r="116" spans="1:13">
       <c r="B116" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D116" s="7">
         <v>0.1</v>
       </c>
       <c r="E116" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G116" s="7">
         <v>620</v>
@@ -6528,24 +6540,24 @@
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="117" spans="1:13">
       <c r="B117" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D117" s="7">
         <v>0.1</v>
       </c>
       <c r="E117" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="G117" s="7">
         <v>320</v>
@@ -6554,7 +6566,7 @@
         <v>160</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="J117" s="16">
         <v>11201</v>
@@ -6563,24 +6575,24 @@
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="118" s="2" customFormat="1" spans="1:13">
       <c r="B118" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D118" s="8">
         <v>0.1</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G118" s="8">
         <v>320</v>
@@ -6598,25 +6610,25 @@
         <v>0</v>
       </c>
       <c r="L118" s="9" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="M118" s="9"/>
     </row>
     <row r="119" spans="1:13">
       <c r="B119" s="1" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D119" s="7">
         <v>0.1</v>
       </c>
       <c r="E119" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G119" s="7">
         <v>550</v>
@@ -6634,24 +6646,24 @@
         <v>0</v>
       </c>
       <c r="L119" s="7" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="120" spans="1:13">
       <c r="B120" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D120" s="7">
         <v>0.1</v>
       </c>
       <c r="E120" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G120" s="7">
         <v>300</v>
@@ -6666,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="121" s="2" customFormat="1" spans="1:13">
@@ -6674,16 +6686,16 @@
         <v>426</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D121" s="8">
         <v>0.1</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F121" s="9" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="G121" s="8">
         <v>400</v>
@@ -6701,7 +6713,7 @@
         <v>1</v>
       </c>
       <c r="L121" s="9" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M121" s="9"/>
     </row>
@@ -6710,16 +6722,16 @@
         <v>427</v>
       </c>
       <c r="C122" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D122" s="7">
         <v>0.1</v>
       </c>
       <c r="E122" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F122" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="G122" s="7">
         <v>330</v>
@@ -6734,7 +6746,7 @@
         <v>1</v>
       </c>
       <c r="L122" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="123" s="2" customFormat="1" spans="1:13">
@@ -6742,16 +6754,16 @@
         <v>428</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D123" s="8">
         <v>0.1</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="G123" s="8">
         <v>260</v>
@@ -6767,7 +6779,7 @@
         <v>2</v>
       </c>
       <c r="L123" s="9" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="M123" s="9"/>
     </row>
@@ -6776,16 +6788,16 @@
         <v>429</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D124" s="8">
         <v>0.1</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G124" s="8">
         <v>270</v>
@@ -6801,7 +6813,7 @@
         <v>2</v>
       </c>
       <c r="L124" s="9" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="M124" s="9"/>
     </row>
@@ -6810,16 +6822,16 @@
         <v>430</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D125" s="8">
         <v>0.1</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="G125" s="8">
         <v>280</v>
@@ -6837,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="L125" s="9" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="M125" s="9"/>
     </row>
@@ -6847,16 +6859,16 @@
         <v>431</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D126" s="8">
         <v>0.1</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="G126" s="2">
         <v>260</v>
@@ -6872,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="L126" s="9" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="M126" s="9"/>
     </row>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16830" windowHeight="11025"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="558">
   <si>
     <t>##var</t>
   </si>
@@ -964,6 +964,738 @@
     <t>每次进入商店提供1次免费刷新的机会</t>
   </si>
   <si>
+    <t>致命黑八</t>
+  </si>
+  <si>
+    <t>DeadlyBlackEight</t>
+  </si>
+  <si>
+    <t>30007</t>
+  </si>
+  <si>
+    <t>亮出的每张8在结算时提供+100攻击力</t>
+  </si>
+  <si>
+    <t>偶数韵律</t>
+  </si>
+  <si>
+    <t>EvenRhythm</t>
+  </si>
+  <si>
+    <t>30008</t>
+  </si>
+  <si>
+    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>奇数韵律</t>
+  </si>
+  <si>
+    <t>OddRhythm</t>
+  </si>
+  <si>
+    <t>30009</t>
+  </si>
+  <si>
+    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
+  </si>
+  <si>
+    <t>贵族</t>
+  </si>
+  <si>
+    <t>Noble</t>
+  </si>
+  <si>
+    <t>30010</t>
+  </si>
+  <si>
+    <t>亮出的每张人头牌在结算时提供+4倍率</t>
+  </si>
+  <si>
+    <t>工资卡</t>
+  </si>
+  <si>
+    <t>SalaryCard</t>
+  </si>
+  <si>
+    <t>30011</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,这件圣物的出售价格+10金币</t>
+  </si>
+  <si>
+    <t>训练</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>回合首次亮牌时,随机有1张牌提供的攻击力永久+1</t>
+  </si>
+  <si>
+    <t>九霄云外</t>
+  </si>
+  <si>
+    <t>BeyondTheClouds</t>
+  </si>
+  <si>
+    <t>30013</t>
+  </si>
+  <si>
+    <t>亮出的每张9在结算时提供30金币</t>
+  </si>
+  <si>
+    <t>后备计划</t>
+  </si>
+  <si>
+    <t>BackupPlan</t>
+  </si>
+  <si>
+    <t>30014</t>
+  </si>
+  <si>
+    <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点血量</t>
+  </si>
+  <si>
+    <t>护身符</t>
+  </si>
+  <si>
+    <t>Amulet</t>
+  </si>
+  <si>
+    <t>30015</t>
+  </si>
+  <si>
+    <t>每关受到的首次伤害完全免疫</t>
+  </si>
+  <si>
+    <t>复盘笔记</t>
+  </si>
+  <si>
+    <t>ReviewPlan</t>
+  </si>
+  <si>
+    <t>30016</t>
+  </si>
+  <si>
+    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
+  </si>
+  <si>
+    <t>幸运同花</t>
+  </si>
+  <si>
+    <t>LuckySameSuit</t>
+  </si>
+  <si>
+    <t>30017</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
+  </si>
+  <si>
+    <t>逆转沙漏</t>
+  </si>
+  <si>
+    <t>ReverseHourglass</t>
+  </si>
+  <si>
+    <t>30018</t>
+  </si>
+  <si>
+    <t>当牌型小于敌人时,有50%概率反转对比结果,但伤害按自身牌型计算</t>
+  </si>
+  <si>
+    <t>练习卷</t>
+  </si>
+  <si>
+    <t>PracticePaper</t>
+  </si>
+  <si>
+    <t>30019</t>
+  </si>
+  <si>
+    <t>每击杀1名敌人,结算时就永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>小本本</t>
+  </si>
+  <si>
+    <t>LittleNotebook</t>
+  </si>
+  <si>
+    <t>30020</t>
+  </si>
+  <si>
+    <t>本局内,对自己曾经输过的敌人造成伤害时,伤害+50%</t>
+  </si>
+  <si>
+    <t>高贵徽章</t>
+  </si>
+  <si>
+    <t>NobleBadge</t>
+  </si>
+  <si>
+    <t>30021</t>
+  </si>
+  <si>
+    <t>每关开始时,若血量高于50%,则获得50金币</t>
+  </si>
+  <si>
+    <t>陷阱</t>
+  </si>
+  <si>
+    <t>Trap</t>
+  </si>
+  <si>
+    <t>30022</t>
+  </si>
+  <si>
+    <t>本局内,曾经赢过自己的敌人在造成伤害时,伤害-30%</t>
+  </si>
+  <si>
+    <t>好运来</t>
+  </si>
+  <si>
+    <t>LuckComes</t>
+  </si>
+  <si>
+    <t>30023</t>
+  </si>
+  <si>
+    <t>每回合有25%概率使本回合所有敌人亮出的牌型顺位降1级</t>
+  </si>
+  <si>
+    <t>入场券</t>
+  </si>
+  <si>
+    <t>AdmissionTicket</t>
+  </si>
+  <si>
+    <t>30024</t>
+  </si>
+  <si>
+    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>条约</t>
+  </si>
+  <si>
+    <t>Treaty</t>
+  </si>
+  <si>
+    <t>30025</t>
+  </si>
+  <si>
+    <t>所有敌人造成的伤害降低30%</t>
+  </si>
+  <si>
+    <t>豹子精髓</t>
+  </si>
+  <si>
+    <t>LeopardEssence</t>
+  </si>
+  <si>
+    <t>30026</t>
+  </si>
+  <si>
+    <t>使用后,本局内你亮出豹子时,就会获得300金币</t>
+  </si>
+  <si>
+    <t>时之沙</t>
+  </si>
+  <si>
+    <t>TimeSand</t>
+  </si>
+  <si>
+    <t>30027</t>
+  </si>
+  <si>
+    <t>使用后,本关内你比牌获胜时的伤害+20%</t>
+  </si>
+  <si>
+    <t>巨人药剂</t>
+  </si>
+  <si>
+    <t>GiantPotion</t>
+  </si>
+  <si>
+    <t>30028</t>
+  </si>
+  <si>
+    <t>使用后,玩家生命上限+80,并立即恢复80点血量</t>
+  </si>
+  <si>
+    <t>净化药水</t>
+  </si>
+  <si>
+    <t>PurifyPotion</t>
+  </si>
+  <si>
+    <t>30031</t>
+  </si>
+  <si>
+    <t>使用后,移除本关内的1条BOSS词缀效果</t>
+  </si>
+  <si>
+    <t>三花聚顶</t>
+  </si>
+  <si>
+    <t>ThreeFlowersGatherAtTheTop</t>
+  </si>
+  <si>
+    <t>30032</t>
+  </si>
+  <si>
+    <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>TwoThreeFive</t>
+  </si>
+  <si>
+    <t>40001</t>
+  </si>
+  <si>
+    <t>高牌235等同于豹子牌型,并且可以战胜所有牌型</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>奢华沙发</t>
+  </si>
+  <si>
+    <t>LuxurySofa</t>
+  </si>
+  <si>
+    <t>40002</t>
+  </si>
+  <si>
+    <t>获得500点生命上限</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>老花眼</t>
+  </si>
+  <si>
+    <t>Presbyopia</t>
+  </si>
+  <si>
+    <t>40003</t>
+  </si>
+  <si>
+    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>周星星</t>
+  </si>
+  <si>
+    <t>ZhouXingxing</t>
+  </si>
+  <si>
+    <t>40004</t>
+  </si>
+  <si>
+    <t>每关[搓牌]使用次数+1</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>穷途末路</t>
+  </si>
+  <si>
+    <t>DeadEnd</t>
+  </si>
+  <si>
+    <t>40005</t>
+  </si>
+  <si>
+    <t>结算时,若所有技能都无剩余使用次数,则提供+12倍率</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>收藏夹</t>
+  </si>
+  <si>
+    <t>FavoriteFolder</t>
+  </si>
+  <si>
+    <t>40006</t>
+  </si>
+  <si>
+    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>奢侈品</t>
+  </si>
+  <si>
+    <t>LuxuryGoods</t>
+  </si>
+  <si>
+    <t>40007</t>
+  </si>
+  <si>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+3倍率</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>近视眼</t>
+  </si>
+  <si>
+    <t>Myopia</t>
+  </si>
+  <si>
+    <t>40008</t>
+  </si>
+  <si>
+    <t>所有牌均视为人头牌</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>顶尖学者</t>
+  </si>
+  <si>
+    <t>TopScholar</t>
+  </si>
+  <si>
+    <t>40009|400091</t>
+  </si>
+  <si>
+    <t>亮出的每张A在结算伤害时提供+66攻击力和+6倍率</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>老千</t>
+  </si>
+  <si>
+    <t>CheatPlayer</t>
+  </si>
+  <si>
+    <t>40010</t>
+  </si>
+  <si>
+    <t>亮牌时,该牌型本局内每重复亮出1次就提供+1倍率</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>天使</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>40011</t>
+  </si>
+  <si>
+    <t>亮牌时,有50%概率将该牌型提供的倍率永久+1</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>双刃剑</t>
+  </si>
+  <si>
+    <t>DoubleEdgedSword</t>
+  </si>
+  <si>
+    <t>40012|400121</t>
+  </si>
+  <si>
+    <t>失去2次搓牌机会,但结算时提供+15倍率</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>老搓家</t>
+  </si>
+  <si>
+    <t>OldCardPlayer</t>
+  </si>
+  <si>
+    <t>40013</t>
+  </si>
+  <si>
+    <t>每使用1次搓牌,该圣物永久提供+0.1倍率</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>幸运七</t>
+  </si>
+  <si>
+    <t>LuckySeven</t>
+  </si>
+  <si>
+    <t>40014|400141|400142</t>
+  </si>
+  <si>
+    <t>亮出的每张7结算时必定提供+77攻击力和+7倍率</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>武林秘籍</t>
+  </si>
+  <si>
+    <t>MartialSecretBook</t>
+  </si>
+  <si>
+    <t>40015|400151</t>
+  </si>
+  <si>
+    <t>获得50%闪避率,且闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>幸运对子</t>
+  </si>
+  <si>
+    <t>LuckyPair</t>
+  </si>
+  <si>
+    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>小强</t>
+  </si>
+  <si>
+    <t>LittleCockroach</t>
+  </si>
+  <si>
+    <t>每输1次敌人,后续自身造成的伤害提高10%</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>救命稻草</t>
+  </si>
+  <si>
+    <t>LifeSavingStraw</t>
+  </si>
+  <si>
+    <t>受到致命伤害时血量降为1,且下次造成伤害时回复该伤害20%的血量,每关生效1次</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>专注</t>
+  </si>
+  <si>
+    <t>Concentration</t>
+  </si>
+  <si>
+    <t>当场上只剩一个敌人时,对其造成的伤害+100%</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>毒药</t>
+  </si>
+  <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>所有敌人血量降低30%[BOSS除外]</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>刺客秘籍</t>
+  </si>
+  <si>
+    <t>AssassinSecretBook</t>
+  </si>
+  <si>
+    <t>40022|400221</t>
+  </si>
+  <si>
+    <t>获得50%暴击率,且触发暴击时会对其他敌人造成1次自身攻击力的伤害</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>透视眼</t>
+  </si>
+  <si>
+    <t>PerspectiveEye</t>
+  </si>
+  <si>
+    <t>每关[透视]使用次数+1</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>TreasurePot</t>
+  </si>
+  <si>
+    <t>每回合结束后,本回合自身总伤害输出的20%转化为金币</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>差距胶囊</t>
+  </si>
+  <si>
+    <t>GapCapsule</t>
+  </si>
+  <si>
+    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>神之左手</t>
+  </si>
+  <si>
+    <t>GodLeftHand</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你造成的伤害提高200%</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>凤凰羽毛</t>
+  </si>
+  <si>
+    <t>PhoenixFeather</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你受到的所有伤害变为0,并恢复30%血量</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>时光宝盒</t>
+  </si>
+  <si>
+    <t>TimeTreasureBox</t>
+  </si>
+  <si>
+    <t>使用后,随机3种牌型的提供的倍率永久+5</t>
+  </si>
+  <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>龙心</t>
+  </si>
+  <si>
+    <t>DragonHeart</t>
+  </si>
+  <si>
+    <t>使用后,获得120点生命上限,并立即恢复120点血量</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>贪欲之冠</t>
+  </si>
+  <si>
+    <t>GreedCrown</t>
+  </si>
+  <si>
+    <t>每拥有40金币,你造成的伤害+10%,至多叠加20层</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>旗帜</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>降低</t>
+  </si>
+  <si>
+    <t>LowerStatus</t>
+  </si>
+  <si>
+    <t>30029</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>比牌时,对方的牌型顺位降低1级</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>升职</t>
+  </si>
+  <si>
+    <t>Promote</t>
+  </si>
+  <si>
+    <t>30030</t>
+  </si>
+  <si>
+    <t>比牌时,自己的牌型顺位提高1级</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
     <t>错峰出行</t>
   </si>
   <si>
@@ -974,723 +1706,6 @@
   </si>
   <si>
     <t>顺子牌型可以相隔1点组成[例如:2,4,5]</t>
-  </si>
-  <si>
-    <t>致命黑八</t>
-  </si>
-  <si>
-    <t>DeadlyBlackEight</t>
-  </si>
-  <si>
-    <t>30007</t>
-  </si>
-  <si>
-    <t>亮出的每张8在结算时提供+100攻击力</t>
-  </si>
-  <si>
-    <t>偶数韵律</t>
-  </si>
-  <si>
-    <t>EvenRhythm</t>
-  </si>
-  <si>
-    <t>30008</t>
-  </si>
-  <si>
-    <t>亮出的每张偶数牌[2、4、6、8、10]在结算时提供+2倍率</t>
-  </si>
-  <si>
-    <t>奇数韵律</t>
-  </si>
-  <si>
-    <t>OddRhythm</t>
-  </si>
-  <si>
-    <t>30009</t>
-  </si>
-  <si>
-    <t>亮出的每张奇数牌[A、3、5、7、9]在结算时提供+2倍率</t>
-  </si>
-  <si>
-    <t>贵族</t>
-  </si>
-  <si>
-    <t>Noble</t>
-  </si>
-  <si>
-    <t>30010</t>
-  </si>
-  <si>
-    <t>亮出的每张人头牌在结算时提供+4倍率</t>
-  </si>
-  <si>
-    <t>工资卡</t>
-  </si>
-  <si>
-    <t>SalaryCard</t>
-  </si>
-  <si>
-    <t>30011</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,这件圣物的出售价格+10金币</t>
-  </si>
-  <si>
-    <t>训练</t>
-  </si>
-  <si>
-    <t>Training</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>回合首次亮牌时,随机有1张牌提供的攻击力永久+1</t>
-  </si>
-  <si>
-    <t>九霄云外</t>
-  </si>
-  <si>
-    <t>BeyondTheClouds</t>
-  </si>
-  <si>
-    <t>30013</t>
-  </si>
-  <si>
-    <t>亮出的每张9在结算时提供30金币</t>
-  </si>
-  <si>
-    <t>后备计划</t>
-  </si>
-  <si>
-    <t>BackupPlan</t>
-  </si>
-  <si>
-    <t>30014</t>
-  </si>
-  <si>
-    <t>如果本回合牌型小于所有敌人,则立即获得15金币并回复20点血量</t>
-  </si>
-  <si>
-    <t>护身符</t>
-  </si>
-  <si>
-    <t>Amulet</t>
-  </si>
-  <si>
-    <t>30015</t>
-  </si>
-  <si>
-    <t>每关受到的首次伤害完全免疫</t>
-  </si>
-  <si>
-    <t>复盘笔记</t>
-  </si>
-  <si>
-    <t>ReviewPlan</t>
-  </si>
-  <si>
-    <t>30016</t>
-  </si>
-  <si>
-    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
-  </si>
-  <si>
-    <t>幸运同花</t>
-  </si>
-  <si>
-    <t>LuckySameSuit</t>
-  </si>
-  <si>
-    <t>30017</t>
-  </si>
-  <si>
-    <t>亮牌时,若敌人的牌型大于同花,则会被强行视作同花</t>
-  </si>
-  <si>
-    <t>逆转沙漏</t>
-  </si>
-  <si>
-    <t>ReverseHourglass</t>
-  </si>
-  <si>
-    <t>30018</t>
-  </si>
-  <si>
-    <t>当牌型小于敌人时,有50%概率反转对比结果,但伤害按自身牌型计算</t>
-  </si>
-  <si>
-    <t>练习卷</t>
-  </si>
-  <si>
-    <t>PracticePaper</t>
-  </si>
-  <si>
-    <t>30019</t>
-  </si>
-  <si>
-    <t>每击杀1名敌人,结算时就永久提供+0.5倍率</t>
-  </si>
-  <si>
-    <t>小本本</t>
-  </si>
-  <si>
-    <t>LittleNotebook</t>
-  </si>
-  <si>
-    <t>30020</t>
-  </si>
-  <si>
-    <t>本局内,对自己曾经输过的敌人造成伤害时,伤害+50%</t>
-  </si>
-  <si>
-    <t>高贵徽章</t>
-  </si>
-  <si>
-    <t>NobleBadge</t>
-  </si>
-  <si>
-    <t>30021</t>
-  </si>
-  <si>
-    <t>每关开始时,若血量高于50%,则获得50金币</t>
-  </si>
-  <si>
-    <t>陷阱</t>
-  </si>
-  <si>
-    <t>Trap</t>
-  </si>
-  <si>
-    <t>30022</t>
-  </si>
-  <si>
-    <t>本局内,曾经赢过自己的敌人在造成伤害时,伤害-30%</t>
-  </si>
-  <si>
-    <t>好运来</t>
-  </si>
-  <si>
-    <t>LuckComes</t>
-  </si>
-  <si>
-    <t>30023</t>
-  </si>
-  <si>
-    <t>每回合有50%概率使本回合所有敌人亮出的牌型顺位降1级</t>
-  </si>
-  <si>
-    <t>入场券</t>
-  </si>
-  <si>
-    <t>AdmissionTicket</t>
-  </si>
-  <si>
-    <t>30024</t>
-  </si>
-  <si>
-    <t>每回合开始时,对所有敌人造成1次自身攻击力的伤害</t>
-  </si>
-  <si>
-    <t>条约</t>
-  </si>
-  <si>
-    <t>Treaty</t>
-  </si>
-  <si>
-    <t>30025</t>
-  </si>
-  <si>
-    <t>所有敌人造成的伤害降低30%</t>
-  </si>
-  <si>
-    <t>豹子精髓</t>
-  </si>
-  <si>
-    <t>LeopardEssence</t>
-  </si>
-  <si>
-    <t>30026</t>
-  </si>
-  <si>
-    <t>使用后,本局内你亮出豹子时,就会获得300金币</t>
-  </si>
-  <si>
-    <t>时之沙</t>
-  </si>
-  <si>
-    <t>TimeSand</t>
-  </si>
-  <si>
-    <t>30027</t>
-  </si>
-  <si>
-    <t>使用后,本关内你比牌获胜时的伤害+20%</t>
-  </si>
-  <si>
-    <t>巨人药剂</t>
-  </si>
-  <si>
-    <t>GiantPotion</t>
-  </si>
-  <si>
-    <t>30028</t>
-  </si>
-  <si>
-    <t>使用后,玩家生命上限+80,并立即恢复80点血量</t>
-  </si>
-  <si>
-    <t>降低</t>
-  </si>
-  <si>
-    <t>LowerStatus</t>
-  </si>
-  <si>
-    <t>30029</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>比牌时,对方的牌型顺位降低1级</t>
-  </si>
-  <si>
-    <t>升职</t>
-  </si>
-  <si>
-    <t>Promote</t>
-  </si>
-  <si>
-    <t>30030</t>
-  </si>
-  <si>
-    <t>比牌时,自己的牌型顺位提高1级</t>
-  </si>
-  <si>
-    <t>净化药水</t>
-  </si>
-  <si>
-    <t>PurifyPotion</t>
-  </si>
-  <si>
-    <t>30031</t>
-  </si>
-  <si>
-    <t>使用后,移除本关内的1条BOSS词缀效果</t>
-  </si>
-  <si>
-    <t>三花聚顶</t>
-  </si>
-  <si>
-    <t>ThreeFlowersGatherAtTheTop</t>
-  </si>
-  <si>
-    <t>30032</t>
-  </si>
-  <si>
-    <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>Legend</t>
-  </si>
-  <si>
-    <t>TwoThreeFive</t>
-  </si>
-  <si>
-    <t>40001</t>
-  </si>
-  <si>
-    <t>高牌235等同于豹子牌型,并且可以战胜所有牌型</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>奢华沙发</t>
-  </si>
-  <si>
-    <t>LuxurySofa</t>
-  </si>
-  <si>
-    <t>40002</t>
-  </si>
-  <si>
-    <t>获得500点生命上限</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>老花眼</t>
-  </si>
-  <si>
-    <t>Presbyopia</t>
-  </si>
-  <si>
-    <t>40003</t>
-  </si>
-  <si>
-    <t>红桃和方片视为同一花色,黑桃和梅花视为同一花色</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>周星星</t>
-  </si>
-  <si>
-    <t>ZhouXingxing</t>
-  </si>
-  <si>
-    <t>40004</t>
-  </si>
-  <si>
-    <t>每关[搓牌]使用次数+1</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>穷途末路</t>
-  </si>
-  <si>
-    <t>DeadEnd</t>
-  </si>
-  <si>
-    <t>40005</t>
-  </si>
-  <si>
-    <t>结算时,若所有技能都无剩余使用次数,则提供+12倍率</t>
-  </si>
-  <si>
-    <t>406</t>
-  </si>
-  <si>
-    <t>收藏夹</t>
-  </si>
-  <si>
-    <t>FavoriteFolder</t>
-  </si>
-  <si>
-    <t>40006</t>
-  </si>
-  <si>
-    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>奢侈品</t>
-  </si>
-  <si>
-    <t>LuxuryGoods</t>
-  </si>
-  <si>
-    <t>40007</t>
-  </si>
-  <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+3倍率</t>
-  </si>
-  <si>
-    <t>408</t>
-  </si>
-  <si>
-    <t>近视眼</t>
-  </si>
-  <si>
-    <t>Myopia</t>
-  </si>
-  <si>
-    <t>40008</t>
-  </si>
-  <si>
-    <t>所有牌均视为人头牌</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>顶尖学者</t>
-  </si>
-  <si>
-    <t>TopScholar</t>
-  </si>
-  <si>
-    <t>40009|400091</t>
-  </si>
-  <si>
-    <t>亮出的每张A在结算伤害时提供+66攻击力和+6倍率</t>
-  </si>
-  <si>
-    <t>410</t>
-  </si>
-  <si>
-    <t>老千</t>
-  </si>
-  <si>
-    <t>CheatPlayer</t>
-  </si>
-  <si>
-    <t>40010</t>
-  </si>
-  <si>
-    <t>亮牌时,该牌型本局内每重复亮出1次就提供+1倍率</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>天使</t>
-  </si>
-  <si>
-    <t>Angel</t>
-  </si>
-  <si>
-    <t>40011</t>
-  </si>
-  <si>
-    <t>亮牌时,有50%概率将该牌型提供的倍率永久+1</t>
-  </si>
-  <si>
-    <t>412</t>
-  </si>
-  <si>
-    <t>双刃剑</t>
-  </si>
-  <si>
-    <t>DoubleEdgedSword</t>
-  </si>
-  <si>
-    <t>40012|400121</t>
-  </si>
-  <si>
-    <t>失去2次搓牌机会,但结算时提供+15倍率</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>老搓家</t>
-  </si>
-  <si>
-    <t>OldCardPlayer</t>
-  </si>
-  <si>
-    <t>40013</t>
-  </si>
-  <si>
-    <t>每使用1次搓牌,该圣物永久提供+0.1倍率</t>
-  </si>
-  <si>
-    <t>414</t>
-  </si>
-  <si>
-    <t>幸运七</t>
-  </si>
-  <si>
-    <t>LuckySeven</t>
-  </si>
-  <si>
-    <t>40014|400141|400142</t>
-  </si>
-  <si>
-    <t>亮出的每张7结算时必定提供+77攻击力和+7倍率</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>武林秘籍</t>
-  </si>
-  <si>
-    <t>MartialSecretBook</t>
-  </si>
-  <si>
-    <t>40015|400151</t>
-  </si>
-  <si>
-    <t>获得50%闪避率,且闪避成功时会对敌人造成1次自身攻击力200%的伤害</t>
-  </si>
-  <si>
-    <t>416</t>
-  </si>
-  <si>
-    <t>幸运对子</t>
-  </si>
-  <si>
-    <t>LuckyPair</t>
-  </si>
-  <si>
-    <t>亮牌时,若敌人的牌型大于对子,则会被强行视作对子</t>
-  </si>
-  <si>
-    <t>417</t>
-  </si>
-  <si>
-    <t>小强</t>
-  </si>
-  <si>
-    <t>LittleCockroach</t>
-  </si>
-  <si>
-    <t>每输1次敌人,后续自身造成的伤害提高10%</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>救命稻草</t>
-  </si>
-  <si>
-    <t>LifeSavingStraw</t>
-  </si>
-  <si>
-    <t>受到致命伤害时血量降为1,且下次造成伤害时回复该伤害20%的血量,每关生效1次</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>专注</t>
-  </si>
-  <si>
-    <t>Concentration</t>
-  </si>
-  <si>
-    <t>当场上只剩一个敌人时,对其造成的伤害+100%</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>变形魔方</t>
-  </si>
-  <si>
-    <t>TransformCube</t>
-  </si>
-  <si>
-    <t>每回合亮出的牌型顺位提升一级</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>毒药</t>
-  </si>
-  <si>
-    <t>Poison</t>
-  </si>
-  <si>
-    <t>所有敌人血量降低30%[BOSS除外]</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>刺客秘籍</t>
-  </si>
-  <si>
-    <t>AssassinSecretBook</t>
-  </si>
-  <si>
-    <t>40022|400221</t>
-  </si>
-  <si>
-    <t>获得50%暴击率,且触发暴击时会对其他敌人造成1次自身攻击力的伤害</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>透视眼</t>
-  </si>
-  <si>
-    <t>PerspectiveEye</t>
-  </si>
-  <si>
-    <t>每关[透视]使用次数+1</t>
-  </si>
-  <si>
-    <t>424</t>
-  </si>
-  <si>
-    <t>聚宝盆</t>
-  </si>
-  <si>
-    <t>TreasurePot</t>
-  </si>
-  <si>
-    <t>每回合结束后,本回合自身总伤害输出的20%转化为金币</t>
-  </si>
-  <si>
-    <t>425</t>
-  </si>
-  <si>
-    <t>差距胶囊</t>
-  </si>
-  <si>
-    <t>GapCapsule</t>
-  </si>
-  <si>
-    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
-  </si>
-  <si>
-    <t>神之左手</t>
-  </si>
-  <si>
-    <t>GodLeftHand</t>
-  </si>
-  <si>
-    <t>使用后,本次比牌你造成的伤害提高200%</t>
-  </si>
-  <si>
-    <t>凤凰羽毛</t>
-  </si>
-  <si>
-    <t>PhoenixFeather</t>
-  </si>
-  <si>
-    <t>使用后,本次比牌你受到的所有伤害变为0,并恢复30%血量</t>
-  </si>
-  <si>
-    <t>时光宝盒</t>
-  </si>
-  <si>
-    <t>TimeTreasureBox</t>
-  </si>
-  <si>
-    <t>使用后,随机3种牌型的提供的倍率永久+5</t>
-  </si>
-  <si>
-    <t>龙心</t>
-  </si>
-  <si>
-    <t>DragonHeart</t>
-  </si>
-  <si>
-    <t>使用后,获得120点生命上限,并立即恢复120点血量</t>
-  </si>
-  <si>
-    <t>贪欲之冠</t>
-  </si>
-  <si>
-    <t>GreedCrown</t>
-  </si>
-  <si>
-    <t>每拥有40金币,你造成的伤害+10%,至多叠加20层</t>
-  </si>
-  <si>
-    <t>旗帜</t>
-  </si>
-  <si>
-    <t>Flag</t>
-  </si>
-  <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
   </si>
 </sst>
 </file>
@@ -1862,7 +1877,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1878,6 +1893,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2200,7 +2221,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -2224,16 +2245,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -2242,89 +2263,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2338,6 +2359,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -2374,7 +2398,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2725,21 +2761,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8" style="6" customWidth="1"/>
-    <col min="4" max="4" width="4.78333333333333" style="7" customWidth="1"/>
-    <col min="5" max="5" width="8.8" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.1083333333333" style="7" customWidth="1"/>
-    <col min="7" max="7" width="5.975" style="7" customWidth="1"/>
-    <col min="8" max="8" width="4.78333333333333" style="7" customWidth="1"/>
-    <col min="9" max="9" width="7.38333333333333" style="7" customWidth="1"/>
-    <col min="10" max="10" width="5.53333333333333" style="7" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="7" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="8" customWidth="1"/>
+    <col min="5" max="5" width="8.8" style="8" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" style="8" customWidth="1"/>
+    <col min="7" max="7" width="5.975" style="8" customWidth="1"/>
+    <col min="8" max="8" width="4.78333333333333" style="8" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="8" customWidth="1"/>
+    <col min="10" max="10" width="5.53333333333333" style="8" customWidth="1"/>
     <col min="11" max="11" width="8.03333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.70833333333333" style="7" customWidth="1"/>
+    <col min="12" max="12" width="7.70833333333333" style="8" customWidth="1"/>
     <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
@@ -2754,31 +2790,31 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2792,31 +2828,31 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2830,31 +2866,31 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2865,25 +2901,25 @@
       <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <v>0.8</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="8">
         <v>30</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="8">
         <v>15</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="8">
         <v>10001</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="8">
         <v>0</v>
       </c>
       <c r="L5" t="s">
@@ -2897,26 +2933,26 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <v>0.8</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="8">
         <v>28</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="8">
         <v>14</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <v>10002</v>
       </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7">
+      <c r="J6" s="8"/>
+      <c r="K6" s="8">
         <v>0</v>
       </c>
       <c r="L6" t="s">
@@ -2931,26 +2967,26 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <v>0.8</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="8">
         <v>28</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="8">
         <v>14</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="8">
         <v>10003</v>
       </c>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7">
+      <c r="J7" s="8"/>
+      <c r="K7" s="8">
         <v>0</v>
       </c>
       <c r="L7" t="s">
@@ -2965,26 +3001,26 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <v>0.8</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="8">
         <v>28</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <v>14</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="8">
         <v>10004</v>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7">
+      <c r="J8" s="8"/>
+      <c r="K8" s="8">
         <v>0</v>
       </c>
       <c r="L8" t="s">
@@ -2999,26 +3035,26 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <v>0.8</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="8">
         <v>28</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="8">
         <v>14</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="8">
         <v>10005</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8">
         <v>0</v>
       </c>
       <c r="L9" t="s">
@@ -3033,26 +3069,26 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <v>0.8</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="8">
         <v>28</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="8">
         <v>14</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="8">
         <v>10006</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8">
         <v>0</v>
       </c>
       <c r="L10" t="s">
@@ -3067,26 +3103,26 @@
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <v>0.8</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="8">
         <v>22</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="8">
         <v>11</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="8">
         <v>10007</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8">
         <v>0</v>
       </c>
       <c r="L11" t="s">
@@ -3101,26 +3137,26 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <v>0.8</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>35</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="8">
         <v>17</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="8">
         <v>10008</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7">
+      <c r="J12" s="8"/>
+      <c r="K12" s="8">
         <v>0</v>
       </c>
       <c r="L12" t="s">
@@ -3135,26 +3171,26 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <v>0.8</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="8">
         <v>16</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="8">
         <v>8</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="8">
         <v>10009</v>
       </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7">
+      <c r="J13" s="8"/>
+      <c r="K13" s="8">
         <v>0</v>
       </c>
       <c r="L13" t="s">
@@ -3169,26 +3205,26 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <v>0.8</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="8">
         <v>16</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="8">
         <v>8</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="8">
         <v>10010</v>
       </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7">
+      <c r="J14" s="8"/>
+      <c r="K14" s="8">
         <v>0</v>
       </c>
       <c r="L14" t="s">
@@ -3203,32 +3239,32 @@
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <v>0.8</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <v>15</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <v>7</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <v>10011</v>
       </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="9" t="s">
+      <c r="J15" s="9"/>
+      <c r="K15" s="9">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="9"/>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:13">
       <c r="B16" s="1" t="s">
@@ -3237,26 +3273,26 @@
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <v>0.8</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="8">
         <v>30</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="8">
         <v>15</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="8">
         <v>10012</v>
       </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8">
         <v>0</v>
       </c>
       <c r="L16" t="s">
@@ -3270,26 +3306,26 @@
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <v>0.8</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="8">
         <v>35</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="8">
         <v>17</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I17" s="8">
         <v>10013</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7">
+      <c r="J17" s="8"/>
+      <c r="K17" s="8">
         <v>0</v>
       </c>
       <c r="L17" t="s">
@@ -3303,26 +3339,26 @@
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <v>0.8</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="8">
         <v>26</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="8">
         <v>13</v>
       </c>
-      <c r="I18" s="7">
+      <c r="I18" s="8">
         <v>10014</v>
       </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7">
+      <c r="J18" s="8"/>
+      <c r="K18" s="8">
         <v>0</v>
       </c>
       <c r="L18" t="s">
@@ -3336,26 +3372,26 @@
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <v>0.8</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="8">
         <v>22</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="8">
         <v>11</v>
       </c>
-      <c r="I19" s="7">
+      <c r="I19" s="8">
         <v>10015</v>
       </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8">
         <v>0</v>
       </c>
       <c r="L19" t="s">
@@ -3369,29 +3405,29 @@
       <c r="C20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="9">
         <v>0.8</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G20" s="9">
         <v>28</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="9">
         <v>14</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="9">
         <v>10016</v>
       </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8">
-        <v>0</v>
-      </c>
-      <c r="L20" s="9" t="s">
+      <c r="J20" s="9"/>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3402,29 +3438,29 @@
       <c r="C21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="9">
         <v>0.8</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="9">
         <v>20</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="9">
         <v>10</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="9">
         <v>10017</v>
       </c>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8">
-        <v>0</v>
-      </c>
-      <c r="L21" s="9" t="s">
+      <c r="J21" s="9"/>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="10" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3435,7 +3471,7 @@
       <c r="C22" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <v>0.8</v>
       </c>
       <c r="E22" t="s">
@@ -3444,16 +3480,16 @@
       <c r="F22" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="8">
         <v>25</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="8">
         <v>12</v>
       </c>
-      <c r="I22" s="7">
+      <c r="I22" s="8">
         <v>10018</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="8">
         <v>1</v>
       </c>
       <c r="L22" t="s">
@@ -3467,7 +3503,7 @@
       <c r="C23" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <v>0.8</v>
       </c>
       <c r="E23" t="s">
@@ -3476,16 +3512,16 @@
       <c r="F23" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="8">
         <v>25</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="8">
         <v>12</v>
       </c>
-      <c r="I23" s="7">
+      <c r="I23" s="8">
         <v>10019</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23" s="8">
         <v>1</v>
       </c>
       <c r="L23" t="s">
@@ -3496,35 +3532,35 @@
       <c r="B24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="9">
         <v>0.8</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="9">
         <v>30</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="9">
         <v>15</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="9">
         <v>10020</v>
       </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="9" t="s">
+      <c r="J24" s="9"/>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="9"/>
+      <c r="M24" s="10"/>
     </row>
     <row r="25" spans="1:13">
       <c r="B25" s="1" t="s">
@@ -3533,7 +3569,7 @@
       <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <v>0.8</v>
       </c>
       <c r="E25" t="s">
@@ -3542,16 +3578,16 @@
       <c r="F25" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="8">
         <v>35</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="8">
         <v>17</v>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="8">
         <v>10021</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="8">
         <v>2</v>
       </c>
       <c r="L25" t="s">
@@ -3563,7 +3599,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="K26" s="7"/>
+      <c r="K26" s="8"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
       <c r="B27" s="1" t="s">
@@ -3572,13 +3608,13 @@
       <c r="C27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <v>0.4</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="8" t="s">
         <v>116</v>
       </c>
       <c r="G27" s="1">
@@ -3590,8 +3626,8 @@
       <c r="I27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7">
+      <c r="J27" s="8"/>
+      <c r="K27" s="8">
         <v>0</v>
       </c>
       <c r="L27" t="s">
@@ -3606,13 +3642,13 @@
       <c r="C28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <v>0.4</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="8" t="s">
         <v>121</v>
       </c>
       <c r="G28" s="1">
@@ -3624,8 +3660,8 @@
       <c r="I28" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7">
+      <c r="J28" s="8"/>
+      <c r="K28" s="8">
         <v>0</v>
       </c>
       <c r="L28" t="s">
@@ -3641,13 +3677,13 @@
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <v>0.4</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="8" t="s">
         <v>126</v>
       </c>
       <c r="G29" s="1">
@@ -3659,8 +3695,8 @@
       <c r="I29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7">
+      <c r="J29" s="8"/>
+      <c r="K29" s="8">
         <v>0</v>
       </c>
       <c r="L29" t="s">
@@ -3676,13 +3712,13 @@
       <c r="C30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <v>0.4</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="8" t="s">
         <v>131</v>
       </c>
       <c r="G30" s="1">
@@ -3694,8 +3730,8 @@
       <c r="I30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7">
+      <c r="J30" s="8"/>
+      <c r="K30" s="8">
         <v>0</v>
       </c>
       <c r="L30" t="s">
@@ -3711,13 +3747,13 @@
       <c r="C31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <v>0.4</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="8" t="s">
         <v>136</v>
       </c>
       <c r="G31" s="1">
@@ -3729,8 +3765,8 @@
       <c r="I31" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7">
+      <c r="J31" s="8"/>
+      <c r="K31" s="8">
         <v>0</v>
       </c>
       <c r="L31" t="s">
@@ -3746,13 +3782,13 @@
       <c r="C32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="8">
         <v>0.4</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="8" t="s">
         <v>141</v>
       </c>
       <c r="G32" s="1">
@@ -3764,8 +3800,8 @@
       <c r="I32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7">
+      <c r="J32" s="8"/>
+      <c r="K32" s="8">
         <v>0</v>
       </c>
       <c r="L32" t="s">
@@ -3781,13 +3817,13 @@
       <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <v>0.4</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="8" t="s">
         <v>146</v>
       </c>
       <c r="G33" s="1">
@@ -3799,8 +3835,8 @@
       <c r="I33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7">
+      <c r="J33" s="8"/>
+      <c r="K33" s="8">
         <v>0</v>
       </c>
       <c r="L33" t="s">
@@ -3816,13 +3852,13 @@
       <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="8">
         <v>0.4</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="8" t="s">
         <v>151</v>
       </c>
       <c r="G34" s="1">
@@ -3834,8 +3870,8 @@
       <c r="I34" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7">
+      <c r="J34" s="8"/>
+      <c r="K34" s="8">
         <v>0</v>
       </c>
       <c r="L34" t="s">
@@ -3851,13 +3887,13 @@
       <c r="C35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="8">
         <v>0.4</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="8" t="s">
         <v>156</v>
       </c>
       <c r="G35" s="1">
@@ -3869,8 +3905,8 @@
       <c r="I35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7">
+      <c r="J35" s="8"/>
+      <c r="K35" s="8">
         <v>0</v>
       </c>
       <c r="L35" t="s">
@@ -3879,20 +3915,20 @@
       <c r="M35"/>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:13">
-      <c r="A36" s="10"/>
+      <c r="A36" s="11"/>
       <c r="B36" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="12">
         <v>0.4</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="12" t="s">
         <v>161</v>
       </c>
       <c r="G36" s="3">
@@ -3904,14 +3940,14 @@
       <c r="I36" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11">
+      <c r="J36" s="12"/>
+      <c r="K36" s="12">
         <v>0</v>
       </c>
       <c r="L36" t="s">
         <v>163</v>
       </c>
-      <c r="M36" s="10"/>
+      <c r="M36" s="11"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37"/>
@@ -3921,13 +3957,13 @@
       <c r="C37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="8">
         <v>0.4</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="8" t="s">
         <v>166</v>
       </c>
       <c r="G37" s="1">
@@ -3939,28 +3975,28 @@
       <c r="I37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="7">
-        <v>0</v>
-      </c>
-      <c r="L37" s="7" t="s">
+      <c r="K37" s="8">
+        <v>0</v>
+      </c>
+      <c r="L37" s="8" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="38" s="4" customFormat="1" spans="1:13">
-      <c r="A38" s="12"/>
+      <c r="A38" s="13"/>
       <c r="B38" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="14">
         <v>0.4</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="14" t="s">
         <v>171</v>
       </c>
       <c r="G38" s="4">
@@ -3972,14 +4008,14 @@
       <c r="I38" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13">
-        <v>0</v>
-      </c>
-      <c r="L38" s="12" t="s">
+      <c r="J38" s="14"/>
+      <c r="K38" s="14">
+        <v>0</v>
+      </c>
+      <c r="L38" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="M38" s="12"/>
+      <c r="M38" s="13"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39"/>
@@ -3989,13 +4025,13 @@
       <c r="C39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="8">
         <v>0.4</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="8" t="s">
         <v>176</v>
       </c>
       <c r="G39" s="1">
@@ -4007,7 +4043,7 @@
       <c r="I39" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39" s="8">
         <v>0</v>
       </c>
       <c r="L39" t="s">
@@ -4022,13 +4058,13 @@
       <c r="C40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="8">
         <v>0.4</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="8" t="s">
         <v>181</v>
       </c>
       <c r="G40" s="1">
@@ -4040,7 +4076,7 @@
       <c r="I40" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40" s="8">
         <v>0</v>
       </c>
       <c r="L40" t="s">
@@ -4055,13 +4091,13 @@
       <c r="C41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="8">
         <v>0.4</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="8" t="s">
         <v>186</v>
       </c>
       <c r="G41" s="1">
@@ -4073,7 +4109,7 @@
       <c r="I41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K41" s="8">
         <v>0</v>
       </c>
       <c r="L41" t="s">
@@ -4088,13 +4124,13 @@
       <c r="C42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="8">
         <v>0.4</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="8" t="s">
         <v>191</v>
       </c>
       <c r="G42" s="1">
@@ -4106,7 +4142,7 @@
       <c r="I42" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K42" s="8">
         <v>0</v>
       </c>
       <c r="L42" t="s">
@@ -4121,13 +4157,13 @@
       <c r="C43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="8">
         <v>0.4</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="8" t="s">
         <v>196</v>
       </c>
       <c r="G43" s="1">
@@ -4139,7 +4175,7 @@
       <c r="I43" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K43" s="7">
+      <c r="K43" s="8">
         <v>0</v>
       </c>
       <c r="L43" t="s">
@@ -4154,97 +4190,97 @@
       <c r="C44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="8">
         <v>0.4</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="8">
         <v>85</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="8">
         <v>42</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7">
-        <v>0</v>
-      </c>
-      <c r="L44" s="7" t="s">
+      <c r="J44" s="8"/>
+      <c r="K44" s="8">
+        <v>0</v>
+      </c>
+      <c r="L44" s="8" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" spans="1:13">
-      <c r="A45" s="9"/>
+      <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="9">
         <v>0.4</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="8" t="s">
+      <c r="F45" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="9">
         <v>75</v>
       </c>
-      <c r="H45" s="8">
+      <c r="H45" s="9">
         <v>37</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8">
-        <v>0</v>
-      </c>
-      <c r="L45" s="9" t="s">
+      <c r="J45" s="9"/>
+      <c r="K45" s="9">
+        <v>0</v>
+      </c>
+      <c r="L45" s="10" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="1:13">
-      <c r="A46" s="9"/>
+      <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="9">
         <v>0.4</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F46" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="9">
         <v>75</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="9">
         <v>37</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8">
-        <v>0</v>
-      </c>
-      <c r="L46" s="9" t="s">
+      <c r="J46" s="9"/>
+      <c r="K46" s="9">
+        <v>0</v>
+      </c>
+      <c r="L46" s="10" t="s">
         <v>213</v>
       </c>
     </row>
@@ -4256,26 +4292,26 @@
       <c r="C47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="8">
         <v>0.4</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="8">
         <v>70</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="8">
         <v>35</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7">
+      <c r="J47" s="8"/>
+      <c r="K47" s="8">
         <v>0</v>
       </c>
       <c r="L47" t="s">
@@ -4290,26 +4326,26 @@
       <c r="C48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="8">
         <v>0.4</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="8">
         <v>75</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="8">
         <v>37</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7">
+      <c r="J48" s="8"/>
+      <c r="K48" s="8">
         <v>0</v>
       </c>
       <c r="L48" t="s">
@@ -4323,31 +4359,31 @@
       <c r="C49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="8">
         <v>0.4</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="8">
         <v>90</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="8">
         <v>45</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J49" s="7">
+      <c r="J49" s="8">
         <v>10301</v>
       </c>
-      <c r="K49" s="7">
-        <v>0</v>
-      </c>
-      <c r="L49" s="7" t="s">
+      <c r="K49" s="8">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8" t="s">
         <v>228</v>
       </c>
     </row>
@@ -4359,28 +4395,28 @@
       <c r="C50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="8">
         <v>0.4</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="8">
         <v>120</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="8">
         <v>60</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K50" s="7">
-        <v>0</v>
-      </c>
-      <c r="L50" s="7" t="s">
+      <c r="K50" s="8">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4392,25 +4428,25 @@
       <c r="C51" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="8">
         <v>0.4</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51" s="8">
         <v>110</v>
       </c>
-      <c r="H51" s="7">
+      <c r="H51" s="8">
         <v>55</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="K51" s="7">
+      <c r="K51" s="8">
         <v>0</v>
       </c>
       <c r="L51" t="s">
@@ -4418,39 +4454,39 @@
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:13">
-      <c r="A52" s="9"/>
+      <c r="A52" s="10"/>
       <c r="B52" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="9">
         <v>0.4</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F52" s="8" t="s">
+      <c r="F52" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52" s="9">
         <v>70</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="9">
         <v>35</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8">
-        <v>0</v>
-      </c>
-      <c r="L52" s="9" t="s">
+      <c r="J52" s="9"/>
+      <c r="K52" s="9">
+        <v>0</v>
+      </c>
+      <c r="L52" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="M52" s="9"/>
+      <c r="M52" s="10"/>
     </row>
     <row r="53" spans="1:13">
       <c r="B53" s="1" t="s">
@@ -4459,7 +4495,7 @@
       <c r="C53" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="8">
         <v>0.4</v>
       </c>
       <c r="E53" t="s">
@@ -4468,16 +4504,16 @@
       <c r="F53" t="s">
         <v>246</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="8">
         <v>90</v>
       </c>
-      <c r="H53" s="7">
+      <c r="H53" s="8">
         <v>45</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K53" s="7">
+      <c r="K53" s="8">
         <v>1</v>
       </c>
       <c r="L53" t="s">
@@ -4491,7 +4527,7 @@
       <c r="C54" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="8">
         <v>0.4</v>
       </c>
       <c r="E54" t="s">
@@ -4500,16 +4536,16 @@
       <c r="F54" t="s">
         <v>251</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="8">
         <v>145</v>
       </c>
-      <c r="H54" s="7">
+      <c r="H54" s="8">
         <v>72</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="K54" s="7">
+      <c r="K54" s="8">
         <v>1</v>
       </c>
       <c r="L54" t="s">
@@ -4523,7 +4559,7 @@
       <c r="C55" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="8">
         <v>0.4</v>
       </c>
       <c r="E55" t="s">
@@ -4532,16 +4568,16 @@
       <c r="F55" t="s">
         <v>256</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="8">
         <v>75</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H55" s="8">
         <v>37</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K55" s="7">
+      <c r="K55" s="8">
         <v>0</v>
       </c>
       <c r="L55" t="s">
@@ -4555,7 +4591,7 @@
       <c r="C56" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="8">
         <v>0.4</v>
       </c>
       <c r="E56" t="s">
@@ -4564,16 +4600,16 @@
       <c r="F56" t="s">
         <v>261</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="8">
         <v>110</v>
       </c>
-      <c r="H56" s="7">
+      <c r="H56" s="8">
         <v>55</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="K56" s="7">
+      <c r="K56" s="8">
         <v>1</v>
       </c>
       <c r="L56" t="s">
@@ -4587,7 +4623,7 @@
       <c r="C57" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="8">
         <v>0.4</v>
       </c>
       <c r="E57" t="s">
@@ -4596,17 +4632,17 @@
       <c r="F57" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="8">
         <v>160</v>
       </c>
-      <c r="H57" s="7">
+      <c r="H57" s="8">
         <v>80</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7">
+      <c r="J57" s="8"/>
+      <c r="K57" s="8">
         <v>2</v>
       </c>
       <c r="L57" t="s">
@@ -4621,7 +4657,7 @@
       <c r="C58" t="s">
         <v>114</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="8">
         <v>0.4</v>
       </c>
       <c r="E58" t="s">
@@ -4630,151 +4666,151 @@
       <c r="F58" t="s">
         <v>271</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58" s="8">
         <v>160</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H58" s="8">
         <v>80</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="K58" s="7">
+      <c r="K58" s="8">
         <v>2</v>
       </c>
-      <c r="L58" s="7" t="s">
+      <c r="L58" s="8" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="59" s="5" customFormat="1" spans="1:13">
-      <c r="A59" s="14"/>
+      <c r="A59" s="15"/>
       <c r="B59" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="15">
+      <c r="D59" s="16">
         <v>0.4</v>
       </c>
-      <c r="E59" s="15" t="s">
+      <c r="E59" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="16">
         <v>80</v>
       </c>
-      <c r="H59" s="15">
+      <c r="H59" s="16">
         <v>40</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15">
-        <v>0</v>
-      </c>
-      <c r="L59" s="14" t="s">
+      <c r="J59" s="16"/>
+      <c r="K59" s="16">
+        <v>0</v>
+      </c>
+      <c r="L59" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="M59" s="14"/>
+      <c r="M59" s="15"/>
     </row>
     <row r="60" s="5" customFormat="1" spans="1:13">
-      <c r="A60" s="14"/>
+      <c r="A60" s="15"/>
       <c r="B60" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="15">
+      <c r="D60" s="16">
         <v>0.4</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="16">
         <v>80</v>
       </c>
-      <c r="H60" s="15">
+      <c r="H60" s="16">
         <v>40</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15">
-        <v>0</v>
-      </c>
-      <c r="L60" s="14" t="s">
+      <c r="J60" s="16"/>
+      <c r="K60" s="16">
+        <v>0</v>
+      </c>
+      <c r="L60" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="M60" s="14"/>
+      <c r="M60" s="15"/>
     </row>
     <row r="61" s="5" customFormat="1" spans="1:13">
-      <c r="A61" s="14"/>
+      <c r="A61" s="15"/>
       <c r="B61" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D61" s="15">
+      <c r="D61" s="16">
         <v>0.4</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="G61" s="15">
+      <c r="G61" s="16">
         <v>80</v>
       </c>
-      <c r="H61" s="15">
+      <c r="H61" s="16">
         <v>40</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15">
-        <v>0</v>
-      </c>
-      <c r="L61" s="14" t="s">
+      <c r="J61" s="16"/>
+      <c r="K61" s="16">
+        <v>0</v>
+      </c>
+      <c r="L61" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="M61" s="14"/>
+      <c r="M61" s="15"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62"/>
-      <c r="B62" s="7"/>
+      <c r="B62" s="8"/>
       <c r="C62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="K62" s="7"/>
+      <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63"/>
-      <c r="B63" s="7">
+      <c r="B63" s="8">
         <v>301</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="8">
         <v>0.2</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="8" t="s">
         <v>291</v>
       </c>
       <c r="G63" s="1">
@@ -4786,10 +4822,10 @@
       <c r="I63" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="J63" s="7">
+      <c r="J63" s="8">
         <v>10401</v>
       </c>
-      <c r="K63" s="7">
+      <c r="K63" s="8">
         <v>0</v>
       </c>
       <c r="L63" t="s">
@@ -4798,19 +4834,19 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64"/>
-      <c r="B64" s="7">
+      <c r="B64" s="8">
         <v>302</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="8">
         <v>0.2</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="8" t="s">
         <v>295</v>
       </c>
       <c r="G64" s="1">
@@ -4822,28 +4858,28 @@
       <c r="I64" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="K64" s="7">
+      <c r="K64" s="8">
         <v>0</v>
       </c>
       <c r="L64" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:13">
       <c r="A65"/>
-      <c r="B65" s="7">
+      <c r="B65" s="8">
         <v>303</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="8">
         <v>0.2</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="8" t="s">
         <v>299</v>
       </c>
       <c r="G65" s="1">
@@ -4855,31 +4891,31 @@
       <c r="I65" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="J65" s="16">
+      <c r="J65" s="17">
         <v>10501</v>
       </c>
-      <c r="K65" s="7">
+      <c r="K65" s="8">
         <v>0</v>
       </c>
       <c r="L65" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" spans="1:12">
-      <c r="A66" s="9"/>
-      <c r="B66" s="8">
+    <row r="66" s="2" customFormat="1" spans="1:13">
+      <c r="A66" s="10"/>
+      <c r="B66" s="18">
         <v>304</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="9">
         <v>0.2</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="F66" s="8" t="s">
+      <c r="F66" s="9" t="s">
         <v>303</v>
       </c>
       <c r="G66" s="2">
@@ -4891,31 +4927,31 @@
       <c r="I66" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="J66" s="8">
+      <c r="J66" s="9">
         <v>10601</v>
       </c>
-      <c r="K66" s="8">
-        <v>0</v>
-      </c>
-      <c r="L66" s="9" t="s">
+      <c r="K66" s="9">
+        <v>0</v>
+      </c>
+      <c r="L66" s="10" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" spans="1:12">
+    <row r="67" s="1" customFormat="1" spans="1:13">
       <c r="A67"/>
-      <c r="B67" s="7">
+      <c r="B67" s="8">
         <v>305</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="8">
         <v>0.2</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="8" t="s">
         <v>307</v>
       </c>
       <c r="G67" s="1">
@@ -4927,30 +4963,30 @@
       <c r="I67" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="J67" s="7">
+      <c r="J67" s="8">
         <v>10701</v>
       </c>
-      <c r="K67" s="7">
+      <c r="K67" s="8">
         <v>0</v>
       </c>
       <c r="L67" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" spans="1:12">
-      <c r="B68" s="7">
+    <row r="68" s="1" customFormat="1" spans="1:13">
+      <c r="B68" s="8">
         <v>306</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="8">
         <v>0.2</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="8" t="s">
         <v>311</v>
       </c>
       <c r="G68" s="1">
@@ -4962,181 +4998,180 @@
       <c r="I68" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="J68" s="7"/>
-      <c r="K68" s="7">
+      <c r="K68" s="8">
         <v>0</v>
       </c>
       <c r="L68" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" spans="1:12">
-      <c r="B69" s="7">
+    <row r="69" s="1" customFormat="1" spans="1:13">
+      <c r="B69" s="8">
         <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="8">
         <v>0.2</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="8" t="s">
         <v>315</v>
       </c>
       <c r="G69" s="1">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="H69" s="1">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K69" s="7">
+      <c r="J69" s="8"/>
+      <c r="K69" s="8">
         <v>0</v>
       </c>
       <c r="L69" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" spans="1:12">
-      <c r="B70" s="7">
+    <row r="70" s="1" customFormat="1" spans="1:13">
+      <c r="B70" s="8">
         <v>308</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="8">
         <v>0.2</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="8" t="s">
         <v>319</v>
       </c>
       <c r="G70" s="1">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="H70" s="1">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7">
+      <c r="K70" s="8">
         <v>0</v>
       </c>
       <c r="L70" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" spans="1:12">
-      <c r="B71" s="7">
+    <row r="71" s="1" customFormat="1" spans="1:13">
+      <c r="B71" s="8">
         <v>309</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="8">
         <v>0.2</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="F71" s="8" t="s">
         <v>323</v>
       </c>
       <c r="G71" s="1">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="H71" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K71" s="7">
-        <v>0</v>
-      </c>
-      <c r="L71" t="s">
+      <c r="J71" s="8"/>
+      <c r="K71" s="8">
+        <v>0</v>
+      </c>
+      <c r="L71" s="8" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" spans="1:12">
-      <c r="B72" s="7">
+    <row r="72" s="2" customFormat="1" spans="1:13">
+      <c r="B72" s="18">
         <v>310</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="9">
         <v>0.2</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="G72" s="1">
-        <v>275</v>
-      </c>
-      <c r="H72" s="1">
-        <v>137</v>
-      </c>
-      <c r="I72" s="1" t="s">
+      <c r="G72" s="2">
+        <v>170</v>
+      </c>
+      <c r="H72" s="2">
+        <v>85</v>
+      </c>
+      <c r="I72" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="J72" s="7"/>
-      <c r="K72" s="7">
-        <v>0</v>
-      </c>
-      <c r="L72" s="7" t="s">
+      <c r="K72" s="9">
+        <v>0</v>
+      </c>
+      <c r="L72" s="10" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="73" s="2" customFormat="1" spans="1:12">
-      <c r="B73" s="8">
+    <row r="73" s="2" customFormat="1" spans="1:13">
+      <c r="B73" s="18">
         <v>311</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="9">
         <v>0.2</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="F73" s="8" t="s">
+      <c r="F73" s="9" t="s">
         <v>331</v>
       </c>
       <c r="G73" s="2">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="H73" s="2">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="K73" s="8">
-        <v>0</v>
-      </c>
-      <c r="L73" s="9" t="s">
+      <c r="K73" s="9">
+        <v>0</v>
+      </c>
+      <c r="L73" s="10" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="74" s="2" customFormat="1" spans="1:12">
+    <row r="74" s="1" customFormat="1" spans="1:13">
       <c r="B74" s="8">
         <v>312</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="1" t="s">
         <v>289</v>
       </c>
       <c r="D74" s="8">
@@ -5148,228 +5183,232 @@
       <c r="F74" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="G74" s="2">
-        <v>210</v>
-      </c>
-      <c r="H74" s="2">
-        <v>105</v>
-      </c>
-      <c r="I74" s="2" t="s">
+      <c r="G74" s="1">
+        <v>160</v>
+      </c>
+      <c r="H74" s="1">
+        <v>80</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>336</v>
       </c>
+      <c r="J74" s="8"/>
       <c r="K74" s="8">
         <v>0</v>
       </c>
-      <c r="L74" s="9" t="s">
+      <c r="L74" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" spans="1:12">
-      <c r="B75" s="7">
+    <row r="75" s="1" customFormat="1" spans="1:13">
+      <c r="B75" s="8">
         <v>313</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="8">
         <v>0.2</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F75" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="G75" s="1">
-        <v>160</v>
-      </c>
-      <c r="H75" s="1">
-        <v>80</v>
+      <c r="G75" s="8">
+        <v>180</v>
+      </c>
+      <c r="H75" s="8">
+        <v>90</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7">
+      <c r="J75" s="8"/>
+      <c r="K75" s="8">
         <v>0</v>
       </c>
       <c r="L75" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="1:12">
-      <c r="B76" s="7">
+    <row r="76" s="1" customFormat="1" spans="1:13">
+      <c r="B76" s="8">
         <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="8">
         <v>0.2</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F76" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="G76" s="7">
-        <v>180</v>
-      </c>
-      <c r="H76" s="7">
-        <v>90</v>
+      <c r="G76" s="8">
+        <v>380</v>
+      </c>
+      <c r="H76" s="8">
+        <v>190</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7">
+      <c r="J76" s="8"/>
+      <c r="K76" s="8">
         <v>0</v>
       </c>
       <c r="L76" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" spans="1:12">
-      <c r="B77" s="7">
+    <row r="77" spans="1:13">
+      <c r="B77" s="8">
         <v>315</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="8">
         <v>0.2</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="G77" s="7">
-        <v>380</v>
-      </c>
-      <c r="H77" s="7">
-        <v>190</v>
+      <c r="G77" s="8">
+        <v>170</v>
+      </c>
+      <c r="H77" s="8">
+        <v>85</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="J77" s="7"/>
-      <c r="K77" s="7">
+      <c r="K77" s="8">
         <v>0</v>
       </c>
       <c r="L77" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
-      <c r="B78" s="7">
+    <row r="78" spans="1:13">
+      <c r="B78" s="8">
         <v>316</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="8">
         <v>0.2</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="G78" s="7">
-        <v>170</v>
-      </c>
-      <c r="H78" s="7">
-        <v>85</v>
+      <c r="G78" s="8">
+        <v>200</v>
+      </c>
+      <c r="H78" s="8">
+        <v>100</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="K78" s="7">
-        <v>0</v>
-      </c>
-      <c r="L78" t="s">
+      <c r="J78" s="8">
+        <v>10201</v>
+      </c>
+      <c r="K78" s="8">
+        <v>0</v>
+      </c>
+      <c r="L78" s="8" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
-      <c r="B79" s="7">
+    <row r="79" spans="1:13">
+      <c r="B79" s="8">
         <v>317</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="8">
         <v>0.2</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F79" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="G79" s="7">
-        <v>200</v>
-      </c>
-      <c r="H79" s="7">
-        <v>100</v>
+      <c r="G79" s="8">
+        <v>170</v>
+      </c>
+      <c r="H79" s="8">
+        <v>85</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J79" s="7">
-        <v>10201</v>
-      </c>
-      <c r="K79" s="7">
-        <v>0</v>
-      </c>
-      <c r="L79" s="7" t="s">
+      <c r="J79" s="17">
+        <v>10801</v>
+      </c>
+      <c r="K79" s="8">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
-      <c r="B80" s="7">
+    <row r="80" s="2" customFormat="1" spans="1:13">
+      <c r="B80" s="18">
         <v>318</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="9">
         <v>0.2</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="F80" s="7" t="s">
+      <c r="F80" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="G80" s="7">
-        <v>170</v>
-      </c>
-      <c r="H80" s="7">
-        <v>85</v>
-      </c>
-      <c r="I80" s="1" t="s">
+      <c r="G80" s="9">
+        <v>160</v>
+      </c>
+      <c r="H80" s="9">
+        <v>80</v>
+      </c>
+      <c r="I80" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="J80" s="16">
-        <v>10801</v>
-      </c>
-      <c r="K80" s="7">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
+      <c r="J80" s="9">
+        <v>10402</v>
+      </c>
+      <c r="K80" s="9">
+        <v>0</v>
+      </c>
+      <c r="L80" s="10" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="81" s="2" customFormat="1" spans="2:13">
+      <c r="M80" s="10"/>
+    </row>
+    <row r="81" spans="2:13">
       <c r="B81" s="8">
         <v>319</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>289</v>
       </c>
       <c r="D81" s="8">
@@ -5387,46 +5426,42 @@
       <c r="H81" s="8">
         <v>80</v>
       </c>
-      <c r="I81" s="2" t="s">
+      <c r="I81" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="J81" s="8">
-        <v>10402</v>
-      </c>
       <c r="K81" s="8">
         <v>0</v>
       </c>
-      <c r="L81" s="9" t="s">
+      <c r="L81" t="s">
         <v>365</v>
       </c>
-      <c r="M81" s="9"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="7">
+      <c r="B82" s="8">
         <v>320</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="8">
         <v>0.2</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="F82" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G82" s="8">
         <v>160</v>
       </c>
-      <c r="H82" s="7">
+      <c r="H82" s="8">
         <v>80</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="K82" s="7">
+      <c r="K82" s="8">
         <v>0</v>
       </c>
       <c r="L82" t="s">
@@ -5434,31 +5469,31 @@
       </c>
     </row>
     <row r="83" spans="2:13">
-      <c r="B83" s="7">
+      <c r="B83" s="8">
         <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D83" s="8">
         <v>0.2</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="F83" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G83" s="8">
         <v>160</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H83" s="8">
         <v>80</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K83" s="7">
+      <c r="K83" s="8">
         <v>0</v>
       </c>
       <c r="L83" t="s">
@@ -5466,74 +5501,76 @@
       </c>
     </row>
     <row r="84" spans="2:13">
-      <c r="B84" s="7">
+      <c r="B84" s="8">
         <v>322</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D84" s="8">
         <v>0.2</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E84" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="F84" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G84" s="7">
-        <v>160</v>
-      </c>
-      <c r="H84" s="7">
-        <v>80</v>
+      <c r="G84" s="8">
+        <v>190</v>
+      </c>
+      <c r="H84" s="8">
+        <v>95</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="K84" s="7">
+      <c r="K84" s="8">
         <v>0</v>
       </c>
       <c r="L84" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="85" spans="2:13">
-      <c r="B85" s="7">
+    <row r="85" s="2" customFormat="1" spans="2:13">
+      <c r="B85" s="18">
         <v>323</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="9">
         <v>0.2</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="F85" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="G85" s="7">
-        <v>190</v>
-      </c>
-      <c r="H85" s="7">
-        <v>95</v>
-      </c>
-      <c r="I85" s="1" t="s">
+      <c r="G85" s="9">
+        <v>175</v>
+      </c>
+      <c r="H85" s="9">
+        <v>87</v>
+      </c>
+      <c r="I85" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="K85" s="7">
-        <v>0</v>
-      </c>
-      <c r="L85" t="s">
+      <c r="J85" s="9"/>
+      <c r="K85" s="9">
+        <v>0</v>
+      </c>
+      <c r="L85" s="10" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="86" s="2" customFormat="1" spans="2:13">
+      <c r="M85" s="10"/>
+    </row>
+    <row r="86" spans="2:13">
       <c r="B86" s="8">
         <v>324</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="1" t="s">
         <v>289</v>
       </c>
       <c r="D86" s="8">
@@ -5546,765 +5583,768 @@
         <v>383</v>
       </c>
       <c r="G86" s="8">
-        <v>175</v>
+        <v>270</v>
       </c>
       <c r="H86" s="8">
-        <v>87</v>
-      </c>
-      <c r="I86" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I86" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="J86" s="8"/>
+      <c r="J86" s="17">
+        <v>10502</v>
+      </c>
       <c r="K86" s="8">
         <v>0</v>
       </c>
-      <c r="L86" s="9" t="s">
+      <c r="L86" t="s">
         <v>385</v>
       </c>
-      <c r="M86" s="9"/>
-    </row>
-    <row r="87" spans="2:13">
-      <c r="B87" s="7">
+    </row>
+    <row r="87" s="2" customFormat="1" spans="2:13">
+      <c r="B87" s="18">
         <v>325</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D87" s="7">
+      <c r="D87" s="9">
         <v>0.2</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F87" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="G87" s="7">
-        <v>270</v>
-      </c>
-      <c r="H87" s="7">
-        <v>135</v>
-      </c>
-      <c r="I87" s="1" t="s">
+      <c r="G87" s="9">
+        <v>160</v>
+      </c>
+      <c r="H87" s="9">
+        <v>80</v>
+      </c>
+      <c r="I87" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="J87" s="16">
-        <v>10502</v>
-      </c>
-      <c r="K87" s="7">
-        <v>0</v>
-      </c>
-      <c r="L87" t="s">
+      <c r="J87" s="9"/>
+      <c r="K87" s="9">
+        <v>2</v>
+      </c>
+      <c r="L87" s="10" t="s">
         <v>389</v>
       </c>
+      <c r="M87" s="10"/>
     </row>
     <row r="88" s="2" customFormat="1" spans="2:13">
-      <c r="B88" s="8">
+      <c r="B88" s="18">
         <v>326</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="9">
         <v>0.2</v>
       </c>
-      <c r="E88" s="9" t="s">
+      <c r="E88" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="F88" s="9" t="s">
+      <c r="F88" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="G88" s="8">
-        <v>160</v>
-      </c>
-      <c r="H88" s="8">
-        <v>80</v>
+      <c r="G88" s="9">
+        <v>200</v>
+      </c>
+      <c r="H88" s="9">
+        <v>100</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8">
+      <c r="J88" s="9">
+        <v>10901</v>
+      </c>
+      <c r="K88" s="9">
         <v>2</v>
       </c>
-      <c r="L88" s="9" t="s">
+      <c r="L88" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="M88" s="9"/>
+      <c r="M88" s="10"/>
     </row>
     <row r="89" s="2" customFormat="1" spans="2:13">
-      <c r="B89" s="8">
+      <c r="B89" s="18">
         <v>327</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="9">
         <v>0.2</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="F89" s="9" t="s">
+      <c r="F89" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="G89" s="8">
-        <v>200</v>
-      </c>
-      <c r="H89" s="8">
-        <v>100</v>
+      <c r="G89" s="9">
+        <v>170</v>
+      </c>
+      <c r="H89" s="9">
+        <v>85</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="J89" s="16">
-        <v>10901</v>
-      </c>
-      <c r="K89" s="8">
-        <v>2</v>
-      </c>
-      <c r="L89" s="9" t="s">
+      <c r="J89" s="9"/>
+      <c r="K89" s="9">
+        <v>1</v>
+      </c>
+      <c r="L89" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="M89" s="9"/>
-    </row>
-    <row r="90" s="2" customFormat="1" spans="2:13">
+      <c r="M89" s="10"/>
+    </row>
+    <row r="90" s="6" customFormat="1" spans="2:13">
       <c r="B90" s="8">
         <v>328</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="20">
         <v>0.2</v>
       </c>
-      <c r="E90" s="9" t="s">
+      <c r="E90" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="F90" s="9" t="s">
+      <c r="F90" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="G90" s="8">
-        <v>170</v>
-      </c>
-      <c r="H90" s="8">
-        <v>85</v>
-      </c>
-      <c r="I90" s="2" t="s">
+      <c r="G90" s="20">
+        <v>160</v>
+      </c>
+      <c r="H90" s="20">
+        <v>80</v>
+      </c>
+      <c r="I90" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8">
+      <c r="J90" s="20"/>
+      <c r="K90" s="20">
         <v>1</v>
       </c>
-      <c r="L90" s="9" t="s">
+      <c r="L90" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="M90" s="9"/>
-    </row>
-    <row r="91" s="1" customFormat="1" spans="2:13">
-      <c r="B91" s="7">
+      <c r="M90" s="19"/>
+    </row>
+    <row r="91" s="6" customFormat="1" spans="2:13">
+      <c r="B91" s="8">
         <v>329</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="20">
         <v>0.2</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="G91" s="7">
-        <v>260</v>
-      </c>
-      <c r="H91" s="7">
-        <v>130</v>
-      </c>
-      <c r="I91" s="1" t="s">
+      <c r="G91" s="20">
+        <v>200</v>
+      </c>
+      <c r="H91" s="20">
+        <v>100</v>
+      </c>
+      <c r="I91" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="K91" s="1" t="s">
+      <c r="J91" s="21">
+        <v>11005</v>
+      </c>
+      <c r="K91" s="20">
+        <v>0</v>
+      </c>
+      <c r="L91" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="L91" t="s">
+    </row>
+    <row r="92" s="1" customFormat="1" spans="2:13">
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="2:13">
+      <c r="B93" s="1" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="2:13">
-      <c r="B92" s="7">
-        <v>330</v>
-      </c>
-      <c r="C92" t="s">
-        <v>289</v>
-      </c>
-      <c r="D92" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="E92" t="s">
+      <c r="C93" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="D93" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E93" s="8">
+        <v>235</v>
+      </c>
+      <c r="F93" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="G92" s="7">
-        <v>260</v>
-      </c>
-      <c r="H92" s="7">
-        <v>130</v>
-      </c>
-      <c r="I92" s="1" t="s">
+      <c r="G93" s="8">
+        <v>650</v>
+      </c>
+      <c r="H93" s="8">
+        <v>325</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="L92" t="s">
+      <c r="J93" s="8">
+        <v>11001</v>
+      </c>
+      <c r="K93" s="8">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="93" spans="2:13">
-      <c r="B93" s="7">
-        <v>331</v>
-      </c>
-      <c r="C93" t="s">
-        <v>289</v>
-      </c>
-      <c r="D93" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="E93" t="s">
+    <row r="94" s="1" customFormat="1" spans="2:13">
+      <c r="B94" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="F93" t="s">
+      <c r="C94" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D94" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E94" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="G93" s="7">
-        <v>160</v>
-      </c>
-      <c r="H93" s="7">
-        <v>80</v>
-      </c>
-      <c r="I93" s="1" t="s">
+      <c r="F94" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="K93" s="7">
-        <v>1</v>
-      </c>
-      <c r="L93" t="s">
+      <c r="G94" s="8">
+        <v>680</v>
+      </c>
+      <c r="H94" s="8">
+        <v>340</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="94" s="5" customFormat="1" spans="2:13">
-      <c r="B94" s="15">
-        <v>332</v>
-      </c>
-      <c r="C94" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="D94" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="E94" s="15" t="s">
+      <c r="J94" s="8"/>
+      <c r="K94" s="8">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
         <v>415</v>
       </c>
-      <c r="F94" s="14" t="s">
+    </row>
+    <row r="95" s="1" customFormat="1" spans="2:13">
+      <c r="B95" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="G94" s="15">
-        <v>200</v>
-      </c>
-      <c r="H94" s="15">
-        <v>100</v>
-      </c>
-      <c r="I94" s="5" t="s">
+      <c r="C95" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D95" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E95" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="J94" s="17">
-        <v>11005</v>
-      </c>
-      <c r="K94" s="15">
-        <v>0</v>
-      </c>
-      <c r="L94" s="14" t="s">
+      <c r="F95" s="8" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="2:13">
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-      <c r="H95" s="7"/>
-      <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
-      <c r="L95" s="7"/>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="2:13">
-      <c r="B96" s="1" t="s">
+      <c r="G95" s="8">
+        <v>600</v>
+      </c>
+      <c r="H95" s="8">
+        <v>300</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="K95" s="8">
+        <v>0</v>
+      </c>
+      <c r="L95" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="D96" s="7">
+    </row>
+    <row r="96" s="2" customFormat="1" spans="2:13">
+      <c r="B96" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D96" s="9">
         <v>0.1</v>
       </c>
-      <c r="E96" s="7">
-        <v>235</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="G96" s="7">
-        <v>650</v>
-      </c>
-      <c r="H96" s="7">
-        <v>325</v>
-      </c>
-      <c r="I96" s="1" t="s">
+      <c r="E96" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="J96" s="7">
-        <v>11001</v>
-      </c>
-      <c r="K96" s="7">
-        <v>0</v>
-      </c>
-      <c r="L96" t="s">
+      <c r="F96" s="9" t="s">
         <v>423</v>
+      </c>
+      <c r="G96" s="9">
+        <v>480</v>
+      </c>
+      <c r="H96" s="9">
+        <v>240</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="J96" s="9">
+        <v>11002</v>
+      </c>
+      <c r="K96" s="9">
+        <v>0</v>
+      </c>
+      <c r="L96" s="10" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="2:13">
       <c r="B97" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D97" s="7">
+        <v>407</v>
+      </c>
+      <c r="D97" s="8">
         <v>0.1</v>
       </c>
-      <c r="E97" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="G97" s="7">
-        <v>680</v>
-      </c>
-      <c r="H97" s="7">
-        <v>340</v>
+      <c r="E97" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="G97" s="8">
+        <v>460</v>
+      </c>
+      <c r="H97" s="8">
+        <v>230</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="J97" s="7"/>
-      <c r="K97" s="7">
+        <v>429</v>
+      </c>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8">
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:13">
       <c r="B98" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D98" s="7">
+        <v>407</v>
+      </c>
+      <c r="D98" s="8">
         <v>0.1</v>
       </c>
-      <c r="E98" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="G98" s="7">
-        <v>600</v>
-      </c>
-      <c r="H98" s="7">
-        <v>300</v>
+      <c r="E98" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="G98" s="8">
+        <v>320</v>
+      </c>
+      <c r="H98" s="8">
+        <v>160</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="K98" s="7">
-        <v>0</v>
-      </c>
-      <c r="L98" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
+      </c>
+      <c r="K98" s="8">
+        <v>0</v>
+      </c>
+      <c r="L98" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" spans="2:13">
       <c r="B99" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D99" s="8">
+        <v>407</v>
+      </c>
+      <c r="D99" s="9">
         <v>0.1</v>
       </c>
-      <c r="E99" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="G99" s="8">
-        <v>480</v>
-      </c>
-      <c r="H99" s="8">
-        <v>240</v>
+      <c r="E99" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="G99" s="9">
+        <v>380</v>
+      </c>
+      <c r="H99" s="9">
+        <v>190</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="J99" s="8">
-        <v>11002</v>
-      </c>
-      <c r="K99" s="8">
-        <v>0</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
+      </c>
+      <c r="J99" s="17">
+        <v>11003</v>
+      </c>
+      <c r="K99" s="9">
+        <v>0</v>
+      </c>
+      <c r="L99" s="10" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="2:13">
       <c r="B100" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D100" s="7">
+        <v>407</v>
+      </c>
+      <c r="D100" s="8">
         <v>0.1</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="G100" s="7">
-        <v>460</v>
-      </c>
-      <c r="H100" s="7">
-        <v>230</v>
+      <c r="E100" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G100" s="8">
+        <v>600</v>
+      </c>
+      <c r="H100" s="8">
+        <v>300</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="J100" s="7"/>
-      <c r="K100" s="7">
-        <v>0</v>
-      </c>
-      <c r="L100" t="s">
-        <v>443</v>
+        <v>444</v>
+      </c>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8">
+        <v>0</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:13">
       <c r="B101" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D101" s="7">
+        <v>407</v>
+      </c>
+      <c r="D101" s="8">
         <v>0.1</v>
       </c>
-      <c r="E101" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="G101" s="7">
-        <v>320</v>
-      </c>
-      <c r="H101" s="7">
-        <v>160</v>
+      <c r="E101" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G101" s="8">
+        <v>280</v>
+      </c>
+      <c r="H101" s="8">
+        <v>140</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="K101" s="7">
+        <v>449</v>
+      </c>
+      <c r="K101" s="8">
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" spans="2:13">
       <c r="B102" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D102" s="8">
+        <v>407</v>
+      </c>
+      <c r="D102" s="9">
         <v>0.1</v>
       </c>
-      <c r="E102" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="G102" s="8">
-        <v>380</v>
-      </c>
-      <c r="H102" s="8">
-        <v>190</v>
+      <c r="E102" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="G102" s="9">
+        <v>300</v>
+      </c>
+      <c r="H102" s="9">
+        <v>150</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="J102" s="16">
-        <v>11003</v>
-      </c>
-      <c r="K102" s="8">
-        <v>0</v>
-      </c>
-      <c r="L102" s="9" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="2:13">
+        <v>454</v>
+      </c>
+      <c r="K102" s="9">
+        <v>0</v>
+      </c>
+      <c r="L102" s="10" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13">
       <c r="B103" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D103" s="7">
+        <v>407</v>
+      </c>
+      <c r="D103" s="8">
         <v>0.1</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="G103" s="7">
-        <v>600</v>
-      </c>
-      <c r="H103" s="7">
-        <v>300</v>
+      <c r="E103" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="G103" s="8">
+        <v>400</v>
+      </c>
+      <c r="H103" s="8">
+        <v>200</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J103" s="7"/>
-      <c r="K103" s="7">
-        <v>0</v>
-      </c>
-      <c r="L103" s="7" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" spans="2:13">
-      <c r="B104" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D104" s="7">
+      <c r="J103" s="17">
+        <v>11004</v>
+      </c>
+      <c r="K103" s="8">
+        <v>0</v>
+      </c>
+      <c r="L103" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="104" s="2" customFormat="1" spans="2:13">
+      <c r="B104" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D104" s="9">
         <v>0.1</v>
       </c>
-      <c r="E104" s="7" t="s">
+      <c r="E104" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="G104" s="9">
         <v>460</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="G104" s="7">
-        <v>280</v>
-      </c>
-      <c r="H104" s="7">
-        <v>140</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="K104" s="7">
-        <v>0</v>
-      </c>
-      <c r="L104" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="105" s="2" customFormat="1" spans="2:13">
-      <c r="B105" s="2" t="s">
+      <c r="H104" s="9">
+        <v>230</v>
+      </c>
+      <c r="I104" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>420</v>
+      <c r="J104" s="9"/>
+      <c r="K104" s="9">
+        <v>0</v>
+      </c>
+      <c r="L104" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="M104" s="10"/>
+    </row>
+    <row r="105" spans="2:13">
+      <c r="B105" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="D105" s="8">
         <v>0.1</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G105" s="8">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="H105" s="8">
-        <v>150</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>467</v>
+        <v>170</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="J105" s="8">
+        <v>10602</v>
       </c>
       <c r="K105" s="8">
         <v>0</v>
       </c>
-      <c r="L105" s="9" t="s">
-        <v>468</v>
+      <c r="L105" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="106" spans="2:13">
       <c r="B106" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D106" s="7">
+        <v>407</v>
+      </c>
+      <c r="D106" s="8">
         <v>0.1</v>
       </c>
-      <c r="E106" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="G106" s="7">
-        <v>400</v>
-      </c>
-      <c r="H106" s="7">
-        <v>200</v>
+      <c r="E106" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="G106" s="8">
+        <v>280</v>
+      </c>
+      <c r="H106" s="8">
+        <v>140</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="J106" s="16">
-        <v>11004</v>
-      </c>
-      <c r="K106" s="7">
+        <v>474</v>
+      </c>
+      <c r="K106" s="8">
         <v>0</v>
       </c>
       <c r="L106" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="107" s="2" customFormat="1" spans="2:13">
-      <c r="B107" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>420</v>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13">
+      <c r="B107" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="D107" s="8">
         <v>0.1</v>
       </c>
-      <c r="E107" s="8" t="s">
-        <v>475</v>
+      <c r="E107" t="s">
+        <v>477</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G107" s="8">
-        <v>460</v>
+        <v>600</v>
       </c>
       <c r="H107" s="8">
-        <v>230</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="J107" s="8"/>
+        <v>300</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>479</v>
+      </c>
       <c r="K107" s="8">
         <v>0</v>
       </c>
-      <c r="L107" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="M107" s="9"/>
+      <c r="L107" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="108" spans="2:13">
       <c r="B108" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D108" s="7">
+        <v>407</v>
+      </c>
+      <c r="D108" s="8">
         <v>0.1</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="G108" s="7">
-        <v>340</v>
-      </c>
-      <c r="H108" s="7">
-        <v>170</v>
-      </c>
-      <c r="I108" s="1" t="s">
+      <c r="E108" t="s">
         <v>482</v>
       </c>
-      <c r="J108" s="7">
-        <v>10602</v>
-      </c>
-      <c r="K108" s="7">
-        <v>0</v>
-      </c>
-      <c r="L108" t="s">
+      <c r="F108" s="8" t="s">
         <v>483</v>
+      </c>
+      <c r="G108" s="8">
+        <v>280</v>
+      </c>
+      <c r="H108" s="8">
+        <v>140</v>
+      </c>
+      <c r="I108" s="8">
+        <v>40016</v>
+      </c>
+      <c r="J108" s="17">
+        <v>10101</v>
+      </c>
+      <c r="K108" s="8">
+        <v>0</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="109" spans="2:13">
       <c r="B109" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D109" s="7">
+        <v>407</v>
+      </c>
+      <c r="D109" s="8">
         <v>0.1</v>
       </c>
-      <c r="E109" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="F109" s="7" t="s">
+      <c r="E109" t="s">
         <v>486</v>
       </c>
-      <c r="G109" s="7">
-        <v>280</v>
-      </c>
-      <c r="H109" s="7">
-        <v>140</v>
-      </c>
-      <c r="I109" s="1" t="s">
+      <c r="F109" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="K109" s="7">
+      <c r="G109" s="8">
+        <v>300</v>
+      </c>
+      <c r="H109" s="8">
+        <v>150</v>
+      </c>
+      <c r="I109" s="8">
+        <v>40017</v>
+      </c>
+      <c r="K109" s="8">
         <v>0</v>
       </c>
       <c r="L109" t="s">
@@ -6316,577 +6356,541 @@
         <v>489</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D110" s="7">
+        <v>407</v>
+      </c>
+      <c r="D110" s="8">
         <v>0.1</v>
       </c>
       <c r="E110" t="s">
         <v>490</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="F110" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="G110" s="7">
-        <v>600</v>
-      </c>
-      <c r="H110" s="7">
-        <v>300</v>
-      </c>
-      <c r="I110" s="7" t="s">
+      <c r="G110" s="8">
+        <v>520</v>
+      </c>
+      <c r="H110" s="8">
+        <v>260</v>
+      </c>
+      <c r="I110" s="8">
+        <v>40018</v>
+      </c>
+      <c r="J110" s="17">
+        <v>11101</v>
+      </c>
+      <c r="K110" s="8">
+        <v>0</v>
+      </c>
+      <c r="L110" t="s">
         <v>492</v>
-      </c>
-      <c r="K110" s="7">
-        <v>0</v>
-      </c>
-      <c r="L110" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="111" spans="2:13">
       <c r="B111" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D111" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E111" t="s">
         <v>494</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D111" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="F111" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="F111" s="7" t="s">
+      <c r="G111" s="8">
+        <v>300</v>
+      </c>
+      <c r="H111" s="8">
+        <v>150</v>
+      </c>
+      <c r="I111" s="8">
+        <v>40019</v>
+      </c>
+      <c r="K111" s="8">
+        <v>0</v>
+      </c>
+      <c r="L111" t="s">
         <v>496</v>
-      </c>
-      <c r="G111" s="7">
-        <v>280</v>
-      </c>
-      <c r="H111" s="7">
-        <v>140</v>
-      </c>
-      <c r="I111" s="7">
-        <v>40016</v>
-      </c>
-      <c r="J111" s="16">
-        <v>10101</v>
-      </c>
-      <c r="K111" s="7">
-        <v>0</v>
-      </c>
-      <c r="L111" s="7" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="112" spans="2:13">
       <c r="B112" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D112" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E112" t="s">
         <v>498</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D112" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="G112" s="8">
+        <v>620</v>
+      </c>
+      <c r="H112" s="8">
+        <v>310</v>
+      </c>
+      <c r="I112" s="8">
+        <v>40021</v>
+      </c>
+      <c r="K112" s="8">
+        <v>0</v>
+      </c>
+      <c r="L112" t="s">
         <v>500</v>
-      </c>
-      <c r="G112" s="7">
-        <v>300</v>
-      </c>
-      <c r="H112" s="7">
-        <v>150</v>
-      </c>
-      <c r="I112" s="7">
-        <v>40017</v>
-      </c>
-      <c r="K112" s="7">
-        <v>0</v>
-      </c>
-      <c r="L112" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="113" spans="1:13">
       <c r="B113" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D113" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E113" t="s">
         <v>502</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D113" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="F113" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="F113" s="7" t="s">
+      <c r="G113" s="8">
+        <v>320</v>
+      </c>
+      <c r="H113" s="8">
+        <v>160</v>
+      </c>
+      <c r="I113" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="G113" s="7">
-        <v>520</v>
-      </c>
-      <c r="H113" s="7">
-        <v>260</v>
-      </c>
-      <c r="I113" s="7">
-        <v>40018</v>
-      </c>
-      <c r="J113" s="16">
-        <v>11101</v>
-      </c>
-      <c r="K113" s="7">
+      <c r="J113" s="17">
+        <v>11201</v>
+      </c>
+      <c r="K113" s="8">
         <v>0</v>
       </c>
       <c r="L113" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
-      <c r="B114" s="1" t="s">
+    <row r="114" s="2" customFormat="1" spans="1:13">
+      <c r="B114" s="22" t="s">
         <v>506</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D114" s="7">
+      <c r="C114" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D114" s="9">
         <v>0.1</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="F114" s="7" t="s">
+      <c r="F114" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="G114" s="7">
-        <v>300</v>
-      </c>
-      <c r="H114" s="7">
-        <v>150</v>
-      </c>
-      <c r="I114" s="7">
-        <v>40019</v>
-      </c>
-      <c r="K114" s="7">
-        <v>0</v>
-      </c>
-      <c r="L114" t="s">
+      <c r="G114" s="9">
+        <v>320</v>
+      </c>
+      <c r="H114" s="9">
+        <v>160</v>
+      </c>
+      <c r="I114" s="9">
+        <v>40023</v>
+      </c>
+      <c r="J114" s="9">
+        <v>11301</v>
+      </c>
+      <c r="K114" s="9">
+        <v>0</v>
+      </c>
+      <c r="L114" s="10" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="115" s="1" customFormat="1" spans="1:13">
+      <c r="M114" s="10"/>
+    </row>
+    <row r="115" spans="1:13">
       <c r="B115" s="1" t="s">
         <v>510</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D115" s="7">
+        <v>407</v>
+      </c>
+      <c r="D115" s="8">
         <v>0.1</v>
       </c>
       <c r="E115" t="s">
         <v>511</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="F115" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="G115" s="7">
-        <v>560</v>
-      </c>
-      <c r="H115" s="7">
-        <v>280</v>
-      </c>
-      <c r="I115" s="7">
-        <v>40020</v>
-      </c>
-      <c r="J115" s="7"/>
-      <c r="K115" s="7">
-        <v>0</v>
-      </c>
-      <c r="L115" t="s">
+      <c r="G115" s="8">
+        <v>550</v>
+      </c>
+      <c r="H115" s="8">
+        <v>275</v>
+      </c>
+      <c r="I115" s="8">
+        <v>40024</v>
+      </c>
+      <c r="J115" s="17">
+        <v>11401</v>
+      </c>
+      <c r="K115" s="8">
+        <v>0</v>
+      </c>
+      <c r="L115" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="M115"/>
     </row>
     <row r="116" spans="1:13">
       <c r="B116" s="1" t="s">
         <v>514</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D116" s="7">
+        <v>407</v>
+      </c>
+      <c r="D116" s="8">
         <v>0.1</v>
       </c>
       <c r="E116" t="s">
         <v>515</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="F116" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="G116" s="7">
-        <v>620</v>
-      </c>
-      <c r="H116" s="7">
-        <v>310</v>
-      </c>
-      <c r="I116" s="7">
-        <v>40021</v>
-      </c>
-      <c r="K116" s="7">
-        <v>0</v>
-      </c>
-      <c r="L116" t="s">
+      <c r="G116" s="8">
+        <v>300</v>
+      </c>
+      <c r="H116" s="8">
+        <v>150</v>
+      </c>
+      <c r="I116" s="8">
+        <v>40025</v>
+      </c>
+      <c r="K116" s="8">
+        <v>0</v>
+      </c>
+      <c r="L116" s="8" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="117" spans="1:13">
-      <c r="B117" s="1" t="s">
+    <row r="117" s="2" customFormat="1" spans="1:13">
+      <c r="B117" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D117" s="7">
+      <c r="C117" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D117" s="9">
         <v>0.1</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="10" t="s">
         <v>519</v>
       </c>
-      <c r="F117" s="7" t="s">
+      <c r="F117" s="10" t="s">
         <v>520</v>
       </c>
-      <c r="G117" s="7">
-        <v>320</v>
-      </c>
-      <c r="H117" s="7">
-        <v>160</v>
-      </c>
-      <c r="I117" s="7" t="s">
+      <c r="G117" s="9">
+        <v>400</v>
+      </c>
+      <c r="H117" s="9">
+        <v>200</v>
+      </c>
+      <c r="I117" s="9">
+        <v>40026</v>
+      </c>
+      <c r="J117" s="9">
+        <v>11501</v>
+      </c>
+      <c r="K117" s="9">
+        <v>1</v>
+      </c>
+      <c r="L117" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="J117" s="16">
-        <v>11201</v>
-      </c>
-      <c r="K117" s="7">
-        <v>0</v>
-      </c>
-      <c r="L117" t="s">
+      <c r="M117" s="10"/>
+    </row>
+    <row r="118" spans="1:13">
+      <c r="B118" s="1" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="118" s="2" customFormat="1" spans="1:13">
-      <c r="B118" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>420</v>
+      <c r="C118" t="s">
+        <v>407</v>
       </c>
       <c r="D118" s="8">
         <v>0.1</v>
       </c>
-      <c r="E118" s="9" t="s">
+      <c r="E118" t="s">
+        <v>523</v>
+      </c>
+      <c r="F118" t="s">
         <v>524</v>
       </c>
-      <c r="F118" s="8" t="s">
+      <c r="G118" s="8">
+        <v>330</v>
+      </c>
+      <c r="H118" s="8">
+        <v>165</v>
+      </c>
+      <c r="I118" s="8">
+        <v>40027</v>
+      </c>
+      <c r="K118" s="8">
+        <v>1</v>
+      </c>
+      <c r="L118" t="s">
         <v>525</v>
       </c>
-      <c r="G118" s="8">
-        <v>320</v>
-      </c>
-      <c r="H118" s="8">
-        <v>160</v>
-      </c>
-      <c r="I118" s="8">
-        <v>40023</v>
-      </c>
-      <c r="J118" s="16">
-        <v>11301</v>
-      </c>
-      <c r="K118" s="8">
-        <v>0</v>
-      </c>
-      <c r="L118" s="9" t="s">
+    </row>
+    <row r="119" s="2" customFormat="1" spans="1:13">
+      <c r="B119" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="M118" s="9"/>
-    </row>
-    <row r="119" spans="1:13">
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D119" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E119" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D119" s="7">
+      <c r="F119" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="G119" s="9">
+        <v>260</v>
+      </c>
+      <c r="H119" s="9">
+        <v>130</v>
+      </c>
+      <c r="I119" s="9">
+        <v>40028</v>
+      </c>
+      <c r="J119" s="9"/>
+      <c r="K119" s="9">
+        <v>2</v>
+      </c>
+      <c r="L119" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="M119" s="10"/>
+    </row>
+    <row r="120" s="2" customFormat="1" spans="1:13">
+      <c r="B120" s="22" t="s">
+        <v>530</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D120" s="9">
         <v>0.1</v>
       </c>
-      <c r="E119" t="s">
-        <v>528</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="G119" s="7">
-        <v>550</v>
-      </c>
-      <c r="H119" s="7">
-        <v>275</v>
-      </c>
-      <c r="I119" s="7">
-        <v>40024</v>
-      </c>
-      <c r="J119" s="16">
-        <v>11401</v>
-      </c>
-      <c r="K119" s="7">
-        <v>0</v>
-      </c>
-      <c r="L119" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13">
-      <c r="B120" s="1" t="s">
+      <c r="E120" s="10" t="s">
         <v>531</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D120" s="7">
+      <c r="F120" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="G120" s="9">
+        <v>270</v>
+      </c>
+      <c r="H120" s="9">
+        <v>135</v>
+      </c>
+      <c r="I120" s="9">
+        <v>40029</v>
+      </c>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9">
+        <v>2</v>
+      </c>
+      <c r="L120" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="M120" s="10"/>
+    </row>
+    <row r="121" s="2" customFormat="1" spans="1:13">
+      <c r="B121" s="22" t="s">
+        <v>534</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D121" s="9">
         <v>0.1</v>
       </c>
-      <c r="E120" t="s">
-        <v>532</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="G120" s="7">
-        <v>300</v>
-      </c>
-      <c r="H120" s="7">
-        <v>150</v>
-      </c>
-      <c r="I120" s="7">
-        <v>40025</v>
-      </c>
-      <c r="K120" s="7">
-        <v>0</v>
-      </c>
-      <c r="L120" s="7" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="121" s="2" customFormat="1" spans="1:13">
-      <c r="B121" s="8">
-        <v>426</v>
-      </c>
-      <c r="C121" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="D121" s="8">
+      <c r="E121" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="G121" s="9">
+        <v>280</v>
+      </c>
+      <c r="H121" s="9">
+        <v>140</v>
+      </c>
+      <c r="I121" s="9">
+        <v>40030</v>
+      </c>
+      <c r="J121" s="9">
+        <v>11601</v>
+      </c>
+      <c r="K121" s="9">
+        <v>0</v>
+      </c>
+      <c r="L121" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="M121" s="10"/>
+    </row>
+    <row r="122" s="2" customFormat="1" spans="1:13">
+      <c r="A122" s="10"/>
+      <c r="B122" s="22" t="s">
+        <v>538</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D122" s="9">
         <v>0.1</v>
       </c>
-      <c r="E121" s="9" t="s">
-        <v>535</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="G121" s="8">
-        <v>400</v>
-      </c>
-      <c r="H121" s="8">
-        <v>200</v>
-      </c>
-      <c r="I121" s="8">
-        <v>40026</v>
-      </c>
-      <c r="J121" s="16">
-        <v>11501</v>
-      </c>
-      <c r="K121" s="8">
-        <v>1</v>
-      </c>
-      <c r="L121" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="M121" s="9"/>
-    </row>
-    <row r="122" spans="1:13">
-      <c r="B122" s="7">
-        <v>427</v>
-      </c>
-      <c r="C122" t="s">
-        <v>420</v>
-      </c>
-      <c r="D122" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E122" t="s">
-        <v>538</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="E122" s="9" t="s">
         <v>539</v>
       </c>
-      <c r="G122" s="7">
-        <v>330</v>
-      </c>
-      <c r="H122" s="7">
-        <v>165</v>
-      </c>
-      <c r="I122" s="7">
-        <v>40027</v>
-      </c>
-      <c r="K122" s="7">
-        <v>1</v>
-      </c>
-      <c r="L122" t="s">
+      <c r="F122" s="9" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="123" s="2" customFormat="1" spans="1:13">
-      <c r="B123" s="8">
-        <v>428</v>
-      </c>
-      <c r="C123" s="9" t="s">
-        <v>420</v>
+      <c r="G122" s="2">
+        <v>260</v>
+      </c>
+      <c r="H122" s="2">
+        <v>130</v>
+      </c>
+      <c r="I122" s="9">
+        <v>40031</v>
+      </c>
+      <c r="J122" s="9"/>
+      <c r="K122" s="9">
+        <v>0</v>
+      </c>
+      <c r="L122" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="M122" s="10"/>
+    </row>
+    <row r="123" s="1" customFormat="1" spans="1:13">
+      <c r="B123" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C123" t="s">
+        <v>407</v>
       </c>
       <c r="D123" s="8">
         <v>0.1</v>
       </c>
-      <c r="E123" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>542</v>
+      <c r="E123" t="s">
+        <v>543</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>544</v>
       </c>
       <c r="G123" s="8">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="H123" s="8">
-        <v>130</v>
-      </c>
-      <c r="I123" s="8">
-        <v>40028</v>
-      </c>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8">
-        <v>2</v>
-      </c>
-      <c r="L123" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="M123" s="9"/>
-    </row>
-    <row r="124" s="2" customFormat="1" spans="1:13">
-      <c r="B124" s="8">
-        <v>429</v>
-      </c>
-      <c r="C124" s="9" t="s">
-        <v>420</v>
+        <v>250</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="L123" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="124" s="1" customFormat="1" spans="1:13">
+      <c r="B124" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C124" t="s">
+        <v>407</v>
       </c>
       <c r="D124" s="8">
         <v>0.1</v>
       </c>
-      <c r="E124" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="F124" s="9" t="s">
-        <v>545</v>
+      <c r="E124" t="s">
+        <v>549</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="G124" s="8">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="H124" s="8">
-        <v>135</v>
-      </c>
-      <c r="I124" s="8">
-        <v>40029</v>
-      </c>
-      <c r="J124" s="8"/>
-      <c r="K124" s="8">
-        <v>2</v>
-      </c>
-      <c r="L124" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="K124" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="M124" s="9"/>
-    </row>
-    <row r="125" s="2" customFormat="1" spans="1:13">
-      <c r="B125" s="8">
-        <v>430</v>
-      </c>
-      <c r="C125" s="9" t="s">
-        <v>420</v>
+      <c r="L124" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="125" s="1" customFormat="1" spans="1:13">
+      <c r="B125" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C125" t="s">
+        <v>407</v>
       </c>
       <c r="D125" s="8">
         <v>0.1</v>
       </c>
-      <c r="E125" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="F125" s="9" t="s">
-        <v>548</v>
+      <c r="E125" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>555</v>
       </c>
       <c r="G125" s="8">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="H125" s="8">
-        <v>140</v>
-      </c>
-      <c r="I125" s="8">
-        <v>40030</v>
-      </c>
-      <c r="J125" s="16">
-        <v>11601</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J125" s="8"/>
       <c r="K125" s="8">
         <v>0</v>
       </c>
-      <c r="L125" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="M125" s="9"/>
-    </row>
-    <row r="126" s="2" customFormat="1" spans="1:13">
-      <c r="A126" s="9"/>
-      <c r="B126" s="8">
-        <v>431</v>
-      </c>
-      <c r="C126" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="D126" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>550</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>551</v>
-      </c>
-      <c r="G126" s="2">
-        <v>260</v>
-      </c>
-      <c r="H126" s="2">
-        <v>130</v>
-      </c>
-      <c r="I126" s="8">
-        <v>40031</v>
-      </c>
-      <c r="J126" s="8"/>
-      <c r="K126" s="8">
-        <v>0</v>
-      </c>
-      <c r="L126" s="9" t="s">
-        <v>552</v>
-      </c>
-      <c r="M126" s="9"/>
+      <c r="L125" t="s">
+        <v>557</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -1081,7 +1081,7 @@
     <t>30016</t>
   </si>
   <si>
-    <t>每输1次敌人,结算时就永久提供+0.2倍率</t>
+    <t>每输1次敌人,结算时就永久提供+1倍率</t>
   </si>
   <si>
     <t>幸运同花</t>
@@ -1877,7 +1877,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1893,12 +1893,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2221,7 +2215,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -2245,16 +2239,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -2263,89 +2257,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2359,9 +2353,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -2398,19 +2389,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2766,16 +2745,16 @@
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8" style="7" customWidth="1"/>
-    <col min="4" max="4" width="4.78333333333333" style="8" customWidth="1"/>
-    <col min="5" max="5" width="8.8" style="8" customWidth="1"/>
-    <col min="6" max="6" width="10.1083333333333" style="8" customWidth="1"/>
-    <col min="7" max="7" width="5.975" style="8" customWidth="1"/>
-    <col min="8" max="8" width="4.78333333333333" style="8" customWidth="1"/>
-    <col min="9" max="9" width="7.38333333333333" style="8" customWidth="1"/>
-    <col min="10" max="10" width="5.53333333333333" style="8" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="6" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="7" customWidth="1"/>
+    <col min="5" max="5" width="8.8" style="7" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" style="7" customWidth="1"/>
+    <col min="7" max="7" width="5.975" style="7" customWidth="1"/>
+    <col min="8" max="8" width="4.78333333333333" style="7" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="7" customWidth="1"/>
+    <col min="10" max="10" width="5.53333333333333" style="7" customWidth="1"/>
     <col min="11" max="11" width="8.03333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.70833333333333" style="8" customWidth="1"/>
+    <col min="12" max="12" width="7.70833333333333" style="7" customWidth="1"/>
     <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
@@ -2790,31 +2769,31 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2828,31 +2807,31 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2866,31 +2845,31 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2901,25 +2880,25 @@
       <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>0.8</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>30</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>15</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>10001</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>0</v>
       </c>
       <c r="L5" t="s">
@@ -2933,26 +2912,26 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>0.8</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>28</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>14</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>10002</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8">
+      <c r="J6" s="7"/>
+      <c r="K6" s="7">
         <v>0</v>
       </c>
       <c r="L6" t="s">
@@ -2967,26 +2946,26 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>0.8</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>28</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>14</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <v>10003</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8">
+      <c r="J7" s="7"/>
+      <c r="K7" s="7">
         <v>0</v>
       </c>
       <c r="L7" t="s">
@@ -3001,26 +2980,26 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>0.8</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>28</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>14</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>10004</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8">
+      <c r="J8" s="7"/>
+      <c r="K8" s="7">
         <v>0</v>
       </c>
       <c r="L8" t="s">
@@ -3035,26 +3014,26 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>0.8</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>28</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>14</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <v>10005</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8">
+      <c r="J9" s="7"/>
+      <c r="K9" s="7">
         <v>0</v>
       </c>
       <c r="L9" t="s">
@@ -3069,26 +3048,26 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>0.8</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>28</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>14</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="7">
         <v>10006</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8">
+      <c r="J10" s="7"/>
+      <c r="K10" s="7">
         <v>0</v>
       </c>
       <c r="L10" t="s">
@@ -3103,26 +3082,26 @@
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>0.8</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="7">
         <v>22</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>11</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <v>10007</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8">
+      <c r="J11" s="7"/>
+      <c r="K11" s="7">
         <v>0</v>
       </c>
       <c r="L11" t="s">
@@ -3137,26 +3116,26 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>0.8</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="7">
         <v>35</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>17</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>10008</v>
       </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8">
+      <c r="J12" s="7"/>
+      <c r="K12" s="7">
         <v>0</v>
       </c>
       <c r="L12" t="s">
@@ -3171,26 +3150,26 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>0.8</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>16</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <v>8</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>10009</v>
       </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7">
         <v>0</v>
       </c>
       <c r="L13" t="s">
@@ -3205,26 +3184,26 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>0.8</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="7">
         <v>16</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <v>8</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <v>10010</v>
       </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8">
+      <c r="J14" s="7"/>
+      <c r="K14" s="7">
         <v>0</v>
       </c>
       <c r="L14" t="s">
@@ -3239,32 +3218,32 @@
       <c r="C15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>0.8</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="8">
         <v>15</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>7</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="8">
         <v>10011</v>
       </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10" t="s">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="10"/>
+      <c r="M15" s="9"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:13">
       <c r="B16" s="1" t="s">
@@ -3273,26 +3252,26 @@
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>0.8</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>30</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>15</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <v>10012</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8">
+      <c r="J16" s="7"/>
+      <c r="K16" s="7">
         <v>0</v>
       </c>
       <c r="L16" t="s">
@@ -3306,26 +3285,26 @@
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>0.8</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>35</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>17</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <v>10013</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7">
         <v>0</v>
       </c>
       <c r="L17" t="s">
@@ -3339,26 +3318,26 @@
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>0.8</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="7">
         <v>26</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>13</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <v>10014</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8">
+      <c r="J18" s="7"/>
+      <c r="K18" s="7">
         <v>0</v>
       </c>
       <c r="L18" t="s">
@@ -3372,26 +3351,26 @@
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>0.8</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>22</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>11</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <v>10015</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8">
+      <c r="J19" s="7"/>
+      <c r="K19" s="7">
         <v>0</v>
       </c>
       <c r="L19" t="s">
@@ -3405,29 +3384,29 @@
       <c r="C20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>0.8</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="8">
         <v>28</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="8">
         <v>14</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="8">
         <v>10016</v>
       </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="10" t="s">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3438,29 +3417,29 @@
       <c r="C21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>0.8</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>20</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>10</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="8">
         <v>10017</v>
       </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9">
-        <v>0</v>
-      </c>
-      <c r="L21" s="10" t="s">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3471,7 +3450,7 @@
       <c r="C22" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>0.8</v>
       </c>
       <c r="E22" t="s">
@@ -3480,16 +3459,16 @@
       <c r="F22" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="7">
         <v>25</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="7">
         <v>12</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="7">
         <v>10018</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="7">
         <v>1</v>
       </c>
       <c r="L22" t="s">
@@ -3503,7 +3482,7 @@
       <c r="C23" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>0.8</v>
       </c>
       <c r="E23" t="s">
@@ -3512,16 +3491,16 @@
       <c r="F23" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="7">
         <v>25</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <v>12</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="7">
         <v>10019</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="7">
         <v>1</v>
       </c>
       <c r="L23" t="s">
@@ -3532,35 +3511,35 @@
       <c r="B24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>0.8</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="8">
         <v>30</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="8">
         <v>15</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="8">
         <v>10020</v>
       </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9">
-        <v>0</v>
-      </c>
-      <c r="L24" s="10" t="s">
+      <c r="J24" s="8"/>
+      <c r="K24" s="8">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="10"/>
+      <c r="M24" s="9"/>
     </row>
     <row r="25" spans="1:13">
       <c r="B25" s="1" t="s">
@@ -3569,7 +3548,7 @@
       <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>0.8</v>
       </c>
       <c r="E25" t="s">
@@ -3578,16 +3557,16 @@
       <c r="F25" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="7">
         <v>35</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>17</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="7">
         <v>10021</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="7">
         <v>2</v>
       </c>
       <c r="L25" t="s">
@@ -3599,7 +3578,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="K26" s="8"/>
+      <c r="K26" s="7"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
       <c r="B27" s="1" t="s">
@@ -3608,13 +3587,13 @@
       <c r="C27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>0.4</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>116</v>
       </c>
       <c r="G27" s="1">
@@ -3626,8 +3605,8 @@
       <c r="I27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8">
+      <c r="J27" s="7"/>
+      <c r="K27" s="7">
         <v>0</v>
       </c>
       <c r="L27" t="s">
@@ -3642,13 +3621,13 @@
       <c r="C28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>0.4</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="7" t="s">
         <v>121</v>
       </c>
       <c r="G28" s="1">
@@ -3660,8 +3639,8 @@
       <c r="I28" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8">
+      <c r="J28" s="7"/>
+      <c r="K28" s="7">
         <v>0</v>
       </c>
       <c r="L28" t="s">
@@ -3677,13 +3656,13 @@
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>0.4</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="7" t="s">
         <v>126</v>
       </c>
       <c r="G29" s="1">
@@ -3695,8 +3674,8 @@
       <c r="I29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8">
+      <c r="J29" s="7"/>
+      <c r="K29" s="7">
         <v>0</v>
       </c>
       <c r="L29" t="s">
@@ -3712,13 +3691,13 @@
       <c r="C30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>0.4</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="7" t="s">
         <v>131</v>
       </c>
       <c r="G30" s="1">
@@ -3730,8 +3709,8 @@
       <c r="I30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8">
+      <c r="J30" s="7"/>
+      <c r="K30" s="7">
         <v>0</v>
       </c>
       <c r="L30" t="s">
@@ -3747,13 +3726,13 @@
       <c r="C31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>0.4</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="7" t="s">
         <v>136</v>
       </c>
       <c r="G31" s="1">
@@ -3765,8 +3744,8 @@
       <c r="I31" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8">
+      <c r="J31" s="7"/>
+      <c r="K31" s="7">
         <v>0</v>
       </c>
       <c r="L31" t="s">
@@ -3782,13 +3761,13 @@
       <c r="C32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>0.4</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="7" t="s">
         <v>141</v>
       </c>
       <c r="G32" s="1">
@@ -3800,8 +3779,8 @@
       <c r="I32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8">
+      <c r="J32" s="7"/>
+      <c r="K32" s="7">
         <v>0</v>
       </c>
       <c r="L32" t="s">
@@ -3817,13 +3796,13 @@
       <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>0.4</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="7" t="s">
         <v>146</v>
       </c>
       <c r="G33" s="1">
@@ -3835,8 +3814,8 @@
       <c r="I33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8">
+      <c r="J33" s="7"/>
+      <c r="K33" s="7">
         <v>0</v>
       </c>
       <c r="L33" t="s">
@@ -3852,13 +3831,13 @@
       <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <v>0.4</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="7" t="s">
         <v>151</v>
       </c>
       <c r="G34" s="1">
@@ -3870,8 +3849,8 @@
       <c r="I34" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8">
+      <c r="J34" s="7"/>
+      <c r="K34" s="7">
         <v>0</v>
       </c>
       <c r="L34" t="s">
@@ -3887,13 +3866,13 @@
       <c r="C35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>0.4</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="7" t="s">
         <v>156</v>
       </c>
       <c r="G35" s="1">
@@ -3905,8 +3884,8 @@
       <c r="I35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8">
+      <c r="J35" s="7"/>
+      <c r="K35" s="7">
         <v>0</v>
       </c>
       <c r="L35" t="s">
@@ -3915,20 +3894,20 @@
       <c r="M35"/>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:13">
-      <c r="A36" s="11"/>
+      <c r="A36" s="10"/>
       <c r="B36" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="11">
         <v>0.4</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="11" t="s">
         <v>161</v>
       </c>
       <c r="G36" s="3">
@@ -3940,14 +3919,14 @@
       <c r="I36" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12">
+      <c r="J36" s="11"/>
+      <c r="K36" s="11">
         <v>0</v>
       </c>
       <c r="L36" t="s">
         <v>163</v>
       </c>
-      <c r="M36" s="11"/>
+      <c r="M36" s="10"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37"/>
@@ -3957,13 +3936,13 @@
       <c r="C37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="7">
         <v>0.4</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="7" t="s">
         <v>166</v>
       </c>
       <c r="G37" s="1">
@@ -3975,28 +3954,28 @@
       <c r="I37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="K37" s="8">
-        <v>0</v>
-      </c>
-      <c r="L37" s="8" t="s">
+      <c r="K37" s="7">
+        <v>0</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="38" s="4" customFormat="1" spans="1:13">
-      <c r="A38" s="13"/>
+      <c r="A38" s="12"/>
       <c r="B38" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="13">
         <v>0.4</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="13" t="s">
         <v>171</v>
       </c>
       <c r="G38" s="4">
@@ -4008,14 +3987,14 @@
       <c r="I38" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14">
-        <v>0</v>
-      </c>
-      <c r="L38" s="13" t="s">
+      <c r="J38" s="13"/>
+      <c r="K38" s="13">
+        <v>0</v>
+      </c>
+      <c r="L38" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="M38" s="13"/>
+      <c r="M38" s="12"/>
     </row>
     <row r="39" spans="1:13">
       <c r="A39"/>
@@ -4025,13 +4004,13 @@
       <c r="C39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="7">
         <v>0.4</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="7" t="s">
         <v>176</v>
       </c>
       <c r="G39" s="1">
@@ -4043,7 +4022,7 @@
       <c r="I39" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="K39" s="8">
+      <c r="K39" s="7">
         <v>0</v>
       </c>
       <c r="L39" t="s">
@@ -4058,13 +4037,13 @@
       <c r="C40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="7">
         <v>0.4</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="7" t="s">
         <v>181</v>
       </c>
       <c r="G40" s="1">
@@ -4076,7 +4055,7 @@
       <c r="I40" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K40" s="8">
+      <c r="K40" s="7">
         <v>0</v>
       </c>
       <c r="L40" t="s">
@@ -4091,13 +4070,13 @@
       <c r="C41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="7">
         <v>0.4</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G41" s="1">
@@ -4109,7 +4088,7 @@
       <c r="I41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K41" s="8">
+      <c r="K41" s="7">
         <v>0</v>
       </c>
       <c r="L41" t="s">
@@ -4124,13 +4103,13 @@
       <c r="C42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>0.4</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="7" t="s">
         <v>191</v>
       </c>
       <c r="G42" s="1">
@@ -4142,7 +4121,7 @@
       <c r="I42" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K42" s="8">
+      <c r="K42" s="7">
         <v>0</v>
       </c>
       <c r="L42" t="s">
@@ -4157,13 +4136,13 @@
       <c r="C43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="7">
         <v>0.4</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="7" t="s">
         <v>196</v>
       </c>
       <c r="G43" s="1">
@@ -4175,7 +4154,7 @@
       <c r="I43" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K43" s="8">
+      <c r="K43" s="7">
         <v>0</v>
       </c>
       <c r="L43" t="s">
@@ -4190,97 +4169,97 @@
       <c r="C44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="7">
         <v>0.4</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="7">
         <v>85</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="7">
         <v>42</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8">
-        <v>0</v>
-      </c>
-      <c r="L44" s="8" t="s">
+      <c r="J44" s="7"/>
+      <c r="K44" s="7">
+        <v>0</v>
+      </c>
+      <c r="L44" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" spans="1:13">
-      <c r="A45" s="10"/>
+      <c r="A45" s="9"/>
       <c r="B45" s="2" t="s">
         <v>204</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="8">
         <v>0.4</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="8">
         <v>75</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="8">
         <v>37</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9">
-        <v>0</v>
-      </c>
-      <c r="L45" s="10" t="s">
+      <c r="J45" s="8"/>
+      <c r="K45" s="8">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" spans="1:13">
-      <c r="A46" s="10"/>
+      <c r="A46" s="9"/>
       <c r="B46" s="2" t="s">
         <v>209</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>0.4</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="8">
         <v>75</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="8">
         <v>37</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9">
-        <v>0</v>
-      </c>
-      <c r="L46" s="10" t="s">
+      <c r="J46" s="8"/>
+      <c r="K46" s="8">
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="s">
         <v>213</v>
       </c>
     </row>
@@ -4292,26 +4271,26 @@
       <c r="C47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="7">
         <v>0.4</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="7">
         <v>70</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="7">
         <v>35</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8">
+      <c r="J47" s="7"/>
+      <c r="K47" s="7">
         <v>0</v>
       </c>
       <c r="L47" t="s">
@@ -4326,26 +4305,26 @@
       <c r="C48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="7">
         <v>0.4</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="7">
         <v>75</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="7">
         <v>37</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8">
+      <c r="J48" s="7"/>
+      <c r="K48" s="7">
         <v>0</v>
       </c>
       <c r="L48" t="s">
@@ -4359,31 +4338,31 @@
       <c r="C49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="7">
         <v>0.4</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="7">
         <v>90</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="7">
         <v>45</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="7">
         <v>10301</v>
       </c>
-      <c r="K49" s="8">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8" t="s">
+      <c r="K49" s="7">
+        <v>0</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>228</v>
       </c>
     </row>
@@ -4395,28 +4374,28 @@
       <c r="C50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="7">
         <v>0.4</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="7">
         <v>120</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="7">
         <v>60</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="K50" s="8">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8" t="s">
+      <c r="K50" s="7">
+        <v>0</v>
+      </c>
+      <c r="L50" s="7" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4428,25 +4407,25 @@
       <c r="C51" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="7">
         <v>0.4</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="7">
         <v>110</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="7">
         <v>55</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="K51" s="8">
+      <c r="K51" s="7">
         <v>0</v>
       </c>
       <c r="L51" t="s">
@@ -4454,39 +4433,39 @@
       </c>
     </row>
     <row r="52" s="2" customFormat="1" spans="1:13">
-      <c r="A52" s="10"/>
+      <c r="A52" s="9"/>
       <c r="B52" s="2" t="s">
         <v>239</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>0.4</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="8">
         <v>70</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="8">
         <v>35</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9">
-        <v>0</v>
-      </c>
-      <c r="L52" s="10" t="s">
+      <c r="J52" s="8"/>
+      <c r="K52" s="8">
+        <v>0</v>
+      </c>
+      <c r="L52" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="M52" s="10"/>
+      <c r="M52" s="9"/>
     </row>
     <row r="53" spans="1:13">
       <c r="B53" s="1" t="s">
@@ -4495,7 +4474,7 @@
       <c r="C53" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="7">
         <v>0.4</v>
       </c>
       <c r="E53" t="s">
@@ -4504,16 +4483,16 @@
       <c r="F53" t="s">
         <v>246</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="7">
         <v>90</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="7">
         <v>45</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K53" s="8">
+      <c r="K53" s="7">
         <v>1</v>
       </c>
       <c r="L53" t="s">
@@ -4527,7 +4506,7 @@
       <c r="C54" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="7">
         <v>0.4</v>
       </c>
       <c r="E54" t="s">
@@ -4536,16 +4515,16 @@
       <c r="F54" t="s">
         <v>251</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="7">
         <v>145</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="7">
         <v>72</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="K54" s="8">
+      <c r="K54" s="7">
         <v>1</v>
       </c>
       <c r="L54" t="s">
@@ -4559,7 +4538,7 @@
       <c r="C55" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="7">
         <v>0.4</v>
       </c>
       <c r="E55" t="s">
@@ -4568,16 +4547,16 @@
       <c r="F55" t="s">
         <v>256</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="7">
         <v>75</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="7">
         <v>37</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="K55" s="8">
+      <c r="K55" s="7">
         <v>0</v>
       </c>
       <c r="L55" t="s">
@@ -4591,7 +4570,7 @@
       <c r="C56" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="7">
         <v>0.4</v>
       </c>
       <c r="E56" t="s">
@@ -4600,16 +4579,16 @@
       <c r="F56" t="s">
         <v>261</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="7">
         <v>110</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="7">
         <v>55</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="K56" s="8">
+      <c r="K56" s="7">
         <v>1</v>
       </c>
       <c r="L56" t="s">
@@ -4623,7 +4602,7 @@
       <c r="C57" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="7">
         <v>0.4</v>
       </c>
       <c r="E57" t="s">
@@ -4632,17 +4611,17 @@
       <c r="F57" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="7">
         <v>160</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="7">
         <v>80</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8">
+      <c r="J57" s="7"/>
+      <c r="K57" s="7">
         <v>2</v>
       </c>
       <c r="L57" t="s">
@@ -4657,7 +4636,7 @@
       <c r="C58" t="s">
         <v>114</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="7">
         <v>0.4</v>
       </c>
       <c r="E58" t="s">
@@ -4666,151 +4645,151 @@
       <c r="F58" t="s">
         <v>271</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="7">
         <v>160</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="7">
         <v>80</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="K58" s="8">
+      <c r="K58" s="7">
         <v>2</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L58" s="7" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="59" s="5" customFormat="1" spans="1:13">
-      <c r="A59" s="15"/>
+      <c r="A59" s="14"/>
       <c r="B59" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="16">
+      <c r="D59" s="15">
         <v>0.4</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="F59" s="15" t="s">
+      <c r="F59" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="15">
         <v>80</v>
       </c>
-      <c r="H59" s="16">
+      <c r="H59" s="15">
         <v>40</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="J59" s="16"/>
-      <c r="K59" s="16">
-        <v>0</v>
-      </c>
-      <c r="L59" s="15" t="s">
+      <c r="J59" s="15"/>
+      <c r="K59" s="15">
+        <v>0</v>
+      </c>
+      <c r="L59" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="M59" s="15"/>
+      <c r="M59" s="14"/>
     </row>
     <row r="60" s="5" customFormat="1" spans="1:13">
-      <c r="A60" s="15"/>
+      <c r="A60" s="14"/>
       <c r="B60" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="16">
+      <c r="D60" s="15">
         <v>0.4</v>
       </c>
-      <c r="E60" s="16" t="s">
+      <c r="E60" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="F60" s="15" t="s">
+      <c r="F60" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="15">
         <v>80</v>
       </c>
-      <c r="H60" s="16">
+      <c r="H60" s="15">
         <v>40</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="J60" s="16"/>
-      <c r="K60" s="16">
-        <v>0</v>
-      </c>
-      <c r="L60" s="15" t="s">
+      <c r="J60" s="15"/>
+      <c r="K60" s="15">
+        <v>0</v>
+      </c>
+      <c r="L60" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="M60" s="15"/>
+      <c r="M60" s="14"/>
     </row>
     <row r="61" s="5" customFormat="1" spans="1:13">
-      <c r="A61" s="15"/>
+      <c r="A61" s="14"/>
       <c r="B61" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D61" s="16">
+      <c r="D61" s="15">
         <v>0.4</v>
       </c>
-      <c r="E61" s="16" t="s">
+      <c r="E61" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="F61" s="15" t="s">
+      <c r="F61" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="15">
         <v>80</v>
       </c>
-      <c r="H61" s="16">
+      <c r="H61" s="15">
         <v>40</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="16"/>
-      <c r="K61" s="16">
-        <v>0</v>
-      </c>
-      <c r="L61" s="15" t="s">
+      <c r="J61" s="15"/>
+      <c r="K61" s="15">
+        <v>0</v>
+      </c>
+      <c r="L61" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="M61" s="15"/>
+      <c r="M61" s="14"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62"/>
-      <c r="B62" s="8"/>
+      <c r="B62" s="7"/>
       <c r="C62" s="1"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="K62" s="8"/>
+      <c r="K62" s="7"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63"/>
-      <c r="B63" s="8">
+      <c r="B63" s="7">
         <v>301</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="7">
         <v>0.2</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="F63" s="7" t="s">
         <v>291</v>
       </c>
       <c r="G63" s="1">
@@ -4822,10 +4801,10 @@
       <c r="I63" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="J63" s="8">
+      <c r="J63" s="7">
         <v>10401</v>
       </c>
-      <c r="K63" s="8">
+      <c r="K63" s="7">
         <v>0</v>
       </c>
       <c r="L63" t="s">
@@ -4834,19 +4813,19 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64"/>
-      <c r="B64" s="8">
+      <c r="B64" s="7">
         <v>302</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="7">
         <v>0.2</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="F64" s="7" t="s">
         <v>295</v>
       </c>
       <c r="G64" s="1">
@@ -4858,7 +4837,7 @@
       <c r="I64" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="K64" s="8">
+      <c r="K64" s="7">
         <v>0</v>
       </c>
       <c r="L64" t="s">
@@ -4867,19 +4846,19 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65"/>
-      <c r="B65" s="8">
+      <c r="B65" s="7">
         <v>303</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="7">
         <v>0.2</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="F65" s="7" t="s">
         <v>299</v>
       </c>
       <c r="G65" s="1">
@@ -4891,10 +4870,10 @@
       <c r="I65" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="J65" s="17">
+      <c r="J65" s="16">
         <v>10501</v>
       </c>
-      <c r="K65" s="8">
+      <c r="K65" s="7">
         <v>0</v>
       </c>
       <c r="L65" t="s">
@@ -4902,20 +4881,20 @@
       </c>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:13">
-      <c r="A66" s="10"/>
-      <c r="B66" s="18">
+      <c r="A66" s="9"/>
+      <c r="B66" s="8">
         <v>304</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="8">
         <v>0.2</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="E66" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="F66" s="8" t="s">
         <v>303</v>
       </c>
       <c r="G66" s="2">
@@ -4927,31 +4906,31 @@
       <c r="I66" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="J66" s="9">
+      <c r="J66" s="8">
         <v>10601</v>
       </c>
-      <c r="K66" s="9">
-        <v>0</v>
-      </c>
-      <c r="L66" s="10" t="s">
+      <c r="K66" s="8">
+        <v>0</v>
+      </c>
+      <c r="L66" s="9" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:13">
       <c r="A67"/>
-      <c r="B67" s="8">
+      <c r="B67" s="7">
         <v>305</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="7">
         <v>0.2</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="7" t="s">
         <v>307</v>
       </c>
       <c r="G67" s="1">
@@ -4963,10 +4942,10 @@
       <c r="I67" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="J67" s="8">
+      <c r="J67" s="7">
         <v>10701</v>
       </c>
-      <c r="K67" s="8">
+      <c r="K67" s="7">
         <v>0</v>
       </c>
       <c r="L67" t="s">
@@ -4974,19 +4953,19 @@
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:13">
-      <c r="B68" s="8">
+      <c r="B68" s="7">
         <v>306</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="7">
         <v>0.2</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="7" t="s">
         <v>311</v>
       </c>
       <c r="G68" s="1">
@@ -4998,7 +4977,7 @@
       <c r="I68" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="K68" s="8">
+      <c r="K68" s="7">
         <v>0</v>
       </c>
       <c r="L68" t="s">
@@ -5006,19 +4985,19 @@
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:13">
-      <c r="B69" s="8">
+      <c r="B69" s="7">
         <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="7">
         <v>0.2</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="7" t="s">
         <v>315</v>
       </c>
       <c r="G69" s="1">
@@ -5030,8 +5009,8 @@
       <c r="I69" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8">
+      <c r="J69" s="7"/>
+      <c r="K69" s="7">
         <v>0</v>
       </c>
       <c r="L69" t="s">
@@ -5039,19 +5018,19 @@
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:13">
-      <c r="B70" s="8">
+      <c r="B70" s="7">
         <v>308</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="7">
         <v>0.2</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="7" t="s">
         <v>319</v>
       </c>
       <c r="G70" s="1">
@@ -5063,7 +5042,7 @@
       <c r="I70" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="K70" s="8">
+      <c r="K70" s="7">
         <v>0</v>
       </c>
       <c r="L70" t="s">
@@ -5071,19 +5050,19 @@
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:13">
-      <c r="B71" s="8">
+      <c r="B71" s="7">
         <v>309</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="7">
         <v>0.2</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="7" t="s">
         <v>323</v>
       </c>
       <c r="G71" s="1">
@@ -5095,28 +5074,28 @@
       <c r="I71" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8">
-        <v>0</v>
-      </c>
-      <c r="L71" s="8" t="s">
+      <c r="J71" s="7"/>
+      <c r="K71" s="7">
+        <v>0</v>
+      </c>
+      <c r="L71" s="7" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" spans="1:13">
-      <c r="B72" s="18">
+      <c r="B72" s="8">
         <v>310</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>0.2</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="E72" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="F72" s="9" t="s">
+      <c r="F72" s="8" t="s">
         <v>327</v>
       </c>
       <c r="G72" s="2">
@@ -5128,27 +5107,27 @@
       <c r="I72" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="K72" s="9">
-        <v>0</v>
-      </c>
-      <c r="L72" s="10" t="s">
+      <c r="K72" s="8">
+        <v>0</v>
+      </c>
+      <c r="L72" s="9" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" spans="1:13">
-      <c r="B73" s="18">
+      <c r="B73" s="8">
         <v>311</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D73" s="9">
+      <c r="D73" s="8">
         <v>0.2</v>
       </c>
-      <c r="E73" s="9" t="s">
+      <c r="E73" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F73" s="8" t="s">
         <v>331</v>
       </c>
       <c r="G73" s="2">
@@ -5160,27 +5139,27 @@
       <c r="I73" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="K73" s="9">
-        <v>0</v>
-      </c>
-      <c r="L73" s="10" t="s">
+      <c r="K73" s="8">
+        <v>0</v>
+      </c>
+      <c r="L73" s="9" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:13">
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>312</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="7">
         <v>0.2</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="7" t="s">
         <v>335</v>
       </c>
       <c r="G74" s="1">
@@ -5192,8 +5171,8 @@
       <c r="I74" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8">
+      <c r="J74" s="7"/>
+      <c r="K74" s="7">
         <v>0</v>
       </c>
       <c r="L74" t="s">
@@ -5201,32 +5180,32 @@
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:13">
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>313</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="7">
         <v>0.2</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="7">
         <v>180</v>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="7">
         <v>90</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8">
+      <c r="J75" s="7"/>
+      <c r="K75" s="7">
         <v>0</v>
       </c>
       <c r="L75" t="s">
@@ -5234,32 +5213,32 @@
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:13">
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="7">
         <v>0.2</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="7">
         <v>380</v>
       </c>
-      <c r="H76" s="8">
+      <c r="H76" s="7">
         <v>190</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8">
+      <c r="J76" s="7"/>
+      <c r="K76" s="7">
         <v>0</v>
       </c>
       <c r="L76" t="s">
@@ -5267,31 +5246,31 @@
       </c>
     </row>
     <row r="77" spans="1:13">
-      <c r="B77" s="8">
+      <c r="B77" s="7">
         <v>315</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="7">
         <v>0.2</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E77" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="7">
         <v>170</v>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="7">
         <v>85</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="K77" s="8">
+      <c r="K77" s="7">
         <v>0</v>
       </c>
       <c r="L77" t="s">
@@ -5299,69 +5278,69 @@
       </c>
     </row>
     <row r="78" spans="1:13">
-      <c r="B78" s="8">
+      <c r="B78" s="7">
         <v>316</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="7">
         <v>0.2</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F78" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="7">
         <v>200</v>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="7">
         <v>100</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="J78" s="8">
+      <c r="J78" s="7">
         <v>10201</v>
       </c>
-      <c r="K78" s="8">
-        <v>0</v>
-      </c>
-      <c r="L78" s="8" t="s">
+      <c r="K78" s="7">
+        <v>0</v>
+      </c>
+      <c r="L78" s="7" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="79" spans="1:13">
-      <c r="B79" s="8">
+      <c r="B79" s="7">
         <v>317</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="7">
         <v>0.2</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="7">
         <v>170</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="7">
         <v>85</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J79" s="17">
+      <c r="J79" s="16">
         <v>10801</v>
       </c>
-      <c r="K79" s="8">
+      <c r="K79" s="7">
         <v>0</v>
       </c>
       <c r="L79" t="s">
@@ -5369,67 +5348,67 @@
       </c>
     </row>
     <row r="80" s="2" customFormat="1" spans="1:13">
-      <c r="B80" s="18">
+      <c r="B80" s="8">
         <v>318</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <v>0.2</v>
       </c>
-      <c r="E80" s="9" t="s">
+      <c r="E80" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="F80" s="9" t="s">
+      <c r="F80" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="8">
         <v>160</v>
       </c>
-      <c r="H80" s="9">
+      <c r="H80" s="8">
         <v>80</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="J80" s="9">
+      <c r="J80" s="8">
         <v>10402</v>
       </c>
-      <c r="K80" s="9">
-        <v>0</v>
-      </c>
-      <c r="L80" s="10" t="s">
+      <c r="K80" s="8">
+        <v>0</v>
+      </c>
+      <c r="L80" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="M80" s="10"/>
+      <c r="M80" s="9"/>
     </row>
     <row r="81" spans="2:13">
-      <c r="B81" s="8">
+      <c r="B81" s="7">
         <v>319</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="7">
         <v>0.2</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="F81" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="7">
         <v>160</v>
       </c>
-      <c r="H81" s="8">
+      <c r="H81" s="7">
         <v>80</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="K81" s="8">
+      <c r="K81" s="7">
         <v>0</v>
       </c>
       <c r="L81" t="s">
@@ -5437,31 +5416,31 @@
       </c>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="8">
+      <c r="B82" s="7">
         <v>320</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="7">
         <v>0.2</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="F82" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="7">
         <v>160</v>
       </c>
-      <c r="H82" s="8">
+      <c r="H82" s="7">
         <v>80</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="K82" s="8">
+      <c r="K82" s="7">
         <v>0</v>
       </c>
       <c r="L82" t="s">
@@ -5469,31 +5448,31 @@
       </c>
     </row>
     <row r="83" spans="2:13">
-      <c r="B83" s="8">
+      <c r="B83" s="7">
         <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="7">
         <v>0.2</v>
       </c>
-      <c r="E83" s="8" t="s">
+      <c r="E83" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="F83" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="G83" s="8">
+      <c r="G83" s="7">
         <v>160</v>
       </c>
-      <c r="H83" s="8">
+      <c r="H83" s="7">
         <v>80</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="K83" s="8">
+      <c r="K83" s="7">
         <v>0</v>
       </c>
       <c r="L83" t="s">
@@ -5501,31 +5480,31 @@
       </c>
     </row>
     <row r="84" spans="2:13">
-      <c r="B84" s="8">
+      <c r="B84" s="7">
         <v>322</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="7">
         <v>0.2</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F84" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="7">
         <v>190</v>
       </c>
-      <c r="H84" s="8">
+      <c r="H84" s="7">
         <v>95</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="K84" s="8">
+      <c r="K84" s="7">
         <v>0</v>
       </c>
       <c r="L84" t="s">
@@ -5533,68 +5512,68 @@
       </c>
     </row>
     <row r="85" s="2" customFormat="1" spans="2:13">
-      <c r="B85" s="18">
+      <c r="B85" s="8">
         <v>323</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="8">
         <v>0.2</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="E85" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="F85" s="9" t="s">
+      <c r="F85" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="8">
         <v>175</v>
       </c>
-      <c r="H85" s="9">
+      <c r="H85" s="8">
         <v>87</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="J85" s="9"/>
-      <c r="K85" s="9">
-        <v>0</v>
-      </c>
-      <c r="L85" s="10" t="s">
+      <c r="J85" s="8"/>
+      <c r="K85" s="8">
+        <v>0</v>
+      </c>
+      <c r="L85" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="M85" s="10"/>
+      <c r="M85" s="9"/>
     </row>
     <row r="86" spans="2:13">
-      <c r="B86" s="8">
+      <c r="B86" s="7">
         <v>324</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="7">
         <v>0.2</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="F86" s="8" t="s">
+      <c r="F86" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="7">
         <v>270</v>
       </c>
-      <c r="H86" s="8">
+      <c r="H86" s="7">
         <v>135</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="J86" s="17">
+      <c r="J86" s="16">
         <v>10502</v>
       </c>
-      <c r="K86" s="8">
+      <c r="K86" s="7">
         <v>0</v>
       </c>
       <c r="L86" t="s">
@@ -5602,187 +5581,187 @@
       </c>
     </row>
     <row r="87" s="2" customFormat="1" spans="2:13">
-      <c r="B87" s="18">
+      <c r="B87" s="8">
         <v>325</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="8">
         <v>0.2</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="9" t="s">
         <v>386</v>
       </c>
-      <c r="F87" s="10" t="s">
+      <c r="F87" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="8">
         <v>160</v>
       </c>
-      <c r="H87" s="9">
+      <c r="H87" s="8">
         <v>80</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="J87" s="9"/>
-      <c r="K87" s="9">
+      <c r="J87" s="8"/>
+      <c r="K87" s="8">
         <v>2</v>
       </c>
-      <c r="L87" s="10" t="s">
+      <c r="L87" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="M87" s="10"/>
+      <c r="M87" s="9"/>
     </row>
     <row r="88" s="2" customFormat="1" spans="2:13">
-      <c r="B88" s="18">
+      <c r="B88" s="8">
         <v>326</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="8">
         <v>0.2</v>
       </c>
-      <c r="E88" s="10" t="s">
+      <c r="E88" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="F88" s="10" t="s">
+      <c r="F88" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="8">
         <v>200</v>
       </c>
-      <c r="H88" s="9">
+      <c r="H88" s="8">
         <v>100</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="J88" s="9">
+      <c r="J88" s="8">
         <v>10901</v>
       </c>
-      <c r="K88" s="9">
+      <c r="K88" s="8">
         <v>2</v>
       </c>
-      <c r="L88" s="10" t="s">
+      <c r="L88" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="M88" s="10"/>
+      <c r="M88" s="9"/>
     </row>
     <row r="89" s="2" customFormat="1" spans="2:13">
-      <c r="B89" s="18">
+      <c r="B89" s="8">
         <v>327</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C89" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="8">
         <v>0.2</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="9" t="s">
         <v>394</v>
       </c>
-      <c r="F89" s="10" t="s">
+      <c r="F89" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="8">
         <v>170</v>
       </c>
-      <c r="H89" s="9">
+      <c r="H89" s="8">
         <v>85</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="J89" s="9"/>
-      <c r="K89" s="9">
+      <c r="J89" s="8"/>
+      <c r="K89" s="8">
         <v>1</v>
       </c>
-      <c r="L89" s="10" t="s">
+      <c r="L89" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="M89" s="10"/>
-    </row>
-    <row r="90" s="6" customFormat="1" spans="2:13">
-      <c r="B90" s="8">
+      <c r="M89" s="9"/>
+    </row>
+    <row r="90" s="5" customFormat="1" spans="2:13">
+      <c r="B90" s="7">
         <v>328</v>
       </c>
-      <c r="C90" s="19" t="s">
+      <c r="C90" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="20">
+      <c r="D90" s="15">
         <v>0.2</v>
       </c>
-      <c r="E90" s="19" t="s">
+      <c r="E90" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="F90" s="19" t="s">
+      <c r="F90" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="G90" s="20">
+      <c r="G90" s="15">
         <v>160</v>
       </c>
-      <c r="H90" s="20">
+      <c r="H90" s="15">
         <v>80</v>
       </c>
-      <c r="I90" s="6" t="s">
+      <c r="I90" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="J90" s="20"/>
-      <c r="K90" s="20">
+      <c r="J90" s="15"/>
+      <c r="K90" s="15">
         <v>1</v>
       </c>
-      <c r="L90" s="19" t="s">
+      <c r="L90" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="M90" s="19"/>
-    </row>
-    <row r="91" s="6" customFormat="1" spans="2:13">
-      <c r="B91" s="8">
+      <c r="M90" s="14"/>
+    </row>
+    <row r="91" s="5" customFormat="1" spans="2:13">
+      <c r="B91" s="7">
         <v>329</v>
       </c>
-      <c r="C91" s="19" t="s">
+      <c r="C91" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="D91" s="20">
+      <c r="D91" s="15">
         <v>0.2</v>
       </c>
-      <c r="E91" s="20" t="s">
+      <c r="E91" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="F91" s="19" t="s">
+      <c r="F91" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="G91" s="20">
+      <c r="G91" s="15">
         <v>200</v>
       </c>
-      <c r="H91" s="20">
+      <c r="H91" s="15">
         <v>100</v>
       </c>
-      <c r="I91" s="6" t="s">
+      <c r="I91" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="J91" s="21">
+      <c r="J91" s="17">
         <v>11005</v>
       </c>
-      <c r="K91" s="20">
-        <v>0</v>
-      </c>
-      <c r="L91" s="19" t="s">
+      <c r="K91" s="15">
+        <v>0</v>
+      </c>
+      <c r="L91" s="14" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:13">
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:13">
       <c r="B93" s="1" t="s">
@@ -5791,28 +5770,28 @@
       <c r="C93" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="7">
         <v>0.1</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="7">
         <v>235</v>
       </c>
-      <c r="F93" s="8" t="s">
+      <c r="F93" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="G93" s="8">
+      <c r="G93" s="7">
         <v>650</v>
       </c>
-      <c r="H93" s="8">
+      <c r="H93" s="7">
         <v>325</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="J93" s="8">
+      <c r="J93" s="7">
         <v>11001</v>
       </c>
-      <c r="K93" s="8">
+      <c r="K93" s="7">
         <v>0</v>
       </c>
       <c r="L93" t="s">
@@ -5826,26 +5805,26 @@
       <c r="C94" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="7">
         <v>0.1</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F94" s="8" t="s">
+      <c r="F94" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="G94" s="8">
+      <c r="G94" s="7">
         <v>680</v>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="7">
         <v>340</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8">
+      <c r="J94" s="7"/>
+      <c r="K94" s="7">
         <v>0</v>
       </c>
       <c r="L94" t="s">
@@ -5859,28 +5838,28 @@
       <c r="C95" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="7">
         <v>0.1</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="E95" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="F95" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="G95" s="8">
+      <c r="G95" s="7">
         <v>600</v>
       </c>
-      <c r="H95" s="8">
+      <c r="H95" s="7">
         <v>300</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="K95" s="8">
-        <v>0</v>
-      </c>
-      <c r="L95" s="8" t="s">
+      <c r="K95" s="7">
+        <v>0</v>
+      </c>
+      <c r="L95" s="7" t="s">
         <v>420</v>
       </c>
     </row>
@@ -5891,31 +5870,31 @@
       <c r="C96" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="8">
         <v>0.1</v>
       </c>
-      <c r="E96" s="9" t="s">
+      <c r="E96" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="F96" s="9" t="s">
+      <c r="F96" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96" s="8">
         <v>480</v>
       </c>
-      <c r="H96" s="9">
+      <c r="H96" s="8">
         <v>240</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="J96" s="9">
+      <c r="J96" s="8">
         <v>11002</v>
       </c>
-      <c r="K96" s="9">
-        <v>0</v>
-      </c>
-      <c r="L96" s="10" t="s">
+      <c r="K96" s="8">
+        <v>0</v>
+      </c>
+      <c r="L96" s="9" t="s">
         <v>425</v>
       </c>
     </row>
@@ -5926,26 +5905,26 @@
       <c r="C97" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="7">
         <v>0.1</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="E97" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="F97" s="8" t="s">
+      <c r="F97" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="G97" s="8">
+      <c r="G97" s="7">
         <v>460</v>
       </c>
-      <c r="H97" s="8">
+      <c r="H97" s="7">
         <v>230</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8">
+      <c r="J97" s="7"/>
+      <c r="K97" s="7">
         <v>0</v>
       </c>
       <c r="L97" t="s">
@@ -5959,25 +5938,25 @@
       <c r="C98" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="7">
         <v>0.1</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="F98" s="8" t="s">
+      <c r="F98" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="G98" s="8">
+      <c r="G98" s="7">
         <v>320</v>
       </c>
-      <c r="H98" s="8">
+      <c r="H98" s="7">
         <v>160</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="K98" s="8">
+      <c r="K98" s="7">
         <v>0</v>
       </c>
       <c r="L98" t="s">
@@ -5991,31 +5970,31 @@
       <c r="C99" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="8">
         <v>0.1</v>
       </c>
-      <c r="E99" s="9" t="s">
+      <c r="E99" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="F99" s="9" t="s">
+      <c r="F99" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="G99" s="9">
+      <c r="G99" s="8">
         <v>380</v>
       </c>
-      <c r="H99" s="9">
+      <c r="H99" s="8">
         <v>190</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="J99" s="17">
+      <c r="J99" s="16">
         <v>11003</v>
       </c>
-      <c r="K99" s="9">
-        <v>0</v>
-      </c>
-      <c r="L99" s="10" t="s">
+      <c r="K99" s="8">
+        <v>0</v>
+      </c>
+      <c r="L99" s="9" t="s">
         <v>440</v>
       </c>
     </row>
@@ -6026,29 +6005,29 @@
       <c r="C100" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="7">
         <v>0.1</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="F100" s="8" t="s">
+      <c r="F100" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="G100" s="8">
+      <c r="G100" s="7">
         <v>600</v>
       </c>
-      <c r="H100" s="8">
+      <c r="H100" s="7">
         <v>300</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8">
-        <v>0</v>
-      </c>
-      <c r="L100" s="8" t="s">
+      <c r="J100" s="7"/>
+      <c r="K100" s="7">
+        <v>0</v>
+      </c>
+      <c r="L100" s="7" t="s">
         <v>445</v>
       </c>
     </row>
@@ -6059,25 +6038,25 @@
       <c r="C101" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="7">
         <v>0.1</v>
       </c>
-      <c r="E101" s="8" t="s">
+      <c r="E101" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="F101" s="8" t="s">
+      <c r="F101" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="G101" s="8">
+      <c r="G101" s="7">
         <v>280</v>
       </c>
-      <c r="H101" s="8">
+      <c r="H101" s="7">
         <v>140</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="K101" s="8">
+      <c r="K101" s="7">
         <v>0</v>
       </c>
       <c r="L101" t="s">
@@ -6091,28 +6070,28 @@
       <c r="C102" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <v>0.1</v>
       </c>
-      <c r="E102" s="9" t="s">
+      <c r="E102" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="F102" s="9" t="s">
+      <c r="F102" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="8">
         <v>300</v>
       </c>
-      <c r="H102" s="9">
+      <c r="H102" s="8">
         <v>150</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="K102" s="9">
-        <v>0</v>
-      </c>
-      <c r="L102" s="10" t="s">
+      <c r="K102" s="8">
+        <v>0</v>
+      </c>
+      <c r="L102" s="9" t="s">
         <v>455</v>
       </c>
     </row>
@@ -6123,28 +6102,28 @@
       <c r="C103" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="7">
         <v>0.1</v>
       </c>
-      <c r="E103" s="8" t="s">
+      <c r="E103" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="F103" s="8" t="s">
+      <c r="F103" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G103" s="8">
+      <c r="G103" s="7">
         <v>400</v>
       </c>
-      <c r="H103" s="8">
+      <c r="H103" s="7">
         <v>200</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="J103" s="17">
+      <c r="J103" s="16">
         <v>11004</v>
       </c>
-      <c r="K103" s="8">
+      <c r="K103" s="7">
         <v>0</v>
       </c>
       <c r="L103" t="s">
@@ -6158,32 +6137,32 @@
       <c r="C104" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="8">
         <v>0.1</v>
       </c>
-      <c r="E104" s="9" t="s">
+      <c r="E104" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="F104" s="9" t="s">
+      <c r="F104" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="8">
         <v>460</v>
       </c>
-      <c r="H104" s="9">
+      <c r="H104" s="8">
         <v>230</v>
       </c>
       <c r="I104" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="J104" s="9"/>
-      <c r="K104" s="9">
-        <v>0</v>
-      </c>
-      <c r="L104" s="10" t="s">
+      <c r="J104" s="8"/>
+      <c r="K104" s="8">
+        <v>0</v>
+      </c>
+      <c r="L104" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="M104" s="10"/>
+      <c r="M104" s="9"/>
     </row>
     <row r="105" spans="2:13">
       <c r="B105" s="1" t="s">
@@ -6192,28 +6171,28 @@
       <c r="C105" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="7">
         <v>0.1</v>
       </c>
-      <c r="E105" s="8" t="s">
+      <c r="E105" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="F105" s="8" t="s">
+      <c r="F105" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="G105" s="8">
+      <c r="G105" s="7">
         <v>340</v>
       </c>
-      <c r="H105" s="8">
+      <c r="H105" s="7">
         <v>170</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="J105" s="8">
+      <c r="J105" s="7">
         <v>10602</v>
       </c>
-      <c r="K105" s="8">
+      <c r="K105" s="7">
         <v>0</v>
       </c>
       <c r="L105" t="s">
@@ -6227,25 +6206,25 @@
       <c r="C106" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="7">
         <v>0.1</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F106" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="G106" s="8">
+      <c r="G106" s="7">
         <v>280</v>
       </c>
-      <c r="H106" s="8">
+      <c r="H106" s="7">
         <v>140</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="K106" s="8">
+      <c r="K106" s="7">
         <v>0</v>
       </c>
       <c r="L106" t="s">
@@ -6259,25 +6238,25 @@
       <c r="C107" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="7">
         <v>0.1</v>
       </c>
       <c r="E107" t="s">
         <v>477</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F107" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="G107" s="8">
+      <c r="G107" s="7">
         <v>600</v>
       </c>
-      <c r="H107" s="8">
+      <c r="H107" s="7">
         <v>300</v>
       </c>
-      <c r="I107" s="8" t="s">
+      <c r="I107" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="K107" s="8">
+      <c r="K107" s="7">
         <v>0</v>
       </c>
       <c r="L107" t="s">
@@ -6291,31 +6270,31 @@
       <c r="C108" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="7">
         <v>0.1</v>
       </c>
       <c r="E108" t="s">
         <v>482</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="F108" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="G108" s="8">
+      <c r="G108" s="7">
         <v>280</v>
       </c>
-      <c r="H108" s="8">
+      <c r="H108" s="7">
         <v>140</v>
       </c>
-      <c r="I108" s="8">
+      <c r="I108" s="7">
         <v>40016</v>
       </c>
-      <c r="J108" s="17">
+      <c r="J108" s="16">
         <v>10101</v>
       </c>
-      <c r="K108" s="8">
-        <v>0</v>
-      </c>
-      <c r="L108" s="8" t="s">
+      <c r="K108" s="7">
+        <v>0</v>
+      </c>
+      <c r="L108" s="7" t="s">
         <v>484</v>
       </c>
     </row>
@@ -6326,25 +6305,25 @@
       <c r="C109" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="7">
         <v>0.1</v>
       </c>
       <c r="E109" t="s">
         <v>486</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="G109" s="8">
+      <c r="G109" s="7">
         <v>300</v>
       </c>
-      <c r="H109" s="8">
+      <c r="H109" s="7">
         <v>150</v>
       </c>
-      <c r="I109" s="8">
+      <c r="I109" s="7">
         <v>40017</v>
       </c>
-      <c r="K109" s="8">
+      <c r="K109" s="7">
         <v>0</v>
       </c>
       <c r="L109" t="s">
@@ -6358,28 +6337,28 @@
       <c r="C110" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="7">
         <v>0.1</v>
       </c>
       <c r="E110" t="s">
         <v>490</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="G110" s="8">
+      <c r="G110" s="7">
         <v>520</v>
       </c>
-      <c r="H110" s="8">
+      <c r="H110" s="7">
         <v>260</v>
       </c>
-      <c r="I110" s="8">
+      <c r="I110" s="7">
         <v>40018</v>
       </c>
-      <c r="J110" s="17">
+      <c r="J110" s="16">
         <v>11101</v>
       </c>
-      <c r="K110" s="8">
+      <c r="K110" s="7">
         <v>0</v>
       </c>
       <c r="L110" t="s">
@@ -6393,25 +6372,25 @@
       <c r="C111" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="7">
         <v>0.1</v>
       </c>
       <c r="E111" t="s">
         <v>494</v>
       </c>
-      <c r="F111" s="8" t="s">
+      <c r="F111" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="G111" s="8">
+      <c r="G111" s="7">
         <v>300</v>
       </c>
-      <c r="H111" s="8">
+      <c r="H111" s="7">
         <v>150</v>
       </c>
-      <c r="I111" s="8">
+      <c r="I111" s="7">
         <v>40019</v>
       </c>
-      <c r="K111" s="8">
+      <c r="K111" s="7">
         <v>0</v>
       </c>
       <c r="L111" t="s">
@@ -6425,25 +6404,25 @@
       <c r="C112" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="7">
         <v>0.1</v>
       </c>
       <c r="E112" t="s">
         <v>498</v>
       </c>
-      <c r="F112" s="8" t="s">
+      <c r="F112" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="G112" s="8">
+      <c r="G112" s="7">
         <v>620</v>
       </c>
-      <c r="H112" s="8">
+      <c r="H112" s="7">
         <v>310</v>
       </c>
-      <c r="I112" s="8">
+      <c r="I112" s="7">
         <v>40021</v>
       </c>
-      <c r="K112" s="8">
+      <c r="K112" s="7">
         <v>0</v>
       </c>
       <c r="L112" t="s">
@@ -6457,28 +6436,28 @@
       <c r="C113" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="7">
         <v>0.1</v>
       </c>
       <c r="E113" t="s">
         <v>502</v>
       </c>
-      <c r="F113" s="8" t="s">
+      <c r="F113" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="G113" s="8">
+      <c r="G113" s="7">
         <v>320</v>
       </c>
-      <c r="H113" s="8">
+      <c r="H113" s="7">
         <v>160</v>
       </c>
-      <c r="I113" s="8" t="s">
+      <c r="I113" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="J113" s="17">
+      <c r="J113" s="16">
         <v>11201</v>
       </c>
-      <c r="K113" s="8">
+      <c r="K113" s="7">
         <v>0</v>
       </c>
       <c r="L113" t="s">
@@ -6486,40 +6465,40 @@
       </c>
     </row>
     <row r="114" s="2" customFormat="1" spans="1:13">
-      <c r="B114" s="22" t="s">
+      <c r="B114" s="2" t="s">
         <v>506</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="8">
         <v>0.1</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="E114" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="F114" s="9" t="s">
+      <c r="F114" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="G114" s="9">
+      <c r="G114" s="8">
         <v>320</v>
       </c>
-      <c r="H114" s="9">
+      <c r="H114" s="8">
         <v>160</v>
       </c>
-      <c r="I114" s="9">
+      <c r="I114" s="8">
         <v>40023</v>
       </c>
-      <c r="J114" s="9">
+      <c r="J114" s="8">
         <v>11301</v>
       </c>
-      <c r="K114" s="9">
-        <v>0</v>
-      </c>
-      <c r="L114" s="10" t="s">
+      <c r="K114" s="8">
+        <v>0</v>
+      </c>
+      <c r="L114" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="M114" s="10"/>
+      <c r="M114" s="9"/>
     </row>
     <row r="115" spans="1:13">
       <c r="B115" s="1" t="s">
@@ -6528,31 +6507,31 @@
       <c r="C115" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="7">
         <v>0.1</v>
       </c>
       <c r="E115" t="s">
         <v>511</v>
       </c>
-      <c r="F115" s="8" t="s">
+      <c r="F115" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="G115" s="8">
+      <c r="G115" s="7">
         <v>550</v>
       </c>
-      <c r="H115" s="8">
+      <c r="H115" s="7">
         <v>275</v>
       </c>
-      <c r="I115" s="8">
+      <c r="I115" s="7">
         <v>40024</v>
       </c>
-      <c r="J115" s="17">
+      <c r="J115" s="16">
         <v>11401</v>
       </c>
-      <c r="K115" s="8">
-        <v>0</v>
-      </c>
-      <c r="L115" s="8" t="s">
+      <c r="K115" s="7">
+        <v>0</v>
+      </c>
+      <c r="L115" s="7" t="s">
         <v>513</v>
       </c>
     </row>
@@ -6563,66 +6542,66 @@
       <c r="C116" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D116" s="7">
         <v>0.1</v>
       </c>
       <c r="E116" t="s">
         <v>515</v>
       </c>
-      <c r="F116" s="8" t="s">
+      <c r="F116" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="G116" s="8">
+      <c r="G116" s="7">
         <v>300</v>
       </c>
-      <c r="H116" s="8">
+      <c r="H116" s="7">
         <v>150</v>
       </c>
-      <c r="I116" s="8">
+      <c r="I116" s="7">
         <v>40025</v>
       </c>
-      <c r="K116" s="8">
-        <v>0</v>
-      </c>
-      <c r="L116" s="8" t="s">
+      <c r="K116" s="7">
+        <v>0</v>
+      </c>
+      <c r="L116" s="7" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="117" s="2" customFormat="1" spans="1:13">
-      <c r="B117" s="22" t="s">
+      <c r="B117" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C117" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="D117" s="9">
+      <c r="D117" s="8">
         <v>0.1</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="E117" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="F117" s="10" t="s">
+      <c r="F117" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="G117" s="9">
+      <c r="G117" s="8">
         <v>400</v>
       </c>
-      <c r="H117" s="9">
+      <c r="H117" s="8">
         <v>200</v>
       </c>
-      <c r="I117" s="9">
+      <c r="I117" s="8">
         <v>40026</v>
       </c>
-      <c r="J117" s="9">
+      <c r="J117" s="8">
         <v>11501</v>
       </c>
-      <c r="K117" s="9">
+      <c r="K117" s="8">
         <v>1</v>
       </c>
-      <c r="L117" s="10" t="s">
+      <c r="L117" s="9" t="s">
         <v>521</v>
       </c>
-      <c r="M117" s="10"/>
+      <c r="M117" s="9"/>
     </row>
     <row r="118" spans="1:13">
       <c r="B118" s="1" t="s">
@@ -6631,7 +6610,7 @@
       <c r="C118" t="s">
         <v>407</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D118" s="7">
         <v>0.1</v>
       </c>
       <c r="E118" t="s">
@@ -6640,16 +6619,16 @@
       <c r="F118" t="s">
         <v>524</v>
       </c>
-      <c r="G118" s="8">
+      <c r="G118" s="7">
         <v>330</v>
       </c>
-      <c r="H118" s="8">
+      <c r="H118" s="7">
         <v>165</v>
       </c>
-      <c r="I118" s="8">
+      <c r="I118" s="7">
         <v>40027</v>
       </c>
-      <c r="K118" s="8">
+      <c r="K118" s="7">
         <v>1</v>
       </c>
       <c r="L118" t="s">
@@ -6657,124 +6636,124 @@
       </c>
     </row>
     <row r="119" s="2" customFormat="1" spans="1:13">
-      <c r="B119" s="22" t="s">
+      <c r="B119" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C119" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="D119" s="9">
+      <c r="D119" s="8">
         <v>0.1</v>
       </c>
-      <c r="E119" s="10" t="s">
+      <c r="E119" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="F119" s="10" t="s">
+      <c r="F119" s="9" t="s">
         <v>528</v>
       </c>
-      <c r="G119" s="9">
+      <c r="G119" s="8">
         <v>260</v>
       </c>
-      <c r="H119" s="9">
+      <c r="H119" s="8">
         <v>130</v>
       </c>
-      <c r="I119" s="9">
+      <c r="I119" s="8">
         <v>40028</v>
       </c>
-      <c r="J119" s="9"/>
-      <c r="K119" s="9">
+      <c r="J119" s="8"/>
+      <c r="K119" s="8">
         <v>2</v>
       </c>
-      <c r="L119" s="10" t="s">
+      <c r="L119" s="9" t="s">
         <v>529</v>
       </c>
-      <c r="M119" s="10"/>
+      <c r="M119" s="9"/>
     </row>
     <row r="120" s="2" customFormat="1" spans="1:13">
-      <c r="B120" s="22" t="s">
+      <c r="B120" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C120" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="8">
         <v>0.1</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="E120" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="F120" s="10" t="s">
+      <c r="F120" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="G120" s="9">
+      <c r="G120" s="8">
         <v>270</v>
       </c>
-      <c r="H120" s="9">
+      <c r="H120" s="8">
         <v>135</v>
       </c>
-      <c r="I120" s="9">
+      <c r="I120" s="8">
         <v>40029</v>
       </c>
-      <c r="J120" s="9"/>
-      <c r="K120" s="9">
+      <c r="J120" s="8"/>
+      <c r="K120" s="8">
         <v>2</v>
       </c>
-      <c r="L120" s="10" t="s">
+      <c r="L120" s="9" t="s">
         <v>533</v>
       </c>
-      <c r="M120" s="10"/>
+      <c r="M120" s="9"/>
     </row>
     <row r="121" s="2" customFormat="1" spans="1:13">
-      <c r="B121" s="22" t="s">
+      <c r="B121" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C121" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="D121" s="9">
+      <c r="D121" s="8">
         <v>0.1</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="E121" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="F121" s="10" t="s">
+      <c r="F121" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="G121" s="9">
+      <c r="G121" s="8">
         <v>280</v>
       </c>
-      <c r="H121" s="9">
+      <c r="H121" s="8">
         <v>140</v>
       </c>
-      <c r="I121" s="9">
+      <c r="I121" s="8">
         <v>40030</v>
       </c>
-      <c r="J121" s="9">
+      <c r="J121" s="8">
         <v>11601</v>
       </c>
-      <c r="K121" s="9">
-        <v>0</v>
-      </c>
-      <c r="L121" s="10" t="s">
+      <c r="K121" s="8">
+        <v>0</v>
+      </c>
+      <c r="L121" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="M121" s="10"/>
+      <c r="M121" s="9"/>
     </row>
     <row r="122" s="2" customFormat="1" spans="1:13">
-      <c r="A122" s="10"/>
-      <c r="B122" s="22" t="s">
+      <c r="A122" s="9"/>
+      <c r="B122" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C122" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="8">
         <v>0.1</v>
       </c>
-      <c r="E122" s="9" t="s">
+      <c r="E122" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="F122" s="9" t="s">
+      <c r="F122" s="8" t="s">
         <v>540</v>
       </c>
       <c r="G122" s="2">
@@ -6783,17 +6762,17 @@
       <c r="H122" s="2">
         <v>130</v>
       </c>
-      <c r="I122" s="9">
+      <c r="I122" s="8">
         <v>40031</v>
       </c>
-      <c r="J122" s="9"/>
-      <c r="K122" s="9">
-        <v>0</v>
-      </c>
-      <c r="L122" s="10" t="s">
+      <c r="J122" s="8"/>
+      <c r="K122" s="8">
+        <v>0</v>
+      </c>
+      <c r="L122" s="9" t="s">
         <v>541</v>
       </c>
-      <c r="M122" s="10"/>
+      <c r="M122" s="9"/>
     </row>
     <row r="123" s="1" customFormat="1" spans="1:13">
       <c r="B123" s="1" t="s">
@@ -6802,7 +6781,7 @@
       <c r="C123" t="s">
         <v>407</v>
       </c>
-      <c r="D123" s="8">
+      <c r="D123" s="7">
         <v>0.1</v>
       </c>
       <c r="E123" t="s">
@@ -6811,10 +6790,10 @@
       <c r="F123" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G123" s="8">
+      <c r="G123" s="7">
         <v>500</v>
       </c>
-      <c r="H123" s="8">
+      <c r="H123" s="7">
         <v>250</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -6834,7 +6813,7 @@
       <c r="C124" t="s">
         <v>407</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D124" s="7">
         <v>0.1</v>
       </c>
       <c r="E124" t="s">
@@ -6843,10 +6822,10 @@
       <c r="F124" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="G124" s="8">
+      <c r="G124" s="7">
         <v>500</v>
       </c>
-      <c r="H124" s="8">
+      <c r="H124" s="7">
         <v>250</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -6866,26 +6845,26 @@
       <c r="C125" t="s">
         <v>407</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="7">
         <v>0.1</v>
       </c>
-      <c r="E125" s="8" t="s">
+      <c r="E125" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="F125" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="G125" s="8">
+      <c r="G125" s="7">
         <v>500</v>
       </c>
-      <c r="H125" s="8">
+      <c r="H125" s="7">
         <v>250</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="J125" s="8"/>
-      <c r="K125" s="8">
+      <c r="J125" s="7"/>
+      <c r="K125" s="7">
         <v>0</v>
       </c>
       <c r="L125" t="s">

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="17355" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="557">
   <si>
     <t>##var</t>
   </si>
@@ -1252,6 +1252,15 @@
     <t>亮出的每张牌都提供其点数对应的攻击力加成</t>
   </si>
   <si>
+    <t>差距胶囊</t>
+  </si>
+  <si>
+    <t>GapCapsule</t>
+  </si>
+  <si>
+    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
+  </si>
+  <si>
     <t>401</t>
   </si>
   <si>
@@ -1339,7 +1348,7 @@
     <t>40006</t>
   </si>
   <si>
-    <t>每拥有1个圣物,结算时提供+0.5倍率</t>
+    <t>每拥有1个圣物,结算时提供+3倍率</t>
   </si>
   <si>
     <t>407</t>
@@ -1579,121 +1588,109 @@
     <t>424</t>
   </si>
   <si>
-    <t>差距胶囊</t>
-  </si>
-  <si>
-    <t>GapCapsule</t>
-  </si>
-  <si>
-    <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
+    <t>神之左手</t>
+  </si>
+  <si>
+    <t>GodsLeftHand</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你造成的伤害提高200%</t>
   </si>
   <si>
     <t>425</t>
   </si>
   <si>
-    <t>神之左手</t>
-  </si>
-  <si>
-    <t>GodLeftHand</t>
-  </si>
-  <si>
-    <t>使用后,本次比牌你造成的伤害提高200%</t>
+    <t>凤凰羽毛</t>
+  </si>
+  <si>
+    <t>PhoenixFeather</t>
+  </si>
+  <si>
+    <t>使用后,本次比牌你受到的所有伤害变为0,并恢复30%血量</t>
   </si>
   <si>
     <t>426</t>
   </si>
   <si>
-    <t>凤凰羽毛</t>
-  </si>
-  <si>
-    <t>PhoenixFeather</t>
-  </si>
-  <si>
-    <t>使用后,本次比牌你受到的所有伤害变为0,并恢复30%血量</t>
+    <t>时光宝盒</t>
+  </si>
+  <si>
+    <t>TimeTreasureBox</t>
+  </si>
+  <si>
+    <t>使用后,随机3种牌型的提供的倍率永久+5</t>
   </si>
   <si>
     <t>427</t>
   </si>
   <si>
-    <t>时光宝盒</t>
-  </si>
-  <si>
-    <t>TimeTreasureBox</t>
-  </si>
-  <si>
-    <t>使用后,随机3种牌型的提供的倍率永久+5</t>
+    <t>龙心</t>
+  </si>
+  <si>
+    <t>DragonHeart</t>
+  </si>
+  <si>
+    <t>使用后,获得120点生命上限,并立即恢复120点血量</t>
   </si>
   <si>
     <t>428</t>
   </si>
   <si>
-    <t>龙心</t>
-  </si>
-  <si>
-    <t>DragonHeart</t>
-  </si>
-  <si>
-    <t>使用后,获得120点生命上限,并立即恢复120点血量</t>
+    <t>贪欲之冠</t>
+  </si>
+  <si>
+    <t>GreedCrown</t>
+  </si>
+  <si>
+    <t>每拥有40金币,你造成的伤害+10%,至多叠加20层</t>
   </si>
   <si>
     <t>429</t>
   </si>
   <si>
-    <t>贪欲之冠</t>
-  </si>
-  <si>
-    <t>GreedCrown</t>
-  </si>
-  <si>
-    <t>每拥有40金币,你造成的伤害+10%,至多叠加20层</t>
+    <t>旗帜</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
   </si>
   <si>
     <t>430</t>
   </si>
   <si>
-    <t>旗帜</t>
-  </si>
-  <si>
-    <t>Flag</t>
-  </si>
-  <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
+    <t>降低</t>
+  </si>
+  <si>
+    <t>LowerStatus</t>
+  </si>
+  <si>
+    <t>30029</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>比牌时,对方的牌型顺位降低1级</t>
   </si>
   <si>
     <t>431</t>
   </si>
   <si>
-    <t>降低</t>
-  </si>
-  <si>
-    <t>LowerStatus</t>
-  </si>
-  <si>
-    <t>30029</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>比牌时,对方的牌型顺位降低1级</t>
+    <t>升职</t>
+  </si>
+  <si>
+    <t>Promote</t>
+  </si>
+  <si>
+    <t>30030</t>
+  </si>
+  <si>
+    <t>比牌时,自己的牌型顺位提高1级</t>
   </si>
   <si>
     <t>432</t>
-  </si>
-  <si>
-    <t>升职</t>
-  </si>
-  <si>
-    <t>Promote</t>
-  </si>
-  <si>
-    <t>30030</t>
-  </si>
-  <si>
-    <t>比牌时,自己的牌型顺位提高1级</t>
-  </si>
-  <si>
-    <t>433</t>
   </si>
   <si>
     <t>错峰出行</t>
@@ -5753,835 +5750,835 @@
         <v>405</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" spans="2:13">
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7"/>
+    <row r="92" spans="2:13">
+      <c r="B92" s="7">
+        <v>330</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="D92" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="E92" t="s">
+        <v>406</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="G92" s="7">
+        <v>300</v>
+      </c>
+      <c r="H92" s="7">
+        <v>150</v>
+      </c>
+      <c r="I92" s="7">
+        <v>40025</v>
+      </c>
+      <c r="K92" s="7">
+        <v>0</v>
+      </c>
+      <c r="L92" s="7" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:13">
-      <c r="B93" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D93" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E93" s="7">
-        <v>235</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="G93" s="7">
-        <v>650</v>
-      </c>
-      <c r="H93" s="7">
-        <v>325</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="J93" s="7">
-        <v>11001</v>
-      </c>
-      <c r="K93" s="7">
-        <v>0</v>
-      </c>
-      <c r="L93" t="s">
-        <v>410</v>
-      </c>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="J93" s="7"/>
+      <c r="K93" s="7"/>
+      <c r="L93" s="7"/>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:13">
       <c r="B94" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D94" s="7">
         <v>0.1</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="7">
+        <v>235</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G94" s="7">
+        <v>650</v>
+      </c>
+      <c r="H94" s="7">
+        <v>325</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="J94" s="7">
+        <v>11001</v>
+      </c>
+      <c r="K94" s="7">
+        <v>0</v>
+      </c>
+      <c r="L94" t="s">
         <v>413</v>
-      </c>
-      <c r="G94" s="7">
-        <v>680</v>
-      </c>
-      <c r="H94" s="7">
-        <v>340</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="J94" s="7"/>
-      <c r="K94" s="7">
-        <v>0</v>
-      </c>
-      <c r="L94" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="2:13">
       <c r="B95" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D95" s="7">
         <v>0.1</v>
       </c>
       <c r="E95" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="G95" s="7">
+        <v>680</v>
+      </c>
+      <c r="H95" s="7">
+        <v>340</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="J95" s="7"/>
+      <c r="K95" s="7">
+        <v>0</v>
+      </c>
+      <c r="L95" t="s">
         <v>418</v>
       </c>
-      <c r="G95" s="7">
+    </row>
+    <row r="96" s="1" customFormat="1" spans="2:13">
+      <c r="B96" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D96" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="G96" s="7">
         <v>600</v>
       </c>
-      <c r="H95" s="7">
+      <c r="H96" s="7">
         <v>300</v>
       </c>
-      <c r="I95" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="K95" s="7">
-        <v>0</v>
-      </c>
-      <c r="L95" s="7" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="96" s="2" customFormat="1" spans="2:13">
-      <c r="B96" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D96" s="8">
+      <c r="I96" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="K96" s="7">
+        <v>0</v>
+      </c>
+      <c r="L96" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="97" s="2" customFormat="1" spans="2:13">
+      <c r="B97" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D97" s="8">
         <v>0.1</v>
       </c>
-      <c r="E96" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="G96" s="8">
+      <c r="E97" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="G97" s="8">
         <v>480</v>
       </c>
-      <c r="H96" s="8">
+      <c r="H97" s="8">
         <v>240</v>
       </c>
-      <c r="I96" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="J96" s="8">
+      <c r="I97" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="J97" s="8">
         <v>11002</v>
       </c>
-      <c r="K96" s="8">
-        <v>0</v>
-      </c>
-      <c r="L96" s="9" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="2:13">
-      <c r="B97" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D97" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="F97" s="7" t="s">
+      <c r="K97" s="8">
+        <v>0</v>
+      </c>
+      <c r="L97" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="G97" s="7">
-        <v>460</v>
-      </c>
-      <c r="H97" s="7">
-        <v>230</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="J97" s="7"/>
-      <c r="K97" s="7">
-        <v>0</v>
-      </c>
-      <c r="L97" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="2:13">
       <c r="B98" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D98" s="7">
         <v>0.1</v>
       </c>
       <c r="E98" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="G98" s="7">
+        <v>460</v>
+      </c>
+      <c r="H98" s="7">
+        <v>230</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="J98" s="7"/>
+      <c r="K98" s="7">
+        <v>0</v>
+      </c>
+      <c r="L98" t="s">
         <v>433</v>
       </c>
-      <c r="G98" s="7">
+    </row>
+    <row r="99" s="1" customFormat="1" spans="2:13">
+      <c r="B99" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D99" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="G99" s="7">
         <v>320</v>
       </c>
-      <c r="H98" s="7">
+      <c r="H99" s="7">
         <v>160</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="K98" s="7">
-        <v>0</v>
-      </c>
-      <c r="L98" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="99" s="2" customFormat="1" spans="2:13">
-      <c r="B99" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D99" s="8">
+      <c r="I99" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K99" s="7">
+        <v>0</v>
+      </c>
+      <c r="L99" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="100" s="2" customFormat="1" spans="2:13">
+      <c r="B100" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D100" s="8">
         <v>0.1</v>
       </c>
-      <c r="E99" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="G99" s="8">
+      <c r="E100" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="G100" s="8">
         <v>380</v>
       </c>
-      <c r="H99" s="8">
+      <c r="H100" s="8">
         <v>190</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="J99" s="16">
+      <c r="I100" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="J100" s="16">
         <v>11003</v>
       </c>
-      <c r="K99" s="8">
-        <v>0</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" spans="2:13">
-      <c r="B100" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D100" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="F100" s="7" t="s">
+      <c r="K100" s="8">
+        <v>0</v>
+      </c>
+      <c r="L100" s="9" t="s">
         <v>443</v>
-      </c>
-      <c r="G100" s="7">
-        <v>600</v>
-      </c>
-      <c r="H100" s="7">
-        <v>300</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="J100" s="7"/>
-      <c r="K100" s="7">
-        <v>0</v>
-      </c>
-      <c r="L100" s="7" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="2:13">
       <c r="B101" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D101" s="7">
         <v>0.1</v>
       </c>
       <c r="E101" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="G101" s="7">
+        <v>600</v>
+      </c>
+      <c r="H101" s="7">
+        <v>300</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F101" s="7" t="s">
+      <c r="J101" s="7"/>
+      <c r="K101" s="7">
+        <v>0</v>
+      </c>
+      <c r="L101" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="G101" s="7">
+    </row>
+    <row r="102" s="1" customFormat="1" spans="2:13">
+      <c r="B102" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D102" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="G102" s="7">
         <v>280</v>
       </c>
-      <c r="H101" s="7">
+      <c r="H102" s="7">
         <v>140</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="K101" s="7">
-        <v>0</v>
-      </c>
-      <c r="L101" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="102" s="2" customFormat="1" spans="2:13">
-      <c r="B102" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D102" s="8">
+      <c r="I102" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="K102" s="7">
+        <v>0</v>
+      </c>
+      <c r="L102" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="103" s="2" customFormat="1" spans="2:13">
+      <c r="B103" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D103" s="8">
         <v>0.1</v>
       </c>
-      <c r="E102" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="F102" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="G102" s="8">
+      <c r="E103" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="G103" s="8">
         <v>300</v>
       </c>
-      <c r="H102" s="8">
+      <c r="H103" s="8">
         <v>150</v>
       </c>
-      <c r="I102" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="K102" s="8">
-        <v>0</v>
-      </c>
-      <c r="L102" s="9" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="103" spans="2:13">
-      <c r="B103" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D103" s="7">
+      <c r="I103" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K103" s="8">
+        <v>0</v>
+      </c>
+      <c r="L103" s="9" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="104" spans="2:13">
+      <c r="B104" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D104" s="7">
         <v>0.1</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="G103" s="7">
+      <c r="E104" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="G104" s="7">
         <v>400</v>
       </c>
-      <c r="H103" s="7">
+      <c r="H104" s="7">
         <v>200</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="J103" s="16">
+      <c r="I104" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J104" s="16">
         <v>11004</v>
       </c>
-      <c r="K103" s="7">
-        <v>0</v>
-      </c>
-      <c r="L103" t="s">
+      <c r="K104" s="7">
+        <v>0</v>
+      </c>
+      <c r="L104" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="105" s="2" customFormat="1" spans="2:13">
+      <c r="B105" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D105" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="G105" s="8">
         <v>460</v>
       </c>
-    </row>
-    <row r="104" s="2" customFormat="1" spans="2:13">
-      <c r="B104" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D104" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="F104" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="G104" s="8">
-        <v>460</v>
-      </c>
-      <c r="H104" s="8">
+      <c r="H105" s="8">
         <v>230</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8">
-        <v>0</v>
-      </c>
-      <c r="L104" s="9" t="s">
-        <v>465</v>
-      </c>
-      <c r="M104" s="9"/>
-    </row>
-    <row r="105" spans="2:13">
-      <c r="B105" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D105" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E105" s="7" t="s">
+      <c r="I105" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="J105" s="8"/>
+      <c r="K105" s="8">
+        <v>0</v>
+      </c>
+      <c r="L105" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="G105" s="7">
-        <v>340</v>
-      </c>
-      <c r="H105" s="7">
-        <v>170</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="J105" s="7">
-        <v>10602</v>
-      </c>
-      <c r="K105" s="7">
-        <v>0</v>
-      </c>
-      <c r="L105" t="s">
-        <v>470</v>
-      </c>
+      <c r="M105" s="9"/>
     </row>
     <row r="106" spans="2:13">
       <c r="B106" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D106" s="7">
         <v>0.1</v>
       </c>
       <c r="E106" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="G106" s="7">
+        <v>340</v>
+      </c>
+      <c r="H106" s="7">
+        <v>170</v>
+      </c>
+      <c r="I106" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="J106" s="7">
+        <v>10602</v>
+      </c>
+      <c r="K106" s="7">
+        <v>0</v>
+      </c>
+      <c r="L106" t="s">
         <v>473</v>
-      </c>
-      <c r="G106" s="7">
-        <v>280</v>
-      </c>
-      <c r="H106" s="7">
-        <v>140</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="K106" s="7">
-        <v>0</v>
-      </c>
-      <c r="L106" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="107" spans="2:13">
       <c r="B107" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D107" s="7">
         <v>0.1</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="G107" s="7">
+        <v>280</v>
+      </c>
+      <c r="H107" s="7">
+        <v>140</v>
+      </c>
+      <c r="I107" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F107" s="7" t="s">
+      <c r="K107" s="7">
+        <v>0</v>
+      </c>
+      <c r="L107" t="s">
         <v>478</v>
-      </c>
-      <c r="G107" s="7">
-        <v>600</v>
-      </c>
-      <c r="H107" s="7">
-        <v>300</v>
-      </c>
-      <c r="I107" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="K107" s="7">
-        <v>0</v>
-      </c>
-      <c r="L107" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="108" spans="2:13">
       <c r="B108" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D108" s="7">
         <v>0.1</v>
       </c>
       <c r="E108" t="s">
+        <v>480</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="G108" s="7">
+        <v>600</v>
+      </c>
+      <c r="H108" s="7">
+        <v>300</v>
+      </c>
+      <c r="I108" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="F108" s="7" t="s">
+      <c r="K108" s="7">
+        <v>0</v>
+      </c>
+      <c r="L108" t="s">
         <v>483</v>
-      </c>
-      <c r="G108" s="7">
-        <v>280</v>
-      </c>
-      <c r="H108" s="7">
-        <v>140</v>
-      </c>
-      <c r="I108" s="7">
-        <v>40016</v>
-      </c>
-      <c r="J108" s="16">
-        <v>10101</v>
-      </c>
-      <c r="K108" s="7">
-        <v>0</v>
-      </c>
-      <c r="L108" s="7" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="109" spans="2:13">
       <c r="B109" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D109" s="7">
         <v>0.1</v>
       </c>
       <c r="E109" t="s">
+        <v>485</v>
+      </c>
+      <c r="F109" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="F109" s="7" t="s">
+      <c r="G109" s="7">
+        <v>280</v>
+      </c>
+      <c r="H109" s="7">
+        <v>140</v>
+      </c>
+      <c r="I109" s="7">
+        <v>40016</v>
+      </c>
+      <c r="J109" s="16">
+        <v>10101</v>
+      </c>
+      <c r="K109" s="7">
+        <v>0</v>
+      </c>
+      <c r="L109" s="7" t="s">
         <v>487</v>
-      </c>
-      <c r="G109" s="7">
-        <v>300</v>
-      </c>
-      <c r="H109" s="7">
-        <v>150</v>
-      </c>
-      <c r="I109" s="7">
-        <v>40017</v>
-      </c>
-      <c r="K109" s="7">
-        <v>0</v>
-      </c>
-      <c r="L109" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="110" spans="2:13">
       <c r="B110" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D110" s="7">
         <v>0.1</v>
       </c>
       <c r="E110" t="s">
+        <v>489</v>
+      </c>
+      <c r="F110" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="G110" s="7">
+        <v>300</v>
+      </c>
+      <c r="H110" s="7">
+        <v>150</v>
+      </c>
+      <c r="I110" s="7">
+        <v>40017</v>
+      </c>
+      <c r="K110" s="7">
+        <v>0</v>
+      </c>
+      <c r="L110" t="s">
         <v>491</v>
-      </c>
-      <c r="G110" s="7">
-        <v>520</v>
-      </c>
-      <c r="H110" s="7">
-        <v>260</v>
-      </c>
-      <c r="I110" s="7">
-        <v>40018</v>
-      </c>
-      <c r="J110" s="16">
-        <v>11101</v>
-      </c>
-      <c r="K110" s="7">
-        <v>0</v>
-      </c>
-      <c r="L110" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="111" spans="2:13">
       <c r="B111" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D111" s="7">
         <v>0.1</v>
       </c>
       <c r="E111" t="s">
+        <v>493</v>
+      </c>
+      <c r="F111" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="F111" s="7" t="s">
+      <c r="G111" s="7">
+        <v>520</v>
+      </c>
+      <c r="H111" s="7">
+        <v>260</v>
+      </c>
+      <c r="I111" s="7">
+        <v>40018</v>
+      </c>
+      <c r="J111" s="16">
+        <v>11101</v>
+      </c>
+      <c r="K111" s="7">
+        <v>0</v>
+      </c>
+      <c r="L111" t="s">
         <v>495</v>
-      </c>
-      <c r="G111" s="7">
-        <v>300</v>
-      </c>
-      <c r="H111" s="7">
-        <v>150</v>
-      </c>
-      <c r="I111" s="7">
-        <v>40019</v>
-      </c>
-      <c r="K111" s="7">
-        <v>0</v>
-      </c>
-      <c r="L111" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="112" spans="2:13">
       <c r="B112" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D112" s="7">
         <v>0.1</v>
       </c>
       <c r="E112" t="s">
+        <v>497</v>
+      </c>
+      <c r="F112" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="G112" s="7">
+        <v>300</v>
+      </c>
+      <c r="H112" s="7">
+        <v>150</v>
+      </c>
+      <c r="I112" s="7">
+        <v>40019</v>
+      </c>
+      <c r="K112" s="7">
+        <v>0</v>
+      </c>
+      <c r="L112" t="s">
         <v>499</v>
-      </c>
-      <c r="G112" s="7">
-        <v>620</v>
-      </c>
-      <c r="H112" s="7">
-        <v>310</v>
-      </c>
-      <c r="I112" s="7">
-        <v>40021</v>
-      </c>
-      <c r="K112" s="7">
-        <v>0</v>
-      </c>
-      <c r="L112" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="113" spans="1:13">
       <c r="B113" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D113" s="7">
         <v>0.1</v>
       </c>
       <c r="E113" t="s">
+        <v>501</v>
+      </c>
+      <c r="F113" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="F113" s="7" t="s">
+      <c r="G113" s="7">
+        <v>620</v>
+      </c>
+      <c r="H113" s="7">
+        <v>310</v>
+      </c>
+      <c r="I113" s="7">
+        <v>40021</v>
+      </c>
+      <c r="K113" s="7">
+        <v>0</v>
+      </c>
+      <c r="L113" t="s">
         <v>503</v>
       </c>
-      <c r="G113" s="7">
+    </row>
+    <row r="114" spans="1:13">
+      <c r="B114" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D114" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="E114" t="s">
+        <v>505</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="G114" s="7">
         <v>320</v>
       </c>
-      <c r="H113" s="7">
+      <c r="H114" s="7">
         <v>160</v>
       </c>
-      <c r="I113" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="J113" s="16">
+      <c r="I114" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="J114" s="16">
         <v>11201</v>
       </c>
-      <c r="K113" s="7">
-        <v>0</v>
-      </c>
-      <c r="L113" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="114" s="2" customFormat="1" spans="1:13">
-      <c r="B114" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D114" s="8">
+      <c r="K114" s="7">
+        <v>0</v>
+      </c>
+      <c r="L114" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="115" s="2" customFormat="1" spans="1:13">
+      <c r="B115" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D115" s="8">
         <v>0.1</v>
       </c>
-      <c r="E114" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="F114" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="G114" s="8">
+      <c r="E115" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="G115" s="8">
         <v>320</v>
       </c>
-      <c r="H114" s="8">
+      <c r="H115" s="8">
         <v>160</v>
       </c>
-      <c r="I114" s="8">
+      <c r="I115" s="8">
         <v>40023</v>
       </c>
-      <c r="J114" s="8">
+      <c r="J115" s="8">
         <v>11301</v>
       </c>
-      <c r="K114" s="8">
-        <v>0</v>
-      </c>
-      <c r="L114" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="M114" s="9"/>
-    </row>
-    <row r="115" spans="1:13">
-      <c r="B115" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="D115" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E115" t="s">
-        <v>511</v>
-      </c>
-      <c r="F115" s="7" t="s">
+      <c r="K115" s="8">
+        <v>0</v>
+      </c>
+      <c r="L115" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="G115" s="7">
-        <v>550</v>
-      </c>
-      <c r="H115" s="7">
-        <v>275</v>
-      </c>
-      <c r="I115" s="7">
-        <v>40024</v>
-      </c>
-      <c r="J115" s="16">
-        <v>11401</v>
-      </c>
-      <c r="K115" s="7">
-        <v>0</v>
-      </c>
-      <c r="L115" s="7" t="s">
-        <v>513</v>
-      </c>
+      <c r="M115" s="9"/>
     </row>
     <row r="116" spans="1:13">
       <c r="B116" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D116" s="7">
         <v>0.1</v>
       </c>
       <c r="E116" t="s">
+        <v>514</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="G116" s="7">
+        <v>550</v>
+      </c>
+      <c r="H116" s="7">
+        <v>275</v>
+      </c>
+      <c r="I116" s="7">
+        <v>40024</v>
+      </c>
+      <c r="J116" s="16">
+        <v>11401</v>
+      </c>
+      <c r="K116" s="7">
+        <v>0</v>
+      </c>
+      <c r="L116" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="G116" s="7">
-        <v>300</v>
-      </c>
-      <c r="H116" s="7">
-        <v>150</v>
-      </c>
-      <c r="I116" s="7">
-        <v>40025</v>
-      </c>
-      <c r="K116" s="7">
-        <v>0</v>
-      </c>
-      <c r="L116" s="7" t="s">
+    </row>
+    <row r="117" s="2" customFormat="1" spans="1:13">
+      <c r="B117" s="1" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="117" s="2" customFormat="1" spans="1:13">
-      <c r="B117" s="2" t="s">
-        <v>518</v>
-      </c>
       <c r="C117" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D117" s="8">
         <v>0.1</v>
       </c>
       <c r="E117" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="F117" s="9" t="s">
         <v>519</v>
-      </c>
-      <c r="F117" s="9" t="s">
-        <v>520</v>
       </c>
       <c r="G117" s="8">
         <v>400</v>
@@ -6599,25 +6596,25 @@
         <v>1</v>
       </c>
       <c r="L117" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M117" s="9"/>
     </row>
     <row r="118" spans="1:13">
       <c r="B118" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C118" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D118" s="7">
         <v>0.1</v>
       </c>
       <c r="E118" t="s">
+        <v>522</v>
+      </c>
+      <c r="F118" t="s">
         <v>523</v>
-      </c>
-      <c r="F118" t="s">
-        <v>524</v>
       </c>
       <c r="G118" s="7">
         <v>330</v>
@@ -6632,24 +6629,24 @@
         <v>1</v>
       </c>
       <c r="L118" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="119" s="2" customFormat="1" spans="1:13">
+      <c r="B119" s="1" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="119" s="2" customFormat="1" spans="1:13">
-      <c r="B119" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="C119" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D119" s="8">
         <v>0.1</v>
       </c>
       <c r="E119" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="F119" s="9" t="s">
         <v>527</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>528</v>
       </c>
       <c r="G119" s="8">
         <v>260</v>
@@ -6665,25 +6662,25 @@
         <v>2</v>
       </c>
       <c r="L119" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="M119" s="9"/>
+    </row>
+    <row r="120" s="2" customFormat="1" spans="1:13">
+      <c r="B120" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="M119" s="9"/>
-    </row>
-    <row r="120" s="2" customFormat="1" spans="1:13">
-      <c r="B120" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="C120" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D120" s="8">
         <v>0.1</v>
       </c>
       <c r="E120" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="F120" s="9" t="s">
         <v>531</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>532</v>
       </c>
       <c r="G120" s="8">
         <v>270</v>
@@ -6699,25 +6696,25 @@
         <v>2</v>
       </c>
       <c r="L120" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="M120" s="9"/>
+    </row>
+    <row r="121" s="2" customFormat="1" spans="1:13">
+      <c r="B121" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="M120" s="9"/>
-    </row>
-    <row r="121" s="2" customFormat="1" spans="1:13">
-      <c r="B121" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="C121" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D121" s="8">
         <v>0.1</v>
       </c>
       <c r="E121" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="F121" s="9" t="s">
         <v>535</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>536</v>
       </c>
       <c r="G121" s="8">
         <v>280</v>
@@ -6735,26 +6732,26 @@
         <v>0</v>
       </c>
       <c r="L121" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M121" s="9"/>
     </row>
     <row r="122" s="2" customFormat="1" spans="1:13">
       <c r="A122" s="9"/>
-      <c r="B122" s="2" t="s">
-        <v>538</v>
+      <c r="B122" s="1" t="s">
+        <v>537</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D122" s="8">
         <v>0.1</v>
       </c>
       <c r="E122" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="F122" s="8" t="s">
         <v>539</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>540</v>
       </c>
       <c r="G122" s="2">
         <v>260</v>
@@ -6770,25 +6767,25 @@
         <v>0</v>
       </c>
       <c r="L122" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M122" s="9"/>
     </row>
     <row r="123" s="1" customFormat="1" spans="1:13">
       <c r="B123" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C123" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D123" s="7">
         <v>0.1</v>
       </c>
       <c r="E123" t="s">
+        <v>542</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="G123" s="7">
         <v>500</v>
@@ -6797,30 +6794,30 @@
         <v>250</v>
       </c>
       <c r="I123" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="K123" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="K123" s="1" t="s">
+      <c r="L123" t="s">
         <v>546</v>
-      </c>
-      <c r="L123" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="1:13">
       <c r="B124" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C124" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D124" s="7">
         <v>0.1</v>
       </c>
       <c r="E124" t="s">
+        <v>548</v>
+      </c>
+      <c r="F124" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>550</v>
       </c>
       <c r="G124" s="7">
         <v>500</v>
@@ -6829,30 +6826,30 @@
         <v>250</v>
       </c>
       <c r="I124" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="L124" t="s">
         <v>551</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="L124" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" spans="1:13">
       <c r="B125" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C125" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D125" s="7">
         <v>0.1</v>
       </c>
       <c r="E125" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="F125" s="7" t="s">
         <v>554</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>555</v>
       </c>
       <c r="G125" s="7">
         <v>500</v>
@@ -6861,14 +6858,14 @@
         <v>250</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="J125" s="7"/>
       <c r="K125" s="7">
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17640" windowHeight="12240"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -238,7 +238,7 @@
     <t>WoodenLongAxe</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+7攻击力</t>
+    <t>亮出的炸弹牌型在结算时提供+7攻击力</t>
   </si>
   <si>
     <t>111</t>
@@ -508,7 +508,7 @@
     <t>20009</t>
   </si>
   <si>
-    <t>亮出的豹子牌型在结算时提供+7倍率</t>
+    <t>亮出的炸弹牌型在结算时提供+7倍率</t>
   </si>
   <si>
     <t>210</t>
@@ -1192,7 +1192,7 @@
     <t>所有敌人造成的伤害降低30%</t>
   </si>
   <si>
-    <t>豹子精髓</t>
+    <t>炸弹精髓</t>
   </si>
   <si>
     <t>LeopardEssence</t>
@@ -1201,7 +1201,7 @@
     <t>30026</t>
   </si>
   <si>
-    <t>使用后,本局内你亮出豹子时,就会获得300金币</t>
+    <t>使用后,本局内你亮出炸弹时,就会获得300金币</t>
   </si>
   <si>
     <t>时之沙</t>
@@ -1273,7 +1273,7 @@
     <t>40001</t>
   </si>
   <si>
-    <t>高牌235等同于豹子牌型,并且可以战胜所有牌型</t>
+    <t>高牌235等同于炸弹牌型,并且可以战胜所有牌型</t>
   </si>
   <si>
     <t>402</t>
@@ -2324,17 +2324,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2352,18 +2346,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2723,133 +2705,133 @@
   <dimension ref="A1:M137"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="2.93333333333333" style="5" customWidth="1"/>
-    <col min="2" max="2" width="4.125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="8.8" style="6" customWidth="1"/>
-    <col min="4" max="4" width="4.78333333333333" style="7" customWidth="1"/>
-    <col min="5" max="5" width="8.8" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.1083333333333" style="7" customWidth="1"/>
-    <col min="7" max="7" width="5.975" style="7" customWidth="1"/>
-    <col min="8" max="8" width="4.78333333333333" style="7" customWidth="1"/>
-    <col min="9" max="9" width="7.38333333333333" style="7" customWidth="1"/>
-    <col min="10" max="10" width="5.53333333333333" style="7" customWidth="1"/>
-    <col min="11" max="11" width="8.03333333333333" style="5" customWidth="1"/>
-    <col min="12" max="12" width="7.70833333333333" style="7" customWidth="1"/>
-    <col min="14" max="14" width="34.75" style="5" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="5" customWidth="1"/>
+    <col min="1" max="1" width="2.93333333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="4" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="5" customWidth="1"/>
+    <col min="5" max="5" width="8.8" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.1083333333333" style="5" customWidth="1"/>
+    <col min="7" max="7" width="5.975" style="5" customWidth="1"/>
+    <col min="8" max="8" width="4.78333333333333" style="5" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="5" customWidth="1"/>
+    <col min="10" max="10" width="5.53333333333333" style="5" customWidth="1"/>
+    <col min="11" max="11" width="8.03333333333333" style="3" customWidth="1"/>
+    <col min="12" max="12" width="7.70833333333333" style="5" customWidth="1"/>
+    <col min="14" max="14" width="34.75" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2860,32 +2842,32 @@
       <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>0.8</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="6">
         <v>45</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="6">
         <v>22</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="6">
         <v>10001</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9" t="s">
+      <c r="J5" s="6"/>
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="9"/>
+      <c r="M5" s="7"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:13">
       <c r="B6" s="1" t="s">
@@ -2894,32 +2876,32 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <v>0.8</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="6">
         <v>28</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="6">
         <v>14</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="6">
         <v>10002</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" s="9" t="s">
+      <c r="J6" s="6"/>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="9"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:13">
       <c r="B7" s="1" t="s">
@@ -2928,32 +2910,32 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>0.8</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>28</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="6">
         <v>14</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>10003</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9" t="s">
+      <c r="J7" s="6"/>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="9"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:13">
       <c r="B8" s="1" t="s">
@@ -2962,32 +2944,32 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>0.8</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>28</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>14</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="6">
         <v>10004</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9" t="s">
+      <c r="J8" s="6"/>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="9"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:13">
       <c r="B9" s="1" t="s">
@@ -2996,32 +2978,32 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>0.8</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <v>28</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="6">
         <v>14</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="6">
         <v>10005</v>
       </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="9" t="s">
+      <c r="J9" s="6"/>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="9"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:13">
       <c r="B10" s="1" t="s">
@@ -3030,32 +3012,32 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>0.8</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="6">
         <v>28</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="6">
         <v>14</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="6">
         <v>10006</v>
       </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9" t="s">
+      <c r="J10" s="6"/>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="9"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:13">
       <c r="B11" s="1" t="s">
@@ -3064,32 +3046,32 @@
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>0.8</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="6">
         <v>22</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="6">
         <v>11</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="6">
         <v>10007</v>
       </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="s">
+      <c r="J11" s="6"/>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="9"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:13">
       <c r="B12" s="1" t="s">
@@ -3098,32 +3080,32 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="6">
         <v>0.8</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="6">
         <v>35</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="6">
         <v>17</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="6">
         <v>10008</v>
       </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9" t="s">
+      <c r="J12" s="6"/>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="9"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:13">
       <c r="B13" s="1" t="s">
@@ -3132,32 +3114,32 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>0.8</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="6">
         <v>16</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="6">
         <v>8</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="6">
         <v>10009</v>
       </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9" t="s">
+      <c r="J13" s="6"/>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="M13" s="9"/>
+      <c r="M13" s="7"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:13">
       <c r="B14" s="1" t="s">
@@ -3166,66 +3148,66 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="6">
         <v>0.8</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="6">
         <v>16</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="6">
         <v>8</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="6">
         <v>10010</v>
       </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9" t="s">
+      <c r="J14" s="6"/>
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="9"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:13">
-      <c r="B15" s="2" t="s">
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:13">
+      <c r="B15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="6">
         <v>0.8</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="6">
         <v>15</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="6">
         <v>7</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="6">
         <v>10011</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="s">
+      <c r="J15" s="6"/>
+      <c r="K15" s="6">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="11"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:13">
       <c r="B16" s="1" t="s">
@@ -3234,29 +3216,29 @@
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="6">
         <v>0.8</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="6">
         <v>30</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="6">
         <v>15</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="6">
         <v>10012</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9" t="s">
+      <c r="J16" s="6"/>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3267,29 +3249,29 @@
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>0.8</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="6">
         <v>35</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="6">
         <v>17</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="6">
         <v>10013</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="9" t="s">
+      <c r="J17" s="6"/>
+      <c r="K17" s="6">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3300,29 +3282,29 @@
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="6">
         <v>0.8</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="6">
         <v>26</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="6">
         <v>13</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="6">
         <v>10014</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9" t="s">
+      <c r="J18" s="6"/>
+      <c r="K18" s="6">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3333,95 +3315,95 @@
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="6">
         <v>0.8</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="6">
         <v>22</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="6">
         <v>11</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="6">
         <v>10015</v>
       </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8">
-        <v>0</v>
-      </c>
-      <c r="L19" s="9" t="s">
+      <c r="J19" s="6"/>
+      <c r="K19" s="6">
+        <v>0</v>
+      </c>
+      <c r="L19" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" spans="1:13">
-      <c r="B20" s="2" t="s">
+    <row r="20" s="1" customFormat="1" spans="1:13">
+      <c r="B20" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="6">
         <v>0.8</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="6">
         <v>28</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="6">
         <v>14</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="6">
         <v>10016</v>
       </c>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10">
-        <v>0</v>
-      </c>
-      <c r="L20" s="11" t="s">
+      <c r="J20" s="6"/>
+      <c r="K20" s="6">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" spans="1:13">
-      <c r="B21" s="2" t="s">
+    <row r="21" s="1" customFormat="1" spans="1:13">
+      <c r="B21" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="6">
         <v>0.8</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="6">
         <v>20</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="6">
         <v>10</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="6">
         <v>10017</v>
       </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="s">
+      <c r="J21" s="6"/>
+      <c r="K21" s="6">
+        <v>0</v>
+      </c>
+      <c r="L21" s="7" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3429,149 +3411,149 @@
       <c r="B22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="6">
         <v>0.8</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="6">
         <v>25</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="6">
         <v>12</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="6">
         <v>10018</v>
       </c>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8">
+      <c r="J22" s="6"/>
+      <c r="K22" s="6">
         <v>1</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="M22" s="9"/>
+      <c r="M22" s="7"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:13">
       <c r="B23" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="6">
         <v>0.8</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="6">
         <v>25</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="6">
         <v>12</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="6">
         <v>10019</v>
       </c>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8">
+      <c r="J23" s="6"/>
+      <c r="K23" s="6">
         <v>1</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="M23" s="9"/>
-    </row>
-    <row r="24" s="2" customFormat="1" spans="1:13">
-      <c r="B24" s="2" t="s">
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:13">
+      <c r="B24" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="6">
         <v>0.8</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="6">
         <v>30</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="6">
         <v>15</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="6">
         <v>10020</v>
       </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10">
-        <v>0</v>
-      </c>
-      <c r="L24" s="11" t="s">
+      <c r="J24" s="6"/>
+      <c r="K24" s="6">
+        <v>0</v>
+      </c>
+      <c r="L24" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="11"/>
+      <c r="M24" s="7"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:13">
       <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="6">
         <v>0.8</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="6">
         <v>35</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="6">
         <v>17</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="6">
         <v>10021</v>
       </c>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8">
+      <c r="J25" s="6"/>
+      <c r="K25" s="6">
         <v>2</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="M25" s="9"/>
+      <c r="M25" s="7"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:13">
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="9"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="7"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
       <c r="B27" s="1" t="s">
@@ -3580,13 +3562,13 @@
       <c r="C27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="6">
         <v>0.4</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="6" t="s">
         <v>116</v>
       </c>
       <c r="G27" s="1">
@@ -3598,14 +3580,14 @@
       <c r="I27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8">
-        <v>0</v>
-      </c>
-      <c r="L27" s="9" t="s">
+      <c r="J27" s="6"/>
+      <c r="K27" s="6">
+        <v>0</v>
+      </c>
+      <c r="L27" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="M27" s="9"/>
+      <c r="M27" s="7"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:13">
       <c r="B28" s="1" t="s">
@@ -3614,13 +3596,13 @@
       <c r="C28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="6">
         <v>0.4</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="6" t="s">
         <v>121</v>
       </c>
       <c r="G28" s="1">
@@ -3632,30 +3614,30 @@
       <c r="I28" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8">
-        <v>0</v>
-      </c>
-      <c r="L28" s="9" t="s">
+      <c r="J28" s="6"/>
+      <c r="K28" s="6">
+        <v>0</v>
+      </c>
+      <c r="L28" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="M28" s="9"/>
+      <c r="M28" s="7"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="9"/>
+      <c r="A29" s="7"/>
       <c r="B29" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="6">
         <v>0.4</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G29" s="1">
@@ -3667,30 +3649,30 @@
       <c r="I29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9" t="s">
+      <c r="J29" s="6"/>
+      <c r="K29" s="6">
+        <v>0</v>
+      </c>
+      <c r="L29" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="M29" s="9"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:13">
-      <c r="A30" s="9"/>
+      <c r="A30" s="7"/>
       <c r="B30" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="6">
         <v>0.4</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="6" t="s">
         <v>131</v>
       </c>
       <c r="G30" s="1">
@@ -3702,30 +3684,30 @@
       <c r="I30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8">
-        <v>0</v>
-      </c>
-      <c r="L30" s="9" t="s">
+      <c r="J30" s="6"/>
+      <c r="K30" s="6">
+        <v>0</v>
+      </c>
+      <c r="L30" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="M30" s="9"/>
+      <c r="M30" s="7"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:13">
-      <c r="A31" s="9"/>
+      <c r="A31" s="7"/>
       <c r="B31" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="6">
         <v>0.4</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="6" t="s">
         <v>136</v>
       </c>
       <c r="G31" s="1">
@@ -3737,30 +3719,30 @@
       <c r="I31" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8">
-        <v>0</v>
-      </c>
-      <c r="L31" s="9" t="s">
+      <c r="J31" s="6"/>
+      <c r="K31" s="6">
+        <v>0</v>
+      </c>
+      <c r="L31" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="M31" s="9"/>
+      <c r="M31" s="7"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:13">
-      <c r="A32" s="9"/>
+      <c r="A32" s="7"/>
       <c r="B32" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="6">
         <v>0.4</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="6" t="s">
         <v>141</v>
       </c>
       <c r="G32" s="1">
@@ -3772,30 +3754,30 @@
       <c r="I32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8">
-        <v>0</v>
-      </c>
-      <c r="L32" s="9" t="s">
+      <c r="J32" s="6"/>
+      <c r="K32" s="6">
+        <v>0</v>
+      </c>
+      <c r="L32" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="M32" s="9"/>
+      <c r="M32" s="7"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="9"/>
+      <c r="A33" s="7"/>
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="6">
         <v>0.4</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="6" t="s">
         <v>146</v>
       </c>
       <c r="G33" s="1">
@@ -3807,30 +3789,30 @@
       <c r="I33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8">
-        <v>0</v>
-      </c>
-      <c r="L33" s="9" t="s">
+      <c r="J33" s="6"/>
+      <c r="K33" s="6">
+        <v>0</v>
+      </c>
+      <c r="L33" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="M33" s="9"/>
+      <c r="M33" s="7"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:13">
-      <c r="A34" s="9"/>
+      <c r="A34" s="7"/>
       <c r="B34" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="6">
         <v>0.4</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="6" t="s">
         <v>151</v>
       </c>
       <c r="G34" s="1">
@@ -3842,30 +3824,30 @@
       <c r="I34" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8">
-        <v>0</v>
-      </c>
-      <c r="L34" s="9" t="s">
+      <c r="J34" s="6"/>
+      <c r="K34" s="6">
+        <v>0</v>
+      </c>
+      <c r="L34" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="M34" s="9"/>
+      <c r="M34" s="7"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="9"/>
+      <c r="A35" s="7"/>
       <c r="B35" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="6">
         <v>0.4</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="6" t="s">
         <v>156</v>
       </c>
       <c r="G35" s="1">
@@ -3877,65 +3859,65 @@
       <c r="I35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8">
-        <v>0</v>
-      </c>
-      <c r="L35" s="9" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="6">
+        <v>0</v>
+      </c>
+      <c r="L35" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="M35" s="9"/>
-    </row>
-    <row r="36" s="3" customFormat="1" spans="1:13">
-      <c r="A36" s="12"/>
+      <c r="M35" s="7"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:13">
+      <c r="A36" s="8"/>
       <c r="B36" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="9">
         <v>0.4</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="2">
         <v>140</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="2">
         <v>70</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13">
-        <v>0</v>
-      </c>
-      <c r="L36" s="9" t="s">
+      <c r="J36" s="9"/>
+      <c r="K36" s="9">
+        <v>0</v>
+      </c>
+      <c r="L36" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="M36" s="12"/>
+      <c r="M36" s="8"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:13">
-      <c r="A37" s="9"/>
+      <c r="A37" s="7"/>
       <c r="B37" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="6">
         <v>0.4</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="6" t="s">
         <v>166</v>
       </c>
       <c r="G37" s="1">
@@ -3947,65 +3929,65 @@
       <c r="I37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8">
-        <v>0</v>
-      </c>
-      <c r="L37" s="8" t="s">
+      <c r="J37" s="6"/>
+      <c r="K37" s="6">
+        <v>0</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="M37" s="9"/>
-    </row>
-    <row r="38" s="4" customFormat="1" spans="1:13">
-      <c r="A38" s="14"/>
-      <c r="B38" s="2" t="s">
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="1:13">
+      <c r="A38" s="8"/>
+      <c r="B38" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="9">
         <v>0.4</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="2">
         <v>135</v>
       </c>
-      <c r="H38" s="4">
+      <c r="H38" s="2">
         <v>67</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15">
-        <v>0</v>
-      </c>
-      <c r="L38" s="14" t="s">
+      <c r="J38" s="9"/>
+      <c r="K38" s="9">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="M38" s="14"/>
+      <c r="M38" s="8"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:13">
-      <c r="A39" s="9"/>
+      <c r="A39" s="7"/>
       <c r="B39" s="1" t="s">
         <v>174</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="6">
         <v>0.4</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="E39" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F39" s="8" t="s">
+      <c r="F39" s="6" t="s">
         <v>176</v>
       </c>
       <c r="G39" s="1">
@@ -4017,30 +3999,30 @@
       <c r="I39" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8">
-        <v>0</v>
-      </c>
-      <c r="L39" s="9" t="s">
+      <c r="J39" s="6"/>
+      <c r="K39" s="6">
+        <v>0</v>
+      </c>
+      <c r="L39" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="M39" s="9"/>
+      <c r="M39" s="7"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:13">
-      <c r="A40" s="9"/>
+      <c r="A40" s="7"/>
       <c r="B40" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="6">
         <v>0.4</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F40" s="8" t="s">
+      <c r="F40" s="6" t="s">
         <v>181</v>
       </c>
       <c r="G40" s="1">
@@ -4052,28 +4034,28 @@
       <c r="I40" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K40" s="8">
-        <v>0</v>
-      </c>
-      <c r="L40" s="9" t="s">
+      <c r="K40" s="6">
+        <v>0</v>
+      </c>
+      <c r="L40" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:13">
-      <c r="A41" s="9"/>
+      <c r="A41" s="7"/>
       <c r="B41" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="6">
         <v>0.4</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="E41" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="6" t="s">
         <v>186</v>
       </c>
       <c r="G41" s="1">
@@ -4085,28 +4067,28 @@
       <c r="I41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K41" s="8">
-        <v>0</v>
-      </c>
-      <c r="L41" s="9" t="s">
+      <c r="K41" s="6">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:13">
-      <c r="A42" s="9"/>
+      <c r="A42" s="7"/>
       <c r="B42" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="6">
         <v>0.4</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="6" t="s">
         <v>191</v>
       </c>
       <c r="G42" s="1">
@@ -4118,28 +4100,28 @@
       <c r="I42" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K42" s="8">
-        <v>0</v>
-      </c>
-      <c r="L42" s="9" t="s">
+      <c r="K42" s="6">
+        <v>0</v>
+      </c>
+      <c r="L42" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
-      <c r="A43" s="9"/>
+      <c r="A43" s="7"/>
       <c r="B43" s="1" t="s">
         <v>194</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="6">
         <v>0.4</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="6" t="s">
         <v>196</v>
       </c>
       <c r="G43" s="1">
@@ -4151,180 +4133,180 @@
       <c r="I43" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K43" s="8">
-        <v>0</v>
-      </c>
-      <c r="L43" s="9" t="s">
+      <c r="K43" s="6">
+        <v>0</v>
+      </c>
+      <c r="L43" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:13">
-      <c r="A44" s="9"/>
+      <c r="A44" s="7"/>
       <c r="B44" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="6">
         <v>0.4</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="6">
         <v>85</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="6">
         <v>42</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8">
-        <v>0</v>
-      </c>
-      <c r="L44" s="8" t="s">
+      <c r="J44" s="6"/>
+      <c r="K44" s="6">
+        <v>0</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="45" s="2" customFormat="1" spans="1:13">
-      <c r="A45" s="11"/>
-      <c r="B45" s="2" t="s">
+    <row r="45" s="1" customFormat="1" spans="1:13">
+      <c r="A45" s="7"/>
+      <c r="B45" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="6">
         <v>0.4</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="6">
         <v>75</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="6">
         <v>37</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I45" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10">
-        <v>0</v>
-      </c>
-      <c r="L45" s="11" t="s">
+      <c r="J45" s="6"/>
+      <c r="K45" s="6">
+        <v>0</v>
+      </c>
+      <c r="L45" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="46" s="2" customFormat="1" spans="1:13">
-      <c r="A46" s="11"/>
-      <c r="B46" s="2" t="s">
+    <row r="46" s="1" customFormat="1" spans="1:13">
+      <c r="A46" s="7"/>
+      <c r="B46" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="6">
         <v>0.4</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="6">
         <v>75</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="6">
         <v>37</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="I46" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10">
-        <v>0</v>
-      </c>
-      <c r="L46" s="11" t="s">
+      <c r="J46" s="6"/>
+      <c r="K46" s="6">
+        <v>0</v>
+      </c>
+      <c r="L46" s="7" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:13">
-      <c r="A47" s="9"/>
+      <c r="A47" s="7"/>
       <c r="B47" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="6">
         <v>0.4</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="F47" s="8" t="s">
+      <c r="F47" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="6">
         <v>70</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="6">
         <v>35</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8">
-        <v>0</v>
-      </c>
-      <c r="L47" s="9" t="s">
+      <c r="J47" s="6"/>
+      <c r="K47" s="6">
+        <v>0</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:13">
-      <c r="A48" s="9"/>
+      <c r="A48" s="7"/>
       <c r="B48" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="6">
         <v>0.4</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="F48" s="8" t="s">
+      <c r="F48" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="6">
         <v>75</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="6">
         <v>37</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8">
-        <v>0</v>
-      </c>
-      <c r="L48" s="9" t="s">
+      <c r="J48" s="6"/>
+      <c r="K48" s="6">
+        <v>0</v>
+      </c>
+      <c r="L48" s="7" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4335,479 +4317,479 @@
       <c r="C49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="6">
         <v>0.4</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49" s="6">
         <v>90</v>
       </c>
-      <c r="H49" s="8">
+      <c r="H49" s="6">
         <v>45</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J49" s="8">
+      <c r="J49" s="6">
         <v>10301</v>
       </c>
-      <c r="K49" s="8">
-        <v>0</v>
-      </c>
-      <c r="L49" s="8" t="s">
+      <c r="K49" s="6">
+        <v>0</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="M49" s="9"/>
+      <c r="M49" s="7"/>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:13">
-      <c r="A50" s="9"/>
+      <c r="A50" s="7"/>
       <c r="B50" s="1" t="s">
         <v>229</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="6">
         <v>0.4</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="F50" s="8" t="s">
+      <c r="F50" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50" s="6">
         <v>120</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="6">
         <v>60</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8">
-        <v>0</v>
-      </c>
-      <c r="L50" s="8" t="s">
+      <c r="J50" s="6"/>
+      <c r="K50" s="6">
+        <v>0</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="M50" s="9"/>
+      <c r="M50" s="7"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:13">
-      <c r="A51" s="9"/>
+      <c r="A51" s="7"/>
       <c r="B51" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="6">
         <v>0.4</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F51" s="8" t="s">
+      <c r="F51" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51" s="6">
         <v>110</v>
       </c>
-      <c r="H51" s="8">
+      <c r="H51" s="6">
         <v>55</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8">
-        <v>0</v>
-      </c>
-      <c r="L51" s="9" t="s">
+      <c r="J51" s="6"/>
+      <c r="K51" s="6">
+        <v>0</v>
+      </c>
+      <c r="L51" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="M51" s="9"/>
-    </row>
-    <row r="52" s="2" customFormat="1" spans="1:13">
-      <c r="A52" s="11"/>
-      <c r="B52" s="2" t="s">
+      <c r="M51" s="7"/>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:13">
+      <c r="A52" s="7"/>
+      <c r="B52" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="6">
         <v>0.4</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="6">
         <v>70</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="6">
         <v>35</v>
       </c>
-      <c r="I52" s="2" t="s">
+      <c r="I52" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10">
-        <v>0</v>
-      </c>
-      <c r="L52" s="11" t="s">
+      <c r="J52" s="6"/>
+      <c r="K52" s="6">
+        <v>0</v>
+      </c>
+      <c r="L52" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="M52" s="11"/>
+      <c r="M52" s="7"/>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:13">
       <c r="B53" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="C53" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="6">
         <v>0.4</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53" s="6">
         <v>90</v>
       </c>
-      <c r="H53" s="8">
+      <c r="H53" s="6">
         <v>45</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8">
+      <c r="J53" s="6"/>
+      <c r="K53" s="6">
         <v>1</v>
       </c>
-      <c r="L53" s="9" t="s">
+      <c r="L53" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="M53" s="9"/>
+      <c r="M53" s="7"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:13">
       <c r="B54" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C54" s="9" t="s">
+      <c r="C54" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="6">
         <v>0.4</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54" s="6">
         <v>145</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="6">
         <v>72</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8">
+      <c r="J54" s="6"/>
+      <c r="K54" s="6">
         <v>1</v>
       </c>
-      <c r="L54" s="9" t="s">
+      <c r="L54" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="M54" s="9"/>
+      <c r="M54" s="7"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:13">
       <c r="B55" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="6">
         <v>0.4</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F55" s="9" t="s">
+      <c r="F55" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="6">
         <v>95</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="6">
         <v>47</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8">
-        <v>0</v>
-      </c>
-      <c r="L55" s="9" t="s">
+      <c r="J55" s="6"/>
+      <c r="K55" s="6">
+        <v>0</v>
+      </c>
+      <c r="L55" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="M55" s="9"/>
+      <c r="M55" s="7"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:13">
       <c r="B56" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="6">
         <v>0.4</v>
       </c>
-      <c r="E56" s="9" t="s">
+      <c r="E56" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56" s="6">
         <v>110</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="6">
         <v>55</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8">
+      <c r="J56" s="6"/>
+      <c r="K56" s="6">
         <v>1</v>
       </c>
-      <c r="L56" s="9" t="s">
+      <c r="L56" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="M56" s="9"/>
+      <c r="M56" s="7"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:13">
       <c r="B57" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C57" s="9" t="s">
+      <c r="C57" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="6">
         <v>0.4</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="F57" s="9" t="s">
+      <c r="F57" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57" s="6">
         <v>160</v>
       </c>
-      <c r="H57" s="8">
+      <c r="H57" s="6">
         <v>80</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8">
+      <c r="J57" s="6"/>
+      <c r="K57" s="6">
         <v>2</v>
       </c>
-      <c r="L57" s="9" t="s">
+      <c r="L57" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="M57" s="9"/>
+      <c r="M57" s="7"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:13">
       <c r="B58" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="6">
         <v>0.4</v>
       </c>
-      <c r="E58" s="9" t="s">
+      <c r="E58" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="6">
         <v>160</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="6">
         <v>80</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8">
+      <c r="J58" s="6"/>
+      <c r="K58" s="6">
         <v>2</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L58" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="M58" s="9"/>
+      <c r="M58" s="7"/>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:13">
-      <c r="A59" s="9"/>
+      <c r="A59" s="7"/>
       <c r="B59" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C59" s="9" t="s">
+      <c r="C59" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="6">
         <v>0.4</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F59" s="9" t="s">
+      <c r="F59" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="6">
         <v>80</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="6">
         <v>40</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8">
-        <v>0</v>
-      </c>
-      <c r="L59" s="9" t="s">
+      <c r="J59" s="6"/>
+      <c r="K59" s="6">
+        <v>0</v>
+      </c>
+      <c r="L59" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="M59" s="9"/>
+      <c r="M59" s="7"/>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:13">
-      <c r="A60" s="9"/>
+      <c r="A60" s="7"/>
       <c r="B60" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="6">
         <v>0.4</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="6">
         <v>80</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="6">
         <v>40</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8">
-        <v>0</v>
-      </c>
-      <c r="L60" s="9" t="s">
+      <c r="J60" s="6"/>
+      <c r="K60" s="6">
+        <v>0</v>
+      </c>
+      <c r="L60" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="M60" s="9"/>
+      <c r="M60" s="7"/>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:13">
-      <c r="A61" s="9"/>
+      <c r="A61" s="7"/>
       <c r="B61" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="6">
         <v>0.4</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F61" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="6">
         <v>80</v>
       </c>
-      <c r="H61" s="8">
+      <c r="H61" s="6">
         <v>40</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8">
-        <v>0</v>
-      </c>
-      <c r="L61" s="9" t="s">
+      <c r="J61" s="6"/>
+      <c r="K61" s="6">
+        <v>0</v>
+      </c>
+      <c r="L61" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="M61" s="9"/>
+      <c r="M61" s="7"/>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:13">
-      <c r="A62" s="9"/>
-      <c r="B62" s="8"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="6"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="9"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="7"/>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:13">
-      <c r="A63" s="9"/>
-      <c r="B63" s="8">
+      <c r="A63" s="7"/>
+      <c r="B63" s="6">
         <v>301</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="6">
         <v>0.2</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="F63" s="8" t="s">
+      <c r="F63" s="6" t="s">
         <v>291</v>
       </c>
       <c r="G63" s="1">
@@ -4819,32 +4801,32 @@
       <c r="I63" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="J63" s="8">
+      <c r="J63" s="6">
         <v>10401</v>
       </c>
-      <c r="K63" s="8">
-        <v>0</v>
-      </c>
-      <c r="L63" s="9" t="s">
+      <c r="K63" s="6">
+        <v>0</v>
+      </c>
+      <c r="L63" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="M63" s="9"/>
+      <c r="M63" s="7"/>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:13">
-      <c r="A64" s="9"/>
-      <c r="B64" s="8">
+      <c r="A64" s="7"/>
+      <c r="B64" s="6">
         <v>302</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="6">
         <v>0.2</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="F64" s="8" t="s">
+      <c r="F64" s="6" t="s">
         <v>295</v>
       </c>
       <c r="G64" s="1">
@@ -4856,30 +4838,30 @@
       <c r="I64" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8">
-        <v>0</v>
-      </c>
-      <c r="L64" s="9" t="s">
+      <c r="J64" s="6"/>
+      <c r="K64" s="6">
+        <v>0</v>
+      </c>
+      <c r="L64" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="M64" s="9"/>
+      <c r="M64" s="7"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:13">
-      <c r="A65" s="9"/>
-      <c r="B65" s="8">
+      <c r="A65" s="7"/>
+      <c r="B65" s="6">
         <v>303</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="6">
         <v>0.2</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="F65" s="6" t="s">
         <v>299</v>
       </c>
       <c r="G65" s="1">
@@ -4891,68 +4873,68 @@
       <c r="I65" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="J65" s="10">
+      <c r="J65" s="6">
         <v>10501</v>
       </c>
-      <c r="K65" s="8">
-        <v>0</v>
-      </c>
-      <c r="L65" s="9" t="s">
+      <c r="K65" s="6">
+        <v>0</v>
+      </c>
+      <c r="L65" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="M65" s="9"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:13">
-      <c r="A66" s="11"/>
-      <c r="B66" s="10">
+      <c r="M65" s="7"/>
+    </row>
+    <row r="66" s="1" customFormat="1" spans="1:13">
+      <c r="A66" s="7"/>
+      <c r="B66" s="6">
         <v>304</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="6">
         <v>0.2</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F66" s="10" t="s">
+      <c r="F66" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G66" s="1">
         <v>160</v>
       </c>
-      <c r="H66" s="2">
+      <c r="H66" s="1">
         <v>80</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="I66" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="J66" s="10">
+      <c r="J66" s="6">
         <v>10601</v>
       </c>
-      <c r="K66" s="10">
-        <v>0</v>
-      </c>
-      <c r="L66" s="11" t="s">
+      <c r="K66" s="6">
+        <v>0</v>
+      </c>
+      <c r="L66" s="7" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:13">
-      <c r="A67" s="9"/>
-      <c r="B67" s="8">
+      <c r="A67" s="7"/>
+      <c r="B67" s="6">
         <v>305</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="6">
         <v>0.2</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F67" s="6" t="s">
         <v>307</v>
       </c>
       <c r="G67" s="1">
@@ -4964,30 +4946,30 @@
       <c r="I67" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="J67" s="8">
+      <c r="J67" s="6">
         <v>10701</v>
       </c>
-      <c r="K67" s="8">
-        <v>0</v>
-      </c>
-      <c r="L67" s="9" t="s">
+      <c r="K67" s="6">
+        <v>0</v>
+      </c>
+      <c r="L67" s="7" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:13">
-      <c r="B68" s="8">
+      <c r="B68" s="6">
         <v>306</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="6">
         <v>0.2</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="6" t="s">
         <v>311</v>
       </c>
       <c r="G68" s="1">
@@ -4999,27 +4981,27 @@
       <c r="I68" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="K68" s="8">
-        <v>0</v>
-      </c>
-      <c r="L68" s="9" t="s">
+      <c r="K68" s="6">
+        <v>0</v>
+      </c>
+      <c r="L68" s="7" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:13">
-      <c r="B69" s="8">
+      <c r="B69" s="6">
         <v>307</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="6">
         <v>0.2</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="6" t="s">
         <v>315</v>
       </c>
       <c r="G69" s="1">
@@ -5031,28 +5013,28 @@
       <c r="I69" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8">
-        <v>0</v>
-      </c>
-      <c r="L69" s="9" t="s">
+      <c r="J69" s="6"/>
+      <c r="K69" s="6">
+        <v>0</v>
+      </c>
+      <c r="L69" s="7" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:13">
-      <c r="B70" s="8">
+      <c r="B70" s="6">
         <v>308</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="6">
         <v>0.2</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F70" s="8" t="s">
+      <c r="F70" s="6" t="s">
         <v>319</v>
       </c>
       <c r="G70" s="1">
@@ -5064,27 +5046,27 @@
       <c r="I70" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="K70" s="8">
-        <v>0</v>
-      </c>
-      <c r="L70" s="9" t="s">
+      <c r="K70" s="6">
+        <v>0</v>
+      </c>
+      <c r="L70" s="7" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:13">
-      <c r="B71" s="8">
+      <c r="B71" s="6">
         <v>309</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="6">
         <v>0.2</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="6" t="s">
         <v>323</v>
       </c>
       <c r="G71" s="1">
@@ -5096,92 +5078,92 @@
       <c r="I71" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8">
-        <v>0</v>
-      </c>
-      <c r="L71" s="8" t="s">
+      <c r="J71" s="6"/>
+      <c r="K71" s="6">
+        <v>0</v>
+      </c>
+      <c r="L71" s="6" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" spans="1:13">
-      <c r="B72" s="10">
+    <row r="72" s="1" customFormat="1" spans="1:13">
+      <c r="B72" s="6">
         <v>310</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D72" s="10">
+      <c r="D72" s="6">
         <v>0.2</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="F72" s="10" t="s">
+      <c r="F72" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G72" s="1">
         <v>170</v>
       </c>
-      <c r="H72" s="2">
+      <c r="H72" s="1">
         <v>85</v>
       </c>
-      <c r="I72" s="2" t="s">
+      <c r="I72" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K72" s="10">
-        <v>0</v>
-      </c>
-      <c r="L72" s="11" t="s">
+      <c r="K72" s="6">
+        <v>0</v>
+      </c>
+      <c r="L72" s="7" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="73" s="2" customFormat="1" spans="1:13">
-      <c r="B73" s="10">
+    <row r="73" s="1" customFormat="1" spans="1:13">
+      <c r="B73" s="6">
         <v>311</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73" s="6">
         <v>0.2</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="F73" s="10" t="s">
+      <c r="F73" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="G73" s="2">
+      <c r="G73" s="1">
         <v>130</v>
       </c>
-      <c r="H73" s="2">
+      <c r="H73" s="1">
         <v>65</v>
       </c>
-      <c r="I73" s="2" t="s">
+      <c r="I73" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="K73" s="10">
-        <v>0</v>
-      </c>
-      <c r="L73" s="11" t="s">
+      <c r="K73" s="6">
+        <v>0</v>
+      </c>
+      <c r="L73" s="7" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:13">
-      <c r="B74" s="8">
+      <c r="B74" s="6">
         <v>312</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="6">
         <v>0.2</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="F74" s="8" t="s">
+      <c r="F74" s="6" t="s">
         <v>335</v>
       </c>
       <c r="G74" s="1">
@@ -5193,644 +5175,644 @@
       <c r="I74" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8">
-        <v>0</v>
-      </c>
-      <c r="L74" s="9" t="s">
+      <c r="J74" s="6"/>
+      <c r="K74" s="6">
+        <v>0</v>
+      </c>
+      <c r="L74" s="7" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:13">
-      <c r="B75" s="8">
+      <c r="B75" s="6">
         <v>313</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="6">
         <v>0.2</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="F75" s="8" t="s">
+      <c r="F75" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="6">
         <v>120</v>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="6">
         <v>60</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8">
-        <v>0</v>
-      </c>
-      <c r="L75" s="9" t="s">
+      <c r="J75" s="6"/>
+      <c r="K75" s="6">
+        <v>0</v>
+      </c>
+      <c r="L75" s="7" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:13">
-      <c r="B76" s="8">
+      <c r="B76" s="6">
         <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="6">
         <v>0.2</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F76" s="8" t="s">
+      <c r="F76" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="6">
         <v>380</v>
       </c>
-      <c r="H76" s="8">
+      <c r="H76" s="6">
         <v>190</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8">
-        <v>0</v>
-      </c>
-      <c r="L76" s="9" t="s">
+      <c r="J76" s="6"/>
+      <c r="K76" s="6">
+        <v>0</v>
+      </c>
+      <c r="L76" s="7" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:13">
-      <c r="B77" s="8">
+      <c r="B77" s="6">
         <v>315</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="6">
         <v>0.2</v>
       </c>
-      <c r="E77" s="8" t="s">
+      <c r="E77" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="6">
         <v>170</v>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="6">
         <v>85</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8">
-        <v>0</v>
-      </c>
-      <c r="L77" s="9" t="s">
+      <c r="J77" s="6"/>
+      <c r="K77" s="6">
+        <v>0</v>
+      </c>
+      <c r="L77" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="M77" s="9"/>
+      <c r="M77" s="7"/>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:13">
-      <c r="B78" s="8">
+      <c r="B78" s="6">
         <v>316</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="6">
         <v>0.2</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="F78" s="8" t="s">
+      <c r="F78" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="6">
         <v>200</v>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="6">
         <v>100</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="J78" s="8">
+      <c r="J78" s="6">
         <v>10201</v>
       </c>
-      <c r="K78" s="8">
-        <v>0</v>
-      </c>
-      <c r="L78" s="8" t="s">
+      <c r="K78" s="6">
+        <v>0</v>
+      </c>
+      <c r="L78" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="M78" s="9"/>
+      <c r="M78" s="7"/>
     </row>
     <row r="79" s="1" customFormat="1" spans="1:13">
-      <c r="B79" s="8">
+      <c r="B79" s="6">
         <v>317</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="6">
         <v>0.2</v>
       </c>
-      <c r="E79" s="8" t="s">
+      <c r="E79" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F79" s="8" t="s">
+      <c r="F79" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="6">
         <v>170</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="6">
         <v>85</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J79" s="10">
+      <c r="J79" s="6">
         <v>10801</v>
       </c>
-      <c r="K79" s="8">
-        <v>0</v>
-      </c>
-      <c r="L79" s="9" t="s">
+      <c r="K79" s="6">
+        <v>0</v>
+      </c>
+      <c r="L79" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="M79" s="9"/>
-    </row>
-    <row r="80" s="2" customFormat="1" spans="1:13">
-      <c r="B80" s="10">
+      <c r="M79" s="7"/>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="1:13">
+      <c r="B80" s="6">
         <v>318</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C80" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D80" s="10">
+      <c r="D80" s="6">
         <v>0.2</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="F80" s="10" t="s">
+      <c r="F80" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="G80" s="10">
+      <c r="G80" s="6">
         <v>160</v>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="6">
         <v>80</v>
       </c>
-      <c r="I80" s="2" t="s">
+      <c r="I80" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="J80" s="10">
+      <c r="J80" s="6">
         <v>10402</v>
       </c>
-      <c r="K80" s="10">
-        <v>0</v>
-      </c>
-      <c r="L80" s="11" t="s">
+      <c r="K80" s="6">
+        <v>0</v>
+      </c>
+      <c r="L80" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="M80" s="11"/>
+      <c r="M80" s="7"/>
     </row>
     <row r="81" s="1" customFormat="1" spans="2:13">
-      <c r="B81" s="8">
+      <c r="B81" s="6">
         <v>319</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="6">
         <v>0.2</v>
       </c>
-      <c r="E81" s="8" t="s">
+      <c r="E81" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="F81" s="8" t="s">
+      <c r="F81" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G81" s="8">
+      <c r="G81" s="6">
         <v>160</v>
       </c>
-      <c r="H81" s="8">
+      <c r="H81" s="6">
         <v>80</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8">
-        <v>0</v>
-      </c>
-      <c r="L81" s="9" t="s">
+      <c r="J81" s="6"/>
+      <c r="K81" s="6">
+        <v>0</v>
+      </c>
+      <c r="L81" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="M81" s="9"/>
+      <c r="M81" s="7"/>
     </row>
     <row r="82" s="1" customFormat="1" spans="2:13">
-      <c r="B82" s="8">
+      <c r="B82" s="6">
         <v>320</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="6">
         <v>0.2</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="F82" s="8" t="s">
+      <c r="F82" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G82" s="8">
+      <c r="G82" s="6">
         <v>160</v>
       </c>
-      <c r="H82" s="8">
+      <c r="H82" s="6">
         <v>80</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8">
-        <v>0</v>
-      </c>
-      <c r="L82" s="9" t="s">
+      <c r="J82" s="6"/>
+      <c r="K82" s="6">
+        <v>0</v>
+      </c>
+      <c r="L82" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="M82" s="9"/>
+      <c r="M82" s="7"/>
     </row>
     <row r="83" s="1" customFormat="1" spans="2:13">
-      <c r="B83" s="8">
+      <c r="B83" s="6">
         <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="6">
         <v>0.2</v>
       </c>
-      <c r="E83" s="8" t="s">
+      <c r="E83" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="F83" s="8" t="s">
+      <c r="F83" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="G83" s="8">
+      <c r="G83" s="6">
         <v>160</v>
       </c>
-      <c r="H83" s="8">
+      <c r="H83" s="6">
         <v>80</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8">
-        <v>0</v>
-      </c>
-      <c r="L83" s="9" t="s">
+      <c r="J83" s="6"/>
+      <c r="K83" s="6">
+        <v>0</v>
+      </c>
+      <c r="L83" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="M83" s="9"/>
+      <c r="M83" s="7"/>
     </row>
     <row r="84" s="1" customFormat="1" spans="2:13">
-      <c r="B84" s="8">
+      <c r="B84" s="6">
         <v>322</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="6">
         <v>0.2</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="F84" s="8" t="s">
+      <c r="F84" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="6">
         <v>190</v>
       </c>
-      <c r="H84" s="8">
+      <c r="H84" s="6">
         <v>95</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8">
-        <v>0</v>
-      </c>
-      <c r="L84" s="9" t="s">
+      <c r="J84" s="6"/>
+      <c r="K84" s="6">
+        <v>0</v>
+      </c>
+      <c r="L84" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="M84" s="9"/>
-    </row>
-    <row r="85" s="2" customFormat="1" spans="2:13">
-      <c r="B85" s="10">
+      <c r="M84" s="7"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="2:13">
+      <c r="B85" s="6">
         <v>323</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C85" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85" s="6">
         <v>0.2</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="F85" s="10" t="s">
+      <c r="F85" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="G85" s="10">
+      <c r="G85" s="6">
         <v>175</v>
       </c>
-      <c r="H85" s="10">
+      <c r="H85" s="6">
         <v>87</v>
       </c>
-      <c r="I85" s="2" t="s">
+      <c r="I85" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="J85" s="10"/>
-      <c r="K85" s="10">
-        <v>0</v>
-      </c>
-      <c r="L85" s="11" t="s">
+      <c r="J85" s="6"/>
+      <c r="K85" s="6">
+        <v>0</v>
+      </c>
+      <c r="L85" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="M85" s="11"/>
+      <c r="M85" s="7"/>
     </row>
     <row r="86" s="1" customFormat="1" spans="2:13">
-      <c r="B86" s="8">
+      <c r="B86" s="6">
         <v>324</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="6">
         <v>0.2</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="F86" s="8" t="s">
+      <c r="F86" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G86" s="8">
+      <c r="G86" s="6">
         <v>270</v>
       </c>
-      <c r="H86" s="8">
+      <c r="H86" s="6">
         <v>135</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="J86" s="10">
+      <c r="J86" s="6">
         <v>10502</v>
       </c>
-      <c r="K86" s="8">
-        <v>0</v>
-      </c>
-      <c r="L86" s="9" t="s">
+      <c r="K86" s="6">
+        <v>0</v>
+      </c>
+      <c r="L86" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="M86" s="9"/>
-    </row>
-    <row r="87" s="2" customFormat="1" spans="2:13">
-      <c r="B87" s="10">
+      <c r="M86" s="7"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="2:13">
+      <c r="B87" s="6">
         <v>325</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D87" s="10">
+      <c r="D87" s="6">
         <v>0.2</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="G87" s="10">
+      <c r="G87" s="6">
         <v>160</v>
       </c>
-      <c r="H87" s="10">
+      <c r="H87" s="6">
         <v>80</v>
       </c>
-      <c r="I87" s="2" t="s">
+      <c r="I87" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="J87" s="10"/>
-      <c r="K87" s="10">
+      <c r="J87" s="6"/>
+      <c r="K87" s="6">
         <v>2</v>
       </c>
-      <c r="L87" s="11" t="s">
+      <c r="L87" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="M87" s="11"/>
-    </row>
-    <row r="88" s="2" customFormat="1" spans="2:13">
-      <c r="B88" s="10">
+      <c r="M87" s="7"/>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="2:13">
+      <c r="B88" s="6">
         <v>326</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D88" s="10">
+      <c r="D88" s="6">
         <v>0.2</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="G88" s="10">
+      <c r="G88" s="6">
         <v>200</v>
       </c>
-      <c r="H88" s="10">
+      <c r="H88" s="6">
         <v>100</v>
       </c>
-      <c r="I88" s="2" t="s">
+      <c r="I88" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="J88" s="10">
+      <c r="J88" s="6">
         <v>10901</v>
       </c>
-      <c r="K88" s="10">
+      <c r="K88" s="6">
         <v>2</v>
       </c>
-      <c r="L88" s="11" t="s">
+      <c r="L88" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="M88" s="11"/>
-    </row>
-    <row r="89" s="2" customFormat="1" spans="2:13">
-      <c r="B89" s="10">
+      <c r="M88" s="7"/>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="2:13">
+      <c r="B89" s="6">
         <v>327</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D89" s="10">
+      <c r="D89" s="6">
         <v>0.2</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="G89" s="10">
+      <c r="G89" s="6">
         <v>170</v>
       </c>
-      <c r="H89" s="10">
+      <c r="H89" s="6">
         <v>85</v>
       </c>
-      <c r="I89" s="2" t="s">
+      <c r="I89" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="J89" s="10"/>
-      <c r="K89" s="10">
+      <c r="J89" s="6"/>
+      <c r="K89" s="6">
         <v>1</v>
       </c>
-      <c r="L89" s="11" t="s">
+      <c r="L89" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="M89" s="11"/>
+      <c r="M89" s="7"/>
     </row>
     <row r="90" s="1" customFormat="1" spans="2:13">
-      <c r="B90" s="8">
+      <c r="B90" s="6">
         <v>328</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="6">
         <v>0.2</v>
       </c>
-      <c r="E90" s="9" t="s">
+      <c r="E90" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="F90" s="9" t="s">
+      <c r="F90" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="G90" s="8">
+      <c r="G90" s="6">
         <v>160</v>
       </c>
-      <c r="H90" s="8">
+      <c r="H90" s="6">
         <v>80</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8">
+      <c r="J90" s="6"/>
+      <c r="K90" s="6">
         <v>1</v>
       </c>
-      <c r="L90" s="9" t="s">
+      <c r="L90" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="M90" s="9"/>
+      <c r="M90" s="7"/>
     </row>
     <row r="91" s="1" customFormat="1" spans="2:13">
-      <c r="B91" s="8">
+      <c r="B91" s="6">
         <v>329</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C91" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="6">
         <v>0.2</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F91" s="9" t="s">
+      <c r="F91" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="G91" s="8">
+      <c r="G91" s="6">
         <v>200</v>
       </c>
-      <c r="H91" s="8">
+      <c r="H91" s="6">
         <v>100</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J91" s="13">
+      <c r="J91" s="9">
         <v>11005</v>
       </c>
-      <c r="K91" s="8">
-        <v>0</v>
-      </c>
-      <c r="L91" s="9" t="s">
+      <c r="K91" s="6">
+        <v>0</v>
+      </c>
+      <c r="L91" s="7" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:13">
-      <c r="B92" s="8">
+      <c r="B92" s="6">
         <v>330</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="6">
         <v>0.2</v>
       </c>
-      <c r="E92" s="9" t="s">
+      <c r="E92" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="F92" s="8" t="s">
+      <c r="F92" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="G92" s="8">
+      <c r="G92" s="6">
         <v>300</v>
       </c>
-      <c r="H92" s="8">
+      <c r="H92" s="6">
         <v>150</v>
       </c>
-      <c r="I92" s="8">
+      <c r="I92" s="6">
         <v>40025</v>
       </c>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8">
-        <v>0</v>
-      </c>
-      <c r="L92" s="8" t="s">
+      <c r="J92" s="6"/>
+      <c r="K92" s="6">
+        <v>0</v>
+      </c>
+      <c r="L92" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="M92" s="9"/>
+      <c r="M92" s="7"/>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:13">
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
     </row>
     <row r="94" s="1" customFormat="1" spans="2:13">
       <c r="B94" s="1" t="s">
@@ -5839,31 +5821,31 @@
       <c r="C94" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="6">
         <v>0.1</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E94" s="6">
         <v>235</v>
       </c>
-      <c r="F94" s="8" t="s">
+      <c r="F94" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="G94" s="8">
+      <c r="G94" s="6">
         <v>650</v>
       </c>
-      <c r="H94" s="8">
+      <c r="H94" s="6">
         <v>325</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="J94" s="8">
+      <c r="J94" s="6">
         <v>11001</v>
       </c>
-      <c r="K94" s="8">
-        <v>0</v>
-      </c>
-      <c r="L94" s="9" t="s">
+      <c r="K94" s="6">
+        <v>0</v>
+      </c>
+      <c r="L94" s="7" t="s">
         <v>413</v>
       </c>
     </row>
@@ -5874,29 +5856,29 @@
       <c r="C95" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="6">
         <v>0.1</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="E95" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="F95" s="8" t="s">
+      <c r="F95" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G95" s="8">
+      <c r="G95" s="6">
         <v>680</v>
       </c>
-      <c r="H95" s="8">
+      <c r="H95" s="6">
         <v>340</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8">
-        <v>0</v>
-      </c>
-      <c r="L95" s="9" t="s">
+      <c r="J95" s="6"/>
+      <c r="K95" s="6">
+        <v>0</v>
+      </c>
+      <c r="L95" s="7" t="s">
         <v>418</v>
       </c>
     </row>
@@ -5907,63 +5889,63 @@
       <c r="C96" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="6">
         <v>0.1</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="E96" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="F96" s="8" t="s">
+      <c r="F96" s="6" t="s">
         <v>421</v>
       </c>
-      <c r="G96" s="8">
+      <c r="G96" s="6">
         <v>600</v>
       </c>
-      <c r="H96" s="8">
+      <c r="H96" s="6">
         <v>300</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="K96" s="8">
-        <v>0</v>
-      </c>
-      <c r="L96" s="8" t="s">
+      <c r="K96" s="6">
+        <v>0</v>
+      </c>
+      <c r="L96" s="6" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="97" s="2" customFormat="1" spans="2:13">
-      <c r="B97" s="2" t="s">
+    <row r="97" s="1" customFormat="1" spans="2:13">
+      <c r="B97" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D97" s="10">
+      <c r="D97" s="6">
         <v>0.1</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="F97" s="10" t="s">
+      <c r="F97" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="G97" s="10">
+      <c r="G97" s="6">
         <v>480</v>
       </c>
-      <c r="H97" s="10">
+      <c r="H97" s="6">
         <v>240</v>
       </c>
-      <c r="I97" s="2" t="s">
+      <c r="I97" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="J97" s="10">
+      <c r="J97" s="6">
         <v>11002</v>
       </c>
-      <c r="K97" s="10">
-        <v>0</v>
-      </c>
-      <c r="L97" s="11" t="s">
+      <c r="K97" s="6">
+        <v>0</v>
+      </c>
+      <c r="L97" s="7" t="s">
         <v>428</v>
       </c>
     </row>
@@ -5974,29 +5956,29 @@
       <c r="C98" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="6">
         <v>0.1</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="F98" s="8" t="s">
+      <c r="F98" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="G98" s="8">
+      <c r="G98" s="6">
         <v>460</v>
       </c>
-      <c r="H98" s="8">
+      <c r="H98" s="6">
         <v>230</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8">
-        <v>0</v>
-      </c>
-      <c r="L98" s="9" t="s">
+      <c r="J98" s="6"/>
+      <c r="K98" s="6">
+        <v>0</v>
+      </c>
+      <c r="L98" s="7" t="s">
         <v>433</v>
       </c>
     </row>
@@ -6007,63 +5989,63 @@
       <c r="C99" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="6">
         <v>0.1</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E99" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="F99" s="8" t="s">
+      <c r="F99" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="G99" s="8">
+      <c r="G99" s="6">
         <v>320</v>
       </c>
-      <c r="H99" s="8">
+      <c r="H99" s="6">
         <v>160</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="K99" s="8">
-        <v>0</v>
-      </c>
-      <c r="L99" s="9" t="s">
+      <c r="K99" s="6">
+        <v>0</v>
+      </c>
+      <c r="L99" s="7" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="100" s="2" customFormat="1" spans="2:13">
-      <c r="B100" s="2" t="s">
+    <row r="100" s="1" customFormat="1" spans="2:13">
+      <c r="B100" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="C100" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D100" s="10">
+      <c r="D100" s="6">
         <v>0.1</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="E100" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="F100" s="10" t="s">
+      <c r="F100" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="G100" s="10">
+      <c r="G100" s="6">
         <v>380</v>
       </c>
-      <c r="H100" s="10">
+      <c r="H100" s="6">
         <v>190</v>
       </c>
-      <c r="I100" s="2" t="s">
+      <c r="I100" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="J100" s="10">
+      <c r="J100" s="6">
         <v>11003</v>
       </c>
-      <c r="K100" s="10">
-        <v>0</v>
-      </c>
-      <c r="L100" s="11" t="s">
+      <c r="K100" s="6">
+        <v>0</v>
+      </c>
+      <c r="L100" s="7" t="s">
         <v>443</v>
       </c>
     </row>
@@ -6074,29 +6056,29 @@
       <c r="C101" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="6">
         <v>0.1</v>
       </c>
-      <c r="E101" s="8" t="s">
+      <c r="E101" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="F101" s="8" t="s">
+      <c r="F101" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="G101" s="8">
+      <c r="G101" s="6">
         <v>600</v>
       </c>
-      <c r="H101" s="8">
+      <c r="H101" s="6">
         <v>300</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8">
-        <v>0</v>
-      </c>
-      <c r="L101" s="8" t="s">
+      <c r="J101" s="6"/>
+      <c r="K101" s="6">
+        <v>0</v>
+      </c>
+      <c r="L101" s="6" t="s">
         <v>448</v>
       </c>
     </row>
@@ -6107,60 +6089,60 @@
       <c r="C102" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="6">
         <v>0.1</v>
       </c>
-      <c r="E102" s="8" t="s">
+      <c r="E102" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="F102" s="8" t="s">
+      <c r="F102" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="G102" s="8">
+      <c r="G102" s="6">
         <v>280</v>
       </c>
-      <c r="H102" s="8">
+      <c r="H102" s="6">
         <v>140</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="K102" s="8">
-        <v>0</v>
-      </c>
-      <c r="L102" s="9" t="s">
+      <c r="K102" s="6">
+        <v>0</v>
+      </c>
+      <c r="L102" s="7" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="103" s="2" customFormat="1" spans="2:13">
-      <c r="B103" s="2" t="s">
+    <row r="103" s="1" customFormat="1" spans="2:13">
+      <c r="B103" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C103" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D103" s="10">
+      <c r="D103" s="6">
         <v>0.1</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="E103" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="F103" s="10" t="s">
+      <c r="F103" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="G103" s="10">
+      <c r="G103" s="6">
         <v>300</v>
       </c>
-      <c r="H103" s="10">
+      <c r="H103" s="6">
         <v>150</v>
       </c>
-      <c r="I103" s="2" t="s">
+      <c r="I103" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="K103" s="10">
-        <v>0</v>
-      </c>
-      <c r="L103" s="11" t="s">
+      <c r="K103" s="6">
+        <v>0</v>
+      </c>
+      <c r="L103" s="7" t="s">
         <v>458</v>
       </c>
     </row>
@@ -6171,68 +6153,68 @@
       <c r="C104" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D104" s="6">
         <v>0.1</v>
       </c>
-      <c r="E104" s="8" t="s">
+      <c r="E104" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="F104" s="8" t="s">
+      <c r="F104" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="G104" s="8">
+      <c r="G104" s="6">
         <v>400</v>
       </c>
-      <c r="H104" s="8">
+      <c r="H104" s="6">
         <v>200</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="J104" s="10">
+      <c r="J104" s="6">
         <v>11004</v>
       </c>
-      <c r="K104" s="8">
-        <v>0</v>
-      </c>
-      <c r="L104" s="9" t="s">
+      <c r="K104" s="6">
+        <v>0</v>
+      </c>
+      <c r="L104" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="M104" s="9"/>
-    </row>
-    <row r="105" s="2" customFormat="1" spans="2:13">
-      <c r="B105" s="2" t="s">
+      <c r="M104" s="7"/>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="2:13">
+      <c r="B105" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="C105" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D105" s="10">
+      <c r="D105" s="6">
         <v>0.1</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="F105" s="10" t="s">
+      <c r="F105" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="G105" s="10">
+      <c r="G105" s="6">
         <v>460</v>
       </c>
-      <c r="H105" s="10">
+      <c r="H105" s="6">
         <v>230</v>
       </c>
-      <c r="I105" s="2" t="s">
+      <c r="I105" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="J105" s="10"/>
-      <c r="K105" s="10">
-        <v>0</v>
-      </c>
-      <c r="L105" s="11" t="s">
+      <c r="J105" s="6"/>
+      <c r="K105" s="6">
+        <v>0</v>
+      </c>
+      <c r="L105" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="M105" s="11"/>
+      <c r="M105" s="7"/>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:13">
       <c r="B106" s="1" t="s">
@@ -6241,34 +6223,34 @@
       <c r="C106" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="6">
         <v>0.1</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F106" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="G106" s="8">
+      <c r="G106" s="6">
         <v>220</v>
       </c>
-      <c r="H106" s="8">
+      <c r="H106" s="6">
         <v>110</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="J106" s="8">
+      <c r="J106" s="6">
         <v>10602</v>
       </c>
-      <c r="K106" s="8">
-        <v>0</v>
-      </c>
-      <c r="L106" s="9" t="s">
+      <c r="K106" s="6">
+        <v>0</v>
+      </c>
+      <c r="L106" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="M106" s="9"/>
+      <c r="M106" s="7"/>
     </row>
     <row r="107" s="1" customFormat="1" spans="2:13">
       <c r="B107" s="1" t="s">
@@ -6277,32 +6259,32 @@
       <c r="C107" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="6">
         <v>0.1</v>
       </c>
-      <c r="E107" s="8" t="s">
+      <c r="E107" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="F107" s="8" t="s">
+      <c r="F107" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="G107" s="8">
+      <c r="G107" s="6">
         <v>280</v>
       </c>
-      <c r="H107" s="8">
+      <c r="H107" s="6">
         <v>140</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8">
-        <v>0</v>
-      </c>
-      <c r="L107" s="9" t="s">
+      <c r="J107" s="6"/>
+      <c r="K107" s="6">
+        <v>0</v>
+      </c>
+      <c r="L107" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="M107" s="9"/>
+      <c r="M107" s="7"/>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:13">
       <c r="B108" s="1" t="s">
@@ -6311,32 +6293,32 @@
       <c r="C108" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="6">
         <v>0.1</v>
       </c>
-      <c r="E108" s="9" t="s">
+      <c r="E108" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="F108" s="8" t="s">
+      <c r="F108" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="G108" s="8">
+      <c r="G108" s="6">
         <v>600</v>
       </c>
-      <c r="H108" s="8">
+      <c r="H108" s="6">
         <v>300</v>
       </c>
-      <c r="I108" s="8" t="s">
+      <c r="I108" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8">
-        <v>0</v>
-      </c>
-      <c r="L108" s="9" t="s">
+      <c r="J108" s="6"/>
+      <c r="K108" s="6">
+        <v>0</v>
+      </c>
+      <c r="L108" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="M108" s="9"/>
+      <c r="M108" s="7"/>
     </row>
     <row r="109" s="1" customFormat="1" spans="2:13">
       <c r="B109" s="1" t="s">
@@ -6345,34 +6327,34 @@
       <c r="C109" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="6">
         <v>0.1</v>
       </c>
-      <c r="E109" s="9" t="s">
+      <c r="E109" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="G109" s="8">
+      <c r="G109" s="6">
         <v>280</v>
       </c>
-      <c r="H109" s="8">
+      <c r="H109" s="6">
         <v>140</v>
       </c>
-      <c r="I109" s="8">
+      <c r="I109" s="6">
         <v>40016</v>
       </c>
-      <c r="J109" s="10">
+      <c r="J109" s="6">
         <v>10101</v>
       </c>
-      <c r="K109" s="8">
-        <v>0</v>
-      </c>
-      <c r="L109" s="8" t="s">
+      <c r="K109" s="6">
+        <v>0</v>
+      </c>
+      <c r="L109" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="M109" s="9"/>
+      <c r="M109" s="7"/>
     </row>
     <row r="110" s="1" customFormat="1" spans="2:13">
       <c r="B110" s="1" t="s">
@@ -6381,32 +6363,32 @@
       <c r="C110" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="6">
         <v>0.1</v>
       </c>
-      <c r="E110" s="9" t="s">
+      <c r="E110" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="F110" s="8" t="s">
+      <c r="F110" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="G110" s="8">
+      <c r="G110" s="6">
         <v>300</v>
       </c>
-      <c r="H110" s="8">
+      <c r="H110" s="6">
         <v>150</v>
       </c>
-      <c r="I110" s="8">
+      <c r="I110" s="6">
         <v>40017</v>
       </c>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8">
-        <v>0</v>
-      </c>
-      <c r="L110" s="9" t="s">
+      <c r="J110" s="6"/>
+      <c r="K110" s="6">
+        <v>0</v>
+      </c>
+      <c r="L110" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="M110" s="9"/>
+      <c r="M110" s="7"/>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:13">
       <c r="B111" s="1" t="s">
@@ -6415,34 +6397,34 @@
       <c r="C111" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="6">
         <v>0.1</v>
       </c>
-      <c r="E111" s="9" t="s">
+      <c r="E111" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="F111" s="8" t="s">
+      <c r="F111" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="G111" s="8">
+      <c r="G111" s="6">
         <v>520</v>
       </c>
-      <c r="H111" s="8">
+      <c r="H111" s="6">
         <v>260</v>
       </c>
-      <c r="I111" s="8">
+      <c r="I111" s="6">
         <v>40018</v>
       </c>
-      <c r="J111" s="10">
+      <c r="J111" s="6">
         <v>11101</v>
       </c>
-      <c r="K111" s="8">
-        <v>0</v>
-      </c>
-      <c r="L111" s="9" t="s">
+      <c r="K111" s="6">
+        <v>0</v>
+      </c>
+      <c r="L111" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="M111" s="9"/>
+      <c r="M111" s="7"/>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:13">
       <c r="B112" s="1" t="s">
@@ -6451,32 +6433,32 @@
       <c r="C112" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="6">
         <v>0.1</v>
       </c>
-      <c r="E112" s="9" t="s">
+      <c r="E112" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="F112" s="8" t="s">
+      <c r="F112" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="G112" s="8">
+      <c r="G112" s="6">
         <v>300</v>
       </c>
-      <c r="H112" s="8">
+      <c r="H112" s="6">
         <v>150</v>
       </c>
-      <c r="I112" s="8">
+      <c r="I112" s="6">
         <v>40019</v>
       </c>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8">
-        <v>0</v>
-      </c>
-      <c r="L112" s="9" t="s">
+      <c r="J112" s="6"/>
+      <c r="K112" s="6">
+        <v>0</v>
+      </c>
+      <c r="L112" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="M112" s="9"/>
+      <c r="M112" s="7"/>
     </row>
     <row r="113" s="1" customFormat="1" spans="1:13">
       <c r="B113" s="1" t="s">
@@ -6485,32 +6467,32 @@
       <c r="C113" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="6">
         <v>0.1</v>
       </c>
-      <c r="E113" s="9" t="s">
+      <c r="E113" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="F113" s="8" t="s">
+      <c r="F113" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="G113" s="8">
+      <c r="G113" s="6">
         <v>620</v>
       </c>
-      <c r="H113" s="8">
+      <c r="H113" s="6">
         <v>310</v>
       </c>
-      <c r="I113" s="8">
+      <c r="I113" s="6">
         <v>40021</v>
       </c>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8">
-        <v>0</v>
-      </c>
-      <c r="L113" s="9" t="s">
+      <c r="J113" s="6"/>
+      <c r="K113" s="6">
+        <v>0</v>
+      </c>
+      <c r="L113" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="M113" s="9"/>
+      <c r="M113" s="7"/>
     </row>
     <row r="114" s="1" customFormat="1" spans="1:13">
       <c r="B114" s="1" t="s">
@@ -6519,70 +6501,70 @@
       <c r="C114" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="6">
         <v>0.1</v>
       </c>
-      <c r="E114" s="9" t="s">
+      <c r="E114" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="F114" s="8" t="s">
+      <c r="F114" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="G114" s="8">
+      <c r="G114" s="6">
         <v>320</v>
       </c>
-      <c r="H114" s="8">
+      <c r="H114" s="6">
         <v>160</v>
       </c>
-      <c r="I114" s="8" t="s">
+      <c r="I114" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="J114" s="10">
+      <c r="J114" s="6">
         <v>11201</v>
       </c>
-      <c r="K114" s="8">
-        <v>0</v>
-      </c>
-      <c r="L114" s="9" t="s">
+      <c r="K114" s="6">
+        <v>0</v>
+      </c>
+      <c r="L114" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="M114" s="9"/>
-    </row>
-    <row r="115" s="2" customFormat="1" spans="1:13">
-      <c r="B115" s="2" t="s">
+      <c r="M114" s="7"/>
+    </row>
+    <row r="115" s="1" customFormat="1" spans="1:13">
+      <c r="B115" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C115" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D115" s="10">
+      <c r="D115" s="6">
         <v>0.1</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="F115" s="10" t="s">
+      <c r="F115" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="G115" s="10">
+      <c r="G115" s="6">
         <v>320</v>
       </c>
-      <c r="H115" s="10">
+      <c r="H115" s="6">
         <v>160</v>
       </c>
-      <c r="I115" s="10">
+      <c r="I115" s="6">
         <v>40023</v>
       </c>
-      <c r="J115" s="10">
+      <c r="J115" s="6">
         <v>11301</v>
       </c>
-      <c r="K115" s="10">
-        <v>0</v>
-      </c>
-      <c r="L115" s="11" t="s">
+      <c r="K115" s="6">
+        <v>0</v>
+      </c>
+      <c r="L115" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="M115" s="11"/>
+      <c r="M115" s="7"/>
     </row>
     <row r="116" s="1" customFormat="1" spans="1:13">
       <c r="B116" s="1" t="s">
@@ -6591,264 +6573,264 @@
       <c r="C116" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D116" s="6">
         <v>0.1</v>
       </c>
-      <c r="E116" s="9" t="s">
+      <c r="E116" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="F116" s="8" t="s">
+      <c r="F116" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="G116" s="8">
+      <c r="G116" s="6">
         <v>550</v>
       </c>
-      <c r="H116" s="8">
+      <c r="H116" s="6">
         <v>275</v>
       </c>
-      <c r="I116" s="8">
+      <c r="I116" s="6">
         <v>40024</v>
       </c>
-      <c r="J116" s="10">
+      <c r="J116" s="6">
         <v>11401</v>
       </c>
-      <c r="K116" s="8">
-        <v>0</v>
-      </c>
-      <c r="L116" s="8" t="s">
+      <c r="K116" s="6">
+        <v>0</v>
+      </c>
+      <c r="L116" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="M116" s="9"/>
-    </row>
-    <row r="117" s="2" customFormat="1" spans="1:13">
+      <c r="M116" s="7"/>
+    </row>
+    <row r="117" s="1" customFormat="1" spans="1:13">
       <c r="B117" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D117" s="10">
+      <c r="D117" s="6">
         <v>0.1</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E117" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="F117" s="11" t="s">
+      <c r="F117" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="G117" s="10">
+      <c r="G117" s="6">
         <v>400</v>
       </c>
-      <c r="H117" s="10">
+      <c r="H117" s="6">
         <v>200</v>
       </c>
-      <c r="I117" s="10">
+      <c r="I117" s="6">
         <v>40026</v>
       </c>
-      <c r="J117" s="10">
+      <c r="J117" s="6">
         <v>11501</v>
       </c>
-      <c r="K117" s="10">
+      <c r="K117" s="6">
         <v>1</v>
       </c>
-      <c r="L117" s="11" t="s">
+      <c r="L117" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="M117" s="11"/>
+      <c r="M117" s="7"/>
     </row>
     <row r="118" s="1" customFormat="1" spans="1:13">
       <c r="B118" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C118" s="9" t="s">
+      <c r="C118" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D118" s="6">
         <v>0.1</v>
       </c>
-      <c r="E118" s="9" t="s">
+      <c r="E118" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="F118" s="9" t="s">
+      <c r="F118" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="G118" s="8">
+      <c r="G118" s="6">
         <v>330</v>
       </c>
-      <c r="H118" s="8">
+      <c r="H118" s="6">
         <v>165</v>
       </c>
-      <c r="I118" s="8">
+      <c r="I118" s="6">
         <v>40027</v>
       </c>
-      <c r="J118" s="8"/>
-      <c r="K118" s="8">
+      <c r="J118" s="6"/>
+      <c r="K118" s="6">
         <v>1</v>
       </c>
-      <c r="L118" s="9" t="s">
+      <c r="L118" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="M118" s="9"/>
-    </row>
-    <row r="119" s="2" customFormat="1" spans="1:13">
+      <c r="M118" s="7"/>
+    </row>
+    <row r="119" s="1" customFormat="1" spans="1:13">
       <c r="B119" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D119" s="10">
+      <c r="D119" s="6">
         <v>0.1</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="F119" s="11" t="s">
+      <c r="F119" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="G119" s="10">
+      <c r="G119" s="6">
         <v>260</v>
       </c>
-      <c r="H119" s="10">
+      <c r="H119" s="6">
         <v>130</v>
       </c>
-      <c r="I119" s="10">
+      <c r="I119" s="6">
         <v>40028</v>
       </c>
-      <c r="J119" s="10"/>
-      <c r="K119" s="10">
+      <c r="J119" s="6"/>
+      <c r="K119" s="6">
         <v>2</v>
       </c>
-      <c r="L119" s="11" t="s">
+      <c r="L119" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="M119" s="11"/>
-    </row>
-    <row r="120" s="2" customFormat="1" spans="1:13">
+      <c r="M119" s="7"/>
+    </row>
+    <row r="120" s="1" customFormat="1" spans="1:13">
       <c r="B120" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D120" s="10">
+      <c r="D120" s="6">
         <v>0.1</v>
       </c>
-      <c r="E120" s="11" t="s">
+      <c r="E120" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="F120" s="11" t="s">
+      <c r="F120" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="G120" s="10">
+      <c r="G120" s="6">
         <v>270</v>
       </c>
-      <c r="H120" s="10">
+      <c r="H120" s="6">
         <v>135</v>
       </c>
-      <c r="I120" s="10">
+      <c r="I120" s="6">
         <v>40029</v>
       </c>
-      <c r="J120" s="10"/>
-      <c r="K120" s="10">
+      <c r="J120" s="6"/>
+      <c r="K120" s="6">
         <v>2</v>
       </c>
-      <c r="L120" s="11" t="s">
+      <c r="L120" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="M120" s="11"/>
-    </row>
-    <row r="121" s="2" customFormat="1" spans="1:13">
+      <c r="M120" s="7"/>
+    </row>
+    <row r="121" s="1" customFormat="1" spans="1:13">
       <c r="B121" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C121" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D121" s="10">
+      <c r="D121" s="6">
         <v>0.1</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E121" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="F121" s="11" t="s">
+      <c r="F121" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="G121" s="10">
+      <c r="G121" s="6">
         <v>280</v>
       </c>
-      <c r="H121" s="10">
+      <c r="H121" s="6">
         <v>140</v>
       </c>
-      <c r="I121" s="10">
+      <c r="I121" s="6">
         <v>40030</v>
       </c>
-      <c r="J121" s="10">
+      <c r="J121" s="6">
         <v>11601</v>
       </c>
-      <c r="K121" s="10">
-        <v>0</v>
-      </c>
-      <c r="L121" s="11" t="s">
+      <c r="K121" s="6">
+        <v>0</v>
+      </c>
+      <c r="L121" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="M121" s="11"/>
-    </row>
-    <row r="122" s="2" customFormat="1" spans="1:13">
-      <c r="A122" s="11"/>
+      <c r="M121" s="7"/>
+    </row>
+    <row r="122" s="1" customFormat="1" spans="1:13">
+      <c r="A122" s="7"/>
       <c r="B122" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D122" s="10">
+      <c r="D122" s="6">
         <v>0.1</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="E122" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="F122" s="10" t="s">
+      <c r="F122" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="G122" s="2">
+      <c r="G122" s="1">
         <v>320</v>
       </c>
-      <c r="H122" s="2">
+      <c r="H122" s="1">
         <v>160</v>
       </c>
-      <c r="I122" s="10">
+      <c r="I122" s="6">
         <v>40031</v>
       </c>
-      <c r="J122" s="10"/>
-      <c r="K122" s="10">
-        <v>0</v>
-      </c>
-      <c r="L122" s="11" t="s">
+      <c r="J122" s="6"/>
+      <c r="K122" s="6">
+        <v>0</v>
+      </c>
+      <c r="L122" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="M122" s="11"/>
+      <c r="M122" s="7"/>
     </row>
     <row r="123" s="1" customFormat="1" spans="1:13">
       <c r="B123" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="C123" s="9" t="s">
+      <c r="C123" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D123" s="8">
+      <c r="D123" s="6">
         <v>0.1</v>
       </c>
-      <c r="E123" s="9" t="s">
+      <c r="E123" s="7" t="s">
         <v>542</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="G123" s="8">
+      <c r="G123" s="6">
         <v>500</v>
       </c>
-      <c r="H123" s="8">
+      <c r="H123" s="6">
         <v>250</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -6857,7 +6839,7 @@
       <c r="K123" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="L123" s="9" t="s">
+      <c r="L123" s="7" t="s">
         <v>546</v>
       </c>
     </row>
@@ -6865,22 +6847,22 @@
       <c r="B124" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C124" s="9" t="s">
+      <c r="C124" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D124" s="6">
         <v>0.1</v>
       </c>
-      <c r="E124" s="9" t="s">
+      <c r="E124" s="7" t="s">
         <v>548</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="G124" s="8">
+      <c r="G124" s="6">
         <v>500</v>
       </c>
-      <c r="H124" s="8">
+      <c r="H124" s="6">
         <v>250</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -6889,7 +6871,7 @@
       <c r="K124" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="L124" s="9" t="s">
+      <c r="L124" s="7" t="s">
         <v>551</v>
       </c>
     </row>
@@ -6897,190 +6879,190 @@
       <c r="B125" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="6">
         <v>0.1</v>
       </c>
-      <c r="E125" s="8" t="s">
+      <c r="E125" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="F125" s="8" t="s">
+      <c r="F125" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="G125" s="8">
+      <c r="G125" s="6">
         <v>500</v>
       </c>
-      <c r="H125" s="8">
+      <c r="H125" s="6">
         <v>250</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="J125" s="8"/>
-      <c r="K125" s="8">
-        <v>0</v>
-      </c>
-      <c r="L125" s="9" t="s">
+      <c r="J125" s="6"/>
+      <c r="K125" s="6">
+        <v>0</v>
+      </c>
+      <c r="L125" s="7" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" spans="1:13">
-      <c r="C126" s="16"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="8"/>
-      <c r="G126" s="8"/>
-      <c r="H126" s="8"/>
-      <c r="I126" s="8"/>
-      <c r="J126" s="8"/>
+      <c r="C126" s="10"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
+      <c r="F126" s="6"/>
+      <c r="G126" s="6"/>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
       <c r="K126" s="1"/>
-      <c r="L126" s="8"/>
-      <c r="M126" s="9"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="7"/>
     </row>
     <row r="127" s="1" customFormat="1" spans="1:13">
-      <c r="C127" s="16"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="8"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="8"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="8"/>
+      <c r="C127" s="10"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
+      <c r="F127" s="6"/>
+      <c r="G127" s="6"/>
+      <c r="H127" s="6"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="6"/>
       <c r="K127" s="1"/>
-      <c r="L127" s="8"/>
-      <c r="M127" s="9"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="7"/>
     </row>
     <row r="128" s="1" customFormat="1" spans="1:13">
-      <c r="C128" s="16"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8"/>
-      <c r="H128" s="8"/>
-      <c r="I128" s="8"/>
-      <c r="J128" s="8"/>
+      <c r="C128" s="10"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="6"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="6"/>
       <c r="K128" s="1"/>
-      <c r="L128" s="8"/>
-      <c r="M128" s="9"/>
+      <c r="L128" s="6"/>
+      <c r="M128" s="7"/>
     </row>
     <row r="129" s="1" customFormat="1" spans="3:13">
-      <c r="C129" s="16"/>
-      <c r="D129" s="8"/>
-      <c r="E129" s="8"/>
-      <c r="F129" s="8"/>
-      <c r="G129" s="8"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="8"/>
-      <c r="J129" s="8"/>
+      <c r="C129" s="10"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="6"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="6"/>
       <c r="K129" s="1"/>
-      <c r="L129" s="8"/>
-      <c r="M129" s="9"/>
+      <c r="L129" s="6"/>
+      <c r="M129" s="7"/>
     </row>
     <row r="130" s="1" customFormat="1" spans="3:13">
-      <c r="C130" s="16"/>
-      <c r="D130" s="8"/>
-      <c r="E130" s="8"/>
-      <c r="F130" s="8"/>
-      <c r="G130" s="8"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="8"/>
-      <c r="J130" s="8"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="6"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="6"/>
       <c r="K130" s="1"/>
-      <c r="L130" s="8"/>
-      <c r="M130" s="9"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="7"/>
     </row>
     <row r="131" s="1" customFormat="1" spans="3:13">
-      <c r="C131" s="16"/>
-      <c r="D131" s="8"/>
-      <c r="E131" s="8"/>
-      <c r="F131" s="8"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="8"/>
-      <c r="I131" s="8"/>
-      <c r="J131" s="8"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
+      <c r="F131" s="6"/>
+      <c r="G131" s="6"/>
+      <c r="H131" s="6"/>
+      <c r="I131" s="6"/>
+      <c r="J131" s="6"/>
       <c r="K131" s="1"/>
-      <c r="L131" s="8"/>
-      <c r="M131" s="9"/>
+      <c r="L131" s="6"/>
+      <c r="M131" s="7"/>
     </row>
     <row r="132" s="1" customFormat="1" spans="3:13">
-      <c r="C132" s="16"/>
-      <c r="D132" s="8"/>
-      <c r="E132" s="8"/>
-      <c r="F132" s="8"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="8"/>
-      <c r="J132" s="8"/>
+      <c r="C132" s="10"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="6"/>
+      <c r="G132" s="6"/>
+      <c r="H132" s="6"/>
+      <c r="I132" s="6"/>
+      <c r="J132" s="6"/>
       <c r="K132" s="1"/>
-      <c r="L132" s="8"/>
-      <c r="M132" s="9"/>
+      <c r="L132" s="6"/>
+      <c r="M132" s="7"/>
     </row>
     <row r="133" s="1" customFormat="1" spans="3:13">
-      <c r="C133" s="16"/>
-      <c r="D133" s="8"/>
-      <c r="E133" s="8"/>
-      <c r="F133" s="8"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="8"/>
-      <c r="I133" s="8"/>
-      <c r="J133" s="8"/>
+      <c r="C133" s="10"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="6"/>
+      <c r="G133" s="6"/>
+      <c r="H133" s="6"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6"/>
       <c r="K133" s="1"/>
-      <c r="L133" s="8"/>
-      <c r="M133" s="9"/>
+      <c r="L133" s="6"/>
+      <c r="M133" s="7"/>
     </row>
     <row r="134" s="1" customFormat="1" spans="3:13">
-      <c r="C134" s="16"/>
-      <c r="D134" s="8"/>
-      <c r="E134" s="8"/>
-      <c r="F134" s="8"/>
-      <c r="G134" s="8"/>
-      <c r="H134" s="8"/>
-      <c r="I134" s="8"/>
-      <c r="J134" s="8"/>
+      <c r="C134" s="10"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="6"/>
+      <c r="G134" s="6"/>
+      <c r="H134" s="6"/>
+      <c r="I134" s="6"/>
+      <c r="J134" s="6"/>
       <c r="K134" s="1"/>
-      <c r="L134" s="8"/>
-      <c r="M134" s="9"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="7"/>
     </row>
     <row r="135" s="1" customFormat="1" spans="3:13">
-      <c r="C135" s="16"/>
-      <c r="D135" s="8"/>
-      <c r="E135" s="8"/>
-      <c r="F135" s="8"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="8"/>
-      <c r="I135" s="8"/>
-      <c r="J135" s="8"/>
+      <c r="C135" s="10"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="6"/>
+      <c r="G135" s="6"/>
+      <c r="H135" s="6"/>
+      <c r="I135" s="6"/>
+      <c r="J135" s="6"/>
       <c r="K135" s="1"/>
-      <c r="L135" s="8"/>
-      <c r="M135" s="9"/>
+      <c r="L135" s="6"/>
+      <c r="M135" s="7"/>
     </row>
     <row r="136" s="1" customFormat="1" spans="3:13">
-      <c r="C136" s="16"/>
-      <c r="D136" s="8"/>
-      <c r="E136" s="8"/>
-      <c r="F136" s="8"/>
-      <c r="G136" s="8"/>
-      <c r="H136" s="8"/>
-      <c r="I136" s="8"/>
-      <c r="J136" s="8"/>
+      <c r="C136" s="10"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="6"/>
+      <c r="H136" s="6"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="6"/>
       <c r="K136" s="1"/>
-      <c r="L136" s="8"/>
-      <c r="M136" s="9"/>
+      <c r="L136" s="6"/>
+      <c r="M136" s="7"/>
     </row>
     <row r="137" s="1" customFormat="1" spans="3:13">
-      <c r="C137" s="16"/>
-      <c r="D137" s="8"/>
-      <c r="E137" s="8"/>
-      <c r="F137" s="8"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="8"/>
-      <c r="I137" s="8"/>
-      <c r="J137" s="8"/>
+      <c r="C137" s="10"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="6"/>
+      <c r="G137" s="6"/>
+      <c r="H137" s="6"/>
+      <c r="I137" s="6"/>
+      <c r="J137" s="6"/>
       <c r="K137" s="1"/>
-      <c r="L137" s="8"/>
-      <c r="M137" s="9"/>
+      <c r="L137" s="6"/>
+      <c r="M137" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="617">
   <si>
     <t>##var</t>
   </si>
@@ -901,6 +901,30 @@
     <t>亮牌时的第三张牌提供其点数对应的攻击力加成</t>
   </si>
   <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>疯狂猴子</t>
+  </si>
+  <si>
+    <t>20036|20037</t>
+  </si>
+  <si>
+    <t>结算时提供+8倍率,但回合结束后有18%的概率摧毁此圣物</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>贪婪</t>
+  </si>
+  <si>
+    <t>20038</t>
+  </si>
+  <si>
+    <t>每次获胜该圣物+1倍率,每次失败该圣物-1倍率</t>
+  </si>
+  <si>
     <t>Epic</t>
   </si>
   <si>
@@ -1261,6 +1285,78 @@
     <t>比牌时,你的牌型与对方牌型每相隔1级,则造成/承受的伤害对应提高/降低20%</t>
   </si>
   <si>
+    <t>倍率叠加</t>
+  </si>
+  <si>
+    <t>30033</t>
+  </si>
+  <si>
+    <t>每使用过1次消耗类的圣物,此圣物就会在结算时永久提供+0.5倍率</t>
+  </si>
+  <si>
+    <t>力量叠加</t>
+  </si>
+  <si>
+    <t>30034</t>
+  </si>
+  <si>
+    <t>每使用过1次消耗类的圣物,此圣物就会永久提供+1攻击力</t>
+  </si>
+  <si>
+    <t>召唤</t>
+  </si>
+  <si>
+    <t>30035</t>
+  </si>
+  <si>
+    <t>如果你亮出的牌型为同花顺,则会随机生成一个消耗性圣物,前提是圣物栏有空位</t>
+  </si>
+  <si>
+    <t>国王领域</t>
+  </si>
+  <si>
+    <t>30036</t>
+  </si>
+  <si>
+    <t>比牌时留在手牌中的每一张K,都会提供+9倍率</t>
+  </si>
+  <si>
+    <t>皇后领域</t>
+  </si>
+  <si>
+    <t>30037</t>
+  </si>
+  <si>
+    <t>比牌时留在手牌中的每一张Q,都会提供+9倍率</t>
+  </si>
+  <si>
+    <t>复制</t>
+  </si>
+  <si>
+    <t>30038</t>
+  </si>
+  <si>
+    <t>每回合随机复制1个你栏位中其他圣物的能力</t>
+  </si>
+  <si>
+    <t>借花献佛</t>
+  </si>
+  <si>
+    <t>30039</t>
+  </si>
+  <si>
+    <t>本关每存在1条关卡机制,你造成的伤害+40%</t>
+  </si>
+  <si>
+    <t>妙手</t>
+  </si>
+  <si>
+    <t>30040</t>
+  </si>
+  <si>
+    <t>使用透视时,随机抽走该敌人1张手牌,与你手中点数最小的1张交换</t>
+  </si>
+  <si>
     <t>401</t>
   </si>
   <si>
@@ -1703,6 +1799,90 @@
   </si>
   <si>
     <t>顺子牌型可以相隔1点组成[例如:2,4,5]</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>高档甜品</t>
+  </si>
+  <si>
+    <t>40032</t>
+  </si>
+  <si>
+    <t>提供+100攻击力,但每次比牌后此效果会-5攻击力</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>第六感</t>
+  </si>
+  <si>
+    <t>40033</t>
+  </si>
+  <si>
+    <t>比牌即使牌型小于对方,也会有10%的概率获胜</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>炸弹恶魔</t>
+  </si>
+  <si>
+    <t>40034</t>
+  </si>
+  <si>
+    <t>每亮出过1次炸弹,该圣物就会在结算时提供+10倍率</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>消费主义</t>
+  </si>
+  <si>
+    <t>40035</t>
+  </si>
+  <si>
+    <t>在商店中每刷新1次,该圣物就会提供+1倍率</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>高档饮品</t>
+  </si>
+  <si>
+    <t>40036</t>
+  </si>
+  <si>
+    <t>提供+20倍率,但每次比牌后此效果会-1倍率</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>幸运之子</t>
+  </si>
+  <si>
+    <t>40037</t>
+  </si>
+  <si>
+    <t>将你持有的圣物中所有关于概率的数字翻倍</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>万能A</t>
+  </si>
+  <si>
+    <t>40038</t>
+  </si>
+  <si>
+    <t>你的A可以当作任意花色与任意点数使用</t>
   </si>
 </sst>
 </file>
@@ -1874,12 +2054,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2200,7 +2386,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -2224,16 +2410,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -2242,118 +2428,117 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2702,11 +2887,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="2.93333333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.8" style="4" customWidth="1"/>
     <col min="4" max="4" width="4.78333333333333" style="5" customWidth="1"/>
     <col min="5" max="5" width="8.8" style="5" customWidth="1"/>
@@ -2715,17 +2900,17 @@
     <col min="8" max="8" width="4.78333333333333" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="5" customWidth="1"/>
     <col min="10" max="10" width="5.53333333333333" style="5" customWidth="1"/>
-    <col min="11" max="11" width="8.03333333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="8.03333333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="7.70833333333333" style="5" customWidth="1"/>
-    <col min="14" max="14" width="34.75" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -2760,10 +2945,10 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
@@ -2798,10 +2983,10 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -2842,32 +3027,32 @@
       <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>0.8</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>45</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>22</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>10001</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7" t="s">
+      <c r="J5" s="5"/>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5"/>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:13">
       <c r="B6" s="1" t="s">
@@ -2876,32 +3061,32 @@
       <c r="C6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>0.8</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>28</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>14</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>10002</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7" t="s">
+      <c r="J6" s="5"/>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="7"/>
+      <c r="M6"/>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:13">
       <c r="B7" s="1" t="s">
@@ -2910,32 +3095,32 @@
       <c r="C7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>0.8</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>28</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>14</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>10003</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="J7" s="5"/>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="7"/>
+      <c r="M7"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:13">
       <c r="B8" s="1" t="s">
@@ -2944,32 +3129,32 @@
       <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>0.8</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>28</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>14</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>10004</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7" t="s">
+      <c r="J8" s="5"/>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="7"/>
+      <c r="M8"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:13">
       <c r="B9" s="1" t="s">
@@ -2978,32 +3163,32 @@
       <c r="C9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>0.8</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>28</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>14</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>10005</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="7" t="s">
+      <c r="J9" s="5"/>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:13">
       <c r="B10" s="1" t="s">
@@ -3012,32 +3197,32 @@
       <c r="C10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>0.8</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>28</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>14</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>10006</v>
       </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="7" t="s">
+      <c r="J10" s="5"/>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" t="s">
         <v>52</v>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:13">
       <c r="B11" s="1" t="s">
@@ -3046,32 +3231,32 @@
       <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>0.8</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>22</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>11</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>10007</v>
       </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="7" t="s">
+      <c r="J11" s="5"/>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11"/>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:13">
       <c r="B12" s="1" t="s">
@@ -3080,32 +3265,32 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>0.8</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>35</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>17</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>10008</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="7" t="s">
+      <c r="J12" s="5"/>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:13">
       <c r="B13" s="1" t="s">
@@ -3114,32 +3299,32 @@
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>0.8</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>16</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>8</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>10009</v>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="7" t="s">
+      <c r="J13" s="5"/>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" t="s">
         <v>64</v>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:13">
       <c r="B14" s="1" t="s">
@@ -3148,32 +3333,32 @@
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>0.8</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>16</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>8</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>10010</v>
       </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="J14" s="5"/>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
         <v>68</v>
       </c>
-      <c r="M14" s="7"/>
+      <c r="M14"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:13">
       <c r="B15" s="1" t="s">
@@ -3182,32 +3367,32 @@
       <c r="C15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>0.8</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>15</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>7</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>10011</v>
       </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="7" t="s">
+      <c r="J15" s="5"/>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
         <v>72</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15"/>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:13">
       <c r="B16" s="1" t="s">
@@ -3216,29 +3401,29 @@
       <c r="C16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>0.8</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>30</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>15</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>10012</v>
       </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7" t="s">
+      <c r="J16" s="5"/>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3249,29 +3434,29 @@
       <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>0.8</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>35</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>17</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>10013</v>
       </c>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="s">
+      <c r="J17" s="5"/>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3282,29 +3467,29 @@
       <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>0.8</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>26</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>13</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>10014</v>
       </c>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6">
-        <v>0</v>
-      </c>
-      <c r="L18" s="7" t="s">
+      <c r="J18" s="5"/>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3315,29 +3500,29 @@
       <c r="C19" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>0.8</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>22</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>11</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>10015</v>
       </c>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6">
-        <v>0</v>
-      </c>
-      <c r="L19" s="7" t="s">
+      <c r="J19" s="5"/>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3348,29 +3533,29 @@
       <c r="C20" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>0.8</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>28</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>14</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>10016</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6">
-        <v>0</v>
-      </c>
-      <c r="L20" s="7" t="s">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3381,29 +3566,29 @@
       <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>0.8</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>20</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>10</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>10017</v>
       </c>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6">
-        <v>0</v>
-      </c>
-      <c r="L21" s="7" t="s">
+      <c r="J21" s="5"/>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3411,149 +3596,149 @@
       <c r="B22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>0.8</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" t="s">
         <v>99</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>25</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>12</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>10018</v>
       </c>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5">
         <v>1</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" t="s">
         <v>100</v>
       </c>
-      <c r="M22" s="7"/>
+      <c r="M22"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:13">
       <c r="B23" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>0.8</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" t="s">
         <v>102</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>25</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>12</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>10019</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6">
+      <c r="J23" s="5"/>
+      <c r="K23" s="5">
         <v>1</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="L23" t="s">
         <v>104</v>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:13">
       <c r="B24" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>0.8</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>30</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>15</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>10020</v>
       </c>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6">
-        <v>0</v>
-      </c>
-      <c r="L24" s="7" t="s">
+      <c r="J24" s="5"/>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" t="s">
         <v>108</v>
       </c>
-      <c r="M24" s="7"/>
+      <c r="M24"/>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:13">
       <c r="B25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>0.8</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" t="s">
         <v>110</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" t="s">
         <v>111</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>35</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>17</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>10021</v>
       </c>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6">
+      <c r="J25" s="5"/>
+      <c r="K25" s="5">
         <v>2</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="L25" t="s">
         <v>112</v>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25"/>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:13">
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="7"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26"/>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
       <c r="B27" s="1" t="s">
@@ -3562,13 +3747,13 @@
       <c r="C27" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>0.4</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>116</v>
       </c>
       <c r="G27" s="1">
@@ -3580,14 +3765,14 @@
       <c r="I27" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6">
-        <v>0</v>
-      </c>
-      <c r="L27" s="7" t="s">
+      <c r="J27" s="5"/>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
         <v>118</v>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27"/>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:13">
       <c r="B28" s="1" t="s">
@@ -3596,13 +3781,13 @@
       <c r="C28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <v>0.4</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="5" t="s">
         <v>121</v>
       </c>
       <c r="G28" s="1">
@@ -3614,30 +3799,30 @@
       <c r="I28" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6">
-        <v>0</v>
-      </c>
-      <c r="L28" s="7" t="s">
+      <c r="J28" s="5"/>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
         <v>123</v>
       </c>
-      <c r="M28" s="7"/>
+      <c r="M28"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
-      <c r="A29" s="7"/>
+      <c r="A29"/>
       <c r="B29" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <v>0.4</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" s="5" t="s">
         <v>126</v>
       </c>
       <c r="G29" s="1">
@@ -3649,30 +3834,30 @@
       <c r="I29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6">
-        <v>0</v>
-      </c>
-      <c r="L29" s="7" t="s">
+      <c r="J29" s="5"/>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
         <v>128</v>
       </c>
-      <c r="M29" s="7"/>
+      <c r="M29"/>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:13">
-      <c r="A30" s="7"/>
+      <c r="A30"/>
       <c r="B30" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <v>0.4</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G30" s="1">
@@ -3684,30 +3869,30 @@
       <c r="I30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6">
-        <v>0</v>
-      </c>
-      <c r="L30" s="7" t="s">
+      <c r="J30" s="5"/>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
         <v>133</v>
       </c>
-      <c r="M30" s="7"/>
+      <c r="M30"/>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:13">
-      <c r="A31" s="7"/>
+      <c r="A31"/>
       <c r="B31" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>0.4</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>136</v>
       </c>
       <c r="G31" s="1">
@@ -3719,30 +3904,30 @@
       <c r="I31" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6">
-        <v>0</v>
-      </c>
-      <c r="L31" s="7" t="s">
+      <c r="J31" s="5"/>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
         <v>138</v>
       </c>
-      <c r="M31" s="7"/>
+      <c r="M31"/>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:13">
-      <c r="A32" s="7"/>
+      <c r="A32"/>
       <c r="B32" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="5">
         <v>0.4</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>141</v>
       </c>
       <c r="G32" s="1">
@@ -3754,30 +3939,30 @@
       <c r="I32" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7" t="s">
+      <c r="J32" s="5"/>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" t="s">
         <v>143</v>
       </c>
-      <c r="M32" s="7"/>
+      <c r="M32"/>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="A33" s="7"/>
+      <c r="A33"/>
       <c r="B33" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>0.4</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>146</v>
       </c>
       <c r="G33" s="1">
@@ -3789,30 +3974,30 @@
       <c r="I33" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6">
-        <v>0</v>
-      </c>
-      <c r="L33" s="7" t="s">
+      <c r="J33" s="5"/>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" t="s">
         <v>148</v>
       </c>
-      <c r="M33" s="7"/>
+      <c r="M33"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:13">
-      <c r="A34" s="7"/>
+      <c r="A34"/>
       <c r="B34" s="1" t="s">
         <v>149</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <v>0.4</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>151</v>
       </c>
       <c r="G34" s="1">
@@ -3824,30 +4009,30 @@
       <c r="I34" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6">
-        <v>0</v>
-      </c>
-      <c r="L34" s="7" t="s">
+      <c r="J34" s="5"/>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" t="s">
         <v>153</v>
       </c>
-      <c r="M34" s="7"/>
+      <c r="M34"/>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
-      <c r="A35" s="7"/>
+      <c r="A35"/>
       <c r="B35" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>0.4</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>156</v>
       </c>
       <c r="G35" s="1">
@@ -3859,30 +4044,30 @@
       <c r="I35" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6">
-        <v>0</v>
-      </c>
-      <c r="L35" s="7" t="s">
+      <c r="J35" s="5"/>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
+      <c r="L35" t="s">
         <v>158</v>
       </c>
-      <c r="M35" s="7"/>
+      <c r="M35"/>
     </row>
     <row r="36" s="2" customFormat="1" spans="1:13">
-      <c r="A36" s="8"/>
+      <c r="A36" s="6"/>
       <c r="B36" s="1" t="s">
         <v>159</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="7">
         <v>0.4</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="7" t="s">
         <v>161</v>
       </c>
       <c r="G36" s="2">
@@ -3894,30 +4079,30 @@
       <c r="I36" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9">
-        <v>0</v>
-      </c>
-      <c r="L36" s="7" t="s">
+      <c r="J36" s="7"/>
+      <c r="K36" s="7">
+        <v>0</v>
+      </c>
+      <c r="L36" t="s">
         <v>163</v>
       </c>
-      <c r="M36" s="8"/>
+      <c r="M36" s="6"/>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:13">
-      <c r="A37" s="7"/>
+      <c r="A37"/>
       <c r="B37" s="1" t="s">
         <v>164</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>0.4</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>166</v>
       </c>
       <c r="G37" s="1">
@@ -3929,30 +4114,30 @@
       <c r="I37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6">
-        <v>0</v>
-      </c>
-      <c r="L37" s="6" t="s">
+      <c r="J37" s="5"/>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="M37" s="7"/>
+      <c r="M37"/>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:13">
-      <c r="A38" s="8"/>
+      <c r="A38" s="6"/>
       <c r="B38" s="1" t="s">
         <v>169</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="7">
         <v>0.4</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="7" t="s">
         <v>171</v>
       </c>
       <c r="G38" s="2">
@@ -3964,30 +4149,30 @@
       <c r="I38" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9">
-        <v>0</v>
-      </c>
-      <c r="L38" s="8" t="s">
+      <c r="J38" s="7"/>
+      <c r="K38" s="7">
+        <v>0</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="M38" s="8"/>
+      <c r="M38" s="6"/>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:13">
-      <c r="A39" s="7"/>
+      <c r="A39"/>
       <c r="B39" s="1" t="s">
         <v>174</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>0.4</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>176</v>
       </c>
       <c r="G39" s="1">
@@ -3999,30 +4184,30 @@
       <c r="I39" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6">
-        <v>0</v>
-      </c>
-      <c r="L39" s="7" t="s">
+      <c r="J39" s="5"/>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
+      <c r="L39" t="s">
         <v>178</v>
       </c>
-      <c r="M39" s="7"/>
+      <c r="M39"/>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:13">
-      <c r="A40" s="7"/>
+      <c r="A40"/>
       <c r="B40" s="1" t="s">
         <v>179</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="5">
         <v>0.4</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>181</v>
       </c>
       <c r="G40" s="1">
@@ -4034,28 +4219,28 @@
       <c r="I40" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K40" s="6">
-        <v>0</v>
-      </c>
-      <c r="L40" s="7" t="s">
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
+      <c r="L40" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:13">
-      <c r="A41" s="7"/>
+      <c r="A41"/>
       <c r="B41" s="1" t="s">
         <v>184</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="5">
         <v>0.4</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>186</v>
       </c>
       <c r="G41" s="1">
@@ -4067,28 +4252,28 @@
       <c r="I41" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K41" s="6">
-        <v>0</v>
-      </c>
-      <c r="L41" s="7" t="s">
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
+      <c r="L41" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:13">
-      <c r="A42" s="7"/>
+      <c r="A42"/>
       <c r="B42" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="5">
         <v>0.4</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>191</v>
       </c>
       <c r="G42" s="1">
@@ -4100,28 +4285,28 @@
       <c r="I42" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K42" s="6">
-        <v>0</v>
-      </c>
-      <c r="L42" s="7" t="s">
+      <c r="K42" s="5">
+        <v>0</v>
+      </c>
+      <c r="L42" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
-      <c r="A43" s="7"/>
+      <c r="A43"/>
       <c r="B43" s="1" t="s">
         <v>194</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="5">
         <v>0.4</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F43" s="5" t="s">
         <v>196</v>
       </c>
       <c r="G43" s="1">
@@ -4133,180 +4318,180 @@
       <c r="I43" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K43" s="6">
-        <v>0</v>
-      </c>
-      <c r="L43" s="7" t="s">
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
+      <c r="L43" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:13">
-      <c r="A44" s="7"/>
+      <c r="A44"/>
       <c r="B44" s="1" t="s">
         <v>199</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="5">
         <v>0.4</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="5">
         <v>85</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="5">
         <v>42</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6">
-        <v>0</v>
-      </c>
-      <c r="L44" s="6" t="s">
+      <c r="J44" s="5"/>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
+      <c r="L44" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:13">
-      <c r="A45" s="7"/>
+      <c r="A45"/>
       <c r="B45" s="1" t="s">
         <v>204</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="5">
         <v>0.4</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <v>75</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="5">
         <v>37</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6">
-        <v>0</v>
-      </c>
-      <c r="L45" s="7" t="s">
+      <c r="J45" s="5"/>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
+      <c r="L45" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:13">
-      <c r="A46" s="7"/>
+      <c r="A46"/>
       <c r="B46" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="5">
         <v>0.4</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="5">
         <v>75</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="5">
         <v>37</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6">
-        <v>0</v>
-      </c>
-      <c r="L46" s="7" t="s">
+      <c r="J46" s="5"/>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:13">
-      <c r="A47" s="7"/>
+      <c r="A47"/>
       <c r="B47" s="1" t="s">
         <v>214</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>0.4</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="5">
         <v>70</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="5">
         <v>35</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6">
-        <v>0</v>
-      </c>
-      <c r="L47" s="7" t="s">
+      <c r="J47" s="5"/>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:13">
-      <c r="A48" s="7"/>
+      <c r="A48"/>
       <c r="B48" s="1" t="s">
         <v>219</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <v>0.4</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G48" s="5">
         <v>75</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="5">
         <v>37</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6">
-        <v>0</v>
-      </c>
-      <c r="L48" s="7" t="s">
+      <c r="J48" s="5"/>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
+      <c r="L48" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4317,551 +4502,545 @@
       <c r="C49" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="5">
         <v>0.4</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G49" s="6">
+      <c r="G49" s="5">
         <v>90</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="5">
         <v>45</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J49" s="6">
+      <c r="J49" s="5">
         <v>10301</v>
       </c>
-      <c r="K49" s="6">
-        <v>0</v>
-      </c>
-      <c r="L49" s="6" t="s">
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
+      <c r="L49" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="M49" s="7"/>
+      <c r="M49"/>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:13">
-      <c r="A50" s="7"/>
+      <c r="A50"/>
       <c r="B50" s="1" t="s">
         <v>229</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="5">
         <v>0.4</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="5">
         <v>120</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="5">
         <v>60</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6">
-        <v>0</v>
-      </c>
-      <c r="L50" s="6" t="s">
+      <c r="J50" s="5"/>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
+      <c r="L50" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="M50" s="7"/>
+      <c r="M50"/>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:13">
-      <c r="A51" s="7"/>
+      <c r="A51"/>
       <c r="B51" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="5">
         <v>0.4</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <v>110</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="5">
         <v>55</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6">
-        <v>0</v>
-      </c>
-      <c r="L51" s="7" t="s">
+      <c r="J51" s="5"/>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
+      <c r="L51" t="s">
         <v>238</v>
       </c>
-      <c r="M51" s="7"/>
+      <c r="M51"/>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:13">
-      <c r="A52" s="7"/>
+      <c r="A52"/>
       <c r="B52" s="1" t="s">
         <v>239</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="5">
         <v>0.4</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="5">
         <v>70</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H52" s="5">
         <v>35</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6">
-        <v>0</v>
-      </c>
-      <c r="L52" s="7" t="s">
+      <c r="J52" s="5"/>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
+      <c r="L52" t="s">
         <v>243</v>
       </c>
-      <c r="M52" s="7"/>
+      <c r="M52"/>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:13">
       <c r="B53" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="5">
         <v>0.4</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" t="s">
         <v>245</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" t="s">
         <v>246</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="5">
         <v>90</v>
       </c>
-      <c r="H53" s="6">
+      <c r="H53" s="5">
         <v>45</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6">
+      <c r="J53" s="5"/>
+      <c r="K53" s="5">
         <v>1</v>
       </c>
-      <c r="L53" s="7" t="s">
+      <c r="L53" t="s">
         <v>248</v>
       </c>
-      <c r="M53" s="7"/>
+      <c r="M53"/>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:13">
       <c r="B54" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="5">
         <v>0.4</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" t="s">
         <v>250</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" t="s">
         <v>251</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="5">
         <v>145</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="5">
         <v>72</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6">
+      <c r="J54" s="5"/>
+      <c r="K54" s="5">
         <v>1</v>
       </c>
-      <c r="L54" s="7" t="s">
+      <c r="L54" t="s">
         <v>253</v>
       </c>
-      <c r="M54" s="7"/>
+      <c r="M54"/>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:13">
       <c r="B55" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="5">
         <v>0.4</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" t="s">
         <v>255</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" t="s">
         <v>256</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="5">
         <v>95</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="5">
         <v>47</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6">
-        <v>0</v>
-      </c>
-      <c r="L55" s="7" t="s">
+      <c r="J55" s="5"/>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
+      <c r="L55" t="s">
         <v>258</v>
       </c>
-      <c r="M55" s="7"/>
+      <c r="M55"/>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:13">
       <c r="B56" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="5">
         <v>0.4</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" t="s">
         <v>260</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" t="s">
         <v>261</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="5">
         <v>110</v>
       </c>
-      <c r="H56" s="6">
+      <c r="H56" s="5">
         <v>55</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6">
+      <c r="J56" s="5"/>
+      <c r="K56" s="5">
         <v>1</v>
       </c>
-      <c r="L56" s="7" t="s">
+      <c r="L56" t="s">
         <v>263</v>
       </c>
-      <c r="M56" s="7"/>
+      <c r="M56"/>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:13">
       <c r="B57" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" t="s">
         <v>114</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="5">
         <v>0.4</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" t="s">
         <v>265</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" t="s">
         <v>266</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="5">
         <v>160</v>
       </c>
-      <c r="H57" s="6">
+      <c r="H57" s="5">
         <v>80</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6">
+      <c r="J57" s="5"/>
+      <c r="K57" s="5">
         <v>2</v>
       </c>
-      <c r="L57" s="7" t="s">
+      <c r="L57" t="s">
         <v>268</v>
       </c>
-      <c r="M57" s="7"/>
+      <c r="M57"/>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:13">
       <c r="B58" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" t="s">
         <v>114</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="5">
         <v>0.4</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" t="s">
         <v>270</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" t="s">
         <v>271</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="5">
         <v>160</v>
       </c>
-      <c r="H58" s="6">
+      <c r="H58" s="5">
         <v>80</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6">
+      <c r="J58" s="5"/>
+      <c r="K58" s="5">
         <v>2</v>
       </c>
-      <c r="L58" s="6" t="s">
+      <c r="L58" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="M58" s="7"/>
+      <c r="M58"/>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:13">
-      <c r="A59" s="7"/>
+      <c r="A59"/>
       <c r="B59" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="5">
         <v>0.4</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" t="s">
         <v>276</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="5">
         <v>80</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H59" s="5">
         <v>40</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6">
-        <v>0</v>
-      </c>
-      <c r="L59" s="7" t="s">
+      <c r="J59" s="5"/>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
+      <c r="L59" t="s">
         <v>278</v>
       </c>
-      <c r="M59" s="7"/>
+      <c r="M59"/>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:13">
-      <c r="A60" s="7"/>
+      <c r="A60"/>
       <c r="B60" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" t="s">
         <v>114</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="5">
         <v>0.4</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" t="s">
         <v>281</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G60" s="5">
         <v>80</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H60" s="5">
         <v>40</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6">
-        <v>0</v>
-      </c>
-      <c r="L60" s="7" t="s">
+      <c r="J60" s="5"/>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
         <v>283</v>
       </c>
-      <c r="M60" s="7"/>
-    </row>
-    <row r="61" s="1" customFormat="1" spans="1:13">
-      <c r="A61" s="7"/>
+      <c r="M60"/>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:13">
+      <c r="A61"/>
       <c r="B61" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" t="s">
         <v>114</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="5">
         <v>0.4</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" t="s">
         <v>286</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="5">
         <v>80</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H61" s="5">
         <v>40</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6">
-        <v>0</v>
-      </c>
-      <c r="L61" s="7" t="s">
+      <c r="J61" s="5"/>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
+      <c r="L61" t="s">
         <v>288</v>
       </c>
-      <c r="M61" s="7"/>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="1:13">
-      <c r="A62" s="7"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="7"/>
-    </row>
-    <row r="63" s="1" customFormat="1" spans="1:13">
-      <c r="A63" s="7"/>
-      <c r="B63" s="6">
+      <c r="M61"/>
+    </row>
+    <row r="62" s="3" customFormat="1" spans="1:13">
+      <c r="A62" s="8"/>
+      <c r="B62" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9">
+        <v>150</v>
+      </c>
+      <c r="H62" s="9">
+        <v>75</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9">
+        <v>0</v>
+      </c>
+      <c r="L62" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" s="3" customFormat="1" spans="1:13">
+      <c r="A63" s="8"/>
+      <c r="B63" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" s="9">
+        <v>0.4</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9">
+        <v>110</v>
+      </c>
+      <c r="H63" s="9">
+        <v>55</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9">
+        <v>0</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" s="1" customFormat="1" spans="1:13">
+      <c r="A64"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64"/>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:13">
+      <c r="A65"/>
+      <c r="B65" s="5">
         <v>301</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C65" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D65" s="5">
         <v>0.2</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="G63" s="1">
-        <v>190</v>
-      </c>
-      <c r="H63" s="1">
-        <v>95</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="J63" s="6">
-        <v>10401</v>
-      </c>
-      <c r="K63" s="6">
-        <v>0</v>
-      </c>
-      <c r="L63" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="M63" s="7"/>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:13">
-      <c r="A64" s="7"/>
-      <c r="B64" s="6">
-        <v>302</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D64" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="G64" s="1">
-        <v>270</v>
-      </c>
-      <c r="H64" s="1">
-        <v>135</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6">
-        <v>0</v>
-      </c>
-      <c r="L64" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="M64" s="7"/>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:13">
-      <c r="A65" s="7"/>
-      <c r="B65" s="6">
-        <v>303</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D65" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="F65" s="6" t="s">
+      <c r="F65" s="5" t="s">
         <v>299</v>
       </c>
       <c r="G65" s="1">
@@ -4873,2196 +5052,2644 @@
       <c r="I65" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="J65" s="6">
-        <v>10501</v>
-      </c>
-      <c r="K65" s="6">
-        <v>0</v>
-      </c>
-      <c r="L65" s="7" t="s">
+      <c r="J65" s="5">
+        <v>10401</v>
+      </c>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
         <v>301</v>
       </c>
-      <c r="M65" s="7"/>
+      <c r="M65"/>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:13">
-      <c r="A66" s="7"/>
-      <c r="B66" s="6">
-        <v>304</v>
+      <c r="A66"/>
+      <c r="B66" s="5">
+        <v>302</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D66" s="6">
+        <v>297</v>
+      </c>
+      <c r="D66" s="5">
         <v>0.2</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="F66" s="6" t="s">
+      <c r="F66" s="5" t="s">
         <v>303</v>
       </c>
       <c r="G66" s="1">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="H66" s="1">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="J66" s="6">
-        <v>10601</v>
-      </c>
-      <c r="K66" s="6">
-        <v>0</v>
-      </c>
-      <c r="L66" s="7" t="s">
+      <c r="J66" s="5"/>
+      <c r="K66" s="5">
+        <v>0</v>
+      </c>
+      <c r="L66" t="s">
         <v>305</v>
       </c>
+      <c r="M66"/>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:13">
-      <c r="A67" s="7"/>
-      <c r="B67" s="6">
-        <v>305</v>
+      <c r="A67"/>
+      <c r="B67" s="5">
+        <v>303</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D67" s="6">
+        <v>297</v>
+      </c>
+      <c r="D67" s="5">
         <v>0.2</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="F67" s="6" t="s">
+      <c r="F67" s="5" t="s">
         <v>307</v>
       </c>
       <c r="G67" s="1">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="H67" s="1">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="J67" s="6">
-        <v>10701</v>
-      </c>
-      <c r="K67" s="6">
-        <v>0</v>
-      </c>
-      <c r="L67" s="7" t="s">
+      <c r="J67" s="5">
+        <v>10501</v>
+      </c>
+      <c r="K67" s="5">
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
         <v>309</v>
       </c>
+      <c r="M67"/>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:13">
-      <c r="B68" s="6">
-        <v>306</v>
+      <c r="A68"/>
+      <c r="B68" s="5">
+        <v>304</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D68" s="6">
+        <v>297</v>
+      </c>
+      <c r="D68" s="5">
         <v>0.2</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="E68" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="F68" s="6" t="s">
+      <c r="F68" s="5" t="s">
         <v>311</v>
       </c>
       <c r="G68" s="1">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="H68" s="1">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="K68" s="6">
-        <v>0</v>
-      </c>
-      <c r="L68" s="7" t="s">
+      <c r="J68" s="5">
+        <v>10601</v>
+      </c>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:13">
-      <c r="B69" s="6">
-        <v>307</v>
+      <c r="A69"/>
+      <c r="B69" s="5">
+        <v>305</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D69" s="6">
+        <v>297</v>
+      </c>
+      <c r="D69" s="5">
         <v>0.2</v>
       </c>
-      <c r="E69" s="6" t="s">
+      <c r="E69" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F69" s="6" t="s">
+      <c r="F69" s="5" t="s">
         <v>315</v>
       </c>
       <c r="G69" s="1">
-        <v>280</v>
+        <v>170</v>
       </c>
       <c r="H69" s="1">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="J69" s="6"/>
-      <c r="K69" s="6">
-        <v>0</v>
-      </c>
-      <c r="L69" s="7" t="s">
+      <c r="J69" s="5">
+        <v>10701</v>
+      </c>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:13">
-      <c r="B70" s="6">
-        <v>308</v>
+      <c r="B70" s="5">
+        <v>306</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D70" s="6">
+        <v>297</v>
+      </c>
+      <c r="D70" s="5">
         <v>0.2</v>
       </c>
-      <c r="E70" s="6" t="s">
+      <c r="E70" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="5" t="s">
         <v>319</v>
       </c>
       <c r="G70" s="1">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="H70" s="1">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="K70" s="6">
-        <v>0</v>
-      </c>
-      <c r="L70" s="7" t="s">
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:13">
-      <c r="B71" s="6">
-        <v>309</v>
+      <c r="B71" s="5">
+        <v>307</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D71" s="6">
+        <v>297</v>
+      </c>
+      <c r="D71" s="5">
         <v>0.2</v>
       </c>
-      <c r="E71" s="6" t="s">
+      <c r="E71" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="F71" s="6" t="s">
+      <c r="F71" s="5" t="s">
         <v>323</v>
       </c>
       <c r="G71" s="1">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H71" s="1">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6">
-        <v>0</v>
-      </c>
-      <c r="L71" s="6" t="s">
+      <c r="J71" s="5"/>
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:13">
-      <c r="B72" s="6">
-        <v>310</v>
+      <c r="B72" s="5">
+        <v>308</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D72" s="6">
+        <v>297</v>
+      </c>
+      <c r="D72" s="5">
         <v>0.2</v>
       </c>
-      <c r="E72" s="6" t="s">
+      <c r="E72" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="F72" s="6" t="s">
+      <c r="F72" s="5" t="s">
         <v>327</v>
       </c>
       <c r="G72" s="1">
-        <v>170</v>
+        <v>270</v>
       </c>
       <c r="H72" s="1">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="K72" s="6">
-        <v>0</v>
-      </c>
-      <c r="L72" s="7" t="s">
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:13">
-      <c r="B73" s="6">
-        <v>311</v>
+      <c r="B73" s="5">
+        <v>309</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D73" s="6">
+        <v>297</v>
+      </c>
+      <c r="D73" s="5">
         <v>0.2</v>
       </c>
-      <c r="E73" s="6" t="s">
+      <c r="E73" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="F73" s="6" t="s">
+      <c r="F73" s="5" t="s">
         <v>331</v>
       </c>
       <c r="G73" s="1">
-        <v>130</v>
+        <v>275</v>
       </c>
       <c r="H73" s="1">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="K73" s="6">
-        <v>0</v>
-      </c>
-      <c r="L73" s="7" t="s">
+      <c r="J73" s="5"/>
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:13">
-      <c r="B74" s="6">
-        <v>312</v>
+      <c r="B74" s="5">
+        <v>310</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D74" s="6">
+        <v>297</v>
+      </c>
+      <c r="D74" s="5">
         <v>0.2</v>
       </c>
-      <c r="E74" s="6" t="s">
+      <c r="E74" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="F74" s="6" t="s">
+      <c r="F74" s="5" t="s">
         <v>335</v>
       </c>
       <c r="G74" s="1">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="H74" s="1">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6">
-        <v>0</v>
-      </c>
-      <c r="L74" s="7" t="s">
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:13">
-      <c r="B75" s="6">
-        <v>313</v>
+      <c r="B75" s="5">
+        <v>311</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D75" s="6">
+        <v>297</v>
+      </c>
+      <c r="D75" s="5">
         <v>0.2</v>
       </c>
-      <c r="E75" s="6" t="s">
+      <c r="E75" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="F75" s="6" t="s">
+      <c r="F75" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G75" s="6">
-        <v>120</v>
-      </c>
-      <c r="H75" s="6">
-        <v>60</v>
+      <c r="G75" s="1">
+        <v>130</v>
+      </c>
+      <c r="H75" s="1">
+        <v>65</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6">
-        <v>0</v>
-      </c>
-      <c r="L75" s="7" t="s">
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:13">
-      <c r="B76" s="6">
-        <v>314</v>
+      <c r="B76" s="5">
+        <v>312</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D76" s="6">
+        <v>297</v>
+      </c>
+      <c r="D76" s="5">
         <v>0.2</v>
       </c>
-      <c r="E76" s="6" t="s">
+      <c r="E76" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="G76" s="6">
-        <v>380</v>
-      </c>
-      <c r="H76" s="6">
-        <v>190</v>
+      <c r="G76" s="1">
+        <v>160</v>
+      </c>
+      <c r="H76" s="1">
+        <v>80</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6">
-        <v>0</v>
-      </c>
-      <c r="L76" s="7" t="s">
+      <c r="J76" s="5"/>
+      <c r="K76" s="5">
+        <v>0</v>
+      </c>
+      <c r="L76" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:13">
-      <c r="B77" s="6">
-        <v>315</v>
+      <c r="B77" s="5">
+        <v>313</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D77" s="6">
+        <v>297</v>
+      </c>
+      <c r="D77" s="5">
         <v>0.2</v>
       </c>
-      <c r="E77" s="6" t="s">
+      <c r="E77" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="F77" s="6" t="s">
+      <c r="F77" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="G77" s="6">
-        <v>170</v>
-      </c>
-      <c r="H77" s="6">
-        <v>85</v>
+      <c r="G77" s="5">
+        <v>120</v>
+      </c>
+      <c r="H77" s="5">
+        <v>60</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6">
-        <v>0</v>
-      </c>
-      <c r="L77" s="7" t="s">
+      <c r="J77" s="5"/>
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
         <v>349</v>
       </c>
-      <c r="M77" s="7"/>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:13">
-      <c r="B78" s="6">
-        <v>316</v>
+      <c r="B78" s="5">
+        <v>314</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D78" s="6">
+        <v>297</v>
+      </c>
+      <c r="D78" s="5">
         <v>0.2</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E78" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F78" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="G78" s="6">
-        <v>200</v>
-      </c>
-      <c r="H78" s="6">
-        <v>100</v>
+      <c r="G78" s="5">
+        <v>380</v>
+      </c>
+      <c r="H78" s="5">
+        <v>190</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="J78" s="6">
-        <v>10201</v>
-      </c>
-      <c r="K78" s="6">
-        <v>0</v>
-      </c>
-      <c r="L78" s="6" t="s">
+      <c r="J78" s="5"/>
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
         <v>353</v>
       </c>
-      <c r="M78" s="7"/>
     </row>
     <row r="79" s="1" customFormat="1" spans="1:13">
-      <c r="B79" s="6">
-        <v>317</v>
+      <c r="B79" s="5">
+        <v>315</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D79" s="6">
+        <v>297</v>
+      </c>
+      <c r="D79" s="5">
         <v>0.2</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="E79" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="F79" s="6" t="s">
+      <c r="F79" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G79" s="5">
         <v>170</v>
       </c>
-      <c r="H79" s="6">
+      <c r="H79" s="5">
         <v>85</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="J79" s="6">
-        <v>10801</v>
-      </c>
-      <c r="K79" s="6">
-        <v>0</v>
-      </c>
-      <c r="L79" s="7" t="s">
+      <c r="J79" s="5"/>
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
         <v>357</v>
       </c>
-      <c r="M79" s="7"/>
+      <c r="M79"/>
     </row>
     <row r="80" s="1" customFormat="1" spans="1:13">
-      <c r="B80" s="6">
-        <v>318</v>
+      <c r="B80" s="5">
+        <v>316</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D80" s="6">
+        <v>297</v>
+      </c>
+      <c r="D80" s="5">
         <v>0.2</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="E80" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="F80" s="6" t="s">
+      <c r="F80" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="G80" s="6">
-        <v>160</v>
-      </c>
-      <c r="H80" s="6">
-        <v>80</v>
+      <c r="G80" s="5">
+        <v>200</v>
+      </c>
+      <c r="H80" s="5">
+        <v>100</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="J80" s="6">
-        <v>10402</v>
-      </c>
-      <c r="K80" s="6">
-        <v>0</v>
-      </c>
-      <c r="L80" s="7" t="s">
+      <c r="J80" s="5">
+        <v>10201</v>
+      </c>
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="M80" s="7"/>
+      <c r="M80"/>
     </row>
     <row r="81" s="1" customFormat="1" spans="2:13">
-      <c r="B81" s="6">
-        <v>319</v>
+      <c r="B81" s="5">
+        <v>317</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D81" s="6">
+        <v>297</v>
+      </c>
+      <c r="D81" s="5">
         <v>0.2</v>
       </c>
-      <c r="E81" s="6" t="s">
+      <c r="E81" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="F81" s="6" t="s">
+      <c r="F81" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="G81" s="6">
-        <v>160</v>
-      </c>
-      <c r="H81" s="6">
-        <v>80</v>
+      <c r="G81" s="5">
+        <v>170</v>
+      </c>
+      <c r="H81" s="5">
+        <v>85</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6">
-        <v>0</v>
-      </c>
-      <c r="L81" s="7" t="s">
+      <c r="J81" s="5">
+        <v>10801</v>
+      </c>
+      <c r="K81" s="5">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
         <v>365</v>
       </c>
-      <c r="M81" s="7"/>
+      <c r="M81"/>
     </row>
     <row r="82" s="1" customFormat="1" spans="2:13">
-      <c r="B82" s="6">
-        <v>320</v>
+      <c r="B82" s="5">
+        <v>318</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D82" s="6">
+        <v>297</v>
+      </c>
+      <c r="D82" s="5">
         <v>0.2</v>
       </c>
-      <c r="E82" s="6" t="s">
+      <c r="E82" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="F82" s="6" t="s">
+      <c r="F82" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G82" s="5">
         <v>160</v>
       </c>
-      <c r="H82" s="6">
+      <c r="H82" s="5">
         <v>80</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6">
-        <v>0</v>
-      </c>
-      <c r="L82" s="7" t="s">
+      <c r="J82" s="5">
+        <v>10402</v>
+      </c>
+      <c r="K82" s="5">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
         <v>369</v>
       </c>
-      <c r="M82" s="7"/>
+      <c r="M82"/>
     </row>
     <row r="83" s="1" customFormat="1" spans="2:13">
-      <c r="B83" s="6">
-        <v>321</v>
+      <c r="B83" s="5">
+        <v>319</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D83" s="6">
+        <v>297</v>
+      </c>
+      <c r="D83" s="5">
         <v>0.2</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="E83" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G83" s="5">
         <v>160</v>
       </c>
-      <c r="H83" s="6">
+      <c r="H83" s="5">
         <v>80</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6">
-        <v>0</v>
-      </c>
-      <c r="L83" s="7" t="s">
+      <c r="J83" s="5"/>
+      <c r="K83" s="5">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
         <v>373</v>
       </c>
-      <c r="M83" s="7"/>
+      <c r="M83"/>
     </row>
     <row r="84" s="1" customFormat="1" spans="2:13">
-      <c r="B84" s="6">
-        <v>322</v>
+      <c r="B84" s="5">
+        <v>320</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D84" s="6">
+        <v>297</v>
+      </c>
+      <c r="D84" s="5">
         <v>0.2</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="E84" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="G84" s="6">
-        <v>190</v>
-      </c>
-      <c r="H84" s="6">
-        <v>95</v>
+      <c r="G84" s="5">
+        <v>160</v>
+      </c>
+      <c r="H84" s="5">
+        <v>80</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6">
-        <v>0</v>
-      </c>
-      <c r="L84" s="7" t="s">
+      <c r="J84" s="5"/>
+      <c r="K84" s="5">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
         <v>377</v>
       </c>
-      <c r="M84" s="7"/>
+      <c r="M84"/>
     </row>
     <row r="85" s="1" customFormat="1" spans="2:13">
-      <c r="B85" s="6">
-        <v>323</v>
+      <c r="B85" s="5">
+        <v>321</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D85" s="6">
+        <v>297</v>
+      </c>
+      <c r="D85" s="5">
         <v>0.2</v>
       </c>
-      <c r="E85" s="6" t="s">
+      <c r="E85" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="G85" s="6">
-        <v>175</v>
-      </c>
-      <c r="H85" s="6">
-        <v>87</v>
+      <c r="G85" s="5">
+        <v>160</v>
+      </c>
+      <c r="H85" s="5">
+        <v>80</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6">
-        <v>0</v>
-      </c>
-      <c r="L85" s="7" t="s">
+      <c r="J85" s="5"/>
+      <c r="K85" s="5">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
         <v>381</v>
       </c>
-      <c r="M85" s="7"/>
+      <c r="M85"/>
     </row>
     <row r="86" s="1" customFormat="1" spans="2:13">
-      <c r="B86" s="6">
-        <v>324</v>
+      <c r="B86" s="5">
+        <v>322</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="D86" s="6">
+        <v>297</v>
+      </c>
+      <c r="D86" s="5">
         <v>0.2</v>
       </c>
-      <c r="E86" s="6" t="s">
+      <c r="E86" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="G86" s="6">
-        <v>270</v>
-      </c>
-      <c r="H86" s="6">
-        <v>135</v>
+      <c r="G86" s="5">
+        <v>190</v>
+      </c>
+      <c r="H86" s="5">
+        <v>95</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="J86" s="6">
-        <v>10502</v>
-      </c>
-      <c r="K86" s="6">
-        <v>0</v>
-      </c>
-      <c r="L86" s="7" t="s">
+      <c r="J86" s="5"/>
+      <c r="K86" s="5">
+        <v>0</v>
+      </c>
+      <c r="L86" t="s">
         <v>385</v>
       </c>
-      <c r="M86" s="7"/>
+      <c r="M86"/>
     </row>
     <row r="87" s="1" customFormat="1" spans="2:13">
-      <c r="B87" s="6">
-        <v>325</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D87" s="6">
+      <c r="B87" s="5">
+        <v>323</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D87" s="5">
         <v>0.2</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F87" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="G87" s="6">
-        <v>160</v>
-      </c>
-      <c r="H87" s="6">
-        <v>80</v>
+      <c r="G87" s="5">
+        <v>175</v>
+      </c>
+      <c r="H87" s="5">
+        <v>87</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6">
-        <v>2</v>
-      </c>
-      <c r="L87" s="7" t="s">
+      <c r="J87" s="5"/>
+      <c r="K87" s="5">
+        <v>0</v>
+      </c>
+      <c r="L87" t="s">
         <v>389</v>
       </c>
-      <c r="M87" s="7"/>
+      <c r="M87"/>
     </row>
     <row r="88" s="1" customFormat="1" spans="2:13">
-      <c r="B88" s="6">
-        <v>326</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D88" s="6">
+      <c r="B88" s="5">
+        <v>324</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D88" s="5">
         <v>0.2</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="F88" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="G88" s="6">
-        <v>200</v>
-      </c>
-      <c r="H88" s="6">
-        <v>100</v>
+      <c r="G88" s="5">
+        <v>270</v>
+      </c>
+      <c r="H88" s="5">
+        <v>135</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="J88" s="6">
-        <v>10901</v>
-      </c>
-      <c r="K88" s="6">
-        <v>2</v>
-      </c>
-      <c r="L88" s="7" t="s">
+      <c r="J88" s="5">
+        <v>10502</v>
+      </c>
+      <c r="K88" s="5">
+        <v>0</v>
+      </c>
+      <c r="L88" t="s">
         <v>393</v>
       </c>
-      <c r="M88" s="7"/>
+      <c r="M88"/>
     </row>
     <row r="89" s="1" customFormat="1" spans="2:13">
-      <c r="B89" s="6">
-        <v>327</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D89" s="6">
+      <c r="B89" s="5">
+        <v>325</v>
+      </c>
+      <c r="C89" t="s">
+        <v>297</v>
+      </c>
+      <c r="D89" s="5">
         <v>0.2</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" t="s">
         <v>394</v>
       </c>
-      <c r="F89" s="7" t="s">
+      <c r="F89" t="s">
         <v>395</v>
       </c>
-      <c r="G89" s="6">
-        <v>170</v>
-      </c>
-      <c r="H89" s="6">
-        <v>85</v>
+      <c r="G89" s="5">
+        <v>160</v>
+      </c>
+      <c r="H89" s="5">
+        <v>80</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6">
-        <v>1</v>
-      </c>
-      <c r="L89" s="7" t="s">
+      <c r="J89" s="5"/>
+      <c r="K89" s="5">
+        <v>2</v>
+      </c>
+      <c r="L89" t="s">
         <v>397</v>
       </c>
-      <c r="M89" s="7"/>
+      <c r="M89"/>
     </row>
     <row r="90" s="1" customFormat="1" spans="2:13">
-      <c r="B90" s="6">
-        <v>328</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D90" s="6">
+      <c r="B90" s="5">
+        <v>326</v>
+      </c>
+      <c r="C90" t="s">
+        <v>297</v>
+      </c>
+      <c r="D90" s="5">
         <v>0.2</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" t="s">
         <v>398</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="F90" t="s">
         <v>399</v>
       </c>
-      <c r="G90" s="6">
-        <v>160</v>
-      </c>
-      <c r="H90" s="6">
-        <v>80</v>
+      <c r="G90" s="5">
+        <v>200</v>
+      </c>
+      <c r="H90" s="5">
+        <v>100</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="J90" s="6"/>
-      <c r="K90" s="6">
-        <v>1</v>
-      </c>
-      <c r="L90" s="7" t="s">
+      <c r="J90" s="5">
+        <v>10901</v>
+      </c>
+      <c r="K90" s="5">
+        <v>2</v>
+      </c>
+      <c r="L90" t="s">
         <v>401</v>
       </c>
-      <c r="M90" s="7"/>
+      <c r="M90"/>
     </row>
     <row r="91" s="1" customFormat="1" spans="2:13">
-      <c r="B91" s="6">
-        <v>329</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D91" s="6">
+      <c r="B91" s="5">
+        <v>327</v>
+      </c>
+      <c r="C91" t="s">
+        <v>297</v>
+      </c>
+      <c r="D91" s="5">
         <v>0.2</v>
       </c>
-      <c r="E91" s="6" t="s">
+      <c r="E91" t="s">
         <v>402</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="F91" t="s">
         <v>403</v>
       </c>
-      <c r="G91" s="6">
-        <v>200</v>
-      </c>
-      <c r="H91" s="6">
-        <v>100</v>
+      <c r="G91" s="5">
+        <v>170</v>
+      </c>
+      <c r="H91" s="5">
+        <v>85</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J91" s="9">
+      <c r="J91" s="5"/>
+      <c r="K91" s="5">
+        <v>1</v>
+      </c>
+      <c r="L91" t="s">
+        <v>405</v>
+      </c>
+      <c r="M91"/>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="2:13">
+      <c r="B92" s="5">
+        <v>328</v>
+      </c>
+      <c r="C92" t="s">
+        <v>297</v>
+      </c>
+      <c r="D92" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E92" t="s">
+        <v>406</v>
+      </c>
+      <c r="F92" t="s">
+        <v>407</v>
+      </c>
+      <c r="G92" s="5">
+        <v>160</v>
+      </c>
+      <c r="H92" s="5">
+        <v>80</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5">
+        <v>1</v>
+      </c>
+      <c r="L92" t="s">
+        <v>409</v>
+      </c>
+      <c r="M92"/>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="2:13">
+      <c r="B93" s="5">
+        <v>329</v>
+      </c>
+      <c r="C93" t="s">
+        <v>297</v>
+      </c>
+      <c r="D93" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="F93" t="s">
+        <v>411</v>
+      </c>
+      <c r="G93" s="5">
+        <v>200</v>
+      </c>
+      <c r="H93" s="5">
+        <v>100</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="J93" s="7">
         <v>11005</v>
       </c>
-      <c r="K91" s="6">
-        <v>0</v>
-      </c>
-      <c r="L91" s="7" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="2:13">
-      <c r="B92" s="6">
+      <c r="K93" s="5">
+        <v>0</v>
+      </c>
+      <c r="L93" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" ht="14.25" customHeight="1" spans="2:13">
+      <c r="B94" s="5">
         <v>330</v>
       </c>
-      <c r="C92" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="D92" s="6">
+      <c r="C94" t="s">
+        <v>297</v>
+      </c>
+      <c r="D94" s="5">
         <v>0.2</v>
       </c>
-      <c r="E92" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="G92" s="6">
+      <c r="E94" t="s">
+        <v>414</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G94" s="5">
         <v>300</v>
       </c>
-      <c r="H92" s="6">
+      <c r="H94" s="5">
         <v>150</v>
       </c>
-      <c r="I92" s="6">
+      <c r="I94" s="5">
         <v>40025</v>
       </c>
-      <c r="J92" s="6"/>
-      <c r="K92" s="6">
-        <v>0</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="M92" s="7"/>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="2:13">
-      <c r="D93" s="6"/>
-      <c r="E93" s="6"/>
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="2:13">
-      <c r="B94" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D94" s="6">
+      <c r="J94" s="5"/>
+      <c r="K94" s="5">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="M94"/>
+    </row>
+    <row r="95" s="3" customFormat="1" spans="2:13">
+      <c r="B95" s="9">
+        <v>331</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D95" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9">
+        <v>260</v>
+      </c>
+      <c r="H95" s="9">
+        <v>130</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9">
+        <v>0</v>
+      </c>
+      <c r="L95" s="8" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="96" s="3" customFormat="1" spans="2:13">
+      <c r="B96" s="9">
+        <v>332</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D96" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="F96" s="9"/>
+      <c r="G96" s="9">
+        <v>260</v>
+      </c>
+      <c r="H96" s="9">
+        <v>130</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="J96" s="9"/>
+      <c r="K96" s="9">
+        <v>0</v>
+      </c>
+      <c r="L96" s="8" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="97" s="3" customFormat="1" spans="2:12">
+      <c r="B97" s="9">
+        <v>333</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D97" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9">
+        <v>260</v>
+      </c>
+      <c r="H97" s="9">
+        <v>130</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9">
+        <v>0</v>
+      </c>
+      <c r="L97" s="8" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="98" s="3" customFormat="1" spans="2:12">
+      <c r="B98" s="9">
+        <v>334</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D98" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9">
+        <v>250</v>
+      </c>
+      <c r="H98" s="9">
+        <v>125</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9">
+        <v>0</v>
+      </c>
+      <c r="L98" s="8" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="99" s="3" customFormat="1" spans="2:12">
+      <c r="B99" s="9">
+        <v>335</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D99" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9">
+        <v>250</v>
+      </c>
+      <c r="H99" s="9">
+        <v>125</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9">
+        <v>0</v>
+      </c>
+      <c r="L99" s="8" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="100" s="3" customFormat="1" spans="2:12">
+      <c r="B100" s="9">
+        <v>336</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D100" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9">
+        <v>260</v>
+      </c>
+      <c r="H100" s="9">
+        <v>130</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9">
+        <v>0</v>
+      </c>
+      <c r="L100" s="8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="101" s="3" customFormat="1" spans="2:12">
+      <c r="B101" s="9">
+        <v>337</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D101" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="F101" s="9"/>
+      <c r="G101" s="9">
+        <v>260</v>
+      </c>
+      <c r="H101" s="9">
+        <v>130</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9">
+        <v>0</v>
+      </c>
+      <c r="L101" s="8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="102" s="3" customFormat="1" spans="2:12">
+      <c r="B102" s="9">
+        <v>338</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D102" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="F102" s="9"/>
+      <c r="G102" s="9">
+        <v>240</v>
+      </c>
+      <c r="H102" s="9">
+        <v>120</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="J102" s="9"/>
+      <c r="K102" s="9">
+        <v>0</v>
+      </c>
+      <c r="L102" s="8" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="2:12">
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="J103" s="5"/>
+      <c r="K103" s="5"/>
+      <c r="L103" s="5"/>
+    </row>
+    <row r="104" s="1" customFormat="1" spans="2:12">
+      <c r="B104" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D104" s="5">
         <v>0.1</v>
       </c>
-      <c r="E94" s="6">
+      <c r="E104" s="5">
         <v>235</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="G94" s="6">
+      <c r="F104" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="G104" s="5">
         <v>650</v>
       </c>
-      <c r="H94" s="6">
+      <c r="H104" s="5">
         <v>325</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="J94" s="6">
+      <c r="I104" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="J104" s="5">
         <v>11001</v>
       </c>
-      <c r="K94" s="6">
-        <v>0</v>
-      </c>
-      <c r="L94" s="7" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="2:13">
-      <c r="B95" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D95" s="6">
+      <c r="K104" s="5">
+        <v>0</v>
+      </c>
+      <c r="L104" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="2:12">
+      <c r="B105" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D105" s="5">
         <v>0.1</v>
       </c>
-      <c r="E95" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="G95" s="6">
+      <c r="E105" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="G105" s="5">
         <v>680</v>
       </c>
-      <c r="H95" s="6">
+      <c r="H105" s="5">
         <v>340</v>
       </c>
-      <c r="I95" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6">
-        <v>0</v>
-      </c>
-      <c r="L95" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="2:13">
-      <c r="B96" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D96" s="6">
+      <c r="I105" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5">
+        <v>0</v>
+      </c>
+      <c r="L105" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" spans="2:12">
+      <c r="B106" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D106" s="5">
         <v>0.1</v>
       </c>
-      <c r="E96" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="G96" s="6">
+      <c r="E106" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G106" s="5">
         <v>600</v>
       </c>
-      <c r="H96" s="6">
+      <c r="H106" s="5">
         <v>300</v>
       </c>
-      <c r="I96" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="K96" s="6">
-        <v>0</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="2:13">
-      <c r="B97" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D97" s="6">
+      <c r="I106" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="K106" s="5">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" spans="2:12">
+      <c r="B107" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D107" s="5">
         <v>0.1</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="G97" s="6">
+      <c r="E107" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="G107" s="5">
         <v>480</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H107" s="5">
         <v>240</v>
       </c>
-      <c r="I97" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="J97" s="6">
+      <c r="I107" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="J107" s="5">
         <v>11002</v>
       </c>
-      <c r="K97" s="6">
-        <v>0</v>
-      </c>
-      <c r="L97" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="98" s="1" customFormat="1" spans="2:13">
-      <c r="B98" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D98" s="6">
+      <c r="K107" s="5">
+        <v>0</v>
+      </c>
+      <c r="L107" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" spans="2:12">
+      <c r="B108" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D108" s="5">
         <v>0.1</v>
       </c>
-      <c r="E98" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="G98" s="6">
+      <c r="E108" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="G108" s="5">
         <v>460</v>
       </c>
-      <c r="H98" s="6">
+      <c r="H108" s="5">
         <v>230</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="J98" s="6"/>
-      <c r="K98" s="6">
-        <v>0</v>
-      </c>
-      <c r="L98" s="7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1" spans="2:13">
-      <c r="B99" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D99" s="6">
+      <c r="I108" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5">
+        <v>0</v>
+      </c>
+      <c r="L108" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" spans="2:12">
+      <c r="B109" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D109" s="5">
         <v>0.1</v>
       </c>
-      <c r="E99" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="G99" s="6">
+      <c r="E109" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="G109" s="5">
         <v>320</v>
       </c>
-      <c r="H99" s="6">
+      <c r="H109" s="5">
         <v>160</v>
       </c>
-      <c r="I99" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="K99" s="6">
-        <v>0</v>
-      </c>
-      <c r="L99" s="7" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" spans="2:13">
-      <c r="B100" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D100" s="6">
+      <c r="I109" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="K109" s="5">
+        <v>0</v>
+      </c>
+      <c r="L109" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" spans="2:12">
+      <c r="B110" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D110" s="5">
         <v>0.1</v>
       </c>
-      <c r="E100" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="G100" s="6">
+      <c r="E110" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="G110" s="5">
         <v>380</v>
       </c>
-      <c r="H100" s="6">
+      <c r="H110" s="5">
         <v>190</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I110" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="J110" s="5">
+        <v>11003</v>
+      </c>
+      <c r="K110" s="5">
+        <v>0</v>
+      </c>
+      <c r="L110" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" spans="2:12">
+      <c r="B111" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="J100" s="6">
-        <v>11003</v>
-      </c>
-      <c r="K100" s="6">
-        <v>0</v>
-      </c>
-      <c r="L100" s="7" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" spans="2:13">
-      <c r="B101" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D101" s="6">
+      <c r="D111" s="5">
         <v>0.1</v>
       </c>
-      <c r="E101" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="G101" s="6">
+      <c r="E111" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="G111" s="5">
         <v>600</v>
       </c>
-      <c r="H101" s="6">
+      <c r="H111" s="5">
         <v>300</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6">
-        <v>0</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" spans="2:13">
-      <c r="B102" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D102" s="6">
+      <c r="I111" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" spans="2:12">
+      <c r="B112" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D112" s="5">
         <v>0.1</v>
       </c>
-      <c r="E102" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="G102" s="6">
+      <c r="E112" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="G112" s="5">
         <v>280</v>
       </c>
-      <c r="H102" s="6">
+      <c r="H112" s="5">
         <v>140</v>
       </c>
-      <c r="I102" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="K102" s="6">
-        <v>0</v>
-      </c>
-      <c r="L102" s="7" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="2:13">
-      <c r="B103" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D103" s="6">
+      <c r="I112" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="K112" s="5">
+        <v>0</v>
+      </c>
+      <c r="L112" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" spans="2:13">
+      <c r="B113" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D113" s="5">
         <v>0.1</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="G103" s="6">
+      <c r="E113" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="G113" s="5">
         <v>300</v>
       </c>
-      <c r="H103" s="6">
+      <c r="H113" s="5">
         <v>150</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="K103" s="6">
-        <v>0</v>
-      </c>
-      <c r="L103" s="7" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" spans="2:13">
-      <c r="B104" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D104" s="6">
+      <c r="I113" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="K113" s="5">
+        <v>0</v>
+      </c>
+      <c r="L113" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" spans="2:13">
+      <c r="B114" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D114" s="5">
         <v>0.1</v>
       </c>
-      <c r="E104" s="6" t="s">
+      <c r="E114" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="G114" s="5">
+        <v>400</v>
+      </c>
+      <c r="H114" s="5">
+        <v>200</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="J114" s="5">
+        <v>11004</v>
+      </c>
+      <c r="K114" s="5">
+        <v>0</v>
+      </c>
+      <c r="L114" t="s">
+        <v>495</v>
+      </c>
+      <c r="M114"/>
+    </row>
+    <row r="115" s="1" customFormat="1" spans="2:13">
+      <c r="B115" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D115" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="G115" s="5">
         <v>460</v>
       </c>
-      <c r="F104" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="G104" s="6">
+      <c r="H115" s="5">
+        <v>230</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="J115" s="5"/>
+      <c r="K115" s="5">
+        <v>0</v>
+      </c>
+      <c r="L115" t="s">
+        <v>500</v>
+      </c>
+      <c r="M115"/>
+    </row>
+    <row r="116" s="1" customFormat="1" spans="2:13">
+      <c r="B116" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D116" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="G116" s="5">
+        <v>220</v>
+      </c>
+      <c r="H116" s="5">
+        <v>110</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="J116" s="5">
+        <v>10602</v>
+      </c>
+      <c r="K116" s="5">
+        <v>0</v>
+      </c>
+      <c r="L116" t="s">
+        <v>505</v>
+      </c>
+      <c r="M116"/>
+    </row>
+    <row r="117" s="1" customFormat="1" spans="2:13">
+      <c r="B117" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D117" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="G117" s="5">
+        <v>280</v>
+      </c>
+      <c r="H117" s="5">
+        <v>140</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="J117" s="5"/>
+      <c r="K117" s="5">
+        <v>0</v>
+      </c>
+      <c r="L117" t="s">
+        <v>510</v>
+      </c>
+      <c r="M117"/>
+    </row>
+    <row r="118" s="1" customFormat="1" spans="2:13">
+      <c r="B118" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D118" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E118" t="s">
+        <v>512</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="G118" s="5">
+        <v>600</v>
+      </c>
+      <c r="H118" s="5">
+        <v>300</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="J118" s="5"/>
+      <c r="K118" s="5">
+        <v>0</v>
+      </c>
+      <c r="L118" t="s">
+        <v>515</v>
+      </c>
+      <c r="M118"/>
+    </row>
+    <row r="119" s="1" customFormat="1" spans="2:13">
+      <c r="B119" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D119" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E119" t="s">
+        <v>517</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="G119" s="5">
+        <v>280</v>
+      </c>
+      <c r="H119" s="5">
+        <v>140</v>
+      </c>
+      <c r="I119" s="5">
+        <v>40016</v>
+      </c>
+      <c r="J119" s="5">
+        <v>10101</v>
+      </c>
+      <c r="K119" s="5">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="M119"/>
+    </row>
+    <row r="120" s="1" customFormat="1" spans="2:13">
+      <c r="B120" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D120" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E120" t="s">
+        <v>521</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="G120" s="5">
+        <v>300</v>
+      </c>
+      <c r="H120" s="5">
+        <v>150</v>
+      </c>
+      <c r="I120" s="5">
+        <v>40017</v>
+      </c>
+      <c r="J120" s="5"/>
+      <c r="K120" s="5">
+        <v>0</v>
+      </c>
+      <c r="L120" t="s">
+        <v>523</v>
+      </c>
+      <c r="M120"/>
+    </row>
+    <row r="121" s="1" customFormat="1" spans="2:13">
+      <c r="B121" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D121" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E121" t="s">
+        <v>525</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="G121" s="5">
+        <v>520</v>
+      </c>
+      <c r="H121" s="5">
+        <v>260</v>
+      </c>
+      <c r="I121" s="5">
+        <v>40018</v>
+      </c>
+      <c r="J121" s="5">
+        <v>11101</v>
+      </c>
+      <c r="K121" s="5">
+        <v>0</v>
+      </c>
+      <c r="L121" t="s">
+        <v>527</v>
+      </c>
+      <c r="M121"/>
+    </row>
+    <row r="122" s="1" customFormat="1" spans="2:13">
+      <c r="B122" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D122" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E122" t="s">
+        <v>529</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="G122" s="5">
+        <v>300</v>
+      </c>
+      <c r="H122" s="5">
+        <v>150</v>
+      </c>
+      <c r="I122" s="5">
+        <v>40019</v>
+      </c>
+      <c r="J122" s="5"/>
+      <c r="K122" s="5">
+        <v>0</v>
+      </c>
+      <c r="L122" t="s">
+        <v>531</v>
+      </c>
+      <c r="M122"/>
+    </row>
+    <row r="123" s="1" customFormat="1" spans="2:13">
+      <c r="B123" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D123" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E123" t="s">
+        <v>533</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="G123" s="5">
+        <v>620</v>
+      </c>
+      <c r="H123" s="5">
+        <v>310</v>
+      </c>
+      <c r="I123" s="5">
+        <v>40021</v>
+      </c>
+      <c r="J123" s="5"/>
+      <c r="K123" s="5">
+        <v>0</v>
+      </c>
+      <c r="L123" t="s">
+        <v>535</v>
+      </c>
+      <c r="M123"/>
+    </row>
+    <row r="124" s="1" customFormat="1" spans="2:13">
+      <c r="B124" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D124" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E124" t="s">
+        <v>537</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="G124" s="5">
+        <v>320</v>
+      </c>
+      <c r="H124" s="5">
+        <v>160</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="J124" s="5">
+        <v>11201</v>
+      </c>
+      <c r="K124" s="5">
+        <v>0</v>
+      </c>
+      <c r="L124" t="s">
+        <v>540</v>
+      </c>
+      <c r="M124"/>
+    </row>
+    <row r="125" s="1" customFormat="1" spans="2:13">
+      <c r="B125" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D125" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E125" t="s">
+        <v>542</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="G125" s="5">
+        <v>320</v>
+      </c>
+      <c r="H125" s="5">
+        <v>160</v>
+      </c>
+      <c r="I125" s="5">
+        <v>40023</v>
+      </c>
+      <c r="J125" s="5">
+        <v>11301</v>
+      </c>
+      <c r="K125" s="5">
+        <v>0</v>
+      </c>
+      <c r="L125" t="s">
+        <v>544</v>
+      </c>
+      <c r="M125"/>
+    </row>
+    <row r="126" s="1" customFormat="1" spans="2:13">
+      <c r="B126" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D126" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E126" t="s">
+        <v>546</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="G126" s="5">
+        <v>550</v>
+      </c>
+      <c r="H126" s="5">
+        <v>275</v>
+      </c>
+      <c r="I126" s="5">
+        <v>40024</v>
+      </c>
+      <c r="J126" s="5">
+        <v>11401</v>
+      </c>
+      <c r="K126" s="5">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="M126"/>
+    </row>
+    <row r="127" s="1" customFormat="1" spans="2:13">
+      <c r="B127" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C127" t="s">
+        <v>442</v>
+      </c>
+      <c r="D127" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E127" t="s">
+        <v>550</v>
+      </c>
+      <c r="F127" t="s">
+        <v>551</v>
+      </c>
+      <c r="G127" s="5">
         <v>400</v>
       </c>
-      <c r="H104" s="6">
+      <c r="H127" s="5">
         <v>200</v>
       </c>
-      <c r="I104" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J104" s="6">
-        <v>11004</v>
-      </c>
-      <c r="K104" s="6">
-        <v>0</v>
-      </c>
-      <c r="L104" s="7" t="s">
-        <v>463</v>
-      </c>
-      <c r="M104" s="7"/>
-    </row>
-    <row r="105" s="1" customFormat="1" spans="2:13">
-      <c r="B105" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D105" s="6">
+      <c r="I127" s="5">
+        <v>40026</v>
+      </c>
+      <c r="J127" s="5">
+        <v>11501</v>
+      </c>
+      <c r="K127" s="5">
+        <v>1</v>
+      </c>
+      <c r="L127" t="s">
+        <v>552</v>
+      </c>
+      <c r="M127"/>
+    </row>
+    <row r="128" s="1" customFormat="1" spans="2:13">
+      <c r="B128" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C128" t="s">
+        <v>442</v>
+      </c>
+      <c r="D128" s="5">
         <v>0.1</v>
       </c>
-      <c r="E105" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="G105" s="6">
-        <v>460</v>
-      </c>
-      <c r="H105" s="6">
-        <v>230</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6">
-        <v>0</v>
-      </c>
-      <c r="L105" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="M105" s="7"/>
-    </row>
-    <row r="106" s="1" customFormat="1" spans="2:13">
-      <c r="B106" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D106" s="6">
+      <c r="E128" t="s">
+        <v>554</v>
+      </c>
+      <c r="F128" t="s">
+        <v>555</v>
+      </c>
+      <c r="G128" s="5">
+        <v>330</v>
+      </c>
+      <c r="H128" s="5">
+        <v>165</v>
+      </c>
+      <c r="I128" s="5">
+        <v>40027</v>
+      </c>
+      <c r="J128" s="5"/>
+      <c r="K128" s="5">
+        <v>1</v>
+      </c>
+      <c r="L128" t="s">
+        <v>556</v>
+      </c>
+      <c r="M128"/>
+    </row>
+    <row r="129" s="1" customFormat="1" spans="1:13">
+      <c r="B129" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C129" t="s">
+        <v>442</v>
+      </c>
+      <c r="D129" s="5">
         <v>0.1</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="G106" s="6">
-        <v>220</v>
-      </c>
-      <c r="H106" s="6">
-        <v>110</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="J106" s="6">
-        <v>10602</v>
-      </c>
-      <c r="K106" s="6">
-        <v>0</v>
-      </c>
-      <c r="L106" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="M106" s="7"/>
-    </row>
-    <row r="107" s="1" customFormat="1" spans="2:13">
-      <c r="B107" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D107" s="6">
+      <c r="E129" t="s">
+        <v>558</v>
+      </c>
+      <c r="F129" t="s">
+        <v>559</v>
+      </c>
+      <c r="G129" s="5">
+        <v>260</v>
+      </c>
+      <c r="H129" s="5">
+        <v>130</v>
+      </c>
+      <c r="I129" s="5">
+        <v>40028</v>
+      </c>
+      <c r="J129" s="5"/>
+      <c r="K129" s="5">
+        <v>2</v>
+      </c>
+      <c r="L129" t="s">
+        <v>560</v>
+      </c>
+      <c r="M129"/>
+    </row>
+    <row r="130" s="1" customFormat="1" spans="1:13">
+      <c r="B130" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C130" t="s">
+        <v>442</v>
+      </c>
+      <c r="D130" s="5">
         <v>0.1</v>
       </c>
-      <c r="E107" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="G107" s="6">
+      <c r="E130" t="s">
+        <v>562</v>
+      </c>
+      <c r="F130" t="s">
+        <v>563</v>
+      </c>
+      <c r="G130" s="5">
+        <v>270</v>
+      </c>
+      <c r="H130" s="5">
+        <v>135</v>
+      </c>
+      <c r="I130" s="5">
+        <v>40029</v>
+      </c>
+      <c r="J130" s="5"/>
+      <c r="K130" s="5">
+        <v>2</v>
+      </c>
+      <c r="L130" t="s">
+        <v>564</v>
+      </c>
+      <c r="M130"/>
+    </row>
+    <row r="131" s="1" customFormat="1" spans="1:13">
+      <c r="B131" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C131" t="s">
+        <v>442</v>
+      </c>
+      <c r="D131" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E131" t="s">
+        <v>566</v>
+      </c>
+      <c r="F131" t="s">
+        <v>567</v>
+      </c>
+      <c r="G131" s="5">
         <v>280</v>
       </c>
-      <c r="H107" s="6">
+      <c r="H131" s="5">
         <v>140</v>
       </c>
-      <c r="I107" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6">
-        <v>0</v>
-      </c>
-      <c r="L107" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="M107" s="7"/>
-    </row>
-    <row r="108" s="1" customFormat="1" spans="2:13">
-      <c r="B108" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D108" s="6">
+      <c r="I131" s="5">
+        <v>40030</v>
+      </c>
+      <c r="J131" s="5">
+        <v>11601</v>
+      </c>
+      <c r="K131" s="5">
+        <v>0</v>
+      </c>
+      <c r="L131" t="s">
+        <v>568</v>
+      </c>
+      <c r="M131"/>
+    </row>
+    <row r="132" s="1" customFormat="1" spans="1:13">
+      <c r="A132"/>
+      <c r="B132" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C132" t="s">
+        <v>442</v>
+      </c>
+      <c r="D132" s="5">
         <v>0.1</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="G108" s="6">
+      <c r="E132" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="G132" s="1">
+        <v>320</v>
+      </c>
+      <c r="H132" s="1">
+        <v>160</v>
+      </c>
+      <c r="I132" s="5">
+        <v>40031</v>
+      </c>
+      <c r="J132" s="5"/>
+      <c r="K132" s="5">
+        <v>0</v>
+      </c>
+      <c r="L132" t="s">
+        <v>572</v>
+      </c>
+      <c r="M132"/>
+    </row>
+    <row r="133" s="1" customFormat="1" spans="1:13">
+      <c r="B133" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C133" t="s">
+        <v>442</v>
+      </c>
+      <c r="D133" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E133" t="s">
+        <v>574</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G133" s="5">
+        <v>500</v>
+      </c>
+      <c r="H133" s="5">
+        <v>250</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="L133" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="134" s="1" customFormat="1" spans="1:13">
+      <c r="B134" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C134" t="s">
+        <v>442</v>
+      </c>
+      <c r="D134" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E134" t="s">
+        <v>580</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G134" s="5">
+        <v>500</v>
+      </c>
+      <c r="H134" s="5">
+        <v>250</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="L134" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="135" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:13">
+      <c r="B135" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C135" t="s">
+        <v>442</v>
+      </c>
+      <c r="D135" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="G135" s="5">
+        <v>500</v>
+      </c>
+      <c r="H135" s="5">
+        <v>250</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5">
+        <v>0</v>
+      </c>
+      <c r="L135" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="136" s="3" customFormat="1" spans="1:13">
+      <c r="B136" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D136" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="F136" s="9"/>
+      <c r="G136" s="9">
+        <v>280</v>
+      </c>
+      <c r="H136" s="9">
+        <v>140</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="J136" s="9"/>
+      <c r="K136" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L136" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="M136" s="8"/>
+    </row>
+    <row r="137" s="3" customFormat="1" spans="1:13">
+      <c r="B137" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D137" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="F137" s="9"/>
+      <c r="G137" s="9">
+        <v>400</v>
+      </c>
+      <c r="H137" s="9">
+        <v>200</v>
+      </c>
+      <c r="I137" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="J137" s="9"/>
+      <c r="K137" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L137" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="M137" s="8"/>
+    </row>
+    <row r="138" s="3" customFormat="1" spans="1:13">
+      <c r="B138" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D138" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="F138" s="9"/>
+      <c r="G138" s="9">
+        <v>400</v>
+      </c>
+      <c r="H138" s="9">
+        <v>200</v>
+      </c>
+      <c r="I138" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="J138" s="9"/>
+      <c r="K138" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L138" s="8" t="s">
         <v>600</v>
       </c>
-      <c r="H108" s="6">
-        <v>300</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6">
-        <v>0</v>
-      </c>
-      <c r="L108" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="M108" s="7"/>
-    </row>
-    <row r="109" s="1" customFormat="1" spans="2:13">
-      <c r="B109" s="1" t="s">
-        <v>484</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D109" s="6">
+      <c r="M138" s="8"/>
+    </row>
+    <row r="139" s="3" customFormat="1" spans="1:13">
+      <c r="B139" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D139" s="9">
         <v>0.1</v>
       </c>
-      <c r="E109" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="G109" s="6">
-        <v>280</v>
-      </c>
-      <c r="H109" s="6">
-        <v>140</v>
-      </c>
-      <c r="I109" s="6">
-        <v>40016</v>
-      </c>
-      <c r="J109" s="6">
-        <v>10101</v>
-      </c>
-      <c r="K109" s="6">
-        <v>0</v>
-      </c>
-      <c r="L109" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="M109" s="7"/>
-    </row>
-    <row r="110" s="1" customFormat="1" spans="2:13">
-      <c r="B110" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D110" s="6">
+      <c r="E139" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="F139" s="9"/>
+      <c r="G139" s="9">
+        <v>400</v>
+      </c>
+      <c r="H139" s="9">
+        <v>200</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="J139" s="9"/>
+      <c r="K139" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L139" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="M139" s="8"/>
+    </row>
+    <row r="140" s="3" customFormat="1" spans="1:13">
+      <c r="B140" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D140" s="9">
         <v>0.1</v>
       </c>
-      <c r="E110" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="G110" s="6">
-        <v>300</v>
-      </c>
-      <c r="H110" s="6">
-        <v>150</v>
-      </c>
-      <c r="I110" s="6">
-        <v>40017</v>
-      </c>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6">
-        <v>0</v>
-      </c>
-      <c r="L110" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="M110" s="7"/>
-    </row>
-    <row r="111" s="1" customFormat="1" spans="2:13">
-      <c r="B111" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D111" s="6">
+      <c r="E140" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="F140" s="9"/>
+      <c r="G140" s="9">
+        <v>400</v>
+      </c>
+      <c r="H140" s="9">
+        <v>200</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="J140" s="9"/>
+      <c r="K140" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L140" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="M140" s="8"/>
+    </row>
+    <row r="141" s="3" customFormat="1" spans="1:13">
+      <c r="B141" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D141" s="9">
         <v>0.1</v>
       </c>
-      <c r="E111" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="G111" s="6">
-        <v>520</v>
-      </c>
-      <c r="H111" s="6">
-        <v>260</v>
-      </c>
-      <c r="I111" s="6">
-        <v>40018</v>
-      </c>
-      <c r="J111" s="6">
-        <v>11101</v>
-      </c>
-      <c r="K111" s="6">
-        <v>0</v>
-      </c>
-      <c r="L111" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="M111" s="7"/>
-    </row>
-    <row r="112" s="1" customFormat="1" spans="2:13">
-      <c r="B112" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D112" s="6">
+      <c r="E141" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="F141" s="9"/>
+      <c r="G141" s="9">
+        <v>350</v>
+      </c>
+      <c r="H141" s="9">
+        <v>175</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="J141" s="9"/>
+      <c r="K141" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L141" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="M141" s="8"/>
+    </row>
+    <row r="142" s="3" customFormat="1" spans="1:13">
+      <c r="B142" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D142" s="9">
         <v>0.1</v>
       </c>
-      <c r="E112" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="G112" s="6">
-        <v>300</v>
-      </c>
-      <c r="H112" s="6">
-        <v>150</v>
-      </c>
-      <c r="I112" s="6">
-        <v>40019</v>
-      </c>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6">
-        <v>0</v>
-      </c>
-      <c r="L112" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="M112" s="7"/>
-    </row>
-    <row r="113" s="1" customFormat="1" spans="1:13">
-      <c r="B113" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D113" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="G113" s="6">
-        <v>620</v>
-      </c>
-      <c r="H113" s="6">
-        <v>310</v>
-      </c>
-      <c r="I113" s="6">
-        <v>40021</v>
-      </c>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6">
-        <v>0</v>
-      </c>
-      <c r="L113" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="M113" s="7"/>
-    </row>
-    <row r="114" s="1" customFormat="1" spans="1:13">
-      <c r="B114" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D114" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="G114" s="6">
-        <v>320</v>
-      </c>
-      <c r="H114" s="6">
-        <v>160</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="J114" s="6">
-        <v>11201</v>
-      </c>
-      <c r="K114" s="6">
-        <v>0</v>
-      </c>
-      <c r="L114" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="M114" s="7"/>
-    </row>
-    <row r="115" s="1" customFormat="1" spans="1:13">
-      <c r="B115" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D115" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="G115" s="6">
-        <v>320</v>
-      </c>
-      <c r="H115" s="6">
-        <v>160</v>
-      </c>
-      <c r="I115" s="6">
-        <v>40023</v>
-      </c>
-      <c r="J115" s="6">
-        <v>11301</v>
-      </c>
-      <c r="K115" s="6">
-        <v>0</v>
-      </c>
-      <c r="L115" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="M115" s="7"/>
-    </row>
-    <row r="116" s="1" customFormat="1" spans="1:13">
-      <c r="B116" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D116" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="G116" s="6">
-        <v>550</v>
-      </c>
-      <c r="H116" s="6">
-        <v>275</v>
-      </c>
-      <c r="I116" s="6">
-        <v>40024</v>
-      </c>
-      <c r="J116" s="6">
-        <v>11401</v>
-      </c>
-      <c r="K116" s="6">
-        <v>0</v>
-      </c>
-      <c r="L116" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="M116" s="7"/>
-    </row>
-    <row r="117" s="1" customFormat="1" spans="1:13">
-      <c r="B117" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D117" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="G117" s="6">
+      <c r="E142" s="8" t="s">
+        <v>614</v>
+      </c>
+      <c r="F142" s="9"/>
+      <c r="G142" s="9">
         <v>400</v>
       </c>
-      <c r="H117" s="6">
+      <c r="H142" s="9">
         <v>200</v>
       </c>
-      <c r="I117" s="6">
-        <v>40026</v>
-      </c>
-      <c r="J117" s="6">
-        <v>11501</v>
-      </c>
-      <c r="K117" s="6">
-        <v>1</v>
-      </c>
-      <c r="L117" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="M117" s="7"/>
-    </row>
-    <row r="118" s="1" customFormat="1" spans="1:13">
-      <c r="B118" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D118" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="G118" s="6">
-        <v>330</v>
-      </c>
-      <c r="H118" s="6">
-        <v>165</v>
-      </c>
-      <c r="I118" s="6">
-        <v>40027</v>
-      </c>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6">
-        <v>1</v>
-      </c>
-      <c r="L118" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="M118" s="7"/>
-    </row>
-    <row r="119" s="1" customFormat="1" spans="1:13">
-      <c r="B119" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D119" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="G119" s="6">
-        <v>260</v>
-      </c>
-      <c r="H119" s="6">
-        <v>130</v>
-      </c>
-      <c r="I119" s="6">
-        <v>40028</v>
-      </c>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6">
-        <v>2</v>
-      </c>
-      <c r="L119" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="M119" s="7"/>
-    </row>
-    <row r="120" s="1" customFormat="1" spans="1:13">
-      <c r="B120" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D120" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="G120" s="6">
-        <v>270</v>
-      </c>
-      <c r="H120" s="6">
-        <v>135</v>
-      </c>
-      <c r="I120" s="6">
-        <v>40029</v>
-      </c>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6">
-        <v>2</v>
-      </c>
-      <c r="L120" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="M120" s="7"/>
-    </row>
-    <row r="121" s="1" customFormat="1" spans="1:13">
-      <c r="B121" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D121" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="G121" s="6">
-        <v>280</v>
-      </c>
-      <c r="H121" s="6">
-        <v>140</v>
-      </c>
-      <c r="I121" s="6">
-        <v>40030</v>
-      </c>
-      <c r="J121" s="6">
-        <v>11601</v>
-      </c>
-      <c r="K121" s="6">
-        <v>0</v>
-      </c>
-      <c r="L121" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="M121" s="7"/>
-    </row>
-    <row r="122" s="1" customFormat="1" spans="1:13">
-      <c r="A122" s="7"/>
-      <c r="B122" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D122" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="G122" s="1">
-        <v>320</v>
-      </c>
-      <c r="H122" s="1">
-        <v>160</v>
-      </c>
-      <c r="I122" s="6">
-        <v>40031</v>
-      </c>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6">
-        <v>0</v>
-      </c>
-      <c r="L122" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="M122" s="7"/>
-    </row>
-    <row r="123" s="1" customFormat="1" spans="1:13">
-      <c r="B123" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D123" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="G123" s="6">
-        <v>500</v>
-      </c>
-      <c r="H123" s="6">
-        <v>250</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="L123" s="7" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="124" s="1" customFormat="1" spans="1:13">
-      <c r="B124" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D124" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="G124" s="6">
-        <v>500</v>
-      </c>
-      <c r="H124" s="6">
-        <v>250</v>
-      </c>
-      <c r="I124" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="L124" s="7" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="125" s="1" customFormat="1" spans="1:13">
-      <c r="B125" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="C125" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D125" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="G125" s="6">
-        <v>500</v>
-      </c>
-      <c r="H125" s="6">
-        <v>250</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6">
-        <v>0</v>
-      </c>
-      <c r="L125" s="7" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="126" s="1" customFormat="1" spans="1:13">
-      <c r="C126" s="10"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="6"/>
-      <c r="G126" s="6"/>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="6"/>
-      <c r="M126" s="7"/>
-    </row>
-    <row r="127" s="1" customFormat="1" spans="1:13">
-      <c r="C127" s="10"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="6"/>
-      <c r="F127" s="6"/>
-      <c r="G127" s="6"/>
-      <c r="H127" s="6"/>
-      <c r="I127" s="6"/>
-      <c r="J127" s="6"/>
-      <c r="K127" s="1"/>
-      <c r="L127" s="6"/>
-      <c r="M127" s="7"/>
-    </row>
-    <row r="128" s="1" customFormat="1" spans="1:13">
-      <c r="C128" s="10"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="6"/>
-      <c r="I128" s="6"/>
-      <c r="J128" s="6"/>
-      <c r="K128" s="1"/>
-      <c r="L128" s="6"/>
-      <c r="M128" s="7"/>
-    </row>
-    <row r="129" s="1" customFormat="1" spans="3:13">
-      <c r="C129" s="10"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="6"/>
-      <c r="F129" s="6"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="6"/>
-      <c r="I129" s="6"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="1"/>
-      <c r="L129" s="6"/>
-      <c r="M129" s="7"/>
-    </row>
-    <row r="130" s="1" customFormat="1" spans="3:13">
-      <c r="C130" s="10"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="6"/>
-      <c r="F130" s="6"/>
-      <c r="G130" s="6"/>
-      <c r="H130" s="6"/>
-      <c r="I130" s="6"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="1"/>
-      <c r="L130" s="6"/>
-      <c r="M130" s="7"/>
-    </row>
-    <row r="131" s="1" customFormat="1" spans="3:13">
-      <c r="C131" s="10"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="6"/>
-      <c r="F131" s="6"/>
-      <c r="G131" s="6"/>
-      <c r="H131" s="6"/>
-      <c r="I131" s="6"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="1"/>
-      <c r="L131" s="6"/>
-      <c r="M131" s="7"/>
-    </row>
-    <row r="132" s="1" customFormat="1" spans="3:13">
-      <c r="C132" s="10"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="6"/>
-      <c r="F132" s="6"/>
-      <c r="G132" s="6"/>
-      <c r="H132" s="6"/>
-      <c r="I132" s="6"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="1"/>
-      <c r="L132" s="6"/>
-      <c r="M132" s="7"/>
-    </row>
-    <row r="133" s="1" customFormat="1" spans="3:13">
-      <c r="C133" s="10"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="6"/>
-      <c r="F133" s="6"/>
-      <c r="G133" s="6"/>
-      <c r="H133" s="6"/>
-      <c r="I133" s="6"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="1"/>
-      <c r="L133" s="6"/>
-      <c r="M133" s="7"/>
-    </row>
-    <row r="134" s="1" customFormat="1" spans="3:13">
-      <c r="C134" s="10"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="6"/>
-      <c r="G134" s="6"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="1"/>
-      <c r="L134" s="6"/>
-      <c r="M134" s="7"/>
-    </row>
-    <row r="135" s="1" customFormat="1" spans="3:13">
-      <c r="C135" s="10"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="6"/>
-      <c r="F135" s="6"/>
-      <c r="G135" s="6"/>
-      <c r="H135" s="6"/>
-      <c r="I135" s="6"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="1"/>
-      <c r="L135" s="6"/>
-      <c r="M135" s="7"/>
-    </row>
-    <row r="136" s="1" customFormat="1" spans="3:13">
-      <c r="C136" s="10"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
-      <c r="G136" s="6"/>
-      <c r="H136" s="6"/>
-      <c r="I136" s="6"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="1"/>
-      <c r="L136" s="6"/>
-      <c r="M136" s="7"/>
-    </row>
-    <row r="137" s="1" customFormat="1" spans="3:13">
-      <c r="C137" s="10"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="6"/>
-      <c r="G137" s="6"/>
-      <c r="H137" s="6"/>
-      <c r="I137" s="6"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="1"/>
-      <c r="L137" s="6"/>
-      <c r="M137" s="7"/>
+      <c r="I142" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="J142" s="9"/>
+      <c r="K142" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="L142" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="M142" s="8"/>
+    </row>
+    <row r="143" s="1" customFormat="1" spans="1:13">
+      <c r="D143" s="5"/>
+      <c r="E143" s="5"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+      <c r="K143" s="1"/>
+      <c r="L143" s="5"/>
+      <c r="M143"/>
+    </row>
+    <row r="144" s="1" customFormat="1" spans="1:13">
+      <c r="D144" s="5"/>
+      <c r="E144" s="5"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+      <c r="K144" s="1"/>
+      <c r="L144" s="5"/>
+      <c r="M144"/>
+    </row>
+    <row r="145" s="1" customFormat="1" spans="4:13">
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="5"/>
+      <c r="K145" s="1"/>
+      <c r="L145" s="5"/>
+      <c r="M145"/>
+    </row>
+    <row r="146" s="1" customFormat="1" spans="4:13">
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="1"/>
+      <c r="L146" s="5"/>
+      <c r="M146"/>
+    </row>
+    <row r="147" s="1" customFormat="1" spans="4:13">
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
+      <c r="K147" s="1"/>
+      <c r="L147" s="5"/>
+      <c r="M147"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="16005" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="634">
   <si>
     <t>##var</t>
   </si>
@@ -907,6 +907,9 @@
     <t>疯狂猴子</t>
   </si>
   <si>
+    <t>CrazyMonkey</t>
+  </si>
+  <si>
     <t>20036|20037</t>
   </si>
   <si>
@@ -919,6 +922,9 @@
     <t>贪婪</t>
   </si>
   <si>
+    <t>Greed</t>
+  </si>
+  <si>
     <t>20038</t>
   </si>
   <si>
@@ -1288,6 +1294,9 @@
     <t>倍率叠加</t>
   </si>
   <si>
+    <t>MultiplierStacking</t>
+  </si>
+  <si>
     <t>30033</t>
   </si>
   <si>
@@ -1297,6 +1306,9 @@
     <t>力量叠加</t>
   </si>
   <si>
+    <t>PowerStacking</t>
+  </si>
+  <si>
     <t>30034</t>
   </si>
   <si>
@@ -1306,6 +1318,9 @@
     <t>召唤</t>
   </si>
   <si>
+    <t>Summon</t>
+  </si>
+  <si>
     <t>30035</t>
   </si>
   <si>
@@ -1315,6 +1330,9 @@
     <t>国王领域</t>
   </si>
   <si>
+    <t>KingdomDomain</t>
+  </si>
+  <si>
     <t>30036</t>
   </si>
   <si>
@@ -1324,6 +1342,9 @@
     <t>皇后领域</t>
   </si>
   <si>
+    <t>QueenDomain</t>
+  </si>
+  <si>
     <t>30037</t>
   </si>
   <si>
@@ -1333,6 +1354,9 @@
     <t>复制</t>
   </si>
   <si>
+    <t>Copy</t>
+  </si>
+  <si>
     <t>30038</t>
   </si>
   <si>
@@ -1342,6 +1366,9 @@
     <t>借花献佛</t>
   </si>
   <si>
+    <t>BorrowFlowerPresentBuddha</t>
+  </si>
+  <si>
     <t>30039</t>
   </si>
   <si>
@@ -1351,6 +1378,9 @@
     <t>妙手</t>
   </si>
   <si>
+    <t>MagicHand</t>
+  </si>
+  <si>
     <t>30040</t>
   </si>
   <si>
@@ -1807,6 +1837,9 @@
     <t>高档甜品</t>
   </si>
   <si>
+    <t>HighGradeDessert</t>
+  </si>
+  <si>
     <t>40032</t>
   </si>
   <si>
@@ -1819,6 +1852,9 @@
     <t>第六感</t>
   </si>
   <si>
+    <t>SixthSense</t>
+  </si>
+  <si>
     <t>40033</t>
   </si>
   <si>
@@ -1831,6 +1867,9 @@
     <t>炸弹恶魔</t>
   </si>
   <si>
+    <t>BombDemon</t>
+  </si>
+  <si>
     <t>40034</t>
   </si>
   <si>
@@ -1843,6 +1882,9 @@
     <t>消费主义</t>
   </si>
   <si>
+    <t>Consumerism</t>
+  </si>
+  <si>
     <t>40035</t>
   </si>
   <si>
@@ -1855,6 +1897,9 @@
     <t>高档饮品</t>
   </si>
   <si>
+    <t>HighGradeDrink</t>
+  </si>
+  <si>
     <t>40036</t>
   </si>
   <si>
@@ -1867,6 +1912,9 @@
     <t>幸运之子</t>
   </si>
   <si>
+    <t>LuckyChild</t>
+  </si>
+  <si>
     <t>40037</t>
   </si>
   <si>
@@ -1877,6 +1925,9 @@
   </si>
   <si>
     <t>万能A</t>
+  </si>
+  <si>
+    <t>UniversalA</t>
   </si>
   <si>
     <t>40038</t>
@@ -4959,7 +5010,9 @@
       <c r="E62" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="F62" s="9"/>
+      <c r="F62" s="9" t="s">
+        <v>291</v>
+      </c>
       <c r="G62" s="9">
         <v>150</v>
       </c>
@@ -4967,21 +5020,21 @@
         <v>75</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J62" s="9"/>
       <c r="K62" s="9">
         <v>0</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M62" s="8"/>
     </row>
     <row r="63" s="3" customFormat="1" spans="1:13">
       <c r="A63" s="8"/>
       <c r="B63" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>114</v>
@@ -4990,9 +5043,11 @@
         <v>0.4</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="F63" s="9"/>
+        <v>295</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>296</v>
+      </c>
       <c r="G63" s="9">
         <v>110</v>
       </c>
@@ -5000,14 +5055,14 @@
         <v>55</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J63" s="9"/>
       <c r="K63" s="9">
         <v>0</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M63" s="8"/>
     </row>
@@ -5032,16 +5087,16 @@
         <v>301</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D65" s="5">
         <v>0.2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G65" s="1">
         <v>190</v>
@@ -5050,7 +5105,7 @@
         <v>95</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J65" s="5">
         <v>10401</v>
@@ -5059,7 +5114,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M65"/>
     </row>
@@ -5069,16 +5124,16 @@
         <v>302</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D66" s="5">
         <v>0.2</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G66" s="1">
         <v>270</v>
@@ -5087,14 +5142,14 @@
         <v>135</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5">
         <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M66"/>
     </row>
@@ -5104,16 +5159,16 @@
         <v>303</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D67" s="5">
         <v>0.2</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G67" s="1">
         <v>190</v>
@@ -5122,7 +5177,7 @@
         <v>95</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J67" s="5">
         <v>10501</v>
@@ -5131,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M67"/>
     </row>
@@ -5141,16 +5196,16 @@
         <v>304</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D68" s="5">
         <v>0.2</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G68" s="1">
         <v>160</v>
@@ -5159,7 +5214,7 @@
         <v>80</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J68" s="5">
         <v>10601</v>
@@ -5168,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:13">
@@ -5177,16 +5232,16 @@
         <v>305</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D69" s="5">
         <v>0.2</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G69" s="1">
         <v>170</v>
@@ -5195,7 +5250,7 @@
         <v>85</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J69" s="5">
         <v>10701</v>
@@ -5204,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:13">
@@ -5212,16 +5267,16 @@
         <v>306</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D70" s="5">
         <v>0.2</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G70" s="1">
         <v>240</v>
@@ -5230,13 +5285,13 @@
         <v>120</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:13">
@@ -5244,16 +5299,16 @@
         <v>307</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D71" s="5">
         <v>0.2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G71" s="1">
         <v>280</v>
@@ -5262,14 +5317,14 @@
         <v>140</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5">
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:13">
@@ -5277,16 +5332,16 @@
         <v>308</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D72" s="5">
         <v>0.2</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G72" s="1">
         <v>270</v>
@@ -5295,13 +5350,13 @@
         <v>135</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K72" s="5">
         <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:13">
@@ -5309,16 +5364,16 @@
         <v>309</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D73" s="5">
         <v>0.2</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G73" s="1">
         <v>275</v>
@@ -5327,14 +5382,14 @@
         <v>137</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J73" s="5"/>
       <c r="K73" s="5">
         <v>0</v>
       </c>
       <c r="L73" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:13">
@@ -5342,16 +5397,16 @@
         <v>310</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D74" s="5">
         <v>0.2</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G74" s="1">
         <v>170</v>
@@ -5360,13 +5415,13 @@
         <v>85</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K74" s="5">
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:13">
@@ -5374,16 +5429,16 @@
         <v>311</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D75" s="5">
         <v>0.2</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G75" s="1">
         <v>130</v>
@@ -5392,13 +5447,13 @@
         <v>65</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K75" s="5">
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:13">
@@ -5406,16 +5461,16 @@
         <v>312</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D76" s="5">
         <v>0.2</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G76" s="1">
         <v>160</v>
@@ -5424,14 +5479,14 @@
         <v>80</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="5">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:13">
@@ -5439,16 +5494,16 @@
         <v>313</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D77" s="5">
         <v>0.2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G77" s="5">
         <v>120</v>
@@ -5457,14 +5512,14 @@
         <v>60</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J77" s="5"/>
       <c r="K77" s="5">
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:13">
@@ -5472,16 +5527,16 @@
         <v>314</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D78" s="5">
         <v>0.2</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G78" s="5">
         <v>380</v>
@@ -5490,14 +5545,14 @@
         <v>190</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J78" s="5"/>
       <c r="K78" s="5">
         <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" spans="1:13">
@@ -5505,16 +5560,16 @@
         <v>315</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D79" s="5">
         <v>0.2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G79" s="5">
         <v>170</v>
@@ -5523,14 +5578,14 @@
         <v>85</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J79" s="5"/>
       <c r="K79" s="5">
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M79"/>
     </row>
@@ -5539,16 +5594,16 @@
         <v>316</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D80" s="5">
         <v>0.2</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G80" s="5">
         <v>200</v>
@@ -5557,7 +5612,7 @@
         <v>100</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J80" s="5">
         <v>10201</v>
@@ -5566,7 +5621,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M80"/>
     </row>
@@ -5575,16 +5630,16 @@
         <v>317</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D81" s="5">
         <v>0.2</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G81" s="5">
         <v>170</v>
@@ -5593,7 +5648,7 @@
         <v>85</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J81" s="5">
         <v>10801</v>
@@ -5602,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M81"/>
     </row>
@@ -5611,16 +5666,16 @@
         <v>318</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D82" s="5">
         <v>0.2</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G82" s="5">
         <v>160</v>
@@ -5629,7 +5684,7 @@
         <v>80</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J82" s="5">
         <v>10402</v>
@@ -5638,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M82"/>
     </row>
@@ -5647,16 +5702,16 @@
         <v>319</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D83" s="5">
         <v>0.2</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G83" s="5">
         <v>160</v>
@@ -5665,14 +5720,14 @@
         <v>80</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J83" s="5"/>
       <c r="K83" s="5">
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M83"/>
     </row>
@@ -5681,16 +5736,16 @@
         <v>320</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D84" s="5">
         <v>0.2</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G84" s="5">
         <v>160</v>
@@ -5699,14 +5754,14 @@
         <v>80</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J84" s="5"/>
       <c r="K84" s="5">
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M84"/>
     </row>
@@ -5715,16 +5770,16 @@
         <v>321</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D85" s="5">
         <v>0.2</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G85" s="5">
         <v>160</v>
@@ -5733,14 +5788,14 @@
         <v>80</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="5">
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M85"/>
     </row>
@@ -5749,16 +5804,16 @@
         <v>322</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D86" s="5">
         <v>0.2</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G86" s="5">
         <v>190</v>
@@ -5767,14 +5822,14 @@
         <v>95</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="5">
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M86"/>
     </row>
@@ -5783,16 +5838,16 @@
         <v>323</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D87" s="5">
         <v>0.2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G87" s="5">
         <v>175</v>
@@ -5801,14 +5856,14 @@
         <v>87</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J87" s="5"/>
       <c r="K87" s="5">
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="M87"/>
     </row>
@@ -5817,16 +5872,16 @@
         <v>324</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D88" s="5">
         <v>0.2</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G88" s="5">
         <v>270</v>
@@ -5835,7 +5890,7 @@
         <v>135</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J88" s="5">
         <v>10502</v>
@@ -5844,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M88"/>
     </row>
@@ -5853,16 +5908,16 @@
         <v>325</v>
       </c>
       <c r="C89" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D89" s="5">
         <v>0.2</v>
       </c>
       <c r="E89" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F89" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G89" s="5">
         <v>160</v>
@@ -5871,14 +5926,14 @@
         <v>80</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J89" s="5"/>
       <c r="K89" s="5">
         <v>2</v>
       </c>
       <c r="L89" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="M89"/>
     </row>
@@ -5887,16 +5942,16 @@
         <v>326</v>
       </c>
       <c r="C90" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D90" s="5">
         <v>0.2</v>
       </c>
       <c r="E90" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F90" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G90" s="5">
         <v>200</v>
@@ -5905,7 +5960,7 @@
         <v>100</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J90" s="5">
         <v>10901</v>
@@ -5914,7 +5969,7 @@
         <v>2</v>
       </c>
       <c r="L90" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M90"/>
     </row>
@@ -5923,16 +5978,16 @@
         <v>327</v>
       </c>
       <c r="C91" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D91" s="5">
         <v>0.2</v>
       </c>
       <c r="E91" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F91" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G91" s="5">
         <v>170</v>
@@ -5941,14 +5996,14 @@
         <v>85</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J91" s="5"/>
       <c r="K91" s="5">
         <v>1</v>
       </c>
       <c r="L91" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M91"/>
     </row>
@@ -5957,16 +6012,16 @@
         <v>328</v>
       </c>
       <c r="C92" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D92" s="5">
         <v>0.2</v>
       </c>
       <c r="E92" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F92" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G92" s="5">
         <v>160</v>
@@ -5975,14 +6030,14 @@
         <v>80</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="5">
         <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M92"/>
     </row>
@@ -5991,16 +6046,16 @@
         <v>329</v>
       </c>
       <c r="C93" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D93" s="5">
         <v>0.2</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F93" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G93" s="5">
         <v>200</v>
@@ -6009,7 +6064,7 @@
         <v>100</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J93" s="7">
         <v>11005</v>
@@ -6018,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" ht="14.25" customHeight="1" spans="2:13">
@@ -6026,16 +6081,16 @@
         <v>330</v>
       </c>
       <c r="C94" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D94" s="5">
         <v>0.2</v>
       </c>
       <c r="E94" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G94" s="5">
         <v>300</v>
@@ -6051,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M94"/>
     </row>
@@ -6060,15 +6115,17 @@
         <v>331</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D95" s="9">
         <v>0.2</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="F95" s="9"/>
+        <v>419</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>420</v>
+      </c>
       <c r="G95" s="9">
         <v>260</v>
       </c>
@@ -6076,14 +6133,14 @@
         <v>130</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J95" s="9"/>
       <c r="K95" s="9">
         <v>0</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="96" s="3" customFormat="1" spans="2:13">
@@ -6091,15 +6148,17 @@
         <v>332</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D96" s="9">
         <v>0.2</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="F96" s="9"/>
+        <v>423</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>424</v>
+      </c>
       <c r="G96" s="9">
         <v>260</v>
       </c>
@@ -6107,14 +6166,14 @@
         <v>130</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="J96" s="9"/>
       <c r="K96" s="9">
         <v>0</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="97" s="3" customFormat="1" spans="2:12">
@@ -6122,15 +6181,17 @@
         <v>333</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D97" s="9">
         <v>0.2</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="F97" s="9"/>
+        <v>427</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>428</v>
+      </c>
       <c r="G97" s="9">
         <v>260</v>
       </c>
@@ -6138,14 +6199,14 @@
         <v>130</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="J97" s="9"/>
       <c r="K97" s="9">
         <v>0</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="98" s="3" customFormat="1" spans="2:12">
@@ -6153,15 +6214,17 @@
         <v>334</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D98" s="9">
         <v>0.2</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="F98" s="9"/>
+        <v>431</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>432</v>
+      </c>
       <c r="G98" s="9">
         <v>250</v>
       </c>
@@ -6169,14 +6232,14 @@
         <v>125</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J98" s="9"/>
       <c r="K98" s="9">
         <v>0</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="99" s="3" customFormat="1" spans="2:12">
@@ -6184,15 +6247,17 @@
         <v>335</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D99" s="9">
         <v>0.2</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="F99" s="9"/>
+        <v>435</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>436</v>
+      </c>
       <c r="G99" s="9">
         <v>250</v>
       </c>
@@ -6200,14 +6265,14 @@
         <v>125</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="J99" s="9"/>
       <c r="K99" s="9">
         <v>0</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="100" s="3" customFormat="1" spans="2:12">
@@ -6215,15 +6280,17 @@
         <v>336</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D100" s="9">
         <v>0.2</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="F100" s="9"/>
+        <v>439</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>440</v>
+      </c>
       <c r="G100" s="9">
         <v>260</v>
       </c>
@@ -6231,14 +6298,14 @@
         <v>130</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="J100" s="9"/>
       <c r="K100" s="9">
         <v>0</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="101" s="3" customFormat="1" spans="2:12">
@@ -6246,15 +6313,17 @@
         <v>337</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D101" s="9">
         <v>0.2</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="F101" s="9"/>
+        <v>443</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>444</v>
+      </c>
       <c r="G101" s="9">
         <v>260</v>
       </c>
@@ -6262,14 +6331,14 @@
         <v>130</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="J101" s="9"/>
       <c r="K101" s="9">
         <v>0</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="102" s="3" customFormat="1" spans="2:12">
@@ -6277,15 +6346,17 @@
         <v>338</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D102" s="9">
         <v>0.2</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="F102" s="9"/>
+        <v>447</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>448</v>
+      </c>
       <c r="G102" s="9">
         <v>240</v>
       </c>
@@ -6293,14 +6364,14 @@
         <v>120</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="J102" s="9"/>
       <c r="K102" s="9">
         <v>0</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="2:12">
@@ -6315,10 +6386,10 @@
     </row>
     <row r="104" s="1" customFormat="1" spans="2:12">
       <c r="B104" s="1" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D104" s="5">
         <v>0.1</v>
@@ -6327,7 +6398,7 @@
         <v>235</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="G104" s="5">
         <v>650</v>
@@ -6336,7 +6407,7 @@
         <v>325</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="J104" s="5">
         <v>11001</v>
@@ -6345,24 +6416,24 @@
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="2:12">
       <c r="B105" s="1" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D105" s="5">
         <v>0.1</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="G105" s="5">
         <v>680</v>
@@ -6371,31 +6442,31 @@
         <v>340</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="J105" s="5"/>
       <c r="K105" s="5">
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="2:12">
       <c r="B106" s="1" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D106" s="5">
         <v>0.1</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="G106" s="5">
         <v>600</v>
@@ -6404,30 +6475,30 @@
         <v>300</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="2:12">
       <c r="B107" s="1" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D107" s="5">
         <v>0.1</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="G107" s="5">
         <v>480</v>
@@ -6436,7 +6507,7 @@
         <v>240</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="J107" s="5">
         <v>11002</v>
@@ -6445,24 +6516,24 @@
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="2:12">
       <c r="B108" s="1" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D108" s="5">
         <v>0.1</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="G108" s="5">
         <v>460</v>
@@ -6471,31 +6542,31 @@
         <v>230</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="5">
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="2:12">
       <c r="B109" s="1" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D109" s="5">
         <v>0.1</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="G109" s="5">
         <v>320</v>
@@ -6504,30 +6575,30 @@
         <v>160</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" spans="2:12">
       <c r="B110" s="1" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D110" s="5">
         <v>0.1</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="G110" s="5">
         <v>380</v>
@@ -6536,7 +6607,7 @@
         <v>190</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="J110" s="5">
         <v>11003</v>
@@ -6545,24 +6616,24 @@
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="2:12">
       <c r="B111" s="1" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D111" s="5">
         <v>0.1</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="G111" s="5">
         <v>600</v>
@@ -6571,31 +6642,31 @@
         <v>300</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="5">
         <v>0</v>
       </c>
       <c r="L111" s="5" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="2:12">
       <c r="B112" s="1" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D112" s="5">
         <v>0.1</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="G112" s="5">
         <v>280</v>
@@ -6604,30 +6675,30 @@
         <v>140</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="K112" s="5">
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" spans="2:13">
       <c r="B113" s="1" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D113" s="5">
         <v>0.1</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="G113" s="5">
         <v>300</v>
@@ -6636,30 +6707,30 @@
         <v>150</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" spans="2:13">
       <c r="B114" s="1" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D114" s="5">
         <v>0.1</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="G114" s="5">
         <v>400</v>
@@ -6668,7 +6739,7 @@
         <v>200</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="J114" s="5">
         <v>11004</v>
@@ -6677,25 +6748,25 @@
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="M114"/>
     </row>
     <row r="115" s="1" customFormat="1" spans="2:13">
       <c r="B115" s="1" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D115" s="5">
         <v>0.1</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="G115" s="5">
         <v>460</v>
@@ -6704,32 +6775,32 @@
         <v>230</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="5">
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="M115"/>
     </row>
     <row r="116" s="1" customFormat="1" spans="2:13">
       <c r="B116" s="1" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D116" s="5">
         <v>0.1</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="G116" s="5">
         <v>220</v>
@@ -6738,7 +6809,7 @@
         <v>110</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="J116" s="5">
         <v>10602</v>
@@ -6747,25 +6818,25 @@
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="M116"/>
     </row>
     <row r="117" s="1" customFormat="1" spans="2:13">
       <c r="B117" s="1" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D117" s="5">
         <v>0.1</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="G117" s="5">
         <v>280</v>
@@ -6774,32 +6845,32 @@
         <v>140</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="5">
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M117"/>
     </row>
     <row r="118" s="1" customFormat="1" spans="2:13">
       <c r="B118" s="1" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D118" s="5">
         <v>0.1</v>
       </c>
       <c r="E118" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="G118" s="5">
         <v>600</v>
@@ -6808,32 +6879,32 @@
         <v>300</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="J118" s="5"/>
       <c r="K118" s="5">
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="M118"/>
     </row>
     <row r="119" s="1" customFormat="1" spans="2:13">
       <c r="B119" s="1" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D119" s="5">
         <v>0.1</v>
       </c>
       <c r="E119" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="G119" s="5">
         <v>280</v>
@@ -6851,25 +6922,25 @@
         <v>0</v>
       </c>
       <c r="L119" s="5" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="M119"/>
     </row>
     <row r="120" s="1" customFormat="1" spans="2:13">
       <c r="B120" s="1" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D120" s="5">
         <v>0.1</v>
       </c>
       <c r="E120" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="G120" s="5">
         <v>300</v>
@@ -6885,25 +6956,25 @@
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="M120"/>
     </row>
     <row r="121" s="1" customFormat="1" spans="2:13">
       <c r="B121" s="1" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D121" s="5">
         <v>0.1</v>
       </c>
       <c r="E121" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="G121" s="5">
         <v>520</v>
@@ -6921,25 +6992,25 @@
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="M121"/>
     </row>
     <row r="122" s="1" customFormat="1" spans="2:13">
       <c r="B122" s="1" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D122" s="5">
         <v>0.1</v>
       </c>
       <c r="E122" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="G122" s="5">
         <v>300</v>
@@ -6955,25 +7026,25 @@
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="M122"/>
     </row>
     <row r="123" s="1" customFormat="1" spans="2:13">
       <c r="B123" s="1" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D123" s="5">
         <v>0.1</v>
       </c>
       <c r="E123" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="G123" s="5">
         <v>620</v>
@@ -6989,25 +7060,25 @@
         <v>0</v>
       </c>
       <c r="L123" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="M123"/>
     </row>
     <row r="124" s="1" customFormat="1" spans="2:13">
       <c r="B124" s="1" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D124" s="5">
         <v>0.1</v>
       </c>
       <c r="E124" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="G124" s="5">
         <v>320</v>
@@ -7016,7 +7087,7 @@
         <v>160</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="J124" s="5">
         <v>11201</v>
@@ -7025,25 +7096,25 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="M124"/>
     </row>
     <row r="125" s="1" customFormat="1" spans="2:13">
       <c r="B125" s="1" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D125" s="5">
         <v>0.1</v>
       </c>
       <c r="E125" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="G125" s="5">
         <v>320</v>
@@ -7061,25 +7132,25 @@
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="M125"/>
     </row>
     <row r="126" s="1" customFormat="1" spans="2:13">
       <c r="B126" s="1" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D126" s="5">
         <v>0.1</v>
       </c>
       <c r="E126" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="G126" s="5">
         <v>550</v>
@@ -7097,25 +7168,25 @@
         <v>0</v>
       </c>
       <c r="L126" s="5" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="M126"/>
     </row>
     <row r="127" s="1" customFormat="1" spans="2:13">
       <c r="B127" s="1" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="C127" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D127" s="5">
         <v>0.1</v>
       </c>
       <c r="E127" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="F127" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="G127" s="5">
         <v>400</v>
@@ -7133,25 +7204,25 @@
         <v>1</v>
       </c>
       <c r="L127" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="M127"/>
     </row>
     <row r="128" s="1" customFormat="1" spans="2:13">
       <c r="B128" s="1" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="C128" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D128" s="5">
         <v>0.1</v>
       </c>
       <c r="E128" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="F128" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="G128" s="5">
         <v>330</v>
@@ -7167,25 +7238,25 @@
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="M128"/>
     </row>
     <row r="129" s="1" customFormat="1" spans="1:13">
       <c r="B129" s="1" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="C129" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D129" s="5">
         <v>0.1</v>
       </c>
       <c r="E129" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="F129" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="G129" s="5">
         <v>260</v>
@@ -7201,25 +7272,25 @@
         <v>2</v>
       </c>
       <c r="L129" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="M129"/>
     </row>
     <row r="130" s="1" customFormat="1" spans="1:13">
       <c r="B130" s="1" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="C130" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D130" s="5">
         <v>0.1</v>
       </c>
       <c r="E130" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="F130" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="G130" s="5">
         <v>270</v>
@@ -7235,25 +7306,25 @@
         <v>2</v>
       </c>
       <c r="L130" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="M130"/>
     </row>
     <row r="131" s="1" customFormat="1" spans="1:13">
       <c r="B131" s="1" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="C131" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D131" s="5">
         <v>0.1</v>
       </c>
       <c r="E131" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="F131" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="G131" s="5">
         <v>280</v>
@@ -7271,26 +7342,26 @@
         <v>0</v>
       </c>
       <c r="L131" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="M131"/>
     </row>
     <row r="132" s="1" customFormat="1" spans="1:13">
       <c r="A132"/>
       <c r="B132" s="1" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="C132" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D132" s="5">
         <v>0.1</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="G132" s="1">
         <v>320</v>
@@ -7306,25 +7377,25 @@
         <v>0</v>
       </c>
       <c r="L132" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="M132"/>
     </row>
     <row r="133" s="1" customFormat="1" spans="1:13">
       <c r="B133" s="1" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="C133" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D133" s="5">
         <v>0.1</v>
       </c>
       <c r="E133" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="G133" s="5">
         <v>500</v>
@@ -7333,30 +7404,30 @@
         <v>250</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L133" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" spans="1:13">
       <c r="B134" s="1" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="C134" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D134" s="5">
         <v>0.1</v>
       </c>
       <c r="E134" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="G134" s="5">
         <v>500</v>
@@ -7365,30 +7436,30 @@
         <v>250</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L134" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:13">
       <c r="B135" s="1" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="C135" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D135" s="5">
         <v>0.1</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="G135" s="5">
         <v>500</v>
@@ -7397,30 +7468,32 @@
         <v>250</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5">
         <v>0</v>
       </c>
       <c r="L135" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
     </row>
     <row r="136" s="3" customFormat="1" spans="1:13">
       <c r="B136" s="3" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D136" s="9">
         <v>0.1</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="F136" s="9"/>
+        <v>600</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>601</v>
+      </c>
       <c r="G136" s="9">
         <v>280</v>
       </c>
@@ -7428,31 +7501,33 @@
         <v>140</v>
       </c>
       <c r="I136" s="9" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="J136" s="9"/>
       <c r="K136" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L136" s="8" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="M136" s="8"/>
     </row>
     <row r="137" s="3" customFormat="1" spans="1:13">
       <c r="B137" s="3" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D137" s="9">
         <v>0.1</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>594</v>
-      </c>
-      <c r="F137" s="9"/>
+        <v>605</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>606</v>
+      </c>
       <c r="G137" s="9">
         <v>400</v>
       </c>
@@ -7460,31 +7535,33 @@
         <v>200</v>
       </c>
       <c r="I137" s="9" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="J137" s="9"/>
       <c r="K137" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L137" s="8" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="M137" s="8"/>
     </row>
     <row r="138" s="3" customFormat="1" spans="1:13">
       <c r="B138" s="3" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D138" s="9">
         <v>0.1</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="F138" s="9"/>
+        <v>610</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>611</v>
+      </c>
       <c r="G138" s="9">
         <v>400</v>
       </c>
@@ -7492,31 +7569,33 @@
         <v>200</v>
       </c>
       <c r="I138" s="9" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="J138" s="9"/>
       <c r="K138" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L138" s="8" t="s">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="M138" s="8"/>
     </row>
     <row r="139" s="3" customFormat="1" spans="1:13">
       <c r="B139" s="3" t="s">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D139" s="9">
         <v>0.1</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>602</v>
-      </c>
-      <c r="F139" s="9"/>
+        <v>615</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>616</v>
+      </c>
       <c r="G139" s="9">
         <v>400</v>
       </c>
@@ -7524,31 +7603,33 @@
         <v>200</v>
       </c>
       <c r="I139" s="9" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="J139" s="9"/>
       <c r="K139" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L139" s="8" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="M139" s="8"/>
     </row>
     <row r="140" s="3" customFormat="1" spans="1:13">
       <c r="B140" s="3" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D140" s="9">
         <v>0.1</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>606</v>
-      </c>
-      <c r="F140" s="9"/>
+        <v>620</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>621</v>
+      </c>
       <c r="G140" s="9">
         <v>400</v>
       </c>
@@ -7556,31 +7637,33 @@
         <v>200</v>
       </c>
       <c r="I140" s="9" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
       <c r="J140" s="9"/>
       <c r="K140" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L140" s="8" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="M140" s="8"/>
     </row>
     <row r="141" s="3" customFormat="1" spans="1:13">
       <c r="B141" s="3" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D141" s="9">
         <v>0.1</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="F141" s="9"/>
+        <v>625</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>626</v>
+      </c>
       <c r="G141" s="9">
         <v>350</v>
       </c>
@@ -7588,31 +7671,33 @@
         <v>175</v>
       </c>
       <c r="I141" s="9" t="s">
-        <v>611</v>
+        <v>627</v>
       </c>
       <c r="J141" s="9"/>
       <c r="K141" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L141" s="8" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="M141" s="8"/>
     </row>
     <row r="142" s="3" customFormat="1" spans="1:13">
       <c r="B142" s="3" t="s">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="D142" s="9">
         <v>0.1</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="F142" s="9"/>
+        <v>630</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>631</v>
+      </c>
       <c r="G142" s="9">
         <v>400</v>
       </c>
@@ -7620,14 +7705,14 @@
         <v>200</v>
       </c>
       <c r="I142" s="9" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="J142" s="9"/>
       <c r="K142" s="3" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="L142" s="8" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="M142" s="8"/>
     </row>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="637">
   <si>
     <t>##var</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Desc</t>
   </si>
   <si>
+    <t>SpecialDesc</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -118,6 +121,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>特殊描述</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
@@ -131,6 +137,9 @@
   </si>
   <si>
     <t>结算时提供+1倍率</t>
+  </si>
+  <si>
+    <t>玩家通用冒险证明</t>
   </si>
   <si>
     <t>102</t>
@@ -2994,98 +3003,107 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>16</v>
+      <c r="M2" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:13">
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5">
         <v>0.8</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5" s="5">
         <v>45</v>
@@ -3101,25 +3119,27 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5"/>
+        <v>34</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:13">
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" s="5">
         <v>0.8</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G6" s="5">
         <v>28</v>
@@ -3135,25 +3155,27 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6"/>
+        <v>39</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:13">
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5">
         <v>0.8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G7" s="5">
         <v>28</v>
@@ -3169,25 +3191,27 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7"/>
+        <v>43</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:13">
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" s="5">
         <v>0.8</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G8" s="5">
         <v>28</v>
@@ -3203,25 +3227,27 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8"/>
+        <v>47</v>
+      </c>
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:13">
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" s="5">
         <v>0.8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G9" s="5">
         <v>28</v>
@@ -3237,25 +3263,27 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9"/>
+        <v>51</v>
+      </c>
+      <c r="M9" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:13">
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" s="5">
         <v>0.8</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="5">
         <v>28</v>
@@ -3271,25 +3299,27 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>52</v>
-      </c>
-      <c r="M10"/>
+        <v>55</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:13">
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="5">
         <v>0.8</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G11" s="5">
         <v>22</v>
@@ -3305,25 +3335,27 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11"/>
+        <v>59</v>
+      </c>
+      <c r="M11" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:13">
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12" s="5">
         <v>0.8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G12" s="5">
         <v>35</v>
@@ -3339,25 +3371,27 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>60</v>
-      </c>
-      <c r="M12"/>
+        <v>63</v>
+      </c>
+      <c r="M12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:13">
       <c r="B13" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13" s="5">
         <v>0.8</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G13" s="5">
         <v>16</v>
@@ -3373,25 +3407,27 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>64</v>
-      </c>
-      <c r="M13"/>
+        <v>67</v>
+      </c>
+      <c r="M13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:13">
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="5">
         <v>0.8</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" s="5">
         <v>16</v>
@@ -3407,25 +3443,27 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>68</v>
-      </c>
-      <c r="M14"/>
+        <v>71</v>
+      </c>
+      <c r="M14" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:13">
       <c r="B15" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5">
         <v>0.8</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G15" s="5">
         <v>15</v>
@@ -3441,25 +3479,27 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>72</v>
-      </c>
-      <c r="M15"/>
+        <v>75</v>
+      </c>
+      <c r="M15" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:13">
       <c r="B16" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" s="5">
         <v>0.8</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G16" s="5">
         <v>30</v>
@@ -3475,24 +3515,27 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>76</v>
+        <v>79</v>
+      </c>
+      <c r="M16" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:13">
       <c r="B17" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5">
         <v>0.8</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G17" s="5">
         <v>35</v>
@@ -3508,24 +3551,27 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="M17" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:13">
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" s="5">
         <v>0.8</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G18" s="5">
         <v>26</v>
@@ -3541,24 +3587,27 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="M18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:13">
       <c r="B19" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D19" s="5">
         <v>0.8</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G19" s="5">
         <v>22</v>
@@ -3574,24 +3623,27 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="M19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:13">
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D20" s="5">
         <v>0.8</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G20" s="5">
         <v>28</v>
@@ -3607,24 +3659,27 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="M20" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:13">
       <c r="B21" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="5">
         <v>0.8</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G21" s="5">
         <v>20</v>
@@ -3640,24 +3695,27 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>96</v>
+        <v>99</v>
+      </c>
+      <c r="M21" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:13">
       <c r="B22" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D22" s="5">
         <v>0.8</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G22" s="5">
         <v>25</v>
@@ -3673,25 +3731,27 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>100</v>
-      </c>
-      <c r="M22"/>
+        <v>103</v>
+      </c>
+      <c r="M22" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:13">
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D23" s="5">
         <v>0.8</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G23" s="5">
         <v>25</v>
@@ -3707,25 +3767,27 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>104</v>
-      </c>
-      <c r="M23"/>
+        <v>107</v>
+      </c>
+      <c r="M23" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:13">
       <c r="B24" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="5">
         <v>0.8</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G24" s="5">
         <v>30</v>
@@ -3741,25 +3803,27 @@
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>108</v>
-      </c>
-      <c r="M24"/>
+        <v>111</v>
+      </c>
+      <c r="M24" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:13">
       <c r="B25" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" s="5">
         <v>0.8</v>
       </c>
       <c r="E25" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G25" s="5">
         <v>35</v>
@@ -3775,9 +3839,11 @@
         <v>2</v>
       </c>
       <c r="L25" t="s">
-        <v>112</v>
-      </c>
-      <c r="M25"/>
+        <v>115</v>
+      </c>
+      <c r="M25" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:13">
       <c r="D26" s="5"/>
@@ -3793,19 +3859,19 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="1:13">
       <c r="B27" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D27" s="5">
         <v>0.4</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G27" s="1">
         <v>115</v>
@@ -3814,32 +3880,34 @@
         <v>57</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5">
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>118</v>
-      </c>
-      <c r="M27"/>
+        <v>121</v>
+      </c>
+      <c r="M27" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:13">
       <c r="B28" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D28" s="5">
         <v>0.4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G28" s="1">
         <v>115</v>
@@ -3848,33 +3916,35 @@
         <v>57</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5">
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>123</v>
-      </c>
-      <c r="M28"/>
+        <v>126</v>
+      </c>
+      <c r="M28" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:13">
       <c r="A29"/>
       <c r="B29" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D29" s="5">
         <v>0.4</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G29" s="1">
         <v>115</v>
@@ -3883,33 +3953,35 @@
         <v>57</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5">
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>128</v>
-      </c>
-      <c r="M29"/>
+        <v>131</v>
+      </c>
+      <c r="M29" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:13">
       <c r="A30"/>
       <c r="B30" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D30" s="5">
         <v>0.4</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G30" s="1">
         <v>115</v>
@@ -3918,33 +3990,35 @@
         <v>57</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5">
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>133</v>
-      </c>
-      <c r="M30"/>
+        <v>136</v>
+      </c>
+      <c r="M30" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:13">
       <c r="A31"/>
       <c r="B31" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D31" s="5">
         <v>0.4</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G31" s="1">
         <v>120</v>
@@ -3953,33 +4027,35 @@
         <v>60</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5">
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>138</v>
-      </c>
-      <c r="M31"/>
+        <v>141</v>
+      </c>
+      <c r="M31" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:13">
       <c r="A32"/>
       <c r="B32" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D32" s="5">
         <v>0.4</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G32" s="1">
         <v>100</v>
@@ -3988,33 +4064,35 @@
         <v>50</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5">
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>143</v>
-      </c>
-      <c r="M32"/>
+        <v>146</v>
+      </c>
+      <c r="M32" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
       <c r="A33"/>
       <c r="B33" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D33" s="5">
         <v>0.4</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G33" s="1">
         <v>155</v>
@@ -4023,33 +4101,35 @@
         <v>77</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5">
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>148</v>
-      </c>
-      <c r="M33"/>
+        <v>151</v>
+      </c>
+      <c r="M33" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:13">
       <c r="A34"/>
       <c r="B34" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D34" s="5">
         <v>0.4</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G34" s="1">
         <v>75</v>
@@ -4058,33 +4138,35 @@
         <v>37</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5">
         <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>153</v>
-      </c>
-      <c r="M34"/>
+        <v>156</v>
+      </c>
+      <c r="M34" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:13">
       <c r="A35"/>
       <c r="B35" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D35" s="5">
         <v>0.4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G35" s="1">
         <v>75</v>
@@ -4093,33 +4175,35 @@
         <v>37</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5">
         <v>0</v>
       </c>
       <c r="L35" t="s">
-        <v>158</v>
-      </c>
-      <c r="M35"/>
+        <v>161</v>
+      </c>
+      <c r="M35" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="36" s="2" customFormat="1" spans="1:13">
       <c r="A36" s="6"/>
       <c r="B36" s="1" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D36" s="7">
         <v>0.4</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G36" s="2">
         <v>140</v>
@@ -4128,33 +4212,35 @@
         <v>70</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J36" s="7"/>
       <c r="K36" s="7">
         <v>0</v>
       </c>
       <c r="L36" t="s">
-        <v>163</v>
-      </c>
-      <c r="M36" s="6"/>
+        <v>166</v>
+      </c>
+      <c r="M36" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:13">
       <c r="A37"/>
       <c r="B37" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D37" s="5">
         <v>0.4</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G37" s="1">
         <v>80</v>
@@ -4163,33 +4249,35 @@
         <v>40</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5">
         <v>0</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="M37"/>
+        <v>171</v>
+      </c>
+      <c r="M37" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="38" s="2" customFormat="1" spans="1:13">
       <c r="A38" s="6"/>
       <c r="B38" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D38" s="7">
         <v>0.4</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G38" s="2">
         <v>135</v>
@@ -4198,33 +4286,35 @@
         <v>67</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="M38" s="6"/>
+        <v>176</v>
+      </c>
+      <c r="M38" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:13">
       <c r="A39"/>
       <c r="B39" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D39" s="5">
         <v>0.4</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G39" s="1">
         <v>70</v>
@@ -4233,33 +4323,35 @@
         <v>35</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5">
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>178</v>
-      </c>
-      <c r="M39"/>
+        <v>181</v>
+      </c>
+      <c r="M39" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:13">
       <c r="A40"/>
       <c r="B40" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D40" s="5">
         <v>0.4</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G40" s="1">
         <v>110</v>
@@ -4268,31 +4360,34 @@
         <v>55</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K40" s="5">
         <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>183</v>
+        <v>186</v>
+      </c>
+      <c r="M40" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:13">
       <c r="A41"/>
       <c r="B41" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D41" s="5">
         <v>0.4</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G41" s="1">
         <v>110</v>
@@ -4301,31 +4396,34 @@
         <v>55</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>188</v>
+        <v>191</v>
+      </c>
+      <c r="M41" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:13">
       <c r="A42"/>
       <c r="B42" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D42" s="5">
         <v>0.4</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G42" s="1">
         <v>115</v>
@@ -4334,31 +4432,34 @@
         <v>57</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>193</v>
+        <v>196</v>
+      </c>
+      <c r="M42" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
       <c r="A43"/>
       <c r="B43" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D43" s="5">
         <v>0.4</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G43" s="1">
         <v>60</v>
@@ -4367,31 +4468,34 @@
         <v>30</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>198</v>
+        <v>201</v>
+      </c>
+      <c r="M43" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:13">
       <c r="A44"/>
       <c r="B44" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D44" s="5">
         <v>0.4</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G44" s="5">
         <v>85</v>
@@ -4400,32 +4504,35 @@
         <v>42</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5">
         <v>0</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>203</v>
+        <v>206</v>
+      </c>
+      <c r="M44" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:13">
       <c r="A45"/>
       <c r="B45" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D45" s="5">
         <v>0.4</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G45" s="5">
         <v>75</v>
@@ -4434,32 +4541,35 @@
         <v>37</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5">
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>208</v>
+        <v>211</v>
+      </c>
+      <c r="M45" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:13">
       <c r="A46"/>
       <c r="B46" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D46" s="5">
         <v>0.4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G46" s="5">
         <v>75</v>
@@ -4468,32 +4578,35 @@
         <v>37</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5">
         <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>213</v>
+        <v>216</v>
+      </c>
+      <c r="M46" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:13">
       <c r="A47"/>
       <c r="B47" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D47" s="5">
         <v>0.4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G47" s="5">
         <v>70</v>
@@ -4502,32 +4615,35 @@
         <v>35</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5">
         <v>0</v>
       </c>
       <c r="L47" t="s">
-        <v>218</v>
+        <v>221</v>
+      </c>
+      <c r="M47" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:13">
       <c r="A48"/>
       <c r="B48" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D48" s="5">
         <v>0.4</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G48" s="5">
         <v>75</v>
@@ -4536,31 +4652,34 @@
         <v>37</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5">
         <v>0</v>
       </c>
       <c r="L48" t="s">
-        <v>223</v>
+        <v>226</v>
+      </c>
+      <c r="M48" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:13">
       <c r="B49" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D49" s="5">
         <v>0.4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G49" s="5">
         <v>90</v>
@@ -4569,7 +4688,7 @@
         <v>45</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J49" s="5">
         <v>10301</v>
@@ -4578,26 +4697,28 @@
         <v>0</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="M49"/>
+        <v>231</v>
+      </c>
+      <c r="M49" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="50" s="1" customFormat="1" spans="1:13">
       <c r="A50"/>
       <c r="B50" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D50" s="5">
         <v>0.4</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G50" s="5">
         <v>120</v>
@@ -4606,33 +4727,35 @@
         <v>60</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5">
         <v>0</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="M50"/>
+        <v>236</v>
+      </c>
+      <c r="M50" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:13">
       <c r="A51"/>
       <c r="B51" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D51" s="5">
         <v>0.4</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G51" s="5">
         <v>110</v>
@@ -4641,33 +4764,35 @@
         <v>55</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5">
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>238</v>
-      </c>
-      <c r="M51"/>
+        <v>241</v>
+      </c>
+      <c r="M51" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:13">
       <c r="A52"/>
       <c r="B52" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D52" s="5">
         <v>0.4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G52" s="5">
         <v>70</v>
@@ -4676,32 +4801,34 @@
         <v>35</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5">
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>243</v>
-      </c>
-      <c r="M52"/>
+        <v>246</v>
+      </c>
+      <c r="M52" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:13">
       <c r="B53" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D53" s="5">
         <v>0.4</v>
       </c>
       <c r="E53" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F53" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G53" s="5">
         <v>90</v>
@@ -4710,32 +4837,34 @@
         <v>45</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5">
         <v>1</v>
       </c>
       <c r="L53" t="s">
-        <v>248</v>
-      </c>
-      <c r="M53"/>
+        <v>251</v>
+      </c>
+      <c r="M53" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:13">
       <c r="B54" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D54" s="5">
         <v>0.4</v>
       </c>
       <c r="E54" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F54" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G54" s="5">
         <v>145</v>
@@ -4744,32 +4873,34 @@
         <v>72</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5">
         <v>1</v>
       </c>
       <c r="L54" t="s">
-        <v>253</v>
-      </c>
-      <c r="M54"/>
+        <v>256</v>
+      </c>
+      <c r="M54" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:13">
       <c r="B55" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D55" s="5">
         <v>0.4</v>
       </c>
       <c r="E55" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F55" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G55" s="5">
         <v>95</v>
@@ -4778,32 +4909,34 @@
         <v>47</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5">
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>258</v>
-      </c>
-      <c r="M55"/>
+        <v>261</v>
+      </c>
+      <c r="M55" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:13">
       <c r="B56" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D56" s="5">
         <v>0.4</v>
       </c>
       <c r="E56" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F56" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G56" s="5">
         <v>110</v>
@@ -4812,32 +4945,34 @@
         <v>55</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5">
         <v>1</v>
       </c>
       <c r="L56" t="s">
-        <v>263</v>
-      </c>
-      <c r="M56"/>
+        <v>266</v>
+      </c>
+      <c r="M56" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:13">
       <c r="B57" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D57" s="5">
         <v>0.4</v>
       </c>
       <c r="E57" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F57" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G57" s="5">
         <v>160</v>
@@ -4846,32 +4981,34 @@
         <v>80</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>268</v>
-      </c>
-      <c r="M57"/>
+        <v>271</v>
+      </c>
+      <c r="M57" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:13">
       <c r="B58" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D58" s="5">
         <v>0.4</v>
       </c>
       <c r="E58" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F58" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G58" s="5">
         <v>160</v>
@@ -4880,33 +5017,35 @@
         <v>80</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5">
         <v>2</v>
       </c>
       <c r="L58" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="M58"/>
+        <v>276</v>
+      </c>
+      <c r="M58" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:13">
       <c r="A59"/>
       <c r="B59" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D59" s="5">
         <v>0.4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F59" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G59" s="5">
         <v>80</v>
@@ -4915,33 +5054,35 @@
         <v>40</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5">
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>278</v>
-      </c>
-      <c r="M59"/>
+        <v>281</v>
+      </c>
+      <c r="M59" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:13">
       <c r="A60"/>
       <c r="B60" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D60" s="5">
         <v>0.4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F60" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G60" s="5">
         <v>80</v>
@@ -4950,33 +5091,35 @@
         <v>40</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5">
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>283</v>
-      </c>
-      <c r="M60"/>
+        <v>286</v>
+      </c>
+      <c r="M60" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="61" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:13">
       <c r="A61"/>
       <c r="B61" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D61" s="5">
         <v>0.4</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F61" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G61" s="5">
         <v>80</v>
@@ -4985,33 +5128,35 @@
         <v>40</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5">
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>288</v>
-      </c>
-      <c r="M61"/>
+        <v>291</v>
+      </c>
+      <c r="M61" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:13">
       <c r="A62" s="8"/>
       <c r="B62" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D62" s="9">
         <v>0.4</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G62" s="9">
         <v>150</v>
@@ -5020,33 +5165,35 @@
         <v>75</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J62" s="9"/>
       <c r="K62" s="9">
         <v>0</v>
       </c>
       <c r="L62" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="M62" s="8"/>
+        <v>296</v>
+      </c>
+      <c r="M62" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="63" s="3" customFormat="1" spans="1:13">
       <c r="A63" s="8"/>
       <c r="B63" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D63" s="9">
         <v>0.4</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G63" s="9">
         <v>110</v>
@@ -5055,16 +5202,18 @@
         <v>55</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J63" s="9"/>
       <c r="K63" s="9">
         <v>0</v>
       </c>
       <c r="L63" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="M63" s="8"/>
+        <v>301</v>
+      </c>
+      <c r="M63" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:13">
       <c r="A64"/>
@@ -5087,16 +5236,16 @@
         <v>301</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D65" s="5">
         <v>0.2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G65" s="1">
         <v>210</v>
@@ -5105,7 +5254,7 @@
         <v>105</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J65" s="5">
         <v>10401</v>
@@ -5114,9 +5263,11 @@
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>303</v>
-      </c>
-      <c r="M65"/>
+        <v>306</v>
+      </c>
+      <c r="M65" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:13">
       <c r="A66"/>
@@ -5124,16 +5275,16 @@
         <v>302</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D66" s="5">
         <v>0.2</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G66" s="1">
         <v>265</v>
@@ -5142,16 +5293,18 @@
         <v>132</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5">
         <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>307</v>
-      </c>
-      <c r="M66"/>
+        <v>310</v>
+      </c>
+      <c r="M66" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:13">
       <c r="A67"/>
@@ -5159,16 +5312,16 @@
         <v>303</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D67" s="5">
         <v>0.2</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G67" s="1">
         <v>210</v>
@@ -5177,7 +5330,7 @@
         <v>105</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J67" s="5">
         <v>10501</v>
@@ -5186,9 +5339,11 @@
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>311</v>
-      </c>
-      <c r="M67"/>
+        <v>314</v>
+      </c>
+      <c r="M67" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:13">
       <c r="A68"/>
@@ -5196,16 +5351,16 @@
         <v>304</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D68" s="5">
         <v>0.2</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G68" s="1">
         <v>190</v>
@@ -5214,7 +5369,7 @@
         <v>95</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J68" s="5">
         <v>10601</v>
@@ -5223,7 +5378,10 @@
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>315</v>
+        <v>318</v>
+      </c>
+      <c r="M68" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:13">
@@ -5232,16 +5390,16 @@
         <v>305</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D69" s="5">
         <v>0.2</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G69" s="1">
         <v>200</v>
@@ -5250,7 +5408,7 @@
         <v>100</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J69" s="5">
         <v>10701</v>
@@ -5259,7 +5417,10 @@
         <v>0</v>
       </c>
       <c r="L69" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="M69" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:13">
@@ -5267,16 +5428,16 @@
         <v>306</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D70" s="5">
         <v>0.2</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G70" s="1">
         <v>245</v>
@@ -5285,13 +5446,16 @@
         <v>122</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K70" s="5">
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>323</v>
+        <v>326</v>
+      </c>
+      <c r="M70" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:13">
@@ -5299,16 +5463,16 @@
         <v>307</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D71" s="5">
         <v>0.2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G71" s="1">
         <v>275</v>
@@ -5317,14 +5481,17 @@
         <v>137</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5">
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>327</v>
+        <v>330</v>
+      </c>
+      <c r="M71" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:13">
@@ -5332,16 +5499,16 @@
         <v>308</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D72" s="5">
         <v>0.2</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G72" s="1">
         <v>265</v>
@@ -5350,13 +5517,16 @@
         <v>132</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K72" s="5">
         <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>331</v>
+        <v>334</v>
+      </c>
+      <c r="M72" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:13">
@@ -5364,16 +5534,16 @@
         <v>309</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D73" s="5">
         <v>0.2</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G73" s="1">
         <v>270</v>
@@ -5382,14 +5552,17 @@
         <v>135</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J73" s="5"/>
       <c r="K73" s="5">
         <v>0</v>
       </c>
       <c r="L73" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
+      </c>
+      <c r="M73" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:13">
@@ -5397,16 +5570,16 @@
         <v>310</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D74" s="5">
         <v>0.2</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G74" s="1">
         <v>200</v>
@@ -5415,13 +5588,16 @@
         <v>100</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K74" s="5">
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>339</v>
+        <v>342</v>
+      </c>
+      <c r="M74" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:13">
@@ -5429,16 +5605,16 @@
         <v>311</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D75" s="5">
         <v>0.2</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G75" s="1">
         <v>170</v>
@@ -5447,13 +5623,16 @@
         <v>85</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K75" s="5">
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>343</v>
+        <v>346</v>
+      </c>
+      <c r="M75" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:13">
@@ -5461,16 +5640,16 @@
         <v>312</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D76" s="5">
         <v>0.2</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G76" s="1">
         <v>190</v>
@@ -5479,14 +5658,17 @@
         <v>95</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="5">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>347</v>
+        <v>350</v>
+      </c>
+      <c r="M76" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:13">
@@ -5494,16 +5676,16 @@
         <v>313</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D77" s="5">
         <v>0.2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="G77" s="5">
         <v>165</v>
@@ -5512,14 +5694,17 @@
         <v>82</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J77" s="5"/>
       <c r="K77" s="5">
         <v>0</v>
       </c>
       <c r="L77" t="s">
-        <v>351</v>
+        <v>354</v>
+      </c>
+      <c r="M77" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:13">
@@ -5527,16 +5712,16 @@
         <v>314</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D78" s="5">
         <v>0.2</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="G78" s="5">
         <v>340</v>
@@ -5545,14 +5730,17 @@
         <v>170</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J78" s="5"/>
       <c r="K78" s="5">
         <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>355</v>
+        <v>358</v>
+      </c>
+      <c r="M78" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" spans="1:13">
@@ -5560,16 +5748,16 @@
         <v>315</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D79" s="5">
         <v>0.2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="G79" s="5">
         <v>200</v>
@@ -5578,32 +5766,34 @@
         <v>100</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J79" s="5"/>
       <c r="K79" s="5">
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>359</v>
-      </c>
-      <c r="M79"/>
+        <v>362</v>
+      </c>
+      <c r="M79" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="80" s="1" customFormat="1" spans="1:13">
       <c r="B80" s="5">
         <v>316</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D80" s="5">
         <v>0.2</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G80" s="5">
         <v>220</v>
@@ -5612,7 +5802,7 @@
         <v>110</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J80" s="5">
         <v>10201</v>
@@ -5621,25 +5811,27 @@
         <v>0</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="M80"/>
+        <v>366</v>
+      </c>
+      <c r="M80" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="81" s="1" customFormat="1" spans="2:13">
       <c r="B81" s="5">
         <v>317</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D81" s="5">
         <v>0.2</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G81" s="5">
         <v>200</v>
@@ -5648,7 +5840,7 @@
         <v>100</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J81" s="5">
         <v>10801</v>
@@ -5657,25 +5849,27 @@
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>367</v>
-      </c>
-      <c r="M81"/>
+        <v>370</v>
+      </c>
+      <c r="M81" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="82" s="1" customFormat="1" spans="2:13">
       <c r="B82" s="5">
         <v>318</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D82" s="5">
         <v>0.2</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G82" s="5">
         <v>190</v>
@@ -5684,7 +5878,7 @@
         <v>95</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J82" s="5">
         <v>10402</v>
@@ -5693,25 +5887,27 @@
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>371</v>
-      </c>
-      <c r="M82"/>
+        <v>374</v>
+      </c>
+      <c r="M82" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="83" s="1" customFormat="1" spans="2:13">
       <c r="B83" s="5">
         <v>319</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D83" s="5">
         <v>0.2</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G83" s="5">
         <v>190</v>
@@ -5720,32 +5916,34 @@
         <v>95</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J83" s="5"/>
       <c r="K83" s="5">
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>375</v>
-      </c>
-      <c r="M83"/>
+        <v>378</v>
+      </c>
+      <c r="M83" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="84" s="1" customFormat="1" spans="2:13">
       <c r="B84" s="5">
         <v>320</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D84" s="5">
         <v>0.2</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G84" s="5">
         <v>190</v>
@@ -5754,32 +5952,34 @@
         <v>95</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J84" s="5"/>
       <c r="K84" s="5">
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>379</v>
-      </c>
-      <c r="M84"/>
+        <v>382</v>
+      </c>
+      <c r="M84" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="85" s="1" customFormat="1" spans="2:13">
       <c r="B85" s="5">
         <v>321</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D85" s="5">
         <v>0.2</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G85" s="5">
         <v>190</v>
@@ -5788,32 +5988,34 @@
         <v>95</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J85" s="5"/>
       <c r="K85" s="5">
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>383</v>
-      </c>
-      <c r="M85"/>
+        <v>386</v>
+      </c>
+      <c r="M85" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="86" s="1" customFormat="1" spans="2:13">
       <c r="B86" s="5">
         <v>322</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D86" s="5">
         <v>0.2</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G86" s="5">
         <v>210</v>
@@ -5822,32 +6024,34 @@
         <v>105</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="5">
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>387</v>
-      </c>
-      <c r="M86"/>
+        <v>390</v>
+      </c>
+      <c r="M86" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="87" s="1" customFormat="1" spans="2:13">
       <c r="B87" s="5">
         <v>323</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D87" s="5">
         <v>0.2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G87" s="5">
         <v>200</v>
@@ -5856,32 +6060,34 @@
         <v>100</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J87" s="5"/>
       <c r="K87" s="5">
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>391</v>
-      </c>
-      <c r="M87"/>
+        <v>394</v>
+      </c>
+      <c r="M87" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="88" s="1" customFormat="1" spans="2:13">
       <c r="B88" s="5">
         <v>324</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D88" s="5">
         <v>0.2</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="G88" s="5">
         <v>265</v>
@@ -5890,7 +6096,7 @@
         <v>132</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="J88" s="5">
         <v>10502</v>
@@ -5899,25 +6105,27 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>395</v>
-      </c>
-      <c r="M88"/>
+        <v>398</v>
+      </c>
+      <c r="M88" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="89" s="1" customFormat="1" spans="2:13">
       <c r="B89" s="5">
         <v>325</v>
       </c>
       <c r="C89" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D89" s="5">
         <v>0.2</v>
       </c>
       <c r="E89" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F89" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G89" s="5">
         <v>190</v>
@@ -5926,32 +6134,34 @@
         <v>95</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="J89" s="5"/>
       <c r="K89" s="5">
         <v>2</v>
       </c>
       <c r="L89" t="s">
-        <v>399</v>
-      </c>
-      <c r="M89"/>
+        <v>402</v>
+      </c>
+      <c r="M89" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="90" s="1" customFormat="1" spans="2:13">
       <c r="B90" s="5">
         <v>326</v>
       </c>
       <c r="C90" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D90" s="5">
         <v>0.2</v>
       </c>
       <c r="E90" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F90" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G90" s="5">
         <v>220</v>
@@ -5960,7 +6170,7 @@
         <v>110</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J90" s="5">
         <v>10901</v>
@@ -5969,25 +6179,27 @@
         <v>2</v>
       </c>
       <c r="L90" t="s">
-        <v>403</v>
-      </c>
-      <c r="M90"/>
+        <v>406</v>
+      </c>
+      <c r="M90" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="91" s="1" customFormat="1" spans="2:13">
       <c r="B91" s="5">
         <v>327</v>
       </c>
       <c r="C91" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D91" s="5">
         <v>0.2</v>
       </c>
       <c r="E91" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F91" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G91" s="5">
         <v>200</v>
@@ -5996,32 +6208,34 @@
         <v>100</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J91" s="5"/>
       <c r="K91" s="5">
         <v>1</v>
       </c>
       <c r="L91" t="s">
-        <v>407</v>
-      </c>
-      <c r="M91"/>
+        <v>410</v>
+      </c>
+      <c r="M91" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="92" s="1" customFormat="1" spans="2:13">
       <c r="B92" s="5">
         <v>328</v>
       </c>
       <c r="C92" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D92" s="5">
         <v>0.2</v>
       </c>
       <c r="E92" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F92" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G92" s="5">
         <v>190</v>
@@ -6030,32 +6244,34 @@
         <v>95</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="5">
         <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>411</v>
-      </c>
-      <c r="M92"/>
+        <v>414</v>
+      </c>
+      <c r="M92" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="2:13">
       <c r="B93" s="5">
         <v>329</v>
       </c>
       <c r="C93" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D93" s="5">
         <v>0.2</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F93" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G93" s="5">
         <v>220</v>
@@ -6064,7 +6280,7 @@
         <v>110</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J93" s="7">
         <v>11005</v>
@@ -6073,7 +6289,10 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>415</v>
+        <v>418</v>
+      </c>
+      <c r="M93" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" ht="14.25" customHeight="1" spans="2:13">
@@ -6081,16 +6300,16 @@
         <v>330</v>
       </c>
       <c r="C94" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D94" s="5">
         <v>0.2</v>
       </c>
       <c r="E94" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G94" s="5">
         <v>285</v>
@@ -6106,25 +6325,27 @@
         <v>0</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="M94"/>
+        <v>421</v>
+      </c>
+      <c r="M94" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="95" s="3" customFormat="1" spans="2:13">
       <c r="B95" s="9">
         <v>331</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D95" s="9">
         <v>0.2</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G95" s="9">
         <v>260</v>
@@ -6133,14 +6354,17 @@
         <v>130</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="J95" s="9"/>
       <c r="K95" s="9">
         <v>0</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>422</v>
+        <v>425</v>
+      </c>
+      <c r="M95" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="96" s="3" customFormat="1" spans="2:13">
@@ -6148,16 +6372,16 @@
         <v>332</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D96" s="9">
         <v>0.2</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G96" s="9">
         <v>260</v>
@@ -6166,31 +6390,34 @@
         <v>130</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="J96" s="9"/>
       <c r="K96" s="9">
         <v>0</v>
       </c>
       <c r="L96" s="8" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="97" s="3" customFormat="1" spans="2:12">
+        <v>429</v>
+      </c>
+      <c r="M96" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="97" s="3" customFormat="1" spans="2:13">
       <c r="B97" s="9">
         <v>333</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D97" s="9">
         <v>0.2</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G97" s="9">
         <v>260</v>
@@ -6199,31 +6426,34 @@
         <v>130</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J97" s="9"/>
       <c r="K97" s="9">
         <v>0</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="98" s="3" customFormat="1" spans="2:12">
+        <v>433</v>
+      </c>
+      <c r="M97" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="98" s="3" customFormat="1" spans="2:13">
       <c r="B98" s="9">
         <v>334</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D98" s="9">
         <v>0.2</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G98" s="9">
         <v>255</v>
@@ -6232,31 +6462,34 @@
         <v>127</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J98" s="9"/>
       <c r="K98" s="9">
         <v>0</v>
       </c>
       <c r="L98" s="8" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="99" s="3" customFormat="1" spans="2:12">
+        <v>437</v>
+      </c>
+      <c r="M98" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" s="3" customFormat="1" spans="2:13">
       <c r="B99" s="9">
         <v>335</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D99" s="9">
         <v>0.2</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G99" s="9">
         <v>255</v>
@@ -6265,31 +6498,34 @@
         <v>127</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J99" s="9"/>
       <c r="K99" s="9">
         <v>0</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="100" s="3" customFormat="1" spans="2:12">
+        <v>441</v>
+      </c>
+      <c r="M99" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" s="3" customFormat="1" spans="2:13">
       <c r="B100" s="9">
         <v>336</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D100" s="9">
         <v>0.2</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G100" s="9">
         <v>260</v>
@@ -6298,31 +6534,34 @@
         <v>130</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="J100" s="9"/>
       <c r="K100" s="9">
         <v>0</v>
       </c>
       <c r="L100" s="8" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="101" s="3" customFormat="1" spans="2:12">
+        <v>445</v>
+      </c>
+      <c r="M100" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="101" s="3" customFormat="1" spans="2:13">
       <c r="B101" s="9">
         <v>337</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D101" s="9">
         <v>0.2</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G101" s="9">
         <v>260</v>
@@ -6331,31 +6570,34 @@
         <v>130</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J101" s="9"/>
       <c r="K101" s="9">
         <v>0</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="102" s="3" customFormat="1" spans="2:12">
+        <v>449</v>
+      </c>
+      <c r="M101" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102" s="3" customFormat="1" spans="2:13">
       <c r="B102" s="9">
         <v>338</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D102" s="9">
         <v>0.2</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G102" s="9">
         <v>245</v>
@@ -6364,17 +6606,20 @@
         <v>122</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="J102" s="9"/>
       <c r="K102" s="9">
         <v>0</v>
       </c>
       <c r="L102" s="8" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="2:12">
+        <v>453</v>
+      </c>
+      <c r="M102" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="2:13">
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
@@ -6384,12 +6629,12 @@
       <c r="K103" s="5"/>
       <c r="L103" s="5"/>
     </row>
-    <row r="104" s="1" customFormat="1" spans="2:12">
+    <row r="104" s="1" customFormat="1" spans="2:13">
       <c r="B104" s="1" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D104" s="5">
         <v>0.1</v>
@@ -6398,7 +6643,7 @@
         <v>235</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="G104" s="5">
         <v>660</v>
@@ -6407,7 +6652,7 @@
         <v>330</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="J104" s="5">
         <v>11001</v>
@@ -6416,24 +6661,27 @@
         <v>0</v>
       </c>
       <c r="L104" t="s">
+        <v>458</v>
+      </c>
+      <c r="M104" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="2:13">
+      <c r="B105" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>455</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" spans="2:12">
-      <c r="B105" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="D105" s="5">
         <v>0.1</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G105" s="5">
         <v>585</v>
@@ -6442,31 +6690,34 @@
         <v>292</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="J105" s="5"/>
       <c r="K105" s="5">
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="1" spans="2:12">
+        <v>463</v>
+      </c>
+      <c r="M105" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" spans="2:13">
       <c r="B106" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D106" s="5">
         <v>0.1</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="G106" s="5">
         <v>625</v>
@@ -6475,30 +6726,33 @@
         <v>312</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K106" s="5">
         <v>0</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" spans="2:12">
+        <v>468</v>
+      </c>
+      <c r="M106" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" spans="2:13">
       <c r="B107" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D107" s="5">
         <v>0.1</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G107" s="5">
         <v>535</v>
@@ -6507,7 +6761,7 @@
         <v>267</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="J107" s="5">
         <v>11002</v>
@@ -6516,24 +6770,27 @@
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" spans="2:12">
+        <v>473</v>
+      </c>
+      <c r="M107" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" spans="2:13">
       <c r="B108" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D108" s="5">
         <v>0.1</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G108" s="5">
         <v>520</v>
@@ -6542,31 +6799,34 @@
         <v>260</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J108" s="5"/>
       <c r="K108" s="5">
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" spans="2:12">
+        <v>478</v>
+      </c>
+      <c r="M108" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" spans="2:13">
       <c r="B109" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D109" s="5">
         <v>0.1</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G109" s="5">
         <v>420</v>
@@ -6575,30 +6835,33 @@
         <v>210</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K109" s="5">
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" spans="2:12">
+        <v>483</v>
+      </c>
+      <c r="M109" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" spans="2:13">
       <c r="B110" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D110" s="5">
         <v>0.1</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G110" s="5">
         <v>465</v>
@@ -6607,7 +6870,7 @@
         <v>232</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J110" s="5">
         <v>11003</v>
@@ -6616,24 +6879,27 @@
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="111" s="1" customFormat="1" spans="2:12">
+        <v>488</v>
+      </c>
+      <c r="M110" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" spans="2:13">
       <c r="B111" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D111" s="5">
         <v>0.1</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="G111" s="5">
         <v>625</v>
@@ -6642,31 +6908,34 @@
         <v>312</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="J111" s="5"/>
       <c r="K111" s="5">
         <v>0</v>
       </c>
       <c r="L111" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="112" s="1" customFormat="1" spans="2:12">
+        <v>493</v>
+      </c>
+      <c r="M111" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" spans="2:13">
       <c r="B112" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D112" s="5">
         <v>0.1</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G112" s="5">
         <v>395</v>
@@ -6675,30 +6944,33 @@
         <v>197</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K112" s="5">
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>495</v>
+        <v>498</v>
+      </c>
+      <c r="M112" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" spans="2:13">
       <c r="B113" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D113" s="5">
         <v>0.1</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G113" s="5">
         <v>405</v>
@@ -6707,30 +6979,33 @@
         <v>202</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K113" s="5">
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>500</v>
+        <v>503</v>
+      </c>
+      <c r="M113" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" spans="2:13">
       <c r="B114" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D114" s="5">
         <v>0.1</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="G114" s="5">
         <v>480</v>
@@ -6739,7 +7014,7 @@
         <v>240</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="J114" s="5">
         <v>11004</v>
@@ -6748,25 +7023,27 @@
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>505</v>
-      </c>
-      <c r="M114"/>
+        <v>508</v>
+      </c>
+      <c r="M114" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="115" s="1" customFormat="1" spans="2:13">
       <c r="B115" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D115" s="5">
         <v>0.1</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G115" s="5">
         <v>520</v>
@@ -6775,32 +7052,34 @@
         <v>260</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="J115" s="5"/>
       <c r="K115" s="5">
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>510</v>
-      </c>
-      <c r="M115"/>
+        <v>513</v>
+      </c>
+      <c r="M115" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="116" s="1" customFormat="1" spans="2:13">
       <c r="B116" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D116" s="5">
         <v>0.1</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="G116" s="5">
         <v>350</v>
@@ -6809,7 +7088,7 @@
         <v>175</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="J116" s="5">
         <v>10602</v>
@@ -6818,25 +7097,27 @@
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>515</v>
-      </c>
-      <c r="M116"/>
+        <v>518</v>
+      </c>
+      <c r="M116" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="117" s="1" customFormat="1" spans="2:13">
       <c r="B117" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D117" s="5">
         <v>0.1</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="G117" s="5">
         <v>395</v>
@@ -6845,32 +7126,34 @@
         <v>197</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J117" s="5"/>
       <c r="K117" s="5">
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>520</v>
-      </c>
-      <c r="M117"/>
+        <v>523</v>
+      </c>
+      <c r="M117" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="118" s="1" customFormat="1" spans="2:13">
       <c r="B118" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D118" s="5">
         <v>0.1</v>
       </c>
       <c r="E118" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="G118" s="5">
         <v>625</v>
@@ -6879,32 +7162,34 @@
         <v>312</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J118" s="5"/>
       <c r="K118" s="5">
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>525</v>
-      </c>
-      <c r="M118"/>
+        <v>528</v>
+      </c>
+      <c r="M118" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="119" s="1" customFormat="1" spans="2:13">
       <c r="B119" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D119" s="5">
         <v>0.1</v>
       </c>
       <c r="E119" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="G119" s="5">
         <v>395</v>
@@ -6922,25 +7207,27 @@
         <v>0</v>
       </c>
       <c r="L119" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="M119"/>
+        <v>532</v>
+      </c>
+      <c r="M119" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="120" s="1" customFormat="1" spans="2:13">
       <c r="B120" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D120" s="5">
         <v>0.1</v>
       </c>
       <c r="E120" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="G120" s="5">
         <v>405</v>
@@ -6956,25 +7243,27 @@
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>533</v>
-      </c>
-      <c r="M120"/>
+        <v>536</v>
+      </c>
+      <c r="M120" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="121" s="1" customFormat="1" spans="2:13">
       <c r="B121" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D121" s="5">
         <v>0.1</v>
       </c>
       <c r="E121" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="G121" s="5">
         <v>565</v>
@@ -6992,25 +7281,27 @@
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>537</v>
-      </c>
-      <c r="M121"/>
+        <v>540</v>
+      </c>
+      <c r="M121" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="122" s="1" customFormat="1" spans="2:13">
       <c r="B122" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D122" s="5">
         <v>0.1</v>
       </c>
       <c r="E122" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G122" s="5">
         <v>405</v>
@@ -7026,25 +7317,27 @@
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>541</v>
-      </c>
-      <c r="M122"/>
+        <v>544</v>
+      </c>
+      <c r="M122" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="123" s="1" customFormat="1" spans="2:13">
       <c r="B123" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D123" s="5">
         <v>0.1</v>
       </c>
       <c r="E123" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="G123" s="5">
         <v>635</v>
@@ -7060,25 +7353,27 @@
         <v>0</v>
       </c>
       <c r="L123" t="s">
-        <v>545</v>
-      </c>
-      <c r="M123"/>
+        <v>548</v>
+      </c>
+      <c r="M123" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="2:13">
       <c r="B124" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D124" s="5">
         <v>0.1</v>
       </c>
       <c r="E124" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G124" s="5">
         <v>420</v>
@@ -7087,7 +7382,7 @@
         <v>210</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J124" s="5">
         <v>11201</v>
@@ -7096,25 +7391,27 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>550</v>
-      </c>
-      <c r="M124"/>
+        <v>553</v>
+      </c>
+      <c r="M124" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="125" s="1" customFormat="1" spans="2:13">
       <c r="B125" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D125" s="5">
         <v>0.1</v>
       </c>
       <c r="E125" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="G125" s="5">
         <v>420</v>
@@ -7132,25 +7429,27 @@
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>554</v>
-      </c>
-      <c r="M125"/>
+        <v>557</v>
+      </c>
+      <c r="M125" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="126" s="1" customFormat="1" spans="2:13">
       <c r="B126" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D126" s="5">
         <v>0.1</v>
       </c>
       <c r="E126" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G126" s="5">
         <v>585</v>
@@ -7168,25 +7467,27 @@
         <v>0</v>
       </c>
       <c r="L126" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="M126"/>
+        <v>561</v>
+      </c>
+      <c r="M126" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="127" s="1" customFormat="1" spans="2:13">
       <c r="B127" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C127" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D127" s="5">
         <v>0.1</v>
       </c>
       <c r="E127" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F127" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="G127" s="5">
         <v>480</v>
@@ -7204,25 +7505,27 @@
         <v>1</v>
       </c>
       <c r="L127" t="s">
-        <v>562</v>
-      </c>
-      <c r="M127"/>
+        <v>565</v>
+      </c>
+      <c r="M127" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="128" s="1" customFormat="1" spans="2:13">
       <c r="B128" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C128" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D128" s="5">
         <v>0.1</v>
       </c>
       <c r="E128" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="F128" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="G128" s="5">
         <v>430</v>
@@ -7238,25 +7541,27 @@
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>566</v>
-      </c>
-      <c r="M128"/>
+        <v>569</v>
+      </c>
+      <c r="M128" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="129" s="1" customFormat="1" spans="1:13">
       <c r="B129" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C129" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D129" s="5">
         <v>0.1</v>
       </c>
       <c r="E129" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F129" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="G129" s="5">
         <v>380</v>
@@ -7272,25 +7577,27 @@
         <v>2</v>
       </c>
       <c r="L129" t="s">
-        <v>570</v>
-      </c>
-      <c r="M129"/>
+        <v>573</v>
+      </c>
+      <c r="M129" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="130" s="1" customFormat="1" spans="1:13">
       <c r="B130" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C130" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D130" s="5">
         <v>0.1</v>
       </c>
       <c r="E130" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="F130" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G130" s="5">
         <v>385</v>
@@ -7306,25 +7613,27 @@
         <v>2</v>
       </c>
       <c r="L130" t="s">
-        <v>574</v>
-      </c>
-      <c r="M130"/>
+        <v>577</v>
+      </c>
+      <c r="M130" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="131" s="1" customFormat="1" spans="1:13">
       <c r="B131" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C131" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D131" s="5">
         <v>0.1</v>
       </c>
       <c r="E131" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F131" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="G131" s="5">
         <v>395</v>
@@ -7342,26 +7651,28 @@
         <v>0</v>
       </c>
       <c r="L131" t="s">
-        <v>578</v>
-      </c>
-      <c r="M131"/>
+        <v>581</v>
+      </c>
+      <c r="M131" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="132" s="1" customFormat="1" spans="1:13">
       <c r="A132"/>
       <c r="B132" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C132" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D132" s="5">
         <v>0.1</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="G132" s="1">
         <v>420</v>
@@ -7377,25 +7688,27 @@
         <v>0</v>
       </c>
       <c r="L132" t="s">
-        <v>582</v>
-      </c>
-      <c r="M132"/>
+        <v>585</v>
+      </c>
+      <c r="M132" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="133" s="1" customFormat="1" spans="1:13">
       <c r="B133" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C133" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D133" s="5">
         <v>0.1</v>
       </c>
       <c r="E133" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="G133" s="5">
         <v>550</v>
@@ -7404,30 +7717,33 @@
         <v>275</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="K133" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L133" t="s">
-        <v>588</v>
+        <v>591</v>
+      </c>
+      <c r="M133" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" spans="1:13">
       <c r="B134" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C134" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D134" s="5">
         <v>0.1</v>
       </c>
       <c r="E134" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="G134" s="5">
         <v>550</v>
@@ -7436,30 +7752,33 @@
         <v>275</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L134" t="s">
-        <v>593</v>
+        <v>596</v>
+      </c>
+      <c r="M134" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:13">
       <c r="B135" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C135" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D135" s="5">
         <v>0.1</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="G135" s="5">
         <v>550</v>
@@ -7468,31 +7787,34 @@
         <v>275</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5">
         <v>0</v>
       </c>
       <c r="L135" t="s">
-        <v>598</v>
+        <v>601</v>
+      </c>
+      <c r="M135" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="136" s="3" customFormat="1" spans="1:13">
       <c r="B136" s="3" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D136" s="9">
         <v>0.1</v>
       </c>
       <c r="E136" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="G136" s="9">
         <v>395</v>
@@ -7501,32 +7823,34 @@
         <v>197</v>
       </c>
       <c r="I136" s="9" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="J136" s="9"/>
       <c r="K136" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L136" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="M136" s="8"/>
+        <v>606</v>
+      </c>
+      <c r="M136" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="137" s="3" customFormat="1" spans="1:13">
       <c r="B137" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D137" s="9">
         <v>0.1</v>
       </c>
       <c r="E137" s="8" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="G137" s="9">
         <v>480</v>
@@ -7535,32 +7859,34 @@
         <v>240</v>
       </c>
       <c r="I137" s="9" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="J137" s="9"/>
       <c r="K137" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L137" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="M137" s="8"/>
+        <v>611</v>
+      </c>
+      <c r="M137" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="138" s="3" customFormat="1" spans="1:13">
       <c r="B138" s="3" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D138" s="9">
         <v>0.1</v>
       </c>
       <c r="E138" s="8" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="G138" s="9">
         <v>480</v>
@@ -7569,32 +7895,34 @@
         <v>240</v>
       </c>
       <c r="I138" s="9" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J138" s="9"/>
       <c r="K138" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L138" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="M138" s="8"/>
+        <v>616</v>
+      </c>
+      <c r="M138" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="139" s="3" customFormat="1" spans="1:13">
       <c r="B139" s="3" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D139" s="9">
         <v>0.1</v>
       </c>
       <c r="E139" s="8" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G139" s="9">
         <v>480</v>
@@ -7603,32 +7931,34 @@
         <v>240</v>
       </c>
       <c r="I139" s="9" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="J139" s="9"/>
       <c r="K139" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L139" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="M139" s="8"/>
+        <v>621</v>
+      </c>
+      <c r="M139" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="140" s="3" customFormat="1" spans="1:13">
       <c r="B140" s="3" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D140" s="9">
         <v>0.1</v>
       </c>
       <c r="E140" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="G140" s="9">
         <v>480</v>
@@ -7637,32 +7967,34 @@
         <v>240</v>
       </c>
       <c r="I140" s="9" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="J140" s="9"/>
       <c r="K140" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L140" s="8" t="s">
-        <v>623</v>
-      </c>
-      <c r="M140" s="8"/>
+        <v>626</v>
+      </c>
+      <c r="M140" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="141" s="3" customFormat="1" spans="1:13">
       <c r="B141" s="3" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D141" s="9">
         <v>0.1</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F141" s="9" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="G141" s="9">
         <v>445</v>
@@ -7671,32 +8003,34 @@
         <v>222</v>
       </c>
       <c r="I141" s="9" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="J141" s="9"/>
       <c r="K141" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L141" s="8" t="s">
-        <v>628</v>
-      </c>
-      <c r="M141" s="8"/>
+        <v>631</v>
+      </c>
+      <c r="M141" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="142" s="3" customFormat="1" spans="1:13">
       <c r="B142" s="3" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D142" s="9">
         <v>0.1</v>
       </c>
       <c r="E142" s="8" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="G142" s="9">
         <v>480</v>
@@ -7705,16 +8039,18 @@
         <v>240</v>
       </c>
       <c r="I142" s="9" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="J142" s="9"/>
       <c r="K142" s="3" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L142" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="M142" s="8"/>
+        <v>636</v>
+      </c>
+      <c r="M142" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="143" s="1" customFormat="1" spans="1:13">
       <c r="D143" s="5"/>

--- a/Config/RelicConfig.xlsx
+++ b/Config/RelicConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="25080" windowHeight="10920"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="639">
   <si>
     <t>##var</t>
   </si>
@@ -61,6 +61,9 @@
     <t>MechanismId</t>
   </si>
   <si>
+    <t>BindingID</t>
+  </si>
+  <si>
     <t>UnlockConditionId</t>
   </si>
   <si>
@@ -110,6 +113,9 @@
   </si>
   <si>
     <t>机制ID</t>
+  </si>
+  <si>
+    <t>羁绊ID</t>
   </si>
   <si>
     <t>解锁条件ID</t>
@@ -2947,7 +2953,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:N147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
@@ -2959,14 +2965,15 @@
     <col min="7" max="7" width="5.975" style="5" customWidth="1"/>
     <col min="8" max="8" width="4.78333333333333" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.38333333333333" style="5" customWidth="1"/>
-    <col min="10" max="10" width="5.53333333333333" style="5" customWidth="1"/>
-    <col min="11" max="11" width="8.03333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="7.70833333333333" style="5" customWidth="1"/>
-    <col min="14" max="14" width="34.75" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1083333333333" style="5" customWidth="1"/>
+    <col min="11" max="11" width="17.7166666666667" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.03333333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.70833333333333" style="5" customWidth="1"/>
+    <col min="15" max="15" width="34.75" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3003,107 +3010,116 @@
       <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:13">
+      <c r="M3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:14">
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5">
         <v>0.8</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" s="5">
         <v>45</v>
@@ -3114,32 +3130,35 @@
       <c r="I5" s="5">
         <v>10001</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
+      <c r="J5" s="5">
+        <v>101</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5">
+        <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:13">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:14">
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" s="5">
         <v>0.8</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5">
         <v>28</v>
@@ -3151,31 +3170,32 @@
         <v>10002</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" t="s">
-        <v>39</v>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5">
+        <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:13">
+        <v>41</v>
+      </c>
+      <c r="N6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:14">
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="5">
         <v>0.8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G7" s="5">
         <v>28</v>
@@ -3187,31 +3207,32 @@
         <v>10003</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>43</v>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5">
+        <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:13">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:14">
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="5">
         <v>0.8</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8" s="5">
         <v>28</v>
@@ -3223,31 +3244,32 @@
         <v>10004</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="5">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>47</v>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5">
+        <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:13">
+        <v>49</v>
+      </c>
+      <c r="N8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:14">
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5">
         <v>0.8</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" s="5">
         <v>28</v>
@@ -3259,31 +3281,32 @@
         <v>10005</v>
       </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>51</v>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5">
+        <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:13">
+        <v>53</v>
+      </c>
+      <c r="N9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:14">
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="5">
         <v>0.8</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10" s="5">
         <v>28</v>
@@ -3295,31 +3318,32 @@
         <v>10006</v>
       </c>
       <c r="J10" s="5"/>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>55</v>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5">
+        <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:13">
+        <v>57</v>
+      </c>
+      <c r="N10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:14">
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5">
         <v>0.8</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11" s="5">
         <v>22</v>
@@ -3331,31 +3355,32 @@
         <v>10007</v>
       </c>
       <c r="J11" s="5"/>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" t="s">
-        <v>59</v>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5">
+        <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:13">
+        <v>61</v>
+      </c>
+      <c r="N11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:14">
       <c r="B12" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" s="5">
         <v>0.8</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G12" s="5">
         <v>35</v>
@@ -3367,31 +3392,32 @@
         <v>10008</v>
       </c>
       <c r="J12" s="5"/>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>63</v>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5">
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:13">
+        <v>65</v>
+      </c>
+      <c r="N12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:14">
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" s="5">
         <v>0.8</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G13" s="5">
         <v>16</v>
@@ -3403,31 +3429,32 @@
         <v>10009</v>
       </c>
       <c r="J13" s="5"/>
-      <c r="K13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>67</v>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5">
+        <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:13">
+        <v>69</v>
+      </c>
+      <c r="N13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:14">
       <c r="B14" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" s="5">
         <v>0.8</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" s="5">
         <v>16</v>
@@ -3439,31 +3466,32 @@
         <v>10010</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="5">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>71</v>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5">
+        <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:13">
+        <v>73</v>
+      </c>
+      <c r="N14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:14">
       <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="5">
         <v>0.8</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="5">
         <v>15</v>
@@ -3475,31 +3503,32 @@
         <v>10011</v>
       </c>
       <c r="J15" s="5"/>
-      <c r="K15" s="5">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>75</v>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5">
+        <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:13">
+        <v>77</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:14">
       <c r="B16" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" s="5">
         <v>0.8</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G16" s="5">
         <v>30</v>
@@ -3511,31 +3540,32 @@
         <v>10012</v>
       </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="5">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>79</v>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5">
+        <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:13">
+        <v>81</v>
+      </c>
+      <c r="N16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:14">
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D17" s="5">
         <v>0.8</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G17" s="5">
         <v>35</v>
@@ -3547,31 +3577,32 @@
         <v>10013</v>
       </c>
       <c r="J17" s="5"/>
-      <c r="K17" s="5">
-        <v>0</v>
-      </c>
-      <c r="L17" t="s">
-        <v>83</v>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5">
+        <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:13">
+        <v>85</v>
+      </c>
+      <c r="N17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:14">
       <c r="B18" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" s="5">
         <v>0.8</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G18" s="5">
         <v>26</v>
@@ -3583,31 +3614,32 @@
         <v>10014</v>
       </c>
       <c r="J18" s="5"/>
-      <c r="K18" s="5">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>87</v>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5">
+        <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:13">
+        <v>89</v>
+      </c>
+      <c r="N18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:14">
       <c r="B19" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" s="5">
         <v>0.8</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G19" s="5">
         <v>22</v>
@@ -3619,31 +3651,32 @@
         <v>10015</v>
       </c>
       <c r="J19" s="5"/>
-      <c r="K19" s="5">
-        <v>0</v>
-      </c>
-      <c r="L19" t="s">
-        <v>91</v>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5">
+        <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:13">
+        <v>93</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:14">
       <c r="B20" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" s="5">
         <v>0.8</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G20" s="5">
         <v>28</v>
@@ -3655,31 +3688,32 @@
         <v>10016</v>
       </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="5">
-        <v>0</v>
-      </c>
-      <c r="L20" t="s">
-        <v>95</v>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5">
+        <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:13">
+        <v>97</v>
+      </c>
+      <c r="N20" t="s">
+        <v>37</v>
+      <